--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="1779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="1780">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,16 +50,16 @@
     <t xml:space="preserve">8.3010368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.437424659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48081970214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61720752716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80319023132324</t>
+    <t xml:space="preserve">8.43742370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48082160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61720657348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80319118499756</t>
   </si>
   <si>
     <t xml:space="preserve">8.68540000915527</t>
@@ -68,85 +68,85 @@
     <t xml:space="preserve">8.30723667144775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35063362121582</t>
+    <t xml:space="preserve">8.3506326675415</t>
   </si>
   <si>
     <t xml:space="preserve">8.20804500579834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.916672706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97246646881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13985157012939</t>
+    <t xml:space="preserve">7.91667222976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97246599197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13985061645508</t>
   </si>
   <si>
     <t xml:space="preserve">8.15225028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2762393951416</t>
+    <t xml:space="preserve">8.27623844146729</t>
   </si>
   <si>
     <t xml:space="preserve">8.3878288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49321937561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50561809539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39402770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36923122406006</t>
+    <t xml:space="preserve">8.49321842193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50561904907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39402866363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36923027038574</t>
   </si>
   <si>
     <t xml:space="preserve">8.33203315734863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99106502532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5943021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45791387557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31532716751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46411371231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66869401931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63149929046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65629625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65009689331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44551563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60050058364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68109369277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55090618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68729305267334</t>
+    <t xml:space="preserve">7.99106645584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59430170059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45791435241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31532764434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46411418914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66869449615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63149881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6562967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65009737014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44551658630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.600501537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68109464645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55090665817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6872935295105</t>
   </si>
   <si>
     <t xml:space="preserve">7.6067008972168</t>
@@ -155,25 +155,25 @@
     <t xml:space="preserve">7.73688840866089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64389801025391</t>
+    <t xml:space="preserve">7.64389753341675</t>
   </si>
   <si>
     <t xml:space="preserve">7.57570362091064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53230762481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0158634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38162899017334</t>
+    <t xml:space="preserve">7.53230810165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01586437225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38162994384766</t>
   </si>
   <si>
     <t xml:space="preserve">8.67920303344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77219295501709</t>
+    <t xml:space="preserve">8.77219390869141</t>
   </si>
   <si>
     <t xml:space="preserve">8.76599311828613</t>
@@ -182,55 +182,55 @@
     <t xml:space="preserve">8.83418750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78459358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46842098236084</t>
+    <t xml:space="preserve">8.784592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46842193603516</t>
   </si>
   <si>
     <t xml:space="preserve">8.41882514953613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33823299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45602321624756</t>
+    <t xml:space="preserve">8.33823204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45602130889893</t>
   </si>
   <si>
     <t xml:space="preserve">8.49941825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58621120452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43122577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40642738342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34443283081055</t>
+    <t xml:space="preserve">8.58621025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43122386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40642642974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">8.47462177276611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24524211883545</t>
+    <t xml:space="preserve">8.24524307250977</t>
   </si>
   <si>
     <t xml:space="preserve">7.90427398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87327575683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73068904876709</t>
+    <t xml:space="preserve">7.8732762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73068809509277</t>
   </si>
   <si>
     <t xml:space="preserve">7.79268360137939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85467767715454</t>
+    <t xml:space="preserve">7.85467863082886</t>
   </si>
   <si>
     <t xml:space="preserve">7.89807367324829</t>
@@ -239,52 +239,52 @@
     <t xml:space="preserve">7.96006870269775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04685974121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99726533889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96626710891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86707544326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78028631210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.090256690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11505317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17704772949219</t>
+    <t xml:space="preserve">8.04685878753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99726390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96626758575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86707592010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78028535842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1150541305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1770486831665</t>
   </si>
   <si>
     <t xml:space="preserve">8.02206230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88567447662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82987976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0406608581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00966262817383</t>
+    <t xml:space="preserve">7.88567543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8298807144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04066181182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00966358184814</t>
   </si>
   <si>
     <t xml:space="preserve">8.09645652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19564533233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23284435272217</t>
+    <t xml:space="preserve">8.19564628601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23284244537354</t>
   </si>
   <si>
     <t xml:space="preserve">8.18324661254883</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">8.05925846099854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76168632507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5261082649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56330490112305</t>
+    <t xml:space="preserve">7.7616868019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52610874176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56330442428589</t>
   </si>
   <si>
     <t xml:space="preserve">7.42071771621704</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">7.19133901596069</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85656976699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96815919876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9743595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12314510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09073734283447</t>
+    <t xml:space="preserve">6.85656881332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96815872192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97435903549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12314558029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09073781967163</t>
   </si>
   <si>
     <t xml:space="preserve">7.05184888839722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14258909225464</t>
+    <t xml:space="preserve">7.14259052276611</t>
   </si>
   <si>
     <t xml:space="preserve">7.05833005905151</t>
@@ -338,22 +338,22 @@
     <t xml:space="preserve">6.37777519226074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49444246292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61110734939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08425617218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99999761581421</t>
+    <t xml:space="preserve">6.49444198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61110830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08425521850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99999666213989</t>
   </si>
   <si>
     <t xml:space="preserve">7.03888559341431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93518304824829</t>
+    <t xml:space="preserve">6.93518161773682</t>
   </si>
   <si>
     <t xml:space="preserve">6.78610754013062</t>
@@ -362,130 +362,130 @@
     <t xml:space="preserve">6.75370025634766</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82499742507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86388635635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74073791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91573762893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89629459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15555286407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907217025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58332872390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55740451812744</t>
+    <t xml:space="preserve">6.82499647140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86388540267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74073696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91573810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92870140075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89629411697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15555191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58332920074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55740356445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.0694408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0435152053833</t>
+    <t xml:space="preserve">8.04351329803467</t>
   </si>
   <si>
     <t xml:space="preserve">8.01110744476318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16666316986084</t>
+    <t xml:space="preserve">8.16666412353516</t>
   </si>
   <si>
     <t xml:space="preserve">8.17962646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0759220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05647754669189</t>
+    <t xml:space="preserve">8.07592296600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05647945404053</t>
   </si>
   <si>
     <t xml:space="preserve">8.10184764862061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95277404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82962656021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87499809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90740442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481246948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75832986831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74536609649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77129316329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71944189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57684993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65462779998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7064790725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81666374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79073762893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69351434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72592258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69999647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50555229187012</t>
+    <t xml:space="preserve">7.95277452468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82962560653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87499713897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90740394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481199264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75833034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74536752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77129220962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71944141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57684803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65462636947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70647859573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81666469573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79073810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69351530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72592163085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69999694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50555181503296</t>
   </si>
   <si>
     <t xml:space="preserve">7.37592267990112</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39536571502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47314405441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32407093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25277376174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22684812545776</t>
+    <t xml:space="preserve">7.39536666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47314548492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32407140731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25277519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22684907913208</t>
   </si>
   <si>
     <t xml:space="preserve">7.18147802352905</t>
@@ -494,169 +494,169 @@
     <t xml:space="preserve">7.20092248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22036647796631</t>
+    <t xml:space="preserve">7.22036838531494</t>
   </si>
   <si>
     <t xml:space="preserve">7.18796014785767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1685152053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16203308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19444274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17499685287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07129240036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96758985519409</t>
+    <t xml:space="preserve">7.16851615905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.162034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19444179534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17499732971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07129383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96758794784546</t>
   </si>
   <si>
     <t xml:space="preserve">7.04536771774292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98703384399414</t>
+    <t xml:space="preserve">6.98703336715698</t>
   </si>
   <si>
     <t xml:space="preserve">7.23333072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34999704360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41481065750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55092191696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52499532699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64166307449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59629249572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61573791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64814567565918</t>
+    <t xml:space="preserve">7.34999656677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41481161117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55092144012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52499723434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64166259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59629344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6157374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64814424514771</t>
   </si>
   <si>
     <t xml:space="preserve">7.49258995056152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38888597488403</t>
+    <t xml:space="preserve">7.38888549804688</t>
   </si>
   <si>
     <t xml:space="preserve">7.46018171310425</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36944007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30462598800659</t>
+    <t xml:space="preserve">7.36944103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30462646484375</t>
   </si>
   <si>
     <t xml:space="preserve">6.84444189071655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57222032546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59166479110718</t>
+    <t xml:space="preserve">6.57221937179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59166431427002</t>
   </si>
   <si>
     <t xml:space="preserve">6.54629325866699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48147821426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43610906600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47823762893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52684831619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64999723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5333309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59814500808716</t>
+    <t xml:space="preserve">6.48147916793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43610858917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47823905944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52684879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64999675750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53332996368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59814548492432</t>
   </si>
   <si>
     <t xml:space="preserve">6.52036809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42962694168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87036800384521</t>
+    <t xml:space="preserve">6.42962741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8703670501709</t>
   </si>
   <si>
     <t xml:space="preserve">7.10370111465454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25925636291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48610734939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4342565536499</t>
+    <t xml:space="preserve">7.25925588607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48610830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43425559997559</t>
   </si>
   <si>
     <t xml:space="preserve">7.42777395248413</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38240480422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51851654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51203489303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66758918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68055200576782</t>
+    <t xml:space="preserve">7.38240385055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851511001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51203393936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66758966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68055152893066</t>
   </si>
   <si>
     <t xml:space="preserve">7.71295976638794</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89444065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79721879959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84258937835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34351587295532</t>
+    <t xml:space="preserve">7.8944411277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79721784591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84259128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34351539611816</t>
   </si>
   <si>
     <t xml:space="preserve">7.40184879302979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46666479110718</t>
+    <t xml:space="preserve">7.46666383743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.4083309173584</t>
@@ -668,52 +668,52 @@
     <t xml:space="preserve">7.68703460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62222051620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63518047332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73240423202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77777433395386</t>
+    <t xml:space="preserve">7.62221813201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63518142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7324047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77777481079102</t>
   </si>
   <si>
     <t xml:space="preserve">7.83610820770264</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75184869766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62869930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97221851348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85555267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92684698104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03703308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09536743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13425731658936</t>
+    <t xml:space="preserve">7.7518482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62870121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97221803665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85555124282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92684841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03703212738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09536552429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13425636291504</t>
   </si>
   <si>
     <t xml:space="preserve">8.20555210113525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28981113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24444103240967</t>
+    <t xml:space="preserve">8.2898120880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24444198608398</t>
   </si>
   <si>
     <t xml:space="preserve">8.23147869110107</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">8.46481132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45832920074463</t>
+    <t xml:space="preserve">8.45833110809326</t>
   </si>
   <si>
     <t xml:space="preserve">8.43240451812744</t>
@@ -737,37 +737,37 @@
     <t xml:space="preserve">8.42592144012451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35462474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55555248260498</t>
+    <t xml:space="preserve">8.3546257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55555152893066</t>
   </si>
   <si>
     <t xml:space="preserve">8.52314376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39351558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47129154205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6074047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61388397216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62036609649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56203460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80832958221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6786994934082</t>
+    <t xml:space="preserve">8.39351367950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47129249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60740375518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61388492584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62036800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56203269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80833053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67870044708252</t>
   </si>
   <si>
     <t xml:space="preserve">8.81481170654297</t>
@@ -782,28 +782,28 @@
     <t xml:space="preserve">9.12592124938965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17777442932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00277423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9509220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9962911605835</t>
+    <t xml:space="preserve">9.17777347564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00277328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95092105865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99629211425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.18425559997559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01573657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02869987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20370006561279</t>
+    <t xml:space="preserve">9.01573753356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02869892120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20369911193848</t>
   </si>
   <si>
     <t xml:space="preserve">9.2814769744873</t>
@@ -812,13 +812,13 @@
     <t xml:space="preserve">9.30740356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34629344940186</t>
+    <t xml:space="preserve">9.34629249572754</t>
   </si>
   <si>
     <t xml:space="preserve">9.43703365325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32684803009033</t>
+    <t xml:space="preserve">9.32684707641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.43055152893066</t>
@@ -836,25 +836,25 @@
     <t xml:space="preserve">9.5018482208252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50832843780518</t>
+    <t xml:space="preserve">9.50832939147949</t>
   </si>
   <si>
     <t xml:space="preserve">9.44351387023926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54721832275391</t>
+    <t xml:space="preserve">9.54721736907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.41110706329346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35925388336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51501750946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41343402862549</t>
+    <t xml:space="preserve">9.35925483703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51501560211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41343212127686</t>
   </si>
   <si>
     <t xml:space="preserve">9.59628391265869</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">9.44729328155518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48115539550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21026515960693</t>
+    <t xml:space="preserve">9.48115730285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21026611328125</t>
   </si>
   <si>
     <t xml:space="preserve">9.09513759613037</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">9.14931583404541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98678207397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83101940155029</t>
+    <t xml:space="preserve">8.98678112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83101844787598</t>
   </si>
   <si>
     <t xml:space="preserve">8.84456348419189</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">8.81070327758789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93260288238525</t>
+    <t xml:space="preserve">8.93260383605957</t>
   </si>
   <si>
     <t xml:space="preserve">9.04096031188965</t>
@@ -902,43 +902,43 @@
     <t xml:space="preserve">8.87165355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04773139953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08159351348877</t>
+    <t xml:space="preserve">9.04773044586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08159160614014</t>
   </si>
   <si>
     <t xml:space="preserve">9.10190963745117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10868072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12222671508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00709819793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07482051849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87842559814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92583179473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90551376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52626705169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58721828460693</t>
+    <t xml:space="preserve">9.20349407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10868167877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12222576141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00709915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07481956481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87842464447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92583084106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90551280975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52626800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58721733093262</t>
   </si>
   <si>
     <t xml:space="preserve">8.54658508300781</t>
@@ -947,25 +947,25 @@
     <t xml:space="preserve">8.56012916564941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68880081176758</t>
+    <t xml:space="preserve">8.68880176544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.5398120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44500064849854</t>
+    <t xml:space="preserve">8.44499969482422</t>
   </si>
   <si>
     <t xml:space="preserve">8.33664512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47208976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47886180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41113948822021</t>
+    <t xml:space="preserve">8.47209072113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47886276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4111385345459</t>
   </si>
   <si>
     <t xml:space="preserve">8.42468357086182</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">8.3840503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39082336425781</t>
+    <t xml:space="preserve">8.3908224105835</t>
   </si>
   <si>
     <t xml:space="preserve">8.32987213134766</t>
@@ -989,58 +989,58 @@
     <t xml:space="preserve">8.24860572814941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19442653656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16733837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21474361419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37050533294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29601097106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39759540557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81747341156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97323513031006</t>
+    <t xml:space="preserve">8.19442939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16733932495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21474456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37050628662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29601192474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81747531890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97323703765869</t>
   </si>
   <si>
     <t xml:space="preserve">8.76329612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67525672912598</t>
+    <t xml:space="preserve">8.67525863647461</t>
   </si>
   <si>
     <t xml:space="preserve">8.68202972412109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69557476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80392932891846</t>
+    <t xml:space="preserve">8.6955738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80393028259277</t>
   </si>
   <si>
     <t xml:space="preserve">8.8581075668335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74298000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74975204467773</t>
+    <t xml:space="preserve">8.74297904968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74975299835205</t>
   </si>
   <si>
     <t xml:space="preserve">8.79038524627686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88519668579102</t>
+    <t xml:space="preserve">8.88519763946533</t>
   </si>
   <si>
     <t xml:space="preserve">8.96646404266357</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">8.91228580474854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89196968078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18317699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19672012329102</t>
+    <t xml:space="preserve">8.89196872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1831750869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19672107696533</t>
   </si>
   <si>
     <t xml:space="preserve">9.29153251647949</t>
@@ -1064,28 +1064,28 @@
     <t xml:space="preserve">9.24412631988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36602783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40666007995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54210567474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46761035919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38634490966797</t>
+    <t xml:space="preserve">9.36602687835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40666103363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54210662841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46761131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38634395599365</t>
   </si>
   <si>
     <t xml:space="preserve">9.52178955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49469947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84008598327637</t>
+    <t xml:space="preserve">9.49470043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84008407592773</t>
   </si>
   <si>
     <t xml:space="preserve">9.86717319488525</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">9.74527359008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70463943481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58273983001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71818447113037</t>
+    <t xml:space="preserve">9.70464038848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58273887634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71818351745605</t>
   </si>
   <si>
     <t xml:space="preserve">9.67077827453613</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">9.96875858306885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94844055175781</t>
+    <t xml:space="preserve">9.94844150543213</t>
   </si>
   <si>
     <t xml:space="preserve">9.91458034515381</t>
@@ -1127,43 +1127,43 @@
     <t xml:space="preserve">10.0161638259888</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96198654174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92135047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90103626251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2599649429321</t>
+    <t xml:space="preserve">9.96198558807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92135143280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90103530883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2599639892578</t>
   </si>
   <si>
     <t xml:space="preserve">11.4451084136963</t>
   </si>
   <si>
-    <t xml:space="preserve">11.567008972168</t>
+    <t xml:space="preserve">11.5670108795166</t>
   </si>
   <si>
     <t xml:space="preserve">11.4857416152954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5128326416016</t>
+    <t xml:space="preserve">11.5128316879272</t>
   </si>
   <si>
     <t xml:space="preserve">11.4518823623657</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4383373260498</t>
+    <t xml:space="preserve">11.4383382797241</t>
   </si>
   <si>
     <t xml:space="preserve">11.4992876052856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3502969741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0726346969604</t>
+    <t xml:space="preserve">11.3502979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0726356506348</t>
   </si>
   <si>
     <t xml:space="preserve">10.9845952987671</t>
@@ -1178,28 +1178,28 @@
     <t xml:space="preserve">10.8152894973755</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5850315093994</t>
+    <t xml:space="preserve">10.585033416748</t>
   </si>
   <si>
     <t xml:space="preserve">10.4495887756348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5647163391113</t>
+    <t xml:space="preserve">10.5647172927856</t>
   </si>
   <si>
     <t xml:space="preserve">10.5443992614746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4292697906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4699029922485</t>
+    <t xml:space="preserve">10.429271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4699039459229</t>
   </si>
   <si>
     <t xml:space="preserve">10.632438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8220615386963</t>
+    <t xml:space="preserve">10.8220624923706</t>
   </si>
   <si>
     <t xml:space="preserve">10.9168739318848</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">10.9913682937622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8017454147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7204790115356</t>
+    <t xml:space="preserve">10.8017444610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7204780578613</t>
   </si>
   <si>
     <t xml:space="preserve">10.6256656646729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6730709075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8356056213379</t>
+    <t xml:space="preserve">10.6730718612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8356075286865</t>
   </si>
   <si>
     <t xml:space="preserve">10.9371900558472</t>
@@ -1232,40 +1232,40 @@
     <t xml:space="preserve">11.0455465316772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1268148422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9304180145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.842378616333</t>
+    <t xml:space="preserve">11.1268129348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9304161071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8423795700073</t>
   </si>
   <si>
     <t xml:space="preserve">10.7746562957764</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7340221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5918054580688</t>
+    <t xml:space="preserve">10.7340230941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5918045043945</t>
   </si>
   <si>
     <t xml:space="preserve">10.5376272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5173110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3615484237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.097430229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87394714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1922426223755</t>
+    <t xml:space="preserve">10.5173101425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3615493774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0974311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87394618988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1922416687012</t>
   </si>
   <si>
     <t xml:space="preserve">9.92812442779541</t>
@@ -1274,19 +1274,19 @@
     <t xml:space="preserve">10.0364799499512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0567979812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1245203018188</t>
+    <t xml:space="preserve">10.0567970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1245183944702</t>
   </si>
   <si>
     <t xml:space="preserve">10.0838861465454</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97553062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69786739349365</t>
+    <t xml:space="preserve">9.97552967071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69786643981934</t>
   </si>
   <si>
     <t xml:space="preserve">9.50824451446533</t>
@@ -1295,34 +1295,34 @@
     <t xml:space="preserve">9.44052124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64368915557861</t>
+    <t xml:space="preserve">9.64369010925293</t>
   </si>
   <si>
     <t xml:space="preserve">9.66400623321533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67755126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083927154541</t>
+    <t xml:space="preserve">9.67755222320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083736419678</t>
   </si>
   <si>
     <t xml:space="preserve">9.55565071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34570980072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21703815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13576984405518</t>
+    <t xml:space="preserve">9.34571170806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21703720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13577079772949</t>
   </si>
   <si>
     <t xml:space="preserve">9.23058223724365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06804847717285</t>
+    <t xml:space="preserve">9.06804943084717</t>
   </si>
   <si>
     <t xml:space="preserve">9.17640399932861</t>
@@ -1331,43 +1331,43 @@
     <t xml:space="preserve">9.33216571807861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27798843383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23735523223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1628589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29830360412598</t>
+    <t xml:space="preserve">9.27798748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23735427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16286087036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29830455780029</t>
   </si>
   <si>
     <t xml:space="preserve">9.42697811126709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53533267974854</t>
+    <t xml:space="preserve">9.53533363342285</t>
   </si>
   <si>
     <t xml:space="preserve">9.62337303161621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79945182800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8062219619751</t>
+    <t xml:space="preserve">9.79945087432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80622291564941</t>
   </si>
   <si>
     <t xml:space="preserve">9.77236270904541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95521354675293</t>
+    <t xml:space="preserve">9.95521259307861</t>
   </si>
   <si>
     <t xml:space="preserve">9.81976795196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75881767272949</t>
+    <t xml:space="preserve">9.75881862640381</t>
   </si>
   <si>
     <t xml:space="preserve">9.47438335418701</t>
@@ -1376,58 +1376,58 @@
     <t xml:space="preserve">9.71141242980957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30507755279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01387023925781</t>
+    <t xml:space="preserve">9.30507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0138692855835</t>
   </si>
   <si>
     <t xml:space="preserve">8.79715824127197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03418827056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39311695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26281642913818</t>
+    <t xml:space="preserve">9.03418731689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39311504364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26281452178955</t>
   </si>
   <si>
     <t xml:space="preserve">9.29120635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24152088165283</t>
+    <t xml:space="preserve">9.24152183532715</t>
   </si>
   <si>
     <t xml:space="preserve">9.1137580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14924907684326</t>
+    <t xml:space="preserve">9.14924812316895</t>
   </si>
   <si>
     <t xml:space="preserve">9.05697441101074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07116889953613</t>
+    <t xml:space="preserve">9.07116985321045</t>
   </si>
   <si>
     <t xml:space="preserve">9.03568077087402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99309253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04277896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19183540344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27701091766357</t>
+    <t xml:space="preserve">8.99309349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04277801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02148532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19183444976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27700996398926</t>
   </si>
   <si>
     <t xml:space="preserve">9.39767551422119</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">9.2131290435791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10666084289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12795448303223</t>
+    <t xml:space="preserve">9.10665893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12795352935791</t>
   </si>
   <si>
     <t xml:space="preserve">9.22732448577881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26991271972656</t>
+    <t xml:space="preserve">9.26991367340088</t>
   </si>
   <si>
     <t xml:space="preserve">9.1208553314209</t>
@@ -1457,34 +1457,34 @@
     <t xml:space="preserve">9.38348007202148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44026374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41187191009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70288753509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56092834472656</t>
+    <t xml:space="preserve">9.44026279449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4118709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60351753234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7028865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56092929840088</t>
   </si>
   <si>
     <t xml:space="preserve">9.61771297454834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65320205688477</t>
+    <t xml:space="preserve">9.65320301055908</t>
   </si>
   <si>
     <t xml:space="preserve">9.6815938949585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57512378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66029930114746</t>
+    <t xml:space="preserve">9.57512474060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66030025482178</t>
   </si>
   <si>
     <t xml:space="preserve">9.53253650665283</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">9.45445919036865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5041446685791</t>
+    <t xml:space="preserve">9.50414562225342</t>
   </si>
   <si>
     <t xml:space="preserve">9.30540180206299</t>
@@ -1505,19 +1505,19 @@
     <t xml:space="preserve">9.28410816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24861907958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0924654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82274341583252</t>
+    <t xml:space="preserve">9.24861717224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09246444702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8227424621582</t>
   </si>
   <si>
     <t xml:space="preserve">8.71627330780029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68078327178955</t>
+    <t xml:space="preserve">8.68078231811523</t>
   </si>
   <si>
     <t xml:space="preserve">8.78725337982178</t>
@@ -1529,37 +1529,37 @@
     <t xml:space="preserve">9.01438617706299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14215087890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23442363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29830455780029</t>
+    <t xml:space="preserve">9.14214992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23442268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29830551147461</t>
   </si>
   <si>
     <t xml:space="preserve">9.39057636260986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42606830596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37638092041016</t>
+    <t xml:space="preserve">9.42606639862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37638187408447</t>
   </si>
   <si>
     <t xml:space="preserve">9.16344261169434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04987812042236</t>
+    <t xml:space="preserve">9.04987621307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.17054176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74466419219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69497871398926</t>
+    <t xml:space="preserve">8.74466514587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69497966766357</t>
   </si>
   <si>
     <t xml:space="preserve">8.51043319702148</t>
@@ -1571,34 +1571,34 @@
     <t xml:space="preserve">8.39686679840088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59560680389404</t>
+    <t xml:space="preserve">8.59560775756836</t>
   </si>
   <si>
     <t xml:space="preserve">8.49623775482178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26910209655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26200485229492</t>
+    <t xml:space="preserve">8.26910305023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26200580596924</t>
   </si>
   <si>
     <t xml:space="preserve">8.2265157699585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04196834564209</t>
+    <t xml:space="preserve">8.04196739196777</t>
   </si>
   <si>
     <t xml:space="preserve">8.06326293945312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07036018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9355001449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1484375</t>
+    <t xml:space="preserve">8.07036113739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93549919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14843845367432</t>
   </si>
   <si>
     <t xml:space="preserve">8.16263484954834</t>
@@ -1607,34 +1607,34 @@
     <t xml:space="preserve">8.2407112121582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28329944610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38267040252686</t>
+    <t xml:space="preserve">8.28329849243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38266944885254</t>
   </si>
   <si>
     <t xml:space="preserve">8.36137580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50333499908447</t>
+    <t xml:space="preserve">8.50333404541016</t>
   </si>
   <si>
     <t xml:space="preserve">8.42525768280029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15634632110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08536529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06407356262207</t>
+    <t xml:space="preserve">9.15634441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08536624908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06407260894775</t>
   </si>
   <si>
     <t xml:space="preserve">8.80854606628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81564426422119</t>
+    <t xml:space="preserve">8.81564521789551</t>
   </si>
   <si>
     <t xml:space="preserve">8.65948963165283</t>
@@ -1652,19 +1652,19 @@
     <t xml:space="preserve">8.52462959289551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5175313949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40396308898926</t>
+    <t xml:space="preserve">8.51753044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40396404266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.36847400665283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21231937408447</t>
+    <t xml:space="preserve">8.43945217132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21232032775879</t>
   </si>
   <si>
     <t xml:space="preserve">8.80144786834717</t>
@@ -1673,19 +1673,19 @@
     <t xml:space="preserve">8.60980415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34008121490479</t>
+    <t xml:space="preserve">8.3400821685791</t>
   </si>
   <si>
     <t xml:space="preserve">8.19812393188477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37557220458984</t>
+    <t xml:space="preserve">8.37557125091553</t>
   </si>
   <si>
     <t xml:space="preserve">8.46074676513672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62400054931641</t>
+    <t xml:space="preserve">8.62399864196777</t>
   </si>
   <si>
     <t xml:space="preserve">8.38976764678955</t>
@@ -1694,73 +1694,73 @@
     <t xml:space="preserve">8.5317268371582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68788146972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83693885803223</t>
+    <t xml:space="preserve">8.68788242340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83693790435791</t>
   </si>
   <si>
     <t xml:space="preserve">8.85823154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90791702270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25571823120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5112419128418</t>
+    <t xml:space="preserve">8.90791797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25571632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51124382019043</t>
   </si>
   <si>
     <t xml:space="preserve">9.58222198486328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47575378417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35508823394775</t>
+    <t xml:space="preserve">9.475754737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35508918762207</t>
   </si>
   <si>
     <t xml:space="preserve">9.54673194885254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66739749908447</t>
+    <t xml:space="preserve">9.66739845275879</t>
   </si>
   <si>
     <t xml:space="preserve">9.61061382293701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63190746307373</t>
+    <t xml:space="preserve">9.63190841674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.51834106445312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68869018554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90872764587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85904216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88033580780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75967121124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86614036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85194301605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0222949981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2423305511475</t>
+    <t xml:space="preserve">9.68869113922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90872859954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85904121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88033485412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75967025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86613941192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85194396972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0222930908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2423315048218</t>
   </si>
   <si>
     <t xml:space="preserve">10.3275060653687</t>
@@ -1772,10 +1772,10 @@
     <t xml:space="preserve">10.7604808807373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6398143768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6824035644531</t>
+    <t xml:space="preserve">10.6398153305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6824045181274</t>
   </si>
   <si>
     <t xml:space="preserve">10.6043252944946</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">10.7107963562012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6895017623901</t>
+    <t xml:space="preserve">10.6895008087158</t>
   </si>
   <si>
     <t xml:space="preserve">10.7746772766113</t>
@@ -1793,43 +1793,43 @@
     <t xml:space="preserve">10.7249908447266</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7888717651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7533826828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7391862869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178926467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6965999603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9166345596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3567066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3709030151367</t>
+    <t xml:space="preserve">10.788872718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7533836364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7391872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178936004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6965990066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9166355133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.356707572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.370903968811</t>
   </si>
   <si>
     <t xml:space="preserve">11.49866771698</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3141202926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4418849945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4276885986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2999248504639</t>
+    <t xml:space="preserve">11.3141193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4418840408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4276876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2999238967896</t>
   </si>
   <si>
     <t xml:space="preserve">11.1579647064209</t>
@@ -1838,19 +1838,19 @@
     <t xml:space="preserve">10.9876146316528</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0018100738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1863574981689</t>
+    <t xml:space="preserve">11.0018110275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1863565444946</t>
   </si>
   <si>
     <t xml:space="preserve">11.3851003646851</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4134912490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4844703674316</t>
+    <t xml:space="preserve">11.4134922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.484471321106</t>
   </si>
   <si>
     <t xml:space="preserve">11.4702749252319</t>
@@ -1859,40 +1859,40 @@
     <t xml:space="preserve">11.6122341156006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5412540435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8535652160645</t>
+    <t xml:space="preserve">11.5412559509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8535642623901</t>
   </si>
   <si>
     <t xml:space="preserve">11.938738822937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1090888977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9813261032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8677587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8251714706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7399978637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6832113265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7967805862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8961524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9103479385376</t>
+    <t xml:space="preserve">12.1090898513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9813270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8677597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8251724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7399969100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6832132339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7967796325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8961515426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9103469848633</t>
   </si>
   <si>
     <t xml:space="preserve">11.8393678665161</t>
@@ -1904,43 +1904,43 @@
     <t xml:space="preserve">11.8109760284424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0665035247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1942644119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2794408798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3078317642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3504180908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4355955123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5065746307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.520770072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.534966468811</t>
+    <t xml:space="preserve">12.0665016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1942663192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2794399261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3078327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3504190444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4355945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5065755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5207710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5349655151367</t>
   </si>
   <si>
     <t xml:space="preserve">12.5917501449585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6627283096313</t>
+    <t xml:space="preserve">12.6627311706543</t>
   </si>
   <si>
     <t xml:space="preserve">12.6343364715576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7053174972534</t>
+    <t xml:space="preserve">12.7053155899048</t>
   </si>
   <si>
     <t xml:space="preserve">12.8161840438843</t>
@@ -1949,28 +1949,28 @@
     <t xml:space="preserve">12.6683597564697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6387977600098</t>
+    <t xml:space="preserve">12.6387958526611</t>
   </si>
   <si>
     <t xml:space="preserve">12.3874988555908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3727178573608</t>
+    <t xml:space="preserve">12.3727159500122</t>
   </si>
   <si>
     <t xml:space="preserve">12.313588142395</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4466276168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.80140209198</t>
+    <t xml:space="preserve">12.4466285705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8014011383057</t>
   </si>
   <si>
     <t xml:space="preserve">12.7274904251099</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5353212356567</t>
+    <t xml:space="preserve">12.5353202819824</t>
   </si>
   <si>
     <t xml:space="preserve">12.5796689987183</t>
@@ -1979,40 +1979,40 @@
     <t xml:space="preserve">12.7422723770142</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6831436157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8753118515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7866182327271</t>
+    <t xml:space="preserve">12.6831426620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8753128051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7866172790527</t>
   </si>
   <si>
     <t xml:space="preserve">12.7718381881714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8309659957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9344415664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.697925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7127075195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5944499969482</t>
+    <t xml:space="preserve">12.8309669494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.934440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6979265213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7127084732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944509506226</t>
   </si>
   <si>
     <t xml:space="preserve">12.9048757553101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8457469940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8900938034058</t>
+    <t xml:space="preserve">12.8457479476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8900957107544</t>
   </si>
   <si>
     <t xml:space="preserve">13.0674819946289</t>
@@ -2027,82 +2027,82 @@
     <t xml:space="preserve">12.9787874221802</t>
   </si>
   <si>
-    <t xml:space="preserve">13.141393661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0970439910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0822639465332</t>
+    <t xml:space="preserve">13.1413927078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0970468521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0822629928589</t>
   </si>
   <si>
     <t xml:space="preserve">13.023136138916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9492244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.156174659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9935693740845</t>
+    <t xml:space="preserve">12.9492235183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1561737060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9935703277588</t>
   </si>
   <si>
     <t xml:space="preserve">12.6092319488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8605289459229</t>
+    <t xml:space="preserve">12.8605298995972</t>
   </si>
   <si>
     <t xml:space="preserve">12.550103187561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4518184661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3335618972778</t>
+    <t xml:space="preserve">13.4518194198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3335628509521</t>
   </si>
   <si>
     <t xml:space="preserve">13.4961652755737</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3483438491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5405130386353</t>
+    <t xml:space="preserve">13.3483428955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5405111312866</t>
   </si>
   <si>
     <t xml:space="preserve">12.9640064239502</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1857395172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1709575653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.919659614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2744312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2596492767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2892141342163</t>
+    <t xml:space="preserve">13.1857404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1709566116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9196586608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.274432182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2596521377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.289213180542</t>
   </si>
   <si>
     <t xml:space="preserve">13.2448673248291</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1266107559204</t>
+    <t xml:space="preserve">13.1266098022461</t>
   </si>
   <si>
     <t xml:space="preserve">13.762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9396314620972</t>
+    <t xml:space="preserve">13.9396343231201</t>
   </si>
   <si>
     <t xml:space="preserve">13.5552949905396</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">13.7474632263184</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9691982269287</t>
+    <t xml:space="preserve">13.9691953659058</t>
   </si>
   <si>
     <t xml:space="preserve">13.7770280838013</t>
@@ -2120,10 +2120,10 @@
     <t xml:space="preserve">13.6292066574097</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8657217025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9544134140015</t>
+    <t xml:space="preserve">13.8657207489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9544124603271</t>
   </si>
   <si>
     <t xml:space="preserve">13.4665994644165</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">13.4813833236694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4370365142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918090820312</t>
+    <t xml:space="preserve">13.4370384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918081283569</t>
   </si>
   <si>
     <t xml:space="preserve">13.998761177063</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">14.0578899383545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8213739395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6883335113525</t>
+    <t xml:space="preserve">13.8213748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6883354187012</t>
   </si>
   <si>
     <t xml:space="preserve">13.6587696075439</t>
@@ -2156,31 +2156,31 @@
     <t xml:space="preserve">13.6144227981567</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5257301330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3631248474121</t>
+    <t xml:space="preserve">13.525731086731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3631258010864</t>
   </si>
   <si>
     <t xml:space="preserve">13.2300853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.88050365448</t>
+    <t xml:space="preserve">13.8805027008057</t>
   </si>
   <si>
     <t xml:space="preserve">14.457010269165</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4717903137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6343946456909</t>
+    <t xml:space="preserve">14.471791267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6343955993652</t>
   </si>
   <si>
     <t xml:space="preserve">14.8191728591919</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0409069061279</t>
+    <t xml:space="preserve">15.0409078598022</t>
   </si>
   <si>
     <t xml:space="preserve">14.9300422668457</t>
@@ -2189,67 +2189,67 @@
     <t xml:space="preserve">15.0039510726929</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3735065460205</t>
+    <t xml:space="preserve">15.3735084533691</t>
   </si>
   <si>
     <t xml:space="preserve">15.5582838058472</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9278402328491</t>
+    <t xml:space="preserve">15.9278411865234</t>
   </si>
   <si>
     <t xml:space="preserve">16.1126174926758</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0387058258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7800178527832</t>
+    <t xml:space="preserve">16.0387096405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7800188064575</t>
   </si>
   <si>
     <t xml:space="preserve">15.7061080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6321954727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5213308334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4104633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.447416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2256860733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.262640953064</t>
+    <t xml:space="preserve">15.6321964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5213289260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4104623794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4474191665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2256851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2626399993896</t>
   </si>
   <si>
     <t xml:space="preserve">15.8908853530884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9669952392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7378730773926</t>
+    <t xml:space="preserve">14.9669961929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7378721237183</t>
   </si>
   <si>
     <t xml:space="preserve">14.8561296463013</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4126625061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0874528884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3091897964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5161380767822</t>
+    <t xml:space="preserve">14.4126634597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0874557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3091888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5161390304565</t>
   </si>
   <si>
     <t xml:space="preserve">14.5309209823608</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">11.471001625061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87452125549316</t>
+    <t xml:space="preserve">9.87452030181885</t>
   </si>
   <si>
     <t xml:space="preserve">10.2145128250122</t>
@@ -2270,22 +2270,22 @@
     <t xml:space="preserve">9.57887744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63800621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1649751663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29801464080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53453063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65278911590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5545043945312</t>
+    <t xml:space="preserve">9.63800716400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16497421264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29801559448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53452968597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65279006958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5545034408569</t>
   </si>
   <si>
     <t xml:space="preserve">10.7023267745972</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">10.9018859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2123126983643</t>
+    <t xml:space="preserve">11.2123136520386</t>
   </si>
   <si>
     <t xml:space="preserve">11.0275354385376</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">10.9905805587769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0127534866333</t>
+    <t xml:space="preserve">11.012752532959</t>
   </si>
   <si>
     <t xml:space="preserve">11.0718812942505</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">11.3157892227173</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353662490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6801528930664</t>
+    <t xml:space="preserve">10.8353672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6801519393921</t>
   </si>
   <si>
     <t xml:space="preserve">10.7244997024536</t>
@@ -2333,19 +2333,19 @@
     <t xml:space="preserve">10.6505889892578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5175476074219</t>
+    <t xml:space="preserve">10.5175485610962</t>
   </si>
   <si>
     <t xml:space="preserve">10.9462337493896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3749160766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2714405059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5301303863525</t>
+    <t xml:space="preserve">11.3749170303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2714414596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5301313400269</t>
   </si>
   <si>
     <t xml:space="preserve">11.9735975265503</t>
@@ -2354,22 +2354,22 @@
     <t xml:space="preserve">11.6040410995483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2197046279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5153484344482</t>
+    <t xml:space="preserve">11.2197027206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5153493881226</t>
   </si>
   <si>
     <t xml:space="preserve">11.73708152771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1288108825684</t>
+    <t xml:space="preserve">12.128809928894</t>
   </si>
   <si>
     <t xml:space="preserve">12.431845664978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.564887046814</t>
+    <t xml:space="preserve">12.5648860931396</t>
   </si>
   <si>
     <t xml:space="preserve">12.3801078796387</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">12.4392366409302</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4096727371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7644462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8974857330322</t>
+    <t xml:space="preserve">12.4096736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7644453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8974866867065</t>
   </si>
   <si>
     <t xml:space="preserve">12.8235750198364</t>
@@ -2393,28 +2393,28 @@
     <t xml:space="preserve">12.971396446228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6070318222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8065919876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8952836990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0431070327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5331211090088</t>
+    <t xml:space="preserve">13.6070337295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8065929412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8952856063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0431079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5331192016602</t>
   </si>
   <si>
     <t xml:space="preserve">13.473991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0896530151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0600891113281</t>
+    <t xml:space="preserve">13.089653968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0600910186768</t>
   </si>
   <si>
     <t xml:space="preserve">13.4887742996216</t>
@@ -2426,10 +2426,10 @@
     <t xml:space="preserve">13.2512512207031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4521446228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1353530883789</t>
+    <t xml:space="preserve">13.4521455764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1353511810303</t>
   </si>
   <si>
     <t xml:space="preserve">12.9962711334229</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">13.1585330963135</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3980598449707</t>
+    <t xml:space="preserve">13.398060798645</t>
   </si>
   <si>
     <t xml:space="preserve">13.2048921585083</t>
@@ -2447,49 +2447,49 @@
     <t xml:space="preserve">13.4212398529053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.544867515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4444179534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5294132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3594264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1276254653931</t>
+    <t xml:space="preserve">13.5448665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4444198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5294122695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3594255447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1276245117188</t>
   </si>
   <si>
     <t xml:space="preserve">13.0812654495239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9344596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8108310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9576396942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2976112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.150806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3362474441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1894378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7953777313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5944833755493</t>
+    <t xml:space="preserve">12.934458732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8108320236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9576387405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2976121902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1508054733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3362455368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1894388198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7953786849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944843292236</t>
   </si>
   <si>
     <t xml:space="preserve">12.7644710540771</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">13.328519821167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2126197814941</t>
+    <t xml:space="preserve">13.2126178741455</t>
   </si>
   <si>
     <t xml:space="preserve">13.4366912841797</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">13.6453123092651</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9312019348145</t>
+    <t xml:space="preserve">13.9312000274658</t>
   </si>
   <si>
     <t xml:space="preserve">13.506233215332</t>
@@ -2519,34 +2519,34 @@
     <t xml:space="preserve">13.5371408462524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8539342880249</t>
+    <t xml:space="preserve">13.8539333343506</t>
   </si>
   <si>
     <t xml:space="preserve">13.8230257034302</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8848390579224</t>
+    <t xml:space="preserve">13.8848400115967</t>
   </si>
   <si>
     <t xml:space="preserve">14.0702781677246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7843933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6916732788086</t>
+    <t xml:space="preserve">13.7843923568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.69167137146</t>
   </si>
   <si>
     <t xml:space="preserve">13.4289655685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6221323013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5989532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.274432182312</t>
+    <t xml:space="preserve">13.6221332550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.598952293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2744340896606</t>
   </si>
   <si>
     <t xml:space="preserve">13.4675989151001</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">13.7148532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5757722854614</t>
+    <t xml:space="preserve">13.5757732391357</t>
   </si>
   <si>
     <t xml:space="preserve">13.3053388595581</t>
@@ -2573,58 +2573,58 @@
     <t xml:space="preserve">13.5680456161499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4830532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8462057113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9234733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9543809890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5912265777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.367151260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5525941848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7380342483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0007410049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8925657272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9080190658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0780057907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.938928604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8616590499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8384790420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0239200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0471000671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3329877853394</t>
+    <t xml:space="preserve">13.4830522537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8462076187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9234743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9543781280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5912275314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3671522140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5525932312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7380323410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0007400512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8925676345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9080200195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0780076980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9389276504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8616600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8384799957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0239191055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.047101020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.332986831665</t>
   </si>
   <si>
     <t xml:space="preserve">14.1861810684204</t>
@@ -2633,34 +2633,34 @@
     <t xml:space="preserve">14.1784543991089</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8152980804443</t>
+    <t xml:space="preserve">13.8152990341187</t>
   </si>
   <si>
     <t xml:space="preserve">13.6993999481201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3130664825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2667045593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2898855209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3748779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.166259765625</t>
+    <t xml:space="preserve">13.3130655288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2667055130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2898864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3748788833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1662588119507</t>
   </si>
   <si>
     <t xml:space="preserve">13.7766666412354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.761212348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7998476028442</t>
+    <t xml:space="preserve">13.7612133026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7998466491699</t>
   </si>
   <si>
     <t xml:space="preserve">13.5834999084473</t>
@@ -2669,22 +2669,22 @@
     <t xml:space="preserve">13.4907789230347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5139598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0161924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6375856399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0426301956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8880977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8262844085693</t>
+    <t xml:space="preserve">13.5139589309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0161943435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6375875473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.042631149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8880987167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8262853622437</t>
   </si>
   <si>
     <t xml:space="preserve">12.8494653701782</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">12.625391960144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6872034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8031053543091</t>
+    <t xml:space="preserve">12.6872053146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8031063079834</t>
   </si>
   <si>
     <t xml:space="preserve">12.9267320632935</t>
@@ -2717,133 +2717,133 @@
     <t xml:space="preserve">13.3207931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4135141372681</t>
+    <t xml:space="preserve">13.4135131835938</t>
   </si>
   <si>
     <t xml:space="preserve">13.4057865142822</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1817121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8417387008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8726453781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9190044403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8571920394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6331186294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7721996307373</t>
+    <t xml:space="preserve">13.1817111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.841739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8726444244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9190053939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8571910858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6331176757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7721977233887</t>
   </si>
   <si>
     <t xml:space="preserve">12.7490177154541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1971654891968</t>
+    <t xml:space="preserve">13.1971645355225</t>
   </si>
   <si>
     <t xml:space="preserve">13.0967197418213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.34397315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821588516235</t>
+    <t xml:space="preserve">13.3439722061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821598052979</t>
   </si>
   <si>
     <t xml:space="preserve">12.9808177947998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7181100845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7258386611938</t>
+    <t xml:space="preserve">12.718111038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7258367538452</t>
   </si>
   <si>
     <t xml:space="preserve">12.6408452987671</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6176643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7103853225708</t>
+    <t xml:space="preserve">12.6176652908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7103862762451</t>
   </si>
   <si>
     <t xml:space="preserve">12.4554052352905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8803730010986</t>
+    <t xml:space="preserve">12.8803720474243</t>
   </si>
   <si>
     <t xml:space="preserve">13.5603199005127</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6839447021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9621067047119</t>
+    <t xml:space="preserve">13.6839466094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9621057510376</t>
   </si>
   <si>
     <t xml:space="preserve">14.139820098877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3716201782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4102544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5570631027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5338802337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4025278091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2402677536011</t>
+    <t xml:space="preserve">14.371621131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4102535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5570621490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5338792800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4025259017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2402687072754</t>
   </si>
   <si>
     <t xml:space="preserve">14.2557210922241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3948001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5493354797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9588499069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1211080551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8043155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6343278884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7656803131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7579555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6806869506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5261535644531</t>
+    <t xml:space="preserve">14.3947992324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5493335723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9588489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1211071014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.804313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6343297958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7656812667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7579545974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6806888580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5261545181274</t>
   </si>
   <si>
     <t xml:space="preserve">14.696141242981</t>
@@ -2852,28 +2852,28 @@
     <t xml:space="preserve">14.6420545578003</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5725154876709</t>
+    <t xml:space="preserve">14.5725145339966</t>
   </si>
   <si>
     <t xml:space="preserve">14.603422164917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5956945419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.657506942749</t>
+    <t xml:space="preserve">14.5956935882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6575050354004</t>
   </si>
   <si>
     <t xml:space="preserve">14.8352222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9974822998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1983757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0824747085571</t>
+    <t xml:space="preserve">14.9974803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.19837474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0824766159058</t>
   </si>
   <si>
     <t xml:space="preserve">15.0283880233765</t>
@@ -2882,16 +2882,16 @@
     <t xml:space="preserve">15.0979290008545</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1751928329468</t>
+    <t xml:space="preserve">15.1751947402954</t>
   </si>
   <si>
     <t xml:space="preserve">15.2061033248901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0747470855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8506746292114</t>
+    <t xml:space="preserve">15.0747480392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8506736755371</t>
   </si>
   <si>
     <t xml:space="preserve">14.8661289215088</t>
@@ -2903,13 +2903,13 @@
     <t xml:space="preserve">15.0592947006226</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0052089691162</t>
+    <t xml:space="preserve">15.0052080154419</t>
   </si>
   <si>
     <t xml:space="preserve">14.9279403686523</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1520185470581</t>
+    <t xml:space="preserve">15.1520147323608</t>
   </si>
   <si>
     <t xml:space="preserve">15.4147233963013</t>
@@ -2927,46 +2927,46 @@
     <t xml:space="preserve">15.7624235153198</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9169569015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0714893341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9787702560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8860483169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9942235946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1796646118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.056037902832</t>
+    <t xml:space="preserve">15.916955947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0714874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9787693023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8860473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9942245483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1796607971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0560359954834</t>
   </si>
   <si>
     <t xml:space="preserve">16.3496494293213</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4578247070312</t>
+    <t xml:space="preserve">16.4578227996826</t>
   </si>
   <si>
     <t xml:space="preserve">16.2651462554932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0564136505127</t>
+    <t xml:space="preserve">16.0564117431641</t>
   </si>
   <si>
     <t xml:space="preserve">15.8476800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7834548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8717632293701</t>
+    <t xml:space="preserve">15.7834539413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8717641830444</t>
   </si>
   <si>
     <t xml:space="preserve">15.6871166229248</t>
@@ -2978,10 +2978,10 @@
     <t xml:space="preserve">15.5586633682251</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6550025939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192268371582</t>
+    <t xml:space="preserve">15.6550035476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192287445068</t>
   </si>
   <si>
     <t xml:space="preserve">15.7673969268799</t>
@@ -2990,16 +2990,16 @@
     <t xml:space="preserve">16.1045818328857</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5988063812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5827503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7111978530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.727255821228</t>
+    <t xml:space="preserve">15.5988054275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827474594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7111988067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7272548675537</t>
   </si>
   <si>
     <t xml:space="preserve">15.5907773971558</t>
@@ -3014,19 +3014,19 @@
     <t xml:space="preserve">15.2616195678711</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4703550338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6630296707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8557090759277</t>
+    <t xml:space="preserve">15.4703540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6630306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8557081222534</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352848052979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9119062423706</t>
+    <t xml:space="preserve">15.9119052886963</t>
   </si>
   <si>
     <t xml:space="preserve">16.0162734985352</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">15.9921875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2490882873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3454284667969</t>
+    <t xml:space="preserve">16.2490901947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3454303741455</t>
   </si>
   <si>
     <t xml:space="preserve">16.5381050109863</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">16.9876842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0679683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9074039459229</t>
+    <t xml:space="preserve">17.0679664611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9074020385742</t>
   </si>
   <si>
     <t xml:space="preserve">16.5702171325684</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">16.2330341339111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0724716186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4096565246582</t>
+    <t xml:space="preserve">16.0724678039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4096546173096</t>
   </si>
   <si>
     <t xml:space="preserve">16.2009201049805</t>
@@ -3086,10 +3086,10 @@
     <t xml:space="preserve">16.0885257720947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0483837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9841585159302</t>
+    <t xml:space="preserve">16.0483856201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9841613769531</t>
   </si>
   <si>
     <t xml:space="preserve">16.2812042236328</t>
@@ -3104,31 +3104,31 @@
     <t xml:space="preserve">15.8637361526489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.398099899292</t>
+    <t xml:space="preserve">15.3981008529663</t>
   </si>
   <si>
     <t xml:space="preserve">15.1090850830078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9164085388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8040132522583</t>
+    <t xml:space="preserve">14.916407585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8040142059326</t>
   </si>
   <si>
     <t xml:space="preserve">14.9806327819824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9886617660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9645767211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7478160858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8923234939575</t>
+    <t xml:space="preserve">14.9886608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9645757675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7478170394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8923225402832</t>
   </si>
   <si>
     <t xml:space="preserve">14.8120422363281</t>
@@ -3140,85 +3140,85 @@
     <t xml:space="preserve">14.8521823883057</t>
   </si>
   <si>
-    <t xml:space="preserve">15.101056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6755628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.787956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1171140670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2375364303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0930271148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2937316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3900728225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0609149932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.036828994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3419036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2535924911499</t>
+    <t xml:space="preserve">15.1010551452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6755638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7879571914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.117112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2375354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0930290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2937326431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3900709152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0609169006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0368299484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3419027328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2535934448242</t>
   </si>
   <si>
     <t xml:space="preserve">15.197395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5345802307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1251430511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769729614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1492261886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8441534042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076759338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6113348007202</t>
+    <t xml:space="preserve">15.5345792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1251420974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769739151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1492252349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8441543579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076749801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6113376617432</t>
   </si>
   <si>
     <t xml:space="preserve">14.6595058441162</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1858406066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3062629699707</t>
+    <t xml:space="preserve">14.1858425140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.306263923645</t>
   </si>
   <si>
     <t xml:space="preserve">14.3544321060181</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5792226791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3464050292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3142919540405</t>
+    <t xml:space="preserve">14.5792245864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3464059829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3142929077148</t>
   </si>
   <si>
     <t xml:space="preserve">14.6996469497681</t>
@@ -3227,25 +3227,25 @@
     <t xml:space="preserve">14.6193618774414</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5551385879517</t>
+    <t xml:space="preserve">14.5551376342773</t>
   </si>
   <si>
     <t xml:space="preserve">14.5230255126953</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5471124649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273908615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8200674057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9244356155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5711946487427</t>
+    <t xml:space="preserve">14.5471105575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273927688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8200693130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9244365692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5711936950684</t>
   </si>
   <si>
     <t xml:space="preserve">14.3785181045532</t>
@@ -3254,88 +3254,88 @@
     <t xml:space="preserve">14.225980758667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1617555618286</t>
+    <t xml:space="preserve">14.1617565155029</t>
   </si>
   <si>
     <t xml:space="preserve">14.0493621826172</t>
   </si>
   <si>
-    <t xml:space="preserve">14.193868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8326005935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7442903518677</t>
+    <t xml:space="preserve">14.1938695907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7442893981934</t>
   </si>
   <si>
     <t xml:space="preserve">13.8486566543579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8085145950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5355558395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5917530059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406276702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9690790176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3704891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3303489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2179527282715</t>
+    <t xml:space="preserve">13.8085165023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5917539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406286239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9690799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3704900741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3303499221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2179536819458</t>
   </si>
   <si>
     <t xml:space="preserve">13.8727416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6479520797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947092056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5114717483521</t>
+    <t xml:space="preserve">13.6479501724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947101593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5114707946777</t>
   </si>
   <si>
     <t xml:space="preserve">13.5034427642822</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2465410232544</t>
+    <t xml:space="preserve">13.2465400695801</t>
   </si>
   <si>
     <t xml:space="preserve">13.415132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3187942504883</t>
+    <t xml:space="preserve">13.3187952041626</t>
   </si>
   <si>
     <t xml:space="preserve">13.4071054458618</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1100606918335</t>
+    <t xml:space="preserve">13.1100616455078</t>
   </si>
   <si>
     <t xml:space="preserve">13.085976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2224569320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5756959915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6640090942383</t>
+    <t xml:space="preserve">13.2224550247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5756969451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6640071868896</t>
   </si>
   <si>
     <t xml:space="preserve">13.198371887207</t>
@@ -3344,10 +3344,10 @@
     <t xml:space="preserve">13.0217504501343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8611879348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7086505889893</t>
+    <t xml:space="preserve">12.8611869812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7086515426636</t>
   </si>
   <si>
     <t xml:space="preserve">12.604284286499</t>
@@ -3356,13 +3356,13 @@
     <t xml:space="preserve">13.0137224197388</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3589363098145</t>
+    <t xml:space="preserve">13.3589353561401</t>
   </si>
   <si>
     <t xml:space="preserve">13.1261177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8210458755493</t>
+    <t xml:space="preserve">12.8210468292236</t>
   </si>
   <si>
     <t xml:space="preserve">12.6363964080811</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">12.9735813140869</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9093570709229</t>
+    <t xml:space="preserve">12.9093561172485</t>
   </si>
   <si>
     <t xml:space="preserve">12.8772439956665</t>
@@ -3380,10 +3380,10 @@
     <t xml:space="preserve">13.1421747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2706260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5516109466553</t>
+    <t xml:space="preserve">13.2706251144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5516119003296</t>
   </si>
   <si>
     <t xml:space="preserve">13.383020401001</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">13.3910484313965</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4392185211182</t>
+    <t xml:space="preserve">13.4392175674438</t>
   </si>
   <si>
     <t xml:space="preserve">13.3509073257446</t>
@@ -3404,34 +3404,34 @@
     <t xml:space="preserve">14.009220123291</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8807706832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5596389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5997829437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4231595993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3749923706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2304849624634</t>
+    <t xml:space="preserve">13.8807687759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5596399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5997819900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4231615066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3027391433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3749914169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2304840087891</t>
   </si>
   <si>
     <t xml:space="preserve">13.0297794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1020317077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0940036773682</t>
+    <t xml:space="preserve">13.102032661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0940046310425</t>
   </si>
   <si>
     <t xml:space="preserve">12.9494962692261</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">12.6444253921509</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7969608306885</t>
+    <t xml:space="preserve">12.7969617843628</t>
   </si>
   <si>
     <t xml:space="preserve">12.9334411621094</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">12.9816093444824</t>
   </si>
   <si>
-    <t xml:space="preserve">13.463303565979</t>
+    <t xml:space="preserve">13.4633026123047</t>
   </si>
   <si>
     <t xml:space="preserve">13.5837249755859</t>
@@ -3476,37 +3476,37 @@
     <t xml:space="preserve">13.3268232345581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2063999176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2786550521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6845655441284</t>
+    <t xml:space="preserve">13.2064008712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2786540985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6845664978027</t>
   </si>
   <si>
     <t xml:space="preserve">12.4838609695435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3393535614014</t>
+    <t xml:space="preserve">12.3393526077271</t>
   </si>
   <si>
     <t xml:space="preserve">12.5320301055908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1839199066162</t>
+    <t xml:space="preserve">12.1839189529419</t>
   </si>
   <si>
     <t xml:space="preserve">11.8018445968628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7424116134644</t>
+    <t xml:space="preserve">11.74241065979</t>
   </si>
   <si>
     <t xml:space="preserve">11.9546747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3112773895264</t>
+    <t xml:space="preserve">12.3112764358521</t>
   </si>
   <si>
     <t xml:space="preserve">12.1075038909912</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">12.2433528900146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9461841583252</t>
+    <t xml:space="preserve">11.9461832046509</t>
   </si>
   <si>
     <t xml:space="preserve">11.98863697052</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">12.0905227661133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9376935958862</t>
+    <t xml:space="preserve">11.9376945495605</t>
   </si>
   <si>
     <t xml:space="preserve">11.6150531768799</t>
@@ -3554,25 +3554,25 @@
     <t xml:space="preserve">11.6575050354004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.750901222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339200973511</t>
+    <t xml:space="preserve">11.7509021759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339210510254</t>
   </si>
   <si>
     <t xml:space="preserve">11.8358068466187</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7593927383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8867492675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9631652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6744861602783</t>
+    <t xml:space="preserve">11.759391784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8867502212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9631643295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6744871139526</t>
   </si>
   <si>
     <t xml:space="preserve">11.5726003646851</t>
@@ -3584,37 +3584,37 @@
     <t xml:space="preserve">11.5980710983276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5471296310425</t>
+    <t xml:space="preserve">11.5471286773682</t>
   </si>
   <si>
     <t xml:space="preserve">11.581090927124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4707136154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3688268661499</t>
+    <t xml:space="preserve">11.4707145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3688278198242</t>
   </si>
   <si>
     <t xml:space="preserve">11.343355178833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3009042739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2499589920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9358110427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6386404037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6301517486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1461906433105</t>
+    <t xml:space="preserve">11.3009033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2499599456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9358100891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6386413574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6301507949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1461896896362</t>
   </si>
   <si>
     <t xml:space="preserve">10.044303894043</t>
@@ -3635,16 +3635,16 @@
     <t xml:space="preserve">10.0612850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075103759766</t>
+    <t xml:space="preserve">10.3075113296509</t>
   </si>
   <si>
     <t xml:space="preserve">10.1716613769531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0697755813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91694641113281</t>
+    <t xml:space="preserve">10.0697746276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9169454574585</t>
   </si>
   <si>
     <t xml:space="preserve">10.0867567062378</t>
@@ -3662,28 +3662,28 @@
     <t xml:space="preserve">9.26317405700684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53487110137939</t>
+    <t xml:space="preserve">9.53487205505371</t>
   </si>
   <si>
     <t xml:space="preserve">9.27166557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45845794677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74713516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90845584869385</t>
+    <t xml:space="preserve">9.45845699310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7471342086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90845489501953</t>
   </si>
   <si>
     <t xml:space="preserve">9.56034278869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4160041809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36506080627441</t>
+    <t xml:space="preserve">9.41600513458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36506175994873</t>
   </si>
   <si>
     <t xml:space="preserve">9.49241924285889</t>
@@ -3692,40 +3692,40 @@
     <t xml:space="preserve">9.38204288482666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08487224578857</t>
+    <t xml:space="preserve">9.08487319946289</t>
   </si>
   <si>
     <t xml:space="preserve">9.46694755554199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7216625213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.027322769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1037368774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1207180023193</t>
+    <t xml:space="preserve">9.72166347503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0273237228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1037378311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1207189559937</t>
   </si>
   <si>
     <t xml:space="preserve">9.80656909942627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2395858764648</t>
+    <t xml:space="preserve">10.2395868301392</t>
   </si>
   <si>
     <t xml:space="preserve">10.6216602325439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.842414855957</t>
+    <t xml:space="preserve">10.8424139022827</t>
   </si>
   <si>
     <t xml:space="preserve">10.8593950271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8254337310791</t>
+    <t xml:space="preserve">10.8254327774048</t>
   </si>
   <si>
     <t xml:space="preserve">10.8678855895996</t>
@@ -3737,25 +3737,25 @@
     <t xml:space="preserve">10.774489402771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8169431686401</t>
+    <t xml:space="preserve">10.8169422149658</t>
   </si>
   <si>
     <t xml:space="preserve">11.0207147598267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0716590881348</t>
+    <t xml:space="preserve">11.0716581344604</t>
   </si>
   <si>
     <t xml:space="preserve">11.2839221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2754316329956</t>
+    <t xml:space="preserve">11.2754306793213</t>
   </si>
   <si>
     <t xml:space="preserve">11.4452409744263</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1395816802979</t>
+    <t xml:space="preserve">11.1395826339722</t>
   </si>
   <si>
     <t xml:space="preserve">11.2075071334839</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">11.173544883728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0292053222656</t>
+    <t xml:space="preserve">11.0292062759399</t>
   </si>
   <si>
     <t xml:space="preserve">11.2584505081177</t>
@@ -3776,37 +3776,37 @@
     <t xml:space="preserve">11.2924127578735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1141109466553</t>
+    <t xml:space="preserve">11.1141119003296</t>
   </si>
   <si>
     <t xml:space="preserve">11.1650543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2414693832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4197702407837</t>
+    <t xml:space="preserve">11.2414684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.419771194458</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858079910278</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3942995071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3603363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0037336349487</t>
+    <t xml:space="preserve">11.3942985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3603372573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376958847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.003734588623</t>
   </si>
   <si>
     <t xml:space="preserve">11.1226024627686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159976959229</t>
+    <t xml:space="preserve">11.2159986495972</t>
   </si>
   <si>
     <t xml:space="preserve">10.9697723388672</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">11.2244882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.411280632019</t>
+    <t xml:space="preserve">11.4112796783447</t>
   </si>
   <si>
     <t xml:space="preserve">11.5216569900513</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">11.5386381149292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9716558456421</t>
+    <t xml:space="preserve">11.9716567993164</t>
   </si>
   <si>
     <t xml:space="preserve">12.1159944534302</t>
@@ -3848,16 +3848,16 @@
     <t xml:space="preserve">12.1329755783081</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2009000778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2263708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1414661407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0650520324707</t>
+    <t xml:space="preserve">12.2008991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2263717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1414670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0650510787964</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056180953979</t>
@@ -3869,16 +3869,16 @@
     <t xml:space="preserve">11.7169399261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8188257217407</t>
+    <t xml:space="preserve">11.818826675415</t>
   </si>
   <si>
     <t xml:space="preserve">11.5641098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9018478393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5622253417969</t>
+    <t xml:space="preserve">10.9018487930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5622262954712</t>
   </si>
   <si>
     <t xml:space="preserve">10.4263772964478</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">10.604679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8763771057129</t>
+    <t xml:space="preserve">10.8763761520386</t>
   </si>
   <si>
     <t xml:space="preserve">10.6895847320557</t>
@@ -3899,16 +3899,16 @@
     <t xml:space="preserve">10.9867525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914705276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8084506988525</t>
+    <t xml:space="preserve">10.7914714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8084516525269</t>
   </si>
   <si>
     <t xml:space="preserve">10.8509044647217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6980743408203</t>
+    <t xml:space="preserve">10.6980762481689</t>
   </si>
   <si>
     <t xml:space="preserve">10.6641130447388</t>
@@ -3920,22 +3920,22 @@
     <t xml:space="preserve">10.7999620437622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.012225151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3093929290771</t>
+    <t xml:space="preserve">11.0122261047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3093938827515</t>
   </si>
   <si>
     <t xml:space="preserve">11.0886402130127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3773183822632</t>
+    <t xml:space="preserve">11.3773174285889</t>
   </si>
   <si>
     <t xml:space="preserve">11.5046758651733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6320343017578</t>
+    <t xml:space="preserve">11.6320333480835</t>
   </si>
   <si>
     <t xml:space="preserve">11.5131673812866</t>
@@ -3947,13 +3947,13 @@
     <t xml:space="preserve">11.6999578475952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6829776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7678823471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8273162841797</t>
+    <t xml:space="preserve">11.6829767227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7678833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.827317237854</t>
   </si>
   <si>
     <t xml:space="preserve">11.6374282836914</t>
@@ -5349,6 +5349,9 @@
   </si>
   <si>
     <t xml:space="preserve">20.3199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5200004577637</t>
   </si>
 </sst>
 </file>
@@ -70375,7 +70378,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6494907407</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>140343</v>
@@ -70396,6 +70399,32 @@
         <v>1778</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6494212963</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>51031</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>20.5200004577637</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>20.1800003051758</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>20.3199996948242</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>20.5200004577637</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1779</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="1780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="1781">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,127 +44,127 @@
     <t xml:space="preserve">ACE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.611008644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3010368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.437424659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48081970214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61720752716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80319213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68540191650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30723476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3506326675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20804500579834</t>
+    <t xml:space="preserve">8.61100769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30103588104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43742275238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48082160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61720848083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80319023132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68540096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30723571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35063171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20804405212402</t>
   </si>
   <si>
     <t xml:space="preserve">7.91667222976685</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97246694564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13985061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15225124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2762393951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38782787322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49321937561035</t>
+    <t xml:space="preserve">7.97246742248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13985252380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15225028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27624034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38782978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49321842193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.50561809539795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39402866363525</t>
+    <t xml:space="preserve">8.39402770996094</t>
   </si>
   <si>
     <t xml:space="preserve">8.36923027038574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33203315734863</t>
+    <t xml:space="preserve">8.33203411102295</t>
   </si>
   <si>
     <t xml:space="preserve">7.99106454849243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59430074691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45791339874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31532907485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46411323547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6686954498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63149833679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65629577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65009689331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44551563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.600501537323</t>
+    <t xml:space="preserve">7.59430170059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45791292190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31532716751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46411514282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66869497299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63149976730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65629720687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65009641647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44551420211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60050106048584</t>
   </si>
   <si>
     <t xml:space="preserve">7.68109369277954</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55090475082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68729257583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60670042037964</t>
+    <t xml:space="preserve">7.55090665817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6872935295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6067008972168</t>
   </si>
   <si>
     <t xml:space="preserve">7.73688793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64389705657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57570362091064</t>
+    <t xml:space="preserve">7.64389801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57570457458496</t>
   </si>
   <si>
     <t xml:space="preserve">7.53230667114258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01586246490479</t>
+    <t xml:space="preserve">8.0158634185791</t>
   </si>
   <si>
     <t xml:space="preserve">8.38162899017334</t>
@@ -173,25 +173,25 @@
     <t xml:space="preserve">8.67920303344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77219390869141</t>
+    <t xml:space="preserve">8.77219295501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.76599407196045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83418846130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78459167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46842098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41882514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33823299407959</t>
+    <t xml:space="preserve">8.83418750762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.784592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46842193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41882610321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33823394775391</t>
   </si>
   <si>
     <t xml:space="preserve">8.45602321624756</t>
@@ -200,40 +200,40 @@
     <t xml:space="preserve">8.49941825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58620929718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43122482299805</t>
+    <t xml:space="preserve">8.58621120452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43122577667236</t>
   </si>
   <si>
     <t xml:space="preserve">8.40642738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34443378448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47461986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24524116516113</t>
+    <t xml:space="preserve">8.34443283081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4746208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24524021148682</t>
   </si>
   <si>
     <t xml:space="preserve">7.90427350997925</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87327527999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73068904876709</t>
+    <t xml:space="preserve">7.87327480316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73068952560425</t>
   </si>
   <si>
     <t xml:space="preserve">7.79268312454224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8546781539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89807462692261</t>
+    <t xml:space="preserve">7.85467863082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89807224273682</t>
   </si>
   <si>
     <t xml:space="preserve">7.96006774902344</t>
@@ -242,40 +242,40 @@
     <t xml:space="preserve">8.04685974121094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99726629257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96626901626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8670768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78028345108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11505317687988</t>
+    <t xml:space="preserve">7.99726390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96626710891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86707735061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78028440475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.090256690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1150541305542</t>
   </si>
   <si>
     <t xml:space="preserve">8.17704772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02206134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88567495346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82987976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0406608581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00966262817383</t>
+    <t xml:space="preserve">8.02206230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88567638397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82988023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04066181182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00966358184814</t>
   </si>
   <si>
     <t xml:space="preserve">8.09645652770996</t>
@@ -287,127 +287,127 @@
     <t xml:space="preserve">8.23284244537354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18324756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05925941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76168537139893</t>
+    <t xml:space="preserve">8.18324661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05925846099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76168632507324</t>
   </si>
   <si>
     <t xml:space="preserve">7.5261082649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56330347061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4207181930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19133853912354</t>
+    <t xml:space="preserve">7.56330442428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42071771621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19133949279785</t>
   </si>
   <si>
     <t xml:space="preserve">6.85657024383545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9681601524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97435855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12314414978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09073686599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05184936523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14259052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05833148956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68240451812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37777423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4944429397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61110782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08425569534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99999713897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03888511657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93518209457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78610897064209</t>
+    <t xml:space="preserve">6.96815919876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97435808181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12314462661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09073734283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05184841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14258813858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05832958221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6824049949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3777756690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49444198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61110830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08425664901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99999666213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03888607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93518161773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78610801696777</t>
   </si>
   <si>
     <t xml:space="preserve">6.75370121002197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82499742507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86388540267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74073696136475</t>
+    <t xml:space="preserve">6.82499599456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8638858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7407374382019</t>
   </si>
   <si>
     <t xml:space="preserve">6.91573810577393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9286994934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8962926864624</t>
+    <t xml:space="preserve">6.92869997024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89629411697388</t>
   </si>
   <si>
     <t xml:space="preserve">7.15555286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14907073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58333015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55740451812744</t>
+    <t xml:space="preserve">7.14907121658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58332967758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55740356445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.0694408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04351425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01110649108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16666316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17962646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07592296600342</t>
+    <t xml:space="preserve">8.04351615905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0111083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16666412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17962455749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0759220123291</t>
   </si>
   <si>
     <t xml:space="preserve">8.05647850036621</t>
@@ -416,40 +416,40 @@
     <t xml:space="preserve">8.10184764862061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95277500152588</t>
+    <t xml:space="preserve">7.9527759552002</t>
   </si>
   <si>
     <t xml:space="preserve">7.82962656021118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87499666213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90740299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481151580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75832891464233</t>
+    <t xml:space="preserve">7.87499761581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90740394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481103897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75832939147949</t>
   </si>
   <si>
     <t xml:space="preserve">7.74536657333374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77129173278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71944141387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57684755325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65462732315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70647859573364</t>
+    <t xml:space="preserve">7.77129364013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71944093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57684946060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65462779998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70647811889648</t>
   </si>
   <si>
     <t xml:space="preserve">7.81666374206543</t>
@@ -458,172 +458,172 @@
     <t xml:space="preserve">7.79073667526245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69351434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72592163085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69999647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50555229187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37592315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39536571502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47314405441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32407093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25277423858643</t>
+    <t xml:space="preserve">7.69351530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72592306137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69999742507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50555276870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37592267990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39536762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47314500808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3240704536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25277328491211</t>
   </si>
   <si>
     <t xml:space="preserve">7.22684860229492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18147945404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20092296600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22036647796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18796014785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16851615905762</t>
+    <t xml:space="preserve">7.18147802352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2009220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22036743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18796157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1685152053833</t>
   </si>
   <si>
     <t xml:space="preserve">7.16203355789185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19444179534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17499685287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07129287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96759033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04536819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98703289031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23333024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34999561309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41481161117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55092191696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52499723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64166355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59629249572754</t>
+    <t xml:space="preserve">7.19444227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17499589920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07129430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96758890151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0453667640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98703336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23332977294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3499960899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41481256484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55092287063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52499628067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64166212081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59629344940186</t>
   </si>
   <si>
     <t xml:space="preserve">7.61573839187622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64814472198486</t>
+    <t xml:space="preserve">7.64814567565918</t>
   </si>
   <si>
     <t xml:space="preserve">7.49258995056152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38888597488403</t>
+    <t xml:space="preserve">7.38888549804688</t>
   </si>
   <si>
     <t xml:space="preserve">7.46018218994141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36944055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30462646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84444236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57221984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59166431427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54629278182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48147964477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43610858917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47823715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52684926986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64999771118164</t>
+    <t xml:space="preserve">7.36944007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30462837219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84444189071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57222032546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5916633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54629373550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48147916793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43610811233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47823762893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52684879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6499981880188</t>
   </si>
   <si>
     <t xml:space="preserve">6.53333044052124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59814500808716</t>
+    <t xml:space="preserve">6.59814596176147</t>
   </si>
   <si>
     <t xml:space="preserve">6.52036762237549</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42962741851807</t>
+    <t xml:space="preserve">6.42962646484375</t>
   </si>
   <si>
     <t xml:space="preserve">6.87036800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10370206832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25925493240356</t>
+    <t xml:space="preserve">7.10370111465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25925636291504</t>
   </si>
   <si>
     <t xml:space="preserve">7.48610782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43425750732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42777490615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38240432739258</t>
+    <t xml:space="preserve">7.43425607681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42777442932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38240480422974</t>
   </si>
   <si>
     <t xml:space="preserve">7.51851558685303</t>
@@ -632,46 +632,46 @@
     <t xml:space="preserve">7.51203441619873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66758966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68055248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71295833587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89444065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79721879959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84258985519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34351491928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40184879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46666383743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40832996368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73888540267944</t>
+    <t xml:space="preserve">7.66758871078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68055152893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71295928955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89444017410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79721832275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84258937835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34351587295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40184926986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46666288375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40832948684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73888444900513</t>
   </si>
   <si>
     <t xml:space="preserve">7.68703365325928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62222051620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63518238067627</t>
+    <t xml:space="preserve">7.62221908569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63518095016479</t>
   </si>
   <si>
     <t xml:space="preserve">7.7324047088623</t>
@@ -680,22 +680,22 @@
     <t xml:space="preserve">7.7777738571167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83610773086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75184869766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62870025634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97221803665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85555171966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9268479347229</t>
+    <t xml:space="preserve">7.83610868453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7518482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62870216369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97221946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85555219650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92684888839722</t>
   </si>
   <si>
     <t xml:space="preserve">8.03703308105469</t>
@@ -710,127 +710,127 @@
     <t xml:space="preserve">8.20555114746094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28981018066406</t>
+    <t xml:space="preserve">8.28981113433838</t>
   </si>
   <si>
     <t xml:space="preserve">8.24444103240967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147678375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22499465942383</t>
+    <t xml:space="preserve">8.23147773742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22499656677246</t>
   </si>
   <si>
     <t xml:space="preserve">8.27036762237549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46481227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45832920074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43240547180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42592334747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3546257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55555152893066</t>
+    <t xml:space="preserve">8.46481132507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45833015441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43240356445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42592144012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35462474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55555248260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.52314376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39351558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47129154205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60740280151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61388492584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6203670501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56203460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80833053588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81481170654297</t>
+    <t xml:space="preserve">8.39351367950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47129249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60740375518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6138858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62036609649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56203174591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80832958221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6786994934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81481075286865</t>
   </si>
   <si>
     <t xml:space="preserve">8.84073829650879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9249963760376</t>
+    <t xml:space="preserve">8.92499732971191</t>
   </si>
   <si>
     <t xml:space="preserve">9.12592220306396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17777252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00277328491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95092105865479</t>
+    <t xml:space="preserve">9.17777347564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00277423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9509220123291</t>
   </si>
   <si>
     <t xml:space="preserve">8.99629306793213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18425464630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01573657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02870082855225</t>
+    <t xml:space="preserve">9.18425559997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01573753356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02869987487793</t>
   </si>
   <si>
     <t xml:space="preserve">9.20370006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2814769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30740261077881</t>
+    <t xml:space="preserve">9.28147792816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30740451812744</t>
   </si>
   <si>
     <t xml:space="preserve">9.34629249572754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43703365325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32684898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43055057525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38518142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41758823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33332920074463</t>
+    <t xml:space="preserve">9.43703460693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32684803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43055152893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38518047332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41759014129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33333015441895</t>
   </si>
   <si>
     <t xml:space="preserve">9.50184726715088</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">9.50833034515381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44351387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54721832275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41110706329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35925388336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51501750946045</t>
+    <t xml:space="preserve">9.44351291656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54721736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41110610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35925579071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51501655578613</t>
   </si>
   <si>
     <t xml:space="preserve">9.41343402862549</t>
@@ -860,28 +860,28 @@
     <t xml:space="preserve">9.59628391265869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50147151947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44729328155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48115539550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21026611328125</t>
+    <t xml:space="preserve">9.50147247314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44729423522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48115634918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21026515960693</t>
   </si>
   <si>
     <t xml:space="preserve">9.09513664245605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14931488037109</t>
+    <t xml:space="preserve">9.14931392669678</t>
   </si>
   <si>
     <t xml:space="preserve">8.98678112030029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83101844787598</t>
+    <t xml:space="preserve">8.83102035522461</t>
   </si>
   <si>
     <t xml:space="preserve">8.84456348419189</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">8.93937587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81070232391357</t>
+    <t xml:space="preserve">8.81070327758789</t>
   </si>
   <si>
     <t xml:space="preserve">8.93260288238525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04096031188965</t>
+    <t xml:space="preserve">9.04095935821533</t>
   </si>
   <si>
     <t xml:space="preserve">8.87165355682373</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">9.08159255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10190868377686</t>
+    <t xml:space="preserve">9.10190963745117</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349311828613</t>
@@ -917,22 +917,22 @@
     <t xml:space="preserve">9.10868167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12222576141357</t>
+    <t xml:space="preserve">9.12222671508789</t>
   </si>
   <si>
     <t xml:space="preserve">9.0070972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07482051849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87842559814453</t>
+    <t xml:space="preserve">9.07482147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87842464447021</t>
   </si>
   <si>
     <t xml:space="preserve">8.92583084106445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90551376342773</t>
+    <t xml:space="preserve">8.90551280975342</t>
   </si>
   <si>
     <t xml:space="preserve">8.52626800537109</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">8.58721828460693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54658508300781</t>
+    <t xml:space="preserve">8.54658317565918</t>
   </si>
   <si>
     <t xml:space="preserve">8.56012916564941</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">8.5398120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44500064849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33664512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47208881378174</t>
+    <t xml:space="preserve">8.44500160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33664608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47208976745605</t>
   </si>
   <si>
     <t xml:space="preserve">8.47886180877686</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">8.41114044189453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42468357086182</t>
+    <t xml:space="preserve">8.4246826171875</t>
   </si>
   <si>
     <t xml:space="preserve">8.3840503692627</t>
@@ -980,34 +980,34 @@
     <t xml:space="preserve">8.32987308502197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28246593475342</t>
+    <t xml:space="preserve">8.28246688842773</t>
   </si>
   <si>
     <t xml:space="preserve">8.26892185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24860668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19442653656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16733932495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21474361419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37050533294678</t>
+    <t xml:space="preserve">8.2486047744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19442749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16733837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21474456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37050628662109</t>
   </si>
   <si>
     <t xml:space="preserve">8.29601192474365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39759540557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81747531890869</t>
+    <t xml:space="preserve">8.3975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81747436523438</t>
   </si>
   <si>
     <t xml:space="preserve">8.97323608398438</t>
@@ -1016,28 +1016,28 @@
     <t xml:space="preserve">8.76329612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67525768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68202972412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69557476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80393028259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8581075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74297904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74975204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79038619995117</t>
+    <t xml:space="preserve">8.67525863647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68202877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6955738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80392932891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85810852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74298095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74975109100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79038524627686</t>
   </si>
   <si>
     <t xml:space="preserve">8.88519668579102</t>
@@ -1052,61 +1052,61 @@
     <t xml:space="preserve">8.89196968078613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18317794799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1967191696167</t>
+    <t xml:space="preserve">9.18317699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19672203063965</t>
   </si>
   <si>
     <t xml:space="preserve">9.29153251647949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24412631988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36602592468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40666198730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54210662841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46761131286621</t>
+    <t xml:space="preserve">9.24412536621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36602687835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40666103363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54210567474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46760940551758</t>
   </si>
   <si>
     <t xml:space="preserve">9.38634395599365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52178955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49470043182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84008407592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86717414855957</t>
+    <t xml:space="preserve">9.52179050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49470138549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84008693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86717224121094</t>
   </si>
   <si>
     <t xml:space="preserve">9.88749027252197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83331394195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76558971405029</t>
+    <t xml:space="preserve">9.83331203460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76559066772461</t>
   </si>
   <si>
     <t xml:space="preserve">9.74527359008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70464038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58273983001709</t>
+    <t xml:space="preserve">9.70463943481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58273792266846</t>
   </si>
   <si>
     <t xml:space="preserve">9.71818542480469</t>
@@ -1115,25 +1115,25 @@
     <t xml:space="preserve">9.67077827453613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96875858306885</t>
+    <t xml:space="preserve">9.96875953674316</t>
   </si>
   <si>
     <t xml:space="preserve">9.94844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91458129882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0161628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96198558807373</t>
+    <t xml:space="preserve">9.91457843780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0161638259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96198654174805</t>
   </si>
   <si>
     <t xml:space="preserve">9.92135143280029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90103435516357</t>
+    <t xml:space="preserve">9.90103530883789</t>
   </si>
   <si>
     <t xml:space="preserve">10.2599639892578</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">11.4857425689697</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5128316879272</t>
+    <t xml:space="preserve">11.5128326416016</t>
   </si>
   <si>
     <t xml:space="preserve">11.4518814086914</t>
@@ -1157,82 +1157,82 @@
     <t xml:space="preserve">11.4383363723755</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4992866516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3502969741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0726346969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9845952987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.876238822937</t>
+    <t xml:space="preserve">11.4992876052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3502979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0726366043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9845962524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8762378692627</t>
   </si>
   <si>
     <t xml:space="preserve">11.1674470901489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8152894973755</t>
+    <t xml:space="preserve">10.8152885437012</t>
   </si>
   <si>
     <t xml:space="preserve">10.5850324630737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4495887756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5647172927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5443983078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4292697906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4699048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.632438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.822060585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9168729782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9913682937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8017454147339</t>
+    <t xml:space="preserve">10.4495878219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5647163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5443992614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4292707443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4699039459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6324377059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8220624923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9168739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9913673400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8017444610596</t>
   </si>
   <si>
     <t xml:space="preserve">10.7204780578613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6256656646729</t>
+    <t xml:space="preserve">10.6256666183472</t>
   </si>
   <si>
     <t xml:space="preserve">10.6730718612671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8356056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9371900558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.998140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0455455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1268129348755</t>
+    <t xml:space="preserve">10.8356065750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9371910095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9981393814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0455465316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1268138885498</t>
   </si>
   <si>
     <t xml:space="preserve">10.9304170608521</t>
@@ -1253,22 +1253,22 @@
     <t xml:space="preserve">10.5376272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5173110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3615503311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.097430229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87394714355469</t>
+    <t xml:space="preserve">10.5173091888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3615484237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0974311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87394523620605</t>
   </si>
   <si>
     <t xml:space="preserve">10.1922426223755</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92812347412109</t>
+    <t xml:space="preserve">9.92812442779541</t>
   </si>
   <si>
     <t xml:space="preserve">10.0364799499512</t>
@@ -1289,22 +1289,22 @@
     <t xml:space="preserve">9.69786739349365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50824356079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44052124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6436882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66400718688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67755031585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083927154541</t>
+    <t xml:space="preserve">9.50824451446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44052219390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64368915557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66400527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67755222320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083831787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.55565071105957</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">9.34571075439453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21703720092773</t>
+    <t xml:space="preserve">9.21703624725342</t>
   </si>
   <si>
     <t xml:space="preserve">9.13576984405518</t>
@@ -1322,34 +1322,34 @@
     <t xml:space="preserve">9.23058223724365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06804847717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17640495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33216667175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27798652648926</t>
+    <t xml:space="preserve">9.06804752349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17640399932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3321647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27798843383789</t>
   </si>
   <si>
     <t xml:space="preserve">9.23735523223877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16285991668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29830360412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42697811126709</t>
+    <t xml:space="preserve">9.16286087036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29830455780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42697715759277</t>
   </si>
   <si>
     <t xml:space="preserve">9.53533363342285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62337398529053</t>
+    <t xml:space="preserve">9.62337303161621</t>
   </si>
   <si>
     <t xml:space="preserve">9.79945182800293</t>
@@ -1358,22 +1358,22 @@
     <t xml:space="preserve">9.80622291564941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77236270904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95521354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81976795196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75881671905518</t>
+    <t xml:space="preserve">9.77236175537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95521259307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81976890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75881862640381</t>
   </si>
   <si>
     <t xml:space="preserve">9.47438335418701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71141338348389</t>
+    <t xml:space="preserve">9.71141147613525</t>
   </si>
   <si>
     <t xml:space="preserve">9.30507659912109</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">9.03418731689453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39311504364014</t>
+    <t xml:space="preserve">9.39311695098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.26281547546387</t>
@@ -1397,31 +1397,31 @@
     <t xml:space="preserve">9.29120635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24152183532715</t>
+    <t xml:space="preserve">9.24152088165283</t>
   </si>
   <si>
     <t xml:space="preserve">9.1137580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14924907684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697536468506</t>
+    <t xml:space="preserve">9.14924716949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">9.07117080688477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03567981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99309349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04277896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.021484375</t>
+    <t xml:space="preserve">9.03568077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99309253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04277801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02148532867432</t>
   </si>
   <si>
     <t xml:space="preserve">9.19183540344238</t>
@@ -1430,82 +1430,82 @@
     <t xml:space="preserve">9.27701091766357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39767456054688</t>
+    <t xml:space="preserve">9.39767551422119</t>
   </si>
   <si>
     <t xml:space="preserve">9.2131290435791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10665988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12795257568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22732448577881</t>
+    <t xml:space="preserve">9.10666179656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12795448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22732543945312</t>
   </si>
   <si>
     <t xml:space="preserve">9.26991271972656</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12085723876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17763900756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38347911834717</t>
+    <t xml:space="preserve">9.1208553314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17764091491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38348007202148</t>
   </si>
   <si>
     <t xml:space="preserve">9.44026374816895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41187286376953</t>
+    <t xml:space="preserve">9.41187191009521</t>
   </si>
   <si>
     <t xml:space="preserve">9.603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7028865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56092739105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61771297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65320205688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68159294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57512474060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66029930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53253746032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45445919036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50414657592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30540180206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34799003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28410816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24861812591553</t>
+    <t xml:space="preserve">9.70288753509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56092929840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61771106719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65320014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6815938949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57512283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66029834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53253555297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45446014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50414562225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30540084838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34799098968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2841100692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24862003326416</t>
   </si>
   <si>
     <t xml:space="preserve">9.0924654006958</t>
@@ -1520,46 +1520,46 @@
     <t xml:space="preserve">8.68078327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78725337982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97889709472656</t>
+    <t xml:space="preserve">8.78725242614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97889614105225</t>
   </si>
   <si>
     <t xml:space="preserve">9.01438617706299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14214897155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23442363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29830455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39057731628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42606639862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37638282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16344261169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04987716674805</t>
+    <t xml:space="preserve">9.14215087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23442268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29830551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3905782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42606735229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37638187408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16344356536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04987621307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.17054176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74466419219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69497966766357</t>
+    <t xml:space="preserve">8.74466514587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69497871398926</t>
   </si>
   <si>
     <t xml:space="preserve">8.51043319702148</t>
@@ -1574,46 +1574,46 @@
     <t xml:space="preserve">8.59560775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49623680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26910209655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26200580596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22651672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04196834564209</t>
+    <t xml:space="preserve">8.49623775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26910305023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26200485229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22651481628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04197025299072</t>
   </si>
   <si>
     <t xml:space="preserve">8.06326198577881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07036018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93549966812134</t>
+    <t xml:space="preserve">8.0703592300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9355001449585</t>
   </si>
   <si>
     <t xml:space="preserve">8.1484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16263389587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2407112121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28329849243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38266944885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36137580871582</t>
+    <t xml:space="preserve">8.16263294219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24071025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28329944610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38267040252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36137676239014</t>
   </si>
   <si>
     <t xml:space="preserve">8.50333499908447</t>
@@ -1622,22 +1622,22 @@
     <t xml:space="preserve">8.42525768280029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15634536743164</t>
+    <t xml:space="preserve">9.15634632110596</t>
   </si>
   <si>
     <t xml:space="preserve">9.08536624908447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06407165527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80854606628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81564426422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65949058532715</t>
+    <t xml:space="preserve">9.06407260894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8085470199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81564521789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65948963165283</t>
   </si>
   <si>
     <t xml:space="preserve">8.56011867523193</t>
@@ -1655,34 +1655,34 @@
     <t xml:space="preserve">8.5175313949585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40396404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36847496032715</t>
+    <t xml:space="preserve">8.40396499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36847400665283</t>
   </si>
   <si>
     <t xml:space="preserve">8.43945407867432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21231746673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80144882202148</t>
+    <t xml:space="preserve">8.21231842041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80144691467285</t>
   </si>
   <si>
     <t xml:space="preserve">8.60980415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3400821685791</t>
+    <t xml:space="preserve">8.34008312225342</t>
   </si>
   <si>
     <t xml:space="preserve">8.19812393188477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37557315826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4607458114624</t>
+    <t xml:space="preserve">8.37557220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46074771881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.62399959564209</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">8.5317268371582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68788242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83693885803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85823154449463</t>
+    <t xml:space="preserve">8.68788146972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83693695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85823249816895</t>
   </si>
   <si>
     <t xml:space="preserve">8.90791797637939</t>
@@ -1712,22 +1712,22 @@
     <t xml:space="preserve">9.5112419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58222389221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47575378417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35508728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54673099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66739749908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6106128692627</t>
+    <t xml:space="preserve">9.58222198486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47575283050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35508918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54673290252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66739654541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61061382293701</t>
   </si>
   <si>
     <t xml:space="preserve">9.63190841674805</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">9.51834011077881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68869018554688</t>
+    <t xml:space="preserve">9.68869113922119</t>
   </si>
   <si>
     <t xml:space="preserve">9.90872764587402</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">9.88033580780029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75967121124268</t>
+    <t xml:space="preserve">9.75967025756836</t>
   </si>
   <si>
     <t xml:space="preserve">9.86613941192627</t>
@@ -1757,58 +1757,58 @@
     <t xml:space="preserve">9.85194396972656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0222930908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2423305511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.327507019043</t>
+    <t xml:space="preserve">10.0222949981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2423324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3275060653687</t>
   </si>
   <si>
     <t xml:space="preserve">10.6114234924316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7604808807373</t>
+    <t xml:space="preserve">10.760479927063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6398153305054</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6824045181274</t>
+    <t xml:space="preserve">10.6824026107788</t>
   </si>
   <si>
     <t xml:space="preserve">10.6043252944946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7107963562012</t>
+    <t xml:space="preserve">10.7107954025269</t>
   </si>
   <si>
     <t xml:space="preserve">10.6895017623901</t>
   </si>
   <si>
-    <t xml:space="preserve">10.774676322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7249898910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.788872718811</t>
+    <t xml:space="preserve">10.7746772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7249908447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7888717651367</t>
   </si>
   <si>
     <t xml:space="preserve">10.753381729126</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7391862869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178936004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6965980529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9166355133057</t>
+    <t xml:space="preserve">10.7391881942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178926467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6965990066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.91663646698</t>
   </si>
   <si>
     <t xml:space="preserve">11.3567085266113</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">11.370903968811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49866771698</t>
+    <t xml:space="preserve">11.4986667633057</t>
   </si>
   <si>
     <t xml:space="preserve">11.3141202926636</t>
@@ -1826,16 +1826,16 @@
     <t xml:space="preserve">11.4418830871582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4276866912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2999229431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1579647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9876136779785</t>
+    <t xml:space="preserve">11.4276876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2999248504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1579666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9876146316528</t>
   </si>
   <si>
     <t xml:space="preserve">11.0018119812012</t>
@@ -1844,37 +1844,37 @@
     <t xml:space="preserve">11.1863574981689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3851022720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4134902954102</t>
+    <t xml:space="preserve">11.3851003646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4134912490845</t>
   </si>
   <si>
     <t xml:space="preserve">11.4844703674316</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4702749252319</t>
+    <t xml:space="preserve">11.4702739715576</t>
   </si>
   <si>
     <t xml:space="preserve">11.6122341156006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5412530899048</t>
+    <t xml:space="preserve">11.5412540435791</t>
   </si>
   <si>
     <t xml:space="preserve">11.8535642623901</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9387378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1090888977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9813261032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8677587509155</t>
+    <t xml:space="preserve">11.938738822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1090879440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9813270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8677597045898</t>
   </si>
   <si>
     <t xml:space="preserve">11.8251724243164</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">11.7399978637695</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6832113265991</t>
+    <t xml:space="preserve">11.6832132339478</t>
   </si>
   <si>
     <t xml:space="preserve">11.7967805862427</t>
@@ -1892,25 +1892,25 @@
     <t xml:space="preserve">11.8961524963379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9103488922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8393678665161</t>
+    <t xml:space="preserve">11.9103498458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8393688201904</t>
   </si>
   <si>
     <t xml:space="preserve">11.8819551467896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8109741210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0665016174316</t>
+    <t xml:space="preserve">11.8109760284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0665035247803</t>
   </si>
   <si>
     <t xml:space="preserve">12.1942644119263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2794408798218</t>
+    <t xml:space="preserve">12.2794389724731</t>
   </si>
   <si>
     <t xml:space="preserve">12.3078327178955</t>
@@ -1928,37 +1928,37 @@
     <t xml:space="preserve">12.520770072937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5349674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5917510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.66273021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6343355178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7053174972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.81618309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6683616638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6387968063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3874988555908</t>
+    <t xml:space="preserve">12.5349655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5917491912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6627292633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6343364715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7053155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8161840438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.668360710144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6387977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3874998092651</t>
   </si>
   <si>
     <t xml:space="preserve">12.3727169036865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3135890960693</t>
+    <t xml:space="preserve">12.313588142395</t>
   </si>
   <si>
     <t xml:space="preserve">12.4466285705566</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">12.8014001846313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7274894714355</t>
+    <t xml:space="preserve">12.7274904251099</t>
   </si>
   <si>
     <t xml:space="preserve">12.5353212356567</t>
@@ -1976,40 +1976,40 @@
     <t xml:space="preserve">12.5796689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7422714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6831436157227</t>
+    <t xml:space="preserve">12.7422723770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6831426620483</t>
   </si>
   <si>
     <t xml:space="preserve">12.8753128051758</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7866182327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7718372344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8309659957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9344425201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6979265213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7127084732056</t>
+    <t xml:space="preserve">12.7866172790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7718362808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8309669494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.934440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7127075195312</t>
   </si>
   <si>
     <t xml:space="preserve">12.5944509506226</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9048748016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8457469940186</t>
+    <t xml:space="preserve">12.9048757553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8457479476929</t>
   </si>
   <si>
     <t xml:space="preserve">12.8900947570801</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">13.0674810409546</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1118288040161</t>
+    <t xml:space="preserve">13.1118268966675</t>
   </si>
   <si>
     <t xml:space="preserve">13.052698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9787874221802</t>
+    <t xml:space="preserve">12.9787864685059</t>
   </si>
   <si>
     <t xml:space="preserve">13.1413927078247</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">13.0970449447632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0822629928589</t>
+    <t xml:space="preserve">13.0822649002075</t>
   </si>
   <si>
     <t xml:space="preserve">13.023136138916</t>
@@ -2045,28 +2045,28 @@
     <t xml:space="preserve">13.1561737060547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9935693740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6092319488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8605298995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.550103187561</t>
+    <t xml:space="preserve">12.9935712814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6092309951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8605289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5501041412354</t>
   </si>
   <si>
     <t xml:space="preserve">13.4518203735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3335628509521</t>
+    <t xml:space="preserve">13.3335609436035</t>
   </si>
   <si>
     <t xml:space="preserve">13.496166229248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3483428955078</t>
+    <t xml:space="preserve">13.3483448028564</t>
   </si>
   <si>
     <t xml:space="preserve">13.5405120849609</t>
@@ -2075,13 +2075,13 @@
     <t xml:space="preserve">12.9640064239502</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1857404708862</t>
+    <t xml:space="preserve">13.1857385635376</t>
   </si>
   <si>
     <t xml:space="preserve">13.1709575653076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.91965675354</t>
+    <t xml:space="preserve">12.919659614563</t>
   </si>
   <si>
     <t xml:space="preserve">13.274432182312</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">13.2892141342163</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2448663711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1266117095947</t>
+    <t xml:space="preserve">13.2448673248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1266107559204</t>
   </si>
   <si>
     <t xml:space="preserve">13.7622451782227</t>
@@ -2105,37 +2105,37 @@
     <t xml:space="preserve">13.9396324157715</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5552949905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7474632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9691944122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7770261764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.629207611084</t>
+    <t xml:space="preserve">13.5552940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7474641799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9691963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.777027130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6292057037354</t>
   </si>
   <si>
     <t xml:space="preserve">13.8657207489014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9544134140015</t>
+    <t xml:space="preserve">13.9544124603271</t>
   </si>
   <si>
     <t xml:space="preserve">13.4666004180908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4813842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4370365142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918100357056</t>
+    <t xml:space="preserve">13.4813823699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4370374679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918109893799</t>
   </si>
   <si>
     <t xml:space="preserve">13.9987602233887</t>
@@ -2153,13 +2153,13 @@
     <t xml:space="preserve">13.6587696075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6144218444824</t>
+    <t xml:space="preserve">13.6144227981567</t>
   </si>
   <si>
     <t xml:space="preserve">13.5257291793823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3631267547607</t>
+    <t xml:space="preserve">13.3631258010864</t>
   </si>
   <si>
     <t xml:space="preserve">13.2300844192505</t>
@@ -2177,22 +2177,22 @@
     <t xml:space="preserve">14.6343965530396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8191719055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0409069061279</t>
+    <t xml:space="preserve">14.8191738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0409088134766</t>
   </si>
   <si>
     <t xml:space="preserve">14.9300413131714</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039501190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3735084533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5582838058472</t>
+    <t xml:space="preserve">15.0039510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3735046386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5582857131958</t>
   </si>
   <si>
     <t xml:space="preserve">15.9278402328491</t>
@@ -2204,19 +2204,19 @@
     <t xml:space="preserve">16.0387077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7800168991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061052322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6321935653687</t>
+    <t xml:space="preserve">15.7800207138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.706109046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6321954727173</t>
   </si>
   <si>
     <t xml:space="preserve">15.5213289260864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4104642868042</t>
+    <t xml:space="preserve">15.4104633331299</t>
   </si>
   <si>
     <t xml:space="preserve">15.4474182128906</t>
@@ -2225,22 +2225,22 @@
     <t xml:space="preserve">15.2256870269775</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2626399993896</t>
+    <t xml:space="preserve">15.2626419067383</t>
   </si>
   <si>
     <t xml:space="preserve">15.8908853530884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9669952392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7378711700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8561315536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4126644134521</t>
+    <t xml:space="preserve">14.9669981002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7378721237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8561296463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4126625061035</t>
   </si>
   <si>
     <t xml:space="preserve">14.0874547958374</t>
@@ -2249,58 +2249,58 @@
     <t xml:space="preserve">14.3091888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5161380767822</t>
+    <t xml:space="preserve">14.5161371231079</t>
   </si>
   <si>
     <t xml:space="preserve">14.5309219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8257741928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.471001625061</t>
+    <t xml:space="preserve">11.8257751464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4710025787354</t>
   </si>
   <si>
     <t xml:space="preserve">9.87452125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2145118713379</t>
+    <t xml:space="preserve">10.2145137786865</t>
   </si>
   <si>
     <t xml:space="preserve">9.57887744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63800716400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1649751663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29801559448242</t>
+    <t xml:space="preserve">9.63800621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16497421264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29801464080811</t>
   </si>
   <si>
     <t xml:space="preserve">9.53453159332275</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65278816223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5545043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7023258209229</t>
+    <t xml:space="preserve">9.65278911590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5545053482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7023267745972</t>
   </si>
   <si>
     <t xml:space="preserve">10.5988512039185</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9388408660889</t>
+    <t xml:space="preserve">10.9388418197632</t>
   </si>
   <si>
     <t xml:space="preserve">10.7318906784058</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9018869400024</t>
+    <t xml:space="preserve">10.9018859863281</t>
   </si>
   <si>
     <t xml:space="preserve">11.2123136520386</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">10.9905796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.012752532959</t>
+    <t xml:space="preserve">11.0127515792847</t>
   </si>
   <si>
     <t xml:space="preserve">11.0718812942505</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">10.5175485610962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9462337493896</t>
+    <t xml:space="preserve">10.946231842041</t>
   </si>
   <si>
     <t xml:space="preserve">11.3749179840088</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2714405059814</t>
+    <t xml:space="preserve">11.2714424133301</t>
   </si>
   <si>
     <t xml:space="preserve">11.5301303863525</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">11.5153484344482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.73708152771</t>
+    <t xml:space="preserve">11.7370824813843</t>
   </si>
   <si>
     <t xml:space="preserve">12.128809928894</t>
@@ -2369,25 +2369,25 @@
     <t xml:space="preserve">12.431845664978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5648860931396</t>
+    <t xml:space="preserve">12.564887046814</t>
   </si>
   <si>
     <t xml:space="preserve">12.3801078796387</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4392366409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4096746444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7644472122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8974866867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8235731124878</t>
+    <t xml:space="preserve">12.4392375946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4096736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7644462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8974847793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8235750198364</t>
   </si>
   <si>
     <t xml:space="preserve">12.971396446228</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">13.5331211090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4739933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0896530151367</t>
+    <t xml:space="preserve">13.473991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.089653968811</t>
   </si>
   <si>
     <t xml:space="preserve">13.0600900650024</t>
@@ -2423,34 +2423,34 @@
     <t xml:space="preserve">13.2966060638428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2512531280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4521465301514</t>
+    <t xml:space="preserve">13.2512521743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4521455764771</t>
   </si>
   <si>
     <t xml:space="preserve">13.1353521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9962711334229</t>
+    <t xml:space="preserve">12.9962720870972</t>
   </si>
   <si>
     <t xml:space="preserve">13.1585330963135</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3980588912964</t>
+    <t xml:space="preserve">13.3980598449707</t>
   </si>
   <si>
     <t xml:space="preserve">13.2048931121826</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4212408065796</t>
+    <t xml:space="preserve">13.4212398529053</t>
   </si>
   <si>
     <t xml:space="preserve">13.5448665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4444198608398</t>
+    <t xml:space="preserve">13.4444189071655</t>
   </si>
   <si>
     <t xml:space="preserve">13.5294132232666</t>
@@ -2462,25 +2462,25 @@
     <t xml:space="preserve">13.1276254653931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0812654495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.934458732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8108329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9576377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2976112365723</t>
+    <t xml:space="preserve">13.0812644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9344577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8108320236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9576396942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2976121902466</t>
   </si>
   <si>
     <t xml:space="preserve">13.150806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3362464904785</t>
+    <t xml:space="preserve">13.3362455368042</t>
   </si>
   <si>
     <t xml:space="preserve">13.1894388198853</t>
@@ -2492,34 +2492,34 @@
     <t xml:space="preserve">12.5944843292236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7644720077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3285207748413</t>
+    <t xml:space="preserve">12.7644729614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3285188674927</t>
   </si>
   <si>
     <t xml:space="preserve">13.2126197814941</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4366931915283</t>
+    <t xml:space="preserve">13.436692237854</t>
   </si>
   <si>
     <t xml:space="preserve">13.6453132629395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9312019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5062303543091</t>
+    <t xml:space="preserve">13.9312000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.506233215332</t>
   </si>
   <si>
     <t xml:space="preserve">13.5216865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5371398925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8539333343506</t>
+    <t xml:space="preserve">13.5371389389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8539323806763</t>
   </si>
   <si>
     <t xml:space="preserve">13.8230266571045</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">14.0702791213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7843952178955</t>
+    <t xml:space="preserve">13.7843933105469</t>
   </si>
   <si>
     <t xml:space="preserve">13.6916732788086</t>
@@ -2543,55 +2543,55 @@
     <t xml:space="preserve">13.6221323013306</t>
   </si>
   <si>
-    <t xml:space="preserve">13.598952293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4675989151001</t>
+    <t xml:space="preserve">13.5989532470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4675998687744</t>
   </si>
   <si>
     <t xml:space="preserve">13.7148542404175</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5757722854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3053379058838</t>
+    <t xml:space="preserve">13.5757732391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3053398132324</t>
   </si>
   <si>
     <t xml:space="preserve">13.6298589706421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4753255844116</t>
+    <t xml:space="preserve">13.4753265380859</t>
   </si>
   <si>
     <t xml:space="preserve">13.792121887207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5680456161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4830532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8462047576904</t>
+    <t xml:space="preserve">13.5680446624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4830522537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8462057113647</t>
   </si>
   <si>
     <t xml:space="preserve">13.9234733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9543790817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5912256240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3671522140503</t>
+    <t xml:space="preserve">13.9543809890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5912265777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.367151260376</t>
   </si>
   <si>
     <t xml:space="preserve">13.5525932312012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7380332946777</t>
+    <t xml:space="preserve">13.7380342483521</t>
   </si>
   <si>
     <t xml:space="preserve">14.0007400512695</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">14.0780057907104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9389276504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8616600036621</t>
+    <t xml:space="preserve">13.938925743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8616609573364</t>
   </si>
   <si>
     <t xml:space="preserve">13.8384790420532</t>
@@ -2618,10 +2618,10 @@
     <t xml:space="preserve">14.0239200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0471000671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3329877853394</t>
+    <t xml:space="preserve">14.047101020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3329887390137</t>
   </si>
   <si>
     <t xml:space="preserve">14.1861810684204</t>
@@ -2633,19 +2633,19 @@
     <t xml:space="preserve">13.815299987793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6994018554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3130645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2667064666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2898864746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3748788833618</t>
+    <t xml:space="preserve">13.6993999481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3130655288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2667055130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2898855209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3748779296875</t>
   </si>
   <si>
     <t xml:space="preserve">13.166259765625</t>
@@ -2654,22 +2654,22 @@
     <t xml:space="preserve">13.7766666412354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7612113952637</t>
+    <t xml:space="preserve">13.7612142562866</t>
   </si>
   <si>
     <t xml:space="preserve">13.7998485565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5834989547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4907779693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5139589309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0161933898926</t>
+    <t xml:space="preserve">13.5834999084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907789230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5139598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0161914825439</t>
   </si>
   <si>
     <t xml:space="preserve">13.6375865936279</t>
@@ -2687,10 +2687,10 @@
     <t xml:space="preserve">12.8494644165039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7567453384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5867595672607</t>
+    <t xml:space="preserve">12.7567443847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5867586135864</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022109985352</t>
@@ -2702,37 +2702,37 @@
     <t xml:space="preserve">12.6872053146362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031053543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9267320632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1430797576904</t>
+    <t xml:space="preserve">12.8031044006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9267311096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1430788040161</t>
   </si>
   <si>
     <t xml:space="preserve">13.3207921981812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4135122299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4057855606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1817121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8417387008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8726453781128</t>
+    <t xml:space="preserve">13.4135131835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4057865142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1817111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.841739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8726444244385</t>
   </si>
   <si>
     <t xml:space="preserve">12.9190044403076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8571901321411</t>
+    <t xml:space="preserve">12.8571910858154</t>
   </si>
   <si>
     <t xml:space="preserve">12.6331186294556</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">12.7490177154541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1971654891968</t>
+    <t xml:space="preserve">13.1971645355225</t>
   </si>
   <si>
     <t xml:space="preserve">13.096718788147</t>
@@ -2753,16 +2753,16 @@
     <t xml:space="preserve">13.34397315979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9808177947998</t>
+    <t xml:space="preserve">13.2821588516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9808168411255</t>
   </si>
   <si>
     <t xml:space="preserve">12.718111038208</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7258377075195</t>
+    <t xml:space="preserve">12.7258386611938</t>
   </si>
   <si>
     <t xml:space="preserve">12.6408452987671</t>
@@ -2771,40 +2771,40 @@
     <t xml:space="preserve">12.6176652908325</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7103862762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4554052352905</t>
+    <t xml:space="preserve">12.7103853225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4554042816162</t>
   </si>
   <si>
     <t xml:space="preserve">12.8803720474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603189468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6839447021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9621057510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1398191452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3716220855713</t>
+    <t xml:space="preserve">13.5603179931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6839466094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9621076583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.139820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.371621131897</t>
   </si>
   <si>
     <t xml:space="preserve">14.4102535247803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5570621490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5338792800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4025259017944</t>
+    <t xml:space="preserve">14.5570602416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5338802337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4025268554688</t>
   </si>
   <si>
     <t xml:space="preserve">14.2402677536011</t>
@@ -2813,31 +2813,31 @@
     <t xml:space="preserve">14.2557229995728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3948001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5493326187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9588479995728</t>
+    <t xml:space="preserve">14.3947992324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5493335723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9588489532471</t>
   </si>
   <si>
     <t xml:space="preserve">15.1211080551147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8043165206909</t>
+    <t xml:space="preserve">14.8043155670166</t>
   </si>
   <si>
     <t xml:space="preserve">14.6343269348145</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7656803131104</t>
+    <t xml:space="preserve">14.7656812667847</t>
   </si>
   <si>
     <t xml:space="preserve">14.7579545974731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6806869506836</t>
+    <t xml:space="preserve">14.6806879043579</t>
   </si>
   <si>
     <t xml:space="preserve">14.5261535644531</t>
@@ -2849,10 +2849,10 @@
     <t xml:space="preserve">14.6420555114746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5725154876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6034202575684</t>
+    <t xml:space="preserve">14.5725145339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6034212112427</t>
   </si>
   <si>
     <t xml:space="preserve">14.5956926345825</t>
@@ -2864,19 +2864,19 @@
     <t xml:space="preserve">14.8352222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9974822998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1983766555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0824756622314</t>
+    <t xml:space="preserve">14.9974813461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1983757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0824747085571</t>
   </si>
   <si>
     <t xml:space="preserve">15.0283889770508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0979290008545</t>
+    <t xml:space="preserve">15.0979280471802</t>
   </si>
   <si>
     <t xml:space="preserve">15.1751937866211</t>
@@ -2885,13 +2885,13 @@
     <t xml:space="preserve">15.2061023712158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0747480392456</t>
+    <t xml:space="preserve">15.0747489929199</t>
   </si>
   <si>
     <t xml:space="preserve">14.8506736755371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8661270141602</t>
+    <t xml:space="preserve">14.8661260604858</t>
   </si>
   <si>
     <t xml:space="preserve">14.9743013381958</t>
@@ -2921,49 +2921,49 @@
     <t xml:space="preserve">15.6233406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7624235153198</t>
+    <t xml:space="preserve">15.7624216079712</t>
   </si>
   <si>
     <t xml:space="preserve">15.9169569015503</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0714912414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9787702560425</t>
+    <t xml:space="preserve">16.0714893341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9787683486938</t>
   </si>
   <si>
     <t xml:space="preserve">15.8860483169556</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9942255020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1796646118164</t>
+    <t xml:space="preserve">15.9942216873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1796627044678</t>
   </si>
   <si>
     <t xml:space="preserve">16.056037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3496513366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4578247070312</t>
+    <t xml:space="preserve">16.3496494293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.457820892334</t>
   </si>
   <si>
     <t xml:space="preserve">16.2651462554932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0564117431641</t>
+    <t xml:space="preserve">16.0564136505127</t>
   </si>
   <si>
     <t xml:space="preserve">15.8476781845093</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7834548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8717660903931</t>
+    <t xml:space="preserve">15.7834539413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8717641830444</t>
   </si>
   <si>
     <t xml:space="preserve">15.6871166229248</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">15.7112007141113</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7272567749023</t>
+    <t xml:space="preserve">15.7272548675537</t>
   </si>
   <si>
     <t xml:space="preserve">15.5907773971558</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">15.8557081222534</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7352848052979</t>
+    <t xml:space="preserve">15.7352828979492</t>
   </si>
   <si>
     <t xml:space="preserve">15.9119052886963</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">16.0162715911865</t>
   </si>
   <si>
-    <t xml:space="preserve">15.775426864624</t>
+    <t xml:space="preserve">15.7754259109497</t>
   </si>
   <si>
     <t xml:space="preserve">15.9921875</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">16.4096546173096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2009201049805</t>
+    <t xml:space="preserve">16.2009220123291</t>
   </si>
   <si>
     <t xml:space="preserve">16.3133144378662</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">16.0885257720947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0483837127686</t>
+    <t xml:space="preserve">16.0483856201172</t>
   </si>
   <si>
     <t xml:space="preserve">15.9841594696045</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">16.2972583770752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1527519226074</t>
+    <t xml:space="preserve">16.1527538299561</t>
   </si>
   <si>
     <t xml:space="preserve">15.8637361526489</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">15.1090850830078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9164094924927</t>
+    <t xml:space="preserve">14.916407585144</t>
   </si>
   <si>
     <t xml:space="preserve">14.8040142059326</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">14.9645757675171</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7478151321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8923234939575</t>
+    <t xml:space="preserve">14.7478170394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8923225402832</t>
   </si>
   <si>
     <t xml:space="preserve">14.8120422363281</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">14.8521823883057</t>
   </si>
   <si>
-    <t xml:space="preserve">15.101056098938</t>
+    <t xml:space="preserve">15.1010570526123</t>
   </si>
   <si>
     <t xml:space="preserve">14.6755619049072</t>
@@ -3146,13 +3146,13 @@
     <t xml:space="preserve">14.7879571914673</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1171131134033</t>
+    <t xml:space="preserve">15.117112159729</t>
   </si>
   <si>
     <t xml:space="preserve">15.2375354766846</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0930280685425</t>
+    <t xml:space="preserve">15.0930290222168</t>
   </si>
   <si>
     <t xml:space="preserve">15.2937326431274</t>
@@ -3179,22 +3179,22 @@
     <t xml:space="preserve">15.5345792770386</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1251411437988</t>
+    <t xml:space="preserve">15.1251401901245</t>
   </si>
   <si>
     <t xml:space="preserve">15.0769720077515</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1492261886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8441534042358</t>
+    <t xml:space="preserve">15.1492252349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8441543579102</t>
   </si>
   <si>
     <t xml:space="preserve">14.7076749801636</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6113367080688</t>
+    <t xml:space="preserve">14.6113376617432</t>
   </si>
   <si>
     <t xml:space="preserve">14.6595048904419</t>
@@ -3206,13 +3206,13 @@
     <t xml:space="preserve">14.3062648773193</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3544321060181</t>
+    <t xml:space="preserve">14.3544330596924</t>
   </si>
   <si>
     <t xml:space="preserve">14.5792226791382</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3464069366455</t>
+    <t xml:space="preserve">14.3464059829712</t>
   </si>
   <si>
     <t xml:space="preserve">14.3142929077148</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">14.6996469497681</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6193628311157</t>
+    <t xml:space="preserve">14.61936378479</t>
   </si>
   <si>
     <t xml:space="preserve">14.5551376342773</t>
@@ -3230,10 +3230,10 @@
     <t xml:space="preserve">14.5230255126953</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5471115112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273908615112</t>
+    <t xml:space="preserve">14.5471105575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273927688599</t>
   </si>
   <si>
     <t xml:space="preserve">14.8200693130493</t>
@@ -3242,10 +3242,10 @@
     <t xml:space="preserve">14.9244365692139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5711946487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3785181045532</t>
+    <t xml:space="preserve">14.5711936950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3785171508789</t>
   </si>
   <si>
     <t xml:space="preserve">14.2259817123413</t>
@@ -3257,13 +3257,13 @@
     <t xml:space="preserve">14.0493621826172</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1938695907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8326005935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7442903518677</t>
+    <t xml:space="preserve">14.193868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.744291305542</t>
   </si>
   <si>
     <t xml:space="preserve">13.8486566543579</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">13.5355567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5917539596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406276702881</t>
+    <t xml:space="preserve">13.5917530059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406286239624</t>
   </si>
   <si>
     <t xml:space="preserve">13.9690790176392</t>
@@ -3287,31 +3287,31 @@
     <t xml:space="preserve">14.3704881668091</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3303489685059</t>
+    <t xml:space="preserve">14.3303499221802</t>
   </si>
   <si>
     <t xml:space="preserve">14.2179536819458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8727407455444</t>
+    <t xml:space="preserve">13.8727416992188</t>
   </si>
   <si>
     <t xml:space="preserve">13.6479511260986</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2947101593018</t>
+    <t xml:space="preserve">13.2947092056274</t>
   </si>
   <si>
     <t xml:space="preserve">13.5114717483521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034427642822</t>
+    <t xml:space="preserve">13.5034437179565</t>
   </si>
   <si>
     <t xml:space="preserve">13.2465400695801</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4151334762573</t>
+    <t xml:space="preserve">13.415132522583</t>
   </si>
   <si>
     <t xml:space="preserve">13.3187952041626</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">12.604284286499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0137214660645</t>
+    <t xml:space="preserve">13.0137224197388</t>
   </si>
   <si>
     <t xml:space="preserve">13.3589353561401</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">12.8210458755493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6363973617554</t>
+    <t xml:space="preserve">12.6363964080811</t>
   </si>
   <si>
     <t xml:space="preserve">12.9735822677612</t>
@@ -3371,13 +3371,13 @@
     <t xml:space="preserve">12.9093561172485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8772449493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1421737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2706251144409</t>
+    <t xml:space="preserve">12.8772439956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1421747207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2706260681152</t>
   </si>
   <si>
     <t xml:space="preserve">13.5516128540039</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">13.7202062606812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.009220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8807697296143</t>
+    <t xml:space="preserve">14.0092191696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8807687759399</t>
   </si>
   <si>
     <t xml:space="preserve">13.5596408843994</t>
@@ -3425,22 +3425,22 @@
     <t xml:space="preserve">13.0297794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.102032661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0940036773682</t>
+    <t xml:space="preserve">13.1020317077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0940046310425</t>
   </si>
   <si>
     <t xml:space="preserve">12.9494962692261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7487926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8852701187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.524001121521</t>
+    <t xml:space="preserve">12.7487916946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8852710723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5240020751953</t>
   </si>
   <si>
     <t xml:space="preserve">12.6444253921509</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">12.804988861084</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9254140853882</t>
+    <t xml:space="preserve">12.9254131317139</t>
   </si>
   <si>
     <t xml:space="preserve">13.1341466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9816102981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.463303565979</t>
+    <t xml:space="preserve">12.9816093444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4633026123047</t>
   </si>
   <si>
     <t xml:space="preserve">13.5837249755859</t>
@@ -3473,13 +3473,13 @@
     <t xml:space="preserve">13.3268232345581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2063999176025</t>
+    <t xml:space="preserve">13.2064008712769</t>
   </si>
   <si>
     <t xml:space="preserve">13.2786540985107</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6845674514771</t>
+    <t xml:space="preserve">12.6845664978027</t>
   </si>
   <si>
     <t xml:space="preserve">12.4838619232178</t>
@@ -5352,6 +5352,9 @@
   </si>
   <si>
     <t xml:space="preserve">20.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4200000762939</t>
   </si>
 </sst>
 </file>
@@ -70430,7 +70433,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6494560185</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>40856</v>
@@ -70451,6 +70454,32 @@
         <v>1779</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6494444444</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>61674</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>20.4599990844727</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>20.1399993896484</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>20.4200000762939</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>20.4200000762939</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1780</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">ACE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61100959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3010368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43742370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48082065582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61720752716064</t>
+    <t xml:space="preserve">8.61100769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30103588104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.437424659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48082160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61720657348633</t>
   </si>
   <si>
     <t xml:space="preserve">8.80319023132324</t>
@@ -77,25 +77,25 @@
     <t xml:space="preserve">7.91667222976685</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97246646881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13985157012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15225028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27623844146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38782787322998</t>
+    <t xml:space="preserve">7.97246599197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13985252380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15224838256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2762393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3878288269043</t>
   </si>
   <si>
     <t xml:space="preserve">8.49321937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50561809539795</t>
+    <t xml:space="preserve">8.50561714172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.39402770996094</t>
@@ -104,85 +104,85 @@
     <t xml:space="preserve">8.36923027038574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33203315734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99106502532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5943021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45791387557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3153281211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46411323547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66869497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63149833679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65629577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65009641647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44551515579224</t>
+    <t xml:space="preserve">8.33203220367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99106645584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59430265426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45791530609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31532669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46411371231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6686954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63149881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65629482269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65009737014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44551563262939</t>
   </si>
   <si>
     <t xml:space="preserve">7.600501537323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6810941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55090570449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68729209899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60670185089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73688745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64389657974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57570505142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53230714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01586246490479</t>
+    <t xml:space="preserve">7.68109464645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55090618133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68729257583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6067008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73688936233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64389705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57570219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53230667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0158634185791</t>
   </si>
   <si>
     <t xml:space="preserve">8.38162994384766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67920112609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77219295501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76599597930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83418655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78459167480469</t>
+    <t xml:space="preserve">8.67920207977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77219390869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76599407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83418560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.784592628479</t>
   </si>
   <si>
     <t xml:space="preserve">8.46842098236084</t>
@@ -194,70 +194,70 @@
     <t xml:space="preserve">8.33823299407959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45602130889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49941825866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58621215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43122386932373</t>
+    <t xml:space="preserve">8.45602226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49941921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58621025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43122577667236</t>
   </si>
   <si>
     <t xml:space="preserve">8.40642738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34443283081055</t>
+    <t xml:space="preserve">8.34443378448486</t>
   </si>
   <si>
     <t xml:space="preserve">8.4746208190918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24524116516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90427398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87327718734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73069000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79268264770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85467767715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89807367324829</t>
+    <t xml:space="preserve">8.24524211883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90427350997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8732762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73068952560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79268217086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85467720031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89807319641113</t>
   </si>
   <si>
     <t xml:space="preserve">7.9600682258606</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04686069488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99726486206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96626758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86707592010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78028440475464</t>
+    <t xml:space="preserve">8.04685974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99726438522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96626806259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86707735061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78028631210327</t>
   </si>
   <si>
     <t xml:space="preserve">8.090256690979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11505508422852</t>
+    <t xml:space="preserve">8.1150541305542</t>
   </si>
   <si>
     <t xml:space="preserve">8.17704772949219</t>
@@ -272,43 +272,43 @@
     <t xml:space="preserve">7.82988023757935</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04065990447998</t>
+    <t xml:space="preserve">8.04066181182861</t>
   </si>
   <si>
     <t xml:space="preserve">8.00966358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09645462036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19564723968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23284244537354</t>
+    <t xml:space="preserve">8.09645557403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19564628601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23284339904785</t>
   </si>
   <si>
     <t xml:space="preserve">8.18324756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05925941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7616868019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5261082649231</t>
+    <t xml:space="preserve">8.05925846099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76168632507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52610778808594</t>
   </si>
   <si>
     <t xml:space="preserve">7.56330490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42071771621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19133901596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85656929016113</t>
+    <t xml:space="preserve">7.42071914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19133853912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85656976699829</t>
   </si>
   <si>
     <t xml:space="preserve">6.96815919876099</t>
@@ -317,82 +317,82 @@
     <t xml:space="preserve">6.97435855865479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12314462661743</t>
+    <t xml:space="preserve">7.12314510345459</t>
   </si>
   <si>
     <t xml:space="preserve">7.09073734283447</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05184984207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14259052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05833101272583</t>
+    <t xml:space="preserve">7.05184841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1425895690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05833053588867</t>
   </si>
   <si>
     <t xml:space="preserve">6.6824049949646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37777471542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49444150924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61110877990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08425617218018</t>
+    <t xml:space="preserve">6.37777519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49444198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61110782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08425664901733</t>
   </si>
   <si>
     <t xml:space="preserve">6.99999666213989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03888559341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93518114089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78610754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370121002197</t>
+    <t xml:space="preserve">7.03888654708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93518257141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78610897064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370073318481</t>
   </si>
   <si>
     <t xml:space="preserve">6.82499694824219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86388683319092</t>
+    <t xml:space="preserve">6.8638858795166</t>
   </si>
   <si>
     <t xml:space="preserve">6.7407374382019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91573810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89629459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15555286407471</t>
+    <t xml:space="preserve">6.91573858261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92869997024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8962926864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15555334091187</t>
   </si>
   <si>
     <t xml:space="preserve">7.14907073974609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58333015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55740308761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06944179534912</t>
+    <t xml:space="preserve">7.5833306312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55740404129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0694408416748</t>
   </si>
   <si>
     <t xml:space="preserve">8.0435152053833</t>
@@ -407,67 +407,67 @@
     <t xml:space="preserve">8.17962646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07592296600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05647754669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10184764862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95277500152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82962608337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87499666213989</t>
+    <t xml:space="preserve">8.0759220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05647850036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10184860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95277404785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82962560653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87499570846558</t>
   </si>
   <si>
     <t xml:space="preserve">7.90740346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76481151580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75832939147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7453670501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77129364013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71944189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57684898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.654625415802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70647859573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81666374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79073715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69351434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72592210769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69999837875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50555276870728</t>
+    <t xml:space="preserve">7.76481056213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75833082199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74536609649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77129220962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71944141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57684803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65462636947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70647811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81666421890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79073810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69351625442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72592306137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69999647140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50555229187012</t>
   </si>
   <si>
     <t xml:space="preserve">7.37592220306396</t>
@@ -476,76 +476,76 @@
     <t xml:space="preserve">7.39536714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3240704536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25277376174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22684764862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18147850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20092296600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22036647796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18795967102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16851615905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16203498840332</t>
+    <t xml:space="preserve">7.47314596176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32407188415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25277328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22684860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18147802352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20092344284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22036695480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18796014785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16851472854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.162034034729</t>
   </si>
   <si>
     <t xml:space="preserve">7.19444179534912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17499732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07129287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96758890151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04536771774292</t>
+    <t xml:space="preserve">7.17499589920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07129335403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96759033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0453667640686</t>
   </si>
   <si>
     <t xml:space="preserve">6.98703384399414</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23332929611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34999799728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41481113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55092239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52499580383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64166307449341</t>
+    <t xml:space="preserve">7.23333072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34999752044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41481065750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55092191696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52499723434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64166259765625</t>
   </si>
   <si>
     <t xml:space="preserve">7.59629344940186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61573791503906</t>
+    <t xml:space="preserve">7.61573696136475</t>
   </si>
   <si>
     <t xml:space="preserve">7.64814519882202</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">7.49258899688721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38888549804688</t>
+    <t xml:space="preserve">7.38888502120972</t>
   </si>
   <si>
     <t xml:space="preserve">7.46018218994141</t>
@@ -563,121 +563,121 @@
     <t xml:space="preserve">7.36944150924683</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30462694168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84444189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57221937179565</t>
+    <t xml:space="preserve">7.30462646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84444141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57221984863281</t>
   </si>
   <si>
     <t xml:space="preserve">6.59166383743286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54629421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48147964477539</t>
+    <t xml:space="preserve">6.54629278182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48147916793823</t>
   </si>
   <si>
     <t xml:space="preserve">6.43610858917236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47823810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52684831619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64999723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53332996368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59814596176147</t>
+    <t xml:space="preserve">6.47823762893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5268497467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64999675750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5333309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59814500808716</t>
   </si>
   <si>
     <t xml:space="preserve">6.52036762237549</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42962646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87036752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10369968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25925540924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48610830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4342565536499</t>
+    <t xml:space="preserve">6.42962741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87036800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10370111465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25925636291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48610782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43425703048706</t>
   </si>
   <si>
     <t xml:space="preserve">7.42777442932129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38240480422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51851558685303</t>
+    <t xml:space="preserve">7.38240528106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851511001587</t>
   </si>
   <si>
     <t xml:space="preserve">7.51203346252441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66758966445923</t>
+    <t xml:space="preserve">7.66758871078491</t>
   </si>
   <si>
     <t xml:space="preserve">7.68055200576782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71295976638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89444017410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79721927642822</t>
+    <t xml:space="preserve">7.71295785903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89444208145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79721879959106</t>
   </si>
   <si>
     <t xml:space="preserve">7.84258985519409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34351444244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40184831619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46666383743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40833044052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73888492584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68703413009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62221813201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63518238067627</t>
+    <t xml:space="preserve">7.34351539611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40184879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46666431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40833139419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73888540267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68703365325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62221908569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63518190383911</t>
   </si>
   <si>
     <t xml:space="preserve">7.7324047088623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77777481079102</t>
+    <t xml:space="preserve">7.7777738571167</t>
   </si>
   <si>
     <t xml:space="preserve">7.83610725402832</t>
@@ -686,46 +686,46 @@
     <t xml:space="preserve">7.7518482208252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62870073318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97221851348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85555219650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9268479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.037034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09536743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13425540924072</t>
+    <t xml:space="preserve">7.62870168685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97221946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85555267333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92684841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03703308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09536647796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13425636291504</t>
   </si>
   <si>
     <t xml:space="preserve">8.20555305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28981113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24444007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147869110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22499561309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27036762237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46481132507324</t>
+    <t xml:space="preserve">8.28981018066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24443912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147773742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22499656677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27036666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46481037139893</t>
   </si>
   <si>
     <t xml:space="preserve">8.45833015441895</t>
@@ -734,28 +734,28 @@
     <t xml:space="preserve">8.43240451812744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42592239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3546257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55555057525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52314472198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39351463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47129249572754</t>
+    <t xml:space="preserve">8.42592334747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35462665557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55555152893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52314281463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39351367950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47129344940186</t>
   </si>
   <si>
     <t xml:space="preserve">8.60740375518799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61388492584229</t>
+    <t xml:space="preserve">8.61388301849365</t>
   </si>
   <si>
     <t xml:space="preserve">8.62036609649658</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">8.80832862854004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6786994934082</t>
+    <t xml:space="preserve">8.67870044708252</t>
   </si>
   <si>
     <t xml:space="preserve">8.81481170654297</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">8.92499732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12592220306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17777347564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00277328491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9509220123291</t>
+    <t xml:space="preserve">9.1259241104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17777252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00277519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95092296600342</t>
   </si>
   <si>
     <t xml:space="preserve">8.99629211425781</t>
@@ -800,34 +800,34 @@
     <t xml:space="preserve">9.01573657989502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02869892120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20369911193848</t>
+    <t xml:space="preserve">9.02869987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20370006561279</t>
   </si>
   <si>
     <t xml:space="preserve">9.2814769744873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30740356445312</t>
+    <t xml:space="preserve">9.30740261077881</t>
   </si>
   <si>
     <t xml:space="preserve">9.34629249572754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43703174591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32684803009033</t>
+    <t xml:space="preserve">9.43703365325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32684898376465</t>
   </si>
   <si>
     <t xml:space="preserve">9.43055057525635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38518047332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41758823394775</t>
+    <t xml:space="preserve">9.38518142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41758918762207</t>
   </si>
   <si>
     <t xml:space="preserve">9.33332920074463</t>
@@ -836,52 +836,52 @@
     <t xml:space="preserve">9.5018482208252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50833034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44351387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54721832275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41110610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35925579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51501655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41343307495117</t>
+    <t xml:space="preserve">9.50832748413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44351482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54721736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41110706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35925483703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51501750946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41343212127686</t>
   </si>
   <si>
     <t xml:space="preserve">9.59628391265869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50147247314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44729423522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48115634918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21026611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09513854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14931583404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98678112030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83101844787598</t>
+    <t xml:space="preserve">9.50147342681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44729328155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48115539550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21026515960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09513664245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14931488037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98678207397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83102035522461</t>
   </si>
   <si>
     <t xml:space="preserve">8.84456348419189</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">8.93937587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81070232391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93260383605957</t>
+    <t xml:space="preserve">8.81070137023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93260192871094</t>
   </si>
   <si>
     <t xml:space="preserve">9.04095935821533</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">8.87165355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04773044586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08159351348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10190868377686</t>
+    <t xml:space="preserve">9.0477294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08159255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10190963745117</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349311828613</t>
@@ -917,13 +917,13 @@
     <t xml:space="preserve">9.10868167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12222576141357</t>
+    <t xml:space="preserve">9.12222671508789</t>
   </si>
   <si>
     <t xml:space="preserve">9.0070972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07481956481934</t>
+    <t xml:space="preserve">9.07482051849365</t>
   </si>
   <si>
     <t xml:space="preserve">8.87842464447021</t>
@@ -935,46 +935,46 @@
     <t xml:space="preserve">8.90551376342773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52626800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58721733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54658508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56012916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68880081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53981113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44499969482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33664512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47208881378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47886180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41113948822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4246826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38405132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3908224105835</t>
+    <t xml:space="preserve">8.52626705169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58721923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54658317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5601282119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68880176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53981304168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44500064849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33664608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47209072113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47886085510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4111385345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42468357086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38404941558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39082336425781</t>
   </si>
   <si>
     <t xml:space="preserve">8.32987213134766</t>
@@ -986,46 +986,46 @@
     <t xml:space="preserve">8.26892185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24860668182373</t>
+    <t xml:space="preserve">8.24860572814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.19442749023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16733932495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21474456787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37050628662109</t>
+    <t xml:space="preserve">8.16733837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21474361419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37050533294678</t>
   </si>
   <si>
     <t xml:space="preserve">8.29601097106934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39759349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81747436523438</t>
+    <t xml:space="preserve">8.3975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81747531890869</t>
   </si>
   <si>
     <t xml:space="preserve">8.97323608398438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76329708099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67525863647461</t>
+    <t xml:space="preserve">8.76329612731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67525672912598</t>
   </si>
   <si>
     <t xml:space="preserve">8.68202877044678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69557476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80393028259277</t>
+    <t xml:space="preserve">8.6955738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80392932891846</t>
   </si>
   <si>
     <t xml:space="preserve">8.8581075668335</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">8.74298000335693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74975204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79038524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88519763946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96646404266357</t>
+    <t xml:space="preserve">8.74975299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79038619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88519668579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96646308898926</t>
   </si>
   <si>
     <t xml:space="preserve">8.91228580474854</t>
@@ -1052,19 +1052,19 @@
     <t xml:space="preserve">8.89196968078613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18317604064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19672107696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29153347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24412727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36602783203125</t>
+    <t xml:space="preserve">9.18317699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19672012329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29153156280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24412536621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36602687835693</t>
   </si>
   <si>
     <t xml:space="preserve">9.40666103363037</t>
@@ -1073,91 +1073,91 @@
     <t xml:space="preserve">9.54210472106934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46761035919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38634586334229</t>
+    <t xml:space="preserve">9.46761131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38634395599365</t>
   </si>
   <si>
     <t xml:space="preserve">9.52178955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49469947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84008502960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86717414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88749027252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83331394195557</t>
+    <t xml:space="preserve">9.49470043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84008407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86717319488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88749122619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83331298828125</t>
   </si>
   <si>
     <t xml:space="preserve">9.76558971405029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74527549743652</t>
+    <t xml:space="preserve">9.74527454376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.70463943481445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58273887634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71818351745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67077827453613</t>
+    <t xml:space="preserve">9.58274078369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71818447113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67077922821045</t>
   </si>
   <si>
     <t xml:space="preserve">9.96875858306885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94844150543213</t>
+    <t xml:space="preserve">9.94844055175781</t>
   </si>
   <si>
     <t xml:space="preserve">9.91458034515381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0161628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96198654174805</t>
+    <t xml:space="preserve">10.0161638259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96198558807373</t>
   </si>
   <si>
     <t xml:space="preserve">9.92135238647461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90103530883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2599649429321</t>
+    <t xml:space="preserve">9.90103626251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2599639892578</t>
   </si>
   <si>
     <t xml:space="preserve">11.4451093673706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5670108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4857406616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5128316879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518823623657</t>
+    <t xml:space="preserve">11.5670099258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4857416152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5128326416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518814086914</t>
   </si>
   <si>
     <t xml:space="preserve">11.4383363723755</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4992876052856</t>
+    <t xml:space="preserve">11.4992866516113</t>
   </si>
   <si>
     <t xml:space="preserve">11.3502979278564</t>
@@ -1166,64 +1166,64 @@
     <t xml:space="preserve">11.0726356506348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9845952987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8762397766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1674480438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8152914047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5850324630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4495887756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.564715385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5444002151489</t>
+    <t xml:space="preserve">10.9845962524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.876238822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1674470901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5850343704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4495878219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5647163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5443992614746</t>
   </si>
   <si>
     <t xml:space="preserve">10.429271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4699048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.632438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8220615386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9168729782104</t>
+    <t xml:space="preserve">10.4699039459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6324377059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.822060585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9168739318848</t>
   </si>
   <si>
     <t xml:space="preserve">10.9913682937622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8017454147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7204780578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6256656646729</t>
+    <t xml:space="preserve">10.8017444610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.720477104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6256666183472</t>
   </si>
   <si>
     <t xml:space="preserve">10.6730728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8356065750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9371900558472</t>
+    <t xml:space="preserve">10.8356075286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9371891021729</t>
   </si>
   <si>
     <t xml:space="preserve">10.9981412887573</t>
@@ -1232,34 +1232,34 @@
     <t xml:space="preserve">11.0455455780029</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1268129348755</t>
+    <t xml:space="preserve">11.1268138885498</t>
   </si>
   <si>
     <t xml:space="preserve">10.9304170608521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8423805236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7746562957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7340221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5918054580688</t>
+    <t xml:space="preserve">10.842378616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7746553421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7340230941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5918064117432</t>
   </si>
   <si>
     <t xml:space="preserve">10.5376262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5173120498657</t>
+    <t xml:space="preserve">10.5173110961914</t>
   </si>
   <si>
     <t xml:space="preserve">10.3615493774414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0974311828613</t>
+    <t xml:space="preserve">10.097430229187</t>
   </si>
   <si>
     <t xml:space="preserve">9.87394618988037</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">10.1922426223755</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92812442779541</t>
+    <t xml:space="preserve">9.92812347412109</t>
   </si>
   <si>
     <t xml:space="preserve">10.0364809036255</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">10.0567970275879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1245212554932</t>
+    <t xml:space="preserve">10.1245193481445</t>
   </si>
   <si>
     <t xml:space="preserve">10.0838861465454</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">9.44052124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64369010925293</t>
+    <t xml:space="preserve">9.64368915557861</t>
   </si>
   <si>
     <t xml:space="preserve">9.66400718688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67755031585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083831787109</t>
+    <t xml:space="preserve">9.67755126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083927154541</t>
   </si>
   <si>
     <t xml:space="preserve">9.55564975738525</t>
@@ -1316,10 +1316,10 @@
     <t xml:space="preserve">9.21703720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13576889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23058223724365</t>
+    <t xml:space="preserve">9.13576984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23058128356934</t>
   </si>
   <si>
     <t xml:space="preserve">9.06804847717285</t>
@@ -1328,58 +1328,58 @@
     <t xml:space="preserve">9.17640495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3321647644043</t>
+    <t xml:space="preserve">9.33216667175293</t>
   </si>
   <si>
     <t xml:space="preserve">9.27798748016357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23735523223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1628589630127</t>
+    <t xml:space="preserve">9.23735618591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16285800933838</t>
   </si>
   <si>
     <t xml:space="preserve">9.29830360412598</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42697715759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53533363342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62337398529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79945182800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80622386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77236270904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95521354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81976699829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75881767272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47438335418701</t>
+    <t xml:space="preserve">9.42697811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53533458709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62337303161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79945087432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80622291564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77236175537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95521259307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81976890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75881862640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47438144683838</t>
   </si>
   <si>
     <t xml:space="preserve">9.71141242980957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30507564544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0138692855835</t>
+    <t xml:space="preserve">9.30507755279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01387023925781</t>
   </si>
   <si>
     <t xml:space="preserve">8.79715824127197</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">9.03418731689453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39311599731445</t>
+    <t xml:space="preserve">9.39311504364014</t>
   </si>
   <si>
     <t xml:space="preserve">9.26281547546387</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">9.07117080688477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03567981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99309253692627</t>
+    <t xml:space="preserve">9.03568077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99309349060059</t>
   </si>
   <si>
     <t xml:space="preserve">9.04277896881104</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">9.19183540344238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27701091766357</t>
+    <t xml:space="preserve">9.27700901031494</t>
   </si>
   <si>
     <t xml:space="preserve">9.39767551422119</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">9.2131290435791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10665988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12795448303223</t>
+    <t xml:space="preserve">9.10666084289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12795543670654</t>
   </si>
   <si>
     <t xml:space="preserve">9.22732543945312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26991271972656</t>
+    <t xml:space="preserve">9.26991367340088</t>
   </si>
   <si>
     <t xml:space="preserve">9.12085628509521</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">9.17763996124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38348007202148</t>
+    <t xml:space="preserve">9.3834810256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.44026374816895</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">9.4118709564209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60351657867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7028865814209</t>
+    <t xml:space="preserve">9.603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70288753509521</t>
   </si>
   <si>
     <t xml:space="preserve">9.56092834472656</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">9.57512378692627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66029930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53253746032715</t>
+    <t xml:space="preserve">9.66029834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53253555297852</t>
   </si>
   <si>
     <t xml:space="preserve">9.45445823669434</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">9.3054027557373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34799098968506</t>
+    <t xml:space="preserve">9.34799003601074</t>
   </si>
   <si>
     <t xml:space="preserve">9.28410816192627</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">8.8227424621582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71627426147461</t>
+    <t xml:space="preserve">8.71627330780029</t>
   </si>
   <si>
     <t xml:space="preserve">8.68078231811523</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">8.78725242614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97889614105225</t>
+    <t xml:space="preserve">8.97889709472656</t>
   </si>
   <si>
     <t xml:space="preserve">9.01438617706299</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">9.14214992523193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23442363739014</t>
+    <t xml:space="preserve">9.23442268371582</t>
   </si>
   <si>
     <t xml:space="preserve">9.29830455780029</t>
@@ -1541,22 +1541,22 @@
     <t xml:space="preserve">9.39057731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42606639862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37638187408447</t>
+    <t xml:space="preserve">9.42606735229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37638092041016</t>
   </si>
   <si>
     <t xml:space="preserve">9.16344356536865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04987621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17054271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74466419219971</t>
+    <t xml:space="preserve">9.04987812042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17054176330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74466514587402</t>
   </si>
   <si>
     <t xml:space="preserve">8.69497871398926</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">8.51043224334717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48204231262207</t>
+    <t xml:space="preserve">8.48204135894775</t>
   </si>
   <si>
     <t xml:space="preserve">8.39686679840088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59560871124268</t>
+    <t xml:space="preserve">8.59560680389404</t>
   </si>
   <si>
     <t xml:space="preserve">8.49623680114746</t>
@@ -1580,22 +1580,22 @@
     <t xml:space="preserve">8.26910209655762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26200389862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22651481628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04196739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06326198577881</t>
+    <t xml:space="preserve">8.26200485229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2265157699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04196834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06326293945312</t>
   </si>
   <si>
     <t xml:space="preserve">8.07036018371582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93549966812134</t>
+    <t xml:space="preserve">7.93549823760986</t>
   </si>
   <si>
     <t xml:space="preserve">8.1484375</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">8.16263389587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24071025848389</t>
+    <t xml:space="preserve">8.2407112121582</t>
   </si>
   <si>
     <t xml:space="preserve">8.28329849243164</t>
@@ -1613,10 +1613,10 @@
     <t xml:space="preserve">8.38267040252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36137580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50333404541016</t>
+    <t xml:space="preserve">8.3613748550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50333499908447</t>
   </si>
   <si>
     <t xml:space="preserve">8.42525768280029</t>
@@ -1625,28 +1625,28 @@
     <t xml:space="preserve">9.15634536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08536720275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06407260894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8085470199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81564331054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65948867797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56012058258057</t>
+    <t xml:space="preserve">9.08536624908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06407356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80854606628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81564426422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65948963165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56011867523193</t>
   </si>
   <si>
     <t xml:space="preserve">8.57431411743164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44655132293701</t>
+    <t xml:space="preserve">8.4465503692627</t>
   </si>
   <si>
     <t xml:space="preserve">8.52462959289551</t>
@@ -1655,37 +1655,37 @@
     <t xml:space="preserve">8.51753044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40396499633789</t>
+    <t xml:space="preserve">8.40396404266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.36847400665283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43945407867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21231842041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80144786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60980415344238</t>
+    <t xml:space="preserve">8.439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21232032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80144882202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60980319976807</t>
   </si>
   <si>
     <t xml:space="preserve">8.3400821685791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19812297821045</t>
+    <t xml:space="preserve">8.19812393188477</t>
   </si>
   <si>
     <t xml:space="preserve">8.37557315826416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46074771881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62400054931641</t>
+    <t xml:space="preserve">8.46074867248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62399959564209</t>
   </si>
   <si>
     <t xml:space="preserve">8.38976860046387</t>
@@ -1694,46 +1694,46 @@
     <t xml:space="preserve">8.5317268371582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68788146972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83693695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85823154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90791702270508</t>
+    <t xml:space="preserve">8.68788051605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83693790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85823249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90791797637939</t>
   </si>
   <si>
     <t xml:space="preserve">9.25571632385254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51124286651611</t>
+    <t xml:space="preserve">9.5112419128418</t>
   </si>
   <si>
     <t xml:space="preserve">9.58222198486328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47575283050537</t>
+    <t xml:space="preserve">9.47575378417969</t>
   </si>
   <si>
     <t xml:space="preserve">9.35508823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54673290252686</t>
+    <t xml:space="preserve">9.54673194885254</t>
   </si>
   <si>
     <t xml:space="preserve">9.66739749908447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6106128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63190746307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51834106445312</t>
+    <t xml:space="preserve">9.61061382293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63190841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51834011077881</t>
   </si>
   <si>
     <t xml:space="preserve">9.68869113922119</t>
@@ -1742,46 +1742,46 @@
     <t xml:space="preserve">9.90872859954834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85904121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88033580780029</t>
+    <t xml:space="preserve">9.85904216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88033485412598</t>
   </si>
   <si>
     <t xml:space="preserve">9.75967121124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86613941192627</t>
+    <t xml:space="preserve">9.86614036560059</t>
   </si>
   <si>
     <t xml:space="preserve">9.85194396972656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0222940444946</t>
+    <t xml:space="preserve">10.0222949981689</t>
   </si>
   <si>
     <t xml:space="preserve">10.2423315048218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3275051116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.611424446106</t>
+    <t xml:space="preserve">10.3275060653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6114234924316</t>
   </si>
   <si>
     <t xml:space="preserve">10.7604808807373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6398153305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6824045181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6043262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7107963562012</t>
+    <t xml:space="preserve">10.6398143768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6824035644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6043252944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7107954025269</t>
   </si>
   <si>
     <t xml:space="preserve">10.6895017623901</t>
@@ -1790,34 +1790,34 @@
     <t xml:space="preserve">10.774676322937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7249908447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.788872718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7533836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7391872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178936004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6965999603271</t>
+    <t xml:space="preserve">10.7249917984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7888717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7533826828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7391881942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178926467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6965990066528</t>
   </si>
   <si>
     <t xml:space="preserve">10.9166355133057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3567085266113</t>
+    <t xml:space="preserve">11.356707572937</t>
   </si>
   <si>
     <t xml:space="preserve">11.370903968811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4986686706543</t>
+    <t xml:space="preserve">11.49866771698</t>
   </si>
   <si>
     <t xml:space="preserve">11.3141202926636</t>
@@ -1826,43 +1826,43 @@
     <t xml:space="preserve">11.4418840408325</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4276885986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2999248504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1579656600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9876146316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0018110275269</t>
+    <t xml:space="preserve">11.4276876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2999238967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1579666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9876136779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0018100738525</t>
   </si>
   <si>
     <t xml:space="preserve">11.1863574981689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3850994110107</t>
+    <t xml:space="preserve">11.3851013183594</t>
   </si>
   <si>
     <t xml:space="preserve">11.4134912490845</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4844722747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4702758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6122350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5412540435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8535623550415</t>
+    <t xml:space="preserve">11.484471321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4702739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6122331619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5412549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8535642623901</t>
   </si>
   <si>
     <t xml:space="preserve">11.938738822937</t>
@@ -1871,10 +1871,10 @@
     <t xml:space="preserve">12.1090898513794</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9813270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8677577972412</t>
+    <t xml:space="preserve">11.9813251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8677606582642</t>
   </si>
   <si>
     <t xml:space="preserve">11.8251724243164</t>
@@ -1886,34 +1886,34 @@
     <t xml:space="preserve">11.6832122802734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7967805862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8961505889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9103479385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8393678665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8819532394409</t>
+    <t xml:space="preserve">11.796781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8961524963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9103488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8393669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8819551467896</t>
   </si>
   <si>
     <t xml:space="preserve">11.8109760284424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0665016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1942653656006</t>
+    <t xml:space="preserve">12.066502571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1942644119263</t>
   </si>
   <si>
     <t xml:space="preserve">12.2794399261475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3078336715698</t>
+    <t xml:space="preserve">12.3078308105469</t>
   </si>
   <si>
     <t xml:space="preserve">12.3504180908203</t>
@@ -1922,13 +1922,13 @@
     <t xml:space="preserve">12.4355955123901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5065746307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.520770072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5349655151367</t>
+    <t xml:space="preserve">12.5065755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5207691192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5349674224854</t>
   </si>
   <si>
     <t xml:space="preserve">12.5917501449585</t>
@@ -1937,10 +1937,10 @@
     <t xml:space="preserve">12.66273021698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6343374252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7053155899048</t>
+    <t xml:space="preserve">12.6343364715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7053174972534</t>
   </si>
   <si>
     <t xml:space="preserve">12.8161840438843</t>
@@ -1949,28 +1949,28 @@
     <t xml:space="preserve">12.668360710144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6387977600098</t>
+    <t xml:space="preserve">12.6387968063354</t>
   </si>
   <si>
     <t xml:space="preserve">12.3874988555908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3727149963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.313588142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4466276168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.80140209198</t>
+    <t xml:space="preserve">12.3727178573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3135871887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4466285705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8014011383057</t>
   </si>
   <si>
     <t xml:space="preserve">12.7274904251099</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5353202819824</t>
+    <t xml:space="preserve">12.5353212356567</t>
   </si>
   <si>
     <t xml:space="preserve">12.5796689987183</t>
@@ -1979,49 +1979,49 @@
     <t xml:space="preserve">12.7422733306885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6831426620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8753128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7866182327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7718381881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8309659957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.934440612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6979265213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7127075195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5944499969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9048748016357</t>
+    <t xml:space="preserve">12.6831436157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8753118515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7866191864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7718372344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8309669494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9344415664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7127084732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944509506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9048757553101</t>
   </si>
   <si>
     <t xml:space="preserve">12.8457469940186</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8900957107544</t>
+    <t xml:space="preserve">12.8900938034058</t>
   </si>
   <si>
     <t xml:space="preserve">13.0674819946289</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1118288040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0526990890503</t>
+    <t xml:space="preserve">13.1118278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.052698135376</t>
   </si>
   <si>
     <t xml:space="preserve">12.9787874221802</t>
@@ -2030,46 +2030,46 @@
     <t xml:space="preserve">13.1413927078247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0970449447632</t>
+    <t xml:space="preserve">13.0970439910889</t>
   </si>
   <si>
     <t xml:space="preserve">13.0822639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0231342315674</t>
+    <t xml:space="preserve">13.0231351852417</t>
   </si>
   <si>
     <t xml:space="preserve">12.9492244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1561727523804</t>
+    <t xml:space="preserve">13.156174659729</t>
   </si>
   <si>
     <t xml:space="preserve">12.9935703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6092329025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8605298995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5501050949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4518213272095</t>
+    <t xml:space="preserve">12.6092319488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8605289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5501022338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4518184661865</t>
   </si>
   <si>
     <t xml:space="preserve">13.3335628509521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.496166229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3483419418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5405101776123</t>
+    <t xml:space="preserve">13.4961652755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3483428955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5405130386353</t>
   </si>
   <si>
     <t xml:space="preserve">12.9640064239502</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">13.1709566116333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.919659614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2744312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.259651184082</t>
+    <t xml:space="preserve">12.9196605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2744302749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2596502304077</t>
   </si>
   <si>
     <t xml:space="preserve">13.2892141342163</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">13.2448673248291</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1266088485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9396333694458</t>
+    <t xml:space="preserve">13.1266117095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7622470855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9396324157715</t>
   </si>
   <si>
     <t xml:space="preserve">13.5552949905396</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">13.7474641799927</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9691953659058</t>
+    <t xml:space="preserve">13.9691963195801</t>
   </si>
   <si>
     <t xml:space="preserve">13.7770280838013</t>
@@ -2120,19 +2120,19 @@
     <t xml:space="preserve">13.6292066574097</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8657197952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9544134140015</t>
+    <t xml:space="preserve">13.8657207489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9544153213501</t>
   </si>
   <si>
     <t xml:space="preserve">13.4666004180908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4813842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4370374679565</t>
+    <t xml:space="preserve">13.4813823699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4370365142822</t>
   </si>
   <si>
     <t xml:space="preserve">13.7918090820312</t>
@@ -2141,61 +2141,61 @@
     <t xml:space="preserve">13.998761177063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0578889846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8213768005371</t>
+    <t xml:space="preserve">14.0578899383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8213739395142</t>
   </si>
   <si>
     <t xml:space="preserve">13.6883344650269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6587686538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144227981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5257301330566</t>
+    <t xml:space="preserve">13.6587696075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144237518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5257291793823</t>
   </si>
   <si>
     <t xml:space="preserve">13.3631258010864</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2300834655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8805027008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4570121765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4717931747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6343965530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8191738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0409088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300403594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0039520263672</t>
+    <t xml:space="preserve">13.2300853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.88050365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4570083618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4717922210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6343946456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8191757202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0409078598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300413131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0039510726929</t>
   </si>
   <si>
     <t xml:space="preserve">15.3735065460205</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5582838058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9278402328491</t>
+    <t xml:space="preserve">15.5582847595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9278392791748</t>
   </si>
   <si>
     <t xml:space="preserve">16.1126174926758</t>
@@ -2204,19 +2204,19 @@
     <t xml:space="preserve">16.0387077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7800168991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061071395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6321954727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5213289260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4104633331299</t>
+    <t xml:space="preserve">15.7800178527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7061061859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6321935653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5213308334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4104623794556</t>
   </si>
   <si>
     <t xml:space="preserve">15.447416305542</t>
@@ -2225,25 +2225,25 @@
     <t xml:space="preserve">15.2256851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">15.262640953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8908853530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9669981002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7378730773926</t>
+    <t xml:space="preserve">15.2626390457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8908863067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9669961929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7378711700439</t>
   </si>
   <si>
     <t xml:space="preserve">14.8561296463013</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4126644134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0874547958374</t>
+    <t xml:space="preserve">14.4126625061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0874538421631</t>
   </si>
   <si>
     <t xml:space="preserve">14.3091878890991</t>
@@ -2258,34 +2258,34 @@
     <t xml:space="preserve">11.8257751464844</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4710025787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87452220916748</t>
+    <t xml:space="preserve">11.471001625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87452125549316</t>
   </si>
   <si>
     <t xml:space="preserve">10.2145137786865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57887840270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63800621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16497421264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29801464080811</t>
+    <t xml:space="preserve">9.57887744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63800716400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1649751663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29801559448242</t>
   </si>
   <si>
     <t xml:space="preserve">9.53453063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65278911590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5545043945312</t>
+    <t xml:space="preserve">9.65278816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5545034408569</t>
   </si>
   <si>
     <t xml:space="preserve">10.7023258209229</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">10.5988512039185</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9388408660889</t>
+    <t xml:space="preserve">10.9388418197632</t>
   </si>
   <si>
     <t xml:space="preserve">10.7318906784058</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9018850326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2123126983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0275363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9905805587769</t>
+    <t xml:space="preserve">10.9018869400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2123136520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0275344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9905796051025</t>
   </si>
   <si>
     <t xml:space="preserve">11.012752532959</t>
@@ -2318,13 +2318,13 @@
     <t xml:space="preserve">11.0718812942505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.315788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8353662490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6801528930664</t>
+    <t xml:space="preserve">11.3157892227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8353652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6801519393921</t>
   </si>
   <si>
     <t xml:space="preserve">10.7244997024536</t>
@@ -2336,37 +2336,37 @@
     <t xml:space="preserve">10.5175485610962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9462327957153</t>
+    <t xml:space="preserve">10.9462337493896</t>
   </si>
   <si>
     <t xml:space="preserve">11.3749170303345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2714424133301</t>
+    <t xml:space="preserve">11.2714414596558</t>
   </si>
   <si>
     <t xml:space="preserve">11.5301303863525</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9735984802246</t>
+    <t xml:space="preserve">11.9735975265503</t>
   </si>
   <si>
     <t xml:space="preserve">11.6040420532227</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2197036743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5153474807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.73708152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1288108825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.431845664978</t>
+    <t xml:space="preserve">11.2197046279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5153484344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7370824813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.128809928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4318447113037</t>
   </si>
   <si>
     <t xml:space="preserve">12.5648860931396</t>
@@ -2375,16 +2375,16 @@
     <t xml:space="preserve">12.3801078796387</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4392366409302</t>
+    <t xml:space="preserve">12.4392356872559</t>
   </si>
   <si>
     <t xml:space="preserve">12.4096736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7644462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8974866867065</t>
+    <t xml:space="preserve">12.7644453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8974857330322</t>
   </si>
   <si>
     <t xml:space="preserve">12.8235750198364</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">12.971396446228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6070318222046</t>
+    <t xml:space="preserve">13.6070327758789</t>
   </si>
   <si>
     <t xml:space="preserve">13.8065929412842</t>
@@ -2402,70 +2402,70 @@
     <t xml:space="preserve">13.89528465271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0431079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5331201553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4739923477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0896549224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0600910186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887752532959</t>
+    <t xml:space="preserve">14.0431070327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5331220626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4739904403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.089653968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0600891113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887742996216</t>
   </si>
   <si>
     <t xml:space="preserve">13.2966051101685</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2512512207031</t>
+    <t xml:space="preserve">13.2512502670288</t>
   </si>
   <si>
     <t xml:space="preserve">13.4521455764771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1353530883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9962720870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1585321426392</t>
+    <t xml:space="preserve">13.1353521347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9962711334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1585330963135</t>
   </si>
   <si>
     <t xml:space="preserve">13.3980598449707</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2048931121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4212408065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5448665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4444189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5294132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3594264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1276245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.934458732605</t>
+    <t xml:space="preserve">13.2048921585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4212398529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.544867515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4444179534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5294141769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3594274520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1276254653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9344596862793</t>
   </si>
   <si>
     <t xml:space="preserve">12.8108310699463</t>
@@ -2474,19 +2474,19 @@
     <t xml:space="preserve">12.9576396942139</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2976131439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1508054733276</t>
+    <t xml:space="preserve">13.2976121902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.150806427002</t>
   </si>
   <si>
     <t xml:space="preserve">13.3362464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1894378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7953767776489</t>
+    <t xml:space="preserve">13.1894397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7953786849976</t>
   </si>
   <si>
     <t xml:space="preserve">12.5944843292236</t>
@@ -2498,16 +2498,16 @@
     <t xml:space="preserve">13.328519821167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2126197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4366912841797</t>
+    <t xml:space="preserve">13.2126188278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.436692237854</t>
   </si>
   <si>
     <t xml:space="preserve">13.6453123092651</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9312000274658</t>
+    <t xml:space="preserve">13.9312009811401</t>
   </si>
   <si>
     <t xml:space="preserve">13.5062341690063</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">13.5216865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5371398925781</t>
+    <t xml:space="preserve">13.5371408462524</t>
   </si>
   <si>
     <t xml:space="preserve">13.8539323806763</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">13.8230247497559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8848390579224</t>
+    <t xml:space="preserve">13.8848400115967</t>
   </si>
   <si>
     <t xml:space="preserve">14.0702791213989</t>
@@ -2534,16 +2534,16 @@
     <t xml:space="preserve">13.7843942642212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6916732788086</t>
+    <t xml:space="preserve">13.69167137146</t>
   </si>
   <si>
     <t xml:space="preserve">13.4289646148682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6221332550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5989532470703</t>
+    <t xml:space="preserve">13.6221323013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.598952293396</t>
   </si>
   <si>
     <t xml:space="preserve">13.274432182312</t>
@@ -2555,40 +2555,40 @@
     <t xml:space="preserve">13.7148532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5757732391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3053398132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6298589706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4753265380859</t>
+    <t xml:space="preserve">13.5757722854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3053388595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6298599243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4753255844116</t>
   </si>
   <si>
     <t xml:space="preserve">13.7921199798584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5680446624756</t>
+    <t xml:space="preserve">13.5680456161499</t>
   </si>
   <si>
     <t xml:space="preserve">13.4830522537231</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8462066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.92347240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9543800354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5912265777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.367151260376</t>
+    <t xml:space="preserve">13.8462057113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9234743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9543790817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5912256240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3671522140503</t>
   </si>
   <si>
     <t xml:space="preserve">13.5525932312012</t>
@@ -2597,49 +2597,49 @@
     <t xml:space="preserve">13.7380332946777</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0007400512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8925666809082</t>
+    <t xml:space="preserve">14.0007410049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8925657272339</t>
   </si>
   <si>
     <t xml:space="preserve">13.9080200195312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0780067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.938925743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8616609573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8384790420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0239191055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.047101020813</t>
+    <t xml:space="preserve">14.0780057907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.938928604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8616600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8384799957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0239200592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0471000671387</t>
   </si>
   <si>
     <t xml:space="preserve">14.3329877853394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1861801147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1784534454346</t>
+    <t xml:space="preserve">14.1861810684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1784543991089</t>
   </si>
   <si>
     <t xml:space="preserve">13.8152990341187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6993999481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3130655288696</t>
+    <t xml:space="preserve">13.6993980407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3130664825439</t>
   </si>
   <si>
     <t xml:space="preserve">13.2667055130005</t>
@@ -2648,16 +2648,16 @@
     <t xml:space="preserve">13.2898864746094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3748769760132</t>
+    <t xml:space="preserve">13.3748788833618</t>
   </si>
   <si>
     <t xml:space="preserve">13.166259765625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7766675949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7612133026123</t>
+    <t xml:space="preserve">13.7766666412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7612142562866</t>
   </si>
   <si>
     <t xml:space="preserve">13.7998466491699</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">13.5834999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4907789230347</t>
+    <t xml:space="preserve">13.4907779693604</t>
   </si>
   <si>
     <t xml:space="preserve">13.5139598846436</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">14.0161933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6375856399536</t>
+    <t xml:space="preserve">13.6375865936279</t>
   </si>
   <si>
     <t xml:space="preserve">13.042631149292</t>
@@ -2684,19 +2684,19 @@
     <t xml:space="preserve">12.8880987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8262853622437</t>
+    <t xml:space="preserve">12.8262844085693</t>
   </si>
   <si>
     <t xml:space="preserve">12.8494644165039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7567443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5867576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6022109985352</t>
+    <t xml:space="preserve">12.7567453384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5867586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6022100448608</t>
   </si>
   <si>
     <t xml:space="preserve">12.625391960144</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">12.6872053146362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031044006348</t>
+    <t xml:space="preserve">12.8031053543091</t>
   </si>
   <si>
     <t xml:space="preserve">12.9267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1430797576904</t>
+    <t xml:space="preserve">13.1430788040161</t>
   </si>
   <si>
     <t xml:space="preserve">13.3207931518555</t>
@@ -2723,25 +2723,25 @@
     <t xml:space="preserve">13.4057865142822</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1817111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8417387008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8726453781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9190044403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8571920394897</t>
+    <t xml:space="preserve">13.1817121505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8417406082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8726444244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9190053939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8571910858154</t>
   </si>
   <si>
     <t xml:space="preserve">12.6331186294556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721996307373</t>
+    <t xml:space="preserve">12.7721977233887</t>
   </si>
   <si>
     <t xml:space="preserve">12.7490186691284</t>
@@ -2762,19 +2762,19 @@
     <t xml:space="preserve">12.9808177947998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7181119918823</t>
+    <t xml:space="preserve">12.718111038208</t>
   </si>
   <si>
     <t xml:space="preserve">12.7258377075195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6408443450928</t>
+    <t xml:space="preserve">12.6408452987671</t>
   </si>
   <si>
     <t xml:space="preserve">12.6176643371582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7103853225708</t>
+    <t xml:space="preserve">12.7103862762451</t>
   </si>
   <si>
     <t xml:space="preserve">12.4554052352905</t>
@@ -2786,58 +2786,58 @@
     <t xml:space="preserve">13.5603189468384</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6839466094971</t>
+    <t xml:space="preserve">13.6839456558228</t>
   </si>
   <si>
     <t xml:space="preserve">13.9621067047119</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1398210525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3716201782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.410252571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5570602416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5338802337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4025268554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2402687072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2557220458984</t>
+    <t xml:space="preserve">14.1398191452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.371621131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4102544784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5570611953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.533881187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4025278091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2402667999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2557210922241</t>
   </si>
   <si>
     <t xml:space="preserve">14.3947992324829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5493326187134</t>
+    <t xml:space="preserve">14.549334526062</t>
   </si>
   <si>
     <t xml:space="preserve">14.9588489532471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1211090087891</t>
+    <t xml:space="preserve">15.1211071014404</t>
   </si>
   <si>
     <t xml:space="preserve">14.804313659668</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6343288421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7656812667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7579536437988</t>
+    <t xml:space="preserve">14.6343278884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7656831741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7579545974731</t>
   </si>
   <si>
     <t xml:space="preserve">14.6806869506836</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">14.5261535644531</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6961402893066</t>
+    <t xml:space="preserve">14.696141242981</t>
   </si>
   <si>
     <t xml:space="preserve">14.6420564651489</t>
@@ -2855,16 +2855,16 @@
     <t xml:space="preserve">14.5725145339966</t>
   </si>
   <si>
-    <t xml:space="preserve">14.603422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5956935882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6575088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8352212905884</t>
+    <t xml:space="preserve">14.6034202575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5956954956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6575050354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8352222442627</t>
   </si>
   <si>
     <t xml:space="preserve">14.9974803924561</t>
@@ -2876,52 +2876,52 @@
     <t xml:space="preserve">15.0824766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0283870697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0979299545288</t>
+    <t xml:space="preserve">15.0283899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0979270935059</t>
   </si>
   <si>
     <t xml:space="preserve">15.1751947402954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2061014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8506755828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8661279678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9743013381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0592956542969</t>
+    <t xml:space="preserve">15.2061033248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747480392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8506736755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8661270141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9743022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0592947006226</t>
   </si>
   <si>
     <t xml:space="preserve">15.0052080154419</t>
   </si>
   <si>
-    <t xml:space="preserve">14.927942276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1520156860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4147214889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8551425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8087816238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6233415603638</t>
+    <t xml:space="preserve">14.9279403686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1520147323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4147233963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8551435470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8087825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6233425140381</t>
   </si>
   <si>
     <t xml:space="preserve">15.7624235153198</t>
@@ -2930,19 +2930,19 @@
     <t xml:space="preserve">15.916955947876</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0714912414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9787693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8860483169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9942235946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1796627044678</t>
+    <t xml:space="preserve">16.0714893341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9787712097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8860492706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9942245483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1796646118164</t>
   </si>
   <si>
     <t xml:space="preserve">16.0560359954834</t>
@@ -2951,37 +2951,37 @@
     <t xml:space="preserve">16.3496494293213</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4578227996826</t>
+    <t xml:space="preserve">16.4578247070312</t>
   </si>
   <si>
     <t xml:space="preserve">16.2651462554932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0564136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8476791381836</t>
+    <t xml:space="preserve">16.0564117431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8476781845093</t>
   </si>
   <si>
     <t xml:space="preserve">15.7834548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8717651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6871175765991</t>
+    <t xml:space="preserve">15.8717641830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6871147155762</t>
   </si>
   <si>
     <t xml:space="preserve">15.6469745635986</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5586643218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6550016403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192277908325</t>
+    <t xml:space="preserve">15.5586652755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6550025939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192287445068</t>
   </si>
   <si>
     <t xml:space="preserve">15.7673969268799</t>
@@ -2993,22 +2993,22 @@
     <t xml:space="preserve">15.5988054275513</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5827484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7112016677856</t>
+    <t xml:space="preserve">15.5827474594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7111988067627</t>
   </si>
   <si>
     <t xml:space="preserve">15.7272567749023</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5907783508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5104951858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2134523391724</t>
+    <t xml:space="preserve">15.5907773971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5104942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2134532928467</t>
   </si>
   <si>
     <t xml:space="preserve">15.2616214752197</t>
@@ -3017,10 +3017,10 @@
     <t xml:space="preserve">15.4703540802002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.663031578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8557090759277</t>
+    <t xml:space="preserve">15.6630306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8557081222534</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352848052979</t>
@@ -3029,10 +3029,10 @@
     <t xml:space="preserve">15.9119052886963</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0162715911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7754259109497</t>
+    <t xml:space="preserve">16.0162734985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.775426864624</t>
   </si>
   <si>
     <t xml:space="preserve">15.9921875</t>
@@ -3044,28 +3044,28 @@
     <t xml:space="preserve">16.3454303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.538106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6665554046631</t>
+    <t xml:space="preserve">16.5381050109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6665573120117</t>
   </si>
   <si>
     <t xml:space="preserve">16.9876842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0679664611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9074001312256</t>
+    <t xml:space="preserve">17.0679683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9074039459229</t>
   </si>
   <si>
     <t xml:space="preserve">16.5702171325684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2330303192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0724716186523</t>
+    <t xml:space="preserve">16.2330341339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0724697113037</t>
   </si>
   <si>
     <t xml:space="preserve">16.4096546173096</t>
@@ -3074,22 +3074,22 @@
     <t xml:space="preserve">16.2009201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3133163452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1366939544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3293724060059</t>
+    <t xml:space="preserve">16.3133144378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1366958618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3293704986572</t>
   </si>
   <si>
     <t xml:space="preserve">16.0885257720947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0483856201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9841585159302</t>
+    <t xml:space="preserve">16.0483837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9841594696045</t>
   </si>
   <si>
     <t xml:space="preserve">16.2812023162842</t>
@@ -3101,28 +3101,28 @@
     <t xml:space="preserve">16.1527519226074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8637380599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3980989456177</t>
+    <t xml:space="preserve">15.8637361526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3981008529663</t>
   </si>
   <si>
     <t xml:space="preserve">15.1090850830078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.916407585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8040132522583</t>
+    <t xml:space="preserve">14.9164094924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8040142059326</t>
   </si>
   <si>
     <t xml:space="preserve">14.9806327819824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9886627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9645767211914</t>
+    <t xml:space="preserve">14.9886608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9645776748657</t>
   </si>
   <si>
     <t xml:space="preserve">14.7478151321411</t>
@@ -3131,19 +3131,19 @@
     <t xml:space="preserve">14.8923234939575</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8120431900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9003505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8521814346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.101056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6755619049072</t>
+    <t xml:space="preserve">14.8120422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.900351524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.852180480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1010570526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6755638122559</t>
   </si>
   <si>
     <t xml:space="preserve">14.7879571914673</t>
@@ -3155,31 +3155,31 @@
     <t xml:space="preserve">15.2375354766846</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0930290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2937335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3900718688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0609159469604</t>
+    <t xml:space="preserve">15.0930280685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2937326431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3900709152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0609149932861</t>
   </si>
   <si>
     <t xml:space="preserve">15.0368299484253</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3419027328491</t>
+    <t xml:space="preserve">15.3419046401978</t>
   </si>
   <si>
     <t xml:space="preserve">15.2535915374756</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1973943710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5345783233643</t>
+    <t xml:space="preserve">15.197395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5345811843872</t>
   </si>
   <si>
     <t xml:space="preserve">15.1251411437988</t>
@@ -3188,16 +3188,16 @@
     <t xml:space="preserve">15.0769720077515</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1492252349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8441543579102</t>
+    <t xml:space="preserve">15.1492261886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8441534042358</t>
   </si>
   <si>
     <t xml:space="preserve">14.7076749801636</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6113376617432</t>
+    <t xml:space="preserve">14.6113357543945</t>
   </si>
   <si>
     <t xml:space="preserve">14.6595048904419</t>
@@ -3206,67 +3206,67 @@
     <t xml:space="preserve">14.1858406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3062648773193</t>
+    <t xml:space="preserve">14.306263923645</t>
   </si>
   <si>
     <t xml:space="preserve">14.3544321060181</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5792236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3464059829712</t>
+    <t xml:space="preserve">14.5792226791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3464069366455</t>
   </si>
   <si>
     <t xml:space="preserve">14.3142929077148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6996459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.61936378479</t>
+    <t xml:space="preserve">14.6996469497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6193628311157</t>
   </si>
   <si>
     <t xml:space="preserve">14.5551376342773</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5230264663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5471105575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273927688599</t>
+    <t xml:space="preserve">14.5230255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5471115112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273908615112</t>
   </si>
   <si>
     <t xml:space="preserve">14.820068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9244356155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5711936950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3785171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2259817123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1617555618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0493612289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.193868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7442903518677</t>
+    <t xml:space="preserve">14.9244365692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5711946487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3785181045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.225980758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1617565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0493621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1938695907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8326005935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7442893981934</t>
   </si>
   <si>
     <t xml:space="preserve">13.8486566543579</t>
@@ -3278,61 +3278,61 @@
     <t xml:space="preserve">13.5355567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5917539596558</t>
+    <t xml:space="preserve">13.5917530059814</t>
   </si>
   <si>
     <t xml:space="preserve">13.8406286239624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9690790176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3704881668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3303499221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2179536819458</t>
+    <t xml:space="preserve">13.9690780639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3704900741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3303489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2179527282715</t>
   </si>
   <si>
     <t xml:space="preserve">13.8727416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6479520797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947092056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5114717483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5034437179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2465400695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4151334762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3187942504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4071063995361</t>
+    <t xml:space="preserve">13.6479511260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947101593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5114707946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5034427642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2465410232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.415132522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3187952041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4071054458618</t>
   </si>
   <si>
     <t xml:space="preserve">13.1100606918335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0859756469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2224550247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5756978988647</t>
+    <t xml:space="preserve">13.085976600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2224559783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5756969451904</t>
   </si>
   <si>
     <t xml:space="preserve">13.664008140564</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">13.198371887207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0217514038086</t>
+    <t xml:space="preserve">13.0217504501343</t>
   </si>
   <si>
     <t xml:space="preserve">12.8611869812012</t>
@@ -3353,34 +3353,34 @@
     <t xml:space="preserve">12.604284286499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0137224197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3589363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1261177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8210458755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6363973617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9735822677612</t>
+    <t xml:space="preserve">13.0137214660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3589353561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1261186599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8210468292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6363964080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9735813140869</t>
   </si>
   <si>
     <t xml:space="preserve">12.9093561172485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8772449493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1421756744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2706260681152</t>
+    <t xml:space="preserve">12.8772439956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1421747207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2706251144409</t>
   </si>
   <si>
     <t xml:space="preserve">13.5516119003296</t>
@@ -3392,46 +3392,46 @@
     <t xml:space="preserve">13.3910484313965</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4392175674438</t>
+    <t xml:space="preserve">13.4392185211182</t>
   </si>
   <si>
     <t xml:space="preserve">13.3509063720703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7202062606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0092210769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8807697296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5596418380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5997829437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4231605529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3027372360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3749923706055</t>
+    <t xml:space="preserve">13.7202053070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.009220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8807706832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5596399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5997838973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4231615066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3749914169312</t>
   </si>
   <si>
     <t xml:space="preserve">13.2304840087891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0297784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1020317077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0940046310425</t>
+    <t xml:space="preserve">13.0297794342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.102032661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0940036773682</t>
   </si>
   <si>
     <t xml:space="preserve">12.9494972229004</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">12.6444253921509</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7969608306885</t>
+    <t xml:space="preserve">12.7969617843628</t>
   </si>
   <si>
     <t xml:space="preserve">12.9334411621094</t>
@@ -3461,22 +3461,22 @@
     <t xml:space="preserve">12.9254140853882</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1341457366943</t>
+    <t xml:space="preserve">13.1341466903687</t>
   </si>
   <si>
     <t xml:space="preserve">12.9816102981567</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4633026123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5837259292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3268232345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2063999176025</t>
+    <t xml:space="preserve">13.463303565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5837249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3268222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2064008712769</t>
   </si>
   <si>
     <t xml:space="preserve">13.2786540985107</t>
@@ -3488,25 +3488,25 @@
     <t xml:space="preserve">12.4838619232178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3393545150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5320310592651</t>
+    <t xml:space="preserve">12.3393526077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5320301055908</t>
   </si>
   <si>
     <t xml:space="preserve">12.1839189529419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8018436431885</t>
+    <t xml:space="preserve">11.8018445968628</t>
   </si>
   <si>
     <t xml:space="preserve">11.74241065979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9546737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3112773895264</t>
+    <t xml:space="preserve">11.9546747207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3112764358521</t>
   </si>
   <si>
     <t xml:space="preserve">12.1075038909912</t>
@@ -3524,13 +3524,13 @@
     <t xml:space="preserve">12.2433528900146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9461832046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9886360168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0141067504883</t>
+    <t xml:space="preserve">11.9461841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.98863697052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0141077041626</t>
   </si>
   <si>
     <t xml:space="preserve">12.0905227661133</t>
@@ -3539,61 +3539,61 @@
     <t xml:space="preserve">11.9376935958862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6150541305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792051315308</t>
+    <t xml:space="preserve">11.6150531768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792041778564</t>
   </si>
   <si>
     <t xml:space="preserve">11.5556182861328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6659965515137</t>
+    <t xml:space="preserve">11.6659955978394</t>
   </si>
   <si>
     <t xml:space="preserve">11.6575050354004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.750901222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339200973511</t>
+    <t xml:space="preserve">11.7509021759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339210510254</t>
   </si>
   <si>
     <t xml:space="preserve">11.8358068466187</t>
   </si>
   <si>
-    <t xml:space="preserve">11.759391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8867502212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9631643295288</t>
+    <t xml:space="preserve">11.7593927383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8867492675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9631652832031</t>
   </si>
   <si>
     <t xml:space="preserve">11.6744871139526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5726003646851</t>
+    <t xml:space="preserve">11.5725994110107</t>
   </si>
   <si>
     <t xml:space="preserve">11.5301475524902</t>
   </si>
   <si>
-    <t xml:space="preserve">11.598072052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5471286773682</t>
+    <t xml:space="preserve">11.5980710983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5471296310425</t>
   </si>
   <si>
     <t xml:space="preserve">11.581090927124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4707145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3688287734985</t>
+    <t xml:space="preserve">11.4707136154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3688268661499</t>
   </si>
   <si>
     <t xml:space="preserve">11.343355178833</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">11.2499599456787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9358100891113</t>
+    <t xml:space="preserve">10.9358110427856</t>
   </si>
   <si>
     <t xml:space="preserve">10.6386413574219</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">10.1886425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86600208282471</t>
+    <t xml:space="preserve">9.86600303649902</t>
   </si>
   <si>
     <t xml:space="preserve">9.71317291259766</t>
@@ -3635,22 +3635,22 @@
     <t xml:space="preserve">10.0612850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075103759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1716604232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0697746276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9169454574585</t>
+    <t xml:space="preserve">10.3075113296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1716613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0697755813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91694641113281</t>
   </si>
   <si>
     <t xml:space="preserve">10.0867567062378</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69619178771973</t>
+    <t xml:space="preserve">9.69619274139404</t>
   </si>
   <si>
     <t xml:space="preserve">9.47543811798096</t>
@@ -3662,22 +3662,22 @@
     <t xml:space="preserve">9.26317405700684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53487205505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2716646194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45845699310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74713516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90845489501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56034374237061</t>
+    <t xml:space="preserve">9.53487110137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27166557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7471342086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90845584869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56034278869629</t>
   </si>
   <si>
     <t xml:space="preserve">9.4160041809082</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">9.49241924285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38204193115234</t>
+    <t xml:space="preserve">9.38204288482666</t>
   </si>
   <si>
     <t xml:space="preserve">9.08487319946289</t>
@@ -3707,31 +3707,31 @@
     <t xml:space="preserve">10.1037368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1207180023193</t>
+    <t xml:space="preserve">10.1207189559937</t>
   </si>
   <si>
     <t xml:space="preserve">9.80656909942627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2395868301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6216602325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8424139022827</t>
+    <t xml:space="preserve">10.2395858764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6216611862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.842414855957</t>
   </si>
   <si>
     <t xml:space="preserve">10.8593950271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8254327774048</t>
+    <t xml:space="preserve">10.8254337310791</t>
   </si>
   <si>
     <t xml:space="preserve">10.8678855895996</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8339233398438</t>
+    <t xml:space="preserve">10.8339242935181</t>
   </si>
   <si>
     <t xml:space="preserve">10.774489402771</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">11.0292053222656</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2584505081177</t>
+    <t xml:space="preserve">11.2584495544434</t>
   </si>
   <si>
     <t xml:space="preserve">11.2924127578735</t>
@@ -3782,13 +3782,13 @@
     <t xml:space="preserve">11.1650543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2414693832397</t>
+    <t xml:space="preserve">11.2414684295654</t>
   </si>
   <si>
     <t xml:space="preserve">11.419771194458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858089447021</t>
+    <t xml:space="preserve">11.3858079910278</t>
   </si>
   <si>
     <t xml:space="preserve">11.3942995071411</t>
@@ -3797,13 +3797,13 @@
     <t xml:space="preserve">11.3603372573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0376958847046</t>
+    <t xml:space="preserve">11.0376968383789</t>
   </si>
   <si>
     <t xml:space="preserve">11.003734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1226015090942</t>
+    <t xml:space="preserve">11.1226024627686</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159976959229</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">11.2244882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.411280632019</t>
+    <t xml:space="preserve">11.4112796783447</t>
   </si>
   <si>
     <t xml:space="preserve">11.5216569900513</t>
@@ -3827,13 +3827,13 @@
     <t xml:space="preserve">11.9716558456421</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1159944534302</t>
+    <t xml:space="preserve">12.1159954071045</t>
   </si>
   <si>
     <t xml:space="preserve">12.149956703186</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1754283905029</t>
+    <t xml:space="preserve">12.1754293441772</t>
   </si>
   <si>
     <t xml:space="preserve">12.0480699539185</t>
@@ -3851,19 +3851,19 @@
     <t xml:space="preserve">12.2009000778198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2263717651367</t>
+    <t xml:space="preserve">12.2263708114624</t>
   </si>
   <si>
     <t xml:space="preserve">12.1414661407471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0650510787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0056171417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8697690963745</t>
+    <t xml:space="preserve">12.0650520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0056180953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8697681427002</t>
   </si>
   <si>
     <t xml:space="preserve">11.7169399261475</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">10.604679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8763761520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.68958568573</t>
+    <t xml:space="preserve">10.8763771057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6895837783813</t>
   </si>
   <si>
     <t xml:space="preserve">10.9867525100708</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">10.8509044647217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6980762481689</t>
+    <t xml:space="preserve">10.6980752944946</t>
   </si>
   <si>
     <t xml:space="preserve">10.6641130447388</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">10.7320375442505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7999620437622</t>
+    <t xml:space="preserve">10.7999610900879</t>
   </si>
   <si>
     <t xml:space="preserve">11.012225151062</t>
@@ -3926,13 +3926,13 @@
     <t xml:space="preserve">11.3093938827515</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0886392593384</t>
+    <t xml:space="preserve">11.0886402130127</t>
   </si>
   <si>
     <t xml:space="preserve">11.3773183822632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5046758651733</t>
+    <t xml:space="preserve">11.5046768188477</t>
   </si>
   <si>
     <t xml:space="preserve">11.6320343017578</t>
@@ -3941,19 +3941,19 @@
     <t xml:space="preserve">11.5131673812866</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4622240066528</t>
+    <t xml:space="preserve">11.4622230529785</t>
   </si>
   <si>
     <t xml:space="preserve">11.6999578475952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6829776763916</t>
+    <t xml:space="preserve">11.6829767227173</t>
   </si>
   <si>
     <t xml:space="preserve">11.7678823471069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827317237854</t>
+    <t xml:space="preserve">11.8273162841797</t>
   </si>
   <si>
     <t xml:space="preserve">11.6374282836914</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">10.877875328064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7331981658936</t>
+    <t xml:space="preserve">10.7331991195679</t>
   </si>
   <si>
     <t xml:space="preserve">10.8326635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8869180679321</t>
+    <t xml:space="preserve">10.8869171142578</t>
   </si>
   <si>
     <t xml:space="preserve">10.8507490158081</t>
@@ -3995,22 +3995,22 @@
     <t xml:space="preserve">10.6608600616455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3082103729248</t>
+    <t xml:space="preserve">10.3082113265991</t>
   </si>
   <si>
     <t xml:space="preserve">10.1544914245605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1454496383667</t>
+    <t xml:space="preserve">10.145450592041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3262958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3534231185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4167194366455</t>
+    <t xml:space="preserve">10.353422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4167184829712</t>
   </si>
   <si>
     <t xml:space="preserve">10.2539577484131</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">10.3805494308472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4890565872192</t>
+    <t xml:space="preserve">10.4890575408936</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">10.0098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0731115341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95556163787842</t>
+    <t xml:space="preserve">10.073112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95556259155273</t>
   </si>
   <si>
     <t xml:space="preserve">9.8560962677002</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">9.7114200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57578659057617</t>
+    <t xml:space="preserve">9.57578563690186</t>
   </si>
   <si>
     <t xml:space="preserve">9.34068584442139</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">9.43110942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28643226623535</t>
+    <t xml:space="preserve">9.28643321990967</t>
   </si>
   <si>
     <t xml:space="preserve">9.26834774017334</t>
@@ -4073,28 +4073,28 @@
     <t xml:space="preserve">9.30451679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33164405822754</t>
+    <t xml:space="preserve">9.33164310455322</t>
   </si>
   <si>
     <t xml:space="preserve">9.52153205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72046184539795</t>
+    <t xml:space="preserve">9.72046279907227</t>
   </si>
   <si>
     <t xml:space="preserve">9.76567363739014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91035079956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91939353942871</t>
+    <t xml:space="preserve">9.91034984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91939258575439</t>
   </si>
   <si>
     <t xml:space="preserve">9.90130805969238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87418079376221</t>
+    <t xml:space="preserve">9.87418174743652</t>
   </si>
   <si>
     <t xml:space="preserve">9.82896995544434</t>
@@ -4130,10 +4130,10 @@
     <t xml:space="preserve">9.15984058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12367057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32260227203369</t>
+    <t xml:space="preserve">9.12367153167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32260131835938</t>
   </si>
   <si>
     <t xml:space="preserve">9.20505142211914</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">9.89226531982422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84705448150635</t>
+    <t xml:space="preserve">9.84705543518066</t>
   </si>
   <si>
     <t xml:space="preserve">10.0279006958008</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">10.0369424819946</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94651985168457</t>
+    <t xml:space="preserve">9.94651889801025</t>
   </si>
   <si>
     <t xml:space="preserve">10.1906623840332</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">10.4800148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5523529052734</t>
+    <t xml:space="preserve">10.5523538589478</t>
   </si>
   <si>
     <t xml:space="preserve">10.7151145935059</t>
@@ -4187,16 +4187,16 @@
     <t xml:space="preserve">10.4980993270874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2991695404053</t>
+    <t xml:space="preserve">10.299168586731</t>
   </si>
   <si>
     <t xml:space="preserve">10.2901268005371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.181619644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5704364776611</t>
+    <t xml:space="preserve">10.1816186904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5704374313354</t>
   </si>
   <si>
     <t xml:space="preserve">10.7603254318237</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">11.0768060684204</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2124404907227</t>
+    <t xml:space="preserve">11.2124395370483</t>
   </si>
   <si>
     <t xml:space="preserve">11.5560474395752</t>
@@ -4223,19 +4223,19 @@
     <t xml:space="preserve">11.2486085891724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6464700698853</t>
+    <t xml:space="preserve">11.6464710235596</t>
   </si>
   <si>
     <t xml:space="preserve">11.5289211273193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7188091278076</t>
+    <t xml:space="preserve">11.7188081741333</t>
   </si>
   <si>
     <t xml:space="preserve">11.9448661804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9629507064819</t>
+    <t xml:space="preserve">11.9629497528076</t>
   </si>
   <si>
     <t xml:space="preserve">11.9086971282959</t>
@@ -4250,10 +4250,10 @@
     <t xml:space="preserve">12.4783611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5054874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1528377532959</t>
+    <t xml:space="preserve">12.5054883956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1528387069702</t>
   </si>
   <si>
     <t xml:space="preserve">12.3155994415283</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">12.1709232330322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1799650192261</t>
+    <t xml:space="preserve">12.1799659729004</t>
   </si>
   <si>
     <t xml:space="preserve">12.107626914978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2161350250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2703876495361</t>
+    <t xml:space="preserve">12.2161340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2703886032104</t>
   </si>
   <si>
     <t xml:space="preserve">12.4874038696289</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">12.650164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4693193435669</t>
+    <t xml:space="preserve">12.4693183898926</t>
   </si>
   <si>
     <t xml:space="preserve">12.595911026001</t>
@@ -4316,16 +4316,16 @@
     <t xml:space="preserve">12.8852643966675</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0751523971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932359695435</t>
+    <t xml:space="preserve">13.0751514434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932369232178</t>
   </si>
   <si>
     <t xml:space="preserve">13.0028142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2198295593262</t>
+    <t xml:space="preserve">13.2198286056519</t>
   </si>
   <si>
     <t xml:space="preserve">12.9304752349854</t>
@@ -4346,16 +4346,16 @@
     <t xml:space="preserve">12.6772918701172</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2613458633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5507001876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.577826499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4602766036987</t>
+    <t xml:space="preserve">12.2613468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5506992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5778255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4602756500244</t>
   </si>
   <si>
     <t xml:space="preserve">12.3517684936523</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">12.4060230255127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3608112335205</t>
+    <t xml:space="preserve">12.3608121871948</t>
   </si>
   <si>
     <t xml:space="preserve">12.4241065979004</t>
@@ -4391,19 +4391,19 @@
     <t xml:space="preserve">13.5091819763184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2144804000854</t>
+    <t xml:space="preserve">14.2144813537598</t>
   </si>
   <si>
     <t xml:space="preserve">14.1963958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0788469314575</t>
+    <t xml:space="preserve">14.0788459777832</t>
   </si>
   <si>
     <t xml:space="preserve">13.8980007171631</t>
   </si>
   <si>
-    <t xml:space="preserve">13.979380607605</t>
+    <t xml:space="preserve">13.9793815612793</t>
   </si>
   <si>
     <t xml:space="preserve">14.0065078735352</t>
@@ -4424,16 +4424,16 @@
     <t xml:space="preserve">14.6485109329224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8474416732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5671300888062</t>
+    <t xml:space="preserve">14.8474407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5671310424805</t>
   </si>
   <si>
     <t xml:space="preserve">14.6846799850464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8022298812866</t>
+    <t xml:space="preserve">14.8022308349609</t>
   </si>
   <si>
     <t xml:space="preserve">14.7389326095581</t>
@@ -4448,10 +4448,10 @@
     <t xml:space="preserve">14.1511840820312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1873531341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3049030303955</t>
+    <t xml:space="preserve">14.1873540878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3049039840698</t>
   </si>
   <si>
     <t xml:space="preserve">13.9341697692871</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">14.1421422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2958612442017</t>
+    <t xml:space="preserve">14.295862197876</t>
   </si>
   <si>
     <t xml:space="preserve">14.4495801925659</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">14.5490455627441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.874568939209</t>
+    <t xml:space="preserve">14.8745679855347</t>
   </si>
   <si>
     <t xml:space="preserve">14.7208499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6123418807983</t>
+    <t xml:space="preserve">14.612340927124</t>
   </si>
   <si>
     <t xml:space="preserve">14.6304264068604</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">14.9649896621704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6575517654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8926515579224</t>
+    <t xml:space="preserve">14.6575527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8926525115967</t>
   </si>
   <si>
     <t xml:space="preserve">14.9740324020386</t>
@@ -4514,13 +4514,13 @@
     <t xml:space="preserve">15.082540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.471360206604</t>
+    <t xml:space="preserve">15.4713592529297</t>
   </si>
   <si>
     <t xml:space="preserve">15.191047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2633857727051</t>
+    <t xml:space="preserve">15.2633848190308</t>
   </si>
   <si>
     <t xml:space="preserve">15.1458368301392</t>
@@ -4532,16 +4532,16 @@
     <t xml:space="preserve">15.2995548248291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2000904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3718938827515</t>
+    <t xml:space="preserve">15.2000894546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3718948364258</t>
   </si>
   <si>
     <t xml:space="preserve">15.7245426177979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5527410507202</t>
+    <t xml:space="preserve">15.5527391433716</t>
   </si>
   <si>
     <t xml:space="preserve">15.6974172592163</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">15.4171047210693</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2905130386353</t>
+    <t xml:space="preserve">15.2905120849609</t>
   </si>
   <si>
     <t xml:space="preserve">15.0011596679688</t>
@@ -4568,10 +4568,10 @@
     <t xml:space="preserve">14.5128755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6665954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8112707138062</t>
+    <t xml:space="preserve">14.6665945053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8112716674805</t>
   </si>
   <si>
     <t xml:space="preserve">14.5054912567139</t>
@@ -4616,9 +4616,6 @@
     <t xml:space="preserve">15.2890548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8112716674805</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.8017158508301</t>
   </si>
   <si>
@@ -5373,6 +5370,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.6800003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4799995422363</t>
   </si>
 </sst>
 </file>
@@ -62201,7 +62201,7 @@
         <v>15.5</v>
       </c>
       <c r="G2173" t="s">
-        <v>1534</v>
+        <v>1519</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62227,7 +62227,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G2174" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62253,7 +62253,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G2175" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62279,7 +62279,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62305,7 +62305,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G2177" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62331,7 +62331,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G2178" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62357,7 +62357,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G2179" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62383,7 +62383,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G2180" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62409,7 +62409,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G2181" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62435,7 +62435,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G2182" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62461,7 +62461,7 @@
         <v>16.5</v>
       </c>
       <c r="G2183" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62487,7 +62487,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2184" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62513,7 +62513,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G2185" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62539,7 +62539,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G2186" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62565,7 +62565,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G2187" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62591,7 +62591,7 @@
         <v>16.25</v>
       </c>
       <c r="G2188" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62617,7 +62617,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G2189" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62643,7 +62643,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2190" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62669,7 +62669,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2191" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62695,7 +62695,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62721,7 +62721,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G2193" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62747,7 +62747,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G2194" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62773,7 +62773,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G2195" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62799,7 +62799,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G2196" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62825,7 +62825,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2197" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62851,7 +62851,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2198" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62877,7 +62877,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G2199" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62903,7 +62903,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2200" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62929,7 +62929,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G2201" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62955,7 +62955,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G2202" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62981,7 +62981,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2203" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63007,7 +63007,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2204" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63033,7 +63033,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G2205" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63059,7 +63059,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2206" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63085,7 +63085,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G2207" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63111,7 +63111,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2208" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63137,7 +63137,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G2209" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63163,7 +63163,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2210" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63189,7 +63189,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2211" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63215,7 +63215,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G2212" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63241,7 +63241,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2213" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63267,7 +63267,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2214" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63293,7 +63293,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2215" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63319,7 +63319,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2216" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63345,7 +63345,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G2217" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63371,7 +63371,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G2218" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63397,7 +63397,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G2219" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63423,7 +63423,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2220" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63449,7 +63449,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2221" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63475,7 +63475,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G2222" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63501,7 +63501,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G2223" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63527,7 +63527,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2224" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63553,7 +63553,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G2225" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63579,7 +63579,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G2226" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63605,7 +63605,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G2227" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63631,7 +63631,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G2228" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63657,7 +63657,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2229" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63683,7 +63683,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G2230" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63709,7 +63709,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G2231" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63735,7 +63735,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2232" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63761,7 +63761,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G2233" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63787,7 +63787,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2234" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63813,7 +63813,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G2235" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63839,7 +63839,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G2236" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63865,7 +63865,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G2237" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63891,7 +63891,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2238" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63917,7 +63917,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G2239" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63943,7 +63943,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2240" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63969,7 +63969,7 @@
         <v>17.75</v>
       </c>
       <c r="G2241" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63995,7 +63995,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2242" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64021,7 +64021,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2243" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64047,7 +64047,7 @@
         <v>18.5</v>
       </c>
       <c r="G2244" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64073,7 +64073,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G2245" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64099,7 +64099,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2246" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64125,7 +64125,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2247" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64151,7 +64151,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2248" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64177,7 +64177,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64203,7 +64203,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2250" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64229,7 +64229,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2251" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64255,7 +64255,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G2252" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64281,7 +64281,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G2253" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64307,7 +64307,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2254" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64333,7 +64333,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G2255" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64359,7 +64359,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G2256" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64385,7 +64385,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2257" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64411,7 +64411,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G2258" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64437,7 +64437,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2259" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64463,7 +64463,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2260" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64489,7 +64489,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2261" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64515,7 +64515,7 @@
         <v>17</v>
       </c>
       <c r="G2262" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64541,7 +64541,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64567,7 +64567,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G2264" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64593,7 +64593,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G2265" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64619,7 +64619,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2266" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64645,7 +64645,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G2267" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64671,7 +64671,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2268" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64697,7 +64697,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2269" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64723,7 +64723,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G2270" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64749,7 +64749,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G2271" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64775,7 +64775,7 @@
         <v>18</v>
       </c>
       <c r="G2272" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64801,7 +64801,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G2273" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64827,7 +64827,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G2274" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64853,7 +64853,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G2275" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64879,7 +64879,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G2276" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64905,7 +64905,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G2277" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64931,7 +64931,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2278" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64957,7 +64957,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2279" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64983,7 +64983,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G2280" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65009,7 +65009,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G2281" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65035,7 +65035,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G2282" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65061,7 +65061,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2283" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65087,7 +65087,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2284" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65113,7 +65113,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G2285" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65139,7 +65139,7 @@
         <v>18.25</v>
       </c>
       <c r="G2286" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65165,7 +65165,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G2287" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65191,7 +65191,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2288" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65217,7 +65217,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G2289" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65243,7 +65243,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G2290" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65269,7 +65269,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G2291" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65295,7 +65295,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G2292" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65321,7 +65321,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G2293" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65347,7 +65347,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2294" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65373,7 +65373,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G2295" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65399,7 +65399,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G2296" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65425,7 +65425,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G2297" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65451,7 +65451,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2298" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65477,7 +65477,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G2299" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65503,7 +65503,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2300" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65529,7 +65529,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G2301" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65555,7 +65555,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2302" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65581,7 +65581,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G2303" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65607,7 +65607,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G2304" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65633,7 +65633,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G2305" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65659,7 +65659,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G2306" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65685,7 +65685,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65711,7 +65711,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G2308" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65737,7 +65737,7 @@
         <v>18.25</v>
       </c>
       <c r="G2309" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65763,7 +65763,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G2310" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65789,7 +65789,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G2311" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65815,7 +65815,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2312" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65841,7 +65841,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G2313" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65867,7 +65867,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2314" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65893,7 +65893,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G2315" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65919,7 +65919,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2316" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65945,7 +65945,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2317" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -65971,7 +65971,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G2318" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -65997,7 +65997,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G2319" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66023,7 +66023,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G2320" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66049,7 +66049,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G2321" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66075,7 +66075,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G2322" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66101,7 +66101,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2323" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66127,7 +66127,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2324" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66153,7 +66153,7 @@
         <v>17.25</v>
       </c>
       <c r="G2325" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66179,7 +66179,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G2326" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66205,7 +66205,7 @@
         <v>17.25</v>
       </c>
       <c r="G2327" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66231,7 +66231,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66257,7 +66257,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G2329" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66283,7 +66283,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G2330" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66309,7 +66309,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G2331" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66335,7 +66335,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G2332" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66361,7 +66361,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G2333" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66387,7 +66387,7 @@
         <v>17</v>
       </c>
       <c r="G2334" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66413,7 +66413,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66439,7 +66439,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G2336" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66465,7 +66465,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G2337" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66491,7 +66491,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2338" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66517,7 +66517,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2339" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66543,7 +66543,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G2340" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66569,7 +66569,7 @@
         <v>17.75</v>
       </c>
       <c r="G2341" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66595,7 +66595,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G2342" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66621,7 +66621,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G2343" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66647,7 +66647,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G2344" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66673,7 +66673,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2345" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66699,7 +66699,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G2346" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66725,7 +66725,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66751,7 +66751,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G2348" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66777,7 +66777,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G2349" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66803,7 +66803,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G2350" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66829,7 +66829,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66855,7 +66855,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2352" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66881,7 +66881,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G2353" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66907,7 +66907,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G2354" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66933,7 +66933,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G2355" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -66959,7 +66959,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G2356" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -66985,7 +66985,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G2357" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67011,7 +67011,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2358" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67037,7 +67037,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G2359" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67063,7 +67063,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G2360" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67089,7 +67089,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2361" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67115,7 +67115,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G2362" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67141,7 +67141,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G2363" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67167,7 +67167,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G2364" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67193,7 +67193,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2365" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67219,7 +67219,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2366" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67245,7 +67245,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G2367" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67271,7 +67271,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G2368" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67297,7 +67297,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G2369" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67323,7 +67323,7 @@
         <v>20</v>
       </c>
       <c r="G2370" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67349,7 +67349,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2371" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67375,7 +67375,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2372" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67401,7 +67401,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G2373" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67427,7 +67427,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2374" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67453,7 +67453,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G2375" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67479,7 +67479,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G2376" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67505,7 +67505,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67531,7 +67531,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G2378" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67557,7 +67557,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G2379" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67583,7 +67583,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2380" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67609,7 +67609,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2381" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67635,7 +67635,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G2382" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67661,7 +67661,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G2383" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67687,7 +67687,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2384" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67713,7 +67713,7 @@
         <v>21.5</v>
       </c>
       <c r="G2385" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67739,7 +67739,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G2386" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67765,7 +67765,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G2387" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67791,7 +67791,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G2388" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67817,7 +67817,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G2389" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67843,7 +67843,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67869,7 +67869,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G2391" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67895,7 +67895,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G2392" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67921,7 +67921,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G2393" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67947,7 +67947,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G2394" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -67973,7 +67973,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -67999,7 +67999,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2396" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68025,7 +68025,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2397" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68051,7 +68051,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G2398" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68077,7 +68077,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G2399" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68103,7 +68103,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G2400" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68129,7 +68129,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G2401" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68155,7 +68155,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G2402" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68181,7 +68181,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2403" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68207,7 +68207,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2404" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68233,7 +68233,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G2405" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68259,7 +68259,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2406" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68285,7 +68285,7 @@
         <v>21.5</v>
       </c>
       <c r="G2407" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68311,7 +68311,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G2408" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68337,7 +68337,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G2409" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68363,7 +68363,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G2410" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68389,7 +68389,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G2411" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68415,7 +68415,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2412" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68441,7 +68441,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2413" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68467,7 +68467,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2414" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68493,7 +68493,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2415" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68519,7 +68519,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2416" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68545,7 +68545,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68571,7 +68571,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2418" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68597,7 +68597,7 @@
         <v>19.75</v>
       </c>
       <c r="G2419" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68623,7 +68623,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G2420" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68649,7 +68649,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G2421" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68675,7 +68675,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G2422" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68701,7 +68701,7 @@
         <v>19.25</v>
       </c>
       <c r="G2423" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68727,7 +68727,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G2424" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68753,7 +68753,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G2425" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68779,7 +68779,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G2426" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68805,7 +68805,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G2427" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68831,7 +68831,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2428" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68857,7 +68857,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G2429" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68883,7 +68883,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G2430" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68909,7 +68909,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -68935,7 +68935,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G2432" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -68961,7 +68961,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2433" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -68987,7 +68987,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2434" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69013,7 +69013,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G2435" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69039,7 +69039,7 @@
         <v>19.75</v>
       </c>
       <c r="G2436" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69065,7 +69065,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G2437" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69091,7 +69091,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G2438" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69117,7 +69117,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G2439" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69143,7 +69143,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G2440" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69169,7 +69169,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69195,7 +69195,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G2442" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69221,7 +69221,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2443" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69247,7 +69247,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G2444" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69273,7 +69273,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G2445" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69299,7 +69299,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2446" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69325,7 +69325,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G2447" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69351,7 +69351,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2448" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69377,7 +69377,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G2449" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69403,7 +69403,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G2450" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69429,7 +69429,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G2451" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69455,7 +69455,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G2452" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69481,7 +69481,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G2453" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69507,7 +69507,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G2454" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69533,7 +69533,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G2455" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -69559,7 +69559,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G2456" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69585,7 +69585,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G2457" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -69611,7 +69611,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G2458" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69637,7 +69637,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G2459" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69663,7 +69663,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G2460" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69689,7 +69689,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G2461" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69715,7 +69715,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G2462" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69741,7 +69741,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69767,7 +69767,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G2464" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69793,7 +69793,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G2465" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69819,7 +69819,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G2466" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69845,7 +69845,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2467" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69871,7 +69871,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G2468" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69897,7 +69897,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -69923,7 +69923,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G2470" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -69949,7 +69949,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G2471" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -69975,7 +69975,7 @@
         <v>19.25</v>
       </c>
       <c r="G2472" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70001,7 +70001,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70027,7 +70027,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G2474" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70053,7 +70053,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G2475" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70079,7 +70079,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G2476" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70105,7 +70105,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G2477" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70131,7 +70131,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G2478" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70157,7 +70157,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2479" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70183,7 +70183,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G2480" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70209,7 +70209,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70235,7 +70235,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G2482" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70261,7 +70261,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2483" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70287,7 +70287,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2484" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70313,7 +70313,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2485" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70339,7 +70339,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2486" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70365,7 +70365,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2487" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70391,7 +70391,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2488" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70417,7 +70417,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G2489" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70443,7 +70443,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G2490" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70469,7 +70469,7 @@
         <v>20.5</v>
       </c>
       <c r="G2491" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70495,7 +70495,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G2492" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -70521,7 +70521,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G2493" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -70547,7 +70547,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G2494" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -70573,7 +70573,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G2495" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -70581,7 +70581,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6495949074</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>65251</v>
@@ -70599,9 +70599,35 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2496" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6493981481</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>83885</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>21.6800003051758</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>21.2199993133545</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>21.6800003051758</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>21.4799995422363</v>
+      </c>
+      <c r="G2497" t="s">
         <v>1786</v>
       </c>
-      <c r="H2496" t="s">
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="1789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="1790">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,136 +38,136 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59860992431641</t>
+    <t xml:space="preserve">8.59860897064209</t>
   </si>
   <si>
     <t xml:space="preserve">ACE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61100769042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3010368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43742370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48082160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61720657348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80319023132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68540096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30723667144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35063171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20804405212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91667222976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97246646881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13985061645508</t>
+    <t xml:space="preserve">8.611008644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30103778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.437424659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48082065582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61720752716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80319118499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68540000915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30723762512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3506326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20804500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91667127609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97246551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13985157012939</t>
   </si>
   <si>
     <t xml:space="preserve">8.15225028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27624034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38782787322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49321937561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50561714172363</t>
+    <t xml:space="preserve">8.2762393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3878288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49322032928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50561809539795</t>
   </si>
   <si>
     <t xml:space="preserve">8.39402770996094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36922931671143</t>
+    <t xml:space="preserve">8.36923122406006</t>
   </si>
   <si>
     <t xml:space="preserve">8.33203315734863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99106597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59429979324341</t>
+    <t xml:space="preserve">7.99106502532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59430265426636</t>
   </si>
   <si>
     <t xml:space="preserve">7.45791387557983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3153281211853</t>
+    <t xml:space="preserve">7.31532859802246</t>
   </si>
   <si>
     <t xml:space="preserve">7.46411418914795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66869497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63149929046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65629625320435</t>
+    <t xml:space="preserve">7.66869401931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63149833679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65629482269287</t>
   </si>
   <si>
     <t xml:space="preserve">7.65009737014771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44551563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60050106048584</t>
+    <t xml:space="preserve">7.44551658630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.600501537323</t>
   </si>
   <si>
     <t xml:space="preserve">7.6810941696167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55090618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6872935295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60669994354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73688745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64389705657959</t>
+    <t xml:space="preserve">7.55090522766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68729305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60670042037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73688840866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64389848709106</t>
   </si>
   <si>
     <t xml:space="preserve">7.5757040977478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53230619430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0158634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38163089752197</t>
+    <t xml:space="preserve">7.53230762481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01586246490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38162899017334</t>
   </si>
   <si>
     <t xml:space="preserve">8.67920207977295</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">8.76599311828613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83418655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78459167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46842193603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41882610321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33823394775391</t>
+    <t xml:space="preserve">8.83418846130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.784592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46842098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41882514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33823299407959</t>
   </si>
   <si>
     <t xml:space="preserve">8.45602226257324</t>
@@ -206,115 +206,115 @@
     <t xml:space="preserve">8.43122482299805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34443283081055</t>
+    <t xml:space="preserve">8.40642738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">8.4746208190918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24524307250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90427446365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87327575683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73068952560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79268360137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8546781539917</t>
+    <t xml:space="preserve">8.24524211883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90427398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87327718734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73069000244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79268264770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85467767715454</t>
   </si>
   <si>
     <t xml:space="preserve">7.89807462692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96006774902344</t>
+    <t xml:space="preserve">7.9600682258606</t>
   </si>
   <si>
     <t xml:space="preserve">8.04686069488525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99726343154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96626710891724</t>
+    <t xml:space="preserve">7.99726486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96626853942871</t>
   </si>
   <si>
     <t xml:space="preserve">7.86707639694214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78028440475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11505508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17704772949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02206230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88567495346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82988119125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0406608581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00966358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09645557403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19564723968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23284244537354</t>
+    <t xml:space="preserve">7.78028535842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.090256690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11505317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1770486831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02206134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88567447662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82988023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04066181182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00966453552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09645652770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19564533233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23284339904785</t>
   </si>
   <si>
     <t xml:space="preserve">8.18324756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05925941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76168632507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5261082649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56330347061157</t>
+    <t xml:space="preserve">8.05925750732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7616868019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52610731124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56330442428589</t>
   </si>
   <si>
     <t xml:space="preserve">7.42071771621704</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19133949279785</t>
+    <t xml:space="preserve">7.19133901596069</t>
   </si>
   <si>
     <t xml:space="preserve">6.85656929016113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96815967559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97435903549194</t>
+    <t xml:space="preserve">6.96815919876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9743595123291</t>
   </si>
   <si>
     <t xml:space="preserve">7.12314414978027</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">7.09073781967163</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05184888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14259004592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05833005905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6824049949646</t>
+    <t xml:space="preserve">7.05184841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14259052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05833148956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68240404129028</t>
   </si>
   <si>
     <t xml:space="preserve">6.37777471542358</t>
@@ -341,52 +341,52 @@
     <t xml:space="preserve">6.49444150924683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61110830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08425664901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99999666213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03888511657715</t>
+    <t xml:space="preserve">6.61110782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08425712585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99999618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03888559341431</t>
   </si>
   <si>
     <t xml:space="preserve">6.93518114089966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78610754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370073318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82499647140503</t>
+    <t xml:space="preserve">6.78610801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82499742507935</t>
   </si>
   <si>
     <t xml:space="preserve">6.86388683319092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74073791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91573810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89629411697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15555191040039</t>
+    <t xml:space="preserve">6.7407374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91573905944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92869901657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8962926864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15555238723755</t>
   </si>
   <si>
     <t xml:space="preserve">7.14907121658325</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5833306312561</t>
+    <t xml:space="preserve">7.58332967758179</t>
   </si>
   <si>
     <t xml:space="preserve">7.55740356445312</t>
@@ -395,22 +395,22 @@
     <t xml:space="preserve">8.0694408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0435152053833</t>
+    <t xml:space="preserve">8.04351711273193</t>
   </si>
   <si>
     <t xml:space="preserve">8.01110744476318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16666221618652</t>
+    <t xml:space="preserve">8.16666316986084</t>
   </si>
   <si>
     <t xml:space="preserve">8.17962551116943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07592296600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05647754669189</t>
+    <t xml:space="preserve">8.0759220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05647850036621</t>
   </si>
   <si>
     <t xml:space="preserve">8.10184764862061</t>
@@ -419,124 +419,124 @@
     <t xml:space="preserve">7.95277404785156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82962608337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87499523162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90740299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481199264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75832986831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74536609649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77129316329956</t>
+    <t xml:space="preserve">7.82962656021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87499666213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90740346908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481151580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75833034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7453670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77129173278809</t>
   </si>
   <si>
     <t xml:space="preserve">7.71944093704224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57684803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65462589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7064790725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81666421890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79073715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69351577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72592115402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6999979019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50555181503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37592220306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39536714553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47314500808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3240704536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25277376174927</t>
+    <t xml:space="preserve">7.57684898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65462636947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70647859573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81666374206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79073810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69351530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72592210769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69999647140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50555229187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37592363357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39536666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47314405441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32407093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25277423858643</t>
   </si>
   <si>
     <t xml:space="preserve">7.22684812545776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18147802352905</t>
+    <t xml:space="preserve">7.18147897720337</t>
   </si>
   <si>
     <t xml:space="preserve">7.20092296600342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22036647796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18795919418335</t>
+    <t xml:space="preserve">7.22036790847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18796062469482</t>
   </si>
   <si>
     <t xml:space="preserve">7.1685152053833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16203451156616</t>
+    <t xml:space="preserve">7.16203355789185</t>
   </si>
   <si>
     <t xml:space="preserve">7.19444179534912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17499732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07129192352295</t>
+    <t xml:space="preserve">7.17499685287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07129383087158</t>
   </si>
   <si>
     <t xml:space="preserve">6.96758985519409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04536771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98703384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23333024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34999704360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41481113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55092239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52499532699585</t>
+    <t xml:space="preserve">7.0453667640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98703336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2333288192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34999513626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41481161117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55092144012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52499628067017</t>
   </si>
   <si>
     <t xml:space="preserve">7.64166307449341</t>
@@ -545,25 +545,25 @@
     <t xml:space="preserve">7.5962929725647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6157374382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64814567565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49258852005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38888597488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46018218994141</t>
+    <t xml:space="preserve">7.61573839187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64814424514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49258947372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38888549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46018314361572</t>
   </si>
   <si>
     <t xml:space="preserve">7.36944150924683</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30462694168091</t>
+    <t xml:space="preserve">7.30462646484375</t>
   </si>
   <si>
     <t xml:space="preserve">6.84444189071655</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">6.5722188949585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59166383743286</t>
+    <t xml:space="preserve">6.5916633605957</t>
   </si>
   <si>
     <t xml:space="preserve">6.54629373550415</t>
@@ -584,103 +584,103 @@
     <t xml:space="preserve">6.43610906600952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47823810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52684831619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64999723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53332996368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59814691543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52036809921265</t>
+    <t xml:space="preserve">6.47823715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52684926986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64999771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53333044052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59814548492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5203685760498</t>
   </si>
   <si>
     <t xml:space="preserve">6.42962694168091</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87036800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10369920730591</t>
+    <t xml:space="preserve">6.87036848068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10370111465454</t>
   </si>
   <si>
     <t xml:space="preserve">7.25925636291504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48610877990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4342565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42777538299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3824028968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51851558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51203298568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66758918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68055295944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71295881271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8944411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79721879959106</t>
+    <t xml:space="preserve">7.48610830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43425559997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42777442932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38240575790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51203346252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66758966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68055200576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71295976638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89444017410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79721927642822</t>
   </si>
   <si>
     <t xml:space="preserve">7.84258985519409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34351444244385</t>
+    <t xml:space="preserve">7.34351539611816</t>
   </si>
   <si>
     <t xml:space="preserve">7.40184926986694</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46666431427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4083309173584</t>
+    <t xml:space="preserve">7.46666383743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40833044052124</t>
   </si>
   <si>
     <t xml:space="preserve">7.73888492584229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68703413009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6222186088562</t>
+    <t xml:space="preserve">7.68703317642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62221956253052</t>
   </si>
   <si>
     <t xml:space="preserve">7.63518190383911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73240518569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7777738571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83610773086548</t>
+    <t xml:space="preserve">7.73240375518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77777290344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83610868453979</t>
   </si>
   <si>
     <t xml:space="preserve">7.75184917449951</t>
@@ -689,25 +689,25 @@
     <t xml:space="preserve">7.62870073318481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97221899032593</t>
+    <t xml:space="preserve">7.97221755981445</t>
   </si>
   <si>
     <t xml:space="preserve">7.85555219650269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92684888839722</t>
+    <t xml:space="preserve">7.9268479347229</t>
   </si>
   <si>
     <t xml:space="preserve">8.037034034729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09536647796631</t>
+    <t xml:space="preserve">8.09536552429199</t>
   </si>
   <si>
     <t xml:space="preserve">8.13425540924072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20555305480957</t>
+    <t xml:space="preserve">8.20555210113525</t>
   </si>
   <si>
     <t xml:space="preserve">8.28981113433838</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">8.24444103240967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147773742676</t>
+    <t xml:space="preserve">8.23147869110107</t>
   </si>
   <si>
     <t xml:space="preserve">8.22499656677246</t>
@@ -725,46 +725,46 @@
     <t xml:space="preserve">8.27036762237549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46481037139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45832920074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43240356445312</t>
+    <t xml:space="preserve">8.46481132507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45833015441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43240451812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.42592239379883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35462760925293</t>
+    <t xml:space="preserve">8.35462665557861</t>
   </si>
   <si>
     <t xml:space="preserve">8.55555152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52314472198486</t>
+    <t xml:space="preserve">8.52314376831055</t>
   </si>
   <si>
     <t xml:space="preserve">8.39351463317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47129249572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60740375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61388492584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6203670501709</t>
+    <t xml:space="preserve">8.47129154205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6074047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6138858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62036609649658</t>
   </si>
   <si>
     <t xml:space="preserve">8.56203365325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80832862854004</t>
+    <t xml:space="preserve">8.80832958221436</t>
   </si>
   <si>
     <t xml:space="preserve">8.6786994934082</t>
@@ -773,22 +773,22 @@
     <t xml:space="preserve">8.81481170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84073734283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92499542236328</t>
+    <t xml:space="preserve">8.84073638916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9249963760376</t>
   </si>
   <si>
     <t xml:space="preserve">9.12592220306396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17777252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00277328491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95092296600342</t>
+    <t xml:space="preserve">9.17777347564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00277423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9509220123291</t>
   </si>
   <si>
     <t xml:space="preserve">8.99629211425781</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">9.18425464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01573657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02869987487793</t>
+    <t xml:space="preserve">9.01573753356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02870082855225</t>
   </si>
   <si>
     <t xml:space="preserve">9.20369911193848</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">9.2814769744873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30740261077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34629154205322</t>
+    <t xml:space="preserve">9.30740356445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34629249572754</t>
   </si>
   <si>
     <t xml:space="preserve">9.43703269958496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32684803009033</t>
+    <t xml:space="preserve">9.32684993743896</t>
   </si>
   <si>
     <t xml:space="preserve">9.43055057525635</t>
@@ -827,25 +827,25 @@
     <t xml:space="preserve">9.38518047332764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41758918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33332920074463</t>
+    <t xml:space="preserve">9.41758632659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33333015441895</t>
   </si>
   <si>
     <t xml:space="preserve">9.50184726715088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50833034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44351387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54721736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41110801696777</t>
+    <t xml:space="preserve">9.50832843780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44351482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54721832275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41110706329346</t>
   </si>
   <si>
     <t xml:space="preserve">9.35925483703613</t>
@@ -857,19 +857,19 @@
     <t xml:space="preserve">9.41343212127686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59628391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50147342681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44729518890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4811544418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21026515960693</t>
+    <t xml:space="preserve">9.59628295898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50147247314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44729328155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48115634918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21026611328125</t>
   </si>
   <si>
     <t xml:space="preserve">9.09513759613037</t>
@@ -878,19 +878,19 @@
     <t xml:space="preserve">9.14931488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98678016662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83101844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84456253051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93937683105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81070327758789</t>
+    <t xml:space="preserve">8.98678112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83101940155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84456443786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93937492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81070232391357</t>
   </si>
   <si>
     <t xml:space="preserve">8.93260288238525</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">8.87165355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04773139953613</t>
+    <t xml:space="preserve">9.04773044586182</t>
   </si>
   <si>
     <t xml:space="preserve">9.08159255981445</t>
@@ -914,16 +914,16 @@
     <t xml:space="preserve">9.20349311828613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10868167877197</t>
+    <t xml:space="preserve">9.10868072509766</t>
   </si>
   <si>
     <t xml:space="preserve">9.12222576141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00709915161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07482051849365</t>
+    <t xml:space="preserve">9.0070972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07481956481934</t>
   </si>
   <si>
     <t xml:space="preserve">8.87842464447021</t>
@@ -932,52 +932,52 @@
     <t xml:space="preserve">8.92583084106445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90551471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52626800537109</t>
+    <t xml:space="preserve">8.90551280975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52626705169678</t>
   </si>
   <si>
     <t xml:space="preserve">8.58721828460693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5465841293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56013011932373</t>
+    <t xml:space="preserve">8.54658508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5601282119751</t>
   </si>
   <si>
     <t xml:space="preserve">8.68880176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53981113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44500064849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33664512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47208976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47886276245117</t>
+    <t xml:space="preserve">8.53981304168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44500160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33664608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47209072113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47886180877686</t>
   </si>
   <si>
     <t xml:space="preserve">8.41113948822021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42468452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3840503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39082336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32987213134766</t>
+    <t xml:space="preserve">8.42468357086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38405132293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3908224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32987117767334</t>
   </si>
   <si>
     <t xml:space="preserve">8.28246593475342</t>
@@ -986,25 +986,25 @@
     <t xml:space="preserve">8.26892185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2486047744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19442844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16733837127686</t>
+    <t xml:space="preserve">8.24860572814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19442749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16733741760254</t>
   </si>
   <si>
     <t xml:space="preserve">8.21474456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37050628662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29601001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39759349822998</t>
+    <t xml:space="preserve">8.37050533294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29601097106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3975944519043</t>
   </si>
   <si>
     <t xml:space="preserve">8.81747436523438</t>
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">8.76329612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67525768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68202877044678</t>
+    <t xml:space="preserve">8.67525863647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68202781677246</t>
   </si>
   <si>
     <t xml:space="preserve">8.6955738067627</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">8.80392932891846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85810661315918</t>
+    <t xml:space="preserve">8.85810852050781</t>
   </si>
   <si>
     <t xml:space="preserve">8.74298000335693</t>
@@ -1037,19 +1037,19 @@
     <t xml:space="preserve">8.74975204467773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79038524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88519668579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96646404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91228580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89196968078613</t>
+    <t xml:space="preserve">8.79038429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88519763946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96646499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91228485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89197063446045</t>
   </si>
   <si>
     <t xml:space="preserve">9.18317699432373</t>
@@ -1058,25 +1058,25 @@
     <t xml:space="preserve">9.19672107696533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29153347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24412631988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36602783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40666103363037</t>
+    <t xml:space="preserve">9.29153251647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24412536621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36602687835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40666198730469</t>
   </si>
   <si>
     <t xml:space="preserve">9.54210662841797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46761035919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38634395599365</t>
+    <t xml:space="preserve">9.46761131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38634490966797</t>
   </si>
   <si>
     <t xml:space="preserve">9.52178955078125</t>
@@ -1085,34 +1085,34 @@
     <t xml:space="preserve">9.49469947814941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84008407592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86717319488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88749122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83331298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76559066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74527359008789</t>
+    <t xml:space="preserve">9.84008502960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86717414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88748931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83331394195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76558876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74527549743652</t>
   </si>
   <si>
     <t xml:space="preserve">9.70464038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58273887634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71818542480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67077827453613</t>
+    <t xml:space="preserve">9.58273983001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71818447113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67077922821045</t>
   </si>
   <si>
     <t xml:space="preserve">9.96875858306885</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">9.94844150543213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91458034515381</t>
+    <t xml:space="preserve">9.91458129882812</t>
   </si>
   <si>
     <t xml:space="preserve">10.0161638259888</t>
@@ -1130,34 +1130,34 @@
     <t xml:space="preserve">9.96198558807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92135143280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90103626251221</t>
+    <t xml:space="preserve">9.92135047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90103530883789</t>
   </si>
   <si>
     <t xml:space="preserve">10.2599649429321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4451093673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5670099258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4857416152954</t>
+    <t xml:space="preserve">11.445107460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.567008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4857425689697</t>
   </si>
   <si>
     <t xml:space="preserve">11.5128326416016</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4518804550171</t>
+    <t xml:space="preserve">11.4518823623657</t>
   </si>
   <si>
     <t xml:space="preserve">11.4383363723755</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49928855896</t>
+    <t xml:space="preserve">11.4992876052856</t>
   </si>
   <si>
     <t xml:space="preserve">11.3502979278564</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">10.9845952987671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.876238822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1674470901489</t>
+    <t xml:space="preserve">10.8762397766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1674461364746</t>
   </si>
   <si>
     <t xml:space="preserve">10.8152894973755</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5850324630737</t>
+    <t xml:space="preserve">10.585033416748</t>
   </si>
   <si>
     <t xml:space="preserve">10.4495878219604</t>
@@ -1190,16 +1190,16 @@
     <t xml:space="preserve">10.5443992614746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4292697906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4699048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6324396133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8220615386963</t>
+    <t xml:space="preserve">10.4292707443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4699039459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6324377059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8220596313477</t>
   </si>
   <si>
     <t xml:space="preserve">10.9168739318848</t>
@@ -1211,43 +1211,43 @@
     <t xml:space="preserve">10.8017454147339</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7204780578613</t>
+    <t xml:space="preserve">10.7204790115356</t>
   </si>
   <si>
     <t xml:space="preserve">10.6256656646729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6730718612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8356065750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9371910095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.998140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0455455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1268138885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9304170608521</t>
+    <t xml:space="preserve">10.6730728149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8356056213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9371891021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9981412887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0455465316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1268129348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9304180145264</t>
   </si>
   <si>
     <t xml:space="preserve">10.8423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7746562957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7340230941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5918045043945</t>
+    <t xml:space="preserve">10.7746553421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7340221405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5918054580688</t>
   </si>
   <si>
     <t xml:space="preserve">10.5376272201538</t>
@@ -1256,43 +1256,43 @@
     <t xml:space="preserve">10.5173101425171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3615484237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0974311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87394618988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1922426223755</t>
+    <t xml:space="preserve">10.3615493774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.097430229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87394714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1922416687012</t>
   </si>
   <si>
     <t xml:space="preserve">9.92812442779541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0364818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0567960739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1245203018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0838871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97552871704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69786739349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50824356079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44052028656006</t>
+    <t xml:space="preserve">10.0364799499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0567970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1245193481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0838851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97552967071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69786643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50824546813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44052219390869</t>
   </si>
   <si>
     <t xml:space="preserve">9.64369010925293</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">9.66400718688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67755126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55565071105957</t>
+    <t xml:space="preserve">9.67755222320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083831787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55564975738525</t>
   </si>
   <si>
     <t xml:space="preserve">9.34571075439453</t>
@@ -1319,43 +1319,43 @@
     <t xml:space="preserve">9.13577079772949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23058319091797</t>
+    <t xml:space="preserve">9.23058128356934</t>
   </si>
   <si>
     <t xml:space="preserve">9.06804752349854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1764030456543</t>
+    <t xml:space="preserve">9.17640399932861</t>
   </si>
   <si>
     <t xml:space="preserve">9.33216571807861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27798843383789</t>
+    <t xml:space="preserve">9.27798748016357</t>
   </si>
   <si>
     <t xml:space="preserve">9.23735523223877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1628589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29830360412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42697620391846</t>
+    <t xml:space="preserve">9.16285991668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29830455780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42697715759277</t>
   </si>
   <si>
     <t xml:space="preserve">9.53533363342285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62337303161621</t>
+    <t xml:space="preserve">9.62337398529053</t>
   </si>
   <si>
     <t xml:space="preserve">9.79945087432861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80622482299805</t>
+    <t xml:space="preserve">9.80622291564941</t>
   </si>
   <si>
     <t xml:space="preserve">9.77236270904541</t>
@@ -1364,37 +1364,37 @@
     <t xml:space="preserve">9.95521354675293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81976890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75881671905518</t>
+    <t xml:space="preserve">9.81976795196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75881862640381</t>
   </si>
   <si>
     <t xml:space="preserve">9.47438335418701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71141147613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30507659912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0138692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79715919494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03418636322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39311599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26281547546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2912073135376</t>
+    <t xml:space="preserve">9.7114143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30507755279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01387023925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79715728759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03418731689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39311504364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26281452178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29120635986328</t>
   </si>
   <si>
     <t xml:space="preserve">9.24152088165283</t>
@@ -1403,13 +1403,13 @@
     <t xml:space="preserve">9.1137580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14924716949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697631835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07117080688477</t>
+    <t xml:space="preserve">9.14924812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07116985321045</t>
   </si>
   <si>
     <t xml:space="preserve">9.03568077087402</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">8.99309349060059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04277801513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02148532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19183444976807</t>
+    <t xml:space="preserve">9.04277896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19183540344238</t>
   </si>
   <si>
     <t xml:space="preserve">9.27701091766357</t>
@@ -1433,49 +1433,49 @@
     <t xml:space="preserve">9.39767551422119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2131290435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10665988922119</t>
+    <t xml:space="preserve">9.21312808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10666084289551</t>
   </si>
   <si>
     <t xml:space="preserve">9.12795448303223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22732448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26991176605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1208553314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17763900756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3834810256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44026470184326</t>
+    <t xml:space="preserve">9.22732543945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26991271972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12085628509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17763996124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38347911834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44026279449463</t>
   </si>
   <si>
     <t xml:space="preserve">9.4118709564209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70288753509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56092834472656</t>
+    <t xml:space="preserve">9.60351657867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70288562774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56092929840088</t>
   </si>
   <si>
     <t xml:space="preserve">9.61771106719971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65320110321045</t>
+    <t xml:space="preserve">9.65320301055908</t>
   </si>
   <si>
     <t xml:space="preserve">9.6815938949585</t>
@@ -1484,55 +1484,55 @@
     <t xml:space="preserve">9.57512474060059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66029930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53253746032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45445919036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5041446685791</t>
+    <t xml:space="preserve">9.66030025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53253555297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45445823669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50414562225342</t>
   </si>
   <si>
     <t xml:space="preserve">9.30540180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34799098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28410720825195</t>
+    <t xml:space="preserve">9.34799003601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28410816192627</t>
   </si>
   <si>
     <t xml:space="preserve">9.24861907958984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09246444702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8227424621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71627235412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68078327178955</t>
+    <t xml:space="preserve">9.09246349334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82274341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71627330780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68078231811523</t>
   </si>
   <si>
     <t xml:space="preserve">8.78725242614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97889709472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01438617706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14214992523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23442363739014</t>
+    <t xml:space="preserve">8.97889614105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0143871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14215087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23442459106445</t>
   </si>
   <si>
     <t xml:space="preserve">9.29830551147461</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">9.3905782699585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42606639862061</t>
+    <t xml:space="preserve">9.42606830596924</t>
   </si>
   <si>
     <t xml:space="preserve">9.37638092041016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16344356536865</t>
+    <t xml:space="preserve">9.16344451904297</t>
   </si>
   <si>
     <t xml:space="preserve">9.04987621307373</t>
@@ -1556,46 +1556,46 @@
     <t xml:space="preserve">9.17054176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74466514587402</t>
+    <t xml:space="preserve">8.74466419219971</t>
   </si>
   <si>
     <t xml:space="preserve">8.69497871398926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51043128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48204040527344</t>
+    <t xml:space="preserve">8.51043224334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48204135894775</t>
   </si>
   <si>
     <t xml:space="preserve">8.39686584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59560871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49623680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26910305023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26200485229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22651386260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04196739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06326103210449</t>
+    <t xml:space="preserve">8.59560775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49623775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26910209655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26200389862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22651481628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04196834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06326293945312</t>
   </si>
   <si>
     <t xml:space="preserve">8.07036018371582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93549919128418</t>
+    <t xml:space="preserve">7.93549871444702</t>
   </si>
   <si>
     <t xml:space="preserve">8.14843845367432</t>
@@ -1604,13 +1604,13 @@
     <t xml:space="preserve">8.16263389587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2407112121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28329849243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38266944885254</t>
+    <t xml:space="preserve">8.24071025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28329753875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38267230987549</t>
   </si>
   <si>
     <t xml:space="preserve">8.36137580871582</t>
@@ -1622,91 +1622,91 @@
     <t xml:space="preserve">8.42525768280029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15634536743164</t>
+    <t xml:space="preserve">9.15634441375732</t>
   </si>
   <si>
     <t xml:space="preserve">9.08536624908447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06407356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80854606628418</t>
+    <t xml:space="preserve">9.06407260894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8085470199585</t>
   </si>
   <si>
     <t xml:space="preserve">8.81564426422119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65948963165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56011867523193</t>
+    <t xml:space="preserve">8.65948867797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56011962890625</t>
   </si>
   <si>
     <t xml:space="preserve">8.57431411743164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44655323028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52462768554688</t>
+    <t xml:space="preserve">8.44655132293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52462863922119</t>
   </si>
   <si>
     <t xml:space="preserve">8.5175313949585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40396308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36847400665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21231842041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80144691467285</t>
+    <t xml:space="preserve">8.40396404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36847305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43945407867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21232032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8014497756958</t>
   </si>
   <si>
     <t xml:space="preserve">8.6098051071167</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3400821685791</t>
+    <t xml:space="preserve">8.34008121490479</t>
   </si>
   <si>
     <t xml:space="preserve">8.19812297821045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37557125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46074867248535</t>
+    <t xml:space="preserve">8.37557220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46074771881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.62400054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38976669311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5317268371582</t>
+    <t xml:space="preserve">8.38976764678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53172588348389</t>
   </si>
   <si>
     <t xml:space="preserve">8.68788146972656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83693695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85823059082031</t>
+    <t xml:space="preserve">8.83693885803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85823154449463</t>
   </si>
   <si>
     <t xml:space="preserve">8.90791797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25571632385254</t>
+    <t xml:space="preserve">9.25571727752686</t>
   </si>
   <si>
     <t xml:space="preserve">9.51124286651611</t>
@@ -1715,19 +1715,19 @@
     <t xml:space="preserve">9.58222198486328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47575378417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35508823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54673290252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66739845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61061382293701</t>
+    <t xml:space="preserve">9.47575283050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35508728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54673099517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66739749908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6106128692627</t>
   </si>
   <si>
     <t xml:space="preserve">9.63190841674805</t>
@@ -1742,10 +1742,10 @@
     <t xml:space="preserve">9.90872859954834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85904216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88033485412598</t>
+    <t xml:space="preserve">9.85904312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88033580780029</t>
   </si>
   <si>
     <t xml:space="preserve">9.75967025756836</t>
@@ -1763,22 +1763,22 @@
     <t xml:space="preserve">10.2423315048218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3275060653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.611424446106</t>
+    <t xml:space="preserve">10.3275051116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6114234924316</t>
   </si>
   <si>
     <t xml:space="preserve">10.7604808807373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6398153305054</t>
+    <t xml:space="preserve">10.6398162841797</t>
   </si>
   <si>
     <t xml:space="preserve">10.6824035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6043252944946</t>
+    <t xml:space="preserve">10.6043262481689</t>
   </si>
   <si>
     <t xml:space="preserve">10.7107954025269</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">10.6895017623901</t>
   </si>
   <si>
-    <t xml:space="preserve">10.774676322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7249898910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7888717651367</t>
+    <t xml:space="preserve">10.7746782302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7249908447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.788872718811</t>
   </si>
   <si>
     <t xml:space="preserve">10.7533826828003</t>
@@ -1802,46 +1802,46 @@
     <t xml:space="preserve">10.7391862869263</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7178945541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6965980529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9166355133057</t>
+    <t xml:space="preserve">10.7178936004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6965990066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9166345596313</t>
   </si>
   <si>
     <t xml:space="preserve">11.3567085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3709049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4986667633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3141202926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4418840408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4276866912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2999238967896</t>
+    <t xml:space="preserve">11.3709030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4986686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3141193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4418830871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4276876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2999248504639</t>
   </si>
   <si>
     <t xml:space="preserve">11.1579656600952</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9876155853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0018110275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1863565444946</t>
+    <t xml:space="preserve">10.9876146316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0018100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1863584518433</t>
   </si>
   <si>
     <t xml:space="preserve">11.3851003646851</t>
@@ -1856,25 +1856,25 @@
     <t xml:space="preserve">11.4702749252319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6122350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5412530899048</t>
+    <t xml:space="preserve">11.6122341156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5412540435791</t>
   </si>
   <si>
     <t xml:space="preserve">11.8535633087158</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9387397766113</t>
+    <t xml:space="preserve">11.9387378692627</t>
   </si>
   <si>
     <t xml:space="preserve">12.1090888977051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9813280105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8677587509155</t>
+    <t xml:space="preserve">11.9813261032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8677597045898</t>
   </si>
   <si>
     <t xml:space="preserve">11.8251724243164</t>
@@ -1883,40 +1883,40 @@
     <t xml:space="preserve">11.7399978637695</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6832132339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7967805862427</t>
+    <t xml:space="preserve">11.6832122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.796781539917</t>
   </si>
   <si>
     <t xml:space="preserve">11.8961515426636</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9103479385376</t>
+    <t xml:space="preserve">11.9103488922119</t>
   </si>
   <si>
     <t xml:space="preserve">11.8393678665161</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8819541931152</t>
+    <t xml:space="preserve">11.8819551467896</t>
   </si>
   <si>
     <t xml:space="preserve">11.8109760284424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.066502571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1942644119263</t>
+    <t xml:space="preserve">12.0665016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1942653656006</t>
   </si>
   <si>
     <t xml:space="preserve">12.2794399261475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3078336715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3504190444946</t>
+    <t xml:space="preserve">12.3078327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3504180908203</t>
   </si>
   <si>
     <t xml:space="preserve">12.4355955123901</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">12.5065746307373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.520770072937</t>
+    <t xml:space="preserve">12.5207681655884</t>
   </si>
   <si>
     <t xml:space="preserve">12.5349674224854</t>
@@ -1934,28 +1934,28 @@
     <t xml:space="preserve">12.5917510986328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.66273021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6343355178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7053146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8161849975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6683597564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6387968063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3874988555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3727159500122</t>
+    <t xml:space="preserve">12.6627283096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6343374252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7053174972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.81618309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6683616638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6387958526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3874998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3727169036865</t>
   </si>
   <si>
     <t xml:space="preserve">12.313588142395</t>
@@ -1973,13 +1973,13 @@
     <t xml:space="preserve">12.5353202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5796689987183</t>
+    <t xml:space="preserve">12.5796670913696</t>
   </si>
   <si>
     <t xml:space="preserve">12.7422733306885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6831426620483</t>
+    <t xml:space="preserve">12.683144569397</t>
   </si>
   <si>
     <t xml:space="preserve">12.8753128051758</t>
@@ -1991,16 +1991,16 @@
     <t xml:space="preserve">12.7718381881714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8309659957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.934440612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.697925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7127075195312</t>
+    <t xml:space="preserve">12.8309669494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9344415664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6979265213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7127094268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.5944499969482</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">12.8900957107544</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0674829483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1118288040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0527000427246</t>
+    <t xml:space="preserve">13.0674819946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1118278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0526990890503</t>
   </si>
   <si>
     <t xml:space="preserve">12.9787874221802</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">12.9492235183716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1561727523804</t>
+    <t xml:space="preserve">13.1561737060547</t>
   </si>
   <si>
     <t xml:space="preserve">12.9935703277588</t>
@@ -2054,19 +2054,19 @@
     <t xml:space="preserve">12.8605298995972</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5501041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4518213272095</t>
+    <t xml:space="preserve">12.550103187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4518194198608</t>
   </si>
   <si>
     <t xml:space="preserve">13.3335618972778</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4961671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3483419418335</t>
+    <t xml:space="preserve">13.496166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3483438491821</t>
   </si>
   <si>
     <t xml:space="preserve">13.5405111312866</t>
@@ -2075,31 +2075,31 @@
     <t xml:space="preserve">12.9640064239502</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1857404708862</t>
+    <t xml:space="preserve">13.1857385635376</t>
   </si>
   <si>
     <t xml:space="preserve">13.1709566116333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.919659614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2744302749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.259651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.289213180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2448673248291</t>
+    <t xml:space="preserve">12.9196586608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.274432182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2596521377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2892141342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2448682785034</t>
   </si>
   <si>
     <t xml:space="preserve">13.1266098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7622470855713</t>
+    <t xml:space="preserve">13.7622451782227</t>
   </si>
   <si>
     <t xml:space="preserve">13.9396333694458</t>
@@ -2108,46 +2108,46 @@
     <t xml:space="preserve">13.5552949905396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.747465133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9691972732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7770280838013</t>
+    <t xml:space="preserve">13.7474632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9691963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7770261764526</t>
   </si>
   <si>
     <t xml:space="preserve">13.6292057037354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8657197952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9544124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4666013717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4813842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4370374679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918100357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.998761177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0578889846802</t>
+    <t xml:space="preserve">13.8657217025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9544153213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4665994644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4813833236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4370384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918081283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9987621307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0578908920288</t>
   </si>
   <si>
     <t xml:space="preserve">13.8213768005371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6883344650269</t>
+    <t xml:space="preserve">13.6883354187012</t>
   </si>
   <si>
     <t xml:space="preserve">13.6587686538696</t>
@@ -2162,100 +2162,100 @@
     <t xml:space="preserve">13.3631258010864</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2300834655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8805027008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4570121765137</t>
+    <t xml:space="preserve">13.2300853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8805046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.457010269165</t>
   </si>
   <si>
     <t xml:space="preserve">14.4717922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6343955993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8191738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0409088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300413131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0039501190186</t>
+    <t xml:space="preserve">14.6343975067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8191757202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0409078598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300403594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0039520263672</t>
   </si>
   <si>
     <t xml:space="preserve">15.3735065460205</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5582838058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9278383255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1126174926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0387096405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7800188064575</t>
+    <t xml:space="preserve">15.5582857131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9278402328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1126194000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0387058258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7800207138062</t>
   </si>
   <si>
     <t xml:space="preserve">15.7061071395874</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6321973800659</t>
+    <t xml:space="preserve">15.6321954727173</t>
   </si>
   <si>
     <t xml:space="preserve">15.5213289260864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4104652404785</t>
+    <t xml:space="preserve">15.4104633331299</t>
   </si>
   <si>
     <t xml:space="preserve">15.4474182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2256841659546</t>
+    <t xml:space="preserve">15.2256870269775</t>
   </si>
   <si>
     <t xml:space="preserve">15.262640953064</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8908834457397</t>
+    <t xml:space="preserve">15.8908853530884</t>
   </si>
   <si>
     <t xml:space="preserve">14.9669961929321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7378721237183</t>
+    <t xml:space="preserve">14.7378711700439</t>
   </si>
   <si>
     <t xml:space="preserve">14.8561296463013</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4126644134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0874557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3091878890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5161371231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5309209823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8257751464844</t>
+    <t xml:space="preserve">14.4126634597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0874547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3091888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5161380767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5309219360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8257741928101</t>
   </si>
   <si>
     <t xml:space="preserve">11.4710025787354</t>
@@ -2264,37 +2264,37 @@
     <t xml:space="preserve">9.87452220916748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2145137786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57887840270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63800621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16497421264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29801559448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53453063964844</t>
+    <t xml:space="preserve">10.2145118713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57887744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63800716400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1649751663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29801464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53452968597412</t>
   </si>
   <si>
     <t xml:space="preserve">9.65278816223145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5545034408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7023267745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5988502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9388408660889</t>
+    <t xml:space="preserve">10.5545043945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7023258209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5988521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9388418197632</t>
   </si>
   <si>
     <t xml:space="preserve">10.7318906784058</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">10.9018859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2123117446899</t>
+    <t xml:space="preserve">11.2123126983643</t>
   </si>
   <si>
     <t xml:space="preserve">11.0275354385376</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">11.012752532959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0718803405762</t>
+    <t xml:space="preserve">11.0718812942505</t>
   </si>
   <si>
     <t xml:space="preserve">11.3157892227173</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">10.6505880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5175476074219</t>
+    <t xml:space="preserve">10.5175466537476</t>
   </si>
   <si>
     <t xml:space="preserve">10.9462327957153</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">11.2714424133301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5301303863525</t>
+    <t xml:space="preserve">11.5301322937012</t>
   </si>
   <si>
     <t xml:space="preserve">11.9735975265503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6040420532227</t>
+    <t xml:space="preserve">11.6040410995483</t>
   </si>
   <si>
     <t xml:space="preserve">11.2197036743164</t>
@@ -2366,16 +2366,16 @@
     <t xml:space="preserve">12.1288108825684</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4318466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5648860931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.380108833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4392366409302</t>
+    <t xml:space="preserve">12.431845664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5648851394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3801078796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4392356872559</t>
   </si>
   <si>
     <t xml:space="preserve">12.4096736907959</t>
@@ -2384,46 +2384,46 @@
     <t xml:space="preserve">12.7644462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8974876403809</t>
+    <t xml:space="preserve">12.8974866867065</t>
   </si>
   <si>
     <t xml:space="preserve">12.8235750198364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.971396446228</t>
+    <t xml:space="preserve">12.9713973999023</t>
   </si>
   <si>
     <t xml:space="preserve">13.6070327758789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8065929412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.89528465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0431070327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5331201553345</t>
+    <t xml:space="preserve">13.8065919876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8952856063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0431089401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5331211090088</t>
   </si>
   <si>
     <t xml:space="preserve">13.473991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">13.089653968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0600910186768</t>
+    <t xml:space="preserve">13.0896549224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0600900650024</t>
   </si>
   <si>
     <t xml:space="preserve">13.4887742996216</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2966051101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2512512207031</t>
+    <t xml:space="preserve">13.2966041564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2512521743774</t>
   </si>
   <si>
     <t xml:space="preserve">13.4521455764771</t>
@@ -2435,70 +2435,70 @@
     <t xml:space="preserve">12.9962720870972</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1585321426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.398060798645</t>
+    <t xml:space="preserve">13.1585330963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3980588912964</t>
   </si>
   <si>
     <t xml:space="preserve">13.2048931121826</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4212408065796</t>
+    <t xml:space="preserve">13.4212398529053</t>
   </si>
   <si>
     <t xml:space="preserve">13.5448665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4444198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5294132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3594264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1276254653931</t>
+    <t xml:space="preserve">13.4444189071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5294122695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3594274520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1276245117188</t>
   </si>
   <si>
     <t xml:space="preserve">13.0812654495239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9344577789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8108320236206</t>
+    <t xml:space="preserve">12.934458732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8108329772949</t>
   </si>
   <si>
     <t xml:space="preserve">12.9576387405396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2976131439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.150806427002</t>
+    <t xml:space="preserve">13.2976121902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1508045196533</t>
   </si>
   <si>
     <t xml:space="preserve">13.3362464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1894378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7953767776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5944852828979</t>
+    <t xml:space="preserve">13.1894388198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7953786849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944843292236</t>
   </si>
   <si>
     <t xml:space="preserve">12.7644720077515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.328519821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2126197814941</t>
+    <t xml:space="preserve">13.3285188674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2126178741455</t>
   </si>
   <si>
     <t xml:space="preserve">13.4366912841797</t>
@@ -2510,49 +2510,49 @@
     <t xml:space="preserve">13.9312009811401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.506233215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5216865539551</t>
+    <t xml:space="preserve">13.5062322616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5216856002808</t>
   </si>
   <si>
     <t xml:space="preserve">13.5371398925781</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8539323806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8230257034302</t>
+    <t xml:space="preserve">13.8539333343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8230247497559</t>
   </si>
   <si>
     <t xml:space="preserve">13.8848390579224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0702800750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6916732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4289646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6221323013306</t>
+    <t xml:space="preserve">14.0702791213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843923568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6916723251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4289655685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6221332550049</t>
   </si>
   <si>
     <t xml:space="preserve">13.5989532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.274432182312</t>
+    <t xml:space="preserve">13.2744331359863</t>
   </si>
   <si>
     <t xml:space="preserve">13.4675989151001</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7148523330688</t>
+    <t xml:space="preserve">13.7148532867432</t>
   </si>
   <si>
     <t xml:space="preserve">13.5757732391357</t>
@@ -2561,70 +2561,70 @@
     <t xml:space="preserve">13.3053388595581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6298599243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4753265380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7921209335327</t>
+    <t xml:space="preserve">13.6298589706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4753274917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7921199798584</t>
   </si>
   <si>
     <t xml:space="preserve">13.5680456161499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4830522537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8462057113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.92347240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9543809890747</t>
+    <t xml:space="preserve">13.4830532073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8462066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9234743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9543800354004</t>
   </si>
   <si>
     <t xml:space="preserve">13.5912265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3671503067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5525922775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7380323410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0007410049438</t>
+    <t xml:space="preserve">13.3671522140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5525932312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7380332946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0007419586182</t>
   </si>
   <si>
     <t xml:space="preserve">13.8925657272339</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9080200195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0780076980591</t>
+    <t xml:space="preserve">13.9080209732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0780057907104</t>
   </si>
   <si>
     <t xml:space="preserve">13.9389276504517</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8616609573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8384790420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0239191055298</t>
+    <t xml:space="preserve">13.8616619110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8384799957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0239200592041</t>
   </si>
   <si>
     <t xml:space="preserve">14.047101020813</t>
   </si>
   <si>
-    <t xml:space="preserve">14.332986831665</t>
+    <t xml:space="preserve">14.3329877853394</t>
   </si>
   <si>
     <t xml:space="preserve">14.1861810684204</t>
@@ -2633,19 +2633,19 @@
     <t xml:space="preserve">14.1784553527832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.815299987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6993999481201</t>
+    <t xml:space="preserve">13.8152990341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6993989944458</t>
   </si>
   <si>
     <t xml:space="preserve">13.3130655288696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2667055130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2898864746094</t>
+    <t xml:space="preserve">13.2667064666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2898874282837</t>
   </si>
   <si>
     <t xml:space="preserve">13.3748779296875</t>
@@ -2657,52 +2657,52 @@
     <t xml:space="preserve">13.7766666412354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7612133026123</t>
+    <t xml:space="preserve">13.761212348938</t>
   </si>
   <si>
     <t xml:space="preserve">13.7998466491699</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5835008621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4907789230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5139598846436</t>
+    <t xml:space="preserve">13.5834989547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907779693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5139579772949</t>
   </si>
   <si>
     <t xml:space="preserve">14.0161933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6375856399536</t>
+    <t xml:space="preserve">13.6375865936279</t>
   </si>
   <si>
     <t xml:space="preserve">13.042631149292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8880977630615</t>
+    <t xml:space="preserve">12.8880987167358</t>
   </si>
   <si>
     <t xml:space="preserve">12.8262853622437</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8494634628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7567453384399</t>
+    <t xml:space="preserve">12.8494644165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7567443847656</t>
   </si>
   <si>
     <t xml:space="preserve">12.5867586135864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.625391960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6872053146362</t>
+    <t xml:space="preserve">12.6022119522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6253910064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6872043609619</t>
   </si>
   <si>
     <t xml:space="preserve">12.8031053543091</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">13.4135141372681</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4057865142822</t>
+    <t xml:space="preserve">13.4057855606079</t>
   </si>
   <si>
     <t xml:space="preserve">13.1817111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8417387008667</t>
+    <t xml:space="preserve">12.841739654541</t>
   </si>
   <si>
     <t xml:space="preserve">12.8726453781128</t>
@@ -2735,22 +2735,22 @@
     <t xml:space="preserve">12.9190044403076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8571910858154</t>
+    <t xml:space="preserve">12.8571920394897</t>
   </si>
   <si>
     <t xml:space="preserve">12.6331186294556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721996307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7490177154541</t>
+    <t xml:space="preserve">12.772198677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7490186691284</t>
   </si>
   <si>
     <t xml:space="preserve">13.1971654891968</t>
   </si>
   <si>
-    <t xml:space="preserve">13.096718788147</t>
+    <t xml:space="preserve">13.0967197418213</t>
   </si>
   <si>
     <t xml:space="preserve">13.3439722061157</t>
@@ -2765,10 +2765,10 @@
     <t xml:space="preserve">12.7181119918823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7258367538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6408452987671</t>
+    <t xml:space="preserve">12.7258377075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6408443450928</t>
   </si>
   <si>
     <t xml:space="preserve">12.6176643371582</t>
@@ -2783,37 +2783,37 @@
     <t xml:space="preserve">12.8803720474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603189468384</t>
+    <t xml:space="preserve">13.5603199005127</t>
   </si>
   <si>
     <t xml:space="preserve">13.6839466094971</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9621076583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1398210525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.371621131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4102544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5570602416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5338821411133</t>
+    <t xml:space="preserve">13.9621057510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.139820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3716201782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4102535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5570621490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5338802337646</t>
   </si>
   <si>
     <t xml:space="preserve">14.4025259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2402677536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2557210922241</t>
+    <t xml:space="preserve">14.2402696609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2557220458984</t>
   </si>
   <si>
     <t xml:space="preserve">14.3948001861572</t>
@@ -2822,61 +2822,61 @@
     <t xml:space="preserve">14.5493335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9588489532471</t>
+    <t xml:space="preserve">14.9588499069214</t>
   </si>
   <si>
     <t xml:space="preserve">15.1211080551147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8043146133423</t>
+    <t xml:space="preserve">14.804313659668</t>
   </si>
   <si>
     <t xml:space="preserve">14.6343297958374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.765682220459</t>
+    <t xml:space="preserve">14.7656831741333</t>
   </si>
   <si>
     <t xml:space="preserve">14.7579545974731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6806869506836</t>
+    <t xml:space="preserve">14.6806888580322</t>
   </si>
   <si>
     <t xml:space="preserve">14.5261535644531</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6961402893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6420555114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5725135803223</t>
+    <t xml:space="preserve">14.6961421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.642053604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5725154876709</t>
   </si>
   <si>
     <t xml:space="preserve">14.6034212112427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5956935882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6575078964233</t>
+    <t xml:space="preserve">14.5956926345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.657506942749</t>
   </si>
   <si>
     <t xml:space="preserve">14.8352212905884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.997483253479</t>
+    <t xml:space="preserve">14.9974813461304</t>
   </si>
   <si>
     <t xml:space="preserve">15.19837474823</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0824756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0283880233765</t>
+    <t xml:space="preserve">15.0824766159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0283889770508</t>
   </si>
   <si>
     <t xml:space="preserve">15.0979299545288</t>
@@ -2885,10 +2885,10 @@
     <t xml:space="preserve">15.1751947402954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2061023712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747480392456</t>
+    <t xml:space="preserve">15.2061033248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747489929199</t>
   </si>
   <si>
     <t xml:space="preserve">14.8506727218628</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">14.8661279678345</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9743013381958</t>
+    <t xml:space="preserve">14.9742994308472</t>
   </si>
   <si>
     <t xml:space="preserve">15.0592937469482</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0052099227905</t>
+    <t xml:space="preserve">15.0052080154419</t>
   </si>
   <si>
     <t xml:space="preserve">14.9279413223267</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1520147323608</t>
+    <t xml:space="preserve">15.1520137786865</t>
   </si>
   <si>
     <t xml:space="preserve">15.4147233963013</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">15.8551425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8087816238403</t>
+    <t xml:space="preserve">15.808783531189</t>
   </si>
   <si>
     <t xml:space="preserve">15.6233415603638</t>
@@ -2939,19 +2939,19 @@
     <t xml:space="preserve">15.8860483169556</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9942216873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1796607971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0560359954834</t>
+    <t xml:space="preserve">15.9942235946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1796627044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.056037902832</t>
   </si>
   <si>
     <t xml:space="preserve">16.3496494293213</t>
   </si>
   <si>
-    <t xml:space="preserve">16.457820892334</t>
+    <t xml:space="preserve">16.4578227996826</t>
   </si>
   <si>
     <t xml:space="preserve">16.2651462554932</t>
@@ -2960,13 +2960,13 @@
     <t xml:space="preserve">16.0564136505127</t>
   </si>
   <si>
-    <t xml:space="preserve">15.847677230835</t>
+    <t xml:space="preserve">15.8476791381836</t>
   </si>
   <si>
     <t xml:space="preserve">15.7834548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8717651367188</t>
+    <t xml:space="preserve">15.8717632293701</t>
   </si>
   <si>
     <t xml:space="preserve">15.6871175765991</t>
@@ -2975,13 +2975,13 @@
     <t xml:space="preserve">15.64697265625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5586643218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6550016403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192296981812</t>
+    <t xml:space="preserve">15.5586624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6550035476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192277908325</t>
   </si>
   <si>
     <t xml:space="preserve">15.7673969268799</t>
@@ -2993,22 +2993,22 @@
     <t xml:space="preserve">15.5988054275513</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5827503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7112016677856</t>
+    <t xml:space="preserve">15.5827484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.711199760437</t>
   </si>
   <si>
     <t xml:space="preserve">15.7272567749023</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5907783508301</t>
+    <t xml:space="preserve">15.5907764434814</t>
   </si>
   <si>
     <t xml:space="preserve">15.5104951858521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2134523391724</t>
+    <t xml:space="preserve">15.2134504318237</t>
   </si>
   <si>
     <t xml:space="preserve">15.2616195678711</t>
@@ -3023,37 +3023,37 @@
     <t xml:space="preserve">15.8557081222534</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7352828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9119052886963</t>
+    <t xml:space="preserve">15.7352867126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9119033813477</t>
   </si>
   <si>
     <t xml:space="preserve">16.0162734985352</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7754259109497</t>
+    <t xml:space="preserve">15.7754240036011</t>
   </si>
   <si>
     <t xml:space="preserve">15.9921875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2490901947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3454284667969</t>
+    <t xml:space="preserve">16.2490921020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3454303741455</t>
   </si>
   <si>
     <t xml:space="preserve">16.538106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6665573120117</t>
+    <t xml:space="preserve">16.6665554046631</t>
   </si>
   <si>
     <t xml:space="preserve">16.9876842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0679664611816</t>
+    <t xml:space="preserve">17.0679683685303</t>
   </si>
   <si>
     <t xml:space="preserve">16.9074020385742</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">16.2330322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0724716186523</t>
+    <t xml:space="preserve">16.0724697113037</t>
   </si>
   <si>
     <t xml:space="preserve">16.4096546173096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2009220123291</t>
+    <t xml:space="preserve">16.2009201049805</t>
   </si>
   <si>
     <t xml:space="preserve">16.3133163452148</t>
@@ -3107,19 +3107,19 @@
     <t xml:space="preserve">15.3981008529663</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1090850830078</t>
+    <t xml:space="preserve">15.1090860366821</t>
   </si>
   <si>
     <t xml:space="preserve">14.916407585144</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8040132522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9806346893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9886636734009</t>
+    <t xml:space="preserve">14.804012298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9806318283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9886627197266</t>
   </si>
   <si>
     <t xml:space="preserve">14.9645757675171</t>
@@ -3128,34 +3128,34 @@
     <t xml:space="preserve">14.7478160858154</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8923225402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8120422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.900351524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8521823883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1010570526123</t>
+    <t xml:space="preserve">14.8923234939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8120431900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9003496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8521814346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.101056098938</t>
   </si>
   <si>
     <t xml:space="preserve">14.6755609512329</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7879571914673</t>
+    <t xml:space="preserve">14.787956237793</t>
   </si>
   <si>
     <t xml:space="preserve">15.117112159729</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2375364303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0930290222168</t>
+    <t xml:space="preserve">15.2375354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0930280685425</t>
   </si>
   <si>
     <t xml:space="preserve">15.2937335968018</t>
@@ -3164,46 +3164,46 @@
     <t xml:space="preserve">15.3900718688965</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0609149932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0368299484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3419027328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2535915374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1973962783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5345783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1251401901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769720077515</t>
+    <t xml:space="preserve">15.0609169006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0368309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3419046401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2535934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1973943710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5345802307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1251420974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769729614258</t>
   </si>
   <si>
     <t xml:space="preserve">15.1492261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8441543579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076749801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6113376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6595039367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1858406066895</t>
+    <t xml:space="preserve">14.8441553115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076740264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6113367080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6595048904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1858415603638</t>
   </si>
   <si>
     <t xml:space="preserve">14.306263923645</t>
@@ -3227,16 +3227,16 @@
     <t xml:space="preserve">14.61936378479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.555136680603</t>
+    <t xml:space="preserve">14.5551376342773</t>
   </si>
   <si>
     <t xml:space="preserve">14.5230255126953</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5471105575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273927688599</t>
+    <t xml:space="preserve">14.5471115112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273908615112</t>
   </si>
   <si>
     <t xml:space="preserve">14.820068359375</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">14.9244356155396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5711936950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3785171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2259817123413</t>
+    <t xml:space="preserve">14.5711946487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3785181045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.225980758667</t>
   </si>
   <si>
     <t xml:space="preserve">14.1617555618286</t>
@@ -3260,19 +3260,19 @@
     <t xml:space="preserve">14.0493612289429</t>
   </si>
   <si>
-    <t xml:space="preserve">14.193868637085</t>
+    <t xml:space="preserve">14.1938695907593</t>
   </si>
   <si>
     <t xml:space="preserve">13.8325996398926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7442903518677</t>
+    <t xml:space="preserve">13.7442893981934</t>
   </si>
   <si>
     <t xml:space="preserve">13.8486557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8085155487061</t>
+    <t xml:space="preserve">13.8085165023804</t>
   </si>
   <si>
     <t xml:space="preserve">13.5355567932129</t>
@@ -3287,10 +3287,10 @@
     <t xml:space="preserve">13.9690790176392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3704881668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3303499221802</t>
+    <t xml:space="preserve">14.3704900741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3303489685059</t>
   </si>
   <si>
     <t xml:space="preserve">14.2179536819458</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">13.6479511260986</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2947092056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5114717483521</t>
+    <t xml:space="preserve">13.2947101593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5114707946777</t>
   </si>
   <si>
     <t xml:space="preserve">13.5034437179565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2465400695801</t>
+    <t xml:space="preserve">13.2465410232544</t>
   </si>
   <si>
     <t xml:space="preserve">13.415132522583</t>
@@ -3320,31 +3320,31 @@
     <t xml:space="preserve">13.3187952041626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4071054458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1100606918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.085976600647</t>
+    <t xml:space="preserve">13.4071063995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1100616455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0859756469727</t>
   </si>
   <si>
     <t xml:space="preserve">13.2224550247192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5756978988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.664008140564</t>
+    <t xml:space="preserve">13.5756969451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6640071868896</t>
   </si>
   <si>
     <t xml:space="preserve">13.198371887207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0217514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8611869812012</t>
+    <t xml:space="preserve">13.0217504501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8611879348755</t>
   </si>
   <si>
     <t xml:space="preserve">12.7086505889893</t>
@@ -3356,31 +3356,31 @@
     <t xml:space="preserve">13.0137224197388</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3589353561401</t>
+    <t xml:space="preserve">13.3589363098145</t>
   </si>
   <si>
     <t xml:space="preserve">13.1261186599731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8210458755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6363973617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9735822677612</t>
+    <t xml:space="preserve">12.8210468292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6363964080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9735803604126</t>
   </si>
   <si>
     <t xml:space="preserve">12.9093561172485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8772449493408</t>
+    <t xml:space="preserve">12.8772439956665</t>
   </si>
   <si>
     <t xml:space="preserve">13.1421747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2706270217896</t>
+    <t xml:space="preserve">13.2706260681152</t>
   </si>
   <si>
     <t xml:space="preserve">13.5516119003296</t>
@@ -3395,19 +3395,19 @@
     <t xml:space="preserve">13.4392175674438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.350905418396</t>
+    <t xml:space="preserve">13.3509063720703</t>
   </si>
   <si>
     <t xml:space="preserve">13.7202062606812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.009220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8807697296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5596408843994</t>
+    <t xml:space="preserve">14.0092210769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8807706832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5596399307251</t>
   </si>
   <si>
     <t xml:space="preserve">13.5997819900513</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">13.4231605529785</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3027372360229</t>
+    <t xml:space="preserve">13.3027381896973</t>
   </si>
   <si>
     <t xml:space="preserve">13.3749923706055</t>
@@ -3428,22 +3428,22 @@
     <t xml:space="preserve">13.0297794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1020317077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0940046310425</t>
+    <t xml:space="preserve">13.102032661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0940055847168</t>
   </si>
   <si>
     <t xml:space="preserve">12.9494962692261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7487916946411</t>
+    <t xml:space="preserve">12.7487926483154</t>
   </si>
   <si>
     <t xml:space="preserve">12.8852710723877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5240020751953</t>
+    <t xml:space="preserve">12.5240030288696</t>
   </si>
   <si>
     <t xml:space="preserve">12.6444253921509</t>
@@ -3455,13 +3455,13 @@
     <t xml:space="preserve">12.9334411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.804988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9254131317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1341466903687</t>
+    <t xml:space="preserve">12.8049898147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9254121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1341457366943</t>
   </si>
   <si>
     <t xml:space="preserve">12.9816102981567</t>
@@ -3482,22 +3482,22 @@
     <t xml:space="preserve">13.2786540985107</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6845664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4838628768921</t>
+    <t xml:space="preserve">12.6845655441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4838619232178</t>
   </si>
   <si>
     <t xml:space="preserve">12.3393535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5320310592651</t>
+    <t xml:space="preserve">12.5320301055908</t>
   </si>
   <si>
     <t xml:space="preserve">12.1839189529419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8018436431885</t>
+    <t xml:space="preserve">11.8018445968628</t>
   </si>
   <si>
     <t xml:space="preserve">11.74241065979</t>
@@ -3533,28 +3533,28 @@
     <t xml:space="preserve">12.0141067504883</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0905227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9376935958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6150541305542</t>
+    <t xml:space="preserve">12.090521812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9376926422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6150531768799</t>
   </si>
   <si>
     <t xml:space="preserve">11.4792051315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5556182861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6659965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6575050354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.750901222229</t>
+    <t xml:space="preserve">11.5556192398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6659955978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6575059890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7509021759033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7339200973511</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">11.8358068466187</t>
   </si>
   <si>
-    <t xml:space="preserve">11.759391784668</t>
+    <t xml:space="preserve">11.7593927383423</t>
   </si>
   <si>
     <t xml:space="preserve">11.8867502212524</t>
@@ -3584,22 +3584,22 @@
     <t xml:space="preserve">11.598072052002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5471286773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.581090927124</t>
+    <t xml:space="preserve">11.5471296310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5810918807983</t>
   </si>
   <si>
     <t xml:space="preserve">11.4707145690918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3688287734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.343355178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3009033203125</t>
+    <t xml:space="preserve">11.3688278198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3433561325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3009042739868</t>
   </si>
   <si>
     <t xml:space="preserve">11.2499599456787</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">10.1886425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86600208282471</t>
+    <t xml:space="preserve">9.86600303649902</t>
   </si>
   <si>
     <t xml:space="preserve">9.71317291259766</t>
@@ -3638,19 +3638,19 @@
     <t xml:space="preserve">10.3075103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1716604232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0697746276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9169454574585</t>
+    <t xml:space="preserve">10.1716613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0697755813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91694641113281</t>
   </si>
   <si>
     <t xml:space="preserve">10.0867567062378</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69619178771973</t>
+    <t xml:space="preserve">9.69619274139404</t>
   </si>
   <si>
     <t xml:space="preserve">9.47543811798096</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">9.36506080627441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49241924285889</t>
+    <t xml:space="preserve">9.4924201965332</t>
   </si>
   <si>
     <t xml:space="preserve">9.38204193115234</t>
@@ -3701,31 +3701,31 @@
     <t xml:space="preserve">9.72166347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0273237228394</t>
+    <t xml:space="preserve">10.027322769165</t>
   </si>
   <si>
     <t xml:space="preserve">10.1037368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1207180023193</t>
+    <t xml:space="preserve">10.1207189559937</t>
   </si>
   <si>
     <t xml:space="preserve">9.80656909942627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2395868301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6216602325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8424139022827</t>
+    <t xml:space="preserve">10.2395858764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6216611862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.842414855957</t>
   </si>
   <si>
     <t xml:space="preserve">10.8593950271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8254327774048</t>
+    <t xml:space="preserve">10.8254337310791</t>
   </si>
   <si>
     <t xml:space="preserve">10.8678855895996</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">11.173544883728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0292053222656</t>
+    <t xml:space="preserve">11.0292062759399</t>
   </si>
   <si>
     <t xml:space="preserve">11.2584505081177</t>
@@ -3779,16 +3779,16 @@
     <t xml:space="preserve">11.1141109466553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1650543212891</t>
+    <t xml:space="preserve">11.1650533676147</t>
   </si>
   <si>
     <t xml:space="preserve">11.2414693832397</t>
   </si>
   <si>
-    <t xml:space="preserve">11.419771194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3858089447021</t>
+    <t xml:space="preserve">11.4197702407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3858079910278</t>
   </si>
   <si>
     <t xml:space="preserve">11.3942995071411</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">11.003734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1226015090942</t>
+    <t xml:space="preserve">11.1226024627686</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159976959229</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">11.2244882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.411280632019</t>
+    <t xml:space="preserve">11.4112796783447</t>
   </si>
   <si>
     <t xml:space="preserve">11.5216569900513</t>
@@ -3836,13 +3836,13 @@
     <t xml:space="preserve">12.1754283905029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0480699539185</t>
+    <t xml:space="preserve">12.0480690002441</t>
   </si>
   <si>
     <t xml:space="preserve">11.9971265792847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2093906402588</t>
+    <t xml:space="preserve">12.2093915939331</t>
   </si>
   <si>
     <t xml:space="preserve">12.1329755783081</t>
@@ -3860,13 +3860,13 @@
     <t xml:space="preserve">12.0650510787964</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056171417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8697690963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7169399261475</t>
+    <t xml:space="preserve">12.0056180953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8697681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7169389724731</t>
   </si>
   <si>
     <t xml:space="preserve">11.8188257217407</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">10.5622262954712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4263772964478</t>
+    <t xml:space="preserve">10.4263782501221</t>
   </si>
   <si>
     <t xml:space="preserve">10.6556224822998</t>
@@ -3890,16 +3890,16 @@
     <t xml:space="preserve">10.604679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8763761520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.68958568573</t>
+    <t xml:space="preserve">10.8763771057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6895847320557</t>
   </si>
   <si>
     <t xml:space="preserve">10.9867525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914714813232</t>
+    <t xml:space="preserve">10.7914705276489</t>
   </si>
   <si>
     <t xml:space="preserve">10.8084516525269</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">11.012225151062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3093938827515</t>
+    <t xml:space="preserve">11.3093929290771</t>
   </si>
   <si>
     <t xml:space="preserve">11.0886392593384</t>
@@ -3932,16 +3932,16 @@
     <t xml:space="preserve">11.3773183822632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5046758651733</t>
+    <t xml:space="preserve">11.5046768188477</t>
   </si>
   <si>
     <t xml:space="preserve">11.6320343017578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5131673812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4622240066528</t>
+    <t xml:space="preserve">11.5131664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4622230529785</t>
   </si>
   <si>
     <t xml:space="preserve">11.6999578475952</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">11.7678823471069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827317237854</t>
+    <t xml:space="preserve">11.8273162841797</t>
   </si>
   <si>
     <t xml:space="preserve">11.6374282836914</t>
@@ -5379,6 +5379,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.5200004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2800006866455</t>
   </si>
 </sst>
 </file>
@@ -70665,7 +70668,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6911689815</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>43190</v>
@@ -70686,6 +70689,32 @@
         <v>1788</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.69125</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>52160</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>21.2600002288818</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>21.4799995422363</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>21.2800006866455</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1789</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59860897064209</t>
+    <t xml:space="preserve">8.59860992431641</t>
   </si>
   <si>
     <t xml:space="preserve">ACE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.611008644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30103778839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.437424659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48081970214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61720752716064</t>
+    <t xml:space="preserve">8.61100769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3010368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43742561340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48082065582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61720657348633</t>
   </si>
   <si>
     <t xml:space="preserve">8.80319023132324</t>
@@ -65,25 +65,25 @@
     <t xml:space="preserve">8.68540096282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30723476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35063362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20804500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91667318344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97246646881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13985061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15225124359131</t>
+    <t xml:space="preserve">8.30723571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3506326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20804595947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.916672706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97246694564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13985252380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15225028991699</t>
   </si>
   <si>
     <t xml:space="preserve">8.2762393951416</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">8.38782787322998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49321937561035</t>
+    <t xml:space="preserve">8.49321842193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.50561809539795</t>
@@ -101,73 +101,73 @@
     <t xml:space="preserve">8.39402866363525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36923027038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33203315734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99106693267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5943021774292</t>
+    <t xml:space="preserve">8.36923122406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33203411102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99106454849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59430170059204</t>
   </si>
   <si>
     <t xml:space="preserve">7.45791339874268</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31532764434814</t>
+    <t xml:space="preserve">7.3153281211853</t>
   </si>
   <si>
     <t xml:space="preserve">7.46411418914795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66869497299194</t>
+    <t xml:space="preserve">7.66869640350342</t>
   </si>
   <si>
     <t xml:space="preserve">7.63149785995483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65629625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65009737014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44551467895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60050106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6810941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55090713500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6872935295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6067008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73688840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64389610290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57570457458496</t>
+    <t xml:space="preserve">7.6562967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65009689331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44551563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.600501537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68109226226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55090522766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68729162216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60670042037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73688697814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64389705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57570362091064</t>
   </si>
   <si>
     <t xml:space="preserve">7.53230714797974</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01586532592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38162899017334</t>
+    <t xml:space="preserve">8.0158634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38162803649902</t>
   </si>
   <si>
     <t xml:space="preserve">8.67920112609863</t>
@@ -176,25 +176,25 @@
     <t xml:space="preserve">8.77219295501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76599502563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83418655395508</t>
+    <t xml:space="preserve">8.76599311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83418846130371</t>
   </si>
   <si>
     <t xml:space="preserve">8.784592628479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46842002868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41882705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33823394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45602226257324</t>
+    <t xml:space="preserve">8.46842098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41882514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33823204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45602130889893</t>
   </si>
   <si>
     <t xml:space="preserve">8.49941921234131</t>
@@ -206,31 +206,31 @@
     <t xml:space="preserve">8.43122577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34443378448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47461986541748</t>
+    <t xml:space="preserve">8.40642738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34443283081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4746208190918</t>
   </si>
   <si>
     <t xml:space="preserve">8.24524211883545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90427446365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87327575683594</t>
+    <t xml:space="preserve">7.90427350997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8732762336731</t>
   </si>
   <si>
     <t xml:space="preserve">7.73069000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79268264770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8546781539917</t>
+    <t xml:space="preserve">7.79268312454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85467720031738</t>
   </si>
   <si>
     <t xml:space="preserve">7.89807367324829</t>
@@ -248,43 +248,43 @@
     <t xml:space="preserve">7.96626806259155</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86707639694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78028440475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.090256690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1150541305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17704677581787</t>
+    <t xml:space="preserve">7.86707735061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78028345108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11505317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17704772949219</t>
   </si>
   <si>
     <t xml:space="preserve">8.02206134796143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88567590713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82988023757935</t>
+    <t xml:space="preserve">7.88567399978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8298807144165</t>
   </si>
   <si>
     <t xml:space="preserve">8.04066181182861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00966358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09645557403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19564723968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23284244537354</t>
+    <t xml:space="preserve">8.00966453552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09645652770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19564628601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23284339904785</t>
   </si>
   <si>
     <t xml:space="preserve">8.18324756622314</t>
@@ -293,16 +293,16 @@
     <t xml:space="preserve">8.05925941467285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76168632507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5261082649231</t>
+    <t xml:space="preserve">7.76168727874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52610874176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.56330490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42071866989136</t>
+    <t xml:space="preserve">7.4207181930542</t>
   </si>
   <si>
     <t xml:space="preserve">7.19133996963501</t>
@@ -320,40 +320,40 @@
     <t xml:space="preserve">7.12314462661743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09073686599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05184888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1425895690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05833101272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68240547180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37777423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49444198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61110734939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08425569534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99999809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03888702392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93518304824829</t>
+    <t xml:space="preserve">7.09073734283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05184936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14259004592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05833053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68240451812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37777471542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49444246292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61110877990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08425712585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99999713897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03888654708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93518114089966</t>
   </si>
   <si>
     <t xml:space="preserve">6.78610801696777</t>
@@ -362,25 +362,25 @@
     <t xml:space="preserve">6.75370168685913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82499694824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86388540267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7407374382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91573858261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92869997024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89629507064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15555381774902</t>
+    <t xml:space="preserve">6.8249979019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8638858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74073791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91573810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92870044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89629316329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15555286407471</t>
   </si>
   <si>
     <t xml:space="preserve">7.14907073974609</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">7.58333015441895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55740356445312</t>
+    <t xml:space="preserve">7.55740451812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.0694408416748</t>
@@ -398,85 +398,85 @@
     <t xml:space="preserve">8.0435152053833</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01110649108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16666221618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17962455749512</t>
+    <t xml:space="preserve">8.01110744476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16666316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17962646484375</t>
   </si>
   <si>
     <t xml:space="preserve">8.07592296600342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05647754669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10184955596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95277500152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82962608337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87499618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90740394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481103897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75832986831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74536514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77129220962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71944093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57684755325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65462684631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70647811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81666374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79073715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69351482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72592210769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69999694824219</t>
+    <t xml:space="preserve">8.05647850036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10184764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95277404785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82962703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87499666213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90740299224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481151580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75832891464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74536752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77129364013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71944141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57684850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65462732315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70647859573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81666469573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79073858261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69351530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72592258453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69999837875366</t>
   </si>
   <si>
     <t xml:space="preserve">7.50555229187012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37592315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39536619186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47314405441284</t>
+    <t xml:space="preserve">7.37592267990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39536666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47314453125</t>
   </si>
   <si>
     <t xml:space="preserve">7.3240704536438</t>
@@ -485,49 +485,49 @@
     <t xml:space="preserve">7.25277423858643</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22684764862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18147802352905</t>
+    <t xml:space="preserve">7.22684860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18147897720337</t>
   </si>
   <si>
     <t xml:space="preserve">7.20092344284058</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2203688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18796014785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16851568222046</t>
+    <t xml:space="preserve">7.22036695480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18795919418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16851663589478</t>
   </si>
   <si>
     <t xml:space="preserve">7.16203308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1944432258606</t>
+    <t xml:space="preserve">7.1944408416748</t>
   </si>
   <si>
     <t xml:space="preserve">7.17499685287476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07129240036011</t>
+    <t xml:space="preserve">7.07129335403442</t>
   </si>
   <si>
     <t xml:space="preserve">6.96758937835693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04536628723145</t>
+    <t xml:space="preserve">7.04536771774292</t>
   </si>
   <si>
     <t xml:space="preserve">6.98703336715698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23333072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34999704360962</t>
+    <t xml:space="preserve">7.23332929611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34999656677246</t>
   </si>
   <si>
     <t xml:space="preserve">7.41481113433838</t>
@@ -536,64 +536,64 @@
     <t xml:space="preserve">7.55092191696167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52499628067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64166402816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5962929725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61573696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64814567565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49258995056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38888454437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46018123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36944055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30462598800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84444236755371</t>
+    <t xml:space="preserve">7.52499580383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64166355133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59629344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6157374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64814472198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49258947372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38888597488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46018218994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36944198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30462741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84444189071655</t>
   </si>
   <si>
     <t xml:space="preserve">6.57221937179565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59166431427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54629373550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48147773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43610858917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47823762893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52684926986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64999628067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5333309173584</t>
+    <t xml:space="preserve">6.59166383743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54629325866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48147916793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43610811233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47823810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52684879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64999771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53333044052124</t>
   </si>
   <si>
     <t xml:space="preserve">6.59814500808716</t>
@@ -602,31 +602,31 @@
     <t xml:space="preserve">6.52036762237549</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42962741851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87036848068237</t>
+    <t xml:space="preserve">6.42962646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87036800384521</t>
   </si>
   <si>
     <t xml:space="preserve">7.10370016098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25925731658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48610687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43425607681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42777490615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38240337371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51851558685303</t>
+    <t xml:space="preserve">7.25925540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48610830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43425703048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42777442932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38240432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851463317871</t>
   </si>
   <si>
     <t xml:space="preserve">7.51203346252441</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">7.66758871078491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68055295944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71295976638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89444208145142</t>
+    <t xml:space="preserve">7.68055152893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71295833587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8944411277771</t>
   </si>
   <si>
     <t xml:space="preserve">7.79721879959106</t>
@@ -650,61 +650,61 @@
     <t xml:space="preserve">7.84258985519409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34351396560669</t>
+    <t xml:space="preserve">7.34351587295532</t>
   </si>
   <si>
     <t xml:space="preserve">7.40184879302979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46666383743286</t>
+    <t xml:space="preserve">7.46666240692139</t>
   </si>
   <si>
     <t xml:space="preserve">7.40832996368408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73888492584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68703317642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62221908569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63518095016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7324047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77777481079102</t>
+    <t xml:space="preserve">7.73888540267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68703269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6222186088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63518142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73240375518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7777738571167</t>
   </si>
   <si>
     <t xml:space="preserve">7.83610773086548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75184869766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62870025634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97221899032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85555124282837</t>
+    <t xml:space="preserve">7.75184774398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62870121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97221803665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85555171966553</t>
   </si>
   <si>
     <t xml:space="preserve">7.92684698104858</t>
   </si>
   <si>
-    <t xml:space="preserve">8.037034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09536647796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13425445556641</t>
+    <t xml:space="preserve">8.03703308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09536743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13425636291504</t>
   </si>
   <si>
     <t xml:space="preserve">8.20555210113525</t>
@@ -716,34 +716,34 @@
     <t xml:space="preserve">8.24444103240967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147773742676</t>
+    <t xml:space="preserve">8.23147678375244</t>
   </si>
   <si>
     <t xml:space="preserve">8.22499656677246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27036762237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46481132507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45833015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43240356445312</t>
+    <t xml:space="preserve">8.27036571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46481037139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45832824707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43240451812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.42592239379883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35462760925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55555057525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52314567565918</t>
+    <t xml:space="preserve">8.35462665557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55555152893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52314472198486</t>
   </si>
   <si>
     <t xml:space="preserve">8.39351463317871</t>
@@ -752,82 +752,82 @@
     <t xml:space="preserve">8.47129249572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60740375518799</t>
+    <t xml:space="preserve">8.60740280151367</t>
   </si>
   <si>
     <t xml:space="preserve">8.6138858795166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62036609649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56203365325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80832958221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81481170654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84073734283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9249963760376</t>
+    <t xml:space="preserve">8.6203670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56203460693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80833053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6786994934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81481266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84073829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92499732971191</t>
   </si>
   <si>
     <t xml:space="preserve">9.12592315673828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17777252197266</t>
+    <t xml:space="preserve">9.17777156829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.00277423858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9509220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9962911605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1842565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0157356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02870178222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20370006561279</t>
+    <t xml:space="preserve">8.95092296600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99629211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18425464630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01573657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02869987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20369911193848</t>
   </si>
   <si>
     <t xml:space="preserve">9.28147792816162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30740261077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34629154205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43703269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32684707641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43055152893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38517951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41758918762207</t>
+    <t xml:space="preserve">9.30740165710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34629249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43703174591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32684803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43055248260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38518238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41758823394775</t>
   </si>
   <si>
     <t xml:space="preserve">9.33332920074463</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">9.50832939147949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44351387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54721736907959</t>
+    <t xml:space="preserve">9.44351291656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54721832275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.41110706329346</t>
@@ -851,22 +851,22 @@
     <t xml:space="preserve">9.35925483703613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51501846313477</t>
+    <t xml:space="preserve">9.51501750946045</t>
   </si>
   <si>
     <t xml:space="preserve">9.41343307495117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59628582000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50147151947021</t>
+    <t xml:space="preserve">9.59628391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50147247314453</t>
   </si>
   <si>
     <t xml:space="preserve">9.44729423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4811544418335</t>
+    <t xml:space="preserve">9.48115539550781</t>
   </si>
   <si>
     <t xml:space="preserve">9.21026611328125</t>
@@ -881,19 +881,19 @@
     <t xml:space="preserve">8.98678112030029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83101940155029</t>
+    <t xml:space="preserve">8.83101844787598</t>
   </si>
   <si>
     <t xml:space="preserve">8.84456348419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93937397003174</t>
+    <t xml:space="preserve">8.93937587738037</t>
   </si>
   <si>
     <t xml:space="preserve">8.81070327758789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93260288238525</t>
+    <t xml:space="preserve">8.93260383605957</t>
   </si>
   <si>
     <t xml:space="preserve">9.04095935821533</t>
@@ -905,91 +905,91 @@
     <t xml:space="preserve">9.04773139953613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08159160614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10190868377686</t>
+    <t xml:space="preserve">9.08159255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10190963745117</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349311828613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10868072509766</t>
+    <t xml:space="preserve">9.10868167877197</t>
   </si>
   <si>
     <t xml:space="preserve">9.12222671508789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0070972442627</t>
+    <t xml:space="preserve">9.00709819793701</t>
   </si>
   <si>
     <t xml:space="preserve">9.07482051849365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87842559814453</t>
+    <t xml:space="preserve">8.87842464447021</t>
   </si>
   <si>
     <t xml:space="preserve">8.92583084106445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90551471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52626800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58721828460693</t>
+    <t xml:space="preserve">8.90551376342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52626895904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58721733093262</t>
   </si>
   <si>
     <t xml:space="preserve">8.5465841293335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56013011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68880271911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5398120880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44500160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33664417266846</t>
+    <t xml:space="preserve">8.56012916564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68880176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53981113433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44500064849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33664512634277</t>
   </si>
   <si>
     <t xml:space="preserve">8.47208881378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47886180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41114044189453</t>
+    <t xml:space="preserve">8.47886276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4111385345459</t>
   </si>
   <si>
     <t xml:space="preserve">8.42468357086182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3840503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39082336425781</t>
+    <t xml:space="preserve">8.38404941558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3908224105835</t>
   </si>
   <si>
     <t xml:space="preserve">8.32987308502197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2824649810791</t>
+    <t xml:space="preserve">8.28246593475342</t>
   </si>
   <si>
     <t xml:space="preserve">8.26892185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24860668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19442749023438</t>
+    <t xml:space="preserve">8.24860572814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19442844390869</t>
   </si>
   <si>
     <t xml:space="preserve">8.16733932495117</t>
@@ -998,10 +998,10 @@
     <t xml:space="preserve">8.21474361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37050628662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29601097106934</t>
+    <t xml:space="preserve">8.37050533294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29601192474365</t>
   </si>
   <si>
     <t xml:space="preserve">8.39759540557861</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">8.81747531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97323608398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76329517364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67525863647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68202877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6955738067627</t>
+    <t xml:space="preserve">8.97323703765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76329708099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67525768280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68202972412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69557476043701</t>
   </si>
   <si>
     <t xml:space="preserve">8.80393028259277</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">8.85810852050781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74298000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74975204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79038524627686</t>
+    <t xml:space="preserve">8.74297904968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74975109100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79038429260254</t>
   </si>
   <si>
     <t xml:space="preserve">8.88519668579102</t>
@@ -1046,25 +1046,25 @@
     <t xml:space="preserve">8.96646404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91228485107422</t>
+    <t xml:space="preserve">8.91228675842285</t>
   </si>
   <si>
     <t xml:space="preserve">8.89196968078613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18317604064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19672203063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29153347015381</t>
+    <t xml:space="preserve">9.18317794799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19672107696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29153156280518</t>
   </si>
   <si>
     <t xml:space="preserve">9.24412727355957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36602783203125</t>
+    <t xml:space="preserve">9.36602687835693</t>
   </si>
   <si>
     <t xml:space="preserve">9.40666103363037</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">9.54210567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46760940551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38634300231934</t>
+    <t xml:space="preserve">9.46761035919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38634395599365</t>
   </si>
   <si>
     <t xml:space="preserve">9.52178859710693</t>
@@ -1088,46 +1088,46 @@
     <t xml:space="preserve">9.84008502960205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86717414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88749122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83331203460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76558971405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74527263641357</t>
+    <t xml:space="preserve">9.86717319488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88749027252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83331394195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76559066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74527359008789</t>
   </si>
   <si>
     <t xml:space="preserve">9.70464038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58273887634277</t>
+    <t xml:space="preserve">9.58273983001709</t>
   </si>
   <si>
     <t xml:space="preserve">9.71818447113037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67077732086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96875953674316</t>
+    <t xml:space="preserve">9.67077922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96875762939453</t>
   </si>
   <si>
     <t xml:space="preserve">9.94844150543213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91458034515381</t>
+    <t xml:space="preserve">9.91458129882812</t>
   </si>
   <si>
     <t xml:space="preserve">10.0161638259888</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96198558807373</t>
+    <t xml:space="preserve">9.96198654174805</t>
   </si>
   <si>
     <t xml:space="preserve">9.92135238647461</t>
@@ -1136,112 +1136,112 @@
     <t xml:space="preserve">9.90103530883789</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2599649429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4451093673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5670099258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.485743522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5128326416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518814086914</t>
+    <t xml:space="preserve">10.2599639892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.445107460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.567008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4857416152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5128307342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518804550171</t>
   </si>
   <si>
     <t xml:space="preserve">11.4383363723755</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49928855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3502988815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0726346969604</t>
+    <t xml:space="preserve">11.4992866516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3502979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0726337432861</t>
   </si>
   <si>
     <t xml:space="preserve">10.9845962524414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.876238822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1674470901489</t>
+    <t xml:space="preserve">10.8762397766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1674461364746</t>
   </si>
   <si>
     <t xml:space="preserve">10.8152894973755</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5850324630737</t>
+    <t xml:space="preserve">10.5850315093994</t>
   </si>
   <si>
     <t xml:space="preserve">10.4495878219604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5647172927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5443983078003</t>
+    <t xml:space="preserve">10.5647163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5443992614746</t>
   </si>
   <si>
     <t xml:space="preserve">10.4292707443237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4699039459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6324377059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8220615386963</t>
+    <t xml:space="preserve">10.4699058532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.632438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8220624923706</t>
   </si>
   <si>
     <t xml:space="preserve">10.9168739318848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9913673400879</t>
+    <t xml:space="preserve">10.9913682937622</t>
   </si>
   <si>
     <t xml:space="preserve">10.8017454147339</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7204780578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6256656646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6730728149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8356065750122</t>
+    <t xml:space="preserve">10.7204790115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6256647109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6730718612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8356056213379</t>
   </si>
   <si>
     <t xml:space="preserve">10.9371891021729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9981393814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0455465316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1268148422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9304161071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.842378616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7746553421021</t>
+    <t xml:space="preserve">10.998140335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0455455780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1268129348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9304180145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8423795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7746562957764</t>
   </si>
   <si>
     <t xml:space="preserve">10.7340230941772</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">10.5376272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5173091888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3615484237671</t>
+    <t xml:space="preserve">10.5173101425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3615493774414</t>
   </si>
   <si>
     <t xml:space="preserve">10.097430229187</t>
@@ -1265,10 +1265,10 @@
     <t xml:space="preserve">9.87394714355469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1922416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92812442779541</t>
+    <t xml:space="preserve">10.1922426223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92812347412109</t>
   </si>
   <si>
     <t xml:space="preserve">10.0364809036255</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">10.0567970275879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1245193481445</t>
+    <t xml:space="preserve">10.1245203018188</t>
   </si>
   <si>
     <t xml:space="preserve">10.0838871002197</t>
@@ -1289,13 +1289,13 @@
     <t xml:space="preserve">9.69786739349365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50824356079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44052124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64368915557861</t>
+    <t xml:space="preserve">9.50824451446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44052219390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6436882019043</t>
   </si>
   <si>
     <t xml:space="preserve">9.66400623321533</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">9.46083927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55565166473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34570980072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21703815460205</t>
+    <t xml:space="preserve">9.55565071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34571075439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21703910827637</t>
   </si>
   <si>
     <t xml:space="preserve">9.13577079772949</t>
@@ -1322,19 +1322,19 @@
     <t xml:space="preserve">9.23058223724365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06804847717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17640399932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33216571807861</t>
+    <t xml:space="preserve">9.06804752349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17640686035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3321647644043</t>
   </si>
   <si>
     <t xml:space="preserve">9.27798748016357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23735523223877</t>
+    <t xml:space="preserve">9.23735427856445</t>
   </si>
   <si>
     <t xml:space="preserve">9.1628589630127</t>
@@ -1343,25 +1343,25 @@
     <t xml:space="preserve">9.29830360412598</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42697620391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53533458709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62337303161621</t>
+    <t xml:space="preserve">9.42697715759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53533363342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62337207794189</t>
   </si>
   <si>
     <t xml:space="preserve">9.79945182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80622291564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77236175537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95521354675293</t>
+    <t xml:space="preserve">9.8062219619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77236366271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95521450042725</t>
   </si>
   <si>
     <t xml:space="preserve">9.81976890563965</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">9.75881767272949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47438430786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71141052246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30507659912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01387023925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79715919494629</t>
+    <t xml:space="preserve">9.47438335418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71141242980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30507755279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01387119293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79715728759766</t>
   </si>
   <si>
     <t xml:space="preserve">9.03418731689453</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">9.1137580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14924907684326</t>
+    <t xml:space="preserve">9.14924812316895</t>
   </si>
   <si>
     <t xml:space="preserve">9.05697441101074</t>
@@ -1412,25 +1412,25 @@
     <t xml:space="preserve">9.07117080688477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03567981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99309349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04277896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02148532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19183540344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27701091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39767551422119</t>
+    <t xml:space="preserve">9.03567886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99309253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04277801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19183444976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27700996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39767646789551</t>
   </si>
   <si>
     <t xml:space="preserve">9.2131290435791</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">9.12795448303223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22732543945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26991271972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12085628509521</t>
+    <t xml:space="preserve">9.22732448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26991367340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12085723876953</t>
   </si>
   <si>
     <t xml:space="preserve">9.17764091491699</t>
@@ -1457,10 +1457,10 @@
     <t xml:space="preserve">9.38348007202148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44026279449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41187191009521</t>
+    <t xml:space="preserve">9.44026374816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41187286376953</t>
   </si>
   <si>
     <t xml:space="preserve">9.603515625</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">9.7028865814209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56092929840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61771202087402</t>
+    <t xml:space="preserve">9.56092834472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61771392822266</t>
   </si>
   <si>
     <t xml:space="preserve">9.65320205688477</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">9.53253746032715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45445823669434</t>
+    <t xml:space="preserve">9.45446014404297</t>
   </si>
   <si>
     <t xml:space="preserve">9.50414562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3054027557373</t>
+    <t xml:space="preserve">9.30540180206299</t>
   </si>
   <si>
     <t xml:space="preserve">9.34799003601074</t>
@@ -1505,28 +1505,28 @@
     <t xml:space="preserve">9.28410911560059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24862003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0924654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8227424621582</t>
+    <t xml:space="preserve">9.24861907958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09246444702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82274341583252</t>
   </si>
   <si>
     <t xml:space="preserve">8.71627330780029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68078231811523</t>
+    <t xml:space="preserve">8.68078327178955</t>
   </si>
   <si>
     <t xml:space="preserve">8.78725242614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97889804840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01438617706299</t>
+    <t xml:space="preserve">8.97889614105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0143871307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.14214992523193</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">9.42606735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37638187408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16344356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04987812042236</t>
+    <t xml:space="preserve">9.37638282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16344261169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04987621307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.17054176330566</t>
@@ -1562,16 +1562,16 @@
     <t xml:space="preserve">8.69497966766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51043128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48203945159912</t>
+    <t xml:space="preserve">8.51043224334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48204040527344</t>
   </si>
   <si>
     <t xml:space="preserve">8.39686489105225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59560680389404</t>
+    <t xml:space="preserve">8.59560775756836</t>
   </si>
   <si>
     <t xml:space="preserve">8.49623775482178</t>
@@ -1589,13 +1589,13 @@
     <t xml:space="preserve">8.04196739196777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06326198577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07036018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9355001449585</t>
+    <t xml:space="preserve">8.06326103210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07036113739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93549966812134</t>
   </si>
   <si>
     <t xml:space="preserve">8.1484375</t>
@@ -1610,67 +1610,67 @@
     <t xml:space="preserve">8.28329849243164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38267040252686</t>
+    <t xml:space="preserve">8.38266944885254</t>
   </si>
   <si>
     <t xml:space="preserve">8.36137580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50333404541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42525672912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15634632110596</t>
+    <t xml:space="preserve">8.50333309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42525863647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15634536743164</t>
   </si>
   <si>
     <t xml:space="preserve">9.08536624908447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06407356262207</t>
+    <t xml:space="preserve">9.06407260894775</t>
   </si>
   <si>
     <t xml:space="preserve">8.80854606628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81564521789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65948867797852</t>
+    <t xml:space="preserve">8.81564426422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65949058532715</t>
   </si>
   <si>
     <t xml:space="preserve">8.56011962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57431316375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44655132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52462768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5175313949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40396404266357</t>
+    <t xml:space="preserve">8.57431411743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4465503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52462863922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51753234863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40396499633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.36847496032715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21231937408447</t>
+    <t xml:space="preserve">8.43945407867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21231842041016</t>
   </si>
   <si>
     <t xml:space="preserve">8.80144882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60980319976807</t>
+    <t xml:space="preserve">8.6098051071167</t>
   </si>
   <si>
     <t xml:space="preserve">8.3400821685791</t>
@@ -1688,43 +1688,43 @@
     <t xml:space="preserve">8.62400054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38976955413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53172588348389</t>
+    <t xml:space="preserve">8.38976669311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53172779083252</t>
   </si>
   <si>
     <t xml:space="preserve">8.68788146972656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83693885803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85823154449463</t>
+    <t xml:space="preserve">8.83693790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85823059082031</t>
   </si>
   <si>
     <t xml:space="preserve">8.90791702270508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25571727752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51124286651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58222198486328</t>
+    <t xml:space="preserve">9.25571537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5112419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5822229385376</t>
   </si>
   <si>
     <t xml:space="preserve">9.47575378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35508823394775</t>
+    <t xml:space="preserve">9.35508918762207</t>
   </si>
   <si>
     <t xml:space="preserve">9.54673194885254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66739749908447</t>
+    <t xml:space="preserve">9.66739845275879</t>
   </si>
   <si>
     <t xml:space="preserve">9.61061382293701</t>
@@ -1733,34 +1733,34 @@
     <t xml:space="preserve">9.63190841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51834011077881</t>
+    <t xml:space="preserve">9.51834106445312</t>
   </si>
   <si>
     <t xml:space="preserve">9.68869209289551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90872859954834</t>
+    <t xml:space="preserve">9.90872764587402</t>
   </si>
   <si>
     <t xml:space="preserve">9.85904216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88033485412598</t>
+    <t xml:space="preserve">9.88033580780029</t>
   </si>
   <si>
     <t xml:space="preserve">9.75967121124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86614036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85194301605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0222940444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2423305511475</t>
+    <t xml:space="preserve">9.86613941192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85194396972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0222949981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2423315048218</t>
   </si>
   <si>
     <t xml:space="preserve">10.3275060653687</t>
@@ -1769,13 +1769,13 @@
     <t xml:space="preserve">10.6114234924316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7604808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6398143768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6824026107788</t>
+    <t xml:space="preserve">10.760479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6398153305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6824035644531</t>
   </si>
   <si>
     <t xml:space="preserve">10.6043262481689</t>
@@ -1784,10 +1784,10 @@
     <t xml:space="preserve">10.7107944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6895017623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7746772766113</t>
+    <t xml:space="preserve">10.6895008087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.774676322937</t>
   </si>
   <si>
     <t xml:space="preserve">10.7249908447266</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">10.788872718811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7533826828003</t>
+    <t xml:space="preserve">10.753381729126</t>
   </si>
   <si>
     <t xml:space="preserve">10.7391872406006</t>
@@ -1808,22 +1808,22 @@
     <t xml:space="preserve">10.6965990066528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9166355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.356707572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3709030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4986667633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3141212463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4418840408325</t>
+    <t xml:space="preserve">10.9166345596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3567085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3709049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.49866771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3141193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4418830871582</t>
   </si>
   <si>
     <t xml:space="preserve">11.4276876449585</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">11.2999248504639</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1579666137695</t>
+    <t xml:space="preserve">11.1579647064209</t>
   </si>
   <si>
     <t xml:space="preserve">10.9876146316528</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">11.1863574981689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3851003646851</t>
+    <t xml:space="preserve">11.3850994110107</t>
   </si>
   <si>
     <t xml:space="preserve">11.4134912490845</t>
@@ -1859,31 +1859,31 @@
     <t xml:space="preserve">11.6122341156006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5412540435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8535633087158</t>
+    <t xml:space="preserve">11.5412549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8535642623901</t>
   </si>
   <si>
     <t xml:space="preserve">11.938738822937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1090898513794</t>
+    <t xml:space="preserve">12.1090888977051</t>
   </si>
   <si>
     <t xml:space="preserve">11.9813251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8677597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8251714706421</t>
+    <t xml:space="preserve">11.8677587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8251724243164</t>
   </si>
   <si>
     <t xml:space="preserve">11.7399969100952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6832132339478</t>
+    <t xml:space="preserve">11.6832113265991</t>
   </si>
   <si>
     <t xml:space="preserve">11.7967805862427</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">11.9103479385376</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8393669128418</t>
+    <t xml:space="preserve">11.8393678665161</t>
   </si>
   <si>
     <t xml:space="preserve">11.8819551467896</t>
@@ -1904,49 +1904,49 @@
     <t xml:space="preserve">11.8109750747681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.066502571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1942644119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2794399261475</t>
+    <t xml:space="preserve">12.0665006637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1942653656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2794408798218</t>
   </si>
   <si>
     <t xml:space="preserve">12.3078317642212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3504190444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4355945587158</t>
+    <t xml:space="preserve">12.3504199981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4355955123901</t>
   </si>
   <si>
     <t xml:space="preserve">12.5065755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5207691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5349674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5917501449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6627283096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6343374252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7053165435791</t>
+    <t xml:space="preserve">12.520770072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5349655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5917482376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.662727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6343355178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7053155899048</t>
   </si>
   <si>
     <t xml:space="preserve">12.8161840438843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6683597564697</t>
+    <t xml:space="preserve">12.6683616638184</t>
   </si>
   <si>
     <t xml:space="preserve">12.6387968063354</t>
@@ -1961,79 +1961,79 @@
     <t xml:space="preserve">12.3135890960693</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4466276168823</t>
+    <t xml:space="preserve">12.4466285705566</t>
   </si>
   <si>
     <t xml:space="preserve">12.8014011383057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7274894714355</t>
+    <t xml:space="preserve">12.7274904251099</t>
   </si>
   <si>
     <t xml:space="preserve">12.5353202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5796689987183</t>
+    <t xml:space="preserve">12.5796680450439</t>
   </si>
   <si>
     <t xml:space="preserve">12.7422723770142</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6831426620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8753118515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7866172790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7718372344971</t>
+    <t xml:space="preserve">12.6831436157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8753128051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7866191864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7718381881714</t>
   </si>
   <si>
     <t xml:space="preserve">12.8309659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9344396591187</t>
+    <t xml:space="preserve">12.9344415664673</t>
   </si>
   <si>
     <t xml:space="preserve">12.6979265213013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7127075195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5944499969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9048757553101</t>
+    <t xml:space="preserve">12.7127094268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944509506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9048767089844</t>
   </si>
   <si>
     <t xml:space="preserve">12.8457479476929</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8900947570801</t>
+    <t xml:space="preserve">12.8900957107544</t>
   </si>
   <si>
     <t xml:space="preserve">13.0674819946289</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1118288040161</t>
+    <t xml:space="preserve">13.1118268966675</t>
   </si>
   <si>
     <t xml:space="preserve">13.052698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9787874221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.141393661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0970458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0822629928589</t>
+    <t xml:space="preserve">12.9787883758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1413927078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0970449447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0822639465332</t>
   </si>
   <si>
     <t xml:space="preserve">13.0231351852417</t>
@@ -2051,16 +2051,16 @@
     <t xml:space="preserve">12.6092319488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8605298995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5501041412354</t>
+    <t xml:space="preserve">12.8605308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5501022338867</t>
   </si>
   <si>
     <t xml:space="preserve">13.4518203735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3335638046265</t>
+    <t xml:space="preserve">13.3335628509521</t>
   </si>
   <si>
     <t xml:space="preserve">13.4961652755737</t>
@@ -2069,79 +2069,79 @@
     <t xml:space="preserve">13.3483428955078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5405111312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9640073776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857395172119</t>
+    <t xml:space="preserve">13.5405120849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9640064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.185736656189</t>
   </si>
   <si>
     <t xml:space="preserve">13.170955657959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9196605682373</t>
+    <t xml:space="preserve">12.919659614563</t>
   </si>
   <si>
     <t xml:space="preserve">13.2744312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.259651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2892141342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2448673248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1266107559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9396343231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5552949905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7474641799927</t>
+    <t xml:space="preserve">13.2596521377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2892150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2448682785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1266098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7622451782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9396333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5552940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7474632263184</t>
   </si>
   <si>
     <t xml:space="preserve">13.9691963195801</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7770261764526</t>
+    <t xml:space="preserve">13.777027130127</t>
   </si>
   <si>
     <t xml:space="preserve">13.6292057037354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8657207489014</t>
+    <t xml:space="preserve">13.86572265625</t>
   </si>
   <si>
     <t xml:space="preserve">13.9544134140015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4665994644165</t>
+    <t xml:space="preserve">13.4666004180908</t>
   </si>
   <si>
     <t xml:space="preserve">13.4813842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4370365142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918090820312</t>
+    <t xml:space="preserve">13.4370374679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918100357056</t>
   </si>
   <si>
     <t xml:space="preserve">13.998761177063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0578899383545</t>
+    <t xml:space="preserve">14.0578918457031</t>
   </si>
   <si>
     <t xml:space="preserve">13.8213758468628</t>
@@ -2150,67 +2150,67 @@
     <t xml:space="preserve">13.6883335113525</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6587696075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144218444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5257291793823</t>
+    <t xml:space="preserve">13.6587686538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144227981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5257301330566</t>
   </si>
   <si>
     <t xml:space="preserve">13.3631267547607</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2300844192505</t>
+    <t xml:space="preserve">13.2300853729248</t>
   </si>
   <si>
     <t xml:space="preserve">13.88050365448</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4570093154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.471791267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6343965530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8191747665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0409107208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300413131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0039501190186</t>
+    <t xml:space="preserve">14.457010269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4717922210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6343955993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8191738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0409069061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300394058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0039510726929</t>
   </si>
   <si>
     <t xml:space="preserve">15.3735065460205</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5582838058472</t>
+    <t xml:space="preserve">15.5582857131958</t>
   </si>
   <si>
     <t xml:space="preserve">15.9278421401978</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1126174926758</t>
+    <t xml:space="preserve">16.1126194000244</t>
   </si>
   <si>
     <t xml:space="preserve">16.0387077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7800178527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6321973800659</t>
+    <t xml:space="preserve">15.7800207138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7061071395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6321954727173</t>
   </si>
   <si>
     <t xml:space="preserve">15.5213289260864</t>
@@ -2219,40 +2219,40 @@
     <t xml:space="preserve">15.4104633331299</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4474182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2256841659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2626419067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8908834457397</t>
+    <t xml:space="preserve">15.447416305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2256851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2626399993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8908853530884</t>
   </si>
   <si>
     <t xml:space="preserve">14.9669952392578</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7378730773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8561315536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4126634597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0874528884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3091878890991</t>
+    <t xml:space="preserve">14.7378721237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8561296463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4126644134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0874547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3091888427734</t>
   </si>
   <si>
     <t xml:space="preserve">14.5161380767822</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5309209823608</t>
+    <t xml:space="preserve">14.5309200286865</t>
   </si>
   <si>
     <t xml:space="preserve">11.8257741928101</t>
@@ -2264,10 +2264,10 @@
     <t xml:space="preserve">9.87452125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2145128250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57887744903564</t>
+    <t xml:space="preserve">10.2145118713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57887840270996</t>
   </si>
   <si>
     <t xml:space="preserve">9.63800621032715</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">9.29801464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53453063964844</t>
+    <t xml:space="preserve">9.53453159332275</t>
   </si>
   <si>
     <t xml:space="preserve">9.65278911590576</t>
@@ -2288,19 +2288,19 @@
     <t xml:space="preserve">10.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7023258209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5988521575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9388408660889</t>
+    <t xml:space="preserve">10.7023267745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5988512039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9388418197632</t>
   </si>
   <si>
     <t xml:space="preserve">10.7318906784058</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9018859863281</t>
+    <t xml:space="preserve">10.9018869400024</t>
   </si>
   <si>
     <t xml:space="preserve">11.2123126983643</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">11.012752532959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0718812942505</t>
+    <t xml:space="preserve">11.0718803405762</t>
   </si>
   <si>
     <t xml:space="preserve">11.315788269043</t>
@@ -2324,22 +2324,22 @@
     <t xml:space="preserve">10.8353662490845</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6801528930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7245006561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6505880355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5175485610962</t>
+    <t xml:space="preserve">10.6801538467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7244997024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6505889892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5175476074219</t>
   </si>
   <si>
     <t xml:space="preserve">10.9462337493896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3749160766602</t>
+    <t xml:space="preserve">11.3749179840088</t>
   </si>
   <si>
     <t xml:space="preserve">11.2714414596558</t>
@@ -2351,25 +2351,25 @@
     <t xml:space="preserve">11.9735975265503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6040410995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2197036743164</t>
+    <t xml:space="preserve">11.6040420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2197046279907</t>
   </si>
   <si>
     <t xml:space="preserve">11.5153484344482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7370824813843</t>
+    <t xml:space="preserve">11.73708152771</t>
   </si>
   <si>
     <t xml:space="preserve">12.128809928894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4318466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.564884185791</t>
+    <t xml:space="preserve">12.431845664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5648851394653</t>
   </si>
   <si>
     <t xml:space="preserve">12.380108833313</t>
@@ -2378,31 +2378,31 @@
     <t xml:space="preserve">12.4392366409302</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4096736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7644453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8974866867065</t>
+    <t xml:space="preserve">12.4096727371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7644462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8974857330322</t>
   </si>
   <si>
     <t xml:space="preserve">12.8235750198364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.971396446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6070308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8065938949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.89528465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0431089401245</t>
+    <t xml:space="preserve">12.9713973999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6070318222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8065929412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8952856063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0431079864502</t>
   </si>
   <si>
     <t xml:space="preserve">13.5331211090088</t>
@@ -2414,16 +2414,16 @@
     <t xml:space="preserve">13.089653968811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0600900650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887733459473</t>
+    <t xml:space="preserve">13.0600910186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887752532959</t>
   </si>
   <si>
     <t xml:space="preserve">13.2966060638428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2512512207031</t>
+    <t xml:space="preserve">13.2512531280518</t>
   </si>
   <si>
     <t xml:space="preserve">13.4521455764771</t>
@@ -2435,28 +2435,28 @@
     <t xml:space="preserve">12.9962711334229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1585321426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3980579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2048921585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.421238899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.544867515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4444189071655</t>
+    <t xml:space="preserve">13.1585330963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3980598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2048931121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4212398529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5448656082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4444198608398</t>
   </si>
   <si>
     <t xml:space="preserve">13.5294122695923</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3594274520874</t>
+    <t xml:space="preserve">13.3594264984131</t>
   </si>
   <si>
     <t xml:space="preserve">13.1276254653931</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">13.0812654495239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.934458732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.810830116272</t>
+    <t xml:space="preserve">12.9344577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8108320236206</t>
   </si>
   <si>
     <t xml:space="preserve">12.9576387405396</t>
@@ -2480,49 +2480,49 @@
     <t xml:space="preserve">13.150806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3362474441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1894378662109</t>
+    <t xml:space="preserve">13.3362464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1894397735596</t>
   </si>
   <si>
     <t xml:space="preserve">12.7953777313232</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5944833755493</t>
+    <t xml:space="preserve">12.5944843292236</t>
   </si>
   <si>
     <t xml:space="preserve">12.7644720077515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3285188674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2126188278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.436692237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6453132629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9311990737915</t>
+    <t xml:space="preserve">13.328519821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2126197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4366912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6453123092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9312009811401</t>
   </si>
   <si>
     <t xml:space="preserve">13.5062322616577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5216875076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5371389389038</t>
+    <t xml:space="preserve">13.5216865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5371398925781</t>
   </si>
   <si>
     <t xml:space="preserve">13.8539342880249</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8230276107788</t>
+    <t xml:space="preserve">13.8230266571045</t>
   </si>
   <si>
     <t xml:space="preserve">13.8848390579224</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">14.0702781677246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7843933105469</t>
+    <t xml:space="preserve">13.7843914031982</t>
   </si>
   <si>
     <t xml:space="preserve">13.6916723251343</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">13.6221323013306</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5989532470703</t>
+    <t xml:space="preserve">13.598952293396</t>
   </si>
   <si>
     <t xml:space="preserve">13.2744331359863</t>
@@ -2558,46 +2558,46 @@
     <t xml:space="preserve">13.5757732391357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3053379058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6298599243164</t>
+    <t xml:space="preserve">13.3053398132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6298589706421</t>
   </si>
   <si>
     <t xml:space="preserve">13.4753265380859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7921190261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5680465698242</t>
+    <t xml:space="preserve">13.7921199798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5680456161499</t>
   </si>
   <si>
     <t xml:space="preserve">13.4830532073975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8462057113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9234733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9543781280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5912265777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3671522140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5525941848755</t>
+    <t xml:space="preserve">13.8462076187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9234743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9543790817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5912256240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3671531677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5525932312012</t>
   </si>
   <si>
     <t xml:space="preserve">13.7380332946777</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0007400512695</t>
+    <t xml:space="preserve">14.0007410049438</t>
   </si>
   <si>
     <t xml:space="preserve">13.8925676345825</t>
@@ -2606,16 +2606,16 @@
     <t xml:space="preserve">13.9080200195312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0780076980591</t>
+    <t xml:space="preserve">14.0780057907104</t>
   </si>
   <si>
     <t xml:space="preserve">13.938928604126</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8616590499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8384799957275</t>
+    <t xml:space="preserve">13.8616619110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8384790420532</t>
   </si>
   <si>
     <t xml:space="preserve">14.0239200592041</t>
@@ -2624,19 +2624,19 @@
     <t xml:space="preserve">14.047101020813</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3329858779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1861820220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1784543991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8152980804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6993989944458</t>
+    <t xml:space="preserve">14.3329877853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1861801147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1784553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8152990341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6993999481201</t>
   </si>
   <si>
     <t xml:space="preserve">13.3130655288696</t>
@@ -2645,13 +2645,13 @@
     <t xml:space="preserve">13.2667064666748</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2898864746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3748769760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1662588119507</t>
+    <t xml:space="preserve">13.2898874282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3748779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.166259765625</t>
   </si>
   <si>
     <t xml:space="preserve">13.7766666412354</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">13.761212348938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7998476028442</t>
+    <t xml:space="preserve">13.7998456954956</t>
   </si>
   <si>
     <t xml:space="preserve">13.5834989547729</t>
@@ -2669,37 +2669,37 @@
     <t xml:space="preserve">13.4907789230347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5139579772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0161924362183</t>
+    <t xml:space="preserve">13.5139589309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0161933898926</t>
   </si>
   <si>
     <t xml:space="preserve">13.6375865936279</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0426321029663</t>
+    <t xml:space="preserve">13.0426301956177</t>
   </si>
   <si>
     <t xml:space="preserve">12.8880987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.826286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494653701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7567453384399</t>
+    <t xml:space="preserve">12.8262853622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494644165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7567443847656</t>
   </si>
   <si>
     <t xml:space="preserve">12.5867586135864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022119522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6253910064697</t>
+    <t xml:space="preserve">12.6022109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.625391960144</t>
   </si>
   <si>
     <t xml:space="preserve">12.6872053146362</t>
@@ -2711,25 +2711,25 @@
     <t xml:space="preserve">12.9267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1430778503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3207921981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4135141372681</t>
+    <t xml:space="preserve">13.1430797576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3207931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4135131835938</t>
   </si>
   <si>
     <t xml:space="preserve">13.4057865142822</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1817121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8417387008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8726444244385</t>
+    <t xml:space="preserve">13.1817111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.841739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8726453781128</t>
   </si>
   <si>
     <t xml:space="preserve">12.9190044403076</t>
@@ -2741,28 +2741,28 @@
     <t xml:space="preserve">12.6331186294556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721996307373</t>
+    <t xml:space="preserve">12.772198677063</t>
   </si>
   <si>
     <t xml:space="preserve">12.7490186691284</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1971664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.096718788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3439722061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821588516235</t>
+    <t xml:space="preserve">13.1971645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0967197418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.34397315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821598052979</t>
   </si>
   <si>
     <t xml:space="preserve">12.9808177947998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.718111038208</t>
+    <t xml:space="preserve">12.7181100845337</t>
   </si>
   <si>
     <t xml:space="preserve">12.7258377075195</t>
@@ -2771,10 +2771,10 @@
     <t xml:space="preserve">12.6408452987671</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6176652908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7103862762451</t>
+    <t xml:space="preserve">12.6176643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7103853225708</t>
   </si>
   <si>
     <t xml:space="preserve">12.4554052352905</t>
@@ -2783,16 +2783,16 @@
     <t xml:space="preserve">12.8803720474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603179931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6839475631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9621076583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1398181915283</t>
+    <t xml:space="preserve">13.5603199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6839456558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9621057510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.139820098877</t>
   </si>
   <si>
     <t xml:space="preserve">14.371621131897</t>
@@ -2810,19 +2810,19 @@
     <t xml:space="preserve">14.4025259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2402677536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2557210922241</t>
+    <t xml:space="preserve">14.2402687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2557229995728</t>
   </si>
   <si>
     <t xml:space="preserve">14.3948001861572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5493354797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9588470458984</t>
+    <t xml:space="preserve">14.5493335723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9588489532471</t>
   </si>
   <si>
     <t xml:space="preserve">15.1211080551147</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">14.6343278884888</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7656812667847</t>
+    <t xml:space="preserve">14.7656831741333</t>
   </si>
   <si>
     <t xml:space="preserve">14.7579555511475</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">14.6806879043579</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5261535644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.696141242981</t>
+    <t xml:space="preserve">14.5261545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6961421966553</t>
   </si>
   <si>
     <t xml:space="preserve">14.6420545578003</t>
@@ -2855,28 +2855,28 @@
     <t xml:space="preserve">14.5725154876709</t>
   </si>
   <si>
-    <t xml:space="preserve">14.603422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5956935882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6575059890747</t>
+    <t xml:space="preserve">14.6034212112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5956926345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.657506942749</t>
   </si>
   <si>
     <t xml:space="preserve">14.8352222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.997483253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1983757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0824766159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0283880233765</t>
+    <t xml:space="preserve">14.9974822998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1983737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0824747085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0283889770508</t>
   </si>
   <si>
     <t xml:space="preserve">15.0979290008545</t>
@@ -2885,43 +2885,43 @@
     <t xml:space="preserve">15.1751947402954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2061033248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747470855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8506736755371</t>
+    <t xml:space="preserve">15.2061023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747489929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8506746292114</t>
   </si>
   <si>
     <t xml:space="preserve">14.8661270141602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9743003845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0592947006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0052070617676</t>
+    <t xml:space="preserve">14.9743013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0592956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0052080154419</t>
   </si>
   <si>
     <t xml:space="preserve">14.9279413223267</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1520185470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4147233963013</t>
+    <t xml:space="preserve">15.1520137786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.414722442627</t>
   </si>
   <si>
     <t xml:space="preserve">15.8551435470581</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8087825775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6233444213867</t>
+    <t xml:space="preserve">15.8087816238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6233425140381</t>
   </si>
   <si>
     <t xml:space="preserve">15.7624235153198</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">16.056037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3496513366699</t>
+    <t xml:space="preserve">16.3496494293213</t>
   </si>
   <si>
     <t xml:space="preserve">16.4578247070312</t>
@@ -2963,10 +2963,10 @@
     <t xml:space="preserve">15.8476800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7834548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8717651367188</t>
+    <t xml:space="preserve">15.7834539413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8717641830444</t>
   </si>
   <si>
     <t xml:space="preserve">15.6871166229248</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">15.5586633682251</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6550025939941</t>
+    <t xml:space="preserve">15.6550035476685</t>
   </si>
   <si>
     <t xml:space="preserve">15.7192287445068</t>
@@ -2987,61 +2987,61 @@
     <t xml:space="preserve">15.7673969268799</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1045837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5988063812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5827503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.711199760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7272577285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5907754898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5104951858521</t>
+    <t xml:space="preserve">16.1045818328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5988054275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827493667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7112007141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7272567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5907773971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5104942321777</t>
   </si>
   <si>
     <t xml:space="preserve">15.213451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2616214752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4703550338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6630296707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8557090759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7352848052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9119062423706</t>
+    <t xml:space="preserve">15.2616195678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4703540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6630306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8557081222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7352867126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9119052886963</t>
   </si>
   <si>
     <t xml:space="preserve">16.0162734985352</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7754259109497</t>
+    <t xml:space="preserve">15.7754240036011</t>
   </si>
   <si>
     <t xml:space="preserve">15.9921875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2490882873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3454284667969</t>
+    <t xml:space="preserve">16.2490901947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3454303741455</t>
   </si>
   <si>
     <t xml:space="preserve">16.5381050109863</t>
@@ -3053,28 +3053,28 @@
     <t xml:space="preserve">16.9876861572266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0679683685303</t>
+    <t xml:space="preserve">17.0679664611816</t>
   </si>
   <si>
     <t xml:space="preserve">16.9074039459229</t>
   </si>
   <si>
-    <t xml:space="preserve">16.570219039917</t>
+    <t xml:space="preserve">16.5702171325684</t>
   </si>
   <si>
     <t xml:space="preserve">16.2330341339111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0724697113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4096565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2009181976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3133144378662</t>
+    <t xml:space="preserve">16.0724678039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4096546173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2009201049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3133163452148</t>
   </si>
   <si>
     <t xml:space="preserve">16.1366958618164</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">16.3293724060059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0885276794434</t>
+    <t xml:space="preserve">16.0885257720947</t>
   </si>
   <si>
     <t xml:space="preserve">16.0483837127686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9841585159302</t>
+    <t xml:space="preserve">15.9841594696045</t>
   </si>
   <si>
     <t xml:space="preserve">16.2812042236328</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">15.398099899292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1090831756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9164066314697</t>
+    <t xml:space="preserve">15.1090841293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.916407585144</t>
   </si>
   <si>
     <t xml:space="preserve">14.8040132522583</t>
@@ -3119,109 +3119,109 @@
     <t xml:space="preserve">14.9806327819824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9886617660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9645757675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7478151321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8923215866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8120422363281</t>
+    <t xml:space="preserve">14.9886627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9645748138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7478170394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8923225402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8120431900024</t>
   </si>
   <si>
     <t xml:space="preserve">14.900351524353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8521823883057</t>
+    <t xml:space="preserve">14.8521814346313</t>
   </si>
   <si>
     <t xml:space="preserve">15.101056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6755628585815</t>
+    <t xml:space="preserve">14.6755619049072</t>
   </si>
   <si>
     <t xml:space="preserve">14.787956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1171140670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2375364303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0930271148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2937335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3900709152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0609149932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.036828994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3419036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2535924911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.197395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5345783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1251411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769729614258</t>
+    <t xml:space="preserve">15.117112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2375354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0930280685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2937345504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3900728225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0609169006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0368309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3419027328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2535915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1973934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5345811843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1251420974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769720077515</t>
   </si>
   <si>
     <t xml:space="preserve">15.1492261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8441534042358</t>
+    <t xml:space="preserve">14.8441553115845</t>
   </si>
   <si>
     <t xml:space="preserve">14.7076740264893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6113367080688</t>
+    <t xml:space="preserve">14.6113376617432</t>
   </si>
   <si>
     <t xml:space="preserve">14.6595058441162</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1858406066895</t>
+    <t xml:space="preserve">14.1858415603638</t>
   </si>
   <si>
     <t xml:space="preserve">14.3062629699707</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3544321060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5792245864868</t>
+    <t xml:space="preserve">14.3544311523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5792236328125</t>
   </si>
   <si>
     <t xml:space="preserve">14.3464069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3142919540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6996469497681</t>
+    <t xml:space="preserve">14.3142929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6996479034424</t>
   </si>
   <si>
     <t xml:space="preserve">14.6193618774414</t>
@@ -3233,16 +3233,16 @@
     <t xml:space="preserve">14.5230255126953</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5471105575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273927688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8200693130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9244356155396</t>
+    <t xml:space="preserve">14.5471124649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273918151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8200674057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9244375228882</t>
   </si>
   <si>
     <t xml:space="preserve">14.5711946487427</t>
@@ -3263,61 +3263,61 @@
     <t xml:space="preserve">14.1938695907593</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8326005935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7442903518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8486557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8085165023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5355558395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5917539596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406276702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9690790176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3704891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3303480148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2179546356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8727407455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6479511260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947092056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5114717483521</t>
+    <t xml:space="preserve">13.8325996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7442893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8486566543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8085174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5917549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406286239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9690799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3704900741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3303489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2179527282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8727416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6479501724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947101593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5114707946777</t>
   </si>
   <si>
     <t xml:space="preserve">13.5034427642822</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2465410232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.415132522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3187942504883</t>
+    <t xml:space="preserve">13.2465400695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4151334762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3187952041626</t>
   </si>
   <si>
     <t xml:space="preserve">13.4071054458618</t>
@@ -3326,28 +3326,28 @@
     <t xml:space="preserve">13.1100616455078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.085976600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2224559783936</t>
+    <t xml:space="preserve">13.0859756469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2224550247192</t>
   </si>
   <si>
     <t xml:space="preserve">13.5756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6640090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.198371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0217514038086</t>
+    <t xml:space="preserve">13.664008140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1983728408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0217504501343</t>
   </si>
   <si>
     <t xml:space="preserve">12.8611869812012</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7086505889893</t>
+    <t xml:space="preserve">12.7086515426636</t>
   </si>
   <si>
     <t xml:space="preserve">12.604284286499</t>
@@ -3359,22 +3359,22 @@
     <t xml:space="preserve">13.3589353561401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1261177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8210458755493</t>
+    <t xml:space="preserve">13.1261186599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8210468292236</t>
   </si>
   <si>
     <t xml:space="preserve">12.6363964080811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9735822677612</t>
+    <t xml:space="preserve">12.9735813140869</t>
   </si>
   <si>
     <t xml:space="preserve">12.9093561172485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8772449493408</t>
+    <t xml:space="preserve">12.8772439956665</t>
   </si>
   <si>
     <t xml:space="preserve">13.1421747207642</t>
@@ -3395,19 +3395,19 @@
     <t xml:space="preserve">13.4392175674438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3509073257446</t>
+    <t xml:space="preserve">13.3509063720703</t>
   </si>
   <si>
     <t xml:space="preserve">13.7202053070068</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0092210769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8807706832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5596399307251</t>
+    <t xml:space="preserve">14.009220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8807697296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5596408843994</t>
   </si>
   <si>
     <t xml:space="preserve">13.5997819900513</t>
@@ -3434,25 +3434,25 @@
     <t xml:space="preserve">13.0940046310425</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9494972229004</t>
+    <t xml:space="preserve">12.9494962692261</t>
   </si>
   <si>
     <t xml:space="preserve">12.7487926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8852710723877</t>
+    <t xml:space="preserve">12.8852701187134</t>
   </si>
   <si>
     <t xml:space="preserve">12.5240020751953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6444253921509</t>
+    <t xml:space="preserve">12.6444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">12.7969608306885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9334402084351</t>
+    <t xml:space="preserve">12.9334411621094</t>
   </si>
   <si>
     <t xml:space="preserve">12.8049898147583</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">12.9254131317139</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1341466903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9816093444824</t>
+    <t xml:space="preserve">13.1341457366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9816102981567</t>
   </si>
   <si>
     <t xml:space="preserve">13.4633026123047</t>
@@ -3476,10 +3476,10 @@
     <t xml:space="preserve">13.3268241882324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2064008712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2786550521851</t>
+    <t xml:space="preserve">13.2063999176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2786531448364</t>
   </si>
   <si>
     <t xml:space="preserve">12.6845664978027</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">12.5320301055908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1839199066162</t>
+    <t xml:space="preserve">12.1839189529419</t>
   </si>
   <si>
     <t xml:space="preserve">11.8018445968628</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">11.9546747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3112773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1075048446655</t>
+    <t xml:space="preserve">12.3112764358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1075038909912</t>
   </si>
   <si>
     <t xml:space="preserve">12.158447265625</t>
@@ -3521,13 +3521,13 @@
     <t xml:space="preserve">11.9801454544067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2433519363403</t>
+    <t xml:space="preserve">12.2433528900146</t>
   </si>
   <si>
     <t xml:space="preserve">11.9461841583252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9886360168457</t>
+    <t xml:space="preserve">11.98863697052</t>
   </si>
   <si>
     <t xml:space="preserve">12.0141077041626</t>
@@ -3542,10 +3542,10 @@
     <t xml:space="preserve">11.6150531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4792051315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556192398071</t>
+    <t xml:space="preserve">11.4792041778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556182861328</t>
   </si>
   <si>
     <t xml:space="preserve">11.6659955978394</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">11.6575050354004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.750901222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339200973511</t>
+    <t xml:space="preserve">11.7509021759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339210510254</t>
   </si>
   <si>
     <t xml:space="preserve">11.8358068466187</t>
@@ -3566,16 +3566,16 @@
     <t xml:space="preserve">11.7593927383423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8867502212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9631643295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6744861602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5726003646851</t>
+    <t xml:space="preserve">11.8867492675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9631652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6744871139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5725994110107</t>
   </si>
   <si>
     <t xml:space="preserve">11.5301475524902</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">11.581090927124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4707145690918</t>
+    <t xml:space="preserve">11.4707136154175</t>
   </si>
   <si>
     <t xml:space="preserve">11.3688268661499</t>
@@ -3599,28 +3599,28 @@
     <t xml:space="preserve">11.343355178833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3009042739868</t>
+    <t xml:space="preserve">11.3009033203125</t>
   </si>
   <si>
     <t xml:space="preserve">11.2499599456787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9358100891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6386404037476</t>
+    <t xml:space="preserve">10.9358110427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6386413574219</t>
   </si>
   <si>
     <t xml:space="preserve">10.6301507949829</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1461906433105</t>
+    <t xml:space="preserve">10.1461896896362</t>
   </si>
   <si>
     <t xml:space="preserve">10.044303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1886434555054</t>
+    <t xml:space="preserve">10.1886425018311</t>
   </si>
   <si>
     <t xml:space="preserve">9.86600303649902</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">10.0612850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075103759766</t>
+    <t xml:space="preserve">10.3075113296509</t>
   </si>
   <si>
     <t xml:space="preserve">10.1716613769531</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">10.0867567062378</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69619178771973</t>
+    <t xml:space="preserve">9.69619274139404</t>
   </si>
   <si>
     <t xml:space="preserve">9.47543811798096</t>
@@ -3665,19 +3665,19 @@
     <t xml:space="preserve">9.53487110137939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2716646194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45845699310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74713516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90845489501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56034374237061</t>
+    <t xml:space="preserve">9.27166557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7471342086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90845584869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56034278869629</t>
   </si>
   <si>
     <t xml:space="preserve">9.4160041809082</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">9.72166347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.027322769165</t>
+    <t xml:space="preserve">10.0273237228394</t>
   </si>
   <si>
     <t xml:space="preserve">10.1037368774414</t>
@@ -3716,7 +3716,7 @@
     <t xml:space="preserve">10.2395858764648</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6216602325439</t>
+    <t xml:space="preserve">10.6216611862183</t>
   </si>
   <si>
     <t xml:space="preserve">10.842414855957</t>
@@ -3731,28 +3731,28 @@
     <t xml:space="preserve">10.8678855895996</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8339233398438</t>
+    <t xml:space="preserve">10.8339242935181</t>
   </si>
   <si>
     <t xml:space="preserve">10.774489402771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8169431686401</t>
+    <t xml:space="preserve">10.8169422149658</t>
   </si>
   <si>
     <t xml:space="preserve">11.0207147598267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0716590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2839212417603</t>
+    <t xml:space="preserve">11.0716581344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2839221954346</t>
   </si>
   <si>
     <t xml:space="preserve">11.2754316329956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4452409744263</t>
+    <t xml:space="preserve">11.4452419281006</t>
   </si>
   <si>
     <t xml:space="preserve">11.1395826339722</t>
@@ -3767,13 +3767,13 @@
     <t xml:space="preserve">11.173544883728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0292062759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2584505081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2924118041992</t>
+    <t xml:space="preserve">11.0292053222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2584495544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2924127578735</t>
   </si>
   <si>
     <t xml:space="preserve">11.1141109466553</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">11.1650543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2414693832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4197702407837</t>
+    <t xml:space="preserve">11.2414684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.419771194458</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858079910278</t>
@@ -3794,10 +3794,10 @@
     <t xml:space="preserve">11.3942995071411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3603363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376958847046</t>
+    <t xml:space="preserve">11.3603372573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376968383789</t>
   </si>
   <si>
     <t xml:space="preserve">11.003734588623</t>
@@ -3812,13 +3812,13 @@
     <t xml:space="preserve">10.9697723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2244892120361</t>
+    <t xml:space="preserve">11.2244882583618</t>
   </si>
   <si>
     <t xml:space="preserve">11.4112796783447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.521656036377</t>
+    <t xml:space="preserve">11.5216569900513</t>
   </si>
   <si>
     <t xml:space="preserve">11.5386381149292</t>
@@ -3827,13 +3827,13 @@
     <t xml:space="preserve">11.9716558456421</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1159944534302</t>
+    <t xml:space="preserve">12.1159954071045</t>
   </si>
   <si>
     <t xml:space="preserve">12.149956703186</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1754283905029</t>
+    <t xml:space="preserve">12.1754293441772</t>
   </si>
   <si>
     <t xml:space="preserve">12.0480699539185</t>
@@ -3857,13 +3857,13 @@
     <t xml:space="preserve">12.1414661407471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0650510787964</t>
+    <t xml:space="preserve">12.0650520324707</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056180953979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8697690963745</t>
+    <t xml:space="preserve">11.8697681427002</t>
   </si>
   <si>
     <t xml:space="preserve">11.7169399261475</t>
@@ -3875,13 +3875,13 @@
     <t xml:space="preserve">11.5641098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9018487930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5622253417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4263782501221</t>
+    <t xml:space="preserve">10.9018478393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5622262954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4263772964478</t>
   </si>
   <si>
     <t xml:space="preserve">10.6556224822998</t>
@@ -3893,16 +3893,16 @@
     <t xml:space="preserve">10.8763771057129</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6895847320557</t>
+    <t xml:space="preserve">10.6895837783813</t>
   </si>
   <si>
     <t xml:space="preserve">10.9867525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914705276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8084506988525</t>
+    <t xml:space="preserve">10.7914714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8084516525269</t>
   </si>
   <si>
     <t xml:space="preserve">10.8509044647217</t>
@@ -3911,19 +3911,19 @@
     <t xml:space="preserve">10.6980752944946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6641139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320365905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7999620437622</t>
+    <t xml:space="preserve">10.6641130447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320375442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7999610900879</t>
   </si>
   <si>
     <t xml:space="preserve">11.012225151062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3093929290771</t>
+    <t xml:space="preserve">11.3093938827515</t>
   </si>
   <si>
     <t xml:space="preserve">11.0886402130127</t>
@@ -3932,25 +3932,25 @@
     <t xml:space="preserve">11.3773183822632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5046758651733</t>
+    <t xml:space="preserve">11.5046768188477</t>
   </si>
   <si>
     <t xml:space="preserve">11.6320343017578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5131664276123</t>
+    <t xml:space="preserve">11.5131673812866</t>
   </si>
   <si>
     <t xml:space="preserve">11.4622230529785</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6999588012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6829776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7678813934326</t>
+    <t xml:space="preserve">11.6999578475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6829767227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7678823471069</t>
   </si>
   <si>
     <t xml:space="preserve">11.8273162841797</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">10.877875328064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7331981658936</t>
+    <t xml:space="preserve">10.7331991195679</t>
   </si>
   <si>
     <t xml:space="preserve">10.8326635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8869180679321</t>
+    <t xml:space="preserve">10.8869171142578</t>
   </si>
   <si>
     <t xml:space="preserve">10.8507490158081</t>
@@ -3995,22 +3995,22 @@
     <t xml:space="preserve">10.6608600616455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3082103729248</t>
+    <t xml:space="preserve">10.3082113265991</t>
   </si>
   <si>
     <t xml:space="preserve">10.1544914245605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1454496383667</t>
+    <t xml:space="preserve">10.145450592041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3262958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3534231185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4167194366455</t>
+    <t xml:space="preserve">10.353422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4167184829712</t>
   </si>
   <si>
     <t xml:space="preserve">10.2539577484131</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">10.3805494308472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4890565872192</t>
+    <t xml:space="preserve">10.4890575408936</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">10.0098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0731115341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95556163787842</t>
+    <t xml:space="preserve">10.073112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95556259155273</t>
   </si>
   <si>
     <t xml:space="preserve">9.8560962677002</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">9.7114200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57578659057617</t>
+    <t xml:space="preserve">9.57578563690186</t>
   </si>
   <si>
     <t xml:space="preserve">9.34068584442139</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">9.43110942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28643226623535</t>
+    <t xml:space="preserve">9.28643321990967</t>
   </si>
   <si>
     <t xml:space="preserve">9.26834774017334</t>
@@ -4073,28 +4073,28 @@
     <t xml:space="preserve">9.30451679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33164405822754</t>
+    <t xml:space="preserve">9.33164310455322</t>
   </si>
   <si>
     <t xml:space="preserve">9.52153205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72046184539795</t>
+    <t xml:space="preserve">9.72046279907227</t>
   </si>
   <si>
     <t xml:space="preserve">9.76567363739014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91035079956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91939353942871</t>
+    <t xml:space="preserve">9.91034984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91939258575439</t>
   </si>
   <si>
     <t xml:space="preserve">9.90130805969238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87418079376221</t>
+    <t xml:space="preserve">9.87418174743652</t>
   </si>
   <si>
     <t xml:space="preserve">9.82896995544434</t>
@@ -4130,10 +4130,10 @@
     <t xml:space="preserve">9.15984058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12367057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32260227203369</t>
+    <t xml:space="preserve">9.12367153167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32260131835938</t>
   </si>
   <si>
     <t xml:space="preserve">9.20505142211914</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">9.89226531982422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84705448150635</t>
+    <t xml:space="preserve">9.84705543518066</t>
   </si>
   <si>
     <t xml:space="preserve">10.0279006958008</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">10.0369424819946</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94651985168457</t>
+    <t xml:space="preserve">9.94651889801025</t>
   </si>
   <si>
     <t xml:space="preserve">10.1906623840332</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">10.4800148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5523529052734</t>
+    <t xml:space="preserve">10.5523538589478</t>
   </si>
   <si>
     <t xml:space="preserve">10.7151145935059</t>
@@ -4187,16 +4187,16 @@
     <t xml:space="preserve">10.4980993270874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2991695404053</t>
+    <t xml:space="preserve">10.299168586731</t>
   </si>
   <si>
     <t xml:space="preserve">10.2901268005371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.181619644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5704364776611</t>
+    <t xml:space="preserve">10.1816186904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5704374313354</t>
   </si>
   <si>
     <t xml:space="preserve">10.7603254318237</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">11.0768060684204</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2124404907227</t>
+    <t xml:space="preserve">11.2124395370483</t>
   </si>
   <si>
     <t xml:space="preserve">11.5560474395752</t>
@@ -4223,19 +4223,19 @@
     <t xml:space="preserve">11.2486085891724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6464700698853</t>
+    <t xml:space="preserve">11.6464710235596</t>
   </si>
   <si>
     <t xml:space="preserve">11.5289211273193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7188091278076</t>
+    <t xml:space="preserve">11.7188081741333</t>
   </si>
   <si>
     <t xml:space="preserve">11.9448661804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9629507064819</t>
+    <t xml:space="preserve">11.9629497528076</t>
   </si>
   <si>
     <t xml:space="preserve">11.9086971282959</t>
@@ -4250,10 +4250,10 @@
     <t xml:space="preserve">12.4783611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5054874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1528377532959</t>
+    <t xml:space="preserve">12.5054883956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1528387069702</t>
   </si>
   <si>
     <t xml:space="preserve">12.3155994415283</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">12.1709232330322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1799650192261</t>
+    <t xml:space="preserve">12.1799659729004</t>
   </si>
   <si>
     <t xml:space="preserve">12.107626914978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2161350250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2703876495361</t>
+    <t xml:space="preserve">12.2161340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2703886032104</t>
   </si>
   <si>
     <t xml:space="preserve">12.4874038696289</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">12.650164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4693193435669</t>
+    <t xml:space="preserve">12.4693183898926</t>
   </si>
   <si>
     <t xml:space="preserve">12.595911026001</t>
@@ -4316,16 +4316,16 @@
     <t xml:space="preserve">12.8852643966675</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0751523971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932359695435</t>
+    <t xml:space="preserve">13.0751514434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932369232178</t>
   </si>
   <si>
     <t xml:space="preserve">13.0028142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2198295593262</t>
+    <t xml:space="preserve">13.2198286056519</t>
   </si>
   <si>
     <t xml:space="preserve">12.9304752349854</t>
@@ -4346,16 +4346,16 @@
     <t xml:space="preserve">12.6772918701172</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2613458633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5507001876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.577826499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4602766036987</t>
+    <t xml:space="preserve">12.2613468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5506992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5778255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4602756500244</t>
   </si>
   <si>
     <t xml:space="preserve">12.3517684936523</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">12.4060230255127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3608112335205</t>
+    <t xml:space="preserve">12.3608121871948</t>
   </si>
   <si>
     <t xml:space="preserve">12.4241065979004</t>
@@ -4391,19 +4391,19 @@
     <t xml:space="preserve">13.5091819763184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2144804000854</t>
+    <t xml:space="preserve">14.2144813537598</t>
   </si>
   <si>
     <t xml:space="preserve">14.1963958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0788469314575</t>
+    <t xml:space="preserve">14.0788459777832</t>
   </si>
   <si>
     <t xml:space="preserve">13.8980007171631</t>
   </si>
   <si>
-    <t xml:space="preserve">13.979380607605</t>
+    <t xml:space="preserve">13.9793815612793</t>
   </si>
   <si>
     <t xml:space="preserve">14.0065078735352</t>
@@ -4424,16 +4424,16 @@
     <t xml:space="preserve">14.6485109329224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8474416732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5671300888062</t>
+    <t xml:space="preserve">14.8474407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5671310424805</t>
   </si>
   <si>
     <t xml:space="preserve">14.6846799850464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8022298812866</t>
+    <t xml:space="preserve">14.8022308349609</t>
   </si>
   <si>
     <t xml:space="preserve">14.7389326095581</t>
@@ -4448,10 +4448,10 @@
     <t xml:space="preserve">14.1511840820312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1873531341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3049030303955</t>
+    <t xml:space="preserve">14.1873540878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3049039840698</t>
   </si>
   <si>
     <t xml:space="preserve">13.9341697692871</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">14.1421422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2958612442017</t>
+    <t xml:space="preserve">14.295862197876</t>
   </si>
   <si>
     <t xml:space="preserve">14.4495801925659</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">14.5490455627441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.874568939209</t>
+    <t xml:space="preserve">14.8745679855347</t>
   </si>
   <si>
     <t xml:space="preserve">14.7208499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6123418807983</t>
+    <t xml:space="preserve">14.612340927124</t>
   </si>
   <si>
     <t xml:space="preserve">14.6304264068604</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">14.9649896621704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6575517654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8926515579224</t>
+    <t xml:space="preserve">14.6575527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8926525115967</t>
   </si>
   <si>
     <t xml:space="preserve">14.9740324020386</t>
@@ -4514,13 +4514,13 @@
     <t xml:space="preserve">15.082540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.471360206604</t>
+    <t xml:space="preserve">15.4713592529297</t>
   </si>
   <si>
     <t xml:space="preserve">15.191047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2633857727051</t>
+    <t xml:space="preserve">15.2633848190308</t>
   </si>
   <si>
     <t xml:space="preserve">15.1458368301392</t>
@@ -4532,16 +4532,16 @@
     <t xml:space="preserve">15.2995548248291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2000904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3718938827515</t>
+    <t xml:space="preserve">15.2000894546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3718948364258</t>
   </si>
   <si>
     <t xml:space="preserve">15.7245426177979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5527410507202</t>
+    <t xml:space="preserve">15.5527391433716</t>
   </si>
   <si>
     <t xml:space="preserve">15.6974172592163</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">15.4171047210693</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2905130386353</t>
+    <t xml:space="preserve">15.2905120849609</t>
   </si>
   <si>
     <t xml:space="preserve">15.0011596679688</t>
@@ -4568,10 +4568,10 @@
     <t xml:space="preserve">14.5128755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6665954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8112707138062</t>
+    <t xml:space="preserve">14.6665945053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8112716674805</t>
   </si>
   <si>
     <t xml:space="preserve">14.5054912567139</t>
@@ -4616,9 +4616,6 @@
     <t xml:space="preserve">15.2890548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8112716674805</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.8017158508301</t>
   </si>
   <si>
@@ -5391,6 +5388,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.5400009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2399997711182</t>
   </si>
 </sst>
 </file>
@@ -62219,7 +62219,7 @@
         <v>15.5</v>
       </c>
       <c r="G2173" t="s">
-        <v>1534</v>
+        <v>1519</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62245,7 +62245,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G2174" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62271,7 +62271,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G2175" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62297,7 +62297,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62323,7 +62323,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G2177" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62349,7 +62349,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G2178" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62375,7 +62375,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G2179" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62401,7 +62401,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G2180" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62427,7 +62427,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G2181" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62453,7 +62453,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G2182" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62479,7 +62479,7 @@
         <v>16.5</v>
       </c>
       <c r="G2183" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62505,7 +62505,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2184" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62531,7 +62531,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G2185" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62557,7 +62557,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G2186" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62583,7 +62583,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G2187" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62609,7 +62609,7 @@
         <v>16.25</v>
       </c>
       <c r="G2188" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62635,7 +62635,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G2189" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62661,7 +62661,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2190" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62687,7 +62687,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2191" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62713,7 +62713,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62739,7 +62739,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G2193" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62765,7 +62765,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G2194" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62791,7 +62791,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G2195" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62817,7 +62817,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G2196" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62843,7 +62843,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2197" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62869,7 +62869,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2198" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62895,7 +62895,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G2199" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62921,7 +62921,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2200" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62947,7 +62947,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G2201" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62973,7 +62973,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G2202" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62999,7 +62999,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2203" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63025,7 +63025,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2204" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63051,7 +63051,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G2205" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63077,7 +63077,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2206" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63103,7 +63103,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G2207" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63129,7 +63129,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2208" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63155,7 +63155,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G2209" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63181,7 +63181,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2210" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63207,7 +63207,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2211" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63233,7 +63233,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G2212" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63259,7 +63259,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2213" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63285,7 +63285,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2214" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63311,7 +63311,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2215" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63337,7 +63337,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2216" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63363,7 +63363,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G2217" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63389,7 +63389,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G2218" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63415,7 +63415,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G2219" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63441,7 +63441,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2220" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63467,7 +63467,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2221" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63493,7 +63493,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G2222" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63519,7 +63519,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G2223" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63545,7 +63545,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2224" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63571,7 +63571,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G2225" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63597,7 +63597,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G2226" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63623,7 +63623,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G2227" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63649,7 +63649,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G2228" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63675,7 +63675,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2229" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63701,7 +63701,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G2230" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63727,7 +63727,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G2231" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63753,7 +63753,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2232" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63779,7 +63779,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G2233" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63805,7 +63805,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2234" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63831,7 +63831,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G2235" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63857,7 +63857,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G2236" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63883,7 +63883,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G2237" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63909,7 +63909,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2238" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63935,7 +63935,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G2239" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63961,7 +63961,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2240" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63987,7 +63987,7 @@
         <v>17.75</v>
       </c>
       <c r="G2241" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64013,7 +64013,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2242" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64039,7 +64039,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2243" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64065,7 +64065,7 @@
         <v>18.5</v>
       </c>
       <c r="G2244" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64091,7 +64091,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G2245" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64117,7 +64117,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2246" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64143,7 +64143,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2247" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64169,7 +64169,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2248" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64195,7 +64195,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64221,7 +64221,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2250" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64247,7 +64247,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2251" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64273,7 +64273,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G2252" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64299,7 +64299,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G2253" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64325,7 +64325,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2254" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64351,7 +64351,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G2255" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64377,7 +64377,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G2256" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64403,7 +64403,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2257" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64429,7 +64429,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G2258" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64455,7 +64455,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2259" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64481,7 +64481,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2260" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64507,7 +64507,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2261" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64533,7 +64533,7 @@
         <v>17</v>
       </c>
       <c r="G2262" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64559,7 +64559,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64585,7 +64585,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G2264" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64611,7 +64611,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G2265" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64637,7 +64637,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2266" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64663,7 +64663,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G2267" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64689,7 +64689,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2268" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64715,7 +64715,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2269" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64741,7 +64741,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G2270" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64767,7 +64767,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G2271" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64793,7 +64793,7 @@
         <v>18</v>
       </c>
       <c r="G2272" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64819,7 +64819,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G2273" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64845,7 +64845,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G2274" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64871,7 +64871,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G2275" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64897,7 +64897,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G2276" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64923,7 +64923,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G2277" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64949,7 +64949,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2278" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64975,7 +64975,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2279" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65001,7 +65001,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G2280" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65027,7 +65027,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G2281" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65053,7 +65053,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G2282" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65079,7 +65079,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2283" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65105,7 +65105,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2284" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65131,7 +65131,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G2285" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65157,7 +65157,7 @@
         <v>18.25</v>
       </c>
       <c r="G2286" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65183,7 +65183,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G2287" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65209,7 +65209,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2288" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65235,7 +65235,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G2289" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65261,7 +65261,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G2290" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65287,7 +65287,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G2291" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65313,7 +65313,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G2292" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65339,7 +65339,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G2293" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65365,7 +65365,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2294" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65391,7 +65391,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G2295" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65417,7 +65417,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G2296" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65443,7 +65443,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G2297" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65469,7 +65469,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2298" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65495,7 +65495,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G2299" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65521,7 +65521,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2300" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65547,7 +65547,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G2301" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65573,7 +65573,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2302" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65599,7 +65599,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G2303" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65625,7 +65625,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G2304" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65651,7 +65651,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G2305" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65677,7 +65677,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G2306" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65703,7 +65703,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65729,7 +65729,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G2308" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65755,7 +65755,7 @@
         <v>18.25</v>
       </c>
       <c r="G2309" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65781,7 +65781,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G2310" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65807,7 +65807,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G2311" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65833,7 +65833,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2312" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65859,7 +65859,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G2313" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65885,7 +65885,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2314" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65911,7 +65911,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G2315" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65937,7 +65937,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2316" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65963,7 +65963,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2317" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -65989,7 +65989,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G2318" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66015,7 +66015,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G2319" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66041,7 +66041,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G2320" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66067,7 +66067,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G2321" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66093,7 +66093,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G2322" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66119,7 +66119,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2323" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66145,7 +66145,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2324" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66171,7 +66171,7 @@
         <v>17.25</v>
       </c>
       <c r="G2325" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66197,7 +66197,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G2326" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66223,7 +66223,7 @@
         <v>17.25</v>
       </c>
       <c r="G2327" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66249,7 +66249,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66275,7 +66275,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G2329" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66301,7 +66301,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G2330" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66327,7 +66327,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G2331" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66353,7 +66353,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G2332" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66379,7 +66379,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G2333" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66405,7 +66405,7 @@
         <v>17</v>
       </c>
       <c r="G2334" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66431,7 +66431,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66457,7 +66457,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G2336" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66483,7 +66483,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G2337" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66509,7 +66509,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2338" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66535,7 +66535,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2339" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66561,7 +66561,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G2340" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66587,7 +66587,7 @@
         <v>17.75</v>
       </c>
       <c r="G2341" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66613,7 +66613,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G2342" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66639,7 +66639,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G2343" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66665,7 +66665,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G2344" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66691,7 +66691,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2345" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66717,7 +66717,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G2346" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66743,7 +66743,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66769,7 +66769,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G2348" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66795,7 +66795,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G2349" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66821,7 +66821,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G2350" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66847,7 +66847,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66873,7 +66873,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2352" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66899,7 +66899,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G2353" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66925,7 +66925,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G2354" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66951,7 +66951,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G2355" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -66977,7 +66977,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G2356" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67003,7 +67003,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G2357" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67029,7 +67029,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2358" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67055,7 +67055,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G2359" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67081,7 +67081,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G2360" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67107,7 +67107,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2361" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67133,7 +67133,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G2362" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67159,7 +67159,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G2363" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67185,7 +67185,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G2364" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67211,7 +67211,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2365" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67237,7 +67237,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2366" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67263,7 +67263,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G2367" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67289,7 +67289,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G2368" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67315,7 +67315,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G2369" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67341,7 +67341,7 @@
         <v>20</v>
       </c>
       <c r="G2370" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67367,7 +67367,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2371" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67393,7 +67393,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2372" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67419,7 +67419,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G2373" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67445,7 +67445,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2374" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67471,7 +67471,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G2375" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67497,7 +67497,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G2376" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67523,7 +67523,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67549,7 +67549,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G2378" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67575,7 +67575,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G2379" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67601,7 +67601,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2380" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67627,7 +67627,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2381" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67653,7 +67653,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G2382" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67679,7 +67679,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G2383" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67705,7 +67705,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2384" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67731,7 +67731,7 @@
         <v>21.5</v>
       </c>
       <c r="G2385" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67757,7 +67757,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G2386" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67783,7 +67783,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G2387" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67809,7 +67809,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G2388" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67835,7 +67835,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G2389" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67861,7 +67861,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67887,7 +67887,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G2391" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67913,7 +67913,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G2392" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67939,7 +67939,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G2393" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67965,7 +67965,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G2394" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -67991,7 +67991,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68017,7 +68017,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2396" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68043,7 +68043,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2397" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68069,7 +68069,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G2398" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68095,7 +68095,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G2399" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68121,7 +68121,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G2400" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68147,7 +68147,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G2401" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68173,7 +68173,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G2402" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68199,7 +68199,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2403" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68225,7 +68225,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2404" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68251,7 +68251,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G2405" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68277,7 +68277,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2406" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68303,7 +68303,7 @@
         <v>21.5</v>
       </c>
       <c r="G2407" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68329,7 +68329,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G2408" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68355,7 +68355,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G2409" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68381,7 +68381,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G2410" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68407,7 +68407,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G2411" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68433,7 +68433,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2412" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68459,7 +68459,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2413" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68485,7 +68485,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2414" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68511,7 +68511,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2415" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68537,7 +68537,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2416" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68563,7 +68563,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68589,7 +68589,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2418" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68615,7 +68615,7 @@
         <v>19.75</v>
       </c>
       <c r="G2419" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68641,7 +68641,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G2420" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68667,7 +68667,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G2421" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68693,7 +68693,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G2422" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68719,7 +68719,7 @@
         <v>19.25</v>
       </c>
       <c r="G2423" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68745,7 +68745,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G2424" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68771,7 +68771,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G2425" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68797,7 +68797,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G2426" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68823,7 +68823,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G2427" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68849,7 +68849,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2428" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68875,7 +68875,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G2429" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68901,7 +68901,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G2430" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68927,7 +68927,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -68953,7 +68953,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G2432" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -68979,7 +68979,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2433" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69005,7 +69005,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2434" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69031,7 +69031,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G2435" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69057,7 +69057,7 @@
         <v>19.75</v>
       </c>
       <c r="G2436" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69083,7 +69083,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G2437" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69109,7 +69109,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G2438" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69135,7 +69135,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G2439" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69161,7 +69161,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G2440" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69187,7 +69187,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69213,7 +69213,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G2442" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69239,7 +69239,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2443" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69265,7 +69265,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G2444" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69291,7 +69291,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G2445" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69317,7 +69317,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2446" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69343,7 +69343,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G2447" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69369,7 +69369,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2448" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69395,7 +69395,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G2449" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69421,7 +69421,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G2450" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69447,7 +69447,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G2451" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69473,7 +69473,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G2452" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69499,7 +69499,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G2453" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69525,7 +69525,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G2454" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69551,7 +69551,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G2455" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -69577,7 +69577,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G2456" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69603,7 +69603,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G2457" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -69629,7 +69629,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G2458" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69655,7 +69655,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G2459" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69681,7 +69681,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G2460" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69707,7 +69707,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G2461" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69733,7 +69733,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G2462" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69759,7 +69759,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69785,7 +69785,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G2464" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69811,7 +69811,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G2465" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69837,7 +69837,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G2466" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69863,7 +69863,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2467" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69889,7 +69889,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G2468" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69915,7 +69915,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -69941,7 +69941,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G2470" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -69967,7 +69967,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G2471" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -69993,7 +69993,7 @@
         <v>19.25</v>
       </c>
       <c r="G2472" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70019,7 +70019,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70045,7 +70045,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G2474" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70071,7 +70071,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G2475" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70097,7 +70097,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G2476" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70123,7 +70123,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G2477" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70149,7 +70149,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G2478" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70175,7 +70175,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2479" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70201,7 +70201,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G2480" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70227,7 +70227,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70253,7 +70253,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G2482" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70279,7 +70279,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2483" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70305,7 +70305,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2484" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70331,7 +70331,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2485" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70357,7 +70357,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2486" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70383,7 +70383,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2487" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70409,7 +70409,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2488" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70435,7 +70435,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G2489" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70461,7 +70461,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G2490" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70487,7 +70487,7 @@
         <v>20.5</v>
       </c>
       <c r="G2491" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70513,7 +70513,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G2492" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -70539,7 +70539,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G2493" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -70565,7 +70565,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G2494" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -70591,7 +70591,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G2495" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -70617,7 +70617,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2496" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -70643,7 +70643,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2497" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -70669,7 +70669,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2498" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -70695,7 +70695,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G2499" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -70721,7 +70721,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G2500" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -70747,7 +70747,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2501" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -70773,7 +70773,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G2502" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -70799,7 +70799,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G2503" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -70825,7 +70825,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2504" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -70833,25 +70833,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6911805556</v>
+        <v>45967.6912152778</v>
       </c>
       <c r="B2505" t="n">
-        <v>86610</v>
+        <v>75895</v>
       </c>
       <c r="C2505" t="n">
-        <v>21.5799999237061</v>
+        <v>21.5400009155273</v>
       </c>
       <c r="D2505" t="n">
-        <v>21.2600002288818</v>
+        <v>21.0599994659424</v>
       </c>
       <c r="E2505" t="n">
-        <v>21.5400009155273</v>
+        <v>21.5</v>
       </c>
       <c r="F2505" t="n">
-        <v>21.4799995422363</v>
+        <v>21.2399997711182</v>
       </c>
       <c r="G2505" t="s">
-        <v>1787</v>
+        <v>1792</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59860992431641</t>
+    <t xml:space="preserve">8.59860897064209</t>
   </si>
   <si>
     <t xml:space="preserve">ACE.MI</t>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">8.61100769042969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3010368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43742561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48082065582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61720657348633</t>
+    <t xml:space="preserve">8.30103778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43742370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48082160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61720848083496</t>
   </si>
   <si>
     <t xml:space="preserve">8.80319023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68540096282959</t>
+    <t xml:space="preserve">8.68540000915527</t>
   </si>
   <si>
     <t xml:space="preserve">8.30723571777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3506326675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20804595947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.916672706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97246694564819</t>
+    <t xml:space="preserve">8.35063076019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20804405212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91667222976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97246646881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.13985252380371</t>
@@ -89,31 +89,31 @@
     <t xml:space="preserve">8.2762393951416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38782787322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49321842193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50561809539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39402866363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36923122406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33203411102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99106454849243</t>
+    <t xml:space="preserve">8.38782978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49321937561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50561904907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39402770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36923027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33203220367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99106550216675</t>
   </si>
   <si>
     <t xml:space="preserve">7.59430170059204</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45791339874268</t>
+    <t xml:space="preserve">7.45791482925415</t>
   </si>
   <si>
     <t xml:space="preserve">7.3153281211853</t>
@@ -122,85 +122,85 @@
     <t xml:space="preserve">7.46411418914795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66869640350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63149785995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6562967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65009689331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44551563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.600501537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68109226226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55090522766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68729162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60670042037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73688697814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64389705657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57570362091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53230714797974</t>
+    <t xml:space="preserve">7.66869354248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63149881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65629482269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65009641647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44551515579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60050010681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6810941696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55090570449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68729305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6067008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73688793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64389657974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57570266723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53230762481689</t>
   </si>
   <si>
     <t xml:space="preserve">8.0158634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38162803649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67920112609863</t>
+    <t xml:space="preserve">8.38162899017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67920303344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.77219295501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76599311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83418846130371</t>
+    <t xml:space="preserve">8.76599502563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83418655395508</t>
   </si>
   <si>
     <t xml:space="preserve">8.784592628479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46842098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41882514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33823204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45602130889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49941921234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58621025085449</t>
+    <t xml:space="preserve">8.46842288970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41882610321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33823299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45602321624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49941825866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58621120452881</t>
   </si>
   <si>
     <t xml:space="preserve">8.43122577667236</t>
@@ -209,118 +209,118 @@
     <t xml:space="preserve">8.40642738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34443283081055</t>
+    <t xml:space="preserve">8.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">8.4746208190918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24524211883545</t>
+    <t xml:space="preserve">8.24524116516113</t>
   </si>
   <si>
     <t xml:space="preserve">7.90427350997925</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8732762336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73069000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79268312454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85467720031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89807367324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96006774902344</t>
+    <t xml:space="preserve">7.87327575683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73068952560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79268407821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85467767715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89807224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96006870269775</t>
   </si>
   <si>
     <t xml:space="preserve">8.04685974121094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99726533889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96626806259155</t>
+    <t xml:space="preserve">7.99726486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96626901626587</t>
   </si>
   <si>
     <t xml:space="preserve">7.86707735061646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78028345108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11505317687988</t>
+    <t xml:space="preserve">7.78028440475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.090256690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1150541305542</t>
   </si>
   <si>
     <t xml:space="preserve">8.17704772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02206134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88567399978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8298807144165</t>
+    <t xml:space="preserve">8.02206325531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88567543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82988119125366</t>
   </si>
   <si>
     <t xml:space="preserve">8.04066181182861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00966453552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09645652770996</t>
+    <t xml:space="preserve">8.00966358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09645557403564</t>
   </si>
   <si>
     <t xml:space="preserve">8.19564628601074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23284339904785</t>
+    <t xml:space="preserve">8.23284244537354</t>
   </si>
   <si>
     <t xml:space="preserve">8.18324756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05925941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76168727874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52610874176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56330490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4207181930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19133996963501</t>
+    <t xml:space="preserve">8.05926036834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76168632507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5261082649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56330347061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42071676254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19133949279785</t>
   </si>
   <si>
     <t xml:space="preserve">6.85656976699829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96815919876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97435903549194</t>
+    <t xml:space="preserve">6.9681601524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97435855865479</t>
   </si>
   <si>
     <t xml:space="preserve">7.12314462661743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09073734283447</t>
+    <t xml:space="preserve">7.09073781967163</t>
   </si>
   <si>
     <t xml:space="preserve">7.05184936523438</t>
@@ -329,64 +329,64 @@
     <t xml:space="preserve">7.14259004592896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05833053588867</t>
+    <t xml:space="preserve">7.05833101272583</t>
   </si>
   <si>
     <t xml:space="preserve">6.68240451812744</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37777471542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49444246292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61110877990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08425712585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99999713897705</t>
+    <t xml:space="preserve">6.3777756690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49444198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61110830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08425664901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99999618530273</t>
   </si>
   <si>
     <t xml:space="preserve">7.03888654708862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93518114089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78610801696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370168685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8249979019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8638858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74073791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91573810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89629316329956</t>
+    <t xml:space="preserve">6.93518209457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78610849380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370025634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82499694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86388635635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7407374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91573762893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92870092391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89629364013672</t>
   </si>
   <si>
     <t xml:space="preserve">7.15555286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14907073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58333015441895</t>
+    <t xml:space="preserve">7.14907169342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58332967758179</t>
   </si>
   <si>
     <t xml:space="preserve">7.55740451812744</t>
@@ -404,55 +404,55 @@
     <t xml:space="preserve">8.16666316986084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17962646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07592296600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05647850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10184764862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95277404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82962703704834</t>
+    <t xml:space="preserve">8.17962551116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0759220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05647945404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10184860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95277500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82962560653687</t>
   </si>
   <si>
     <t xml:space="preserve">7.87499666213989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90740299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481151580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75832891464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74536752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77129364013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71944141387939</t>
+    <t xml:space="preserve">7.90740394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481199264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75832939147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74536657333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7712926864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71944093704224</t>
   </si>
   <si>
     <t xml:space="preserve">7.57684850692749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65462732315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70647859573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81666469573975</t>
+    <t xml:space="preserve">7.65462589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70647811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81666374206543</t>
   </si>
   <si>
     <t xml:space="preserve">7.79073858261108</t>
@@ -461,115 +461,115 @@
     <t xml:space="preserve">7.69351530075073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72592258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69999837875366</t>
+    <t xml:space="preserve">7.72592163085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69999647140503</t>
   </si>
   <si>
     <t xml:space="preserve">7.50555229187012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37592267990112</t>
+    <t xml:space="preserve">7.37592172622681</t>
   </si>
   <si>
     <t xml:space="preserve">7.39536666870117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47314453125</t>
+    <t xml:space="preserve">7.47314500808716</t>
   </si>
   <si>
     <t xml:space="preserve">7.3240704536438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25277423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22684860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18147897720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20092344284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22036695480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18795919418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16851663589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16203308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1944408416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17499685287476</t>
+    <t xml:space="preserve">7.25277376174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22684907913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18147850036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20092153549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22036743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18796062469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1685152053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.162034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19444227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17499589920044</t>
   </si>
   <si>
     <t xml:space="preserve">7.07129335403442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96758937835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04536771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98703336715698</t>
+    <t xml:space="preserve">6.96758890151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04536724090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98703289031982</t>
   </si>
   <si>
     <t xml:space="preserve">7.23332929611206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34999656677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41481113433838</t>
+    <t xml:space="preserve">7.34999752044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41481256484985</t>
   </si>
   <si>
     <t xml:space="preserve">7.55092191696167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52499580383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64166355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59629344940186</t>
+    <t xml:space="preserve">7.52499628067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64166402816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59629440307617</t>
   </si>
   <si>
     <t xml:space="preserve">7.6157374382019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64814472198486</t>
+    <t xml:space="preserve">7.64814519882202</t>
   </si>
   <si>
     <t xml:space="preserve">7.49258947372437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38888597488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46018218994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36944198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30462741851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84444189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57221937179565</t>
+    <t xml:space="preserve">7.38888549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46018123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36944150924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30462694168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84444141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57222032546997</t>
   </si>
   <si>
     <t xml:space="preserve">6.59166383743286</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">6.54629325866699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48147916793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43610811233521</t>
+    <t xml:space="preserve">6.48147869110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43610906600952</t>
   </si>
   <si>
     <t xml:space="preserve">6.47823810577393</t>
@@ -590,112 +590,112 @@
     <t xml:space="preserve">6.52684879302979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64999771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53333044052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59814500808716</t>
+    <t xml:space="preserve">6.64999723434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53332996368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59814643859863</t>
   </si>
   <si>
     <t xml:space="preserve">6.52036762237549</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42962646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87036800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10370016098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25925540924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48610830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43425703048706</t>
+    <t xml:space="preserve">6.42962741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8703670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10370111465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25925588607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48610782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43425607681274</t>
   </si>
   <si>
     <t xml:space="preserve">7.42777442932129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38240432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51851463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51203346252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66758871078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68055152893066</t>
+    <t xml:space="preserve">7.38240480422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51203393936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66758966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68055248260498</t>
   </si>
   <si>
     <t xml:space="preserve">7.71295833587646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8944411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79721879959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84258985519409</t>
+    <t xml:space="preserve">7.89444208145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79721832275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84258842468262</t>
   </si>
   <si>
     <t xml:space="preserve">7.34351587295532</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40184879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46666240692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40832996368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73888540267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68703269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6222186088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63518142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73240375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7777738571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83610773086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75184774398804</t>
+    <t xml:space="preserve">7.40184926986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46666288375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40832948684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73888444900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68703365325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62221908569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63518095016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7324047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77777481079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83610868453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75184726715088</t>
   </si>
   <si>
     <t xml:space="preserve">7.62870121002197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97221803665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85555171966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92684698104858</t>
+    <t xml:space="preserve">7.97221851348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85555219650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92684888839722</t>
   </si>
   <si>
     <t xml:space="preserve">8.03703308105469</t>
@@ -704,13 +704,13 @@
     <t xml:space="preserve">8.09536743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13425636291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20555210113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2898120880127</t>
+    <t xml:space="preserve">8.13425540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20555114746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28981113433838</t>
   </si>
   <si>
     <t xml:space="preserve">8.24444103240967</t>
@@ -722,25 +722,25 @@
     <t xml:space="preserve">8.22499656677246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27036571502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46481037139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45832824707031</t>
+    <t xml:space="preserve">8.27036666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46481132507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45832920074463</t>
   </si>
   <si>
     <t xml:space="preserve">8.43240451812744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42592239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35462665557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55555152893066</t>
+    <t xml:space="preserve">8.42592144012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35462474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55555248260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.52314472198486</t>
@@ -752,52 +752,52 @@
     <t xml:space="preserve">8.47129249572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60740280151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6138858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6203670501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56203460693359</t>
+    <t xml:space="preserve">8.60740375518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61388492584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62036609649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56203269958496</t>
   </si>
   <si>
     <t xml:space="preserve">8.80833053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6786994934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81481266021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84073829650879</t>
+    <t xml:space="preserve">8.67870044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81481170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84073638916016</t>
   </si>
   <si>
     <t xml:space="preserve">8.92499732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12592315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17777156829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00277423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95092296600342</t>
+    <t xml:space="preserve">9.12592220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17777347564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00277328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9509220123291</t>
   </si>
   <si>
     <t xml:space="preserve">8.99629211425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18425464630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01573657989502</t>
+    <t xml:space="preserve">9.1842565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01573848724365</t>
   </si>
   <si>
     <t xml:space="preserve">9.02869987487793</t>
@@ -809,22 +809,22 @@
     <t xml:space="preserve">9.28147792816162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30740165710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34629249572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43703174591064</t>
+    <t xml:space="preserve">9.30740451812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34629344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43703460693359</t>
   </si>
   <si>
     <t xml:space="preserve">9.32684803009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43055248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38518238067627</t>
+    <t xml:space="preserve">9.43055057525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38518047332764</t>
   </si>
   <si>
     <t xml:space="preserve">9.41758823394775</t>
@@ -836,37 +836,37 @@
     <t xml:space="preserve">9.50184726715088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50832939147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44351291656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54721832275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41110706329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35925483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51501750946045</t>
+    <t xml:space="preserve">9.50833034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44351387023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54721736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41110801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35925579071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51501655578613</t>
   </si>
   <si>
     <t xml:space="preserve">9.41343307495117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59628391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50147247314453</t>
+    <t xml:space="preserve">9.59628486633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50147342681885</t>
   </si>
   <si>
     <t xml:space="preserve">9.44729423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48115539550781</t>
+    <t xml:space="preserve">9.48115634918213</t>
   </si>
   <si>
     <t xml:space="preserve">9.21026611328125</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">9.09513759613037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14931488037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98678112030029</t>
+    <t xml:space="preserve">9.14931392669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98678207397461</t>
   </si>
   <si>
     <t xml:space="preserve">8.83101844787598</t>
@@ -890,37 +890,37 @@
     <t xml:space="preserve">8.93937587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81070327758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93260383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04095935821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87165260314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04773139953613</t>
+    <t xml:space="preserve">8.81070423126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93260192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04095840454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87165355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04773044586182</t>
   </si>
   <si>
     <t xml:space="preserve">9.08159255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10190963745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10868167877197</t>
+    <t xml:space="preserve">9.10190868377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10868072509766</t>
   </si>
   <si>
     <t xml:space="preserve">9.12222671508789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00709819793701</t>
+    <t xml:space="preserve">9.0070972442627</t>
   </si>
   <si>
     <t xml:space="preserve">9.07482051849365</t>
@@ -935,67 +935,67 @@
     <t xml:space="preserve">8.90551376342773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52626895904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58721733093262</t>
+    <t xml:space="preserve">8.52626705169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58721828460693</t>
   </si>
   <si>
     <t xml:space="preserve">8.5465841293335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56012916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68880176544189</t>
+    <t xml:space="preserve">8.56013011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68880271911621</t>
   </si>
   <si>
     <t xml:space="preserve">8.53981113433838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44500064849854</t>
+    <t xml:space="preserve">8.44500160217285</t>
   </si>
   <si>
     <t xml:space="preserve">8.33664512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47208881378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47886276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4111385345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42468357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38404941558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3908224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32987308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28246593475342</t>
+    <t xml:space="preserve">8.47209072113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47886180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41113948822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42468452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3840503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39082336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32987213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28246688842773</t>
   </si>
   <si>
     <t xml:space="preserve">8.26892185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24860572814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19442844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16733932495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21474361419678</t>
+    <t xml:space="preserve">8.24860668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19442653656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16733837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21474456787109</t>
   </si>
   <si>
     <t xml:space="preserve">8.37050533294678</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">8.29601192474365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39759540557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81747531890869</t>
+    <t xml:space="preserve">8.3975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81747436523438</t>
   </si>
   <si>
     <t xml:space="preserve">8.97323703765869</t>
@@ -1022,22 +1022,22 @@
     <t xml:space="preserve">8.68202972412109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69557476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80393028259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85810852050781</t>
+    <t xml:space="preserve">8.6955738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80392932891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8581075668335</t>
   </si>
   <si>
     <t xml:space="preserve">8.74297904968262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74975109100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79038429260254</t>
+    <t xml:space="preserve">8.74975204467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79038524627686</t>
   </si>
   <si>
     <t xml:space="preserve">8.88519668579102</t>
@@ -1052,34 +1052,34 @@
     <t xml:space="preserve">8.89196968078613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18317794799805</t>
+    <t xml:space="preserve">9.18317604064941</t>
   </si>
   <si>
     <t xml:space="preserve">9.19672107696533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29153156280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24412727355957</t>
+    <t xml:space="preserve">9.29153251647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24412536621094</t>
   </si>
   <si>
     <t xml:space="preserve">9.36602687835693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40666103363037</t>
+    <t xml:space="preserve">9.40666007995605</t>
   </si>
   <si>
     <t xml:space="preserve">9.54210567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46761035919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38634395599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52178859710693</t>
+    <t xml:space="preserve">9.46761131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38634300231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52179050445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.49470043182373</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">9.86717319488525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88749027252197</t>
+    <t xml:space="preserve">9.88749122619629</t>
   </si>
   <si>
     <t xml:space="preserve">9.83331394195557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76559066772461</t>
+    <t xml:space="preserve">9.76559162139893</t>
   </si>
   <si>
     <t xml:space="preserve">9.74527359008789</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">9.70464038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58273983001709</t>
+    <t xml:space="preserve">9.58273887634277</t>
   </si>
   <si>
     <t xml:space="preserve">9.71818447113037</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">9.67077922821045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96875762939453</t>
+    <t xml:space="preserve">9.96875858306885</t>
   </si>
   <si>
     <t xml:space="preserve">9.94844150543213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91458129882812</t>
+    <t xml:space="preserve">9.91457843780518</t>
   </si>
   <si>
     <t xml:space="preserve">10.0161638259888</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">9.96198654174805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92135238647461</t>
+    <t xml:space="preserve">9.92135143280029</t>
   </si>
   <si>
     <t xml:space="preserve">9.90103530883789</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">10.2599639892578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.445107460022</t>
+    <t xml:space="preserve">11.4451084136963</t>
   </si>
   <si>
     <t xml:space="preserve">11.567008972168</t>
@@ -1148,22 +1148,22 @@
     <t xml:space="preserve">11.4857416152954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5128307342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518804550171</t>
+    <t xml:space="preserve">11.5128316879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518823623657</t>
   </si>
   <si>
     <t xml:space="preserve">11.4383363723755</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4992866516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3502979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0726337432861</t>
+    <t xml:space="preserve">11.4992876052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3502988815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0726366043091</t>
   </si>
   <si>
     <t xml:space="preserve">10.9845962524414</t>
@@ -1178,34 +1178,34 @@
     <t xml:space="preserve">10.8152894973755</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5850315093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4495878219604</t>
+    <t xml:space="preserve">10.5850324630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4495868682861</t>
   </si>
   <si>
     <t xml:space="preserve">10.5647163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5443992614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4292707443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4699058532715</t>
+    <t xml:space="preserve">10.5444002151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4292697906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4699048995972</t>
   </si>
   <si>
     <t xml:space="preserve">10.632438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8220624923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9168739318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9913682937622</t>
+    <t xml:space="preserve">10.8220615386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9168729782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9913673400879</t>
   </si>
   <si>
     <t xml:space="preserve">10.8017454147339</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">10.7204790115356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6256647109985</t>
+    <t xml:space="preserve">10.6256656646729</t>
   </si>
   <si>
     <t xml:space="preserve">10.6730718612671</t>
@@ -1223,19 +1223,19 @@
     <t xml:space="preserve">10.8356056213379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9371891021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.998140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0455455780029</t>
+    <t xml:space="preserve">10.9371910095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9981412887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0455465316772</t>
   </si>
   <si>
     <t xml:space="preserve">11.1268129348755</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9304180145264</t>
+    <t xml:space="preserve">10.9304161071777</t>
   </si>
   <si>
     <t xml:space="preserve">10.8423795700073</t>
@@ -1244,34 +1244,34 @@
     <t xml:space="preserve">10.7746562957764</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7340230941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5918054580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5376272201538</t>
+    <t xml:space="preserve">10.7340240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5918064117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5376262664795</t>
   </si>
   <si>
     <t xml:space="preserve">10.5173101425171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3615493774414</t>
+    <t xml:space="preserve">10.3615484237671</t>
   </si>
   <si>
     <t xml:space="preserve">10.097430229187</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87394714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1922426223755</t>
+    <t xml:space="preserve">9.87394618988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1922416687012</t>
   </si>
   <si>
     <t xml:space="preserve">9.92812347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0364809036255</t>
+    <t xml:space="preserve">10.0364818572998</t>
   </si>
   <si>
     <t xml:space="preserve">10.0567970275879</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">10.1245203018188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0838871002197</t>
+    <t xml:space="preserve">10.0838861465454</t>
   </si>
   <si>
     <t xml:space="preserve">9.97552967071533</t>
@@ -1292,13 +1292,13 @@
     <t xml:space="preserve">9.50824451446533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44052219390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6436882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66400623321533</t>
+    <t xml:space="preserve">9.44052124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64368915557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66400527954102</t>
   </si>
   <si>
     <t xml:space="preserve">9.67755126953125</t>
@@ -1307,40 +1307,40 @@
     <t xml:space="preserve">9.46083927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55565071105957</t>
+    <t xml:space="preserve">9.55564975738525</t>
   </si>
   <si>
     <t xml:space="preserve">9.34571075439453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21703910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13577079772949</t>
+    <t xml:space="preserve">9.21703815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13576889038086</t>
   </si>
   <si>
     <t xml:space="preserve">9.23058223724365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06804752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17640686035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3321647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27798748016357</t>
+    <t xml:space="preserve">9.06804847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17640495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33216571807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27798843383789</t>
   </si>
   <si>
     <t xml:space="preserve">9.23735427856445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1628589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29830360412598</t>
+    <t xml:space="preserve">9.16286087036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29830455780029</t>
   </si>
   <si>
     <t xml:space="preserve">9.42697715759277</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">9.79945182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8062219619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77236366271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95521450042725</t>
+    <t xml:space="preserve">9.80622291564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77236270904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95521259307861</t>
   </si>
   <si>
     <t xml:space="preserve">9.81976890563965</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">9.47438335418701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71141242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30507755279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01387119293213</t>
+    <t xml:space="preserve">9.71141147613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01387023925781</t>
   </si>
   <si>
     <t xml:space="preserve">8.79715728759766</t>
@@ -1388,31 +1388,31 @@
     <t xml:space="preserve">9.03418731689453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39311599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26281547546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29120635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24152183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1137580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14924812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697441101074</t>
+    <t xml:space="preserve">9.39311695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26281452178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29120540618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24151992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11375713348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14924621582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697536468506</t>
   </si>
   <si>
     <t xml:space="preserve">9.07117080688477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03567886352539</t>
+    <t xml:space="preserve">9.03567981719971</t>
   </si>
   <si>
     <t xml:space="preserve">8.99309253692627</t>
@@ -1421,37 +1421,37 @@
     <t xml:space="preserve">9.04277801513672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19183444976807</t>
+    <t xml:space="preserve">9.02148532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19183540344238</t>
   </si>
   <si>
     <t xml:space="preserve">9.27700996398926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39767646789551</t>
+    <t xml:space="preserve">9.39767551422119</t>
   </si>
   <si>
     <t xml:space="preserve">9.2131290435791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10666084289551</t>
+    <t xml:space="preserve">9.10665988922119</t>
   </si>
   <si>
     <t xml:space="preserve">9.12795448303223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22732448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26991367340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12085723876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17764091491699</t>
+    <t xml:space="preserve">9.22732353210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26991176605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12085628509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17763900756836</t>
   </si>
   <si>
     <t xml:space="preserve">9.38348007202148</t>
@@ -1460,19 +1460,19 @@
     <t xml:space="preserve">9.44026374816895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41187286376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7028865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56092834472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61771392822266</t>
+    <t xml:space="preserve">9.41187191009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60351657867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70288753509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56092739105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61771202087402</t>
   </si>
   <si>
     <t xml:space="preserve">9.65320205688477</t>
@@ -1481,40 +1481,40 @@
     <t xml:space="preserve">9.6815938949585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57512474060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66030025482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53253746032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45446014404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50414562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30540180206299</t>
+    <t xml:space="preserve">9.57512378692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66029930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53253650665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45445919036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5041446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30539989471436</t>
   </si>
   <si>
     <t xml:space="preserve">9.34799003601074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28410911560059</t>
+    <t xml:space="preserve">9.28410816192627</t>
   </si>
   <si>
     <t xml:space="preserve">9.24861907958984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09246444702148</t>
+    <t xml:space="preserve">9.0924654006958</t>
   </si>
   <si>
     <t xml:space="preserve">8.82274341583252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71627330780029</t>
+    <t xml:space="preserve">8.71627235412598</t>
   </si>
   <si>
     <t xml:space="preserve">8.68078327178955</t>
@@ -1523,31 +1523,31 @@
     <t xml:space="preserve">8.78725242614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97889614105225</t>
+    <t xml:space="preserve">8.97889709472656</t>
   </si>
   <si>
     <t xml:space="preserve">9.0143871307373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14214992523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23442363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29830455780029</t>
+    <t xml:space="preserve">9.14215087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23442268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29830551147461</t>
   </si>
   <si>
     <t xml:space="preserve">9.39057731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42606735229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37638282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16344261169434</t>
+    <t xml:space="preserve">9.42606639862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37638187408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16344356536865</t>
   </si>
   <si>
     <t xml:space="preserve">9.04987621307373</t>
@@ -1556,55 +1556,55 @@
     <t xml:space="preserve">9.17054176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74466419219971</t>
+    <t xml:space="preserve">8.74466514587402</t>
   </si>
   <si>
     <t xml:space="preserve">8.69497966766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51043224334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48204040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39686489105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59560775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49623775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26910209655762</t>
+    <t xml:space="preserve">8.51043128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48204135894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39686584472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59560871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49623680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26910305023193</t>
   </si>
   <si>
     <t xml:space="preserve">8.26200580596924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22651481628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04196739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06326103210449</t>
+    <t xml:space="preserve">8.2265157699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04196929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06326198577881</t>
   </si>
   <si>
     <t xml:space="preserve">8.07036113739014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93549966812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1484375</t>
+    <t xml:space="preserve">7.93549919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14843845367432</t>
   </si>
   <si>
     <t xml:space="preserve">8.16263389587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2407112121582</t>
+    <t xml:space="preserve">8.24071025848389</t>
   </si>
   <si>
     <t xml:space="preserve">8.28329849243164</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">8.38266944885254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36137580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50333309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42525863647461</t>
+    <t xml:space="preserve">8.36137676239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50333499908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42525768280029</t>
   </si>
   <si>
     <t xml:space="preserve">9.15634536743164</t>
@@ -1631,16 +1631,16 @@
     <t xml:space="preserve">9.06407260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80854606628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81564426422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65949058532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56011962890625</t>
+    <t xml:space="preserve">8.8085470199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81564521789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65948963165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56011867523193</t>
   </si>
   <si>
     <t xml:space="preserve">8.57431411743164</t>
@@ -1655,16 +1655,16 @@
     <t xml:space="preserve">8.51753234863281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40396499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36847496032715</t>
+    <t xml:space="preserve">8.40396404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36847305297852</t>
   </si>
   <si>
     <t xml:space="preserve">8.43945407867432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21231842041016</t>
+    <t xml:space="preserve">8.21231937408447</t>
   </si>
   <si>
     <t xml:space="preserve">8.80144882202148</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">8.6098051071167</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3400821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19812297821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37557220458984</t>
+    <t xml:space="preserve">8.34008312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19812393188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37557315826416</t>
   </si>
   <si>
     <t xml:space="preserve">8.46074676513672</t>
@@ -1688,43 +1688,43 @@
     <t xml:space="preserve">8.62400054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38976669311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53172779083252</t>
+    <t xml:space="preserve">8.38976764678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53172874450684</t>
   </si>
   <si>
     <t xml:space="preserve">8.68788146972656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83693790435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85823059082031</t>
+    <t xml:space="preserve">8.83693885803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85823154449463</t>
   </si>
   <si>
     <t xml:space="preserve">8.90791702270508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25571537017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5112419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5822229385376</t>
+    <t xml:space="preserve">9.25571632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51124286651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58222198486328</t>
   </si>
   <si>
     <t xml:space="preserve">9.47575378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35508918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54673194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66739845275879</t>
+    <t xml:space="preserve">9.35508823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54673099517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66739749908447</t>
   </si>
   <si>
     <t xml:space="preserve">9.61061382293701</t>
@@ -1733,22 +1733,22 @@
     <t xml:space="preserve">9.63190841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51834106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68869209289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90872764587402</t>
+    <t xml:space="preserve">9.51834011077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68869018554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90872859954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.85904216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88033580780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75967121124268</t>
+    <t xml:space="preserve">9.88033485412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75967025756836</t>
   </si>
   <si>
     <t xml:space="preserve">9.86613941192627</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">9.85194396972656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0222949981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2423315048218</t>
+    <t xml:space="preserve">10.0222940444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2423324584961</t>
   </si>
   <si>
     <t xml:space="preserve">10.3275060653687</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">10.6114234924316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.760479927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6398153305054</t>
+    <t xml:space="preserve">10.7604808807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6398162841797</t>
   </si>
   <si>
     <t xml:space="preserve">10.6824035644531</t>
@@ -1781,22 +1781,22 @@
     <t xml:space="preserve">10.6043262481689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7107944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6895008087158</t>
+    <t xml:space="preserve">10.7107954025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6895017623901</t>
   </si>
   <si>
     <t xml:space="preserve">10.774676322937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7249908447266</t>
+    <t xml:space="preserve">10.7249917984009</t>
   </si>
   <si>
     <t xml:space="preserve">10.788872718811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.753381729126</t>
+    <t xml:space="preserve">10.7533826828003</t>
   </si>
   <si>
     <t xml:space="preserve">10.7391872406006</t>
@@ -1808,22 +1808,22 @@
     <t xml:space="preserve">10.6965990066528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9166345596313</t>
+    <t xml:space="preserve">10.9166355133057</t>
   </si>
   <si>
     <t xml:space="preserve">11.3567085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3709049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.49866771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3141193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4418830871582</t>
+    <t xml:space="preserve">11.370903968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4986667633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3141202926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4418840408325</t>
   </si>
   <si>
     <t xml:space="preserve">11.4276876449585</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">11.2999248504639</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1579647064209</t>
+    <t xml:space="preserve">11.1579656600952</t>
   </si>
   <si>
     <t xml:space="preserve">10.9876146316528</t>
@@ -1841,19 +1841,19 @@
     <t xml:space="preserve">11.0018110275269</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1863574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3850994110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4134912490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.484471321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4702749252319</t>
+    <t xml:space="preserve">11.1863565444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3851003646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4134902954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4844703674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4702739715576</t>
   </si>
   <si>
     <t xml:space="preserve">11.6122341156006</t>
@@ -1865,85 +1865,85 @@
     <t xml:space="preserve">11.8535642623901</t>
   </si>
   <si>
-    <t xml:space="preserve">11.938738822937</t>
+    <t xml:space="preserve">11.9387397766113</t>
   </si>
   <si>
     <t xml:space="preserve">12.1090888977051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9813251495361</t>
+    <t xml:space="preserve">11.9813261032104</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677587509155</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251724243164</t>
+    <t xml:space="preserve">11.8251733779907</t>
   </si>
   <si>
     <t xml:space="preserve">11.7399969100952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6832113265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7967805862427</t>
+    <t xml:space="preserve">11.6832132339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.796781539917</t>
   </si>
   <si>
     <t xml:space="preserve">11.8961524963379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9103479385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8393678665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8819551467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8109750747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0665006637573</t>
+    <t xml:space="preserve">11.9103488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8393688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8819541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8109760284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.066502571106</t>
   </si>
   <si>
     <t xml:space="preserve">12.1942653656006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2794408798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3078317642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3504199981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4355955123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5065755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.520770072937</t>
+    <t xml:space="preserve">12.2794399261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3078336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3504209518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4355945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5065746307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5207691192627</t>
   </si>
   <si>
     <t xml:space="preserve">12.5349655151367</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5917482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.662727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6343355178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7053155899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8161840438843</t>
+    <t xml:space="preserve">12.5917491912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6627292633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6343364715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7053174972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8161849975586</t>
   </si>
   <si>
     <t xml:space="preserve">12.6683616638184</t>
@@ -1955,13 +1955,13 @@
     <t xml:space="preserve">12.3874998092651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3727169036865</t>
+    <t xml:space="preserve">12.3727159500122</t>
   </si>
   <si>
     <t xml:space="preserve">12.3135890960693</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4466285705566</t>
+    <t xml:space="preserve">12.446629524231</t>
   </si>
   <si>
     <t xml:space="preserve">12.8014011383057</t>
@@ -1979,19 +1979,19 @@
     <t xml:space="preserve">12.7422723770142</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6831436157227</t>
+    <t xml:space="preserve">12.683144569397</t>
   </si>
   <si>
     <t xml:space="preserve">12.8753128051758</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7866191864014</t>
+    <t xml:space="preserve">12.7866182327271</t>
   </si>
   <si>
     <t xml:space="preserve">12.7718381881714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8309659957886</t>
+    <t xml:space="preserve">12.8309669494629</t>
   </si>
   <si>
     <t xml:space="preserve">12.9344415664673</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">12.6979265213013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7127094268799</t>
+    <t xml:space="preserve">12.7127103805542</t>
   </si>
   <si>
     <t xml:space="preserve">12.5944509506226</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">12.9048767089844</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8457479476929</t>
+    <t xml:space="preserve">12.8457489013672</t>
   </si>
   <si>
     <t xml:space="preserve">12.8900957107544</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0674819946289</t>
+    <t xml:space="preserve">13.0674810409546</t>
   </si>
   <si>
     <t xml:space="preserve">13.1118268966675</t>
@@ -2027,31 +2027,31 @@
     <t xml:space="preserve">12.9787883758545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1413927078247</t>
+    <t xml:space="preserve">13.1413917541504</t>
   </si>
   <si>
     <t xml:space="preserve">13.0970449447632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0822639465332</t>
+    <t xml:space="preserve">13.0822629928589</t>
   </si>
   <si>
     <t xml:space="preserve">13.0231351852417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9492244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1561727523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9935703277588</t>
+    <t xml:space="preserve">12.9492225646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1561737060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9935693740845</t>
   </si>
   <si>
     <t xml:space="preserve">12.6092319488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8605308532715</t>
+    <t xml:space="preserve">12.8605318069458</t>
   </si>
   <si>
     <t xml:space="preserve">12.5501022338867</t>
@@ -2060,31 +2060,31 @@
     <t xml:space="preserve">13.4518203735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3335628509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4961652755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3483428955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5405120849609</t>
+    <t xml:space="preserve">13.3335618972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.496166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3483419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5405111312866</t>
   </si>
   <si>
     <t xml:space="preserve">12.9640064239502</t>
   </si>
   <si>
-    <t xml:space="preserve">13.185736656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.170955657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.919659614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2744312286377</t>
+    <t xml:space="preserve">13.1857385635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1709547042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9196586608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.274432182312</t>
   </si>
   <si>
     <t xml:space="preserve">13.2596521377563</t>
@@ -2099,37 +2099,37 @@
     <t xml:space="preserve">13.1266098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7622451782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9396333694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5552940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7474632263184</t>
+    <t xml:space="preserve">13.762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9396324157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5552949905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7474613189697</t>
   </si>
   <si>
     <t xml:space="preserve">13.9691963195801</t>
   </si>
   <si>
-    <t xml:space="preserve">13.777027130127</t>
+    <t xml:space="preserve">13.7770261764526</t>
   </si>
   <si>
     <t xml:space="preserve">13.6292057037354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.86572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9544134140015</t>
+    <t xml:space="preserve">13.8657207489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9544153213501</t>
   </si>
   <si>
     <t xml:space="preserve">13.4666004180908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4813842773438</t>
+    <t xml:space="preserve">13.4813823699951</t>
   </si>
   <si>
     <t xml:space="preserve">13.4370374679565</t>
@@ -2141,34 +2141,34 @@
     <t xml:space="preserve">13.998761177063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0578918457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8213758468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6883335113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6587686538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144227981567</t>
+    <t xml:space="preserve">14.0578908920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8213768005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6883354187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6587696075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144218444824</t>
   </si>
   <si>
     <t xml:space="preserve">13.5257301330566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3631267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2300853729248</t>
+    <t xml:space="preserve">13.3631258010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2300863265991</t>
   </si>
   <si>
     <t xml:space="preserve">13.88050365448</t>
   </si>
   <si>
-    <t xml:space="preserve">14.457010269165</t>
+    <t xml:space="preserve">14.4570112228394</t>
   </si>
   <si>
     <t xml:space="preserve">14.4717922210693</t>
@@ -2177,25 +2177,25 @@
     <t xml:space="preserve">14.6343955993652</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8191738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0409069061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300394058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0039510726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3735065460205</t>
+    <t xml:space="preserve">14.8191728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0409078598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300413131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0039529800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3735084533691</t>
   </si>
   <si>
     <t xml:space="preserve">15.5582857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9278421401978</t>
+    <t xml:space="preserve">15.9278411865234</t>
   </si>
   <si>
     <t xml:space="preserve">16.1126194000244</t>
@@ -2204,34 +2204,34 @@
     <t xml:space="preserve">16.0387077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7800207138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061071395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6321954727173</t>
+    <t xml:space="preserve">15.7800188064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7061061859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.632194519043</t>
   </si>
   <si>
     <t xml:space="preserve">15.5213289260864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4104633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.447416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2256851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2626399993896</t>
+    <t xml:space="preserve">15.4104623794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4474191665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2256860733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.262640953064</t>
   </si>
   <si>
     <t xml:space="preserve">15.8908853530884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9669952392578</t>
+    <t xml:space="preserve">14.9669961929321</t>
   </si>
   <si>
     <t xml:space="preserve">14.7378721237183</t>
@@ -2243,67 +2243,67 @@
     <t xml:space="preserve">14.4126644134521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0874547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3091888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5161380767822</t>
+    <t xml:space="preserve">14.0874538421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3091869354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5161390304565</t>
   </si>
   <si>
     <t xml:space="preserve">14.5309200286865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8257741928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4710025787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87452125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2145118713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57887840270996</t>
+    <t xml:space="preserve">11.8257751464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.471001625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87452030181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2145128250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57887744903564</t>
   </si>
   <si>
     <t xml:space="preserve">9.63800621032715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1649751663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29801464080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53453159332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65278911590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5545043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7023267745972</t>
+    <t xml:space="preserve">9.16497611999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29801654815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53453063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65278816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5545034408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7023258209229</t>
   </si>
   <si>
     <t xml:space="preserve">10.5988512039185</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9388418197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7318906784058</t>
+    <t xml:space="preserve">10.9388427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7318916320801</t>
   </si>
   <si>
     <t xml:space="preserve">10.9018869400024</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2123126983643</t>
+    <t xml:space="preserve">11.2123136520386</t>
   </si>
   <si>
     <t xml:space="preserve">11.0275354385376</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">11.012752532959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0718803405762</t>
+    <t xml:space="preserve">11.0718812942505</t>
   </si>
   <si>
     <t xml:space="preserve">11.315788269043</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">10.8353662490845</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6801538467407</t>
+    <t xml:space="preserve">10.6801528930664</t>
   </si>
   <si>
     <t xml:space="preserve">10.7244997024536</t>
@@ -2339,25 +2339,25 @@
     <t xml:space="preserve">10.9462337493896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3749179840088</t>
+    <t xml:space="preserve">11.3749170303345</t>
   </si>
   <si>
     <t xml:space="preserve">11.2714414596558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5301313400269</t>
+    <t xml:space="preserve">11.5301303863525</t>
   </si>
   <si>
     <t xml:space="preserve">11.9735975265503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6040420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2197046279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5153484344482</t>
+    <t xml:space="preserve">11.6040410995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2197036743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5153474807739</t>
   </si>
   <si>
     <t xml:space="preserve">11.73708152771</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">12.128809928894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.431845664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5648851394653</t>
+    <t xml:space="preserve">12.4318466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5648860931396</t>
   </si>
   <si>
     <t xml:space="preserve">12.380108833313</t>
@@ -2378,22 +2378,22 @@
     <t xml:space="preserve">12.4392366409302</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4096727371216</t>
+    <t xml:space="preserve">12.4096736907959</t>
   </si>
   <si>
     <t xml:space="preserve">12.7644462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8974857330322</t>
+    <t xml:space="preserve">12.8974866867065</t>
   </si>
   <si>
     <t xml:space="preserve">12.8235750198364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9713973999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6070318222046</t>
+    <t xml:space="preserve">12.971396446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6070337295532</t>
   </si>
   <si>
     <t xml:space="preserve">13.8065929412842</t>
@@ -2411,25 +2411,25 @@
     <t xml:space="preserve">13.473991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">13.089653968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0600910186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887752532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2966060638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2512531280518</t>
+    <t xml:space="preserve">13.0896530151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0600900650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2966041564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2512512207031</t>
   </si>
   <si>
     <t xml:space="preserve">13.4521455764771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1353521347046</t>
+    <t xml:space="preserve">13.1353511810303</t>
   </si>
   <si>
     <t xml:space="preserve">12.9962711334229</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">13.3980598449707</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2048931121826</t>
+    <t xml:space="preserve">13.2048921585083</t>
   </si>
   <si>
     <t xml:space="preserve">13.4212398529053</t>
@@ -2459,13 +2459,13 @@
     <t xml:space="preserve">13.3594264984131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1276254653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812654495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9344577789307</t>
+    <t xml:space="preserve">13.1276245117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812664031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.934458732605</t>
   </si>
   <si>
     <t xml:space="preserve">12.8108320236206</t>
@@ -2480,25 +2480,25 @@
     <t xml:space="preserve">13.150806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3362464904785</t>
+    <t xml:space="preserve">13.3362455368042</t>
   </si>
   <si>
     <t xml:space="preserve">13.1894397735596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7953777313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5944843292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7644720077515</t>
+    <t xml:space="preserve">12.7953786849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944833755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7644710540771</t>
   </si>
   <si>
     <t xml:space="preserve">13.328519821167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2126197814941</t>
+    <t xml:space="preserve">13.2126178741455</t>
   </si>
   <si>
     <t xml:space="preserve">13.4366912841797</t>
@@ -2507,10 +2507,10 @@
     <t xml:space="preserve">13.6453123092651</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9312009811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5062322616577</t>
+    <t xml:space="preserve">13.9312000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.506233215332</t>
   </si>
   <si>
     <t xml:space="preserve">13.5216865539551</t>
@@ -2519,34 +2519,34 @@
     <t xml:space="preserve">13.5371398925781</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8539342880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8230266571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8848390579224</t>
+    <t xml:space="preserve">13.8539333343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8230247497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8848400115967</t>
   </si>
   <si>
     <t xml:space="preserve">14.0702781677246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7843914031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6916723251343</t>
+    <t xml:space="preserve">13.7843933105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.69167137146</t>
   </si>
   <si>
     <t xml:space="preserve">13.4289655685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6221323013306</t>
+    <t xml:space="preserve">13.6221332550049</t>
   </si>
   <si>
     <t xml:space="preserve">13.598952293396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2744331359863</t>
+    <t xml:space="preserve">13.2744340896606</t>
   </si>
   <si>
     <t xml:space="preserve">13.4675989151001</t>
@@ -2558,13 +2558,13 @@
     <t xml:space="preserve">13.5757732391357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3053398132324</t>
+    <t xml:space="preserve">13.3053388595581</t>
   </si>
   <si>
     <t xml:space="preserve">13.6298589706421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4753265380859</t>
+    <t xml:space="preserve">13.4753255844116</t>
   </si>
   <si>
     <t xml:space="preserve">13.7921199798584</t>
@@ -2573,31 +2573,31 @@
     <t xml:space="preserve">13.5680456161499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4830532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8462076187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9234743118286</t>
+    <t xml:space="preserve">13.4830522537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8462066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9234752655029</t>
   </si>
   <si>
     <t xml:space="preserve">13.9543790817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5912256240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3671531677246</t>
+    <t xml:space="preserve">13.5912275314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3671522140503</t>
   </si>
   <si>
     <t xml:space="preserve">13.5525932312012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7380332946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0007410049438</t>
+    <t xml:space="preserve">13.7380323410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0007419586182</t>
   </si>
   <si>
     <t xml:space="preserve">13.8925676345825</t>
@@ -2606,34 +2606,34 @@
     <t xml:space="preserve">13.9080200195312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0780057907104</t>
+    <t xml:space="preserve">14.0780067443848</t>
   </si>
   <si>
     <t xml:space="preserve">13.938928604126</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8616619110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8384790420532</t>
+    <t xml:space="preserve">13.8616609573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8384799957275</t>
   </si>
   <si>
     <t xml:space="preserve">14.0239200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">14.047101020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3329877853394</t>
+    <t xml:space="preserve">14.0471000671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.332986831665</t>
   </si>
   <si>
     <t xml:space="preserve">14.1861801147461</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1784553527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8152990341187</t>
+    <t xml:space="preserve">14.1784534454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8152980804443</t>
   </si>
   <si>
     <t xml:space="preserve">13.6993999481201</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">13.3130655288696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2667064666748</t>
+    <t xml:space="preserve">13.2667055130005</t>
   </si>
   <si>
     <t xml:space="preserve">13.2898874282837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3748779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.166259765625</t>
+    <t xml:space="preserve">13.3748788833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1662588119507</t>
   </si>
   <si>
     <t xml:space="preserve">13.7766666412354</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">13.761212348938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7998456954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5834989547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4907789230347</t>
+    <t xml:space="preserve">13.7998466491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5834999084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907779693604</t>
   </si>
   <si>
     <t xml:space="preserve">13.5139589309692</t>
@@ -2675,22 +2675,22 @@
     <t xml:space="preserve">14.0161933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6375865936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0426301956177</t>
+    <t xml:space="preserve">13.6375875473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.042631149292</t>
   </si>
   <si>
     <t xml:space="preserve">12.8880987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8262853622437</t>
+    <t xml:space="preserve">12.826286315918</t>
   </si>
   <si>
     <t xml:space="preserve">12.8494644165039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7567443847656</t>
+    <t xml:space="preserve">12.7567453384399</t>
   </si>
   <si>
     <t xml:space="preserve">12.5867586135864</t>
@@ -2708,19 +2708,19 @@
     <t xml:space="preserve">12.8031053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9267311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1430797576904</t>
+    <t xml:space="preserve">12.9267320632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1430788040161</t>
   </si>
   <si>
     <t xml:space="preserve">13.3207931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4135131835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4057865142822</t>
+    <t xml:space="preserve">13.4135141372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4057855606079</t>
   </si>
   <si>
     <t xml:space="preserve">13.1817111968994</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">12.772198677063</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7490186691284</t>
+    <t xml:space="preserve">12.7490177154541</t>
   </si>
   <si>
     <t xml:space="preserve">13.1971645355225</t>
@@ -2753,25 +2753,25 @@
     <t xml:space="preserve">13.0967197418213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.34397315979</t>
+    <t xml:space="preserve">13.3439722061157</t>
   </si>
   <si>
     <t xml:space="preserve">13.2821598052979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9808177947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7181100845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7258377075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6408452987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6176643371582</t>
+    <t xml:space="preserve">12.9808187484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.718111038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7258367538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6408443450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6176652908325</t>
   </si>
   <si>
     <t xml:space="preserve">12.7103853225708</t>
@@ -2783,37 +2783,37 @@
     <t xml:space="preserve">12.8803720474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603199005127</t>
+    <t xml:space="preserve">13.5603189468384</t>
   </si>
   <si>
     <t xml:space="preserve">13.6839456558228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9621057510376</t>
+    <t xml:space="preserve">13.9621047973633</t>
   </si>
   <si>
     <t xml:space="preserve">14.139820098877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.371621131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4102544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5570611953735</t>
+    <t xml:space="preserve">14.3716201782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4102535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5570621490479</t>
   </si>
   <si>
     <t xml:space="preserve">14.5338802337646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4025259017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2402687072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2557229995728</t>
+    <t xml:space="preserve">14.4025249481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2402677536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2557220458984</t>
   </si>
   <si>
     <t xml:space="preserve">14.3948001861572</t>
@@ -2822,46 +2822,46 @@
     <t xml:space="preserve">14.5493335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9588489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1211080551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8043155670166</t>
+    <t xml:space="preserve">14.9588479995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1211090087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.804313659668</t>
   </si>
   <si>
     <t xml:space="preserve">14.6343278884888</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7656831741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7579555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6806879043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5261545181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6961421966553</t>
+    <t xml:space="preserve">14.7656812667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7579545974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6806869506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5261535644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.696141242981</t>
   </si>
   <si>
     <t xml:space="preserve">14.6420545578003</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5725154876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6034212112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5956926345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.657506942749</t>
+    <t xml:space="preserve">14.5725145339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.603422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5956935882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6575050354004</t>
   </si>
   <si>
     <t xml:space="preserve">14.8352222442627</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">14.9974822998047</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1983737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0824747085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0283889770508</t>
+    <t xml:space="preserve">15.19837474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0824766159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0283880233765</t>
   </si>
   <si>
     <t xml:space="preserve">15.0979290008545</t>
@@ -2885,40 +2885,40 @@
     <t xml:space="preserve">15.1751947402954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2061023712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747489929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8506746292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8661270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9743013381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0592956542969</t>
+    <t xml:space="preserve">15.2061033248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747480392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8506736755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8661289215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9743003845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0592947006226</t>
   </si>
   <si>
     <t xml:space="preserve">15.0052080154419</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9279413223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1520137786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.414722442627</t>
+    <t xml:space="preserve">14.9279403686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1520147323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4147233963013</t>
   </si>
   <si>
     <t xml:space="preserve">15.8551435470581</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8087816238403</t>
+    <t xml:space="preserve">15.8087825775146</t>
   </si>
   <si>
     <t xml:space="preserve">15.6233425140381</t>
@@ -2927,28 +2927,28 @@
     <t xml:space="preserve">15.7624235153198</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9169569015503</t>
+    <t xml:space="preserve">15.916955947876</t>
   </si>
   <si>
     <t xml:space="preserve">16.0714893341064</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9787702560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8860483169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9942235946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1796646118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.056037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3496494293213</t>
+    <t xml:space="preserve">15.9787712097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8860473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9942245483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1796627044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0560359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3496513366699</t>
   </si>
   <si>
     <t xml:space="preserve">16.4578247070312</t>
@@ -5390,7 +5390,7 @@
     <t xml:space="preserve">21.5400009155273</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2399997711182</t>
+    <t xml:space="preserve">21.1200008392334</t>
   </si>
 </sst>
 </file>
@@ -70833,22 +70833,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6912152778</v>
+        <v>45968.6912731481</v>
       </c>
       <c r="B2505" t="n">
-        <v>75895</v>
+        <v>53222</v>
       </c>
       <c r="C2505" t="n">
-        <v>21.5400009155273</v>
+        <v>21.2600002288818</v>
       </c>
       <c r="D2505" t="n">
-        <v>21.0599994659424</v>
+        <v>20.8999996185303</v>
       </c>
       <c r="E2505" t="n">
-        <v>21.5</v>
+        <v>21.2199993133545</v>
       </c>
       <c r="F2505" t="n">
-        <v>21.2399997711182</v>
+        <v>21.1200008392334</v>
       </c>
       <c r="G2505" t="s">
         <v>1792</v>

--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="1798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="1799">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59860992431641</t>
+    <t xml:space="preserve">8.59860897064209</t>
   </si>
   <si>
     <t xml:space="preserve">ACE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61100769042969</t>
+    <t xml:space="preserve">8.611008644104</t>
   </si>
   <si>
     <t xml:space="preserve">8.3010368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.437424659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48082160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61720848083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80318927764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68540096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30723571777344</t>
+    <t xml:space="preserve">8.43742370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48081970214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61720752716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80319023132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68540191650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30723667144775</t>
   </si>
   <si>
     <t xml:space="preserve">8.3506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20804500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91667175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97246742248535</t>
+    <t xml:space="preserve">8.20804595947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91667127609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97246551513672</t>
   </si>
   <si>
     <t xml:space="preserve">8.13985157012939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15225028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2762393951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38782978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49321842193604</t>
+    <t xml:space="preserve">8.15225124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27623844146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38782787322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49321937561035</t>
   </si>
   <si>
     <t xml:space="preserve">8.50561809539795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39402866363525</t>
+    <t xml:space="preserve">8.39402770996094</t>
   </si>
   <si>
     <t xml:space="preserve">8.36923027038574</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">7.5943021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45791387557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31532764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46411418914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66869401931763</t>
+    <t xml:space="preserve">7.45791435241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3153281211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46411275863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66869497299194</t>
   </si>
   <si>
     <t xml:space="preserve">7.63149833679199</t>
@@ -131,25 +131,25 @@
     <t xml:space="preserve">7.65629625320435</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65009689331055</t>
+    <t xml:space="preserve">7.65009641647339</t>
   </si>
   <si>
     <t xml:space="preserve">7.44551563262939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60050058364868</t>
+    <t xml:space="preserve">7.600501537323</t>
   </si>
   <si>
     <t xml:space="preserve">7.68109369277954</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55090618133545</t>
+    <t xml:space="preserve">7.55090665817261</t>
   </si>
   <si>
     <t xml:space="preserve">7.68729257583618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60669898986816</t>
+    <t xml:space="preserve">7.6067008972168</t>
   </si>
   <si>
     <t xml:space="preserve">7.73688840866089</t>
@@ -158,43 +158,43 @@
     <t xml:space="preserve">7.64389801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57570362091064</t>
+    <t xml:space="preserve">7.57570314407349</t>
   </si>
   <si>
     <t xml:space="preserve">7.53230762481689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01586246490479</t>
+    <t xml:space="preserve">8.01586437225342</t>
   </si>
   <si>
     <t xml:space="preserve">8.38162899017334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67920207977295</t>
+    <t xml:space="preserve">8.67920112609863</t>
   </si>
   <si>
     <t xml:space="preserve">8.77219295501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76599407196045</t>
+    <t xml:space="preserve">8.76599502563477</t>
   </si>
   <si>
     <t xml:space="preserve">8.83418750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.784592628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46842098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41882514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33823299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45602321624756</t>
+    <t xml:space="preserve">8.78459167480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46842193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41882610321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33823394775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45602226257324</t>
   </si>
   <si>
     <t xml:space="preserve">8.49941825866699</t>
@@ -206,40 +206,40 @@
     <t xml:space="preserve">8.43122577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34443378448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47462272644043</t>
+    <t xml:space="preserve">8.40642738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34443283081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4746208190918</t>
   </si>
   <si>
     <t xml:space="preserve">8.24524307250977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90427207946777</t>
+    <t xml:space="preserve">7.90427398681641</t>
   </si>
   <si>
     <t xml:space="preserve">7.87327575683594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73069000244141</t>
+    <t xml:space="preserve">7.73068952560425</t>
   </si>
   <si>
     <t xml:space="preserve">7.79268264770508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85467672348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89807367324829</t>
+    <t xml:space="preserve">7.85467720031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89807462692261</t>
   </si>
   <si>
     <t xml:space="preserve">7.96006774902344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04685974121094</t>
+    <t xml:space="preserve">8.04686069488525</t>
   </si>
   <si>
     <t xml:space="preserve">7.99726533889771</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">8.090256690979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1150541305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1770486831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02206230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88567447662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8298807144165</t>
+    <t xml:space="preserve">8.11505317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17704677581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02206134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88567399978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82988119125366</t>
   </si>
   <si>
     <t xml:space="preserve">8.0406608581543</t>
@@ -278,118 +278,118 @@
     <t xml:space="preserve">8.00966358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09645462036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19564628601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23284435272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18324756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05925846099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76168727874756</t>
+    <t xml:space="preserve">8.09645652770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19564723968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23284339904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18324851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05925941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76168441772461</t>
   </si>
   <si>
     <t xml:space="preserve">7.5261082649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56330394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42071771621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19133949279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85656929016113</t>
+    <t xml:space="preserve">7.56330442428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4207181930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19133853912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85656976699829</t>
   </si>
   <si>
     <t xml:space="preserve">6.96815919876099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97435903549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12314510345459</t>
+    <t xml:space="preserve">6.97435855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12314414978027</t>
   </si>
   <si>
     <t xml:space="preserve">7.09073734283447</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05184841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14259052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05833148956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68240451812744</t>
+    <t xml:space="preserve">7.05184888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14259004592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05833005905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68240547180176</t>
   </si>
   <si>
     <t xml:space="preserve">6.3777756690979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49444150924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61110925674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08425664901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99999666213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03888511657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93518114089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78610801696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370073318481</t>
+    <t xml:space="preserve">6.49444246292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61110782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08425617218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99999761581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03888607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93518209457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78610897064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370025634766</t>
   </si>
   <si>
     <t xml:space="preserve">6.82499742507935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86388635635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74073696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91573715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92869997024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89629316329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15555191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58332967758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55740547180176</t>
+    <t xml:space="preserve">6.8638858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7407374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91573810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9286994934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89629364013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15555334091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907026290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58333015441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55740451812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.0694408416748</t>
@@ -398,40 +398,40 @@
     <t xml:space="preserve">8.0435152053833</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01110744476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16666316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17962741851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0759220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05647754669189</t>
+    <t xml:space="preserve">8.01110649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16666412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17962551116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07592105865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05647850036621</t>
   </si>
   <si>
     <t xml:space="preserve">8.10184860229492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95277404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82962656021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87499809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90740346908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75832891464233</t>
+    <t xml:space="preserve">7.95277500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82962608337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87499713897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90740394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481103897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75832986831665</t>
   </si>
   <si>
     <t xml:space="preserve">7.74536609649658</t>
@@ -440,70 +440,70 @@
     <t xml:space="preserve">7.77129220962524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71944093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57684898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65462684631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7064790725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81666278839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79073858261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69351577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72592353820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69999742507935</t>
+    <t xml:space="preserve">7.71943998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57684850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65462589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70647811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81666374206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79073715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69351482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72592306137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69999599456787</t>
   </si>
   <si>
     <t xml:space="preserve">7.50555229187012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37592363357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39536714553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47314500808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32407140731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25277423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22684812545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18147850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20092153549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22036695480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18795967102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16851663589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.162034034729</t>
+    <t xml:space="preserve">7.37592267990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39536762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32407093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25277328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22684907913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18147802352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20092344284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22036743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18796062469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16851615905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16203451156616</t>
   </si>
   <si>
     <t xml:space="preserve">7.19444131851196</t>
@@ -512,100 +512,100 @@
     <t xml:space="preserve">7.1749963760376</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07129335403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96758937835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04536771774292</t>
+    <t xml:space="preserve">7.07129240036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96758890151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04536724090576</t>
   </si>
   <si>
     <t xml:space="preserve">6.98703384399414</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23332977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34999704360962</t>
+    <t xml:space="preserve">7.23333024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34999799728394</t>
   </si>
   <si>
     <t xml:space="preserve">7.41481113433838</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55092287063599</t>
+    <t xml:space="preserve">7.55092239379883</t>
   </si>
   <si>
     <t xml:space="preserve">7.52499628067017</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64166402816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59629344940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61573696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64814567565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49258995056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38888549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46018123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36944055557251</t>
+    <t xml:space="preserve">7.64166307449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59629249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6157374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64814472198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49258852005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38888502120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46018171310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36944198608398</t>
   </si>
   <si>
     <t xml:space="preserve">7.30462694168091</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84444189071655</t>
+    <t xml:space="preserve">6.84444236755371</t>
   </si>
   <si>
     <t xml:space="preserve">6.57221984863281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59166383743286</t>
+    <t xml:space="preserve">6.5916633605957</t>
   </si>
   <si>
     <t xml:space="preserve">6.54629325866699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48147821426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43610858917236</t>
+    <t xml:space="preserve">6.48147869110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43610763549805</t>
   </si>
   <si>
     <t xml:space="preserve">6.47823810577393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52684831619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6499981880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53332948684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59814548492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52036714553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42962741851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87036800384521</t>
+    <t xml:space="preserve">6.52684879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64999675750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53333139419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59814500808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52036762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42962646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8703670501709</t>
   </si>
   <si>
     <t xml:space="preserve">7.10370016098022</t>
@@ -614,115 +614,115 @@
     <t xml:space="preserve">7.25925636291504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48610830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43425559997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42777395248413</t>
+    <t xml:space="preserve">7.48610734939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43425512313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42777490615845</t>
   </si>
   <si>
     <t xml:space="preserve">7.38240480422974</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51851463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51203393936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66758918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68055295944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71295976638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89444065093994</t>
+    <t xml:space="preserve">7.51851558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51203441619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66758871078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68055200576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71295881271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89444208145142</t>
   </si>
   <si>
     <t xml:space="preserve">7.79721879959106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84259033203125</t>
+    <t xml:space="preserve">7.84258985519409</t>
   </si>
   <si>
     <t xml:space="preserve">7.34351539611816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4018497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4666633605957</t>
+    <t xml:space="preserve">7.40184879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46666383743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.4083309173584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73888444900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68703365325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6222186088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63518142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73240423202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77777433395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83610868453979</t>
+    <t xml:space="preserve">7.7388858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68703317642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62221956253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63518285751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73240375518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7777738571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83610820770264</t>
   </si>
   <si>
     <t xml:space="preserve">7.75184774398804</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62870025634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97221851348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85555267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92684698104858</t>
+    <t xml:space="preserve">7.62870121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97221803665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85555219650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9268479347229</t>
   </si>
   <si>
     <t xml:space="preserve">8.03703308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09536743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13425636291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20555114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28981113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24444103240967</t>
+    <t xml:space="preserve">8.09536552429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13425540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20555210113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28981018066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24444198608398</t>
   </si>
   <si>
     <t xml:space="preserve">8.23147773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22499561309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27036571502686</t>
+    <t xml:space="preserve">8.22499656677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27036666870117</t>
   </si>
   <si>
     <t xml:space="preserve">8.46481132507324</t>
@@ -731,52 +731,52 @@
     <t xml:space="preserve">8.45833015441895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43240356445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42592239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3546257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55555248260498</t>
+    <t xml:space="preserve">8.43240451812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42592334747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35462665557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55555152893066</t>
   </si>
   <si>
     <t xml:space="preserve">8.52314472198486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39351558685303</t>
+    <t xml:space="preserve">8.39351463317871</t>
   </si>
   <si>
     <t xml:space="preserve">8.47129154205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6074047088623</t>
+    <t xml:space="preserve">8.60740375518799</t>
   </si>
   <si>
     <t xml:space="preserve">8.6138858795166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62036609649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56203365325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80833053588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67869853973389</t>
+    <t xml:space="preserve">8.6203670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56203269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80832958221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6786994934082</t>
   </si>
   <si>
     <t xml:space="preserve">8.81481170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84073734283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92499732971191</t>
+    <t xml:space="preserve">8.84073829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92499542236328</t>
   </si>
   <si>
     <t xml:space="preserve">9.12592220306396</t>
@@ -785,61 +785,61 @@
     <t xml:space="preserve">9.17777252197266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00277423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95092296600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9962911605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18425464630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01573657989502</t>
+    <t xml:space="preserve">9.00277519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9509220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99629306793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18425559997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01573753356934</t>
   </si>
   <si>
     <t xml:space="preserve">9.02869987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20369815826416</t>
+    <t xml:space="preserve">9.20370006561279</t>
   </si>
   <si>
     <t xml:space="preserve">9.28147792816162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30740356445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34629154205322</t>
+    <t xml:space="preserve">9.30740261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34629249572754</t>
   </si>
   <si>
     <t xml:space="preserve">9.43703365325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32684803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43055152893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38518047332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41758823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33332824707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50184631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50833034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44351482391357</t>
+    <t xml:space="preserve">9.32684707641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43055057525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38517951965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41758918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33332920074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50184726715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50832939147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44351387023926</t>
   </si>
   <si>
     <t xml:space="preserve">9.54721736907959</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">9.51501750946045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41343307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59628391265869</t>
+    <t xml:space="preserve">9.41343116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59628582000732</t>
   </si>
   <si>
     <t xml:space="preserve">9.50147247314453</t>
@@ -866,40 +866,40 @@
     <t xml:space="preserve">9.44729423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48115634918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21026515960693</t>
+    <t xml:space="preserve">9.48115539550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21026611328125</t>
   </si>
   <si>
     <t xml:space="preserve">9.09513759613037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14931583404541</t>
+    <t xml:space="preserve">9.14931488037109</t>
   </si>
   <si>
     <t xml:space="preserve">8.98678112030029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83101844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84456348419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93937492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81070327758789</t>
+    <t xml:space="preserve">8.83101940155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84456443786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93937587738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81070232391357</t>
   </si>
   <si>
     <t xml:space="preserve">8.93260192871094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04095935821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8716516494751</t>
+    <t xml:space="preserve">9.04095840454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87165260314941</t>
   </si>
   <si>
     <t xml:space="preserve">9.04773044586182</t>
@@ -911,31 +911,31 @@
     <t xml:space="preserve">9.10190963745117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349311828613</t>
+    <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
     <t xml:space="preserve">9.10868167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12222576141357</t>
+    <t xml:space="preserve">9.12222671508789</t>
   </si>
   <si>
     <t xml:space="preserve">9.0070972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07481956481934</t>
+    <t xml:space="preserve">9.07482051849365</t>
   </si>
   <si>
     <t xml:space="preserve">8.87842464447021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92583179473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90551471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52626705169678</t>
+    <t xml:space="preserve">8.92583084106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90551376342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52626800537109</t>
   </si>
   <si>
     <t xml:space="preserve">8.58721828460693</t>
@@ -947,37 +947,37 @@
     <t xml:space="preserve">8.56012916564941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68880081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5398120880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44500160217285</t>
+    <t xml:space="preserve">8.68880176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53981113433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44500064849854</t>
   </si>
   <si>
     <t xml:space="preserve">8.33664512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47208976745605</t>
+    <t xml:space="preserve">8.47209072113037</t>
   </si>
   <si>
     <t xml:space="preserve">8.47886276245117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41113948822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42468452453613</t>
+    <t xml:space="preserve">8.41114044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42468357086182</t>
   </si>
   <si>
     <t xml:space="preserve">8.3840503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39082336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32987213134766</t>
+    <t xml:space="preserve">8.3908224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32987308502197</t>
   </si>
   <si>
     <t xml:space="preserve">8.2824649810791</t>
@@ -986,40 +986,40 @@
     <t xml:space="preserve">8.26892185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24860572814941</t>
+    <t xml:space="preserve">8.2486047744751</t>
   </si>
   <si>
     <t xml:space="preserve">8.19442844390869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16733741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21474552154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37050437927246</t>
+    <t xml:space="preserve">8.16733932495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21474456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37050533294678</t>
   </si>
   <si>
     <t xml:space="preserve">8.29601097106934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39759540557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81747436523438</t>
+    <t xml:space="preserve">8.3975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81747531890869</t>
   </si>
   <si>
     <t xml:space="preserve">8.97323608398438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76329612731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67525863647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68202972412109</t>
+    <t xml:space="preserve">8.76329517364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67525768280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68202877044678</t>
   </si>
   <si>
     <t xml:space="preserve">8.69557476043701</t>
@@ -1034,25 +1034,25 @@
     <t xml:space="preserve">8.74298000335693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74975204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79038524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8851957321167</t>
+    <t xml:space="preserve">8.74975109100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79038429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88519668579102</t>
   </si>
   <si>
     <t xml:space="preserve">8.96646499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91228675842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8919677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18317604064941</t>
+    <t xml:space="preserve">8.91228580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89197063446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18317699432373</t>
   </si>
   <si>
     <t xml:space="preserve">9.19672203063965</t>
@@ -1061,10 +1061,10 @@
     <t xml:space="preserve">9.29153251647949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24412536621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36602687835693</t>
+    <t xml:space="preserve">9.24412631988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36602592468262</t>
   </si>
   <si>
     <t xml:space="preserve">9.40666103363037</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">9.38634300231934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52178859710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49470138549805</t>
+    <t xml:space="preserve">9.52178955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49470043182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.84008502960205</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">9.86717319488525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88749217987061</t>
+    <t xml:space="preserve">9.88749122619629</t>
   </si>
   <si>
     <t xml:space="preserve">9.83331298828125</t>
@@ -1100,22 +1100,22 @@
     <t xml:space="preserve">9.76558971405029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74527454376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70464038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58273887634277</t>
+    <t xml:space="preserve">9.74527263641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70463943481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58273983001709</t>
   </si>
   <si>
     <t xml:space="preserve">9.71818447113037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67077922821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96875762939453</t>
+    <t xml:space="preserve">9.67077827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96875953674316</t>
   </si>
   <si>
     <t xml:space="preserve">9.94844055175781</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">9.91458034515381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0161647796631</t>
+    <t xml:space="preserve">10.0161638259888</t>
   </si>
   <si>
     <t xml:space="preserve">9.96198558807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92135047912598</t>
+    <t xml:space="preserve">9.92135238647461</t>
   </si>
   <si>
     <t xml:space="preserve">9.90103530883789</t>
@@ -1139,19 +1139,19 @@
     <t xml:space="preserve">10.2599649429321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4451084136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.567008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4857425689697</t>
+    <t xml:space="preserve">11.4451093673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5670099258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4857416152954</t>
   </si>
   <si>
     <t xml:space="preserve">11.5128316879272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4518804550171</t>
+    <t xml:space="preserve">11.4518814086914</t>
   </si>
   <si>
     <t xml:space="preserve">11.4383354187012</t>
@@ -1160,31 +1160,31 @@
     <t xml:space="preserve">11.4992866516113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3502979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0726346969604</t>
+    <t xml:space="preserve">11.3502969741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0726356506348</t>
   </si>
   <si>
     <t xml:space="preserve">10.9845952987671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8762407302856</t>
+    <t xml:space="preserve">10.8762397766113</t>
   </si>
   <si>
     <t xml:space="preserve">11.1674470901489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8152894973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5850343704224</t>
+    <t xml:space="preserve">10.8152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5850315093994</t>
   </si>
   <si>
     <t xml:space="preserve">10.4495878219604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5647172927856</t>
+    <t xml:space="preserve">10.5647163391113</t>
   </si>
   <si>
     <t xml:space="preserve">10.5443992614746</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">10.4292707443237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4699058532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6324377059937</t>
+    <t xml:space="preserve">10.4699039459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6324396133423</t>
   </si>
   <si>
     <t xml:space="preserve">10.8220615386963</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">10.9168729782104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9913673400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8017435073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7204780578613</t>
+    <t xml:space="preserve">10.9913682937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8017444610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.720477104187</t>
   </si>
   <si>
     <t xml:space="preserve">10.6256656646729</t>
@@ -1226,22 +1226,22 @@
     <t xml:space="preserve">10.9371900558472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.998140335083</t>
+    <t xml:space="preserve">10.9981393814087</t>
   </si>
   <si>
     <t xml:space="preserve">11.0455455780029</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1268148422241</t>
+    <t xml:space="preserve">11.1268138885498</t>
   </si>
   <si>
     <t xml:space="preserve">10.9304161071777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8423776626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7746572494507</t>
+    <t xml:space="preserve">10.842378616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7746553421021</t>
   </si>
   <si>
     <t xml:space="preserve">10.7340230941772</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">10.5376272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5173110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3615484237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0974292755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87394714355469</t>
+    <t xml:space="preserve">10.5173101425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3615493774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0974311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.873948097229</t>
   </si>
   <si>
     <t xml:space="preserve">10.1922426223755</t>
@@ -1280,61 +1280,61 @@
     <t xml:space="preserve">10.1245193481445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0838871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97553062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69786834716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50824546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44052219390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64369010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66400623321533</t>
+    <t xml:space="preserve">10.0838861465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97552967071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69786739349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50824356079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44052124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64368915557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66400718688965</t>
   </si>
   <si>
     <t xml:space="preserve">9.67755126953125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46083831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55565166473389</t>
+    <t xml:space="preserve">9.46083927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55564975738525</t>
   </si>
   <si>
     <t xml:space="preserve">9.34570980072021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21703815460205</t>
+    <t xml:space="preserve">9.21703720092773</t>
   </si>
   <si>
     <t xml:space="preserve">9.13576984405518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23058128356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06804752349854</t>
+    <t xml:space="preserve">9.23058223724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06804656982422</t>
   </si>
   <si>
     <t xml:space="preserve">9.17640495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33216571807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27798843383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23735523223877</t>
+    <t xml:space="preserve">9.33216667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27798748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23735618591309</t>
   </si>
   <si>
     <t xml:space="preserve">9.1628589630127</t>
@@ -1343,43 +1343,43 @@
     <t xml:space="preserve">9.29830455780029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42697811126709</t>
+    <t xml:space="preserve">9.42697620391846</t>
   </si>
   <si>
     <t xml:space="preserve">9.53533363342285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62337303161621</t>
+    <t xml:space="preserve">9.62337207794189</t>
   </si>
   <si>
     <t xml:space="preserve">9.79945182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80622291564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77236270904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95521354675293</t>
+    <t xml:space="preserve">9.80622386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77236175537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95521259307861</t>
   </si>
   <si>
     <t xml:space="preserve">9.81976795196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75881862640381</t>
+    <t xml:space="preserve">9.75881671905518</t>
   </si>
   <si>
     <t xml:space="preserve">9.47438335418701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71141242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30507755279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01387023925781</t>
+    <t xml:space="preserve">9.71141338348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01387119293213</t>
   </si>
   <si>
     <t xml:space="preserve">8.79715824127197</t>
@@ -1388,28 +1388,28 @@
     <t xml:space="preserve">9.03418731689453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39311504364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26281452178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29120540618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24152088165283</t>
+    <t xml:space="preserve">9.39311695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26281547546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29120635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24152183532715</t>
   </si>
   <si>
     <t xml:space="preserve">9.11375904083252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14924812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697345733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07117080688477</t>
+    <t xml:space="preserve">9.14924907684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07116985321045</t>
   </si>
   <si>
     <t xml:space="preserve">9.03567981719971</t>
@@ -1418,43 +1418,43 @@
     <t xml:space="preserve">8.99309253692627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04277896881104</t>
+    <t xml:space="preserve">9.04277801513672</t>
   </si>
   <si>
     <t xml:space="preserve">9.02148532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1918363571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27700996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39767551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2131290435791</t>
+    <t xml:space="preserve">9.19183540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27701091766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39767646789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21312808990479</t>
   </si>
   <si>
     <t xml:space="preserve">9.10665988922119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12795352935791</t>
+    <t xml:space="preserve">9.12795448303223</t>
   </si>
   <si>
     <t xml:space="preserve">9.22732543945312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26991271972656</t>
+    <t xml:space="preserve">9.26991367340088</t>
   </si>
   <si>
     <t xml:space="preserve">9.12085628509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17763996124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38348007202148</t>
+    <t xml:space="preserve">9.17764091491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3834810256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.44026279449463</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">9.70288753509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56092834472656</t>
+    <t xml:space="preserve">9.56092929840088</t>
   </si>
   <si>
     <t xml:space="preserve">9.61771297454834</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">9.65320205688477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6815938949585</t>
+    <t xml:space="preserve">9.68159484863281</t>
   </si>
   <si>
     <t xml:space="preserve">9.57512378692627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66030025482178</t>
+    <t xml:space="preserve">9.66029930114746</t>
   </si>
   <si>
     <t xml:space="preserve">9.53253746032715</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">9.24861907958984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0924654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82274341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71627330780029</t>
+    <t xml:space="preserve">9.09246444702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82274150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71627426147461</t>
   </si>
   <si>
     <t xml:space="preserve">8.68078231811523</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">8.78725242614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97889804840088</t>
+    <t xml:space="preserve">8.97889709472656</t>
   </si>
   <si>
     <t xml:space="preserve">9.01438617706299</t>
@@ -1532,16 +1532,16 @@
     <t xml:space="preserve">9.14214992523193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23442363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39057731628418</t>
+    <t xml:space="preserve">9.23442268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3905782699585</t>
   </si>
   <si>
     <t xml:space="preserve">9.42606735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37638282775879</t>
+    <t xml:space="preserve">9.37638187408447</t>
   </si>
   <si>
     <t xml:space="preserve">9.16344356536865</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">9.04987716674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17054176330566</t>
+    <t xml:space="preserve">9.17054080963135</t>
   </si>
   <si>
     <t xml:space="preserve">8.74466419219971</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">8.51043224334717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48204040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39686584472656</t>
+    <t xml:space="preserve">8.48204231262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39686679840088</t>
   </si>
   <si>
     <t xml:space="preserve">8.59560775756836</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">8.26200580596924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2265157699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04196834564209</t>
+    <t xml:space="preserve">8.22651481628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04196929931641</t>
   </si>
   <si>
     <t xml:space="preserve">8.06326198577881</t>
@@ -1592,43 +1592,43 @@
     <t xml:space="preserve">8.07036018371582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93549823760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14843654632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16263294219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24071025848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28329849243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38267040252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36137580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50333404541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42525768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15634536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08536720275879</t>
+    <t xml:space="preserve">7.9355001449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16263389587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2407112121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28329753875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38266944885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3613748550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50333309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42525672912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15634632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08536624908447</t>
   </si>
   <si>
     <t xml:space="preserve">9.06407260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8085470199585</t>
+    <t xml:space="preserve">8.80854606628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.81564521789551</t>
@@ -1637,25 +1637,25 @@
     <t xml:space="preserve">8.65948867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56011867523193</t>
+    <t xml:space="preserve">8.56011962890625</t>
   </si>
   <si>
     <t xml:space="preserve">8.57431411743164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4465503692627</t>
+    <t xml:space="preserve">8.44655132293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.52462863922119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5175313949585</t>
+    <t xml:space="preserve">8.51753044128418</t>
   </si>
   <si>
     <t xml:space="preserve">8.40396404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36847496032715</t>
+    <t xml:space="preserve">8.36847305297852</t>
   </si>
   <si>
     <t xml:space="preserve">8.439453125</t>
@@ -1664,28 +1664,28 @@
     <t xml:space="preserve">8.21231937408447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80144882202148</t>
+    <t xml:space="preserve">8.80144786834717</t>
   </si>
   <si>
     <t xml:space="preserve">8.6098051071167</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3400821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19812393188477</t>
+    <t xml:space="preserve">8.34008312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19812488555908</t>
   </si>
   <si>
     <t xml:space="preserve">8.37557220458984</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46074676513672</t>
+    <t xml:space="preserve">8.46074771881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.62400054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38976860046387</t>
+    <t xml:space="preserve">8.38976764678955</t>
   </si>
   <si>
     <t xml:space="preserve">8.5317268371582</t>
@@ -1694,16 +1694,16 @@
     <t xml:space="preserve">8.68788146972656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83693885803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85823154449463</t>
+    <t xml:space="preserve">8.83693790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85823249816895</t>
   </si>
   <si>
     <t xml:space="preserve">8.90791797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25571632385254</t>
+    <t xml:space="preserve">9.25571727752686</t>
   </si>
   <si>
     <t xml:space="preserve">9.51124286651611</t>
@@ -1715,10 +1715,10 @@
     <t xml:space="preserve">9.47575283050537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35508918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54673194885254</t>
+    <t xml:space="preserve">9.35508823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54673290252686</t>
   </si>
   <si>
     <t xml:space="preserve">9.66739749908447</t>
@@ -1730,10 +1730,10 @@
     <t xml:space="preserve">9.63190746307373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51834011077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68869018554688</t>
+    <t xml:space="preserve">9.51834106445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68869113922119</t>
   </si>
   <si>
     <t xml:space="preserve">9.90872859954834</t>
@@ -1742,19 +1742,19 @@
     <t xml:space="preserve">9.85904216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88033580780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75967025756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86614036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85194301605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0222940444946</t>
+    <t xml:space="preserve">9.88033485412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75967121124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86613845825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85194492340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0222930908203</t>
   </si>
   <si>
     <t xml:space="preserve">10.2423305511475</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.6114234924316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7604818344116</t>
+    <t xml:space="preserve">10.7604808807373</t>
   </si>
   <si>
     <t xml:space="preserve">10.6398143768311</t>
@@ -1775,22 +1775,22 @@
     <t xml:space="preserve">10.6824035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6043252944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7107954025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6895027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7746772766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7249898910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7888736724854</t>
+    <t xml:space="preserve">10.6043262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7107963562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6895017623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.774676322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7249908447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7888717651367</t>
   </si>
   <si>
     <t xml:space="preserve">10.7533826828003</t>
@@ -1799,10 +1799,10 @@
     <t xml:space="preserve">10.7391872406006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7178945541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6965999603271</t>
+    <t xml:space="preserve">10.7178926467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6965980529785</t>
   </si>
   <si>
     <t xml:space="preserve">10.9166355133057</t>
@@ -1811,31 +1811,31 @@
     <t xml:space="preserve">11.356707572937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3709049224854</t>
+    <t xml:space="preserve">11.3709030151367</t>
   </si>
   <si>
     <t xml:space="preserve">11.4986667633057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3141202926636</t>
+    <t xml:space="preserve">11.3141193389893</t>
   </si>
   <si>
     <t xml:space="preserve">11.4418830871582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4276866912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2999248504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1579666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9876155853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0018100738525</t>
+    <t xml:space="preserve">11.4276885986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2999238967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1579647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9876146316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0018110275269</t>
   </si>
   <si>
     <t xml:space="preserve">11.1863574981689</t>
@@ -1844,22 +1844,22 @@
     <t xml:space="preserve">11.3851003646851</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4134902954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4844703674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4702758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6122331619263</t>
+    <t xml:space="preserve">11.4134922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.484471321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4702749252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6122341156006</t>
   </si>
   <si>
     <t xml:space="preserve">11.5412549972534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8535642623901</t>
+    <t xml:space="preserve">11.8535652160645</t>
   </si>
   <si>
     <t xml:space="preserve">11.938738822937</t>
@@ -1871,28 +1871,28 @@
     <t xml:space="preserve">11.9813261032104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8677597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8251714706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7399969100952</t>
+    <t xml:space="preserve">11.8677587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8251724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7399978637695</t>
   </si>
   <si>
     <t xml:space="preserve">11.6832132339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.796781539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8961515426636</t>
+    <t xml:space="preserve">11.7967805862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8961505889893</t>
   </si>
   <si>
     <t xml:space="preserve">11.9103479385376</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8393688201904</t>
+    <t xml:space="preserve">11.8393678665161</t>
   </si>
   <si>
     <t xml:space="preserve">11.8819551467896</t>
@@ -1904,43 +1904,43 @@
     <t xml:space="preserve">12.0665016174316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1942663192749</t>
+    <t xml:space="preserve">12.1942653656006</t>
   </si>
   <si>
     <t xml:space="preserve">12.2794399261475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3078317642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3504199981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4355955123901</t>
+    <t xml:space="preserve">12.3078308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3504190444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4355945587158</t>
   </si>
   <si>
     <t xml:space="preserve">12.5065746307373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.520770072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5349645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5917501449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6627283096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6343364715576</t>
+    <t xml:space="preserve">12.5207691192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.534966468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5917491912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6627292633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6343383789062</t>
   </si>
   <si>
     <t xml:space="preserve">12.7053165435791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8161840438843</t>
+    <t xml:space="preserve">12.8161821365356</t>
   </si>
   <si>
     <t xml:space="preserve">12.668360710144</t>
@@ -1949,43 +1949,43 @@
     <t xml:space="preserve">12.6387958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3875007629395</t>
+    <t xml:space="preserve">12.3874988555908</t>
   </si>
   <si>
     <t xml:space="preserve">12.3727169036865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.313588142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4466276168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.80140209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7274904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5353212356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5796670913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7422733306885</t>
+    <t xml:space="preserve">12.3135890960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.446629524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8014011383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7274894714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5353202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5796699523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7422723770142</t>
   </si>
   <si>
     <t xml:space="preserve">12.6831436157227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8753118515015</t>
+    <t xml:space="preserve">12.8753128051758</t>
   </si>
   <si>
     <t xml:space="preserve">12.7866182327271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7718372344971</t>
+    <t xml:space="preserve">12.7718362808228</t>
   </si>
   <si>
     <t xml:space="preserve">12.8309669494629</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">12.6979265213013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7127084732056</t>
+    <t xml:space="preserve">12.7127094268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.5944509506226</t>
@@ -2009,25 +2009,25 @@
     <t xml:space="preserve">12.8457479476929</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8900957107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0674819946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1118268966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.052698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9787874221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1413927078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0970439910889</t>
+    <t xml:space="preserve">12.8900947570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0674810409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1118288040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0526990890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9787883758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.141393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0970449447632</t>
   </si>
   <si>
     <t xml:space="preserve">13.0822629928589</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">13.0231351852417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9492235183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1561727523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9935703277588</t>
+    <t xml:space="preserve">12.9492225646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.156174659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9935693740845</t>
   </si>
   <si>
     <t xml:space="preserve">12.6092319488525</t>
@@ -2051,61 +2051,61 @@
     <t xml:space="preserve">12.8605298995972</t>
   </si>
   <si>
-    <t xml:space="preserve">12.550103187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4518184661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3335618972778</t>
+    <t xml:space="preserve">12.5501022338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4518194198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3335628509521</t>
   </si>
   <si>
     <t xml:space="preserve">13.496166229248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3483438491821</t>
+    <t xml:space="preserve">13.3483419418335</t>
   </si>
   <si>
     <t xml:space="preserve">13.5405120849609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9640073776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1709566116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.919659614563</t>
+    <t xml:space="preserve">12.9640064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857395172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.170955657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9196577072144</t>
   </si>
   <si>
     <t xml:space="preserve">13.274432182312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.259651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2892141342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2448673248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1266107559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7622451782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9396324157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5552949905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7474641799927</t>
+    <t xml:space="preserve">13.2596502304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2892150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2448682785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1266098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9396333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5552968978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7474632263184</t>
   </si>
   <si>
     <t xml:space="preserve">13.9691972732544</t>
@@ -2114,85 +2114,85 @@
     <t xml:space="preserve">13.777027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">13.629204750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.86572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9544153213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4665994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4813833236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4370384216309</t>
+    <t xml:space="preserve">13.6292066574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8657197952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9544115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4666013717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4813823699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4370365142822</t>
   </si>
   <si>
     <t xml:space="preserve">13.7918090820312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.998761177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0578889846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8213758468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6883344650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6587696075439</t>
+    <t xml:space="preserve">13.9987602233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0578899383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8213739395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6883354187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6587686538696</t>
   </si>
   <si>
     <t xml:space="preserve">13.6144227981567</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5257291793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3631267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2300863265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8805046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4570093154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4717931747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6343946456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8191728591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0409088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300413131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0039539337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3735046386719</t>
+    <t xml:space="preserve">13.525728225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3631258010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2300853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.88050365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4570083618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4717922210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6343955993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8191719055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0409078598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300394058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0039510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3735074996948</t>
   </si>
   <si>
     <t xml:space="preserve">15.5582838058472</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9278402328491</t>
+    <t xml:space="preserve">15.9278373718262</t>
   </si>
   <si>
     <t xml:space="preserve">16.1126174926758</t>
@@ -2201,55 +2201,55 @@
     <t xml:space="preserve">16.0387058258057</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7800216674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061061859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6321954727173</t>
+    <t xml:space="preserve">15.7800168991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7061080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.632194519043</t>
   </si>
   <si>
     <t xml:space="preserve">15.5213289260864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4104633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4474182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2256860733032</t>
+    <t xml:space="preserve">15.4104623794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4474172592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2256851196289</t>
   </si>
   <si>
     <t xml:space="preserve">15.262640953064</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8908853530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9669952392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7378730773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8561277389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4126634597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0874547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3091888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5161361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5309228897095</t>
+    <t xml:space="preserve">15.8908834457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9669961929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7378721237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8561305999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4126625061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0874528884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3091869354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5161380767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5309209823608</t>
   </si>
   <si>
     <t xml:space="preserve">11.8257741928101</t>
@@ -2261,43 +2261,43 @@
     <t xml:space="preserve">9.87452125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2145118713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57887649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63800621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16497611999512</t>
+    <t xml:space="preserve">10.2145137786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57887840270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63800716400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1649751663208</t>
   </si>
   <si>
     <t xml:space="preserve">9.29801559448242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53453063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65278911590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5545043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7023267745972</t>
+    <t xml:space="preserve">9.53453159332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65279006958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5545034408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7023258209229</t>
   </si>
   <si>
     <t xml:space="preserve">10.5988521575928</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9388427734375</t>
+    <t xml:space="preserve">10.9388399124146</t>
   </si>
   <si>
     <t xml:space="preserve">10.7318906784058</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9018859863281</t>
+    <t xml:space="preserve">10.9018869400024</t>
   </si>
   <si>
     <t xml:space="preserve">11.2123126983643</t>
@@ -2306,52 +2306,52 @@
     <t xml:space="preserve">11.0275354385376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9905796051025</t>
+    <t xml:space="preserve">10.9905786514282</t>
   </si>
   <si>
     <t xml:space="preserve">11.012752532959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0718822479248</t>
+    <t xml:space="preserve">11.0718803405762</t>
   </si>
   <si>
     <t xml:space="preserve">11.3157892227173</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6801528930664</t>
+    <t xml:space="preserve">10.8353662490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6801519393921</t>
   </si>
   <si>
     <t xml:space="preserve">10.7244997024536</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6505880355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5175476074219</t>
+    <t xml:space="preserve">10.6505889892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5175485610962</t>
   </si>
   <si>
     <t xml:space="preserve">10.9462337493896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3749170303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2714414596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5301313400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9735975265503</t>
+    <t xml:space="preserve">11.3749179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2714405059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5301303863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.973596572876</t>
   </si>
   <si>
     <t xml:space="preserve">11.6040410995483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2197036743164</t>
+    <t xml:space="preserve">11.2197027206421</t>
   </si>
   <si>
     <t xml:space="preserve">11.5153484344482</t>
@@ -2360,91 +2360,91 @@
     <t xml:space="preserve">11.73708152771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.128809928894</t>
+    <t xml:space="preserve">12.1288108825684</t>
   </si>
   <si>
     <t xml:space="preserve">12.431845664978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5648851394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3801069259644</t>
+    <t xml:space="preserve">12.5648860931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3801078796387</t>
   </si>
   <si>
     <t xml:space="preserve">12.4392366409302</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4096727371216</t>
+    <t xml:space="preserve">12.4096736907959</t>
   </si>
   <si>
     <t xml:space="preserve">12.7644462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8974857330322</t>
+    <t xml:space="preserve">12.8974866867065</t>
   </si>
   <si>
     <t xml:space="preserve">12.8235759735107</t>
   </si>
   <si>
-    <t xml:space="preserve">12.971396446228</t>
+    <t xml:space="preserve">12.9713954925537</t>
   </si>
   <si>
     <t xml:space="preserve">13.6070318222046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8065938949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8952856063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0431089401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5331201553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.473991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.089653968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0600910186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887742996216</t>
+    <t xml:space="preserve">13.8065919876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.89528465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0431079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5331211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4739904403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0896549224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0600900650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887762069702</t>
   </si>
   <si>
     <t xml:space="preserve">13.2966060638428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2512521743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4521455764771</t>
+    <t xml:space="preserve">13.2512512207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4521465301514</t>
   </si>
   <si>
     <t xml:space="preserve">13.1353521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9962720870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1585330963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3980598449707</t>
+    <t xml:space="preserve">12.9962711334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1585321426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3980579376221</t>
   </si>
   <si>
     <t xml:space="preserve">13.2048921585083</t>
   </si>
   <si>
-    <t xml:space="preserve">13.421238899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5448665618896</t>
+    <t xml:space="preserve">13.4212398529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.544867515564</t>
   </si>
   <si>
     <t xml:space="preserve">13.4444189071655</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">13.5294122695923</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3594264984131</t>
+    <t xml:space="preserve">13.3594274520874</t>
   </si>
   <si>
     <t xml:space="preserve">13.1276254653931</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">12.934458732605</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8108320236206</t>
+    <t xml:space="preserve">12.810830116272</t>
   </si>
   <si>
     <t xml:space="preserve">12.9576387405396</t>
@@ -2474,64 +2474,64 @@
     <t xml:space="preserve">13.2976112365723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1508045196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3362474441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1894388198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7953786849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5944833755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7644720077515</t>
+    <t xml:space="preserve">13.1508073806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3362464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1894378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7953777313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944843292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7644710540771</t>
   </si>
   <si>
     <t xml:space="preserve">13.3285188674927</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2126188278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4366912841797</t>
+    <t xml:space="preserve">13.2126178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.436692237854</t>
   </si>
   <si>
     <t xml:space="preserve">13.6453123092651</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9312009811401</t>
+    <t xml:space="preserve">13.9311990737915</t>
   </si>
   <si>
     <t xml:space="preserve">13.5062322616577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5216875076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5371398925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8539333343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8230257034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8848400115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0702791213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843923568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6916723251343</t>
+    <t xml:space="preserve">13.5216865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5371389389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8539342880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8230266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8848390579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0702781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843933105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.69167137146</t>
   </si>
   <si>
     <t xml:space="preserve">13.4289655685425</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">13.5989532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2744340896606</t>
+    <t xml:space="preserve">13.2744331359863</t>
   </si>
   <si>
     <t xml:space="preserve">13.4675989151001</t>
@@ -2555,31 +2555,31 @@
     <t xml:space="preserve">13.5757732391357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3053388595581</t>
+    <t xml:space="preserve">13.3053379058838</t>
   </si>
   <si>
     <t xml:space="preserve">13.6298589706421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4753274917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7921199798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5680456161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4830522537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8462057113647</t>
+    <t xml:space="preserve">13.4753255844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7921190261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5680465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4830532073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8462066650391</t>
   </si>
   <si>
     <t xml:space="preserve">13.9234733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9543800354004</t>
+    <t xml:space="preserve">13.9543781280518</t>
   </si>
   <si>
     <t xml:space="preserve">13.5912275314331</t>
@@ -2588,28 +2588,28 @@
     <t xml:space="preserve">13.3671522140503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5525941848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7380323410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0007419586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8925657272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9080209732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0780057907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9389276504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8616619110107</t>
+    <t xml:space="preserve">13.5525932312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7380342483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0007400512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8925676345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9080190658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0780076980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.938928604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8616600036621</t>
   </si>
   <si>
     <t xml:space="preserve">13.8384799957275</t>
@@ -2618,10 +2618,10 @@
     <t xml:space="preserve">14.0239200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">14.047101020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3329877853394</t>
+    <t xml:space="preserve">14.0471000671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3329858779907</t>
   </si>
   <si>
     <t xml:space="preserve">14.1861810684204</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">14.1784543991089</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8152980804443</t>
+    <t xml:space="preserve">13.8152990341187</t>
   </si>
   <si>
     <t xml:space="preserve">13.6993989944458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3130655288696</t>
+    <t xml:space="preserve">13.3130664825439</t>
   </si>
   <si>
     <t xml:space="preserve">13.2667064666748</t>
@@ -2645,25 +2645,25 @@
     <t xml:space="preserve">13.2898864746094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3748769760132</t>
+    <t xml:space="preserve">13.3748779296875</t>
   </si>
   <si>
     <t xml:space="preserve">13.1662588119507</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7766666412354</t>
+    <t xml:space="preserve">13.776665687561</t>
   </si>
   <si>
     <t xml:space="preserve">13.761212348938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7998466491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5834999084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4907789230347</t>
+    <t xml:space="preserve">13.7998476028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5834989547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907779693604</t>
   </si>
   <si>
     <t xml:space="preserve">13.5139579772949</t>
@@ -2675,76 +2675,76 @@
     <t xml:space="preserve">13.6375865936279</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0426321029663</t>
+    <t xml:space="preserve">13.042631149292</t>
   </si>
   <si>
     <t xml:space="preserve">12.8880987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8262853622437</t>
+    <t xml:space="preserve">12.826286315918</t>
   </si>
   <si>
     <t xml:space="preserve">12.8494653701782</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7567443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5867595672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6022119522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6253910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6872043609619</t>
+    <t xml:space="preserve">12.7567453384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5867586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6022109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.625391960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6872053146362</t>
   </si>
   <si>
     <t xml:space="preserve">12.8031053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9267320632935</t>
+    <t xml:space="preserve">12.9267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">13.1430788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3207931518555</t>
+    <t xml:space="preserve">13.3207921981812</t>
   </si>
   <si>
     <t xml:space="preserve">13.4135141372681</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4057865142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1817121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8417387008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8726444244385</t>
+    <t xml:space="preserve">13.4057874679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1817111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.841739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8726453781128</t>
   </si>
   <si>
     <t xml:space="preserve">12.9190044403076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8571920394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6331186294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7721996307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7490177154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1971654891968</t>
+    <t xml:space="preserve">12.8571910858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6331176757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.772198677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7490186691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1971664428711</t>
   </si>
   <si>
     <t xml:space="preserve">13.096718788147</t>
@@ -2753,13 +2753,13 @@
     <t xml:space="preserve">13.3439722061157</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821588516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9808177947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.718111038208</t>
+    <t xml:space="preserve">13.2821598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9808187484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7181119918823</t>
   </si>
   <si>
     <t xml:space="preserve">12.7258377075195</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">12.6408452987671</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6176643371582</t>
+    <t xml:space="preserve">12.6176652908325</t>
   </si>
   <si>
     <t xml:space="preserve">12.7103862762451</t>
@@ -2777,25 +2777,25 @@
     <t xml:space="preserve">12.4554052352905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8803730010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5603189468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6839466094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9621057510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.139820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3716201782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4102535247803</t>
+    <t xml:space="preserve">12.8803720474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5603179931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6839475631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9621076583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1398181915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.371621131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4102544784546</t>
   </si>
   <si>
     <t xml:space="preserve">14.5570611953735</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">14.5338802337646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4025268554688</t>
+    <t xml:space="preserve">14.4025259017944</t>
   </si>
   <si>
     <t xml:space="preserve">14.2402677536011</t>
@@ -2816,31 +2816,31 @@
     <t xml:space="preserve">14.3948001861572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5493335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9588470458984</t>
+    <t xml:space="preserve">14.5493354797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9588479995728</t>
   </si>
   <si>
     <t xml:space="preserve">15.1211080551147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.804313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6343297958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7656812667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7579545974731</t>
+    <t xml:space="preserve">14.8043146133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6343269348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.765682220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7579565048218</t>
   </si>
   <si>
     <t xml:space="preserve">14.6806879043579</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5261535644531</t>
+    <t xml:space="preserve">14.5261526107788</t>
   </si>
   <si>
     <t xml:space="preserve">14.696141242981</t>
@@ -2855,25 +2855,25 @@
     <t xml:space="preserve">14.603422164917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5956916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6575078964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8352212905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9974813461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1983737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0824747085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0283880233765</t>
+    <t xml:space="preserve">14.5956945419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6575050354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8352222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.997483253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1983766555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0824766159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0283889770508</t>
   </si>
   <si>
     <t xml:space="preserve">15.0979290008545</t>
@@ -2882,16 +2882,16 @@
     <t xml:space="preserve">15.1751947402954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2061014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747489929199</t>
+    <t xml:space="preserve">15.2061033248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747470855713</t>
   </si>
   <si>
     <t xml:space="preserve">14.8506736755371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8661279678345</t>
+    <t xml:space="preserve">14.8661270141602</t>
   </si>
   <si>
     <t xml:space="preserve">14.9743003845215</t>
@@ -2900,16 +2900,16 @@
     <t xml:space="preserve">15.0592947006226</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0052080154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9279403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1520147323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.414722442627</t>
+    <t xml:space="preserve">15.0052070617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9279413223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1520175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4147233963013</t>
   </si>
   <si>
     <t xml:space="preserve">15.8551435470581</t>
@@ -2921,28 +2921,28 @@
     <t xml:space="preserve">15.6233425140381</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7624216079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9169569015503</t>
+    <t xml:space="preserve">15.7624235153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.916955947876</t>
   </si>
   <si>
     <t xml:space="preserve">16.0714893341064</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9787702560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8860483169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9942226409912</t>
+    <t xml:space="preserve">15.9787693023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8860473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9942245483398</t>
   </si>
   <si>
     <t xml:space="preserve">16.1796627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0560359954834</t>
+    <t xml:space="preserve">16.056037902832</t>
   </si>
   <si>
     <t xml:space="preserve">16.3496513366699</t>
@@ -2951,10 +2951,10 @@
     <t xml:space="preserve">16.4578227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2651481628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0564136505127</t>
+    <t xml:space="preserve">16.2651462554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0564117431641</t>
   </si>
   <si>
     <t xml:space="preserve">15.8476800918579</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">15.7834548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8717632293701</t>
+    <t xml:space="preserve">15.8717651367188</t>
   </si>
   <si>
     <t xml:space="preserve">15.6871166229248</t>
@@ -2984,46 +2984,46 @@
     <t xml:space="preserve">15.7673969268799</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1045818328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.598804473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5827484130859</t>
+    <t xml:space="preserve">16.1045837402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5988063812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827503204346</t>
   </si>
   <si>
     <t xml:space="preserve">15.711199760437</t>
   </si>
   <si>
-    <t xml:space="preserve">15.727255821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5907773971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5104942321777</t>
+    <t xml:space="preserve">15.7272577285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5907754898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5104951858521</t>
   </si>
   <si>
     <t xml:space="preserve">15.213451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2616195678711</t>
+    <t xml:space="preserve">15.2616214752197</t>
   </si>
   <si>
     <t xml:space="preserve">15.4703550338745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.663031578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8557071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7352867126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.911904335022</t>
+    <t xml:space="preserve">15.6630296707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8557090759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7352848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9119062423706</t>
   </si>
   <si>
     <t xml:space="preserve">16.0162734985352</t>
@@ -3035,16 +3035,16 @@
     <t xml:space="preserve">15.9921875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2490901947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3454303741455</t>
+    <t xml:space="preserve">16.2490882873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3454284667969</t>
   </si>
   <si>
     <t xml:space="preserve">16.5381050109863</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6665554046631</t>
+    <t xml:space="preserve">16.6665573120117</t>
   </si>
   <si>
     <t xml:space="preserve">16.9876861572266</t>
@@ -3053,13 +3053,13 @@
     <t xml:space="preserve">17.0679683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9074020385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5702171325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2330322265625</t>
+    <t xml:space="preserve">16.9074039459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.570219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2330341339111</t>
   </si>
   <si>
     <t xml:space="preserve">16.0724697113037</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">16.4096565246582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2009201049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3133163452148</t>
+    <t xml:space="preserve">16.2009181976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3133144378662</t>
   </si>
   <si>
     <t xml:space="preserve">16.1366958618164</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">16.3293724060059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0885257720947</t>
+    <t xml:space="preserve">16.0885276794434</t>
   </si>
   <si>
     <t xml:space="preserve">16.0483837127686</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">16.2812042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2972602844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1527538299561</t>
+    <t xml:space="preserve">16.2972583770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1527519226074</t>
   </si>
   <si>
     <t xml:space="preserve">15.8637361526489</t>
@@ -3104,52 +3104,52 @@
     <t xml:space="preserve">15.398099899292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1090850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.916407585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.804012298584</t>
+    <t xml:space="preserve">15.1090831756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9164066314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8040132522583</t>
   </si>
   <si>
     <t xml:space="preserve">14.9806327819824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9886627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9645767211914</t>
+    <t xml:space="preserve">14.9886617660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9645757675171</t>
   </si>
   <si>
     <t xml:space="preserve">14.7478151321411</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8923234939575</t>
+    <t xml:space="preserve">14.8923215866089</t>
   </si>
   <si>
     <t xml:space="preserve">14.8120422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9003505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8521814346313</t>
+    <t xml:space="preserve">14.900351524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8521823883057</t>
   </si>
   <si>
     <t xml:space="preserve">15.101056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6755609512329</t>
+    <t xml:space="preserve">14.6755628585815</t>
   </si>
   <si>
     <t xml:space="preserve">14.787956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.117112159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2375345230103</t>
+    <t xml:space="preserve">15.1171140670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2375364303589</t>
   </si>
   <si>
     <t xml:space="preserve">15.0930271148682</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">15.2937335968018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3900728225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0609169006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0368309020996</t>
+    <t xml:space="preserve">15.3900709152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0609149932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.036828994751</t>
   </si>
   <si>
     <t xml:space="preserve">15.3419036865234</t>
@@ -3173,10 +3173,10 @@
     <t xml:space="preserve">15.2535924911499</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1973943710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5345802307129</t>
+    <t xml:space="preserve">15.197395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5345783233643</t>
   </si>
   <si>
     <t xml:space="preserve">15.1251411437988</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">15.1492261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8441553115845</t>
+    <t xml:space="preserve">14.8441534042358</t>
   </si>
   <si>
     <t xml:space="preserve">14.7076740264893</t>
@@ -3197,10 +3197,10 @@
     <t xml:space="preserve">14.6113367080688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6595048904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1858415603638</t>
+    <t xml:space="preserve">14.6595058441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1858406066895</t>
   </si>
   <si>
     <t xml:space="preserve">14.3062629699707</t>
@@ -3209,19 +3209,19 @@
     <t xml:space="preserve">14.3544321060181</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5792226791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3464059829712</t>
+    <t xml:space="preserve">14.5792245864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3464069366455</t>
   </si>
   <si>
     <t xml:space="preserve">14.3142919540405</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6996459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6193628311157</t>
+    <t xml:space="preserve">14.6996469497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6193618774414</t>
   </si>
   <si>
     <t xml:space="preserve">14.5551385879517</t>
@@ -3230,10 +3230,10 @@
     <t xml:space="preserve">14.5230255126953</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5471124649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273908615112</t>
+    <t xml:space="preserve">14.5471105575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273927688599</t>
   </si>
   <si>
     <t xml:space="preserve">14.8200693130493</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">14.225980758667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1617546081543</t>
+    <t xml:space="preserve">14.1617555618286</t>
   </si>
   <si>
     <t xml:space="preserve">14.0493621826172</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">13.8326005935669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7442893981934</t>
+    <t xml:space="preserve">13.7442903518677</t>
   </si>
   <si>
     <t xml:space="preserve">13.8486557006836</t>
@@ -3278,49 +3278,49 @@
     <t xml:space="preserve">13.5917539596558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8406286239624</t>
+    <t xml:space="preserve">13.8406276702881</t>
   </si>
   <si>
     <t xml:space="preserve">13.9690790176392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3704900741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3303489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2179536819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8727416992188</t>
+    <t xml:space="preserve">14.3704891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3303480148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2179546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8727407455444</t>
   </si>
   <si>
     <t xml:space="preserve">13.6479511260986</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2947101593018</t>
+    <t xml:space="preserve">13.2947092056274</t>
   </si>
   <si>
     <t xml:space="preserve">13.5114717483521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034437179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2465400695801</t>
+    <t xml:space="preserve">13.5034427642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2465410232544</t>
   </si>
   <si>
     <t xml:space="preserve">13.415132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3187952041626</t>
+    <t xml:space="preserve">13.3187942504883</t>
   </si>
   <si>
     <t xml:space="preserve">13.4071054458618</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1100606918335</t>
+    <t xml:space="preserve">13.1100616455078</t>
   </si>
   <si>
     <t xml:space="preserve">13.085976600647</t>
@@ -3332,28 +3332,28 @@
     <t xml:space="preserve">13.5756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6640071868896</t>
+    <t xml:space="preserve">13.6640090942383</t>
   </si>
   <si>
     <t xml:space="preserve">13.198371887207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0217504501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8611879348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7086515426636</t>
+    <t xml:space="preserve">13.0217514038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8611869812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7086505889893</t>
   </si>
   <si>
     <t xml:space="preserve">12.604284286499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0137224197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3589363098145</t>
+    <t xml:space="preserve">13.0137214660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3589353561401</t>
   </si>
   <si>
     <t xml:space="preserve">13.1261177062988</t>
@@ -3365,13 +3365,13 @@
     <t xml:space="preserve">12.6363964080811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9735803604126</t>
+    <t xml:space="preserve">12.9735822677612</t>
   </si>
   <si>
     <t xml:space="preserve">12.9093561172485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8772439956665</t>
+    <t xml:space="preserve">12.8772449493408</t>
   </si>
   <si>
     <t xml:space="preserve">13.1421747207642</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">13.7202053070068</t>
   </si>
   <si>
-    <t xml:space="preserve">14.009220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8807697296143</t>
+    <t xml:space="preserve">14.0092210769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8807706832886</t>
   </si>
   <si>
     <t xml:space="preserve">13.5596399307251</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">13.0940046310425</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9494953155518</t>
+    <t xml:space="preserve">12.9494972229004</t>
   </si>
   <si>
     <t xml:space="preserve">12.7487926483154</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">12.8852710723877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5240030288696</t>
+    <t xml:space="preserve">12.5240020751953</t>
   </si>
   <si>
     <t xml:space="preserve">12.6444253921509</t>
@@ -3449,10 +3449,10 @@
     <t xml:space="preserve">12.7969608306885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9334411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.804988861084</t>
+    <t xml:space="preserve">12.9334402084351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8049898147583</t>
   </si>
   <si>
     <t xml:space="preserve">12.9254131317139</t>
@@ -3470,22 +3470,22 @@
     <t xml:space="preserve">13.5837249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3268232345581</t>
+    <t xml:space="preserve">13.3268241882324</t>
   </si>
   <si>
     <t xml:space="preserve">13.2064008712769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2786540985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6845655441284</t>
+    <t xml:space="preserve">13.2786550521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6845664978027</t>
   </si>
   <si>
     <t xml:space="preserve">12.4838609695435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3393526077271</t>
+    <t xml:space="preserve">12.3393535614014</t>
   </si>
   <si>
     <t xml:space="preserve">12.5320301055908</t>
@@ -5406,6 +5406,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.1800003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3999996185303</t>
   </si>
 </sst>
 </file>
@@ -71004,7 +71007,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.6912962963</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>196214</v>
@@ -71025,6 +71028,32 @@
         <v>1797</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6915972222</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>112138</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>21.4799995422363</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>21.0400009155273</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>21.0799999237061</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>1798</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">8.61100769042969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30103778839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43742370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48082065582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61720848083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80319118499756</t>
+    <t xml:space="preserve">8.3010368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.437424659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48081970214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61720752716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80319023132324</t>
   </si>
   <si>
     <t xml:space="preserve">8.68540191650391</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">8.30723667144775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3506326675415</t>
+    <t xml:space="preserve">8.35063171386719</t>
   </si>
   <si>
     <t xml:space="preserve">8.20804500579834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.916672706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97246694564819</t>
+    <t xml:space="preserve">7.91667222976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97246742248535</t>
   </si>
   <si>
     <t xml:space="preserve">8.13985157012939</t>
@@ -86,94 +86,94 @@
     <t xml:space="preserve">8.15225028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27623748779297</t>
+    <t xml:space="preserve">8.2762393951416</t>
   </si>
   <si>
     <t xml:space="preserve">8.3878288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49321937561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50561714172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39402770996094</t>
+    <t xml:space="preserve">8.49321842193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50561809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39402866363525</t>
   </si>
   <si>
     <t xml:space="preserve">8.36923027038574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33203506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99106454849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59430170059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45791387557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31532859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46411323547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66869497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63149690628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65629482269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65009784698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44551515579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60050201416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68109321594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55090665817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6872935295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6067008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73688745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64389657974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57570457458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53230619430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01586246490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38162994384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67920207977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77219295501709</t>
+    <t xml:space="preserve">8.33203315734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99106645584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59430074691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45791482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31532764434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46411371231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66869354248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63149976730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65629577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65009689331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44551706314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.600501537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68109369277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55090618133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68729448318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60670042037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73688936233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64389705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57570314407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53230762481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0158634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38162803649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67920303344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77219486236572</t>
   </si>
   <si>
     <t xml:space="preserve">8.76599502563477</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">8.78459167480469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46842193603516</t>
+    <t xml:space="preserve">8.46842098236084</t>
   </si>
   <si>
     <t xml:space="preserve">8.41882610321045</t>
@@ -194,88 +194,88 @@
     <t xml:space="preserve">8.33823204040527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45602226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49942016601562</t>
+    <t xml:space="preserve">8.45602321624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49941921234131</t>
   </si>
   <si>
     <t xml:space="preserve">8.58621120452881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43122577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34443187713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4746208190918</t>
+    <t xml:space="preserve">8.43122673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40642738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34443283081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47462177276611</t>
   </si>
   <si>
     <t xml:space="preserve">8.24524211883545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90427350997925</t>
+    <t xml:space="preserve">7.90427255630493</t>
   </si>
   <si>
     <t xml:space="preserve">7.8732762336731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73069000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79268312454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85467863082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89807415008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96006917953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04685878753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99726486206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96626758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8670768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7802848815918</t>
+    <t xml:space="preserve">7.73068952560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79268360137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8546781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89807319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9600682258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04685974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99726438522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96626710891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86707735061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78028535842896</t>
   </si>
   <si>
     <t xml:space="preserve">8.09025573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11505317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17704772949219</t>
+    <t xml:space="preserve">8.1150541305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1770486831665</t>
   </si>
   <si>
     <t xml:space="preserve">8.02206230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88567352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82987976074219</t>
+    <t xml:space="preserve">7.88567447662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82988119125366</t>
   </si>
   <si>
     <t xml:space="preserve">8.0406608581543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00966453552246</t>
+    <t xml:space="preserve">8.00966358184814</t>
   </si>
   <si>
     <t xml:space="preserve">8.09645557403564</t>
@@ -284,67 +284,67 @@
     <t xml:space="preserve">8.19564628601074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23284339904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18324756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05925846099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76168727874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5261082649231</t>
+    <t xml:space="preserve">8.23284244537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18324851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05925941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76168823242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52610778808594</t>
   </si>
   <si>
     <t xml:space="preserve">7.56330442428589</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42071914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19133853912354</t>
+    <t xml:space="preserve">7.42071723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19133806228638</t>
   </si>
   <si>
     <t xml:space="preserve">6.85656929016113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96815919876099</t>
+    <t xml:space="preserve">6.96815967559814</t>
   </si>
   <si>
     <t xml:space="preserve">6.97435855865479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12314414978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09073781967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05184888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14259004592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05833101272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68240451812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37777471542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49444103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61110734939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08425664901733</t>
+    <t xml:space="preserve">7.12314462661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09073829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05184936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14258909225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05833053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6824049949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37777519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49444150924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61110877990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08425760269165</t>
   </si>
   <si>
     <t xml:space="preserve">6.99999713897705</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">7.03888654708862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93518114089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78610706329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370073318481</t>
+    <t xml:space="preserve">6.93518209457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78610801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370121002197</t>
   </si>
   <si>
     <t xml:space="preserve">6.82499647140503</t>
@@ -368,76 +368,76 @@
     <t xml:space="preserve">6.8638858795166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7407374382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91573858261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89629316329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15555238723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907121658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58333015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55740547180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0694408416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04351615905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01110649108887</t>
+    <t xml:space="preserve">6.74073791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91573810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92870140075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89629364013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15555191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58332967758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55740451812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06944179534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0435152053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01110744476318</t>
   </si>
   <si>
     <t xml:space="preserve">8.16666412353516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17962455749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07592296600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05647850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10184860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95277547836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82962703704834</t>
+    <t xml:space="preserve">8.17962551116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0759220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05647945404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10184764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95277404785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82962656021118</t>
   </si>
   <si>
     <t xml:space="preserve">7.87499666213989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90740394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481151580811</t>
+    <t xml:space="preserve">7.90740346908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481056213379</t>
   </si>
   <si>
     <t xml:space="preserve">7.75832986831665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74536752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7712926864624</t>
+    <t xml:space="preserve">7.7453670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77129125595093</t>
   </si>
   <si>
     <t xml:space="preserve">7.71944141387939</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">7.57684850692749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65462779998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70647811889648</t>
+    <t xml:space="preserve">7.65462636947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7064790725708</t>
   </si>
   <si>
     <t xml:space="preserve">7.81666421890259</t>
@@ -458,31 +458,31 @@
     <t xml:space="preserve">7.79073810577393</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69351434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72592258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69999694824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50555229187012</t>
+    <t xml:space="preserve">7.69351530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72592306137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69999742507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5055513381958</t>
   </si>
   <si>
     <t xml:space="preserve">7.37592315673828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39536666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32407140731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25277471542358</t>
+    <t xml:space="preserve">7.39536762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47314405441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32407093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25277280807495</t>
   </si>
   <si>
     <t xml:space="preserve">7.22684812545776</t>
@@ -497,37 +497,37 @@
     <t xml:space="preserve">7.22036743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18795967102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1685152053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16203498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19444179534912</t>
+    <t xml:space="preserve">7.18795919418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16851472854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16203355789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19444131851196</t>
   </si>
   <si>
     <t xml:space="preserve">7.1749963760376</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07129287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96758985519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04536771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9870343208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23333024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34999704360962</t>
+    <t xml:space="preserve">7.0712947845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96758890151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04536819458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98703384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23332977294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34999847412109</t>
   </si>
   <si>
     <t xml:space="preserve">7.41481161117554</t>
@@ -536,70 +536,70 @@
     <t xml:space="preserve">7.55092239379883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52499675750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64166307449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59629392623901</t>
+    <t xml:space="preserve">7.52499532699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64166259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59629344940186</t>
   </si>
   <si>
     <t xml:space="preserve">7.61573696136475</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64814472198486</t>
+    <t xml:space="preserve">7.64814519882202</t>
   </si>
   <si>
     <t xml:space="preserve">7.49258899688721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38888597488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46018123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36944150924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30462646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84444141387939</t>
+    <t xml:space="preserve">7.38888645172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46018266677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36944246292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30462694168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84444189071655</t>
   </si>
   <si>
     <t xml:space="preserve">6.57221984863281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5916633605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54629325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48147916793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43610858917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47823762893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52684879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64999723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53333044052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59814643859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52036809921265</t>
+    <t xml:space="preserve">6.59166383743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54629278182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48147821426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43610763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47823810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52684783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64999771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53332996368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59814548492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52036714553833</t>
   </si>
   <si>
     <t xml:space="preserve">6.42962694168091</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">6.87036800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10370063781738</t>
+    <t xml:space="preserve">7.10370111465454</t>
   </si>
   <si>
     <t xml:space="preserve">7.25925636291504</t>
@@ -617,19 +617,19 @@
     <t xml:space="preserve">7.48610877990723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43425607681274</t>
+    <t xml:space="preserve">7.43425559997559</t>
   </si>
   <si>
     <t xml:space="preserve">7.42777538299561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38240385055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51851463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51203393936157</t>
+    <t xml:space="preserve">7.38240432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851415634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51203346252441</t>
   </si>
   <si>
     <t xml:space="preserve">7.66758871078491</t>
@@ -638,43 +638,43 @@
     <t xml:space="preserve">7.68055295944214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71295928955078</t>
+    <t xml:space="preserve">7.71295881271362</t>
   </si>
   <si>
     <t xml:space="preserve">7.89444160461426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79721879959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84258937835693</t>
+    <t xml:space="preserve">7.79721927642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84259080886841</t>
   </si>
   <si>
     <t xml:space="preserve">7.34351491928101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40184783935547</t>
+    <t xml:space="preserve">7.40184879302979</t>
   </si>
   <si>
     <t xml:space="preserve">7.46666288375854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4083309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73888444900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68703126907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62221908569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63518238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73240423202515</t>
+    <t xml:space="preserve">7.40833044052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73888635635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68703269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6222186088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63518142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73240375518799</t>
   </si>
   <si>
     <t xml:space="preserve">7.77777481079102</t>
@@ -683,34 +683,34 @@
     <t xml:space="preserve">7.83610820770264</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75184774398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62870073318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97221851348877</t>
+    <t xml:space="preserve">7.7518482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6286997795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97221755981445</t>
   </si>
   <si>
     <t xml:space="preserve">7.85555171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9268479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03703308105469</t>
+    <t xml:space="preserve">7.92684745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.037034034729</t>
   </si>
   <si>
     <t xml:space="preserve">8.09536743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13425540924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20555114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2898120880127</t>
+    <t xml:space="preserve">8.13425636291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20555305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28981113433838</t>
   </si>
   <si>
     <t xml:space="preserve">8.24444007873535</t>
@@ -719,28 +719,28 @@
     <t xml:space="preserve">8.23147773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22499465942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27036762237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46481227874756</t>
+    <t xml:space="preserve">8.22499656677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27036571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46481132507324</t>
   </si>
   <si>
     <t xml:space="preserve">8.45832920074463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43240356445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42592239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35462665557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55555248260498</t>
+    <t xml:space="preserve">8.43240261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42592334747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35462760925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55555152893066</t>
   </si>
   <si>
     <t xml:space="preserve">8.52314472198486</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">8.60740375518799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6138858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6203670501709</t>
+    <t xml:space="preserve">8.61388492584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62036800384521</t>
   </si>
   <si>
     <t xml:space="preserve">8.56203460693359</t>
@@ -767,46 +767,46 @@
     <t xml:space="preserve">8.80832958221436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67870140075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81481075286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84073734283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92499732971191</t>
+    <t xml:space="preserve">8.6786994934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81481266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84073638916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9249963760376</t>
   </si>
   <si>
     <t xml:space="preserve">9.12592220306396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17777442932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00277423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95092105865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9962911605835</t>
+    <t xml:space="preserve">9.17777347564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00277328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95092296600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99629306793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.18425559997559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01573657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02869987487793</t>
+    <t xml:space="preserve">9.01573753356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02869892120361</t>
   </si>
   <si>
     <t xml:space="preserve">9.20369911193848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28147602081299</t>
+    <t xml:space="preserve">9.28147888183594</t>
   </si>
   <si>
     <t xml:space="preserve">9.30740451812744</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">9.34629154205322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43703365325928</t>
+    <t xml:space="preserve">9.43703269958496</t>
   </si>
   <si>
     <t xml:space="preserve">9.32684803009033</t>
@@ -827,19 +827,19 @@
     <t xml:space="preserve">9.38518142700195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41758823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33333015441895</t>
+    <t xml:space="preserve">9.41758728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33332920074463</t>
   </si>
   <si>
     <t xml:space="preserve">9.5018482208252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50832939147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44351387023926</t>
+    <t xml:space="preserve">9.50832843780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44351482391357</t>
   </si>
   <si>
     <t xml:space="preserve">9.54721832275391</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">9.35925388336182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51501655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41343402862549</t>
+    <t xml:space="preserve">9.51501750946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41343212127686</t>
   </si>
   <si>
     <t xml:space="preserve">9.59628391265869</t>
@@ -866,22 +866,22 @@
     <t xml:space="preserve">9.44729328155518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48115730285645</t>
+    <t xml:space="preserve">9.48115539550781</t>
   </si>
   <si>
     <t xml:space="preserve">9.21026515960693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09513759613037</t>
+    <t xml:space="preserve">9.09513664245605</t>
   </si>
   <si>
     <t xml:space="preserve">9.14931488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98678112030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83101940155029</t>
+    <t xml:space="preserve">8.98678207397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83102035522461</t>
   </si>
   <si>
     <t xml:space="preserve">8.84456443786621</t>
@@ -890,16 +890,16 @@
     <t xml:space="preserve">8.93937587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81070232391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93260192871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04095935821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87165355682373</t>
+    <t xml:space="preserve">8.81070327758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93260288238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04095840454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87165260314941</t>
   </si>
   <si>
     <t xml:space="preserve">9.04773139953613</t>
@@ -908,31 +908,31 @@
     <t xml:space="preserve">9.08159160614014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10190963745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10867977142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12222766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00709819793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07482051849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87842559814453</t>
+    <t xml:space="preserve">9.10190868377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10868072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12222576141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0070972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07481861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8784236907959</t>
   </si>
   <si>
     <t xml:space="preserve">8.92583084106445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90551376342773</t>
+    <t xml:space="preserve">8.90551471710205</t>
   </si>
   <si>
     <t xml:space="preserve">8.52626800537109</t>
@@ -941,31 +941,31 @@
     <t xml:space="preserve">8.58721923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54658317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56013011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68880176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53981304168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44500064849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33664417266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47208976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47886276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41114044189453</t>
+    <t xml:space="preserve">8.54658508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5601282119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68880271911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5398120880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44500160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33664512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47209072113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47886180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41113948822021</t>
   </si>
   <si>
     <t xml:space="preserve">8.42468357086182</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">8.38405132293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3908224105835</t>
+    <t xml:space="preserve">8.39082336425781</t>
   </si>
   <si>
     <t xml:space="preserve">8.32987213134766</t>
@@ -992,58 +992,58 @@
     <t xml:space="preserve">8.19442749023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16733932495117</t>
+    <t xml:space="preserve">8.16733837127686</t>
   </si>
   <si>
     <t xml:space="preserve">8.21474361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37050437927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29601097106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3975944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81747341156006</t>
+    <t xml:space="preserve">8.37050628662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29601001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39759540557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81747531890869</t>
   </si>
   <si>
     <t xml:space="preserve">8.97323703765869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76329708099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67525863647461</t>
+    <t xml:space="preserve">8.76329517364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67525768280029</t>
   </si>
   <si>
     <t xml:space="preserve">8.68202972412109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69557285308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80393028259277</t>
+    <t xml:space="preserve">8.69557476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80393123626709</t>
   </si>
   <si>
     <t xml:space="preserve">8.8581075668335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74298000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74975204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79038524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88519668579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96646499633789</t>
+    <t xml:space="preserve">8.74297904968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74975299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79038619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88519763946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96646404266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.91228580474854</t>
@@ -1058,25 +1058,25 @@
     <t xml:space="preserve">9.19672107696533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29153251647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24412727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36602783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40666103363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54210662841797</t>
+    <t xml:space="preserve">9.29153347015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24412631988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36602592468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40666007995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54210567474365</t>
   </si>
   <si>
     <t xml:space="preserve">9.46761035919189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38634395599365</t>
+    <t xml:space="preserve">9.38634300231934</t>
   </si>
   <si>
     <t xml:space="preserve">9.52178955078125</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">9.49470043182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84008502960205</t>
+    <t xml:space="preserve">9.84008407592773</t>
   </si>
   <si>
     <t xml:space="preserve">9.86717319488525</t>
@@ -1097,28 +1097,28 @@
     <t xml:space="preserve">9.83331394195557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76558971405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74527359008789</t>
+    <t xml:space="preserve">9.76559066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74527454376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.70464134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58273983001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71818447113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67077827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96875858306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94844150543213</t>
+    <t xml:space="preserve">9.58273887634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71818542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67077922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96875762939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94844055175781</t>
   </si>
   <si>
     <t xml:space="preserve">9.91457939147949</t>
@@ -1136,13 +1136,13 @@
     <t xml:space="preserve">9.90103530883789</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2599639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4451093673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5670099258423</t>
+    <t xml:space="preserve">10.2599649429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4451084136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.567008972168</t>
   </si>
   <si>
     <t xml:space="preserve">11.4857416152954</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">11.5128316879272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4518814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4383354187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4992876052856</t>
+    <t xml:space="preserve">11.4518804550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4383344650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4992866516113</t>
   </si>
   <si>
     <t xml:space="preserve">11.3502979278564</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">10.5850324630737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4495878219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5647172927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5443992614746</t>
+    <t xml:space="preserve">10.4495868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.564715385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5443983078003</t>
   </si>
   <si>
     <t xml:space="preserve">10.4292697906494</t>
@@ -1196,58 +1196,58 @@
     <t xml:space="preserve">10.4699039459229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.632438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8220615386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9168739318848</t>
+    <t xml:space="preserve">10.6324396133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.822060585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9168729782104</t>
   </si>
   <si>
     <t xml:space="preserve">10.9913673400879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8017444610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7204780578613</t>
+    <t xml:space="preserve">10.8017454147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7204790115356</t>
   </si>
   <si>
     <t xml:space="preserve">10.6256666183472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6730709075928</t>
+    <t xml:space="preserve">10.6730718612671</t>
   </si>
   <si>
     <t xml:space="preserve">10.8356065750122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9371900558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.998140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0455465316772</t>
+    <t xml:space="preserve">10.9371891021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9981412887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0455455780029</t>
   </si>
   <si>
     <t xml:space="preserve">11.1268138885498</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9304180145264</t>
+    <t xml:space="preserve">10.9304170608521</t>
   </si>
   <si>
     <t xml:space="preserve">10.842378616333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7746553421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7340230941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5918054580688</t>
+    <t xml:space="preserve">10.7746562957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7340240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5918045043945</t>
   </si>
   <si>
     <t xml:space="preserve">10.5376272201538</t>
@@ -1256,127 +1256,127 @@
     <t xml:space="preserve">10.5173101425171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3615484237671</t>
+    <t xml:space="preserve">10.3615474700928</t>
   </si>
   <si>
     <t xml:space="preserve">10.097430229187</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87394618988037</t>
+    <t xml:space="preserve">9.87394523620605</t>
   </si>
   <si>
     <t xml:space="preserve">10.1922426223755</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92812442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0364799499512</t>
+    <t xml:space="preserve">9.92812347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0364809036255</t>
   </si>
   <si>
     <t xml:space="preserve">10.0567970275879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1245203018188</t>
+    <t xml:space="preserve">10.1245183944702</t>
   </si>
   <si>
     <t xml:space="preserve">10.0838861465454</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97553062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69786643981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50824546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44052219390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6436882019043</t>
+    <t xml:space="preserve">9.97552967071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69786834716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50824356079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44052124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64368915557861</t>
   </si>
   <si>
     <t xml:space="preserve">9.66400623321533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67755031585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083927154541</t>
+    <t xml:space="preserve">9.67755126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083831787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.55565071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34571075439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21703624725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13576889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23058128356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06804943084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17640495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3321647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27798748016357</t>
+    <t xml:space="preserve">9.34570980072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21703720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13576984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23058223724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06804847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17640399932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33216667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27798843383789</t>
   </si>
   <si>
     <t xml:space="preserve">9.23735523223877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16285991668701</t>
+    <t xml:space="preserve">9.1628589630127</t>
   </si>
   <si>
     <t xml:space="preserve">9.29830455780029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42697811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53533363342285</t>
+    <t xml:space="preserve">9.42697620391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53533458709717</t>
   </si>
   <si>
     <t xml:space="preserve">9.62337207794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79945087432861</t>
+    <t xml:space="preserve">9.79945278167725</t>
   </si>
   <si>
     <t xml:space="preserve">9.80622386932373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77236270904541</t>
+    <t xml:space="preserve">9.77236366271973</t>
   </si>
   <si>
     <t xml:space="preserve">9.95521354675293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81976699829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75881767272949</t>
+    <t xml:space="preserve">9.81976890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75881862640381</t>
   </si>
   <si>
     <t xml:space="preserve">9.47438335418701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71141338348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30507659912109</t>
+    <t xml:space="preserve">9.71141242980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30507755279541</t>
   </si>
   <si>
     <t xml:space="preserve">9.01387023925781</t>
@@ -1385,40 +1385,40 @@
     <t xml:space="preserve">8.79715728759766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03418636322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39311599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26281452178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29120635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24151992797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11375713348389</t>
+    <t xml:space="preserve">9.03418731689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39311504364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26281547546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2912073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24152088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11375904083252</t>
   </si>
   <si>
     <t xml:space="preserve">9.14924812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05697536468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07117080688477</t>
+    <t xml:space="preserve">9.05697441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07116985321045</t>
   </si>
   <si>
     <t xml:space="preserve">9.03567981719971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99309349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04277801513672</t>
+    <t xml:space="preserve">8.99309253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04277896881104</t>
   </si>
   <si>
     <t xml:space="preserve">9.02148532867432</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">9.19183540344238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27700996398926</t>
+    <t xml:space="preserve">9.27701091766357</t>
   </si>
   <si>
     <t xml:space="preserve">9.39767551422119</t>
@@ -1436,25 +1436,25 @@
     <t xml:space="preserve">9.2131290435791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10665988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12795448303223</t>
+    <t xml:space="preserve">9.10666084289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12795352935791</t>
   </si>
   <si>
     <t xml:space="preserve">9.22732543945312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26991271972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12085723876953</t>
+    <t xml:space="preserve">9.2699146270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12085628509521</t>
   </si>
   <si>
     <t xml:space="preserve">9.17763900756836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38348007202148</t>
+    <t xml:space="preserve">9.3834810256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.44026374816895</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">9.41187191009521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60351657867432</t>
+    <t xml:space="preserve">9.603515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.70288753509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56092929840088</t>
+    <t xml:space="preserve">9.56092739105225</t>
   </si>
   <si>
     <t xml:space="preserve">9.61771202087402</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">9.53253650665283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45446014404297</t>
+    <t xml:space="preserve">9.45445823669434</t>
   </si>
   <si>
     <t xml:space="preserve">9.50414562225342</t>
@@ -1505,46 +1505,46 @@
     <t xml:space="preserve">9.28410816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24862003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0924654006958</t>
+    <t xml:space="preserve">9.24861907958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09246444702148</t>
   </si>
   <si>
     <t xml:space="preserve">8.82274341583252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71627330780029</t>
+    <t xml:space="preserve">8.71627235412598</t>
   </si>
   <si>
     <t xml:space="preserve">8.68078231811523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78725242614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97889614105225</t>
+    <t xml:space="preserve">8.78725433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97889709472656</t>
   </si>
   <si>
     <t xml:space="preserve">9.01438617706299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14214992523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23442268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3905782699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42606735229492</t>
+    <t xml:space="preserve">9.14214897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23442363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39057731628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42606830596924</t>
   </si>
   <si>
     <t xml:space="preserve">9.37638282775879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16344356536865</t>
+    <t xml:space="preserve">9.16344261169434</t>
   </si>
   <si>
     <t xml:space="preserve">9.04987621307373</t>
@@ -1559,13 +1559,13 @@
     <t xml:space="preserve">8.69497871398926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51043319702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48204135894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39686489105225</t>
+    <t xml:space="preserve">8.51043224334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48204040527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39686584472656</t>
   </si>
   <si>
     <t xml:space="preserve">8.59560775756836</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">8.49623680114746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26910305023193</t>
+    <t xml:space="preserve">8.26910209655762</t>
   </si>
   <si>
     <t xml:space="preserve">8.26200580596924</t>
@@ -1583,37 +1583,37 @@
     <t xml:space="preserve">8.22651481628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04196739196777</t>
+    <t xml:space="preserve">8.04196834564209</t>
   </si>
   <si>
     <t xml:space="preserve">8.06326293945312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07036113739014</t>
+    <t xml:space="preserve">8.07036018371582</t>
   </si>
   <si>
     <t xml:space="preserve">7.93549919128418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14843845367432</t>
+    <t xml:space="preserve">8.14843654632568</t>
   </si>
   <si>
     <t xml:space="preserve">8.16263389587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2407112121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28329944610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38267135620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36137676239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50333404541016</t>
+    <t xml:space="preserve">8.24071025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28329849243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38267040252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36137580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50333309173584</t>
   </si>
   <si>
     <t xml:space="preserve">8.42525672912598</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">9.08536624908447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06407165527344</t>
+    <t xml:space="preserve">9.06407260894775</t>
   </si>
   <si>
     <t xml:space="preserve">8.8085470199585</t>
@@ -1634,85 +1634,85 @@
     <t xml:space="preserve">8.81564521789551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65948963165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56011962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57431411743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44655132293701</t>
+    <t xml:space="preserve">8.65948867797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56011867523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57431507110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4465503692627</t>
   </si>
   <si>
     <t xml:space="preserve">8.52462863922119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5175313949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40396499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36847305297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43945407867432</t>
+    <t xml:space="preserve">8.51753044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40396308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36847400665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.439453125</t>
   </si>
   <si>
     <t xml:space="preserve">8.21231842041016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80144786834717</t>
+    <t xml:space="preserve">8.8014497756958</t>
   </si>
   <si>
     <t xml:space="preserve">8.60980319976807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34008312225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19812393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37557220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46074771881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62400054931641</t>
+    <t xml:space="preserve">8.3400821685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19812297821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37557315826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46074676513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62399959564209</t>
   </si>
   <si>
     <t xml:space="preserve">8.38976764678955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53172779083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68788146972656</t>
+    <t xml:space="preserve">8.5317268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68788051605225</t>
   </si>
   <si>
     <t xml:space="preserve">8.83693885803223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85823154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90791702270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25571632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51124286651611</t>
+    <t xml:space="preserve">8.85823345184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90791797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25571727752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5112419128418</t>
   </si>
   <si>
     <t xml:space="preserve">9.58222198486328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.475754737854</t>
+    <t xml:space="preserve">9.47575283050537</t>
   </si>
   <si>
     <t xml:space="preserve">9.35508918762207</t>
@@ -1721,52 +1721,52 @@
     <t xml:space="preserve">9.54673194885254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66739845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61061477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63190841674805</t>
+    <t xml:space="preserve">9.66739654541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61061382293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63190746307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.51834011077881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68869209289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90872764587402</t>
+    <t xml:space="preserve">9.68869113922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90872859954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.85904216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88033676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75967025756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86614036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85194301605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0222949981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2423315048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3275060653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.611424446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7604808807373</t>
+    <t xml:space="preserve">9.88033485412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75967121124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86613941192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85194396972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0222940444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2423324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.327507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6114225387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.760479927063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6398153305054</t>
@@ -1775,34 +1775,34 @@
     <t xml:space="preserve">10.6824035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6043252944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7107963562012</t>
+    <t xml:space="preserve">10.6043243408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7107954025269</t>
   </si>
   <si>
     <t xml:space="preserve">10.6895027160645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.774676322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7249898910522</t>
+    <t xml:space="preserve">10.7746772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7249917984009</t>
   </si>
   <si>
     <t xml:space="preserve">10.788872718811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.753381729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7391881942749</t>
+    <t xml:space="preserve">10.7533826828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7391872406006</t>
   </si>
   <si>
     <t xml:space="preserve">10.7178936004639</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6965990066528</t>
+    <t xml:space="preserve">10.6965999603271</t>
   </si>
   <si>
     <t xml:space="preserve">10.9166345596313</t>
@@ -1814,25 +1814,25 @@
     <t xml:space="preserve">11.3709049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4986667633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3141193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4418840408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4276866912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2999248504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1579647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9876155853271</t>
+    <t xml:space="preserve">11.4986658096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3141202926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4418830871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4276876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2999258041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1579666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9876146316528</t>
   </si>
   <si>
     <t xml:space="preserve">11.0018110275269</t>
@@ -1844,22 +1844,22 @@
     <t xml:space="preserve">11.3851003646851</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4134902954102</t>
+    <t xml:space="preserve">11.4134912490845</t>
   </si>
   <si>
     <t xml:space="preserve">11.484471321106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4702739715576</t>
+    <t xml:space="preserve">11.4702749252319</t>
   </si>
   <si>
     <t xml:space="preserve">11.6122341156006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5412549972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8535642623901</t>
+    <t xml:space="preserve">11.5412540435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8535652160645</t>
   </si>
   <si>
     <t xml:space="preserve">11.938738822937</t>
@@ -1868,37 +1868,37 @@
     <t xml:space="preserve">12.1090888977051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9813270568848</t>
+    <t xml:space="preserve">11.9813251495361</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677587509155</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251714706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7399969100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6832132339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7967805862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8961524963379</t>
+    <t xml:space="preserve">11.8251724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7399978637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6832122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.796781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8961515426636</t>
   </si>
   <si>
     <t xml:space="preserve">11.9103469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8393688201904</t>
+    <t xml:space="preserve">11.8393678665161</t>
   </si>
   <si>
     <t xml:space="preserve">11.8819551467896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8109760284424</t>
+    <t xml:space="preserve">11.8109750747681</t>
   </si>
   <si>
     <t xml:space="preserve">12.0665016174316</t>
@@ -1910,10 +1910,10 @@
     <t xml:space="preserve">12.2794399261475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3078327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3504190444946</t>
+    <t xml:space="preserve">12.3078336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3504209518433</t>
   </si>
   <si>
     <t xml:space="preserve">12.4355955123901</t>
@@ -1922,13 +1922,13 @@
     <t xml:space="preserve">12.5065755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5207691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5349655151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5917491912842</t>
+    <t xml:space="preserve">12.520770072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.534966468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5917501449585</t>
   </si>
   <si>
     <t xml:space="preserve">12.6627292633057</t>
@@ -1937,76 +1937,76 @@
     <t xml:space="preserve">12.6343364715576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7053174972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8161840438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.668360710144</t>
+    <t xml:space="preserve">12.7053165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8161849975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6683616638184</t>
   </si>
   <si>
     <t xml:space="preserve">12.6387968063354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3874998092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3727169036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3135871887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4466276168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8014030456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7274894714355</t>
+    <t xml:space="preserve">12.3874988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3727159500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.313588142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4466285705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.80140209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7274904251099</t>
   </si>
   <si>
     <t xml:space="preserve">12.5353202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5796670913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7422733306885</t>
+    <t xml:space="preserve">12.5796680450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7422723770142</t>
   </si>
   <si>
     <t xml:space="preserve">12.6831436157227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8753118515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7866182327271</t>
+    <t xml:space="preserve">12.8753128051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7866191864014</t>
   </si>
   <si>
     <t xml:space="preserve">12.7718381881714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8309669494629</t>
+    <t xml:space="preserve">12.8309659957886</t>
   </si>
   <si>
     <t xml:space="preserve">12.9344415664673</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6979274749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7127084732056</t>
+    <t xml:space="preserve">12.6979265213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7127094268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.5944499969482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9048757553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8457469940186</t>
+    <t xml:space="preserve">12.9048767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8457479476929</t>
   </si>
   <si>
     <t xml:space="preserve">12.8900957107544</t>
@@ -2015,25 +2015,25 @@
     <t xml:space="preserve">13.0674819946289</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1118268966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.052698135376</t>
+    <t xml:space="preserve">13.1118278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0526990890503</t>
   </si>
   <si>
     <t xml:space="preserve">12.9787874221802</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1413917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0970439910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0822639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.023136138916</t>
+    <t xml:space="preserve">13.1413927078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0970449447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0822649002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0231351852417</t>
   </si>
   <si>
     <t xml:space="preserve">12.9492235183716</t>
@@ -2045,37 +2045,37 @@
     <t xml:space="preserve">12.9935703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6092319488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8605298995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.550103187561</t>
+    <t xml:space="preserve">12.6092309951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8605308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5501022338867</t>
   </si>
   <si>
     <t xml:space="preserve">13.4518194198608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3335628509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.496166229248</t>
+    <t xml:space="preserve">13.3335609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4961652755737</t>
   </si>
   <si>
     <t xml:space="preserve">13.3483428955078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5405111312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9640073776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857395172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1709566116333</t>
+    <t xml:space="preserve">13.5405130386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9640064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857385635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.170955657959</t>
   </si>
   <si>
     <t xml:space="preserve">12.9196586608887</t>
@@ -2090,13 +2090,13 @@
     <t xml:space="preserve">13.2892141342163</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2448673248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1266098022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7622451782227</t>
+    <t xml:space="preserve">13.2448692321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1266107559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7622470855713</t>
   </si>
   <si>
     <t xml:space="preserve">13.9396324157715</t>
@@ -2105,28 +2105,28 @@
     <t xml:space="preserve">13.5552949905396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7474632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9691982269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.777027130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.629204750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.86572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9544153213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4666004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4813833236694</t>
+    <t xml:space="preserve">13.7474641799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9691963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7770261764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6292066574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8657236099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9544143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4666013717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4813842773438</t>
   </si>
   <si>
     <t xml:space="preserve">13.4370374679565</t>
@@ -2135,76 +2135,76 @@
     <t xml:space="preserve">13.7918090820312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9987630844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0578899383545</t>
+    <t xml:space="preserve">13.9987621307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0578908920288</t>
   </si>
   <si>
     <t xml:space="preserve">13.8213758468628</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6883344650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6587696075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144227981567</t>
+    <t xml:space="preserve">13.6883354187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6587705612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144237518311</t>
   </si>
   <si>
     <t xml:space="preserve">13.5257301330566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3631258010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2300863265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.88050365448</t>
+    <t xml:space="preserve">13.3631248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2300853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8805046081543</t>
   </si>
   <si>
     <t xml:space="preserve">14.4570093154907</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4717931747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6343955993652</t>
+    <t xml:space="preserve">14.471791267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6343946456909</t>
   </si>
   <si>
     <t xml:space="preserve">14.8191747665405</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0409088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300394058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0039539337158</t>
+    <t xml:space="preserve">15.0409078598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300413131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0039520263672</t>
   </si>
   <si>
     <t xml:space="preserve">15.3735065460205</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5582857131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9278402328491</t>
+    <t xml:space="preserve">15.5582847595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9278411865234</t>
   </si>
   <si>
     <t xml:space="preserve">16.1126194000244</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0387058258057</t>
+    <t xml:space="preserve">16.0387077331543</t>
   </si>
   <si>
     <t xml:space="preserve">15.7800197601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7061061859131</t>
+    <t xml:space="preserve">15.7061080932617</t>
   </si>
   <si>
     <t xml:space="preserve">15.6321954727173</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">15.5213289260864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4104633331299</t>
+    <t xml:space="preserve">15.4104642868042</t>
   </si>
   <si>
     <t xml:space="preserve">15.4474182128906</t>
@@ -2225,61 +2225,61 @@
     <t xml:space="preserve">15.262640953064</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8908853530884</t>
+    <t xml:space="preserve">15.8908863067627</t>
   </si>
   <si>
     <t xml:space="preserve">14.9669961929321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7378740310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8561296463013</t>
+    <t xml:space="preserve">14.7378721237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8561277389526</t>
   </si>
   <si>
     <t xml:space="preserve">14.4126634597778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0874547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3091869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5161380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5309219360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8257741928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4710025787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87452125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2145128250122</t>
+    <t xml:space="preserve">14.0874557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3091878890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5161371231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5309209823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8257751464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4710006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87452220916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2145118713379</t>
   </si>
   <si>
     <t xml:space="preserve">9.57887744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63800621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1649751663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29801464080811</t>
+    <t xml:space="preserve">9.63800716400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16497611999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29801559448242</t>
   </si>
   <si>
     <t xml:space="preserve">9.53453063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65278911590576</t>
+    <t xml:space="preserve">9.65279006958008</t>
   </si>
   <si>
     <t xml:space="preserve">10.5545043945312</t>
@@ -2288,10 +2288,10 @@
     <t xml:space="preserve">10.7023267745972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5988521575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9388427734375</t>
+    <t xml:space="preserve">10.5988512039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9388418197632</t>
   </si>
   <si>
     <t xml:space="preserve">10.7318916320801</t>
@@ -2300,40 +2300,40 @@
     <t xml:space="preserve">10.9018859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2123126983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0275354385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9905805587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0127534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0718822479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3157892227173</t>
+    <t xml:space="preserve">11.2123136520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0275344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9905786514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0127515792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0718812942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.315788269043</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353652954102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6801538467407</t>
+    <t xml:space="preserve">10.6801528930664</t>
   </si>
   <si>
     <t xml:space="preserve">10.7244997024536</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6505880355835</t>
+    <t xml:space="preserve">10.6505889892578</t>
   </si>
   <si>
     <t xml:space="preserve">10.5175476074219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9462337493896</t>
+    <t xml:space="preserve">10.9462327957153</t>
   </si>
   <si>
     <t xml:space="preserve">11.3749170303345</t>
@@ -2342,19 +2342,19 @@
     <t xml:space="preserve">11.2714414596558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5301313400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9735975265503</t>
+    <t xml:space="preserve">11.5301294326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.973596572876</t>
   </si>
   <si>
     <t xml:space="preserve">11.6040420532227</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2197036743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5153484344482</t>
+    <t xml:space="preserve">11.2197046279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5153474807739</t>
   </si>
   <si>
     <t xml:space="preserve">11.7370824813843</t>
@@ -2363,19 +2363,19 @@
     <t xml:space="preserve">12.128809928894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.431845664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5648851394653</t>
+    <t xml:space="preserve">12.4318447113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5648860931396</t>
   </si>
   <si>
     <t xml:space="preserve">12.3801078796387</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4392366409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4096736907959</t>
+    <t xml:space="preserve">12.4392356872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4096727371216</t>
   </si>
   <si>
     <t xml:space="preserve">12.7644453048706</t>
@@ -2387,22 +2387,22 @@
     <t xml:space="preserve">12.8235750198364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.971396446228</t>
+    <t xml:space="preserve">12.9713973999023</t>
   </si>
   <si>
     <t xml:space="preserve">13.6070327758789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8065929412842</t>
+    <t xml:space="preserve">13.8065948486328</t>
   </si>
   <si>
     <t xml:space="preserve">13.89528465271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0431070327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5331201553345</t>
+    <t xml:space="preserve">14.0431079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5331211090088</t>
   </si>
   <si>
     <t xml:space="preserve">13.473991394043</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">13.0600900650024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4887742996216</t>
+    <t xml:space="preserve">13.4887733459473</t>
   </si>
   <si>
     <t xml:space="preserve">13.2966051101685</t>
@@ -2429,25 +2429,25 @@
     <t xml:space="preserve">13.1353521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9962720870972</t>
+    <t xml:space="preserve">12.9962711334229</t>
   </si>
   <si>
     <t xml:space="preserve">13.1585330963135</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3980598449707</t>
+    <t xml:space="preserve">13.398060798645</t>
   </si>
   <si>
     <t xml:space="preserve">13.2048921585083</t>
   </si>
   <si>
-    <t xml:space="preserve">13.421238899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5448665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4444189071655</t>
+    <t xml:space="preserve">13.4212398529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5448656082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4444198608398</t>
   </si>
   <si>
     <t xml:space="preserve">13.5294122695923</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">13.0812654495239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.934458732605</t>
+    <t xml:space="preserve">12.9344577789307</t>
   </si>
   <si>
     <t xml:space="preserve">12.8108320236206</t>
@@ -2471,28 +2471,28 @@
     <t xml:space="preserve">12.9576387405396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2976112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1508045196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3362474441528</t>
+    <t xml:space="preserve">13.2976121902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1508054733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">13.1894388198853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7953786849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5944833755493</t>
+    <t xml:space="preserve">12.7953777313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944843292236</t>
   </si>
   <si>
     <t xml:space="preserve">12.7644720077515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3285188674927</t>
+    <t xml:space="preserve">13.328519821167</t>
   </si>
   <si>
     <t xml:space="preserve">13.2126188278198</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">13.4366912841797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6453123092651</t>
+    <t xml:space="preserve">13.6453132629395</t>
   </si>
   <si>
     <t xml:space="preserve">13.9312009811401</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">13.5062322616577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5216875076294</t>
+    <t xml:space="preserve">13.5216865539551</t>
   </si>
   <si>
     <t xml:space="preserve">13.5371398925781</t>
@@ -2519,13 +2519,13 @@
     <t xml:space="preserve">13.8539333343506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8230257034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8848400115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0702791213989</t>
+    <t xml:space="preserve">13.8230266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8848390579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0702781677246</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843923568726</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">13.6221323013306</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5989532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2744340896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4675989151001</t>
+    <t xml:space="preserve">13.598952293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2744331359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4675998687744</t>
   </si>
   <si>
     <t xml:space="preserve">13.7148532867432</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">13.5757732391357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3053388595581</t>
+    <t xml:space="preserve">13.3053398132324</t>
   </si>
   <si>
     <t xml:space="preserve">13.6298589706421</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">13.4753274917603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7921199798584</t>
+    <t xml:space="preserve">13.7921209335327</t>
   </si>
   <si>
     <t xml:space="preserve">13.5680456161499</t>
@@ -2573,40 +2573,40 @@
     <t xml:space="preserve">13.4830522537231</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8462057113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9234733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9543800354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5912275314331</t>
+    <t xml:space="preserve">13.8462076187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9234743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9543790817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5912265777588</t>
   </si>
   <si>
     <t xml:space="preserve">13.3671522140503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5525941848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7380323410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0007419586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8925657272339</t>
+    <t xml:space="preserve">13.5525932312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7380332946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0007400512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8925666809082</t>
   </si>
   <si>
     <t xml:space="preserve">13.9080209732056</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0780057907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9389276504517</t>
+    <t xml:space="preserve">14.0780067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9389266967773</t>
   </si>
   <si>
     <t xml:space="preserve">13.8616619110107</t>
@@ -2615,13 +2615,13 @@
     <t xml:space="preserve">13.8384799957275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0239200592041</t>
+    <t xml:space="preserve">14.0239191055298</t>
   </si>
   <si>
     <t xml:space="preserve">14.047101020813</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3329877853394</t>
+    <t xml:space="preserve">14.332986831665</t>
   </si>
   <si>
     <t xml:space="preserve">14.1861810684204</t>
@@ -2630,22 +2630,22 @@
     <t xml:space="preserve">14.1784543991089</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8152980804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6993989944458</t>
+    <t xml:space="preserve">13.8152990341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6994009017944</t>
   </si>
   <si>
     <t xml:space="preserve">13.3130655288696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2667064666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2898864746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3748769760132</t>
+    <t xml:space="preserve">13.2667055130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2898874282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3748788833618</t>
   </si>
   <si>
     <t xml:space="preserve">13.1662588119507</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">13.7766666412354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.761212348938</t>
+    <t xml:space="preserve">13.7612133026123</t>
   </si>
   <si>
     <t xml:space="preserve">13.7998466491699</t>
@@ -2666,85 +2666,85 @@
     <t xml:space="preserve">13.4907789230347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5139579772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0161924362183</t>
+    <t xml:space="preserve">13.5139589309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0161933898926</t>
   </si>
   <si>
     <t xml:space="preserve">13.6375865936279</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0426321029663</t>
+    <t xml:space="preserve">13.0426301956177</t>
   </si>
   <si>
     <t xml:space="preserve">12.8880987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8262853622437</t>
+    <t xml:space="preserve">12.826286315918</t>
   </si>
   <si>
     <t xml:space="preserve">12.8494653701782</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7567443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5867595672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6022119522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6253910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6872043609619</t>
+    <t xml:space="preserve">12.7567453384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5867586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6022109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.625391960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6872053146362</t>
   </si>
   <si>
     <t xml:space="preserve">12.8031053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9267320632935</t>
+    <t xml:space="preserve">12.9267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">13.1430788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3207931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4135141372681</t>
+    <t xml:space="preserve">13.3207921981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4135131835938</t>
   </si>
   <si>
     <t xml:space="preserve">13.4057865142822</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1817121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8417387008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8726444244385</t>
+    <t xml:space="preserve">13.1817111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.841739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8726453781128</t>
   </si>
   <si>
     <t xml:space="preserve">12.9190044403076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8571920394897</t>
+    <t xml:space="preserve">12.8571910858154</t>
   </si>
   <si>
     <t xml:space="preserve">12.6331186294556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721996307373</t>
+    <t xml:space="preserve">12.772198677063</t>
   </si>
   <si>
     <t xml:space="preserve">12.7490177154541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1971654891968</t>
+    <t xml:space="preserve">13.1971645355225</t>
   </si>
   <si>
     <t xml:space="preserve">13.096718788147</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">13.3439722061157</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821588516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9808177947998</t>
+    <t xml:space="preserve">13.2821598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9808168411255</t>
   </si>
   <si>
     <t xml:space="preserve">12.718111038208</t>
@@ -2768,19 +2768,19 @@
     <t xml:space="preserve">12.6408452987671</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6176643371582</t>
+    <t xml:space="preserve">12.6176652908325</t>
   </si>
   <si>
     <t xml:space="preserve">12.7103862762451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4554052352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8803730010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5603189468384</t>
+    <t xml:space="preserve">12.4554042816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8803720474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5603199005127</t>
   </si>
   <si>
     <t xml:space="preserve">13.6839466094971</t>
@@ -2792,25 +2792,25 @@
     <t xml:space="preserve">14.139820098877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3716201782227</t>
+    <t xml:space="preserve">14.371621131897</t>
   </si>
   <si>
     <t xml:space="preserve">14.4102535247803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5570611953735</t>
+    <t xml:space="preserve">14.5570621490479</t>
   </si>
   <si>
     <t xml:space="preserve">14.5338802337646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4025268554688</t>
+    <t xml:space="preserve">14.4025259017944</t>
   </si>
   <si>
     <t xml:space="preserve">14.2402677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2557210922241</t>
+    <t xml:space="preserve">14.2557220458984</t>
   </si>
   <si>
     <t xml:space="preserve">14.3948001861572</t>
@@ -2819,19 +2819,19 @@
     <t xml:space="preserve">14.5493335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9588470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1211080551147</t>
+    <t xml:space="preserve">14.9588489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1211061477661</t>
   </si>
   <si>
     <t xml:space="preserve">14.804313659668</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6343297958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7656812667847</t>
+    <t xml:space="preserve">14.6343288421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7656831741333</t>
   </si>
   <si>
     <t xml:space="preserve">14.7579545974731</t>
@@ -2843,25 +2843,25 @@
     <t xml:space="preserve">14.5261535644531</t>
   </si>
   <si>
-    <t xml:space="preserve">14.696141242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6420545578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5725154876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.603422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5956916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6575078964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8352212905884</t>
+    <t xml:space="preserve">14.6961421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.642053604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5725145339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6034212112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5956926345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6575059890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8352222442627</t>
   </si>
   <si>
     <t xml:space="preserve">14.9974813461304</t>
@@ -2873,19 +2873,19 @@
     <t xml:space="preserve">15.0824747085571</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0283880233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0979290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1751947402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2061014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747489929199</t>
+    <t xml:space="preserve">15.0283870697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0979299545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1751937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2061023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747470855713</t>
   </si>
   <si>
     <t xml:space="preserve">14.8506736755371</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">14.8661279678345</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9743003845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0592947006226</t>
+    <t xml:space="preserve">14.9742994308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0592937469482</t>
   </si>
   <si>
     <t xml:space="preserve">15.0052080154419</t>
@@ -2909,13 +2909,13 @@
     <t xml:space="preserve">15.1520147323608</t>
   </si>
   <si>
-    <t xml:space="preserve">15.414722442627</t>
+    <t xml:space="preserve">15.4147243499756</t>
   </si>
   <si>
     <t xml:space="preserve">15.8551435470581</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8087825775146</t>
+    <t xml:space="preserve">15.8087816238403</t>
   </si>
   <si>
     <t xml:space="preserve">15.6233425140381</t>
@@ -2930,40 +2930,40 @@
     <t xml:space="preserve">16.0714893341064</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9787702560425</t>
+    <t xml:space="preserve">15.9787683486938</t>
   </si>
   <si>
     <t xml:space="preserve">15.8860483169556</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9942226409912</t>
+    <t xml:space="preserve">15.9942216873169</t>
   </si>
   <si>
     <t xml:space="preserve">16.1796627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0560359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3496513366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4578227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2651481628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0564136505127</t>
+    <t xml:space="preserve">16.056037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3496494293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.457820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2651462554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0564117431641</t>
   </si>
   <si>
     <t xml:space="preserve">15.8476800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7834548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8717632293701</t>
+    <t xml:space="preserve">15.7834539413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8717641830444</t>
   </si>
   <si>
     <t xml:space="preserve">15.6871166229248</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">15.5586633682251</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6550025939941</t>
+    <t xml:space="preserve">15.6550035476685</t>
   </si>
   <si>
     <t xml:space="preserve">15.7192287445068</t>
@@ -2987,16 +2987,16 @@
     <t xml:space="preserve">16.1045818328857</t>
   </si>
   <si>
-    <t xml:space="preserve">15.598804473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5827484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.711199760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.727255821228</t>
+    <t xml:space="preserve">15.5988054275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827474594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7111988067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7272548675537</t>
   </si>
   <si>
     <t xml:space="preserve">15.5907773971558</t>
@@ -3011,19 +3011,19 @@
     <t xml:space="preserve">15.2616195678711</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4703550338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.663031578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8557071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7352867126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.911904335022</t>
+    <t xml:space="preserve">15.4703540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6630306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8557081222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7352848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9119052886963</t>
   </si>
   <si>
     <t xml:space="preserve">16.0162734985352</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">16.5381050109863</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6665554046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9876861572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0679683685303</t>
+    <t xml:space="preserve">16.6665573120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9876842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0679664611816</t>
   </si>
   <si>
     <t xml:space="preserve">16.9074020385742</t>
@@ -3059,19 +3059,19 @@
     <t xml:space="preserve">16.5702171325684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2330322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0724697113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4096565246582</t>
+    <t xml:space="preserve">16.2330341339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0724678039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4096546173096</t>
   </si>
   <si>
     <t xml:space="preserve">16.2009201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3133163452148</t>
+    <t xml:space="preserve">16.3133144378662</t>
   </si>
   <si>
     <t xml:space="preserve">16.1366958618164</t>
@@ -3083,25 +3083,25 @@
     <t xml:space="preserve">16.0885257720947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0483837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9841585159302</t>
+    <t xml:space="preserve">16.0483856201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9841613769531</t>
   </si>
   <si>
     <t xml:space="preserve">16.2812042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2972602844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1527538299561</t>
+    <t xml:space="preserve">16.2972583770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1527519226074</t>
   </si>
   <si>
     <t xml:space="preserve">15.8637361526489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.398099899292</t>
+    <t xml:space="preserve">15.3981008529663</t>
   </si>
   <si>
     <t xml:space="preserve">15.1090850830078</t>
@@ -3110,139 +3110,139 @@
     <t xml:space="preserve">14.916407585144</t>
   </si>
   <si>
-    <t xml:space="preserve">14.804012298584</t>
+    <t xml:space="preserve">14.8040142059326</t>
   </si>
   <si>
     <t xml:space="preserve">14.9806327819824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9886627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9645767211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7478151321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8923234939575</t>
+    <t xml:space="preserve">14.9886608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9645757675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7478170394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8923225402832</t>
   </si>
   <si>
     <t xml:space="preserve">14.8120422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9003505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8521814346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.101056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6755609512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.787956237793</t>
+    <t xml:space="preserve">14.900351524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8521823883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1010551452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6755638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7879571914673</t>
   </si>
   <si>
     <t xml:space="preserve">15.117112159729</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2375345230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0930271148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2937335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3900728225708</t>
+    <t xml:space="preserve">15.2375354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0930290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2937326431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3900709152222</t>
   </si>
   <si>
     <t xml:space="preserve">15.0609169006348</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0368309020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3419036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2535924911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1973943710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5345802307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1251411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769729614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1492261886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8441553115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076740264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6113367080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6595048904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1858415603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3062629699707</t>
+    <t xml:space="preserve">15.0368299484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3419027328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2535934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.197395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5345792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1251420974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769739151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1492252349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8441543579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076749801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6113376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6595058441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1858425140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.306263923645</t>
   </si>
   <si>
     <t xml:space="preserve">14.3544321060181</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5792226791382</t>
+    <t xml:space="preserve">14.5792245864868</t>
   </si>
   <si>
     <t xml:space="preserve">14.3464059829712</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3142919540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6996459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6193628311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5551385879517</t>
+    <t xml:space="preserve">14.3142929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6996469497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6193618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5551376342773</t>
   </si>
   <si>
     <t xml:space="preserve">14.5230255126953</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5471124649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273908615112</t>
+    <t xml:space="preserve">14.5471105575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273927688599</t>
   </si>
   <si>
     <t xml:space="preserve">14.8200693130493</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9244356155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5711946487427</t>
+    <t xml:space="preserve">14.9244365692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5711936950684</t>
   </si>
   <si>
     <t xml:space="preserve">14.3785181045532</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">14.225980758667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1617546081543</t>
+    <t xml:space="preserve">14.1617565155029</t>
   </si>
   <si>
     <t xml:space="preserve">14.0493621826172</t>
@@ -3260,19 +3260,19 @@
     <t xml:space="preserve">14.1938695907593</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8326005935669</t>
+    <t xml:space="preserve">13.8325996398926</t>
   </si>
   <si>
     <t xml:space="preserve">13.7442893981934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8486557006836</t>
+    <t xml:space="preserve">13.8486566543579</t>
   </si>
   <si>
     <t xml:space="preserve">13.8085165023804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5355558395386</t>
+    <t xml:space="preserve">13.5355567932129</t>
   </si>
   <si>
     <t xml:space="preserve">13.5917539596558</t>
@@ -3281,13 +3281,13 @@
     <t xml:space="preserve">13.8406286239624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9690790176392</t>
+    <t xml:space="preserve">13.9690799713135</t>
   </si>
   <si>
     <t xml:space="preserve">14.3704900741577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3303489685059</t>
+    <t xml:space="preserve">14.3303499221802</t>
   </si>
   <si>
     <t xml:space="preserve">14.2179536819458</t>
@@ -3296,16 +3296,16 @@
     <t xml:space="preserve">13.8727416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6479511260986</t>
+    <t xml:space="preserve">13.6479501724243</t>
   </si>
   <si>
     <t xml:space="preserve">13.2947101593018</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5114717483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5034437179565</t>
+    <t xml:space="preserve">13.5114707946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5034427642822</t>
   </si>
   <si>
     <t xml:space="preserve">13.2465400695801</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">13.4071054458618</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1100606918335</t>
+    <t xml:space="preserve">13.1100616455078</t>
   </si>
   <si>
     <t xml:space="preserve">13.085976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2224559783936</t>
+    <t xml:space="preserve">13.2224550247192</t>
   </si>
   <si>
     <t xml:space="preserve">13.5756969451904</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">13.0217504501343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8611879348755</t>
+    <t xml:space="preserve">12.8611869812012</t>
   </si>
   <si>
     <t xml:space="preserve">12.7086515426636</t>
@@ -3353,19 +3353,19 @@
     <t xml:space="preserve">13.0137224197388</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3589363098145</t>
+    <t xml:space="preserve">13.3589353561401</t>
   </si>
   <si>
     <t xml:space="preserve">13.1261177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8210458755493</t>
+    <t xml:space="preserve">12.8210468292236</t>
   </si>
   <si>
     <t xml:space="preserve">12.6363964080811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9735803604126</t>
+    <t xml:space="preserve">12.9735813140869</t>
   </si>
   <si>
     <t xml:space="preserve">12.9093561172485</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">13.1421747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2706260681152</t>
+    <t xml:space="preserve">13.2706251144409</t>
   </si>
   <si>
     <t xml:space="preserve">13.5516119003296</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">14.009220123291</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8807697296143</t>
+    <t xml:space="preserve">13.8807687759399</t>
   </si>
   <si>
     <t xml:space="preserve">13.5596399307251</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">13.5997819900513</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4231605529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3749923706055</t>
+    <t xml:space="preserve">13.4231615066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3027391433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3749914169312</t>
   </si>
   <si>
     <t xml:space="preserve">13.2304840087891</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">13.0940046310425</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9494953155518</t>
+    <t xml:space="preserve">12.9494962692261</t>
   </si>
   <si>
     <t xml:space="preserve">12.7487926483154</t>
@@ -3440,19 +3440,19 @@
     <t xml:space="preserve">12.8852710723877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5240030288696</t>
+    <t xml:space="preserve">12.5240020751953</t>
   </si>
   <si>
     <t xml:space="preserve">12.6444253921509</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7969608306885</t>
+    <t xml:space="preserve">12.7969617843628</t>
   </si>
   <si>
     <t xml:space="preserve">12.9334411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.804988861084</t>
+    <t xml:space="preserve">12.8049898147583</t>
   </si>
   <si>
     <t xml:space="preserve">12.9254131317139</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">13.2786540985107</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6845655441284</t>
+    <t xml:space="preserve">12.6845664978027</t>
   </si>
   <si>
     <t xml:space="preserve">12.4838609695435</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">12.5320301055908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1839199066162</t>
+    <t xml:space="preserve">12.1839189529419</t>
   </si>
   <si>
     <t xml:space="preserve">11.8018445968628</t>
@@ -3503,10 +3503,10 @@
     <t xml:space="preserve">11.9546747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3112773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1075048446655</t>
+    <t xml:space="preserve">12.3112764358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1075038909912</t>
   </si>
   <si>
     <t xml:space="preserve">12.158447265625</t>
@@ -3518,13 +3518,13 @@
     <t xml:space="preserve">11.9801454544067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2433519363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9461841583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9886360168457</t>
+    <t xml:space="preserve">12.2433528900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9461832046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.98863697052</t>
   </si>
   <si>
     <t xml:space="preserve">12.0141077041626</t>
@@ -3533,16 +3533,16 @@
     <t xml:space="preserve">12.0905227661133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9376935958862</t>
+    <t xml:space="preserve">11.9376945495605</t>
   </si>
   <si>
     <t xml:space="preserve">11.6150531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4792051315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556192398071</t>
+    <t xml:space="preserve">11.4792041778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556182861328</t>
   </si>
   <si>
     <t xml:space="preserve">11.6659955978394</t>
@@ -3551,16 +3551,16 @@
     <t xml:space="preserve">11.6575050354004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.750901222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339200973511</t>
+    <t xml:space="preserve">11.7509021759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339210510254</t>
   </si>
   <si>
     <t xml:space="preserve">11.8358068466187</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7593927383423</t>
+    <t xml:space="preserve">11.759391784668</t>
   </si>
   <si>
     <t xml:space="preserve">11.8867502212524</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">11.9631643295288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6744861602783</t>
+    <t xml:space="preserve">11.6744871139526</t>
   </si>
   <si>
     <t xml:space="preserve">11.5726003646851</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">11.5980710983276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5471296310425</t>
+    <t xml:space="preserve">11.5471286773682</t>
   </si>
   <si>
     <t xml:space="preserve">11.581090927124</t>
@@ -3590,13 +3590,13 @@
     <t xml:space="preserve">11.4707145690918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3688268661499</t>
+    <t xml:space="preserve">11.3688278198242</t>
   </si>
   <si>
     <t xml:space="preserve">11.343355178833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3009042739868</t>
+    <t xml:space="preserve">11.3009033203125</t>
   </si>
   <si>
     <t xml:space="preserve">11.2499599456787</t>
@@ -3605,13 +3605,13 @@
     <t xml:space="preserve">10.9358100891113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6386404037476</t>
+    <t xml:space="preserve">10.6386413574219</t>
   </si>
   <si>
     <t xml:space="preserve">10.6301507949829</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1461906433105</t>
+    <t xml:space="preserve">10.1461896896362</t>
   </si>
   <si>
     <t xml:space="preserve">10.044303894043</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">10.1886434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86600303649902</t>
+    <t xml:space="preserve">9.86600208282471</t>
   </si>
   <si>
     <t xml:space="preserve">9.71317291259766</t>
@@ -3632,16 +3632,16 @@
     <t xml:space="preserve">10.0612850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075103759766</t>
+    <t xml:space="preserve">10.3075113296509</t>
   </si>
   <si>
     <t xml:space="preserve">10.1716613769531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0697755813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91694641113281</t>
+    <t xml:space="preserve">10.0697746276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9169454574585</t>
   </si>
   <si>
     <t xml:space="preserve">10.0867567062378</t>
@@ -3659,28 +3659,28 @@
     <t xml:space="preserve">9.26317405700684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53487110137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2716646194458</t>
+    <t xml:space="preserve">9.53487205505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27166557312012</t>
   </si>
   <si>
     <t xml:space="preserve">9.45845699310303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74713516235352</t>
+    <t xml:space="preserve">9.7471342086792</t>
   </si>
   <si>
     <t xml:space="preserve">9.90845489501953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56034374237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4160041809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36506080627441</t>
+    <t xml:space="preserve">9.56034278869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41600513458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36506175994873</t>
   </si>
   <si>
     <t xml:space="preserve">9.49241924285889</t>
@@ -3698,10 +3698,10 @@
     <t xml:space="preserve">9.72166347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.027322769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1037368774414</t>
+    <t xml:space="preserve">10.0273237228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1037378311157</t>
   </si>
   <si>
     <t xml:space="preserve">10.1207189559937</t>
@@ -3710,19 +3710,19 @@
     <t xml:space="preserve">9.80656909942627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2395858764648</t>
+    <t xml:space="preserve">10.2395868301392</t>
   </si>
   <si>
     <t xml:space="preserve">10.6216602325439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.842414855957</t>
+    <t xml:space="preserve">10.8424139022827</t>
   </si>
   <si>
     <t xml:space="preserve">10.8593950271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8254337310791</t>
+    <t xml:space="preserve">10.8254327774048</t>
   </si>
   <si>
     <t xml:space="preserve">10.8678855895996</t>
@@ -3734,19 +3734,19 @@
     <t xml:space="preserve">10.774489402771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8169431686401</t>
+    <t xml:space="preserve">10.8169422149658</t>
   </si>
   <si>
     <t xml:space="preserve">11.0207147598267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0716590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2839212417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2754316329956</t>
+    <t xml:space="preserve">11.0716581344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2839221954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2754306793213</t>
   </si>
   <si>
     <t xml:space="preserve">11.4452409744263</t>
@@ -3770,28 +3770,28 @@
     <t xml:space="preserve">11.2584505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2924118041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1141109466553</t>
+    <t xml:space="preserve">11.2924127578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1141119003296</t>
   </si>
   <si>
     <t xml:space="preserve">11.1650543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2414693832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4197702407837</t>
+    <t xml:space="preserve">11.2414684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.419771194458</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858079910278</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3942995071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3603363037109</t>
+    <t xml:space="preserve">11.3942985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3603372573853</t>
   </si>
   <si>
     <t xml:space="preserve">11.0376958847046</t>
@@ -3803,25 +3803,25 @@
     <t xml:space="preserve">11.1226024627686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159976959229</t>
+    <t xml:space="preserve">11.2159986495972</t>
   </si>
   <si>
     <t xml:space="preserve">10.9697723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2244892120361</t>
+    <t xml:space="preserve">11.2244882583618</t>
   </si>
   <si>
     <t xml:space="preserve">11.4112796783447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.521656036377</t>
+    <t xml:space="preserve">11.5216569900513</t>
   </si>
   <si>
     <t xml:space="preserve">11.5386381149292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9716558456421</t>
+    <t xml:space="preserve">11.9716567993164</t>
   </si>
   <si>
     <t xml:space="preserve">12.1159944534302</t>
@@ -3845,13 +3845,13 @@
     <t xml:space="preserve">12.1329755783081</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2009000778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2263708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1414661407471</t>
+    <t xml:space="preserve">12.2008991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2263717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1414670944214</t>
   </si>
   <si>
     <t xml:space="preserve">12.0650510787964</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">11.7169399261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8188257217407</t>
+    <t xml:space="preserve">11.818826675415</t>
   </si>
   <si>
     <t xml:space="preserve">11.5641098022461</t>
@@ -3875,10 +3875,10 @@
     <t xml:space="preserve">10.9018487930298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5622253417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4263782501221</t>
+    <t xml:space="preserve">10.5622262954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4263772964478</t>
   </si>
   <si>
     <t xml:space="preserve">10.6556224822998</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">10.604679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8763771057129</t>
+    <t xml:space="preserve">10.8763761520386</t>
   </si>
   <si>
     <t xml:space="preserve">10.6895847320557</t>
@@ -3896,61 +3896,61 @@
     <t xml:space="preserve">10.9867525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914705276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8084506988525</t>
+    <t xml:space="preserve">10.7914714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8084516525269</t>
   </si>
   <si>
     <t xml:space="preserve">10.8509044647217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6980752944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6641139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320365905762</t>
+    <t xml:space="preserve">10.6980762481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6641130447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320375442505</t>
   </si>
   <si>
     <t xml:space="preserve">10.7999620437622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.012225151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3093929290771</t>
+    <t xml:space="preserve">11.0122261047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3093938827515</t>
   </si>
   <si>
     <t xml:space="preserve">11.0886402130127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3773183822632</t>
+    <t xml:space="preserve">11.3773174285889</t>
   </si>
   <si>
     <t xml:space="preserve">11.5046758651733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6320343017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5131664276123</t>
+    <t xml:space="preserve">11.6320333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5131673812866</t>
   </si>
   <si>
     <t xml:space="preserve">11.4622230529785</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6999588012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6829776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7678813934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8273162841797</t>
+    <t xml:space="preserve">11.6999578475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6829767227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7678833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.827317237854</t>
   </si>
   <si>
     <t xml:space="preserve">11.6374282836914</t>
@@ -3977,13 +3977,13 @@
     <t xml:space="preserve">10.877875328064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7331981658936</t>
+    <t xml:space="preserve">10.7331991195679</t>
   </si>
   <si>
     <t xml:space="preserve">10.8326635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8869180679321</t>
+    <t xml:space="preserve">10.8869171142578</t>
   </si>
   <si>
     <t xml:space="preserve">10.8507490158081</t>
@@ -3992,22 +3992,22 @@
     <t xml:space="preserve">10.6608600616455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3082103729248</t>
+    <t xml:space="preserve">10.3082113265991</t>
   </si>
   <si>
     <t xml:space="preserve">10.1544914245605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1454496383667</t>
+    <t xml:space="preserve">10.145450592041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3262958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3534231185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4167194366455</t>
+    <t xml:space="preserve">10.353422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4167184829712</t>
   </si>
   <si>
     <t xml:space="preserve">10.2539577484131</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">10.3805494308472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4890565872192</t>
+    <t xml:space="preserve">10.4890575408936</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
@@ -4034,10 +4034,10 @@
     <t xml:space="preserve">10.0098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0731115341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95556163787842</t>
+    <t xml:space="preserve">10.073112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95556259155273</t>
   </si>
   <si>
     <t xml:space="preserve">9.8560962677002</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">9.7114200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57578659057617</t>
+    <t xml:space="preserve">9.57578563690186</t>
   </si>
   <si>
     <t xml:space="preserve">9.34068584442139</t>
@@ -4061,7 +4061,7 @@
     <t xml:space="preserve">9.43110942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28643226623535</t>
+    <t xml:space="preserve">9.28643321990967</t>
   </si>
   <si>
     <t xml:space="preserve">9.26834774017334</t>
@@ -4070,28 +4070,28 @@
     <t xml:space="preserve">9.30451679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33164405822754</t>
+    <t xml:space="preserve">9.33164310455322</t>
   </si>
   <si>
     <t xml:space="preserve">9.52153205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72046184539795</t>
+    <t xml:space="preserve">9.72046279907227</t>
   </si>
   <si>
     <t xml:space="preserve">9.76567363739014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91035079956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91939353942871</t>
+    <t xml:space="preserve">9.91034984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91939258575439</t>
   </si>
   <si>
     <t xml:space="preserve">9.90130805969238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87418079376221</t>
+    <t xml:space="preserve">9.87418174743652</t>
   </si>
   <si>
     <t xml:space="preserve">9.82896995544434</t>
@@ -4127,10 +4127,10 @@
     <t xml:space="preserve">9.15984058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12367057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32260227203369</t>
+    <t xml:space="preserve">9.12367153167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32260131835938</t>
   </si>
   <si>
     <t xml:space="preserve">9.20505142211914</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">9.89226531982422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84705448150635</t>
+    <t xml:space="preserve">9.84705543518066</t>
   </si>
   <si>
     <t xml:space="preserve">10.0279006958008</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">10.0369424819946</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94651985168457</t>
+    <t xml:space="preserve">9.94651889801025</t>
   </si>
   <si>
     <t xml:space="preserve">10.1906623840332</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">10.4800148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5523529052734</t>
+    <t xml:space="preserve">10.5523538589478</t>
   </si>
   <si>
     <t xml:space="preserve">10.7151145935059</t>
@@ -4184,16 +4184,16 @@
     <t xml:space="preserve">10.4980993270874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2991695404053</t>
+    <t xml:space="preserve">10.299168586731</t>
   </si>
   <si>
     <t xml:space="preserve">10.2901268005371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.181619644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5704364776611</t>
+    <t xml:space="preserve">10.1816186904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5704374313354</t>
   </si>
   <si>
     <t xml:space="preserve">10.7603254318237</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">11.0768060684204</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2124404907227</t>
+    <t xml:space="preserve">11.2124395370483</t>
   </si>
   <si>
     <t xml:space="preserve">11.5560474395752</t>
@@ -4220,19 +4220,19 @@
     <t xml:space="preserve">11.2486085891724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6464700698853</t>
+    <t xml:space="preserve">11.6464710235596</t>
   </si>
   <si>
     <t xml:space="preserve">11.5289211273193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7188091278076</t>
+    <t xml:space="preserve">11.7188081741333</t>
   </si>
   <si>
     <t xml:space="preserve">11.9448661804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9629507064819</t>
+    <t xml:space="preserve">11.9629497528076</t>
   </si>
   <si>
     <t xml:space="preserve">11.9086971282959</t>
@@ -4247,10 +4247,10 @@
     <t xml:space="preserve">12.4783611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5054874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1528377532959</t>
+    <t xml:space="preserve">12.5054883956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1528387069702</t>
   </si>
   <si>
     <t xml:space="preserve">12.3155994415283</t>
@@ -4259,16 +4259,16 @@
     <t xml:space="preserve">12.1709232330322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1799650192261</t>
+    <t xml:space="preserve">12.1799659729004</t>
   </si>
   <si>
     <t xml:space="preserve">12.107626914978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2161350250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2703876495361</t>
+    <t xml:space="preserve">12.2161340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2703886032104</t>
   </si>
   <si>
     <t xml:space="preserve">12.4874038696289</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">12.650164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4693193435669</t>
+    <t xml:space="preserve">12.4693183898926</t>
   </si>
   <si>
     <t xml:space="preserve">12.595911026001</t>
@@ -4313,16 +4313,16 @@
     <t xml:space="preserve">12.8852643966675</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0751523971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932359695435</t>
+    <t xml:space="preserve">13.0751514434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932369232178</t>
   </si>
   <si>
     <t xml:space="preserve">13.0028142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2198295593262</t>
+    <t xml:space="preserve">13.2198286056519</t>
   </si>
   <si>
     <t xml:space="preserve">12.9304752349854</t>
@@ -4343,16 +4343,16 @@
     <t xml:space="preserve">12.6772918701172</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2613458633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5507001876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.577826499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4602766036987</t>
+    <t xml:space="preserve">12.2613468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5506992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5778255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4602756500244</t>
   </si>
   <si>
     <t xml:space="preserve">12.3517684936523</t>
@@ -4367,7 +4367,7 @@
     <t xml:space="preserve">12.4060230255127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3608112335205</t>
+    <t xml:space="preserve">12.3608121871948</t>
   </si>
   <si>
     <t xml:space="preserve">12.4241065979004</t>
@@ -4388,19 +4388,19 @@
     <t xml:space="preserve">13.5091819763184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2144804000854</t>
+    <t xml:space="preserve">14.2144813537598</t>
   </si>
   <si>
     <t xml:space="preserve">14.1963958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0788469314575</t>
+    <t xml:space="preserve">14.0788459777832</t>
   </si>
   <si>
     <t xml:space="preserve">13.8980007171631</t>
   </si>
   <si>
-    <t xml:space="preserve">13.979380607605</t>
+    <t xml:space="preserve">13.9793815612793</t>
   </si>
   <si>
     <t xml:space="preserve">14.0065078735352</t>
@@ -4421,16 +4421,16 @@
     <t xml:space="preserve">14.6485109329224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8474416732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5671300888062</t>
+    <t xml:space="preserve">14.8474407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5671310424805</t>
   </si>
   <si>
     <t xml:space="preserve">14.6846799850464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8022298812866</t>
+    <t xml:space="preserve">14.8022308349609</t>
   </si>
   <si>
     <t xml:space="preserve">14.7389326095581</t>
@@ -4445,10 +4445,10 @@
     <t xml:space="preserve">14.1511840820312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1873531341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3049030303955</t>
+    <t xml:space="preserve">14.1873540878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3049039840698</t>
   </si>
   <si>
     <t xml:space="preserve">13.9341697692871</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">14.1421422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2958612442017</t>
+    <t xml:space="preserve">14.295862197876</t>
   </si>
   <si>
     <t xml:space="preserve">14.4495801925659</t>
@@ -4478,13 +4478,13 @@
     <t xml:space="preserve">14.5490455627441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.874568939209</t>
+    <t xml:space="preserve">14.8745679855347</t>
   </si>
   <si>
     <t xml:space="preserve">14.7208499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6123418807983</t>
+    <t xml:space="preserve">14.612340927124</t>
   </si>
   <si>
     <t xml:space="preserve">14.6304264068604</t>
@@ -4499,10 +4499,10 @@
     <t xml:space="preserve">14.9649896621704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6575517654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8926515579224</t>
+    <t xml:space="preserve">14.6575527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8926525115967</t>
   </si>
   <si>
     <t xml:space="preserve">14.9740324020386</t>
@@ -4511,13 +4511,13 @@
     <t xml:space="preserve">15.082540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.471360206604</t>
+    <t xml:space="preserve">15.4713592529297</t>
   </si>
   <si>
     <t xml:space="preserve">15.191047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2633857727051</t>
+    <t xml:space="preserve">15.2633848190308</t>
   </si>
   <si>
     <t xml:space="preserve">15.1458368301392</t>
@@ -4529,16 +4529,16 @@
     <t xml:space="preserve">15.2995548248291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2000904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3718938827515</t>
+    <t xml:space="preserve">15.2000894546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3718948364258</t>
   </si>
   <si>
     <t xml:space="preserve">15.7245426177979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5527410507202</t>
+    <t xml:space="preserve">15.5527391433716</t>
   </si>
   <si>
     <t xml:space="preserve">15.6974172592163</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">15.4171047210693</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2905130386353</t>
+    <t xml:space="preserve">15.2905120849609</t>
   </si>
   <si>
     <t xml:space="preserve">15.0011596679688</t>
@@ -4565,10 +4565,10 @@
     <t xml:space="preserve">14.5128755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6665954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8112707138062</t>
+    <t xml:space="preserve">14.6665945053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8112716674805</t>
   </si>
   <si>
     <t xml:space="preserve">14.5054912567139</t>
@@ -4613,9 +4613,6 @@
     <t xml:space="preserve">15.2890548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8112716674805</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.8017158508301</t>
   </si>
   <si>
@@ -5436,6 +5433,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.6800003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6200008392334</t>
   </si>
 </sst>
 </file>
@@ -62264,7 +62264,7 @@
         <v>15.5</v>
       </c>
       <c r="G2173" t="s">
-        <v>1533</v>
+        <v>1518</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62290,7 +62290,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G2174" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62316,7 +62316,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G2175" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62342,7 +62342,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62368,7 +62368,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G2177" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62394,7 +62394,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G2178" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62420,7 +62420,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G2179" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62446,7 +62446,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G2180" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62472,7 +62472,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G2181" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62498,7 +62498,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G2182" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62524,7 +62524,7 @@
         <v>16.5</v>
       </c>
       <c r="G2183" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62550,7 +62550,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2184" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62576,7 +62576,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G2185" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62602,7 +62602,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G2186" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62628,7 +62628,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G2187" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62654,7 +62654,7 @@
         <v>16.25</v>
       </c>
       <c r="G2188" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62680,7 +62680,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G2189" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62706,7 +62706,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2190" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62732,7 +62732,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2191" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62758,7 +62758,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62784,7 +62784,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G2193" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62810,7 +62810,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G2194" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62836,7 +62836,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G2195" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62862,7 +62862,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G2196" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62888,7 +62888,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2197" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62914,7 +62914,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2198" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62940,7 +62940,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G2199" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62966,7 +62966,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2200" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62992,7 +62992,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G2201" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -63018,7 +63018,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G2202" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63044,7 +63044,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2203" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63070,7 +63070,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2204" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63096,7 +63096,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G2205" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63122,7 +63122,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2206" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63148,7 +63148,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G2207" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63174,7 +63174,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2208" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63200,7 +63200,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G2209" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63226,7 +63226,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2210" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63252,7 +63252,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2211" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63278,7 +63278,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G2212" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63304,7 +63304,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2213" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63330,7 +63330,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2214" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63356,7 +63356,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2215" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63382,7 +63382,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2216" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63408,7 +63408,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G2217" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63434,7 +63434,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G2218" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63460,7 +63460,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G2219" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63486,7 +63486,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2220" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63512,7 +63512,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2221" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63538,7 +63538,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G2222" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63564,7 +63564,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G2223" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63590,7 +63590,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2224" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63616,7 +63616,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G2225" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63642,7 +63642,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G2226" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63668,7 +63668,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G2227" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63694,7 +63694,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G2228" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63720,7 +63720,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2229" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63746,7 +63746,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G2230" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63772,7 +63772,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G2231" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63798,7 +63798,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2232" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63824,7 +63824,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G2233" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63850,7 +63850,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2234" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63876,7 +63876,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G2235" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63902,7 +63902,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G2236" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63928,7 +63928,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G2237" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63954,7 +63954,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2238" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63980,7 +63980,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G2239" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -64006,7 +64006,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2240" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64032,7 +64032,7 @@
         <v>17.75</v>
       </c>
       <c r="G2241" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64058,7 +64058,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2242" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64084,7 +64084,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2243" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64110,7 +64110,7 @@
         <v>18.5</v>
       </c>
       <c r="G2244" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64136,7 +64136,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G2245" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64162,7 +64162,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2246" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64188,7 +64188,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2247" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64214,7 +64214,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2248" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64240,7 +64240,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64266,7 +64266,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2250" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64292,7 +64292,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2251" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64318,7 +64318,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G2252" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64344,7 +64344,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G2253" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64370,7 +64370,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2254" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64396,7 +64396,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G2255" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64422,7 +64422,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G2256" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64448,7 +64448,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2257" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64474,7 +64474,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G2258" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64500,7 +64500,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2259" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64526,7 +64526,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2260" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64552,7 +64552,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2261" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64578,7 +64578,7 @@
         <v>17</v>
       </c>
       <c r="G2262" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64604,7 +64604,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64630,7 +64630,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G2264" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64656,7 +64656,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G2265" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64682,7 +64682,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2266" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64708,7 +64708,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G2267" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64734,7 +64734,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2268" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64760,7 +64760,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2269" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64786,7 +64786,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G2270" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64812,7 +64812,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G2271" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64838,7 +64838,7 @@
         <v>18</v>
       </c>
       <c r="G2272" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64864,7 +64864,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G2273" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64890,7 +64890,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G2274" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64916,7 +64916,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G2275" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64942,7 +64942,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G2276" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64968,7 +64968,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G2277" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64994,7 +64994,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2278" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -65020,7 +65020,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2279" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65046,7 +65046,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G2280" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65072,7 +65072,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G2281" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65098,7 +65098,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G2282" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65124,7 +65124,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2283" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65150,7 +65150,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2284" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65176,7 +65176,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G2285" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65202,7 +65202,7 @@
         <v>18.25</v>
       </c>
       <c r="G2286" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65228,7 +65228,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G2287" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65254,7 +65254,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2288" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65280,7 +65280,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G2289" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65306,7 +65306,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G2290" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65332,7 +65332,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G2291" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65358,7 +65358,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G2292" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65384,7 +65384,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G2293" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65410,7 +65410,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2294" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65436,7 +65436,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G2295" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65462,7 +65462,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G2296" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65488,7 +65488,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G2297" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65514,7 +65514,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2298" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65540,7 +65540,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G2299" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65566,7 +65566,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2300" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65592,7 +65592,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G2301" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65618,7 +65618,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2302" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65644,7 +65644,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G2303" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65670,7 +65670,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G2304" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65696,7 +65696,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G2305" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65722,7 +65722,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G2306" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65748,7 +65748,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65774,7 +65774,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G2308" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65800,7 +65800,7 @@
         <v>18.25</v>
       </c>
       <c r="G2309" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65826,7 +65826,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G2310" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65852,7 +65852,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G2311" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65878,7 +65878,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2312" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65904,7 +65904,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G2313" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65930,7 +65930,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2314" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65956,7 +65956,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G2315" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65982,7 +65982,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2316" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -66008,7 +66008,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2317" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66034,7 +66034,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G2318" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66060,7 +66060,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G2319" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66086,7 +66086,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G2320" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66112,7 +66112,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G2321" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66138,7 +66138,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G2322" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66164,7 +66164,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2323" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66190,7 +66190,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2324" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66216,7 +66216,7 @@
         <v>17.25</v>
       </c>
       <c r="G2325" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66242,7 +66242,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G2326" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66268,7 +66268,7 @@
         <v>17.25</v>
       </c>
       <c r="G2327" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66294,7 +66294,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66320,7 +66320,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G2329" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66346,7 +66346,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G2330" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66372,7 +66372,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G2331" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66398,7 +66398,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G2332" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66424,7 +66424,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G2333" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66450,7 +66450,7 @@
         <v>17</v>
       </c>
       <c r="G2334" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66476,7 +66476,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66502,7 +66502,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G2336" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66528,7 +66528,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G2337" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66554,7 +66554,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2338" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66580,7 +66580,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2339" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66606,7 +66606,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G2340" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66632,7 +66632,7 @@
         <v>17.75</v>
       </c>
       <c r="G2341" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66658,7 +66658,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G2342" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66684,7 +66684,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G2343" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66710,7 +66710,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G2344" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66736,7 +66736,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2345" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66762,7 +66762,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G2346" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66788,7 +66788,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66814,7 +66814,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G2348" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66840,7 +66840,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G2349" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66866,7 +66866,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G2350" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66892,7 +66892,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66918,7 +66918,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2352" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66944,7 +66944,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G2353" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66970,7 +66970,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G2354" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66996,7 +66996,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G2355" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67022,7 +67022,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G2356" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67048,7 +67048,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G2357" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67074,7 +67074,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2358" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67100,7 +67100,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G2359" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67126,7 +67126,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G2360" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67152,7 +67152,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2361" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67178,7 +67178,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G2362" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67204,7 +67204,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G2363" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67230,7 +67230,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G2364" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67256,7 +67256,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2365" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67282,7 +67282,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2366" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67308,7 +67308,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G2367" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67334,7 +67334,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G2368" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67360,7 +67360,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G2369" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67386,7 +67386,7 @@
         <v>20</v>
       </c>
       <c r="G2370" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67412,7 +67412,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2371" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67438,7 +67438,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2372" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67464,7 +67464,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G2373" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67490,7 +67490,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2374" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67516,7 +67516,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G2375" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67542,7 +67542,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G2376" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67568,7 +67568,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67594,7 +67594,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G2378" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67620,7 +67620,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G2379" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67646,7 +67646,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2380" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67672,7 +67672,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2381" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67698,7 +67698,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G2382" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67724,7 +67724,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G2383" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67750,7 +67750,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2384" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67776,7 +67776,7 @@
         <v>21.5</v>
       </c>
       <c r="G2385" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67802,7 +67802,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G2386" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67828,7 +67828,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G2387" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67854,7 +67854,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G2388" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67880,7 +67880,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G2389" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67906,7 +67906,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67932,7 +67932,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G2391" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67958,7 +67958,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G2392" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67984,7 +67984,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G2393" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68010,7 +68010,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G2394" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68036,7 +68036,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68062,7 +68062,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2396" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68088,7 +68088,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2397" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68114,7 +68114,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G2398" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68140,7 +68140,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G2399" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68166,7 +68166,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G2400" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68192,7 +68192,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G2401" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68218,7 +68218,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G2402" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68244,7 +68244,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2403" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68270,7 +68270,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2404" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68296,7 +68296,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G2405" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68322,7 +68322,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2406" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68348,7 +68348,7 @@
         <v>21.5</v>
       </c>
       <c r="G2407" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68374,7 +68374,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G2408" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68400,7 +68400,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G2409" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68426,7 +68426,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G2410" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68452,7 +68452,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G2411" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68478,7 +68478,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2412" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68504,7 +68504,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2413" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68530,7 +68530,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2414" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68556,7 +68556,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2415" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68582,7 +68582,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2416" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68608,7 +68608,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68634,7 +68634,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2418" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68660,7 +68660,7 @@
         <v>19.75</v>
       </c>
       <c r="G2419" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68686,7 +68686,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G2420" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68712,7 +68712,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G2421" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68738,7 +68738,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G2422" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68764,7 +68764,7 @@
         <v>19.25</v>
       </c>
       <c r="G2423" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68790,7 +68790,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G2424" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68816,7 +68816,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G2425" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68842,7 +68842,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G2426" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68868,7 +68868,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G2427" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68894,7 +68894,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2428" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68920,7 +68920,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G2429" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68946,7 +68946,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G2430" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68972,7 +68972,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -68998,7 +68998,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G2432" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69024,7 +69024,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2433" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69050,7 +69050,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2434" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69076,7 +69076,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G2435" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69102,7 +69102,7 @@
         <v>19.75</v>
       </c>
       <c r="G2436" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69128,7 +69128,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G2437" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69154,7 +69154,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G2438" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69180,7 +69180,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G2439" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69206,7 +69206,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G2440" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69232,7 +69232,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69258,7 +69258,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G2442" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69284,7 +69284,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2443" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69310,7 +69310,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G2444" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69336,7 +69336,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G2445" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69362,7 +69362,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2446" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69388,7 +69388,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G2447" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69414,7 +69414,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2448" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69440,7 +69440,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G2449" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69466,7 +69466,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G2450" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69492,7 +69492,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G2451" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69518,7 +69518,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G2452" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69544,7 +69544,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G2453" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69570,7 +69570,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G2454" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69596,7 +69596,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G2455" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -69622,7 +69622,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G2456" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69648,7 +69648,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G2457" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -69674,7 +69674,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G2458" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69700,7 +69700,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G2459" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69726,7 +69726,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G2460" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69752,7 +69752,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G2461" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69778,7 +69778,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G2462" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69804,7 +69804,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69830,7 +69830,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G2464" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69856,7 +69856,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G2465" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69882,7 +69882,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G2466" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69908,7 +69908,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2467" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69934,7 +69934,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G2468" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69960,7 +69960,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -69986,7 +69986,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G2470" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70012,7 +70012,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G2471" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70038,7 +70038,7 @@
         <v>19.25</v>
       </c>
       <c r="G2472" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70064,7 +70064,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70090,7 +70090,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G2474" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70116,7 +70116,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G2475" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70142,7 +70142,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G2476" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70168,7 +70168,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G2477" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70194,7 +70194,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G2478" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70220,7 +70220,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2479" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70246,7 +70246,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G2480" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70272,7 +70272,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70298,7 +70298,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G2482" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70324,7 +70324,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2483" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70350,7 +70350,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2484" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70376,7 +70376,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2485" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70402,7 +70402,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2486" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70428,7 +70428,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2487" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70454,7 +70454,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2488" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70480,7 +70480,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G2489" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70506,7 +70506,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G2490" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70532,7 +70532,7 @@
         <v>20.5</v>
       </c>
       <c r="G2491" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70558,7 +70558,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G2492" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -70584,7 +70584,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G2493" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -70610,7 +70610,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G2494" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -70636,7 +70636,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G2495" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -70662,7 +70662,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2496" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -70688,7 +70688,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2497" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -70714,7 +70714,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2498" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -70740,7 +70740,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G2499" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -70766,7 +70766,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G2500" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -70792,7 +70792,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2501" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -70818,7 +70818,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G2502" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -70844,7 +70844,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G2503" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -70870,7 +70870,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2504" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -70896,7 +70896,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2505" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -70922,7 +70922,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G2506" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -70948,7 +70948,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G2507" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -70974,7 +70974,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2508" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -71000,7 +71000,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G2509" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -71026,7 +71026,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G2510" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -71052,7 +71052,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G2511" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -71078,7 +71078,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2512" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -71104,7 +71104,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2513" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -71130,7 +71130,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G2514" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -71156,7 +71156,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2515" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -71182,7 +71182,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G2516" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -71208,7 +71208,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2517" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -71234,7 +71234,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2518" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -71260,7 +71260,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G2519" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -71286,7 +71286,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G2520" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -71312,7 +71312,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2521" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -71338,7 +71338,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G2522" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -71346,7 +71346,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.6911574074</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>54681</v>
@@ -71364,9 +71364,35 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G2523" t="s">
+        <v>1806</v>
+      </c>
+      <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.6912615741</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>46491</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>22.9799995422363</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>22.6399993896484</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>22.7999992370605</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>22.6200008392334</v>
+      </c>
+      <c r="G2524" t="s">
         <v>1807</v>
       </c>
-      <c r="H2523" t="s">
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">ACE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.611008644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3010368347168</t>
+    <t xml:space="preserve">8.61100769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30103778839111</t>
   </si>
   <si>
     <t xml:space="preserve">8.43742370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48082065582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61720848083496</t>
+    <t xml:space="preserve">8.48081970214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61720561981201</t>
   </si>
   <si>
     <t xml:space="preserve">8.80319023132324</t>
@@ -65,49 +65,49 @@
     <t xml:space="preserve">8.68540191650391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30723667144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3506326675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20804500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91667366027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97246789932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13985252380371</t>
+    <t xml:space="preserve">8.30723571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35063171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20804405212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91667222976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97246599197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13985157012939</t>
   </si>
   <si>
     <t xml:space="preserve">8.15224933624268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27623844146729</t>
+    <t xml:space="preserve">8.2762393951416</t>
   </si>
   <si>
     <t xml:space="preserve">8.3878288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49321842193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50561809539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39402866363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36922931671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33203315734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99106645584106</t>
+    <t xml:space="preserve">8.49321937561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50561904907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39402770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36923027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33203506469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99106454849243</t>
   </si>
   <si>
     <t xml:space="preserve">7.59430265426636</t>
@@ -116,58 +116,58 @@
     <t xml:space="preserve">7.45791387557983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31532764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46411418914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66869497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63149881362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65629625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65009641647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44551706314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.600501537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6810941696167</t>
+    <t xml:space="preserve">7.3153281211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46411275863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6686954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63149833679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65629577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65009784698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44551563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60050058364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68109321594238</t>
   </si>
   <si>
     <t xml:space="preserve">7.55090665817261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6872935295105</t>
+    <t xml:space="preserve">7.68729162216187</t>
   </si>
   <si>
     <t xml:space="preserve">7.60670137405396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73688840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64389801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5757040977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53230667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0158634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38162994384766</t>
+    <t xml:space="preserve">7.73688793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64389610290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57570457458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53230762481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01586246490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38162803649902</t>
   </si>
   <si>
     <t xml:space="preserve">8.67920207977295</t>
@@ -179,46 +179,46 @@
     <t xml:space="preserve">8.76599407196045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83418750762939</t>
+    <t xml:space="preserve">8.83418846130371</t>
   </si>
   <si>
     <t xml:space="preserve">8.784592628479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46842193603516</t>
+    <t xml:space="preserve">8.46842098236084</t>
   </si>
   <si>
     <t xml:space="preserve">8.41882610321045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33823299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45602226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49942016601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58621215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43122577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34443187713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4746208190918</t>
+    <t xml:space="preserve">8.33823490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45602321624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49941730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58621025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43122482299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40642738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34443283081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47461986541748</t>
   </si>
   <si>
     <t xml:space="preserve">8.24524211883545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90427350997925</t>
+    <t xml:space="preserve">7.90427255630493</t>
   </si>
   <si>
     <t xml:space="preserve">7.87327527999878</t>
@@ -227,52 +227,52 @@
     <t xml:space="preserve">7.73068904876709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79268407821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85467672348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89807510375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9600682258606</t>
+    <t xml:space="preserve">7.79268312454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8546781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89807462692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96006774902344</t>
   </si>
   <si>
     <t xml:space="preserve">8.04685974121094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99726581573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96626853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86707782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78028392791748</t>
+    <t xml:space="preserve">7.99726438522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96626710891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8670768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78028535842896</t>
   </si>
   <si>
     <t xml:space="preserve">8.09025573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1150541305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17704772949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02206134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88567447662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82987976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0406608581543</t>
+    <t xml:space="preserve">8.11505317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1770486831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02206230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88567495346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8298807144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04066276550293</t>
   </si>
   <si>
     <t xml:space="preserve">8.00966453552246</t>
@@ -281,109 +281,109 @@
     <t xml:space="preserve">8.09645557403564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19564723968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23284435272217</t>
+    <t xml:space="preserve">8.19564628601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23284244537354</t>
   </si>
   <si>
     <t xml:space="preserve">8.18324756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05925846099854</t>
+    <t xml:space="preserve">8.05926036834717</t>
   </si>
   <si>
     <t xml:space="preserve">7.76168537139893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5261082649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56330347061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4207181930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19133901596069</t>
+    <t xml:space="preserve">7.52610778808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56330442428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42071628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19133806228638</t>
   </si>
   <si>
     <t xml:space="preserve">6.85656976699829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96815872192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97435903549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12314414978027</t>
+    <t xml:space="preserve">6.96815967559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97435808181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12314653396606</t>
   </si>
   <si>
     <t xml:space="preserve">7.09073686599731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05184888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14259004592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05833101272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68240451812744</t>
+    <t xml:space="preserve">7.0518479347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14259099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05833053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6824049949646</t>
   </si>
   <si>
     <t xml:space="preserve">6.37777519226074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49444246292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61110782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08425760269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99999618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03888511657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93518257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78610801696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370073318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82499742507935</t>
+    <t xml:space="preserve">6.49444103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61110877990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08425617218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99999713897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03888654708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93518209457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78610754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82499647140503</t>
   </si>
   <si>
     <t xml:space="preserve">6.86388635635376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74073696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91573715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92870092391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89629411697388</t>
+    <t xml:space="preserve">6.74073648452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91573858261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92870044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89629459381104</t>
   </si>
   <si>
     <t xml:space="preserve">7.15555286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14907169342041</t>
+    <t xml:space="preserve">7.14907073974609</t>
   </si>
   <si>
     <t xml:space="preserve">7.5833306312561</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">8.10184860229492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95277452468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82962608337402</t>
+    <t xml:space="preserve">7.95277500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82962656021118</t>
   </si>
   <si>
     <t xml:space="preserve">7.87499666213989</t>
@@ -431,85 +431,85 @@
     <t xml:space="preserve">7.76481151580811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75833177566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74536752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77129364013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71944046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57684803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65462589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7064790725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81666421890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79073715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69351434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72592163085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69999694824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50555276870728</t>
+    <t xml:space="preserve">7.75832891464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74536561965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7712926864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71944141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57684850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65462636947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70647859573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81666469573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79073667526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69351577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72592258453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69999647140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50555181503296</t>
   </si>
   <si>
     <t xml:space="preserve">7.37592172622681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39536762237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47314405441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32407140731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25277423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22684907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18147802352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20092344284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22036790847778</t>
+    <t xml:space="preserve">7.39536619186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47314357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32407093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25277328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22684764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18147897720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20092248916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22036695480347</t>
   </si>
   <si>
     <t xml:space="preserve">7.18796014785767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16851615905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.162034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19444131851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1749963760376</t>
+    <t xml:space="preserve">7.1685152053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16203594207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19444227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17499732971191</t>
   </si>
   <si>
     <t xml:space="preserve">7.07129287719727</t>
@@ -518,46 +518,46 @@
     <t xml:space="preserve">6.96758937835693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04536628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98703384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23332929611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34999656677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41481113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55092287063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52499675750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64166355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5962929725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61573839187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64814424514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49258995056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3888840675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46018123626709</t>
+    <t xml:space="preserve">7.04536724090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98703289031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23332977294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34999561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41481161117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55092239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52499580383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64166259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59629249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6157374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64814567565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49258947372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38888597488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46018218994141</t>
   </si>
   <si>
     <t xml:space="preserve">7.36944055557251</t>
@@ -566,25 +566,25 @@
     <t xml:space="preserve">7.30462694168091</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84444284439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57222032546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59166431427002</t>
+    <t xml:space="preserve">6.84444189071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5722188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59166479110718</t>
   </si>
   <si>
     <t xml:space="preserve">6.54629421234131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48147821426392</t>
+    <t xml:space="preserve">6.48147916793823</t>
   </si>
   <si>
     <t xml:space="preserve">6.43610858917236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47823715209961</t>
+    <t xml:space="preserve">6.47823858261108</t>
   </si>
   <si>
     <t xml:space="preserve">6.52684831619263</t>
@@ -593,16 +593,16 @@
     <t xml:space="preserve">6.64999675750732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53333044052124</t>
+    <t xml:space="preserve">6.53332996368408</t>
   </si>
   <si>
     <t xml:space="preserve">6.59814596176147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52036809921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42962598800659</t>
+    <t xml:space="preserve">6.52036762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42962646484375</t>
   </si>
   <si>
     <t xml:space="preserve">6.87036800384521</t>
@@ -611,100 +611,100 @@
     <t xml:space="preserve">7.10370016098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25925588607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48610830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43425607681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42777442932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38240528106689</t>
+    <t xml:space="preserve">7.25925540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48610734939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4342565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42777490615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38240432739258</t>
   </si>
   <si>
     <t xml:space="preserve">7.51851511001587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51203441619873</t>
+    <t xml:space="preserve">7.51203346252441</t>
   </si>
   <si>
     <t xml:space="preserve">7.66758966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68055295944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71295928955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89444160461426</t>
+    <t xml:space="preserve">7.6805534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71296072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89444208145142</t>
   </si>
   <si>
     <t xml:space="preserve">7.79721879959106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84259033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34351491928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40184831619263</t>
+    <t xml:space="preserve">7.84258890151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34351444244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4018497467041</t>
   </si>
   <si>
     <t xml:space="preserve">7.46666288375854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40833139419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73888444900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68703508377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62221813201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63518190383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73240518569946</t>
+    <t xml:space="preserve">7.40833234786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73888540267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68703365325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6222186088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63518238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7324047088623</t>
   </si>
   <si>
     <t xml:space="preserve">7.7777738571167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83610725402832</t>
+    <t xml:space="preserve">7.83610773086548</t>
   </si>
   <si>
     <t xml:space="preserve">7.75184774398804</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62870073318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97221946716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85555171966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92684698104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.037034034729</t>
+    <t xml:space="preserve">7.62870121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97221803665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85555267333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9268479347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03703212738037</t>
   </si>
   <si>
     <t xml:space="preserve">8.09536647796631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13425540924072</t>
+    <t xml:space="preserve">8.13425636291504</t>
   </si>
   <si>
     <t xml:space="preserve">8.20555305480957</t>
@@ -713,64 +713,64 @@
     <t xml:space="preserve">8.28981113433838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24444007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147773742676</t>
+    <t xml:space="preserve">8.24444103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147678375244</t>
   </si>
   <si>
     <t xml:space="preserve">8.22499656677246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27036571502686</t>
+    <t xml:space="preserve">8.27036666870117</t>
   </si>
   <si>
     <t xml:space="preserve">8.46481132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45833015441895</t>
+    <t xml:space="preserve">8.45832920074463</t>
   </si>
   <si>
     <t xml:space="preserve">8.43240451812744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42592239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35462760925293</t>
+    <t xml:space="preserve">8.42592334747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3546257019043</t>
   </si>
   <si>
     <t xml:space="preserve">8.55555152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52314472198486</t>
+    <t xml:space="preserve">8.52314376831055</t>
   </si>
   <si>
     <t xml:space="preserve">8.39351463317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47129249572754</t>
+    <t xml:space="preserve">8.47129344940186</t>
   </si>
   <si>
     <t xml:space="preserve">8.60740375518799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6138858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62036609649658</t>
+    <t xml:space="preserve">8.61388492584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6203670501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.56203365325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80832958221436</t>
+    <t xml:space="preserve">8.80832862854004</t>
   </si>
   <si>
     <t xml:space="preserve">8.67870044708252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81481170654297</t>
+    <t xml:space="preserve">8.81481075286865</t>
   </si>
   <si>
     <t xml:space="preserve">8.84073734283447</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">8.9249963760376</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12592124938965</t>
+    <t xml:space="preserve">9.12592315673828</t>
   </si>
   <si>
     <t xml:space="preserve">9.17777347564697</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">9.00277423858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95092296600342</t>
+    <t xml:space="preserve">8.95092105865479</t>
   </si>
   <si>
     <t xml:space="preserve">8.99629211425781</t>
@@ -803,22 +803,22 @@
     <t xml:space="preserve">9.02869987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20369911193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2814769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30740356445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34629249572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43703365325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32684707641602</t>
+    <t xml:space="preserve">9.20370006561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28147792816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30740261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34629154205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43703269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32684898376465</t>
   </si>
   <si>
     <t xml:space="preserve">9.43055152893066</t>
@@ -827,25 +827,25 @@
     <t xml:space="preserve">9.38518047332764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41758918762207</t>
+    <t xml:space="preserve">9.41758823394775</t>
   </si>
   <si>
     <t xml:space="preserve">9.33332920074463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5018482208252</t>
+    <t xml:space="preserve">9.50184726715088</t>
   </si>
   <si>
     <t xml:space="preserve">9.50832939147949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44351482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54721736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41110706329346</t>
+    <t xml:space="preserve">9.44351387023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54721832275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41110801696777</t>
   </si>
   <si>
     <t xml:space="preserve">9.35925483703613</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">9.51501750946045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41343307495117</t>
+    <t xml:space="preserve">9.41343116760254</t>
   </si>
   <si>
     <t xml:space="preserve">9.59628391265869</t>
@@ -869,25 +869,25 @@
     <t xml:space="preserve">9.48115539550781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21026611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09513759613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14931583404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98678112030029</t>
+    <t xml:space="preserve">9.21026515960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09513854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14931488037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98678016662598</t>
   </si>
   <si>
     <t xml:space="preserve">8.83101940155029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84456348419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93937492370605</t>
+    <t xml:space="preserve">8.84456443786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93937587738037</t>
   </si>
   <si>
     <t xml:space="preserve">8.81070327758789</t>
@@ -896,46 +896,46 @@
     <t xml:space="preserve">8.93260288238525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04095840454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87165355682373</t>
+    <t xml:space="preserve">9.04096031188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87165260314941</t>
   </si>
   <si>
     <t xml:space="preserve">9.04773044586182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08159160614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10190963745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10868072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12222671508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0070972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07482147216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87842559814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92583179473877</t>
+    <t xml:space="preserve">9.08159255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10191059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349216461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10868167877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12222576141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00709819793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07481956481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8784236907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92583084106445</t>
   </si>
   <si>
     <t xml:space="preserve">8.90551376342773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52626705169678</t>
+    <t xml:space="preserve">8.52626800537109</t>
   </si>
   <si>
     <t xml:space="preserve">8.58721828460693</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">8.56012916564941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68880176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5398120880127</t>
+    <t xml:space="preserve">8.68880081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53981113433838</t>
   </si>
   <si>
     <t xml:space="preserve">8.44500064849854</t>
@@ -962,34 +962,34 @@
     <t xml:space="preserve">8.47208976745605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47886085510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41114044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4246826171875</t>
+    <t xml:space="preserve">8.47886180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4111385345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42468357086182</t>
   </si>
   <si>
     <t xml:space="preserve">8.3840503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39082336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32987308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2824649810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26892280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24860572814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19442844390869</t>
+    <t xml:space="preserve">8.3908224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32987213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28246593475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26892185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24860668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19442749023438</t>
   </si>
   <si>
     <t xml:space="preserve">8.16733932495117</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">8.21474456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37050533294678</t>
+    <t xml:space="preserve">8.37050628662109</t>
   </si>
   <si>
     <t xml:space="preserve">8.29601192474365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39759540557861</t>
+    <t xml:space="preserve">8.39759349822998</t>
   </si>
   <si>
     <t xml:space="preserve">8.81747531890869</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">8.97323703765869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76329612731934</t>
+    <t xml:space="preserve">8.76329708099365</t>
   </si>
   <si>
     <t xml:space="preserve">8.67525768280029</t>
@@ -1022,13 +1022,13 @@
     <t xml:space="preserve">8.68202972412109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69557476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80393028259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85810852050781</t>
+    <t xml:space="preserve">8.6955738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80393123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8581075668335</t>
   </si>
   <si>
     <t xml:space="preserve">8.74297904968262</t>
@@ -1037,25 +1037,25 @@
     <t xml:space="preserve">8.74975204467773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79038524627686</t>
+    <t xml:space="preserve">8.79038429260254</t>
   </si>
   <si>
     <t xml:space="preserve">8.88519668579102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96646404266357</t>
+    <t xml:space="preserve">8.96646308898926</t>
   </si>
   <si>
     <t xml:space="preserve">8.91228580474854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89197063446045</t>
+    <t xml:space="preserve">8.89196968078613</t>
   </si>
   <si>
     <t xml:space="preserve">9.18317699432373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19672203063965</t>
+    <t xml:space="preserve">9.19672107696533</t>
   </si>
   <si>
     <t xml:space="preserve">9.29153251647949</t>
@@ -1070,22 +1070,22 @@
     <t xml:space="preserve">9.40666103363037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54210662841797</t>
+    <t xml:space="preserve">9.54210567474365</t>
   </si>
   <si>
     <t xml:space="preserve">9.46761131286621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38634395599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52178859710693</t>
+    <t xml:space="preserve">9.38634490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52178955078125</t>
   </si>
   <si>
     <t xml:space="preserve">9.49470043182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84008598327637</t>
+    <t xml:space="preserve">9.84008502960205</t>
   </si>
   <si>
     <t xml:space="preserve">9.86717414855957</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">9.88749027252197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83331298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76559066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74527263641357</t>
+    <t xml:space="preserve">9.83331489562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76558876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74527454376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.70464038848877</t>
@@ -1109,34 +1109,34 @@
     <t xml:space="preserve">9.58273887634277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71818447113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67077732086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96875858306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94844150543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91457939147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0161638259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96198558807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92135334014893</t>
+    <t xml:space="preserve">9.71818351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67077827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96875762939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94844055175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91458129882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0161628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96198654174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92135238647461</t>
   </si>
   <si>
     <t xml:space="preserve">9.90103530883789</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2599649429321</t>
+    <t xml:space="preserve">10.2599658966064</t>
   </si>
   <si>
     <t xml:space="preserve">11.4451093673706</t>
@@ -1151,28 +1151,28 @@
     <t xml:space="preserve">11.5128307342529</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4518814086914</t>
+    <t xml:space="preserve">11.4518823623657</t>
   </si>
   <si>
     <t xml:space="preserve">11.4383363723755</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4992866516113</t>
+    <t xml:space="preserve">11.49928855896</t>
   </si>
   <si>
     <t xml:space="preserve">11.3502969741821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0726366043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9845962524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8762397766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1674461364746</t>
+    <t xml:space="preserve">11.0726356506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9845952987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.876238822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1674470901489</t>
   </si>
   <si>
     <t xml:space="preserve">10.8152904510498</t>
@@ -1184,37 +1184,37 @@
     <t xml:space="preserve">10.4495878219604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.564715385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5443992614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4292707443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4699039459229</t>
+    <t xml:space="preserve">10.5647163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5443983078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.429271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4699048995972</t>
   </si>
   <si>
     <t xml:space="preserve">10.632438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8220615386963</t>
+    <t xml:space="preserve">10.822060585022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9168739318848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9913682937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8017444610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7204790115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6256656646729</t>
+    <t xml:space="preserve">10.9913673400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8017454147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7204780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6256666183472</t>
   </si>
   <si>
     <t xml:space="preserve">10.6730728149414</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">10.8356065750122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9371900558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9981393814087</t>
+    <t xml:space="preserve">10.9371910095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.998140335083</t>
   </si>
   <si>
     <t xml:space="preserve">11.0455455780029</t>
@@ -1241,22 +1241,22 @@
     <t xml:space="preserve">10.8423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7746553421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7340230941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5918054580688</t>
+    <t xml:space="preserve">10.7746572494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7340211868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5918045043945</t>
   </si>
   <si>
     <t xml:space="preserve">10.5376272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5173101425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3615484237671</t>
+    <t xml:space="preserve">10.5173110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3615493774414</t>
   </si>
   <si>
     <t xml:space="preserve">10.097430229187</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">10.1922426223755</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92812442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0364809036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0567989349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1245183944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0838861465454</t>
+    <t xml:space="preserve">9.92812347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0364799499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0567970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1245203018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0838871002197</t>
   </si>
   <si>
     <t xml:space="preserve">9.97552967071533</t>
@@ -1289,43 +1289,43 @@
     <t xml:space="preserve">9.69786739349365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50824356079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44052219390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64368915557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66400718688965</t>
+    <t xml:space="preserve">9.50824451446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44052028656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64369010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66400623321533</t>
   </si>
   <si>
     <t xml:space="preserve">9.67755126953125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46083927154541</t>
+    <t xml:space="preserve">9.46083831787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.55565071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34570980072021</t>
+    <t xml:space="preserve">9.34571075439453</t>
   </si>
   <si>
     <t xml:space="preserve">9.21703720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13577079772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23058128356934</t>
+    <t xml:space="preserve">9.13576984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23058319091797</t>
   </si>
   <si>
     <t xml:space="preserve">9.06804847717285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17640495300293</t>
+    <t xml:space="preserve">9.17640399932861</t>
   </si>
   <si>
     <t xml:space="preserve">9.33216571807861</t>
@@ -1334,22 +1334,22 @@
     <t xml:space="preserve">9.27798843383789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23735523223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16285991668701</t>
+    <t xml:space="preserve">9.23735427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1628589630127</t>
   </si>
   <si>
     <t xml:space="preserve">9.29830455780029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42697620391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53533267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62337207794189</t>
+    <t xml:space="preserve">9.42697715759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53533458709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62337303161621</t>
   </si>
   <si>
     <t xml:space="preserve">9.79945182800293</t>
@@ -1358,22 +1358,22 @@
     <t xml:space="preserve">9.80622291564941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77236270904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95521354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81976795196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75881671905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47438335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71141242980957</t>
+    <t xml:space="preserve">9.77236175537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95521259307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81976890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75881767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4743824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71141147613525</t>
   </si>
   <si>
     <t xml:space="preserve">9.30507659912109</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">9.01387023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79715824127197</t>
+    <t xml:space="preserve">8.79715728759766</t>
   </si>
   <si>
     <t xml:space="preserve">9.03418636322021</t>
@@ -1394,40 +1394,40 @@
     <t xml:space="preserve">9.26281547546387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2912073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24152183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11375904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14924907684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697345733643</t>
+    <t xml:space="preserve">9.29120635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24152088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1137580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14924812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697536468506</t>
   </si>
   <si>
     <t xml:space="preserve">9.07116985321045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03568077087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99309253692627</t>
+    <t xml:space="preserve">9.03567981719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99309349060059</t>
   </si>
   <si>
     <t xml:space="preserve">9.04277801513672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02148532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19183540344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27700996398926</t>
+    <t xml:space="preserve">9.021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19183349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27701091766357</t>
   </si>
   <si>
     <t xml:space="preserve">9.39767551422119</t>
@@ -1439,10 +1439,10 @@
     <t xml:space="preserve">9.10665988922119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12795448303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22732543945312</t>
+    <t xml:space="preserve">9.12795257568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22732448577881</t>
   </si>
   <si>
     <t xml:space="preserve">9.26991271972656</t>
@@ -1451,28 +1451,28 @@
     <t xml:space="preserve">9.12085628509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17764091491699</t>
+    <t xml:space="preserve">9.17763900756836</t>
   </si>
   <si>
     <t xml:space="preserve">9.38348007202148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44026279449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41187191009521</t>
+    <t xml:space="preserve">9.44026470184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4118709564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.60351657867432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70288848876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56092929840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61771297454834</t>
+    <t xml:space="preserve">9.7028865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56092834472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61771202087402</t>
   </si>
   <si>
     <t xml:space="preserve">9.65320205688477</t>
@@ -1490,22 +1490,22 @@
     <t xml:space="preserve">9.53253746032715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45445823669434</t>
+    <t xml:space="preserve">9.45446014404297</t>
   </si>
   <si>
     <t xml:space="preserve">9.50414562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3054027557373</t>
+    <t xml:space="preserve">9.30540180206299</t>
   </si>
   <si>
     <t xml:space="preserve">9.34799098968506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28410911560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24861812591553</t>
+    <t xml:space="preserve">9.28410720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24861907958984</t>
   </si>
   <si>
     <t xml:space="preserve">9.09246444702148</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">8.8227424621582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71627330780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68078231811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78725242614746</t>
+    <t xml:space="preserve">8.71627235412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68078327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78725337982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.97889709472656</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">9.01438617706299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14214992523193</t>
+    <t xml:space="preserve">9.14214897155762</t>
   </si>
   <si>
     <t xml:space="preserve">9.23442363739014</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">9.29830551147461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39057636260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42606735229492</t>
+    <t xml:space="preserve">9.3905782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42606639862061</t>
   </si>
   <si>
     <t xml:space="preserve">9.37638187408447</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">9.16344261169434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04987716674805</t>
+    <t xml:space="preserve">9.04987525939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.17054176330566</t>
@@ -1559,46 +1559,46 @@
     <t xml:space="preserve">8.74466419219971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69498062133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51043319702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48204135894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39686584472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59560775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49623870849609</t>
+    <t xml:space="preserve">8.69497966766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51043224334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48204040527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39686489105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59560871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49623680114746</t>
   </si>
   <si>
     <t xml:space="preserve">8.26910305023193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26200485229492</t>
+    <t xml:space="preserve">8.26200580596924</t>
   </si>
   <si>
     <t xml:space="preserve">8.2265157699585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04196834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06326293945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07036018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9355001449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1484375</t>
+    <t xml:space="preserve">8.04196739196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06326198577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07036113739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93549966812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14843845367432</t>
   </si>
   <si>
     <t xml:space="preserve">8.16263389587402</t>
@@ -1616,28 +1616,28 @@
     <t xml:space="preserve">8.36137580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50333499908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42525672912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15634632110596</t>
+    <t xml:space="preserve">8.50333404541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42525768280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15634536743164</t>
   </si>
   <si>
     <t xml:space="preserve">9.08536624908447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06407356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8085470199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81564521789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65948867797852</t>
+    <t xml:space="preserve">9.06407260894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80854606628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81564426422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65948963165283</t>
   </si>
   <si>
     <t xml:space="preserve">8.56011962890625</t>
@@ -1649,31 +1649,31 @@
     <t xml:space="preserve">8.44655132293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52462959289551</t>
+    <t xml:space="preserve">8.52462863922119</t>
   </si>
   <si>
     <t xml:space="preserve">8.51753044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40396404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36847400665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43945407867432</t>
+    <t xml:space="preserve">8.40396308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36847305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.439453125</t>
   </si>
   <si>
     <t xml:space="preserve">8.21232032775879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80144882202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6098051071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34008312225342</t>
+    <t xml:space="preserve">8.80144786834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60980415344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3400821685791</t>
   </si>
   <si>
     <t xml:space="preserve">8.19812393188477</t>
@@ -1685,19 +1685,19 @@
     <t xml:space="preserve">8.46074676513672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62400054931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38976860046387</t>
+    <t xml:space="preserve">8.62399959564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38976669311523</t>
   </si>
   <si>
     <t xml:space="preserve">8.5317268371582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68788051605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83693885803223</t>
+    <t xml:space="preserve">8.68788242340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83693790435791</t>
   </si>
   <si>
     <t xml:space="preserve">8.85823059082031</t>
@@ -1706,25 +1706,25 @@
     <t xml:space="preserve">8.90791797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25571727752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51124382019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58222103118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47575283050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35508918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54673194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66739654541016</t>
+    <t xml:space="preserve">9.25571632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51124286651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5822229385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47575378417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35508823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54673290252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66739845275879</t>
   </si>
   <si>
     <t xml:space="preserve">9.61061382293701</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">9.63190841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51834011077881</t>
+    <t xml:space="preserve">9.51834106445312</t>
   </si>
   <si>
     <t xml:space="preserve">9.68869113922119</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">9.90872859954834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85904216766357</t>
+    <t xml:space="preserve">9.85904121398926</t>
   </si>
   <si>
     <t xml:space="preserve">9.88033485412598</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75967121124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86614036560059</t>
+    <t xml:space="preserve">9.75967025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86613845825195</t>
   </si>
   <si>
     <t xml:space="preserve">9.85194396972656</t>
@@ -1760,34 +1760,34 @@
     <t xml:space="preserve">10.0222940444946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2423315048218</t>
+    <t xml:space="preserve">10.2423324584961</t>
   </si>
   <si>
     <t xml:space="preserve">10.3275060653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6114225387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.760479927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6398143768311</t>
+    <t xml:space="preserve">10.611424446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7604808807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6398153305054</t>
   </si>
   <si>
     <t xml:space="preserve">10.6824035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6043272018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7107963562012</t>
+    <t xml:space="preserve">10.6043262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7107954025269</t>
   </si>
   <si>
     <t xml:space="preserve">10.6895008087158</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7746772766113</t>
+    <t xml:space="preserve">10.7746753692627</t>
   </si>
   <si>
     <t xml:space="preserve">10.7249908447266</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">10.7888717651367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7533826828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7391872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178936004639</t>
+    <t xml:space="preserve">10.7533836364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7391862869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178945541382</t>
   </si>
   <si>
     <t xml:space="preserve">10.6965990066528</t>
@@ -1814,16 +1814,16 @@
     <t xml:space="preserve">11.356707572937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3709030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4986658096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3141202926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4418840408325</t>
+    <t xml:space="preserve">11.3709049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.49866771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3141193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4418830871582</t>
   </si>
   <si>
     <t xml:space="preserve">11.4276876449585</t>
@@ -1835,10 +1835,10 @@
     <t xml:space="preserve">11.1579656600952</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9876146316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0018119812012</t>
+    <t xml:space="preserve">10.9876155853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0018110275269</t>
   </si>
   <si>
     <t xml:space="preserve">11.1863574981689</t>
@@ -1850,16 +1850,16 @@
     <t xml:space="preserve">11.4134912490845</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4844703674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4702739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6122341156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5412559509277</t>
+    <t xml:space="preserve">11.484471321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4702749252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6122350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5412540435791</t>
   </si>
   <si>
     <t xml:space="preserve">11.8535642623901</t>
@@ -1868,28 +1868,28 @@
     <t xml:space="preserve">11.938738822937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1090898513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9813251495361</t>
+    <t xml:space="preserve">12.1090888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9813270568848</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677587509155</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251724243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7399988174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6832132339478</t>
+    <t xml:space="preserve">11.8251714706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7399978637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6832122802734</t>
   </si>
   <si>
     <t xml:space="preserve">11.7967805862427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8961505889893</t>
+    <t xml:space="preserve">11.8961515426636</t>
   </si>
   <si>
     <t xml:space="preserve">11.9103488922119</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">11.8109750747681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0665006637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1942644119263</t>
+    <t xml:space="preserve">12.0665016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1942653656006</t>
   </si>
   <si>
     <t xml:space="preserve">12.2794399261475</t>
@@ -1919,10 +1919,10 @@
     <t xml:space="preserve">12.3504190444946</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4355945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5065755844116</t>
+    <t xml:space="preserve">12.4355955123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5065746307373</t>
   </si>
   <si>
     <t xml:space="preserve">12.520770072937</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">12.5917501449585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.66273021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6343383789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7053165435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.81618309021</t>
+    <t xml:space="preserve">12.6627311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6343364715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7053155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8161840438843</t>
   </si>
   <si>
     <t xml:space="preserve">12.668360710144</t>
@@ -1952,13 +1952,13 @@
     <t xml:space="preserve">12.6387968063354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3874979019165</t>
+    <t xml:space="preserve">12.3874998092651</t>
   </si>
   <si>
     <t xml:space="preserve">12.3727169036865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3135890960693</t>
+    <t xml:space="preserve">12.313588142395</t>
   </si>
   <si>
     <t xml:space="preserve">12.4466285705566</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">12.7422723770142</t>
   </si>
   <si>
-    <t xml:space="preserve">12.683141708374</t>
+    <t xml:space="preserve">12.6831426620483</t>
   </si>
   <si>
     <t xml:space="preserve">12.8753128051758</t>
@@ -1988,34 +1988,34 @@
     <t xml:space="preserve">12.7866172790527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7718362808228</t>
+    <t xml:space="preserve">12.7718381881714</t>
   </si>
   <si>
     <t xml:space="preserve">12.8309659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9344415664673</t>
+    <t xml:space="preserve">12.934440612793</t>
   </si>
   <si>
     <t xml:space="preserve">12.6979265213013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7127084732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5944499969482</t>
+    <t xml:space="preserve">12.7127075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944509506226</t>
   </si>
   <si>
     <t xml:space="preserve">12.9048757553101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8457479476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8900947570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0674810409546</t>
+    <t xml:space="preserve">12.8457469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8900957107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0674819946289</t>
   </si>
   <si>
     <t xml:space="preserve">13.1118288040161</t>
@@ -2024,25 +2024,25 @@
     <t xml:space="preserve">13.0526990890503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9787893295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.141393661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0970468521118</t>
+    <t xml:space="preserve">12.9787864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1413927078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0970449447632</t>
   </si>
   <si>
     <t xml:space="preserve">13.0822639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0231351852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9492235183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.156174659729</t>
+    <t xml:space="preserve">13.023136138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9492244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1561737060547</t>
   </si>
   <si>
     <t xml:space="preserve">12.9935693740845</t>
@@ -2051,13 +2051,13 @@
     <t xml:space="preserve">12.6092319488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8605298995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5501022338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4518194198608</t>
+    <t xml:space="preserve">12.8605289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5501041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4518203735352</t>
   </si>
   <si>
     <t xml:space="preserve">13.3335628509521</t>
@@ -2066,85 +2066,85 @@
     <t xml:space="preserve">13.496166229248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3483419418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5405130386353</t>
+    <t xml:space="preserve">13.3483438491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5405120849609</t>
   </si>
   <si>
     <t xml:space="preserve">12.9640064239502</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1857385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.170955657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.919659614563</t>
+    <t xml:space="preserve">13.1857404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1709566116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9196586608887</t>
   </si>
   <si>
     <t xml:space="preserve">13.2744312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2596492767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2892150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2448682785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1266107559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7622470855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9396343231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5552959442139</t>
+    <t xml:space="preserve">13.259651184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2892141342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2448663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1266098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9396324157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5552940368652</t>
   </si>
   <si>
     <t xml:space="preserve">13.7474641799927</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9691953659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.777027130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6292066574097</t>
+    <t xml:space="preserve">13.9691972732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7770280838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6292057037354</t>
   </si>
   <si>
     <t xml:space="preserve">13.8657197952271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9544134140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4665994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4813823699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4370355606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918090820312</t>
+    <t xml:space="preserve">13.9544124603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4666013717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4813842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4370374679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918100357056</t>
   </si>
   <si>
     <t xml:space="preserve">13.998761177063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0578908920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8213748931885</t>
+    <t xml:space="preserve">14.0578889846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8213758468628</t>
   </si>
   <si>
     <t xml:space="preserve">13.6883335113525</t>
@@ -2156,106 +2156,106 @@
     <t xml:space="preserve">13.6144218444824</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5257291793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3631267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2300853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.88050365448</t>
+    <t xml:space="preserve">13.5257301330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3631258010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2300834655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8805027008057</t>
   </si>
   <si>
     <t xml:space="preserve">14.457010269165</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4717931747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6343965530396</t>
+    <t xml:space="preserve">14.4717922210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6343946456909</t>
   </si>
   <si>
     <t xml:space="preserve">14.8191728591919</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0409078598022</t>
+    <t xml:space="preserve">15.0409097671509</t>
   </si>
   <si>
     <t xml:space="preserve">14.9300413131714</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039501190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3735074996948</t>
+    <t xml:space="preserve">15.0039510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3735084533691</t>
   </si>
   <si>
     <t xml:space="preserve">15.5582838058472</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9278411865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1126174926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0387096405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7800168991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6321964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5213308334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4104623794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4474172592163</t>
+    <t xml:space="preserve">15.9278402328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1126155853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0387077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7800207138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.706109046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6321973800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5213279724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4104642868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4474182128906</t>
   </si>
   <si>
     <t xml:space="preserve">15.2256851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">15.262640953064</t>
+    <t xml:space="preserve">15.2626399993896</t>
   </si>
   <si>
     <t xml:space="preserve">15.8908834457397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9669952392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7378711700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8561315536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4126625061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0874528884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3091869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5161380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5309190750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8257751464844</t>
+    <t xml:space="preserve">14.9669961929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7378721237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8561296463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4126644134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0874557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3091888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5161371231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5309200286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8257741928101</t>
   </si>
   <si>
     <t xml:space="preserve">11.4710025787354</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">9.87452125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2145137786865</t>
+    <t xml:space="preserve">10.2145128250122</t>
   </si>
   <si>
     <t xml:space="preserve">9.57887840270996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63800716400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16497611999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29801464080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53453159332275</t>
+    <t xml:space="preserve">9.63800621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16497421264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29801654815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53453063964844</t>
   </si>
   <si>
     <t xml:space="preserve">9.65278911590576</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">10.5545034408569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7023248672485</t>
+    <t xml:space="preserve">10.7023267745972</t>
   </si>
   <si>
     <t xml:space="preserve">10.5988502502441</t>
@@ -2297,31 +2297,31 @@
     <t xml:space="preserve">10.9388408660889</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7318916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9018859863281</t>
+    <t xml:space="preserve">10.7318906784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9018850326538</t>
   </si>
   <si>
     <t xml:space="preserve">11.2123126983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.027533531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9905786514282</t>
+    <t xml:space="preserve">11.0275354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9905796051025</t>
   </si>
   <si>
     <t xml:space="preserve">11.012752532959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0718812942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.315788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8353672027588</t>
+    <t xml:space="preserve">11.0718803405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3157892227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8353662490845</t>
   </si>
   <si>
     <t xml:space="preserve">10.6801528930664</t>
@@ -2333,13 +2333,13 @@
     <t xml:space="preserve">10.6505880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5175495147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.946234703064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3749179840088</t>
+    <t xml:space="preserve">10.5175485610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9462327957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3749170303345</t>
   </si>
   <si>
     <t xml:space="preserve">11.2714414596558</t>
@@ -2351,28 +2351,28 @@
     <t xml:space="preserve">11.9735975265503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.604040145874</t>
+    <t xml:space="preserve">11.6040420532227</t>
   </si>
   <si>
     <t xml:space="preserve">11.2197036743164</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5153484344482</t>
+    <t xml:space="preserve">11.5153493881226</t>
   </si>
   <si>
     <t xml:space="preserve">11.73708152771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.128809928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.431845664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5648851394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3801078796387</t>
+    <t xml:space="preserve">12.1288108825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4318466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5648860931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.380108833313</t>
   </si>
   <si>
     <t xml:space="preserve">12.4392366409302</t>
@@ -2381,22 +2381,22 @@
     <t xml:space="preserve">12.4096736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7644462585449</t>
+    <t xml:space="preserve">12.7644453048706</t>
   </si>
   <si>
     <t xml:space="preserve">12.8974866867065</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8235759735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9713954925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6070327758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8065938949585</t>
+    <t xml:space="preserve">12.8235750198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.971396446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6070318222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8065929412842</t>
   </si>
   <si>
     <t xml:space="preserve">13.89528465271</t>
@@ -2405,85 +2405,85 @@
     <t xml:space="preserve">14.0431079864502</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5331211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4739933013916</t>
+    <t xml:space="preserve">13.5331201553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4739923477173</t>
   </si>
   <si>
     <t xml:space="preserve">13.089653968811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0600891113281</t>
+    <t xml:space="preserve">13.0600910186768</t>
   </si>
   <si>
     <t xml:space="preserve">13.4887752532959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2966060638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2512512207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4521465301514</t>
+    <t xml:space="preserve">13.2966051101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2512521743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4521455764771</t>
   </si>
   <si>
     <t xml:space="preserve">13.1353521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9962711334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1585321426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3980579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2048921585083</t>
+    <t xml:space="preserve">12.9962720870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1585330963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.398060798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2048940658569</t>
   </si>
   <si>
     <t xml:space="preserve">13.4212398529053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.544867515564</t>
+    <t xml:space="preserve">13.5448656082153</t>
   </si>
   <si>
     <t xml:space="preserve">13.4444189071655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5294122695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3594274520874</t>
+    <t xml:space="preserve">13.5294132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3594255447388</t>
   </si>
   <si>
     <t xml:space="preserve">13.1276254653931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0812654495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.934458732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.810830116272</t>
+    <t xml:space="preserve">13.0812644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9344577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8108320236206</t>
   </si>
   <si>
     <t xml:space="preserve">12.9576387405396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2976112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1508073806763</t>
+    <t xml:space="preserve">13.2976131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.150806427002</t>
   </si>
   <si>
     <t xml:space="preserve">13.3362464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1894378662109</t>
+    <t xml:space="preserve">13.1894388198853</t>
   </si>
   <si>
     <t xml:space="preserve">12.7953777313232</t>
@@ -2492,22 +2492,22 @@
     <t xml:space="preserve">12.5944843292236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7644710540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3285188674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2126178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.436692237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6453123092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9311990737915</t>
+    <t xml:space="preserve">12.7644729614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.328519821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2126207351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4366912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6453132629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9312000274658</t>
   </si>
   <si>
     <t xml:space="preserve">13.5062322616577</t>
@@ -2519,37 +2519,37 @@
     <t xml:space="preserve">13.5371389389038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8539342880249</t>
+    <t xml:space="preserve">13.8539323806763</t>
   </si>
   <si>
     <t xml:space="preserve">13.8230266571045</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8848390579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0702781677246</t>
+    <t xml:space="preserve">13.8848400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0702800750732</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843933105469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.69167137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4289655685425</t>
+    <t xml:space="preserve">13.6916732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4289646148682</t>
   </si>
   <si>
     <t xml:space="preserve">13.6221323013306</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5989532470703</t>
+    <t xml:space="preserve">13.598952293396</t>
   </si>
   <si>
     <t xml:space="preserve">13.2744331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4675989151001</t>
+    <t xml:space="preserve">13.4675998687744</t>
   </si>
   <si>
     <t xml:space="preserve">13.7148532867432</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">13.5757732391357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3053379058838</t>
+    <t xml:space="preserve">13.3053388595581</t>
   </si>
   <si>
     <t xml:space="preserve">13.6298589706421</t>
@@ -2567,40 +2567,40 @@
     <t xml:space="preserve">13.4753255844116</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7921190261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5680465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4830532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8462066650391</t>
+    <t xml:space="preserve">13.7921209335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5680446624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4830513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8462057113647</t>
   </si>
   <si>
     <t xml:space="preserve">13.9234733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9543781280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5912275314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3671522140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5525932312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7380342483521</t>
+    <t xml:space="preserve">13.9543809890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5912256240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.367151260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5525922775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7380332946777</t>
   </si>
   <si>
     <t xml:space="preserve">14.0007400512695</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8925676345825</t>
+    <t xml:space="preserve">13.8925666809082</t>
   </si>
   <si>
     <t xml:space="preserve">13.9080190658569</t>
@@ -2609,22 +2609,22 @@
     <t xml:space="preserve">14.0780076980591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.938928604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8384799957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0239200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0471000671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3329858779907</t>
+    <t xml:space="preserve">13.9389276504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8616609573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8384790420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0239181518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.047101020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.332986831665</t>
   </si>
   <si>
     <t xml:space="preserve">14.1861810684204</t>
@@ -2633,43 +2633,43 @@
     <t xml:space="preserve">14.1784543991089</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8152990341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6993989944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3130664825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2667064666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2898864746094</t>
+    <t xml:space="preserve">13.815299987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6994009017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3130655288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2667055130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2898855209351</t>
   </si>
   <si>
     <t xml:space="preserve">13.3748779296875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1662588119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.776665687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.761212348938</t>
+    <t xml:space="preserve">13.166259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7766666412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7612142562866</t>
   </si>
   <si>
     <t xml:space="preserve">13.7998476028442</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5834989547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4907779693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5139579772949</t>
+    <t xml:space="preserve">13.5835008621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907789230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5139598846436</t>
   </si>
   <si>
     <t xml:space="preserve">14.0161924362183</t>
@@ -2684,10 +2684,10 @@
     <t xml:space="preserve">12.8880987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.826286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494653701782</t>
+    <t xml:space="preserve">12.8262853622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494644165039</t>
   </si>
   <si>
     <t xml:space="preserve">12.7567453384399</t>
@@ -2705,61 +2705,61 @@
     <t xml:space="preserve">12.6872053146362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031053543091</t>
+    <t xml:space="preserve">12.8031044006348</t>
   </si>
   <si>
     <t xml:space="preserve">12.9267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1430788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3207921981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4135141372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4057874679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1817111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.841739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8726453781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9190044403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8571910858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6331176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.772198677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7490186691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1971664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.096718788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3439722061157</t>
+    <t xml:space="preserve">13.1430797576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3207931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4135131835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4057865142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1817121505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8417387008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8726444244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9190053939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8571920394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6331186294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7721996307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7490177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1971645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0967197418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.34397315979</t>
   </si>
   <si>
     <t xml:space="preserve">13.2821598052979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9808187484741</t>
+    <t xml:space="preserve">12.9808177947998</t>
   </si>
   <si>
     <t xml:space="preserve">12.7181119918823</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">12.6408452987671</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6176652908325</t>
+    <t xml:space="preserve">12.6176643371582</t>
   </si>
   <si>
     <t xml:space="preserve">12.7103862762451</t>
@@ -2786,43 +2786,43 @@
     <t xml:space="preserve">13.5603179931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6839475631714</t>
+    <t xml:space="preserve">13.6839466094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.9621076583862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1398181915283</t>
+    <t xml:space="preserve">14.139820098877</t>
   </si>
   <si>
     <t xml:space="preserve">14.371621131897</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4102544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5570611953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5338802337646</t>
+    <t xml:space="preserve">14.4102535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5570602416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.533881187439</t>
   </si>
   <si>
     <t xml:space="preserve">14.4025259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2402677536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2557210922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3948001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5493354797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9588479995728</t>
+    <t xml:space="preserve">14.2402687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2557220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3947992324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5493335723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9588489532471</t>
   </si>
   <si>
     <t xml:space="preserve">15.1211080551147</t>
@@ -2831,52 +2831,52 @@
     <t xml:space="preserve">14.8043146133423</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6343269348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.765682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7579565048218</t>
+    <t xml:space="preserve">14.6343288421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7656812667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7579545974731</t>
   </si>
   <si>
     <t xml:space="preserve">14.6806879043579</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5261526107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.696141242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6420545578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5725154876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.603422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5956945419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6575050354004</t>
+    <t xml:space="preserve">14.5261545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6961402893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6420555114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5725126266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6034212112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5956926345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.657506942749</t>
   </si>
   <si>
     <t xml:space="preserve">14.8352222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.997483253479</t>
+    <t xml:space="preserve">14.9974813461304</t>
   </si>
   <si>
     <t xml:space="preserve">15.1983766555786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0824766159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0283889770508</t>
+    <t xml:space="preserve">15.0824756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0283880233765</t>
   </si>
   <si>
     <t xml:space="preserve">15.0979290008545</t>
@@ -2888,58 +2888,58 @@
     <t xml:space="preserve">15.2061033248901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0747470855713</t>
+    <t xml:space="preserve">15.0747489929199</t>
   </si>
   <si>
     <t xml:space="preserve">14.8506736755371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8661270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9743003845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0592947006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0052070617676</t>
+    <t xml:space="preserve">14.8661289215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9743022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0592937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0052080154419</t>
   </si>
   <si>
     <t xml:space="preserve">14.9279413223267</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1520175933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4147233963013</t>
+    <t xml:space="preserve">15.1520147323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.414722442627</t>
   </si>
   <si>
     <t xml:space="preserve">15.8551435470581</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8087825775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6233425140381</t>
+    <t xml:space="preserve">15.808783531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6233406066895</t>
   </si>
   <si>
     <t xml:space="preserve">15.7624235153198</t>
   </si>
   <si>
-    <t xml:space="preserve">15.916955947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0714893341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9787693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8860473632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9942245483398</t>
+    <t xml:space="preserve">15.9169588088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0714874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9787683486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8860483169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9942235946655</t>
   </si>
   <si>
     <t xml:space="preserve">16.1796627044678</t>
@@ -2948,25 +2948,25 @@
     <t xml:space="preserve">16.056037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3496513366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4578227996826</t>
+    <t xml:space="preserve">16.3496494293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.457820892334</t>
   </si>
   <si>
     <t xml:space="preserve">16.2651462554932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0564117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8476800918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7834548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8717651367188</t>
+    <t xml:space="preserve">16.0564136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8476781845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7834539413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8717641830444</t>
   </si>
   <si>
     <t xml:space="preserve">15.6871166229248</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">15.6469745635986</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5586633682251</t>
+    <t xml:space="preserve">15.5586652755737</t>
   </si>
   <si>
     <t xml:space="preserve">15.6550025939941</t>
@@ -2987,49 +2987,49 @@
     <t xml:space="preserve">15.7673969268799</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1045837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5988063812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5827503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.711199760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7272577285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5907754898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5104951858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.213451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2616214752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4703550338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6630296707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8557090759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7352848052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9119062423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0162734985352</t>
+    <t xml:space="preserve">16.1045818328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5988054275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827493667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7112007141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7272548675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5907773971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5104942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2134532928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2616195678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4703559875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6630325317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8557081222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7352828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9119052886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0162715911865</t>
   </si>
   <si>
     <t xml:space="preserve">15.7754259109497</t>
@@ -3038,40 +3038,40 @@
     <t xml:space="preserve">15.9921875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2490882873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3454284667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5381050109863</t>
+    <t xml:space="preserve">16.2490901947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3454303741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.538106918335</t>
   </si>
   <si>
     <t xml:space="preserve">16.6665573120117</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9876861572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0679683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9074039459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.570219039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2330341339111</t>
+    <t xml:space="preserve">16.9876842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0679664611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9074020385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5702171325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2330322265625</t>
   </si>
   <si>
     <t xml:space="preserve">16.0724697113037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4096565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2009181976318</t>
+    <t xml:space="preserve">16.4096546173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2009220123291</t>
   </si>
   <si>
     <t xml:space="preserve">16.3133144378662</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">16.1366958618164</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3293724060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0885276794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0483837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9841585159302</t>
+    <t xml:space="preserve">16.3293704986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0885257720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0483856201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9841594696045</t>
   </si>
   <si>
     <t xml:space="preserve">16.2812042236328</t>
@@ -3098,37 +3098,37 @@
     <t xml:space="preserve">16.2972583770752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1527519226074</t>
+    <t xml:space="preserve">16.1527538299561</t>
   </si>
   <si>
     <t xml:space="preserve">15.8637361526489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.398099899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1090831756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9164066314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8040132522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9806327819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9886617660522</t>
+    <t xml:space="preserve">15.3981008529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1090850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.916407585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8040142059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9806346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9886627197266</t>
   </si>
   <si>
     <t xml:space="preserve">14.9645757675171</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7478151321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8923215866089</t>
+    <t xml:space="preserve">14.7478170394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8923225402832</t>
   </si>
   <si>
     <t xml:space="preserve">14.8120422363281</t>
@@ -3140,25 +3140,25 @@
     <t xml:space="preserve">14.8521823883057</t>
   </si>
   <si>
-    <t xml:space="preserve">15.101056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6755628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.787956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1171140670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2375364303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0930271148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2937335968018</t>
+    <t xml:space="preserve">15.1010570526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6755619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7879571914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.117112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2375354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0930290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2937326431274</t>
   </si>
   <si>
     <t xml:space="preserve">15.3900709152222</t>
@@ -3167,67 +3167,67 @@
     <t xml:space="preserve">15.0609149932861</t>
   </si>
   <si>
-    <t xml:space="preserve">15.036828994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3419036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2535924911499</t>
+    <t xml:space="preserve">15.0368299484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3419027328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2535915374756</t>
   </si>
   <si>
     <t xml:space="preserve">15.197395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5345783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1251411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769729614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1492261886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8441534042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076740264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6113367080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6595058441162</t>
+    <t xml:space="preserve">15.5345792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1251401901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769720077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1492252349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8441543579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076749801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6113376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6595048904419</t>
   </si>
   <si>
     <t xml:space="preserve">14.1858406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3062629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3544321060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5792245864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3464069366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3142919540405</t>
+    <t xml:space="preserve">14.3062648773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3544330596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5792226791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3464059829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3142929077148</t>
   </si>
   <si>
     <t xml:space="preserve">14.6996469497681</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6193618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5551385879517</t>
+    <t xml:space="preserve">14.61936378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5551376342773</t>
   </si>
   <si>
     <t xml:space="preserve">14.5230255126953</t>
@@ -3242,61 +3242,61 @@
     <t xml:space="preserve">14.8200693130493</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9244356155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5711946487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3785181045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.225980758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1617555618286</t>
+    <t xml:space="preserve">14.9244365692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5711936950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3785171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2259817123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1617565155029</t>
   </si>
   <si>
     <t xml:space="preserve">14.0493621826172</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1938695907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8326005935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7442903518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8486557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8085165023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5355558395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5917539596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406276702881</t>
+    <t xml:space="preserve">14.193868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.744291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8486566543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8085155487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5917530059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406286239624</t>
   </si>
   <si>
     <t xml:space="preserve">13.9690790176392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3704891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3303480148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2179546356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8727407455444</t>
+    <t xml:space="preserve">14.3704881668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3303499221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2179536819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8727416992188</t>
   </si>
   <si>
     <t xml:space="preserve">13.6479511260986</t>
@@ -3308,40 +3308,40 @@
     <t xml:space="preserve">13.5114717483521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034427642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2465410232544</t>
+    <t xml:space="preserve">13.5034437179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2465400695801</t>
   </si>
   <si>
     <t xml:space="preserve">13.415132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3187942504883</t>
+    <t xml:space="preserve">13.3187952041626</t>
   </si>
   <si>
     <t xml:space="preserve">13.4071054458618</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1100616455078</t>
+    <t xml:space="preserve">13.1100606918335</t>
   </si>
   <si>
     <t xml:space="preserve">13.085976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2224559783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5756969451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6640090942383</t>
+    <t xml:space="preserve">13.2224550247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5756978988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.664008140564</t>
   </si>
   <si>
     <t xml:space="preserve">13.198371887207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0217514038086</t>
+    <t xml:space="preserve">13.0217504501343</t>
   </si>
   <si>
     <t xml:space="preserve">12.8611869812012</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">12.604284286499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0137214660645</t>
+    <t xml:space="preserve">13.0137224197388</t>
   </si>
   <si>
     <t xml:space="preserve">13.3589353561401</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">12.9093561172485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8772449493408</t>
+    <t xml:space="preserve">12.8772439956665</t>
   </si>
   <si>
     <t xml:space="preserve">13.1421747207642</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">13.2706260681152</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5516119003296</t>
+    <t xml:space="preserve">13.5516128540039</t>
   </si>
   <si>
     <t xml:space="preserve">13.383020401001</t>
@@ -3395,31 +3395,31 @@
     <t xml:space="preserve">13.4392175674438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3509073257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7202053070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0092210769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8807706832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5596399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5997819900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4231605529785</t>
+    <t xml:space="preserve">13.3509063720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7202062606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0092191696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8807687759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5596408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5997829437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4231615066528</t>
   </si>
   <si>
     <t xml:space="preserve">13.3027381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3749923706055</t>
+    <t xml:space="preserve">13.3749914169312</t>
   </si>
   <si>
     <t xml:space="preserve">13.2304840087891</t>
@@ -3428,16 +3428,16 @@
     <t xml:space="preserve">13.0297794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.102032661438</t>
+    <t xml:space="preserve">13.1020317077637</t>
   </si>
   <si>
     <t xml:space="preserve">13.0940046310425</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9494972229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7487926483154</t>
+    <t xml:space="preserve">12.9494962692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7487916946411</t>
   </si>
   <si>
     <t xml:space="preserve">12.8852710723877</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">12.6444253921509</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7969608306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9334402084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8049898147583</t>
+    <t xml:space="preserve">12.7969617843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9334411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.804988861084</t>
   </si>
   <si>
     <t xml:space="preserve">12.9254131317139</t>
@@ -3473,19 +3473,19 @@
     <t xml:space="preserve">13.5837249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3268241882324</t>
+    <t xml:space="preserve">13.3268232345581</t>
   </si>
   <si>
     <t xml:space="preserve">13.2064008712769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2786550521851</t>
+    <t xml:space="preserve">13.2786540985107</t>
   </si>
   <si>
     <t xml:space="preserve">12.6845664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4838609695435</t>
+    <t xml:space="preserve">12.4838619232178</t>
   </si>
   <si>
     <t xml:space="preserve">12.3393535614014</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">12.5320301055908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1839199066162</t>
+    <t xml:space="preserve">12.1839189529419</t>
   </si>
   <si>
     <t xml:space="preserve">11.8018445968628</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">11.9546747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3112773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1075048446655</t>
+    <t xml:space="preserve">12.3112764358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1075038909912</t>
   </si>
   <si>
     <t xml:space="preserve">12.158447265625</t>
@@ -3521,13 +3521,13 @@
     <t xml:space="preserve">11.9801454544067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2433519363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9461841583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9886360168457</t>
+    <t xml:space="preserve">12.2433528900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9461832046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.98863697052</t>
   </si>
   <si>
     <t xml:space="preserve">12.0141077041626</t>
@@ -3536,16 +3536,16 @@
     <t xml:space="preserve">12.0905227661133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9376935958862</t>
+    <t xml:space="preserve">11.9376945495605</t>
   </si>
   <si>
     <t xml:space="preserve">11.6150531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4792051315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556192398071</t>
+    <t xml:space="preserve">11.4792041778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556182861328</t>
   </si>
   <si>
     <t xml:space="preserve">11.6659955978394</t>
@@ -3554,16 +3554,16 @@
     <t xml:space="preserve">11.6575050354004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.750901222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339200973511</t>
+    <t xml:space="preserve">11.7509021759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339210510254</t>
   </si>
   <si>
     <t xml:space="preserve">11.8358068466187</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7593927383423</t>
+    <t xml:space="preserve">11.759391784668</t>
   </si>
   <si>
     <t xml:space="preserve">11.8867502212524</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">11.9631643295288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6744861602783</t>
+    <t xml:space="preserve">11.6744871139526</t>
   </si>
   <si>
     <t xml:space="preserve">11.5726003646851</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">11.5980710983276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5471296310425</t>
+    <t xml:space="preserve">11.5471286773682</t>
   </si>
   <si>
     <t xml:space="preserve">11.581090927124</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">11.4707145690918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3688268661499</t>
+    <t xml:space="preserve">11.3688278198242</t>
   </si>
   <si>
     <t xml:space="preserve">11.343355178833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3009042739868</t>
+    <t xml:space="preserve">11.3009033203125</t>
   </si>
   <si>
     <t xml:space="preserve">11.2499599456787</t>
@@ -3608,13 +3608,13 @@
     <t xml:space="preserve">10.9358100891113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6386404037476</t>
+    <t xml:space="preserve">10.6386413574219</t>
   </si>
   <si>
     <t xml:space="preserve">10.6301507949829</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1461906433105</t>
+    <t xml:space="preserve">10.1461896896362</t>
   </si>
   <si>
     <t xml:space="preserve">10.044303894043</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">10.1886434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86600303649902</t>
+    <t xml:space="preserve">9.86600208282471</t>
   </si>
   <si>
     <t xml:space="preserve">9.71317291259766</t>
@@ -3635,16 +3635,16 @@
     <t xml:space="preserve">10.0612850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075103759766</t>
+    <t xml:space="preserve">10.3075113296509</t>
   </si>
   <si>
     <t xml:space="preserve">10.1716613769531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0697755813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91694641113281</t>
+    <t xml:space="preserve">10.0697746276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9169454574585</t>
   </si>
   <si>
     <t xml:space="preserve">10.0867567062378</t>
@@ -3662,28 +3662,28 @@
     <t xml:space="preserve">9.26317405700684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53487110137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2716646194458</t>
+    <t xml:space="preserve">9.53487205505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27166557312012</t>
   </si>
   <si>
     <t xml:space="preserve">9.45845699310303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74713516235352</t>
+    <t xml:space="preserve">9.7471342086792</t>
   </si>
   <si>
     <t xml:space="preserve">9.90845489501953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56034374237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4160041809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36506080627441</t>
+    <t xml:space="preserve">9.56034278869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41600513458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36506175994873</t>
   </si>
   <si>
     <t xml:space="preserve">9.49241924285889</t>
@@ -3701,10 +3701,10 @@
     <t xml:space="preserve">9.72166347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.027322769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1037368774414</t>
+    <t xml:space="preserve">10.0273237228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1037378311157</t>
   </si>
   <si>
     <t xml:space="preserve">10.1207189559937</t>
@@ -3713,19 +3713,19 @@
     <t xml:space="preserve">9.80656909942627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2395858764648</t>
+    <t xml:space="preserve">10.2395868301392</t>
   </si>
   <si>
     <t xml:space="preserve">10.6216602325439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.842414855957</t>
+    <t xml:space="preserve">10.8424139022827</t>
   </si>
   <si>
     <t xml:space="preserve">10.8593950271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8254337310791</t>
+    <t xml:space="preserve">10.8254327774048</t>
   </si>
   <si>
     <t xml:space="preserve">10.8678855895996</t>
@@ -3737,19 +3737,19 @@
     <t xml:space="preserve">10.774489402771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8169431686401</t>
+    <t xml:space="preserve">10.8169422149658</t>
   </si>
   <si>
     <t xml:space="preserve">11.0207147598267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0716590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2839212417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2754316329956</t>
+    <t xml:space="preserve">11.0716581344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2839221954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2754306793213</t>
   </si>
   <si>
     <t xml:space="preserve">11.4452409744263</t>
@@ -3773,28 +3773,28 @@
     <t xml:space="preserve">11.2584505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2924118041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1141109466553</t>
+    <t xml:space="preserve">11.2924127578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1141119003296</t>
   </si>
   <si>
     <t xml:space="preserve">11.1650543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2414693832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4197702407837</t>
+    <t xml:space="preserve">11.2414684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.419771194458</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858079910278</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3942995071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3603363037109</t>
+    <t xml:space="preserve">11.3942985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3603372573853</t>
   </si>
   <si>
     <t xml:space="preserve">11.0376958847046</t>
@@ -3806,25 +3806,25 @@
     <t xml:space="preserve">11.1226024627686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159976959229</t>
+    <t xml:space="preserve">11.2159986495972</t>
   </si>
   <si>
     <t xml:space="preserve">10.9697723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2244892120361</t>
+    <t xml:space="preserve">11.2244882583618</t>
   </si>
   <si>
     <t xml:space="preserve">11.4112796783447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.521656036377</t>
+    <t xml:space="preserve">11.5216569900513</t>
   </si>
   <si>
     <t xml:space="preserve">11.5386381149292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9716558456421</t>
+    <t xml:space="preserve">11.9716567993164</t>
   </si>
   <si>
     <t xml:space="preserve">12.1159944534302</t>
@@ -3848,13 +3848,13 @@
     <t xml:space="preserve">12.1329755783081</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2009000778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2263708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1414661407471</t>
+    <t xml:space="preserve">12.2008991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2263717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1414670944214</t>
   </si>
   <si>
     <t xml:space="preserve">12.0650510787964</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">11.7169399261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8188257217407</t>
+    <t xml:space="preserve">11.818826675415</t>
   </si>
   <si>
     <t xml:space="preserve">11.5641098022461</t>
@@ -3878,10 +3878,10 @@
     <t xml:space="preserve">10.9018487930298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5622253417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4263782501221</t>
+    <t xml:space="preserve">10.5622262954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4263772964478</t>
   </si>
   <si>
     <t xml:space="preserve">10.6556224822998</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">10.604679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8763771057129</t>
+    <t xml:space="preserve">10.8763761520386</t>
   </si>
   <si>
     <t xml:space="preserve">10.6895847320557</t>
@@ -3899,61 +3899,61 @@
     <t xml:space="preserve">10.9867525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914705276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8084506988525</t>
+    <t xml:space="preserve">10.7914714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8084516525269</t>
   </si>
   <si>
     <t xml:space="preserve">10.8509044647217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6980752944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6641139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320365905762</t>
+    <t xml:space="preserve">10.6980762481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6641130447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320375442505</t>
   </si>
   <si>
     <t xml:space="preserve">10.7999620437622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.012225151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3093929290771</t>
+    <t xml:space="preserve">11.0122261047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3093938827515</t>
   </si>
   <si>
     <t xml:space="preserve">11.0886402130127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3773183822632</t>
+    <t xml:space="preserve">11.3773174285889</t>
   </si>
   <si>
     <t xml:space="preserve">11.5046758651733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6320343017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5131664276123</t>
+    <t xml:space="preserve">11.6320333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5131673812866</t>
   </si>
   <si>
     <t xml:space="preserve">11.4622230529785</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6999588012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6829776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7678813934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8273162841797</t>
+    <t xml:space="preserve">11.6999578475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6829767227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7678833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.827317237854</t>
   </si>
   <si>
     <t xml:space="preserve">11.6374282836914</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">10.877875328064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7331981658936</t>
+    <t xml:space="preserve">10.7331991195679</t>
   </si>
   <si>
     <t xml:space="preserve">10.8326635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8869180679321</t>
+    <t xml:space="preserve">10.8869171142578</t>
   </si>
   <si>
     <t xml:space="preserve">10.8507490158081</t>
@@ -3995,22 +3995,22 @@
     <t xml:space="preserve">10.6608600616455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3082103729248</t>
+    <t xml:space="preserve">10.3082113265991</t>
   </si>
   <si>
     <t xml:space="preserve">10.1544914245605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1454496383667</t>
+    <t xml:space="preserve">10.145450592041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3262958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3534231185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4167194366455</t>
+    <t xml:space="preserve">10.353422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4167184829712</t>
   </si>
   <si>
     <t xml:space="preserve">10.2539577484131</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">10.3805494308472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4890565872192</t>
+    <t xml:space="preserve">10.4890575408936</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">10.0098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0731115341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95556163787842</t>
+    <t xml:space="preserve">10.073112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95556259155273</t>
   </si>
   <si>
     <t xml:space="preserve">9.8560962677002</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">9.7114200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57578659057617</t>
+    <t xml:space="preserve">9.57578563690186</t>
   </si>
   <si>
     <t xml:space="preserve">9.34068584442139</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">9.43110942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28643226623535</t>
+    <t xml:space="preserve">9.28643321990967</t>
   </si>
   <si>
     <t xml:space="preserve">9.26834774017334</t>
@@ -4073,28 +4073,28 @@
     <t xml:space="preserve">9.30451679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33164405822754</t>
+    <t xml:space="preserve">9.33164310455322</t>
   </si>
   <si>
     <t xml:space="preserve">9.52153205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72046184539795</t>
+    <t xml:space="preserve">9.72046279907227</t>
   </si>
   <si>
     <t xml:space="preserve">9.76567363739014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91035079956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91939353942871</t>
+    <t xml:space="preserve">9.91034984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91939258575439</t>
   </si>
   <si>
     <t xml:space="preserve">9.90130805969238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87418079376221</t>
+    <t xml:space="preserve">9.87418174743652</t>
   </si>
   <si>
     <t xml:space="preserve">9.82896995544434</t>
@@ -4130,10 +4130,10 @@
     <t xml:space="preserve">9.15984058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12367057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32260227203369</t>
+    <t xml:space="preserve">9.12367153167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32260131835938</t>
   </si>
   <si>
     <t xml:space="preserve">9.20505142211914</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">9.89226531982422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84705448150635</t>
+    <t xml:space="preserve">9.84705543518066</t>
   </si>
   <si>
     <t xml:space="preserve">10.0279006958008</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">10.0369424819946</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94651985168457</t>
+    <t xml:space="preserve">9.94651889801025</t>
   </si>
   <si>
     <t xml:space="preserve">10.1906623840332</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">10.4800148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5523529052734</t>
+    <t xml:space="preserve">10.5523538589478</t>
   </si>
   <si>
     <t xml:space="preserve">10.7151145935059</t>
@@ -4187,16 +4187,16 @@
     <t xml:space="preserve">10.4980993270874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2991695404053</t>
+    <t xml:space="preserve">10.299168586731</t>
   </si>
   <si>
     <t xml:space="preserve">10.2901268005371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.181619644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5704364776611</t>
+    <t xml:space="preserve">10.1816186904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5704374313354</t>
   </si>
   <si>
     <t xml:space="preserve">10.7603254318237</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">11.0768060684204</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2124404907227</t>
+    <t xml:space="preserve">11.2124395370483</t>
   </si>
   <si>
     <t xml:space="preserve">11.5560474395752</t>
@@ -4223,19 +4223,19 @@
     <t xml:space="preserve">11.2486085891724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6464700698853</t>
+    <t xml:space="preserve">11.6464710235596</t>
   </si>
   <si>
     <t xml:space="preserve">11.5289211273193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7188091278076</t>
+    <t xml:space="preserve">11.7188081741333</t>
   </si>
   <si>
     <t xml:space="preserve">11.9448661804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9629507064819</t>
+    <t xml:space="preserve">11.9629497528076</t>
   </si>
   <si>
     <t xml:space="preserve">11.9086971282959</t>
@@ -4250,10 +4250,10 @@
     <t xml:space="preserve">12.4783611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5054874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1528377532959</t>
+    <t xml:space="preserve">12.5054883956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1528387069702</t>
   </si>
   <si>
     <t xml:space="preserve">12.3155994415283</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">12.1709232330322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1799650192261</t>
+    <t xml:space="preserve">12.1799659729004</t>
   </si>
   <si>
     <t xml:space="preserve">12.107626914978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2161350250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2703876495361</t>
+    <t xml:space="preserve">12.2161340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2703886032104</t>
   </si>
   <si>
     <t xml:space="preserve">12.4874038696289</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">12.650164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4693193435669</t>
+    <t xml:space="preserve">12.4693183898926</t>
   </si>
   <si>
     <t xml:space="preserve">12.595911026001</t>
@@ -4316,16 +4316,16 @@
     <t xml:space="preserve">12.8852643966675</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0751523971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932359695435</t>
+    <t xml:space="preserve">13.0751514434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932369232178</t>
   </si>
   <si>
     <t xml:space="preserve">13.0028142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2198295593262</t>
+    <t xml:space="preserve">13.2198286056519</t>
   </si>
   <si>
     <t xml:space="preserve">12.9304752349854</t>
@@ -4346,16 +4346,16 @@
     <t xml:space="preserve">12.6772918701172</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2613458633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5507001876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.577826499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4602766036987</t>
+    <t xml:space="preserve">12.2613468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5506992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5778255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4602756500244</t>
   </si>
   <si>
     <t xml:space="preserve">12.3517684936523</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">12.4060230255127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3608112335205</t>
+    <t xml:space="preserve">12.3608121871948</t>
   </si>
   <si>
     <t xml:space="preserve">12.4241065979004</t>
@@ -4391,19 +4391,19 @@
     <t xml:space="preserve">13.5091819763184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2144804000854</t>
+    <t xml:space="preserve">14.2144813537598</t>
   </si>
   <si>
     <t xml:space="preserve">14.1963958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0788469314575</t>
+    <t xml:space="preserve">14.0788459777832</t>
   </si>
   <si>
     <t xml:space="preserve">13.8980007171631</t>
   </si>
   <si>
-    <t xml:space="preserve">13.979380607605</t>
+    <t xml:space="preserve">13.9793815612793</t>
   </si>
   <si>
     <t xml:space="preserve">14.0065078735352</t>
@@ -4424,16 +4424,16 @@
     <t xml:space="preserve">14.6485109329224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8474416732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5671300888062</t>
+    <t xml:space="preserve">14.8474407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5671310424805</t>
   </si>
   <si>
     <t xml:space="preserve">14.6846799850464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8022298812866</t>
+    <t xml:space="preserve">14.8022308349609</t>
   </si>
   <si>
     <t xml:space="preserve">14.7389326095581</t>
@@ -4448,10 +4448,10 @@
     <t xml:space="preserve">14.1511840820312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1873531341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3049030303955</t>
+    <t xml:space="preserve">14.1873540878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3049039840698</t>
   </si>
   <si>
     <t xml:space="preserve">13.9341697692871</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">14.1421422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2958612442017</t>
+    <t xml:space="preserve">14.295862197876</t>
   </si>
   <si>
     <t xml:space="preserve">14.4495801925659</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">14.5490455627441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.874568939209</t>
+    <t xml:space="preserve">14.8745679855347</t>
   </si>
   <si>
     <t xml:space="preserve">14.7208499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6123418807983</t>
+    <t xml:space="preserve">14.612340927124</t>
   </si>
   <si>
     <t xml:space="preserve">14.6304264068604</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">14.9649896621704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6575517654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8926515579224</t>
+    <t xml:space="preserve">14.6575527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8926525115967</t>
   </si>
   <si>
     <t xml:space="preserve">14.9740324020386</t>
@@ -4514,13 +4514,13 @@
     <t xml:space="preserve">15.082540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.471360206604</t>
+    <t xml:space="preserve">15.4713592529297</t>
   </si>
   <si>
     <t xml:space="preserve">15.191047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2633857727051</t>
+    <t xml:space="preserve">15.2633848190308</t>
   </si>
   <si>
     <t xml:space="preserve">15.1458368301392</t>
@@ -4532,16 +4532,16 @@
     <t xml:space="preserve">15.2995548248291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2000904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3718938827515</t>
+    <t xml:space="preserve">15.2000894546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3718948364258</t>
   </si>
   <si>
     <t xml:space="preserve">15.7245426177979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5527410507202</t>
+    <t xml:space="preserve">15.5527391433716</t>
   </si>
   <si>
     <t xml:space="preserve">15.6974172592163</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">15.4171047210693</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2905130386353</t>
+    <t xml:space="preserve">15.2905120849609</t>
   </si>
   <si>
     <t xml:space="preserve">15.0011596679688</t>
@@ -4568,10 +4568,10 @@
     <t xml:space="preserve">14.5128755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6665954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8112707138062</t>
+    <t xml:space="preserve">14.6665945053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8112716674805</t>
   </si>
   <si>
     <t xml:space="preserve">14.5054912567139</t>
@@ -4616,9 +4616,6 @@
     <t xml:space="preserve">15.2890548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8112716674805</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.8017158508301</t>
   </si>
   <si>
@@ -5454,6 +5451,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.1800003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7999992370605</t>
   </si>
 </sst>
 </file>
@@ -62282,7 +62282,7 @@
         <v>15.5</v>
       </c>
       <c r="G2173" t="s">
-        <v>1534</v>
+        <v>1519</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62308,7 +62308,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G2174" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62334,7 +62334,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G2175" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62360,7 +62360,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62386,7 +62386,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G2177" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62412,7 +62412,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G2178" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62438,7 +62438,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G2179" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62464,7 +62464,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G2180" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62490,7 +62490,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G2181" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62516,7 +62516,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G2182" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62542,7 +62542,7 @@
         <v>16.5</v>
       </c>
       <c r="G2183" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62568,7 +62568,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2184" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62594,7 +62594,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G2185" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62620,7 +62620,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G2186" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62646,7 +62646,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G2187" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62672,7 +62672,7 @@
         <v>16.25</v>
       </c>
       <c r="G2188" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62698,7 +62698,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G2189" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62724,7 +62724,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2190" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62750,7 +62750,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2191" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62776,7 +62776,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62802,7 +62802,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G2193" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62828,7 +62828,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G2194" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62854,7 +62854,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G2195" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62880,7 +62880,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G2196" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62906,7 +62906,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2197" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62932,7 +62932,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2198" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62958,7 +62958,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G2199" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62984,7 +62984,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2200" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -63010,7 +63010,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G2201" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -63036,7 +63036,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G2202" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63062,7 +63062,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2203" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63088,7 +63088,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2204" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63114,7 +63114,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G2205" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63140,7 +63140,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2206" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63166,7 +63166,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G2207" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63192,7 +63192,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2208" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63218,7 +63218,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G2209" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63244,7 +63244,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2210" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63270,7 +63270,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2211" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63296,7 +63296,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G2212" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63322,7 +63322,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2213" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63348,7 +63348,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2214" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63374,7 +63374,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2215" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63400,7 +63400,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2216" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63426,7 +63426,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G2217" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63452,7 +63452,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G2218" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63478,7 +63478,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G2219" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63504,7 +63504,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2220" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63530,7 +63530,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2221" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63556,7 +63556,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G2222" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63582,7 +63582,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G2223" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63608,7 +63608,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2224" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63634,7 +63634,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G2225" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63660,7 +63660,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G2226" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63686,7 +63686,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G2227" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63712,7 +63712,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G2228" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63738,7 +63738,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2229" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63764,7 +63764,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G2230" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63790,7 +63790,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G2231" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63816,7 +63816,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2232" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63842,7 +63842,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G2233" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63868,7 +63868,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2234" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63894,7 +63894,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G2235" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63920,7 +63920,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G2236" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63946,7 +63946,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G2237" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63972,7 +63972,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2238" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63998,7 +63998,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G2239" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -64024,7 +64024,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2240" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64050,7 +64050,7 @@
         <v>17.75</v>
       </c>
       <c r="G2241" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64076,7 +64076,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2242" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64102,7 +64102,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2243" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64128,7 +64128,7 @@
         <v>18.5</v>
       </c>
       <c r="G2244" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64154,7 +64154,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G2245" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64180,7 +64180,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2246" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64206,7 +64206,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2247" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64232,7 +64232,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2248" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64258,7 +64258,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64284,7 +64284,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2250" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64310,7 +64310,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2251" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64336,7 +64336,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G2252" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64362,7 +64362,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G2253" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64388,7 +64388,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2254" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64414,7 +64414,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G2255" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64440,7 +64440,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G2256" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64466,7 +64466,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2257" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64492,7 +64492,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G2258" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64518,7 +64518,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2259" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64544,7 +64544,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2260" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64570,7 +64570,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2261" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64596,7 +64596,7 @@
         <v>17</v>
       </c>
       <c r="G2262" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64622,7 +64622,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64648,7 +64648,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G2264" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64674,7 +64674,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G2265" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64700,7 +64700,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2266" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64726,7 +64726,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G2267" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64752,7 +64752,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2268" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64778,7 +64778,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2269" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64804,7 +64804,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G2270" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64830,7 +64830,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G2271" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64856,7 +64856,7 @@
         <v>18</v>
       </c>
       <c r="G2272" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64882,7 +64882,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G2273" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64908,7 +64908,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G2274" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64934,7 +64934,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G2275" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64960,7 +64960,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G2276" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64986,7 +64986,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G2277" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -65012,7 +65012,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2278" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -65038,7 +65038,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2279" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65064,7 +65064,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G2280" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65090,7 +65090,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G2281" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65116,7 +65116,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G2282" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65142,7 +65142,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2283" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65168,7 +65168,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2284" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65194,7 +65194,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G2285" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65220,7 +65220,7 @@
         <v>18.25</v>
       </c>
       <c r="G2286" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65246,7 +65246,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G2287" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65272,7 +65272,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2288" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65298,7 +65298,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G2289" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65324,7 +65324,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G2290" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65350,7 +65350,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G2291" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65376,7 +65376,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G2292" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65402,7 +65402,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G2293" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65428,7 +65428,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2294" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65454,7 +65454,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G2295" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65480,7 +65480,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G2296" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65506,7 +65506,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G2297" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65532,7 +65532,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2298" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65558,7 +65558,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G2299" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65584,7 +65584,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2300" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65610,7 +65610,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G2301" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65636,7 +65636,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2302" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65662,7 +65662,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G2303" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65688,7 +65688,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G2304" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65714,7 +65714,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G2305" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65740,7 +65740,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G2306" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65766,7 +65766,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65792,7 +65792,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G2308" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65818,7 +65818,7 @@
         <v>18.25</v>
       </c>
       <c r="G2309" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65844,7 +65844,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G2310" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65870,7 +65870,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G2311" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65896,7 +65896,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2312" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65922,7 +65922,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G2313" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65948,7 +65948,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2314" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65974,7 +65974,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G2315" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -66000,7 +66000,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2316" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -66026,7 +66026,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2317" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66052,7 +66052,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G2318" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66078,7 +66078,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G2319" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66104,7 +66104,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G2320" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66130,7 +66130,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G2321" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66156,7 +66156,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G2322" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66182,7 +66182,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2323" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66208,7 +66208,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2324" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66234,7 +66234,7 @@
         <v>17.25</v>
       </c>
       <c r="G2325" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66260,7 +66260,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G2326" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66286,7 +66286,7 @@
         <v>17.25</v>
       </c>
       <c r="G2327" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66312,7 +66312,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66338,7 +66338,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G2329" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66364,7 +66364,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G2330" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66390,7 +66390,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G2331" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66416,7 +66416,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G2332" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66442,7 +66442,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G2333" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66468,7 +66468,7 @@
         <v>17</v>
       </c>
       <c r="G2334" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66494,7 +66494,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66520,7 +66520,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G2336" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66546,7 +66546,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G2337" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66572,7 +66572,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2338" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66598,7 +66598,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2339" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66624,7 +66624,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G2340" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66650,7 +66650,7 @@
         <v>17.75</v>
       </c>
       <c r="G2341" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66676,7 +66676,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G2342" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66702,7 +66702,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G2343" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66728,7 +66728,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G2344" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66754,7 +66754,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2345" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66780,7 +66780,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G2346" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66806,7 +66806,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66832,7 +66832,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G2348" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66858,7 +66858,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G2349" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66884,7 +66884,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G2350" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66910,7 +66910,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66936,7 +66936,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2352" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66962,7 +66962,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G2353" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66988,7 +66988,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G2354" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67014,7 +67014,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G2355" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67040,7 +67040,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G2356" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67066,7 +67066,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G2357" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67092,7 +67092,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2358" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67118,7 +67118,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G2359" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67144,7 +67144,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G2360" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67170,7 +67170,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2361" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67196,7 +67196,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G2362" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67222,7 +67222,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G2363" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67248,7 +67248,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G2364" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67274,7 +67274,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2365" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67300,7 +67300,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2366" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67326,7 +67326,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G2367" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67352,7 +67352,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G2368" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67378,7 +67378,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G2369" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67404,7 +67404,7 @@
         <v>20</v>
       </c>
       <c r="G2370" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67430,7 +67430,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2371" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67456,7 +67456,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2372" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67482,7 +67482,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G2373" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67508,7 +67508,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2374" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67534,7 +67534,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G2375" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67560,7 +67560,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G2376" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67586,7 +67586,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67612,7 +67612,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G2378" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67638,7 +67638,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G2379" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67664,7 +67664,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2380" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67690,7 +67690,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2381" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67716,7 +67716,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G2382" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67742,7 +67742,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G2383" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67768,7 +67768,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2384" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67794,7 +67794,7 @@
         <v>21.5</v>
       </c>
       <c r="G2385" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67820,7 +67820,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G2386" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67846,7 +67846,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G2387" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67872,7 +67872,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G2388" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67898,7 +67898,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G2389" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67924,7 +67924,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67950,7 +67950,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G2391" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67976,7 +67976,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G2392" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68002,7 +68002,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G2393" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68028,7 +68028,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G2394" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68054,7 +68054,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68080,7 +68080,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2396" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68106,7 +68106,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2397" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68132,7 +68132,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G2398" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68158,7 +68158,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G2399" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68184,7 +68184,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G2400" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68210,7 +68210,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G2401" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68236,7 +68236,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G2402" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68262,7 +68262,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2403" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68288,7 +68288,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2404" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68314,7 +68314,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G2405" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68340,7 +68340,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2406" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68366,7 +68366,7 @@
         <v>21.5</v>
       </c>
       <c r="G2407" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68392,7 +68392,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G2408" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68418,7 +68418,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G2409" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68444,7 +68444,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G2410" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68470,7 +68470,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G2411" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68496,7 +68496,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2412" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68522,7 +68522,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2413" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68548,7 +68548,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2414" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68574,7 +68574,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2415" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68600,7 +68600,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2416" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68626,7 +68626,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68652,7 +68652,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2418" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68678,7 +68678,7 @@
         <v>19.75</v>
       </c>
       <c r="G2419" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68704,7 +68704,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G2420" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68730,7 +68730,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G2421" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68756,7 +68756,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G2422" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68782,7 +68782,7 @@
         <v>19.25</v>
       </c>
       <c r="G2423" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68808,7 +68808,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G2424" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68834,7 +68834,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G2425" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68860,7 +68860,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G2426" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68886,7 +68886,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G2427" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68912,7 +68912,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2428" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68938,7 +68938,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G2429" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68964,7 +68964,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G2430" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68990,7 +68990,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69016,7 +69016,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G2432" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69042,7 +69042,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2433" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69068,7 +69068,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2434" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69094,7 +69094,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G2435" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69120,7 +69120,7 @@
         <v>19.75</v>
       </c>
       <c r="G2436" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69146,7 +69146,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G2437" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69172,7 +69172,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G2438" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69198,7 +69198,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G2439" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69224,7 +69224,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G2440" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69250,7 +69250,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69276,7 +69276,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G2442" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69302,7 +69302,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2443" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69328,7 +69328,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G2444" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69354,7 +69354,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G2445" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69380,7 +69380,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2446" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69406,7 +69406,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G2447" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69432,7 +69432,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2448" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69458,7 +69458,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G2449" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69484,7 +69484,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G2450" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69510,7 +69510,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G2451" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69536,7 +69536,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G2452" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69562,7 +69562,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G2453" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69588,7 +69588,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G2454" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69614,7 +69614,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G2455" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -69640,7 +69640,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G2456" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69666,7 +69666,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G2457" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -69692,7 +69692,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G2458" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69718,7 +69718,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G2459" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69744,7 +69744,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G2460" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69770,7 +69770,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G2461" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69796,7 +69796,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G2462" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69822,7 +69822,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69848,7 +69848,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G2464" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69874,7 +69874,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G2465" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69900,7 +69900,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G2466" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69926,7 +69926,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2467" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69952,7 +69952,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G2468" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69978,7 +69978,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70004,7 +70004,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G2470" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70030,7 +70030,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G2471" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70056,7 +70056,7 @@
         <v>19.25</v>
       </c>
       <c r="G2472" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70082,7 +70082,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70108,7 +70108,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G2474" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70134,7 +70134,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G2475" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70160,7 +70160,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G2476" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70186,7 +70186,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G2477" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70212,7 +70212,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G2478" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70238,7 +70238,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2479" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70264,7 +70264,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G2480" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70290,7 +70290,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70316,7 +70316,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G2482" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70342,7 +70342,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2483" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70368,7 +70368,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2484" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70394,7 +70394,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2485" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70420,7 +70420,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2486" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70446,7 +70446,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2487" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70472,7 +70472,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2488" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70498,7 +70498,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G2489" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70524,7 +70524,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G2490" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70550,7 +70550,7 @@
         <v>20.5</v>
       </c>
       <c r="G2491" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70576,7 +70576,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G2492" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -70602,7 +70602,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G2493" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -70628,7 +70628,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G2494" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -70654,7 +70654,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G2495" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -70680,7 +70680,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2496" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -70706,7 +70706,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2497" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -70732,7 +70732,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2498" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -70758,7 +70758,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G2499" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -70784,7 +70784,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G2500" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -70810,7 +70810,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2501" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -70836,7 +70836,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G2502" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -70862,7 +70862,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G2503" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -70888,7 +70888,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2504" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -70914,7 +70914,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2505" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -70940,7 +70940,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G2506" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -70966,7 +70966,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G2507" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -70992,7 +70992,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2508" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -71018,7 +71018,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G2509" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -71044,7 +71044,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G2510" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -71070,7 +71070,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G2511" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -71096,7 +71096,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2512" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -71122,7 +71122,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2513" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -71148,7 +71148,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G2514" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -71174,7 +71174,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2515" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -71200,7 +71200,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G2516" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -71226,7 +71226,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2517" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -71252,7 +71252,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2518" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -71278,7 +71278,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G2519" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -71304,7 +71304,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G2520" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -71330,7 +71330,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2521" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -71356,7 +71356,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G2522" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -71382,7 +71382,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G2523" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -71408,7 +71408,7 @@
         <v>22.6200008392334</v>
       </c>
       <c r="G2524" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -71434,7 +71434,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G2525" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -71460,7 +71460,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2526" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -71486,7 +71486,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2527" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -71512,7 +71512,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G2528" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -71520,7 +71520,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6910185185</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>57871</v>
@@ -71538,9 +71538,35 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G2529" t="s">
+        <v>1812</v>
+      </c>
+      <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.6912731481</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>58926</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>22.3199996948242</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>22.3199996948242</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="G2530" t="s">
         <v>1813</v>
       </c>
-      <c r="H2529" t="s">
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="1814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="1815">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">ACE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61100769042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30103778839111</t>
+    <t xml:space="preserve">8.611008644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3010368347168</t>
   </si>
   <si>
     <t xml:space="preserve">8.43742370605469</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">8.48081970214844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61720561981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80319023132324</t>
+    <t xml:space="preserve">8.61720848083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80318927764893</t>
   </si>
   <si>
     <t xml:space="preserve">8.68540191650391</t>
@@ -68,22 +68,22 @@
     <t xml:space="preserve">8.30723571777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35063171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20804405212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91667222976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97246599197388</t>
+    <t xml:space="preserve">8.3506326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20804500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91667175292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97246742248535</t>
   </si>
   <si>
     <t xml:space="preserve">8.13985157012939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15224933624268</t>
+    <t xml:space="preserve">8.15225028991699</t>
   </si>
   <si>
     <t xml:space="preserve">8.2762393951416</t>
@@ -95,43 +95,43 @@
     <t xml:space="preserve">8.49321937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50561904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39402770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36923027038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33203506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99106454849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59430265426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45791387557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3153281211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46411275863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6686954498291</t>
+    <t xml:space="preserve">8.50561809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39402866363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36923217773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33203411102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99106550216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59430027008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45791482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31532764434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46411323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66869497299194</t>
   </si>
   <si>
     <t xml:space="preserve">7.63149833679199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65629577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65009784698486</t>
+    <t xml:space="preserve">7.65629720687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65009689331055</t>
   </si>
   <si>
     <t xml:space="preserve">7.44551563262939</t>
@@ -140,196 +140,196 @@
     <t xml:space="preserve">7.60050058364868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68109321594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55090665817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68729162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60670137405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73688793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64389610290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57570457458496</t>
+    <t xml:space="preserve">7.68109464645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55090713500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68729305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6067008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73688840866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64389657974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57570362091064</t>
   </si>
   <si>
     <t xml:space="preserve">7.53230762481689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01586246490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38162803649902</t>
+    <t xml:space="preserve">8.0158634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38162899017334</t>
   </si>
   <si>
     <t xml:space="preserve">8.67920207977295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77219295501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76599407196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83418846130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.784592628479</t>
+    <t xml:space="preserve">8.77219390869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76599502563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83418750762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78459358215332</t>
   </si>
   <si>
     <t xml:space="preserve">8.46842098236084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41882610321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33823490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45602321624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49941730499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58621025085449</t>
+    <t xml:space="preserve">8.41882705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33823204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45602226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49941921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58620929718018</t>
   </si>
   <si>
     <t xml:space="preserve">8.43122482299805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40642738342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34443283081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47461986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24524211883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90427255630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87327527999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73068904876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79268312454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8546781539917</t>
+    <t xml:space="preserve">8.40642642974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34443378448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4746208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24524307250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90427398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87327575683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73069000244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79268407821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85467767715454</t>
   </si>
   <si>
     <t xml:space="preserve">7.89807462692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96006774902344</t>
+    <t xml:space="preserve">7.96006679534912</t>
   </si>
   <si>
     <t xml:space="preserve">8.04685974121094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99726438522339</t>
+    <t xml:space="preserve">7.99726533889771</t>
   </si>
   <si>
     <t xml:space="preserve">7.96626710891724</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8670768737793</t>
+    <t xml:space="preserve">7.86707639694214</t>
   </si>
   <si>
     <t xml:space="preserve">7.78028535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09025573730469</t>
+    <t xml:space="preserve">8.09025478363037</t>
   </si>
   <si>
     <t xml:space="preserve">8.11505317687988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1770486831665</t>
+    <t xml:space="preserve">8.17704772949219</t>
   </si>
   <si>
     <t xml:space="preserve">8.02206230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88567495346069</t>
+    <t xml:space="preserve">7.88567447662354</t>
   </si>
   <si>
     <t xml:space="preserve">7.8298807144165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04066276550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00966453552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09645557403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19564628601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23284244537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18324756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05926036834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76168537139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52610778808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56330442428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42071628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19133806228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85656976699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96815967559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97435808181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12314653396606</t>
+    <t xml:space="preserve">8.0406608581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00966262817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09645462036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19564723968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23284339904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18324661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05925941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76168727874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52610921859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56330299377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42071771621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19133853912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85657072067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96815919876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9743595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12314510345459</t>
   </si>
   <si>
     <t xml:space="preserve">7.09073686599731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0518479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14259099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05833053588867</t>
+    <t xml:space="preserve">7.05184936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1425895690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05833005905151</t>
   </si>
   <si>
     <t xml:space="preserve">6.6824049949646</t>
@@ -338,55 +338,55 @@
     <t xml:space="preserve">6.37777519226074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49444103240967</t>
+    <t xml:space="preserve">6.49444246292114</t>
   </si>
   <si>
     <t xml:space="preserve">6.61110877990723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08425617218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99999713897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03888654708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93518209457397</t>
+    <t xml:space="preserve">7.08425712585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99999666213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03888559341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93518304824829</t>
   </si>
   <si>
     <t xml:space="preserve">6.78610754013062</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75370121002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82499647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86388635635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74073648452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91573858261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89629459381104</t>
+    <t xml:space="preserve">6.75370168685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82499742507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86388683319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74073791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91573762893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92869997024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89629316329956</t>
   </si>
   <si>
     <t xml:space="preserve">7.15555286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14907073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5833306312561</t>
+    <t xml:space="preserve">7.14907121658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58332967758179</t>
   </si>
   <si>
     <t xml:space="preserve">7.55740356445312</t>
@@ -395,100 +395,100 @@
     <t xml:space="preserve">8.0694408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0435152053833</t>
+    <t xml:space="preserve">8.04351425170898</t>
   </si>
   <si>
     <t xml:space="preserve">8.01110744476318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16666412353516</t>
+    <t xml:space="preserve">8.16666221618652</t>
   </si>
   <si>
     <t xml:space="preserve">8.17962646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07592296600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05647754669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10184860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95277500152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82962656021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87499666213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90740299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481151580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75832891464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74536561965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7712926864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71944141387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57684850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65462636947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70647859573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81666469573975</t>
+    <t xml:space="preserve">8.0759220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05647850036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10184955596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9527759552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82962465286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87499618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90740346908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481056213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75833082199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74536609649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77129220962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71943998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57684898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65462684631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70647811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81666374206543</t>
   </si>
   <si>
     <t xml:space="preserve">7.79073667526245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69351577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72592258453369</t>
+    <t xml:space="preserve">7.69351530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72592353820801</t>
   </si>
   <si>
     <t xml:space="preserve">7.69999647140503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50555181503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37592172622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39536619186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47314357757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32407093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25277328491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22684764862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18147897720337</t>
+    <t xml:space="preserve">7.50555324554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37592363357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39536714553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47314405441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32407140731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25277423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22684907913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18147754669189</t>
   </si>
   <si>
     <t xml:space="preserve">7.20092248916626</t>
@@ -497,217 +497,217 @@
     <t xml:space="preserve">7.22036695480347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18796014785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1685152053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16203594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19444227218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17499732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07129287719727</t>
+    <t xml:space="preserve">7.18795967102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16851568222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16203355789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19444274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17499542236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07129335403442</t>
   </si>
   <si>
     <t xml:space="preserve">6.96758937835693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04536724090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98703289031982</t>
+    <t xml:space="preserve">7.04536771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98703384399414</t>
   </si>
   <si>
     <t xml:space="preserve">7.23332977294922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34999561309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41481161117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55092239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52499580383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64166259765625</t>
+    <t xml:space="preserve">7.3499960899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41481113433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55092191696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52499628067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64166212081909</t>
   </si>
   <si>
     <t xml:space="preserve">7.59629249572754</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6157374382019</t>
+    <t xml:space="preserve">7.61573696136475</t>
   </si>
   <si>
     <t xml:space="preserve">7.64814567565918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49258947372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38888597488403</t>
+    <t xml:space="preserve">7.49258995056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38888454437256</t>
   </si>
   <si>
     <t xml:space="preserve">7.46018218994141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36944055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30462694168091</t>
+    <t xml:space="preserve">7.36944150924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30462598800659</t>
   </si>
   <si>
     <t xml:space="preserve">6.84444189071655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5722188949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59166479110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54629421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48147916793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43610858917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47823858261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52684831619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64999675750732</t>
+    <t xml:space="preserve">6.57222127914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59166383743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54629278182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48147821426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43610811233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47823810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52684926986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64999771118164</t>
   </si>
   <si>
     <t xml:space="preserve">6.53332996368408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59814596176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52036762237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42962646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87036800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10370016098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25925540924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48610734939575</t>
+    <t xml:space="preserve">6.59814548492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52036714553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42962741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8703670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10370063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25925636291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48610830307007</t>
   </si>
   <si>
     <t xml:space="preserve">7.4342565536499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42777490615845</t>
+    <t xml:space="preserve">7.42777395248413</t>
   </si>
   <si>
     <t xml:space="preserve">7.38240432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51851511001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51203346252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66758966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6805534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71296072006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89444208145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79721879959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84258890151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34351444244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4018497467041</t>
+    <t xml:space="preserve">7.51851558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51203298568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66759014129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68055200576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71295976638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89444065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7972207069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84259033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34351539611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40184879302979</t>
   </si>
   <si>
     <t xml:space="preserve">7.46666288375854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40833234786987</t>
+    <t xml:space="preserve">7.4083309173584</t>
   </si>
   <si>
     <t xml:space="preserve">7.73888540267944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68703365325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6222186088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63518238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7324047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7777738571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83610773086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75184774398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62870121002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97221803665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85555267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9268479347229</t>
+    <t xml:space="preserve">7.68703269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62221956253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63518142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73240423202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77777433395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83610820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75184869766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62870168685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97221946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85555171966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92684888839722</t>
   </si>
   <si>
     <t xml:space="preserve">8.03703212738037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09536647796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13425636291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20555305480957</t>
+    <t xml:space="preserve">8.09536743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13425731658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20555114746094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28981113433838</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">8.24444103240967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147678375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22499656677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27036666870117</t>
+    <t xml:space="preserve">8.23147869110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22499561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27036762237549</t>
   </si>
   <si>
     <t xml:space="preserve">8.46481132507324</t>
@@ -731,49 +731,49 @@
     <t xml:space="preserve">8.45832920074463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43240451812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42592334747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3546257019043</t>
+    <t xml:space="preserve">8.43240356445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42592239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35462665557861</t>
   </si>
   <si>
     <t xml:space="preserve">8.55555152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52314376831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39351463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47129344940186</t>
+    <t xml:space="preserve">8.52314472198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39351558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47129154205322</t>
   </si>
   <si>
     <t xml:space="preserve">8.60740375518799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61388492584229</t>
+    <t xml:space="preserve">8.6138858795166</t>
   </si>
   <si>
     <t xml:space="preserve">8.6203670501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56203365325928</t>
+    <t xml:space="preserve">8.56203269958496</t>
   </si>
   <si>
     <t xml:space="preserve">8.80832862854004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81481075286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84073734283447</t>
+    <t xml:space="preserve">8.6786994934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81481170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84073638916016</t>
   </si>
   <si>
     <t xml:space="preserve">8.9249963760376</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">9.00277423858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95092105865479</t>
+    <t xml:space="preserve">8.9509220123291</t>
   </si>
   <si>
     <t xml:space="preserve">8.99629211425781</t>
@@ -797,121 +797,121 @@
     <t xml:space="preserve">9.18425559997559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01573657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02869987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20370006561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28147792816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30740261077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34629154205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43703269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32684898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43055152893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38518047332764</t>
+    <t xml:space="preserve">9.0157356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02869892120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20369815826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28147602081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30740356445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34629344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43703365325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32684707641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43055248260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38518238067627</t>
   </si>
   <si>
     <t xml:space="preserve">9.41758823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33332920074463</t>
+    <t xml:space="preserve">9.33332824707031</t>
   </si>
   <si>
     <t xml:space="preserve">9.50184726715088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50832939147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44351387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54721832275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41110801696777</t>
+    <t xml:space="preserve">9.50832843780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44351577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54721641540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41110610961914</t>
   </si>
   <si>
     <t xml:space="preserve">9.35925483703613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51501750946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41343116760254</t>
+    <t xml:space="preserve">9.51501846313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41343307495117</t>
   </si>
   <si>
     <t xml:space="preserve">9.59628391265869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50147247314453</t>
+    <t xml:space="preserve">9.50147151947021</t>
   </si>
   <si>
     <t xml:space="preserve">9.44729423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48115539550781</t>
+    <t xml:space="preserve">9.4811544418335</t>
   </si>
   <si>
     <t xml:space="preserve">9.21026515960693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09513854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14931488037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98678016662598</t>
+    <t xml:space="preserve">9.09513664245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14931583404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98678112030029</t>
   </si>
   <si>
     <t xml:space="preserve">8.83101940155029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84456443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93937587738037</t>
+    <t xml:space="preserve">8.84456348419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93937492370605</t>
   </si>
   <si>
     <t xml:space="preserve">8.81070327758789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93260288238525</t>
+    <t xml:space="preserve">8.93260192871094</t>
   </si>
   <si>
     <t xml:space="preserve">9.04096031188965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87165260314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04773044586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08159255981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10191059112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349216461182</t>
+    <t xml:space="preserve">8.87165355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04773139953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08159160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10190868377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349311828613</t>
   </si>
   <si>
     <t xml:space="preserve">9.10868167877197</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">9.12222576141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00709819793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07481956481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8784236907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92583084106445</t>
+    <t xml:space="preserve">9.0070972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07481861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87842559814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92583179473877</t>
   </si>
   <si>
     <t xml:space="preserve">8.90551376342773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52626800537109</t>
+    <t xml:space="preserve">8.52626705169678</t>
   </si>
   <si>
     <t xml:space="preserve">8.58721828460693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54658508300781</t>
+    <t xml:space="preserve">8.5465841293335</t>
   </si>
   <si>
     <t xml:space="preserve">8.56012916564941</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">8.53981113433838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44500064849854</t>
+    <t xml:space="preserve">8.44500160217285</t>
   </si>
   <si>
     <t xml:space="preserve">8.33664512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47208976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47886180877686</t>
+    <t xml:space="preserve">8.47209072113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47886371612549</t>
   </si>
   <si>
     <t xml:space="preserve">8.4111385345459</t>
@@ -971,49 +971,49 @@
     <t xml:space="preserve">8.42468357086182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3840503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3908224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32987213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28246593475342</t>
+    <t xml:space="preserve">8.38404941558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39082336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32987308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28246688842773</t>
   </si>
   <si>
     <t xml:space="preserve">8.26892185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24860668182373</t>
+    <t xml:space="preserve">8.24860572814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.19442749023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16733932495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21474456787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37050628662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29601192474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39759349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81747531890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97323703765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76329708099365</t>
+    <t xml:space="preserve">8.16733837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21474361419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37050437927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29601097106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39759540557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81747627258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97323608398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76329612731934</t>
   </si>
   <si>
     <t xml:space="preserve">8.67525768280029</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">8.68202972412109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6955738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80393123626709</t>
+    <t xml:space="preserve">8.69557476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80393028259277</t>
   </si>
   <si>
     <t xml:space="preserve">8.8581075668335</t>
@@ -1037,13 +1037,13 @@
     <t xml:space="preserve">8.74975204467773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79038429260254</t>
+    <t xml:space="preserve">8.79038524627686</t>
   </si>
   <si>
     <t xml:space="preserve">8.88519668579102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96646308898926</t>
+    <t xml:space="preserve">8.96646595001221</t>
   </si>
   <si>
     <t xml:space="preserve">8.91228580474854</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">9.18317699432373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19672107696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29153251647949</t>
+    <t xml:space="preserve">9.19672203063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29153347015381</t>
   </si>
   <si>
     <t xml:space="preserve">9.24412631988525</t>
@@ -1073,16 +1073,16 @@
     <t xml:space="preserve">9.54210567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46761131286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38634490966797</t>
+    <t xml:space="preserve">9.46761035919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38634395599365</t>
   </si>
   <si>
     <t xml:space="preserve">9.52178955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49470043182373</t>
+    <t xml:space="preserve">9.49469947814941</t>
   </si>
   <si>
     <t xml:space="preserve">9.84008502960205</t>
@@ -1091,67 +1091,67 @@
     <t xml:space="preserve">9.86717414855957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88749027252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83331489562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76558876037598</t>
+    <t xml:space="preserve">9.88749122619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83331298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76559066772461</t>
   </si>
   <si>
     <t xml:space="preserve">9.74527454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70464038848877</t>
+    <t xml:space="preserve">9.70463943481445</t>
   </si>
   <si>
     <t xml:space="preserve">9.58273887634277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71818351745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67077827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96875762939453</t>
+    <t xml:space="preserve">9.71818542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67077922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96875667572021</t>
   </si>
   <si>
     <t xml:space="preserve">9.94844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91458129882812</t>
+    <t xml:space="preserve">9.91457939147949</t>
   </si>
   <si>
     <t xml:space="preserve">10.0161628723145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96198654174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92135238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90103530883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2599658966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4451093673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5670099258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4857416152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5128307342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518823623657</t>
+    <t xml:space="preserve">9.96198558807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92135143280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90103626251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2599649429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4451084136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.567008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.485743522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5128326416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518814086914</t>
   </si>
   <si>
     <t xml:space="preserve">11.4383363723755</t>
@@ -1160,52 +1160,52 @@
     <t xml:space="preserve">11.49928855896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3502969741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0726356506348</t>
+    <t xml:space="preserve">11.3502988815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0726346969604</t>
   </si>
   <si>
     <t xml:space="preserve">10.9845952987671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.876238822937</t>
+    <t xml:space="preserve">10.8762397766113</t>
   </si>
   <si>
     <t xml:space="preserve">11.1674470901489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8152904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5850324630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4495878219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5647163391113</t>
+    <t xml:space="preserve">10.8152894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.585033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4495887756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.56471824646</t>
   </si>
   <si>
     <t xml:space="preserve">10.5443983078003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.429271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4699048995972</t>
+    <t xml:space="preserve">10.4292707443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4699039459229</t>
   </si>
   <si>
     <t xml:space="preserve">10.632438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.822060585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9168739318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9913673400879</t>
+    <t xml:space="preserve">10.8220615386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9168729782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9913682937622</t>
   </si>
   <si>
     <t xml:space="preserve">10.8017454147339</t>
@@ -1214,16 +1214,16 @@
     <t xml:space="preserve">10.7204780578613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6256666183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6730728149414</t>
+    <t xml:space="preserve">10.6256656646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6730718612671</t>
   </si>
   <si>
     <t xml:space="preserve">10.8356065750122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9371910095215</t>
+    <t xml:space="preserve">10.9371900558472</t>
   </si>
   <si>
     <t xml:space="preserve">10.998140335083</t>
@@ -1232,34 +1232,34 @@
     <t xml:space="preserve">11.0455455780029</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1268138885498</t>
+    <t xml:space="preserve">11.1268148422241</t>
   </si>
   <si>
     <t xml:space="preserve">10.9304170608521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8423795700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7746572494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7340211868286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5918045043945</t>
+    <t xml:space="preserve">10.8423776626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7746553421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7340230941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5918054580688</t>
   </si>
   <si>
     <t xml:space="preserve">10.5376272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5173110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3615493774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.097430229187</t>
+    <t xml:space="preserve">10.5173101425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3615484237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0974311828613</t>
   </si>
   <si>
     <t xml:space="preserve">9.87394714355469</t>
@@ -1268,16 +1268,16 @@
     <t xml:space="preserve">10.1922426223755</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92812347412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0364799499512</t>
+    <t xml:space="preserve">9.92812442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0364809036255</t>
   </si>
   <si>
     <t xml:space="preserve">10.0567970275879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1245203018188</t>
+    <t xml:space="preserve">10.1245193481445</t>
   </si>
   <si>
     <t xml:space="preserve">10.0838871002197</t>
@@ -1286,28 +1286,28 @@
     <t xml:space="preserve">9.97552967071533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69786739349365</t>
+    <t xml:space="preserve">9.69786834716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.50824451446533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44052028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64369010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66400623321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67755126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55565071105957</t>
+    <t xml:space="preserve">9.44052219390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64368915557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66400527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67755031585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55564975738525</t>
   </si>
   <si>
     <t xml:space="preserve">9.34571075439453</t>
@@ -1319,22 +1319,22 @@
     <t xml:space="preserve">9.13576984405518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23058319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06804847717285</t>
+    <t xml:space="preserve">9.23058223724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06804752349854</t>
   </si>
   <si>
     <t xml:space="preserve">9.17640399932861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33216571807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27798843383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23735427856445</t>
+    <t xml:space="preserve">9.33216667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27798748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23735523223877</t>
   </si>
   <si>
     <t xml:space="preserve">9.1628589630127</t>
@@ -1343,37 +1343,37 @@
     <t xml:space="preserve">9.29830455780029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42697715759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53533458709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62337303161621</t>
+    <t xml:space="preserve">9.42697811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53533363342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62337398529053</t>
   </si>
   <si>
     <t xml:space="preserve">9.79945182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80622291564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77236175537109</t>
+    <t xml:space="preserve">9.80622386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77236270904541</t>
   </si>
   <si>
     <t xml:space="preserve">9.95521259307861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81976890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75881767272949</t>
+    <t xml:space="preserve">9.81976699829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75881862640381</t>
   </si>
   <si>
     <t xml:space="preserve">9.4743824005127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71141147613525</t>
+    <t xml:space="preserve">9.71141242980957</t>
   </si>
   <si>
     <t xml:space="preserve">9.30507659912109</t>
@@ -1382,22 +1382,22 @@
     <t xml:space="preserve">9.01387023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79715728759766</t>
+    <t xml:space="preserve">8.79715824127197</t>
   </si>
   <si>
     <t xml:space="preserve">9.03418636322021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39311599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26281547546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29120635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24152088165283</t>
+    <t xml:space="preserve">9.39311695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26281452178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2912073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24152278900146</t>
   </si>
   <si>
     <t xml:space="preserve">9.1137580871582</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">9.14924812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05697536468506</t>
+    <t xml:space="preserve">9.05697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">9.07116985321045</t>
@@ -1415,22 +1415,22 @@
     <t xml:space="preserve">9.03567981719971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99309349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04277801513672</t>
+    <t xml:space="preserve">8.99309253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04277896881104</t>
   </si>
   <si>
     <t xml:space="preserve">9.021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19183349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27701091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39767551422119</t>
+    <t xml:space="preserve">9.19183540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27700996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39767646789551</t>
   </si>
   <si>
     <t xml:space="preserve">9.2131290435791</t>
@@ -1439,31 +1439,31 @@
     <t xml:space="preserve">9.10665988922119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12795257568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22732448577881</t>
+    <t xml:space="preserve">9.12795448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22732543945312</t>
   </si>
   <si>
     <t xml:space="preserve">9.26991271972656</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12085628509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17763900756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38348007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44026470184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4118709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60351657867432</t>
+    <t xml:space="preserve">9.1208553314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17763996124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3834810256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44026279449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41187191009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.603515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.7028865814209</t>
@@ -1481,28 +1481,28 @@
     <t xml:space="preserve">9.6815938949585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57512474060059</t>
+    <t xml:space="preserve">9.57512378692627</t>
   </si>
   <si>
     <t xml:space="preserve">9.66029930114746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53253746032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45446014404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50414562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30540180206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34799098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28410720825195</t>
+    <t xml:space="preserve">9.53253650665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45445823669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50414371490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3054027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34799003601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28410816192627</t>
   </si>
   <si>
     <t xml:space="preserve">9.24861907958984</t>
@@ -1514,49 +1514,49 @@
     <t xml:space="preserve">8.8227424621582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71627235412598</t>
+    <t xml:space="preserve">8.71627330780029</t>
   </si>
   <si>
     <t xml:space="preserve">8.68078327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78725337982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97889709472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01438617706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14214897155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23442363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29830551147461</t>
+    <t xml:space="preserve">8.78725242614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97889614105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01438522338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14214992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23442459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29830646514893</t>
   </si>
   <si>
     <t xml:space="preserve">9.3905782699585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42606639862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37638187408447</t>
+    <t xml:space="preserve">9.42606735229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37638092041016</t>
   </si>
   <si>
     <t xml:space="preserve">9.16344261169434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04987525939941</t>
+    <t xml:space="preserve">9.04987812042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.17054176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74466419219971</t>
+    <t xml:space="preserve">8.74466514587402</t>
   </si>
   <si>
     <t xml:space="preserve">8.69497966766357</t>
@@ -1568,70 +1568,70 @@
     <t xml:space="preserve">8.48204040527344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39686489105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59560871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49623680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26910305023193</t>
+    <t xml:space="preserve">8.39686679840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59560680389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49623775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26910209655762</t>
   </si>
   <si>
     <t xml:space="preserve">8.26200580596924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2265157699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04196739196777</t>
+    <t xml:space="preserve">8.22651481628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04196834564209</t>
   </si>
   <si>
     <t xml:space="preserve">8.06326198577881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07036113739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93549966812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14843845367432</t>
+    <t xml:space="preserve">8.07036018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93549919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1484375</t>
   </si>
   <si>
     <t xml:space="preserve">8.16263389587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2407112121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28329849243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38266944885254</t>
+    <t xml:space="preserve">8.24071025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28329944610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38267040252686</t>
   </si>
   <si>
     <t xml:space="preserve">8.36137580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50333404541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42525768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15634536743164</t>
+    <t xml:space="preserve">8.50333499908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42525672912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15634441375732</t>
   </si>
   <si>
     <t xml:space="preserve">9.08536624908447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06407260894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80854606628418</t>
+    <t xml:space="preserve">9.06407356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8085470199585</t>
   </si>
   <si>
     <t xml:space="preserve">8.81564426422119</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">8.56011962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57431411743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44655132293701</t>
+    <t xml:space="preserve">8.57431316375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4465503692627</t>
   </si>
   <si>
     <t xml:space="preserve">8.52462863922119</t>
@@ -1655,22 +1655,22 @@
     <t xml:space="preserve">8.51753044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40396308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36847305297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21232032775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80144786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60980415344238</t>
+    <t xml:space="preserve">8.40396404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36847400665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43945407867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21231937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80144882202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60980319976807</t>
   </si>
   <si>
     <t xml:space="preserve">8.3400821685791</t>
@@ -1679,40 +1679,40 @@
     <t xml:space="preserve">8.19812393188477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37557125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46074676513672</t>
+    <t xml:space="preserve">8.37557315826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46074771881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.62399959564209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38976669311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5317268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68788242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83693790435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85823059082031</t>
+    <t xml:space="preserve">8.38976860046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53172588348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68788146972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83693885803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85823249816895</t>
   </si>
   <si>
     <t xml:space="preserve">8.90791797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25571632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51124286651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5822229385376</t>
+    <t xml:space="preserve">9.25571727752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5112419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58222198486328</t>
   </si>
   <si>
     <t xml:space="preserve">9.47575378417969</t>
@@ -1721,37 +1721,37 @@
     <t xml:space="preserve">9.35508823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54673290252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66739845275879</t>
+    <t xml:space="preserve">9.54673194885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66739749908447</t>
   </si>
   <si>
     <t xml:space="preserve">9.61061382293701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63190841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51834106445312</t>
+    <t xml:space="preserve">9.63190746307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51833915710449</t>
   </si>
   <si>
     <t xml:space="preserve">9.68869113922119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90872859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85904121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88033485412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75967025756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86613845825195</t>
+    <t xml:space="preserve">9.90872764587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85904216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88033580780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75967121124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86614036560059</t>
   </si>
   <si>
     <t xml:space="preserve">9.85194396972656</t>
@@ -1760,49 +1760,49 @@
     <t xml:space="preserve">10.0222940444946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2423324584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3275060653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.611424446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7604808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6398153305054</t>
+    <t xml:space="preserve">10.2423305511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.327507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6114234924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7604818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6398143768311</t>
   </si>
   <si>
     <t xml:space="preserve">10.6824035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6043262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7107954025269</t>
+    <t xml:space="preserve">10.6043252944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7107963562012</t>
   </si>
   <si>
     <t xml:space="preserve">10.6895008087158</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7746753692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7249908447266</t>
+    <t xml:space="preserve">10.7746782302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7249917984009</t>
   </si>
   <si>
     <t xml:space="preserve">10.7888717651367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7533836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7391862869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178945541382</t>
+    <t xml:space="preserve">10.7533826828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7391872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178936004639</t>
   </si>
   <si>
     <t xml:space="preserve">10.6965990066528</t>
@@ -1814,34 +1814,34 @@
     <t xml:space="preserve">11.356707572937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3709049224854</t>
+    <t xml:space="preserve">11.3709030151367</t>
   </si>
   <si>
     <t xml:space="preserve">11.49866771698</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3141193389893</t>
+    <t xml:space="preserve">11.3141212463379</t>
   </si>
   <si>
     <t xml:space="preserve">11.4418830871582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4276876449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2999238967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1579656600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9876155853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0018110275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1863574981689</t>
+    <t xml:space="preserve">11.4276866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2999248504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1579666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9876136779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0018100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1863565444946</t>
   </si>
   <si>
     <t xml:space="preserve">11.3851003646851</t>
@@ -1850,49 +1850,49 @@
     <t xml:space="preserve">11.4134912490845</t>
   </si>
   <si>
-    <t xml:space="preserve">11.484471321106</t>
+    <t xml:space="preserve">11.4844703674316</t>
   </si>
   <si>
     <t xml:space="preserve">11.4702749252319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6122350692749</t>
+    <t xml:space="preserve">11.6122331619263</t>
   </si>
   <si>
     <t xml:space="preserve">11.5412540435791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8535642623901</t>
+    <t xml:space="preserve">11.8535633087158</t>
   </si>
   <si>
     <t xml:space="preserve">11.938738822937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1090888977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9813270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8677587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8251714706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7399978637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6832122802734</t>
+    <t xml:space="preserve">12.1090898513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9813251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8677597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8251724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7399969100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6832132339478</t>
   </si>
   <si>
     <t xml:space="preserve">11.7967805862427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8961515426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9103488922119</t>
+    <t xml:space="preserve">11.8961524963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9103479385376</t>
   </si>
   <si>
     <t xml:space="preserve">11.8393678665161</t>
@@ -1901,10 +1901,10 @@
     <t xml:space="preserve">11.8819551467896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8109750747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0665016174316</t>
+    <t xml:space="preserve">11.8109769821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.066502571106</t>
   </si>
   <si>
     <t xml:space="preserve">12.1942653656006</t>
@@ -1913,19 +1913,19 @@
     <t xml:space="preserve">12.2794399261475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3078327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3504190444946</t>
+    <t xml:space="preserve">12.3078317642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3504180908203</t>
   </si>
   <si>
     <t xml:space="preserve">12.4355955123901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5065746307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.520770072937</t>
+    <t xml:space="preserve">12.5065755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5207681655884</t>
   </si>
   <si>
     <t xml:space="preserve">12.534966468811</t>
@@ -1934,25 +1934,25 @@
     <t xml:space="preserve">12.5917501449585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6627311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6343364715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7053155899048</t>
+    <t xml:space="preserve">12.6627292633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6343374252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7053165435791</t>
   </si>
   <si>
     <t xml:space="preserve">12.8161840438843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.668360710144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6387968063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3874998092651</t>
+    <t xml:space="preserve">12.6683597564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6387977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3875007629395</t>
   </si>
   <si>
     <t xml:space="preserve">12.3727169036865</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">12.8014011383057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7274894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5353202819824</t>
+    <t xml:space="preserve">12.7274904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5353212356567</t>
   </si>
   <si>
     <t xml:space="preserve">12.5796689987183</t>
@@ -1982,25 +1982,25 @@
     <t xml:space="preserve">12.6831426620483</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8753128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7866172790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7718381881714</t>
+    <t xml:space="preserve">12.8753118515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7866182327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7718372344971</t>
   </si>
   <si>
     <t xml:space="preserve">12.8309659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.934440612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6979265213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7127075195312</t>
+    <t xml:space="preserve">12.9344415664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7127084732056</t>
   </si>
   <si>
     <t xml:space="preserve">12.5944509506226</t>
@@ -2012,19 +2012,19 @@
     <t xml:space="preserve">12.8457469940186</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8900957107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0674819946289</t>
+    <t xml:space="preserve">12.8900947570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0674810409546</t>
   </si>
   <si>
     <t xml:space="preserve">13.1118288040161</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0526990890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9787864685059</t>
+    <t xml:space="preserve">13.052698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9787874221802</t>
   </si>
   <si>
     <t xml:space="preserve">13.1413927078247</t>
@@ -2051,70 +2051,70 @@
     <t xml:space="preserve">12.6092319488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8605289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5501041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4518203735352</t>
+    <t xml:space="preserve">12.8605298995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.550103187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4518184661865</t>
   </si>
   <si>
     <t xml:space="preserve">13.3335628509521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.496166229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3483438491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5405120849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9640064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1857404708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1709566116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9196586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2744312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.259651184082</t>
+    <t xml:space="preserve">13.4961643218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3483428955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5405139923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9640073776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1857395172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1709575653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.919659614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2744302749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2596502304077</t>
   </si>
   <si>
     <t xml:space="preserve">13.2892141342163</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2448663711548</t>
+    <t xml:space="preserve">13.2448682785034</t>
   </si>
   <si>
     <t xml:space="preserve">13.1266098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">13.762246131897</t>
+    <t xml:space="preserve">13.7622480392456</t>
   </si>
   <si>
     <t xml:space="preserve">13.9396324157715</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5552940368652</t>
+    <t xml:space="preserve">13.5552949905396</t>
   </si>
   <si>
     <t xml:space="preserve">13.7474641799927</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9691972732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7770280838013</t>
+    <t xml:space="preserve">13.9691963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.777027130127</t>
   </si>
   <si>
     <t xml:space="preserve">13.6292057037354</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">13.8657197952271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9544124603271</t>
+    <t xml:space="preserve">13.9544153213501</t>
   </si>
   <si>
     <t xml:space="preserve">13.4666013717651</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4813842773438</t>
+    <t xml:space="preserve">13.4813833236694</t>
   </si>
   <si>
     <t xml:space="preserve">13.4370374679565</t>
@@ -2144,31 +2144,31 @@
     <t xml:space="preserve">14.0578889846802</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8213758468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6883335113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6587696075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144218444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5257301330566</t>
+    <t xml:space="preserve">13.8213748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6883354187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6587705612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144237518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5257291793823</t>
   </si>
   <si>
     <t xml:space="preserve">13.3631258010864</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2300834655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8805027008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.457010269165</t>
+    <t xml:space="preserve">13.2300853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.88050365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4570083618164</t>
   </si>
   <si>
     <t xml:space="preserve">14.4717922210693</t>
@@ -2177,79 +2177,79 @@
     <t xml:space="preserve">14.6343946456909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8191728591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0409097671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300413131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0039510726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3735084533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5582838058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9278402328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1126155853271</t>
+    <t xml:space="preserve">14.8191747665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0409088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300422668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0039529800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3735065460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5582857131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9278421401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1126194000244</t>
   </si>
   <si>
     <t xml:space="preserve">16.0387077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7800207138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.706109046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6321973800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5213279724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4104642868042</t>
+    <t xml:space="preserve">15.7800197601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7061080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6321954727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5213289260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4104633331299</t>
   </si>
   <si>
     <t xml:space="preserve">15.4474182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2256851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2626399993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8908834457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9669961929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7378721237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8561296463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4126644134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0874557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3091888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5161371231079</t>
+    <t xml:space="preserve">15.2256860733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.262640953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.890887260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9669971466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7378740310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8561305999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4126625061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0874519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3091878890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5161380767822</t>
   </si>
   <si>
     <t xml:space="preserve">14.5309200286865</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">11.8257741928101</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4710025787354</t>
+    <t xml:space="preserve">11.471001625061</t>
   </si>
   <si>
     <t xml:space="preserve">9.87452125549316</t>
@@ -2267,40 +2267,40 @@
     <t xml:space="preserve">10.2145128250122</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57887840270996</t>
+    <t xml:space="preserve">9.57887649536133</t>
   </si>
   <si>
     <t xml:space="preserve">9.63800621032715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16497421264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29801654815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53453063964844</t>
+    <t xml:space="preserve">9.1649751663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29801464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53453159332275</t>
   </si>
   <si>
     <t xml:space="preserve">9.65278911590576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5545034408569</t>
+    <t xml:space="preserve">10.5545043945312</t>
   </si>
   <si>
     <t xml:space="preserve">10.7023267745972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5988502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9388408660889</t>
+    <t xml:space="preserve">10.5988512039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9388418197632</t>
   </si>
   <si>
     <t xml:space="preserve">10.7318906784058</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9018850326538</t>
+    <t xml:space="preserve">10.9018859863281</t>
   </si>
   <si>
     <t xml:space="preserve">11.2123126983643</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">11.012752532959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0718803405762</t>
+    <t xml:space="preserve">11.0718812942505</t>
   </si>
   <si>
     <t xml:space="preserve">11.3157892227173</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">10.8353662490845</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6801528930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7244997024536</t>
+    <t xml:space="preserve">10.6801538467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7245006561279</t>
   </si>
   <si>
     <t xml:space="preserve">10.6505880355835</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">10.5175485610962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9462327957153</t>
+    <t xml:space="preserve">10.9462337493896</t>
   </si>
   <si>
     <t xml:space="preserve">11.3749170303345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2714414596558</t>
+    <t xml:space="preserve">11.2714405059814</t>
   </si>
   <si>
     <t xml:space="preserve">11.5301303863525</t>
@@ -2354,16 +2354,16 @@
     <t xml:space="preserve">11.6040420532227</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2197036743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5153493881226</t>
+    <t xml:space="preserve">11.219705581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5153474807739</t>
   </si>
   <si>
     <t xml:space="preserve">11.73708152771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1288108825684</t>
+    <t xml:space="preserve">12.128809928894</t>
   </si>
   <si>
     <t xml:space="preserve">12.4318466186523</t>
@@ -2372,19 +2372,19 @@
     <t xml:space="preserve">12.5648860931396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.380108833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4392366409302</t>
+    <t xml:space="preserve">12.3801078796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4392356872559</t>
   </si>
   <si>
     <t xml:space="preserve">12.4096736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7644453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8974866867065</t>
+    <t xml:space="preserve">12.7644462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8974857330322</t>
   </si>
   <si>
     <t xml:space="preserve">12.8235750198364</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">12.971396446228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6070318222046</t>
+    <t xml:space="preserve">13.6070308685303</t>
   </si>
   <si>
     <t xml:space="preserve">13.8065929412842</t>
@@ -2402,52 +2402,52 @@
     <t xml:space="preserve">13.89528465271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0431079864502</t>
+    <t xml:space="preserve">14.0431070327759</t>
   </si>
   <si>
     <t xml:space="preserve">13.5331201553345</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4739923477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.089653968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0600910186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887752532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2966051101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2512521743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4521455764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1353521347046</t>
+    <t xml:space="preserve">13.473991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0896530151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0600891113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887723922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2966041564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2512512207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4521446228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1353530883789</t>
   </si>
   <si>
     <t xml:space="preserve">12.9962720870972</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1585330963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.398060798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2048940658569</t>
+    <t xml:space="preserve">13.1585321426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3980588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.204891204834</t>
   </si>
   <si>
     <t xml:space="preserve">13.4212398529053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5448656082153</t>
+    <t xml:space="preserve">13.544867515564</t>
   </si>
   <si>
     <t xml:space="preserve">13.4444189071655</t>
@@ -2456,25 +2456,25 @@
     <t xml:space="preserve">13.5294132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3594255447388</t>
+    <t xml:space="preserve">13.3594264984131</t>
   </si>
   <si>
     <t xml:space="preserve">13.1276254653931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0812644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9344577789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8108320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9576387405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2976131439209</t>
+    <t xml:space="preserve">13.0812654495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.934458732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8108310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9576396942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2976121902466</t>
   </si>
   <si>
     <t xml:space="preserve">13.150806427002</t>
@@ -2489,136 +2489,136 @@
     <t xml:space="preserve">12.7953777313232</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5944843292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7644729614258</t>
+    <t xml:space="preserve">12.5944833755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7644720077515</t>
   </si>
   <si>
     <t xml:space="preserve">13.328519821167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2126207351685</t>
+    <t xml:space="preserve">13.2126188278198</t>
   </si>
   <si>
     <t xml:space="preserve">13.4366912841797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6453132629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9312000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5062322616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5216865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5371389389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8539323806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8230266571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8848400115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0702800750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6916732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4289646148682</t>
+    <t xml:space="preserve">13.6453123092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9312019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.506233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5216875076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5371408462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8539342880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8230257034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8848390579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0702781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843923568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6916723251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4289655685425</t>
   </si>
   <si>
     <t xml:space="preserve">13.6221323013306</t>
   </si>
   <si>
-    <t xml:space="preserve">13.598952293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2744331359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4675998687744</t>
+    <t xml:space="preserve">13.5989542007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.274432182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4675989151001</t>
   </si>
   <si>
     <t xml:space="preserve">13.7148532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5757732391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3053388595581</t>
+    <t xml:space="preserve">13.5757722854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3053398132324</t>
   </si>
   <si>
     <t xml:space="preserve">13.6298589706421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4753255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7921209335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5680446624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4830513000488</t>
+    <t xml:space="preserve">13.4753265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7921199798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5680465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4830532073975</t>
   </si>
   <si>
     <t xml:space="preserve">13.8462057113647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9234733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9543809890747</t>
+    <t xml:space="preserve">13.9234752655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9543790817261</t>
   </si>
   <si>
     <t xml:space="preserve">13.5912256240845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.367151260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5525922775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7380332946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0007400512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8925666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9080190658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0780076980591</t>
+    <t xml:space="preserve">13.3671531677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5525941848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7380342483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0007419586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8925647735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9080200195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0780057907104</t>
   </si>
   <si>
     <t xml:space="preserve">13.9389276504517</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8616609573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8384790420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0239181518555</t>
+    <t xml:space="preserve">13.8616600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8384780883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0239191055298</t>
   </si>
   <si>
     <t xml:space="preserve">14.047101020813</t>
@@ -2627,28 +2627,28 @@
     <t xml:space="preserve">14.332986831665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1861810684204</t>
+    <t xml:space="preserve">14.1861801147461</t>
   </si>
   <si>
     <t xml:space="preserve">14.1784543991089</t>
   </si>
   <si>
-    <t xml:space="preserve">13.815299987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6994009017944</t>
+    <t xml:space="preserve">13.8152990341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6993980407715</t>
   </si>
   <si>
     <t xml:space="preserve">13.3130655288696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2667055130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2898855209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3748779296875</t>
+    <t xml:space="preserve">13.2667045593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2898864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3748788833618</t>
   </si>
   <si>
     <t xml:space="preserve">13.166259765625</t>
@@ -2657,16 +2657,16 @@
     <t xml:space="preserve">13.7766666412354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7612142562866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7998476028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5835008621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4907789230347</t>
+    <t xml:space="preserve">13.761212348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7998456954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5834999084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907779693604</t>
   </si>
   <si>
     <t xml:space="preserve">13.5139598846436</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">14.0161924362183</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6375865936279</t>
+    <t xml:space="preserve">13.6375856399536</t>
   </si>
   <si>
     <t xml:space="preserve">13.042631149292</t>
@@ -2684,10 +2684,10 @@
     <t xml:space="preserve">12.8880987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8262853622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494644165039</t>
+    <t xml:space="preserve">12.8262844085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494653701782</t>
   </si>
   <si>
     <t xml:space="preserve">12.7567453384399</t>
@@ -2702,16 +2702,16 @@
     <t xml:space="preserve">12.625391960144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6872053146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8031044006348</t>
+    <t xml:space="preserve">12.6872043609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8031053543091</t>
   </si>
   <si>
     <t xml:space="preserve">12.9267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1430797576904</t>
+    <t xml:space="preserve">13.1430788040161</t>
   </si>
   <si>
     <t xml:space="preserve">13.3207931518555</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">13.4135131835938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4057865142822</t>
+    <t xml:space="preserve">13.4057855606079</t>
   </si>
   <si>
     <t xml:space="preserve">13.1817121505737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8417387008667</t>
+    <t xml:space="preserve">12.841739654541</t>
   </si>
   <si>
     <t xml:space="preserve">12.8726444244385</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9190053939819</t>
+    <t xml:space="preserve">12.9190044403076</t>
   </si>
   <si>
     <t xml:space="preserve">12.8571920394897</t>
@@ -2741,40 +2741,40 @@
     <t xml:space="preserve">12.6331186294556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721996307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7490177154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1971645355225</t>
+    <t xml:space="preserve">12.772198677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7490186691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1971654891968</t>
   </si>
   <si>
     <t xml:space="preserve">13.0967197418213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.34397315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9808177947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7181119918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7258377075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6408452987671</t>
+    <t xml:space="preserve">13.3439722061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821588516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9808187484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7181100845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7258386611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6408443450928</t>
   </si>
   <si>
     <t xml:space="preserve">12.6176643371582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7103862762451</t>
+    <t xml:space="preserve">12.7103853225708</t>
   </si>
   <si>
     <t xml:space="preserve">12.4554052352905</t>
@@ -2783,10 +2783,10 @@
     <t xml:space="preserve">12.8803720474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603179931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6839466094971</t>
+    <t xml:space="preserve">13.5603199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6839456558228</t>
   </si>
   <si>
     <t xml:space="preserve">13.9621076583862</t>
@@ -2801,34 +2801,34 @@
     <t xml:space="preserve">14.4102535247803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5570602416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.533881187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4025259017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2402687072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2557220458984</t>
+    <t xml:space="preserve">14.5570621490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5338802337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4025278091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2402677536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2557210922241</t>
   </si>
   <si>
     <t xml:space="preserve">14.3947992324829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5493335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9588489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1211080551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8043146133423</t>
+    <t xml:space="preserve">14.5493354797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9588479995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1211061477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8043155670166</t>
   </si>
   <si>
     <t xml:space="preserve">14.6343288421631</t>
@@ -2837,28 +2837,28 @@
     <t xml:space="preserve">14.7656812667847</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7579545974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6806879043579</t>
+    <t xml:space="preserve">14.7579555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6806869506836</t>
   </si>
   <si>
     <t xml:space="preserve">14.5261545181274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6961402893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6420555114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5725126266479</t>
+    <t xml:space="preserve">14.696141242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6420545578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5725145339966</t>
   </si>
   <si>
     <t xml:space="preserve">14.6034212112427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5956926345825</t>
+    <t xml:space="preserve">14.5956945419312</t>
   </si>
   <si>
     <t xml:space="preserve">14.657506942749</t>
@@ -2867,58 +2867,58 @@
     <t xml:space="preserve">14.8352222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9974813461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1983766555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0824756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0283880233765</t>
+    <t xml:space="preserve">14.9974822998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1983757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0824747085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0283899307251</t>
   </si>
   <si>
     <t xml:space="preserve">15.0979290008545</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1751947402954</t>
+    <t xml:space="preserve">15.175196647644</t>
   </si>
   <si>
     <t xml:space="preserve">15.2061033248901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0747489929199</t>
+    <t xml:space="preserve">15.0747470855713</t>
   </si>
   <si>
     <t xml:space="preserve">14.8506736755371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8661289215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9743022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0592937469482</t>
+    <t xml:space="preserve">14.8661279678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9743003845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0592947006226</t>
   </si>
   <si>
     <t xml:space="preserve">15.0052080154419</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9279413223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1520147323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.414722442627</t>
+    <t xml:space="preserve">14.9279403686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1520166397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4147233963013</t>
   </si>
   <si>
     <t xml:space="preserve">15.8551435470581</t>
   </si>
   <si>
-    <t xml:space="preserve">15.808783531189</t>
+    <t xml:space="preserve">15.8087825775146</t>
   </si>
   <si>
     <t xml:space="preserve">15.6233406066895</t>
@@ -2927,13 +2927,13 @@
     <t xml:space="preserve">15.7624235153198</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9169588088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0714874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9787683486938</t>
+    <t xml:space="preserve">15.9169569015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0714893341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9787702560425</t>
   </si>
   <si>
     <t xml:space="preserve">15.8860483169556</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">15.9942235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1796627044678</t>
+    <t xml:space="preserve">16.179666519165</t>
   </si>
   <si>
     <t xml:space="preserve">16.056037902832</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">16.3496494293213</t>
   </si>
   <si>
-    <t xml:space="preserve">16.457820892334</t>
+    <t xml:space="preserve">16.4578247070312</t>
   </si>
   <si>
     <t xml:space="preserve">16.2651462554932</t>
@@ -2960,13 +2960,13 @@
     <t xml:space="preserve">16.0564136505127</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8476781845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7834539413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8717641830444</t>
+    <t xml:space="preserve">15.8476800918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7834548950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8717632293701</t>
   </si>
   <si>
     <t xml:space="preserve">15.6871166229248</t>
@@ -2984,22 +2984,22 @@
     <t xml:space="preserve">15.7192287445068</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7673969268799</t>
+    <t xml:space="preserve">15.7673988342285</t>
   </si>
   <si>
     <t xml:space="preserve">16.1045818328857</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5988054275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5827493667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7112007141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7272548675537</t>
+    <t xml:space="preserve">15.5988063812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7111978530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.727255821228</t>
   </si>
   <si>
     <t xml:space="preserve">15.5907773971558</t>
@@ -3008,28 +3008,28 @@
     <t xml:space="preserve">15.5104942321777</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2134532928467</t>
+    <t xml:space="preserve">15.213451385498</t>
   </si>
   <si>
     <t xml:space="preserve">15.2616195678711</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4703559875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6630325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8557081222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7352828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9119052886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0162715911865</t>
+    <t xml:space="preserve">15.4703531265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6630296707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8557071685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7352848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.911904335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0162734985352</t>
   </si>
   <si>
     <t xml:space="preserve">15.7754259109497</t>
@@ -3041,10 +3041,10 @@
     <t xml:space="preserve">16.2490901947021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3454303741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.538106918335</t>
+    <t xml:space="preserve">16.3454284667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5381050109863</t>
   </si>
   <si>
     <t xml:space="preserve">16.6665573120117</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">16.9876842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0679664611816</t>
+    <t xml:space="preserve">17.0679683685303</t>
   </si>
   <si>
     <t xml:space="preserve">16.9074020385742</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">16.0724697113037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4096546173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2009220123291</t>
+    <t xml:space="preserve">16.4096565246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2009201049805</t>
   </si>
   <si>
     <t xml:space="preserve">16.3133144378662</t>
@@ -3080,85 +3080,85 @@
     <t xml:space="preserve">16.1366958618164</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3293704986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0885257720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0483856201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9841594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2812042236328</t>
+    <t xml:space="preserve">16.3293724060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0885276794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0483837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9841585159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2812023162842</t>
   </si>
   <si>
     <t xml:space="preserve">16.2972583770752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1527538299561</t>
+    <t xml:space="preserve">16.1527519226074</t>
   </si>
   <si>
     <t xml:space="preserve">15.8637361526489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3981008529663</t>
+    <t xml:space="preserve">15.3981018066406</t>
   </si>
   <si>
     <t xml:space="preserve">15.1090850830078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.916407585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8040142059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9806346893311</t>
+    <t xml:space="preserve">14.9164085388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8040132522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9806327819824</t>
   </si>
   <si>
     <t xml:space="preserve">14.9886627197266</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9645757675171</t>
+    <t xml:space="preserve">14.9645767211914</t>
   </si>
   <si>
     <t xml:space="preserve">14.7478170394897</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8923225402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8120422363281</t>
+    <t xml:space="preserve">14.8923234939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8120412826538</t>
   </si>
   <si>
     <t xml:space="preserve">14.900351524353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8521823883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1010570526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6755619049072</t>
+    <t xml:space="preserve">14.8521814346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.101056098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6755638122559</t>
   </si>
   <si>
     <t xml:space="preserve">14.7879571914673</t>
   </si>
   <si>
-    <t xml:space="preserve">15.117112159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2375354766846</t>
+    <t xml:space="preserve">15.1171140670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2375364303589</t>
   </si>
   <si>
     <t xml:space="preserve">15.0930290222168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2937326431274</t>
+    <t xml:space="preserve">15.2937316894531</t>
   </si>
   <si>
     <t xml:space="preserve">15.3900709152222</t>
@@ -3167,46 +3167,46 @@
     <t xml:space="preserve">15.0609149932861</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0368299484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3419027328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2535915374756</t>
+    <t xml:space="preserve">15.0368309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3419036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2535924911499</t>
   </si>
   <si>
     <t xml:space="preserve">15.197395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5345792770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1251401901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769720077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1492252349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8441543579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076749801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6113376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6595048904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1858406066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3062648773193</t>
+    <t xml:space="preserve">15.5345802307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1251430511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769729614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1492261886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8441534042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076759338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6113357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6595039367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1858396530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.306263923645</t>
   </si>
   <si>
     <t xml:space="preserve">14.3544330596924</t>
@@ -3218,43 +3218,43 @@
     <t xml:space="preserve">14.3464059829712</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3142929077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6996469497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.61936378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5551376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5230255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5471105575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273927688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8200693130493</t>
+    <t xml:space="preserve">14.3142919540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6996459960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6193618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5551385879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5230264663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5471124649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273918151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8200674057007</t>
   </si>
   <si>
     <t xml:space="preserve">14.9244365692139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5711936950684</t>
+    <t xml:space="preserve">14.5711946487427</t>
   </si>
   <si>
     <t xml:space="preserve">14.3785171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2259817123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1617565155029</t>
+    <t xml:space="preserve">14.225980758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1617546081543</t>
   </si>
   <si>
     <t xml:space="preserve">14.0493621826172</t>
@@ -3263,10 +3263,10 @@
     <t xml:space="preserve">14.193868637085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8325996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.744291305542</t>
+    <t xml:space="preserve">13.8326005935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7442903518677</t>
   </si>
   <si>
     <t xml:space="preserve">13.8486566543579</t>
@@ -3275,31 +3275,31 @@
     <t xml:space="preserve">13.8085155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5355567932129</t>
+    <t xml:space="preserve">13.5355558395386</t>
   </si>
   <si>
     <t xml:space="preserve">13.5917530059814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8406286239624</t>
+    <t xml:space="preserve">13.8406276702881</t>
   </si>
   <si>
     <t xml:space="preserve">13.9690790176392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3704881668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3303499221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2179536819458</t>
+    <t xml:space="preserve">14.3704891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3303489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2179527282715</t>
   </si>
   <si>
     <t xml:space="preserve">13.8727416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6479511260986</t>
+    <t xml:space="preserve">13.6479520797729</t>
   </si>
   <si>
     <t xml:space="preserve">13.2947092056274</t>
@@ -3311,10 +3311,10 @@
     <t xml:space="preserve">13.5034437179565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2465400695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.415132522583</t>
+    <t xml:space="preserve">13.2465410232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4151315689087</t>
   </si>
   <si>
     <t xml:space="preserve">13.3187952041626</t>
@@ -3329,19 +3329,19 @@
     <t xml:space="preserve">13.085976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2224550247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5756978988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.664008140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.198371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0217504501343</t>
+    <t xml:space="preserve">13.2224569320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5756959915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6640090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1983728408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0217514038086</t>
   </si>
   <si>
     <t xml:space="preserve">12.8611869812012</t>
@@ -3356,10 +3356,10 @@
     <t xml:space="preserve">13.0137224197388</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3589353561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1261177062988</t>
+    <t xml:space="preserve">13.3589363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1261186599731</t>
   </si>
   <si>
     <t xml:space="preserve">12.8210458755493</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">12.6363964080811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9735822677612</t>
+    <t xml:space="preserve">12.9735813140869</t>
   </si>
   <si>
     <t xml:space="preserve">12.9093561172485</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">12.8772439956665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1421747207642</t>
+    <t xml:space="preserve">13.1421756744385</t>
   </si>
   <si>
     <t xml:space="preserve">13.2706260681152</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5516128540039</t>
+    <t xml:space="preserve">13.5516109466553</t>
   </si>
   <si>
     <t xml:space="preserve">13.383020401001</t>
@@ -3395,43 +3395,43 @@
     <t xml:space="preserve">13.4392175674438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3509063720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7202062606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0092191696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8807687759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5596408843994</t>
+    <t xml:space="preserve">13.3509073257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7202043533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.009220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8807697296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5596389770508</t>
   </si>
   <si>
     <t xml:space="preserve">13.5997829437256</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4231615066528</t>
+    <t xml:space="preserve">13.4231605529785</t>
   </si>
   <si>
     <t xml:space="preserve">13.3027381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3749914169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2304840087891</t>
+    <t xml:space="preserve">13.3749923706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2304849624634</t>
   </si>
   <si>
     <t xml:space="preserve">13.0297794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1020317077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0940046310425</t>
+    <t xml:space="preserve">13.102032661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0940036773682</t>
   </si>
   <si>
     <t xml:space="preserve">12.9494962692261</t>
@@ -3446,13 +3446,13 @@
     <t xml:space="preserve">12.5240020751953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6444253921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7969617843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9334411621094</t>
+    <t xml:space="preserve">12.6444244384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7969608306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9334402084351</t>
   </si>
   <si>
     <t xml:space="preserve">12.804988861084</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">13.1341466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9816093444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4633026123047</t>
+    <t xml:space="preserve">12.9816102981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.463303565979</t>
   </si>
   <si>
     <t xml:space="preserve">13.5837249755859</t>
@@ -3482,31 +3482,31 @@
     <t xml:space="preserve">13.2786540985107</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6845664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4838619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3393535614014</t>
+    <t xml:space="preserve">12.6845655441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4838609695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3393526077271</t>
   </si>
   <si>
     <t xml:space="preserve">12.5320301055908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1839189529419</t>
+    <t xml:space="preserve">12.1839199066162</t>
   </si>
   <si>
     <t xml:space="preserve">11.8018445968628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.74241065979</t>
+    <t xml:space="preserve">11.7424116134644</t>
   </si>
   <si>
     <t xml:space="preserve">11.9546747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3112764358521</t>
+    <t xml:space="preserve">12.3112773895264</t>
   </si>
   <si>
     <t xml:space="preserve">12.1075038909912</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">12.2433528900146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9461832046509</t>
+    <t xml:space="preserve">11.9461841583252</t>
   </si>
   <si>
     <t xml:space="preserve">11.98863697052</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">12.0905227661133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9376945495605</t>
+    <t xml:space="preserve">11.9376935958862</t>
   </si>
   <si>
     <t xml:space="preserve">11.6150531768799</t>
@@ -3554,25 +3554,25 @@
     <t xml:space="preserve">11.6575050354004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7509021759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339210510254</t>
+    <t xml:space="preserve">11.750901222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339200973511</t>
   </si>
   <si>
     <t xml:space="preserve">11.8358068466187</t>
   </si>
   <si>
-    <t xml:space="preserve">11.759391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8867502212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9631643295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6744871139526</t>
+    <t xml:space="preserve">11.7593927383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8867492675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9631652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6744861602783</t>
   </si>
   <si>
     <t xml:space="preserve">11.5726003646851</t>
@@ -3584,37 +3584,37 @@
     <t xml:space="preserve">11.5980710983276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5471286773682</t>
+    <t xml:space="preserve">11.5471296310425</t>
   </si>
   <si>
     <t xml:space="preserve">11.581090927124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4707145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3688278198242</t>
+    <t xml:space="preserve">11.4707136154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3688268661499</t>
   </si>
   <si>
     <t xml:space="preserve">11.343355178833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3009033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2499599456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9358100891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6386413574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6301507949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1461896896362</t>
+    <t xml:space="preserve">11.3009042739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2499589920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9358110427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6386404037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6301517486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1461906433105</t>
   </si>
   <si>
     <t xml:space="preserve">10.044303894043</t>
@@ -3635,16 +3635,16 @@
     <t xml:space="preserve">10.0612850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075113296509</t>
+    <t xml:space="preserve">10.3075103759766</t>
   </si>
   <si>
     <t xml:space="preserve">10.1716613769531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0697746276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9169454574585</t>
+    <t xml:space="preserve">10.0697755813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91694641113281</t>
   </si>
   <si>
     <t xml:space="preserve">10.0867567062378</t>
@@ -3662,28 +3662,28 @@
     <t xml:space="preserve">9.26317405700684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53487205505371</t>
+    <t xml:space="preserve">9.53487110137939</t>
   </si>
   <si>
     <t xml:space="preserve">9.27166557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45845699310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7471342086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90845489501953</t>
+    <t xml:space="preserve">9.45845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74713516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90845584869385</t>
   </si>
   <si>
     <t xml:space="preserve">9.56034278869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41600513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36506175994873</t>
+    <t xml:space="preserve">9.4160041809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36506080627441</t>
   </si>
   <si>
     <t xml:space="preserve">9.49241924285889</t>
@@ -3692,40 +3692,40 @@
     <t xml:space="preserve">9.38204288482666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08487319946289</t>
+    <t xml:space="preserve">9.08487224578857</t>
   </si>
   <si>
     <t xml:space="preserve">9.46694755554199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72166347503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0273237228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1037378311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1207189559937</t>
+    <t xml:space="preserve">9.7216625213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.027322769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1037368774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1207180023193</t>
   </si>
   <si>
     <t xml:space="preserve">9.80656909942627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2395868301392</t>
+    <t xml:space="preserve">10.2395858764648</t>
   </si>
   <si>
     <t xml:space="preserve">10.6216602325439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8424139022827</t>
+    <t xml:space="preserve">10.842414855957</t>
   </si>
   <si>
     <t xml:space="preserve">10.8593950271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8254327774048</t>
+    <t xml:space="preserve">10.8254337310791</t>
   </si>
   <si>
     <t xml:space="preserve">10.8678855895996</t>
@@ -3737,25 +3737,25 @@
     <t xml:space="preserve">10.774489402771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8169422149658</t>
+    <t xml:space="preserve">10.8169431686401</t>
   </si>
   <si>
     <t xml:space="preserve">11.0207147598267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0716581344604</t>
+    <t xml:space="preserve">11.0716590881348</t>
   </si>
   <si>
     <t xml:space="preserve">11.2839221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2754306793213</t>
+    <t xml:space="preserve">11.2754316329956</t>
   </si>
   <si>
     <t xml:space="preserve">11.4452409744263</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1395826339722</t>
+    <t xml:space="preserve">11.1395816802979</t>
   </si>
   <si>
     <t xml:space="preserve">11.2075071334839</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">11.173544883728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0292062759399</t>
+    <t xml:space="preserve">11.0292053222656</t>
   </si>
   <si>
     <t xml:space="preserve">11.2584505081177</t>
@@ -3776,37 +3776,37 @@
     <t xml:space="preserve">11.2924127578735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1141119003296</t>
+    <t xml:space="preserve">11.1141109466553</t>
   </si>
   <si>
     <t xml:space="preserve">11.1650543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2414684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.419771194458</t>
+    <t xml:space="preserve">11.2414693832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4197702407837</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858079910278</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3942985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3603372573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376958847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.003734588623</t>
+    <t xml:space="preserve">11.3942995071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3603363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376968383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0037336349487</t>
   </si>
   <si>
     <t xml:space="preserve">11.1226024627686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159986495972</t>
+    <t xml:space="preserve">11.2159976959229</t>
   </si>
   <si>
     <t xml:space="preserve">10.9697723388672</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">11.2244882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4112796783447</t>
+    <t xml:space="preserve">11.411280632019</t>
   </si>
   <si>
     <t xml:space="preserve">11.5216569900513</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">11.5386381149292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9716567993164</t>
+    <t xml:space="preserve">11.9716558456421</t>
   </si>
   <si>
     <t xml:space="preserve">12.1159944534302</t>
@@ -3848,16 +3848,16 @@
     <t xml:space="preserve">12.1329755783081</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2008991241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2263717651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1414670944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0650510787964</t>
+    <t xml:space="preserve">12.2009000778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2263708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1414661407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0650520324707</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056180953979</t>
@@ -3869,16 +3869,16 @@
     <t xml:space="preserve">11.7169399261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.818826675415</t>
+    <t xml:space="preserve">11.8188257217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.5641098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9018487930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5622262954712</t>
+    <t xml:space="preserve">10.9018478393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5622253417969</t>
   </si>
   <si>
     <t xml:space="preserve">10.4263772964478</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">10.604679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8763761520386</t>
+    <t xml:space="preserve">10.8763771057129</t>
   </si>
   <si>
     <t xml:space="preserve">10.6895847320557</t>
@@ -3899,16 +3899,16 @@
     <t xml:space="preserve">10.9867525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914714813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8084516525269</t>
+    <t xml:space="preserve">10.7914705276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8084506988525</t>
   </si>
   <si>
     <t xml:space="preserve">10.8509044647217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6980762481689</t>
+    <t xml:space="preserve">10.6980743408203</t>
   </si>
   <si>
     <t xml:space="preserve">10.6641130447388</t>
@@ -3920,22 +3920,22 @@
     <t xml:space="preserve">10.7999620437622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0122261047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3093938827515</t>
+    <t xml:space="preserve">11.012225151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3093929290771</t>
   </si>
   <si>
     <t xml:space="preserve">11.0886402130127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3773174285889</t>
+    <t xml:space="preserve">11.3773183822632</t>
   </si>
   <si>
     <t xml:space="preserve">11.5046758651733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6320333480835</t>
+    <t xml:space="preserve">11.6320343017578</t>
   </si>
   <si>
     <t xml:space="preserve">11.5131673812866</t>
@@ -3947,13 +3947,13 @@
     <t xml:space="preserve">11.6999578475952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6829767227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7678833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.827317237854</t>
+    <t xml:space="preserve">11.6829776763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7678823471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8273162841797</t>
   </si>
   <si>
     <t xml:space="preserve">11.6374282836914</t>
@@ -5454,6 +5454,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.7999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7199993133545</t>
   </si>
 </sst>
 </file>
@@ -71546,7 +71549,7 @@
     </row>
     <row r="2530">
       <c r="A2530" s="1" t="n">
-        <v>46001.6912731481</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2530" t="n">
         <v>58926</v>
@@ -71567,6 +71570,32 @@
         <v>1813</v>
       </c>
       <c r="H2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46002.6912962963</v>
+      </c>
+      <c r="B2531" t="n">
+        <v>74254</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>21.5400009155273</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>21.7399997711182</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>21.7199993133545</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>1814</v>
+      </c>
+      <c r="H2531" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="1815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="1817">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">ACE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.611008644104</t>
+    <t xml:space="preserve">8.61100769042969</t>
   </si>
   <si>
     <t xml:space="preserve">8.3010368347168</t>
@@ -53,91 +53,91 @@
     <t xml:space="preserve">8.43742370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48081970214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61720848083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80318927764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68540191650391</t>
+    <t xml:space="preserve">8.48082065582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61720752716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80319023132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68540096282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.30723571777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3506326675415</t>
+    <t xml:space="preserve">8.35063171386719</t>
   </si>
   <si>
     <t xml:space="preserve">8.20804500579834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91667175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97246742248535</t>
+    <t xml:space="preserve">7.91667366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97246646881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.13985157012939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15225028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2762393951416</t>
+    <t xml:space="preserve">8.15224933624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27624034881592</t>
   </si>
   <si>
     <t xml:space="preserve">8.3878288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49321937561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50561809539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39402866363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36923217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33203411102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99106550216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59430027008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45791482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31532764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46411323547363</t>
+    <t xml:space="preserve">8.49321746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50561714172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39402770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36923027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33203315734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99106645584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5943021774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45791387557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31532716751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46411514282227</t>
   </si>
   <si>
     <t xml:space="preserve">7.66869497299194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63149833679199</t>
+    <t xml:space="preserve">7.63149929046631</t>
   </si>
   <si>
     <t xml:space="preserve">7.65629720687866</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65009689331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44551563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60050058364868</t>
+    <t xml:space="preserve">7.65009784698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44551610946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.600501537323</t>
   </si>
   <si>
     <t xml:space="preserve">7.68109464645386</t>
@@ -149,25 +149,25 @@
     <t xml:space="preserve">7.68729305267334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6067008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73688840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64389657974243</t>
+    <t xml:space="preserve">7.60670185089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73688936233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64389801025391</t>
   </si>
   <si>
     <t xml:space="preserve">7.57570362091064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53230762481689</t>
+    <t xml:space="preserve">7.53230667114258</t>
   </si>
   <si>
     <t xml:space="preserve">8.0158634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38162899017334</t>
+    <t xml:space="preserve">8.38162994384766</t>
   </si>
   <si>
     <t xml:space="preserve">8.67920207977295</t>
@@ -182,43 +182,43 @@
     <t xml:space="preserve">8.83418750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78459358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46842098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41882705688477</t>
+    <t xml:space="preserve">8.784592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46842193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41882610321045</t>
   </si>
   <si>
     <t xml:space="preserve">8.33823204040527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45602226257324</t>
+    <t xml:space="preserve">8.45602321624756</t>
   </si>
   <si>
     <t xml:space="preserve">8.49941921234131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58620929718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43122482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34443378448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4746208190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24524307250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90427398681641</t>
+    <t xml:space="preserve">8.58621120452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43122673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40642833709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34443283081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47462177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24524211883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90427303314209</t>
   </si>
   <si>
     <t xml:space="preserve">7.87327575683594</t>
@@ -227,40 +227,40 @@
     <t xml:space="preserve">7.73069000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79268407821655</t>
+    <t xml:space="preserve">7.79268264770508</t>
   </si>
   <si>
     <t xml:space="preserve">7.85467767715454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89807462692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96006679534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04685974121094</t>
+    <t xml:space="preserve">7.89807367324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96006870269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04685878753662</t>
   </si>
   <si>
     <t xml:space="preserve">7.99726533889771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96626710891724</t>
+    <t xml:space="preserve">7.96626806259155</t>
   </si>
   <si>
     <t xml:space="preserve">7.86707639694214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78028535842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09025478363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11505317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17704772949219</t>
+    <t xml:space="preserve">7.78028345108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.090256690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1150541305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1770486831665</t>
   </si>
   <si>
     <t xml:space="preserve">8.02206230163574</t>
@@ -269,49 +269,49 @@
     <t xml:space="preserve">7.88567447662354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8298807144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0406608581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00966262817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09645462036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19564723968506</t>
+    <t xml:space="preserve">7.82987976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04065895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00966358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09645557403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19564628601074</t>
   </si>
   <si>
     <t xml:space="preserve">8.23284339904785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18324661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05925941467285</t>
+    <t xml:space="preserve">8.18324756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05925846099854</t>
   </si>
   <si>
     <t xml:space="preserve">7.76168727874756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52610921859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56330299377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42071771621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19133853912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85657072067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96815919876099</t>
+    <t xml:space="preserve">7.5261082649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56330490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42071723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19133901596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85656976699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96815824508667</t>
   </si>
   <si>
     <t xml:space="preserve">6.9743595123291</t>
@@ -320,70 +320,70 @@
     <t xml:space="preserve">7.12314510345459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09073686599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05184936523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1425895690918</t>
+    <t xml:space="preserve">7.09073781967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05184841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14258909225464</t>
   </si>
   <si>
     <t xml:space="preserve">7.05833005905151</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6824049949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37777519226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49444246292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61110877990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08425712585449</t>
+    <t xml:space="preserve">6.68240451812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37777423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49444150924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61110734939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08425664901733</t>
   </si>
   <si>
     <t xml:space="preserve">6.99999666213989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03888559341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93518304824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78610754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370168685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82499742507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86388683319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74073791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91573762893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92869997024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89629316329956</t>
+    <t xml:space="preserve">7.03888607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93518257141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78610849380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7536997795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82499694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8638858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7407374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91573810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92870140075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89629459381104</t>
   </si>
   <si>
     <t xml:space="preserve">7.15555286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14907121658325</t>
+    <t xml:space="preserve">7.14907073974609</t>
   </si>
   <si>
     <t xml:space="preserve">7.58332967758179</t>
@@ -395,106 +395,106 @@
     <t xml:space="preserve">8.0694408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04351425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01110744476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16666221618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17962646484375</t>
+    <t xml:space="preserve">8.04351615905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01110649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16666316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17962551116943</t>
   </si>
   <si>
     <t xml:space="preserve">8.0759220123291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05647850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10184955596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9527759552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82962465286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87499618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90740346908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75833082199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74536609649658</t>
+    <t xml:space="preserve">8.05647754669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10184860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95277500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82962656021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87499523162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90740442276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481151580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75832891464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74536800384521</t>
   </si>
   <si>
     <t xml:space="preserve">7.77129220962524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71943998336792</t>
+    <t xml:space="preserve">7.71944189071655</t>
   </si>
   <si>
     <t xml:space="preserve">7.57684898376465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65462684631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70647811889648</t>
+    <t xml:space="preserve">7.65462589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7064790725708</t>
   </si>
   <si>
     <t xml:space="preserve">7.81666374206543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79073667526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69351530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72592353820801</t>
+    <t xml:space="preserve">7.79073858261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69351577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72592258453369</t>
   </si>
   <si>
     <t xml:space="preserve">7.69999647140503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50555324554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37592363357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39536714553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47314405441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32407140731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25277423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22684907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18147754669189</t>
+    <t xml:space="preserve">7.50555276870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37592267990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39536809921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3240704536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25277519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22684764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18147945404053</t>
   </si>
   <si>
     <t xml:space="preserve">7.20092248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22036695480347</t>
+    <t xml:space="preserve">7.22036838531494</t>
   </si>
   <si>
     <t xml:space="preserve">7.18795967102051</t>
@@ -503,34 +503,34 @@
     <t xml:space="preserve">7.16851568222046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16203355789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19444274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17499542236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07129335403442</t>
+    <t xml:space="preserve">7.16203498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19444131851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1749963760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07129383087158</t>
   </si>
   <si>
     <t xml:space="preserve">6.96758937835693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04536771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98703384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23332977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3499960899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41481113433838</t>
+    <t xml:space="preserve">7.04536867141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98703336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23333072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34999656677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4148120880127</t>
   </si>
   <si>
     <t xml:space="preserve">7.55092191696167</t>
@@ -548,13 +548,13 @@
     <t xml:space="preserve">7.61573696136475</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64814567565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49258995056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38888454437256</t>
+    <t xml:space="preserve">7.64814472198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49259042739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38888502120972</t>
   </si>
   <si>
     <t xml:space="preserve">7.46018218994141</t>
@@ -569,67 +569,67 @@
     <t xml:space="preserve">6.84444189071655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57222127914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59166383743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54629278182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48147821426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43610811233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47823810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52684926986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64999771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53332996368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59814548492432</t>
+    <t xml:space="preserve">6.57222032546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59166479110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54629373550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48147916793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43610858917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47823715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52684831619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64999866485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5333309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59814596176147</t>
   </si>
   <si>
     <t xml:space="preserve">6.52036714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42962741851807</t>
+    <t xml:space="preserve">6.42962694168091</t>
   </si>
   <si>
     <t xml:space="preserve">6.8703670501709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10370063781738</t>
+    <t xml:space="preserve">7.10370111465454</t>
   </si>
   <si>
     <t xml:space="preserve">7.25925636291504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48610830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4342565536499</t>
+    <t xml:space="preserve">7.48610782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43425607681274</t>
   </si>
   <si>
     <t xml:space="preserve">7.42777395248413</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38240432739258</t>
+    <t xml:space="preserve">7.38240480422974</t>
   </si>
   <si>
     <t xml:space="preserve">7.51851558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51203298568726</t>
+    <t xml:space="preserve">7.51203489303589</t>
   </si>
   <si>
     <t xml:space="preserve">7.66759014129639</t>
@@ -641,34 +641,34 @@
     <t xml:space="preserve">7.71295976638794</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89444065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7972207069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84259033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34351539611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40184879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46666288375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4083309173584</t>
+    <t xml:space="preserve">7.89444160461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79721736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84258937835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34351491928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40184736251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46666383743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40832996368408</t>
   </si>
   <si>
     <t xml:space="preserve">7.73888540267944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68703269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62221956253052</t>
+    <t xml:space="preserve">7.68703365325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6222186088562</t>
   </si>
   <si>
     <t xml:space="preserve">7.63518142700195</t>
@@ -677,64 +677,64 @@
     <t xml:space="preserve">7.73240423202515</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77777433395386</t>
+    <t xml:space="preserve">7.77777528762817</t>
   </si>
   <si>
     <t xml:space="preserve">7.83610820770264</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75184869766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62870168685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97221946716309</t>
+    <t xml:space="preserve">7.75184965133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62870121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97221851348877</t>
   </si>
   <si>
     <t xml:space="preserve">7.85555171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92684888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03703212738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09536743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13425731658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20555114746094</t>
+    <t xml:space="preserve">7.9268479347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03703308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09536647796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13425540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20555210113525</t>
   </si>
   <si>
     <t xml:space="preserve">8.28981113433838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24444103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147869110107</t>
+    <t xml:space="preserve">8.24444007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147773742676</t>
   </si>
   <si>
     <t xml:space="preserve">8.22499561309814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27036762237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46481132507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45832920074463</t>
+    <t xml:space="preserve">8.27036666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46481037139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45833015441895</t>
   </si>
   <si>
     <t xml:space="preserve">8.43240356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42592239379883</t>
+    <t xml:space="preserve">8.42592144012451</t>
   </si>
   <si>
     <t xml:space="preserve">8.35462665557861</t>
@@ -743,46 +743,46 @@
     <t xml:space="preserve">8.55555152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52314472198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39351558685303</t>
+    <t xml:space="preserve">8.52314376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39351463317871</t>
   </si>
   <si>
     <t xml:space="preserve">8.47129154205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60740375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6138858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6203670501709</t>
+    <t xml:space="preserve">8.6074047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61388492584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62036609649658</t>
   </si>
   <si>
     <t xml:space="preserve">8.56203269958496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80832862854004</t>
+    <t xml:space="preserve">8.80832958221436</t>
   </si>
   <si>
     <t xml:space="preserve">8.6786994934082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81481170654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84073638916016</t>
+    <t xml:space="preserve">8.81481266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84073734283447</t>
   </si>
   <si>
     <t xml:space="preserve">8.9249963760376</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12592315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17777347564697</t>
+    <t xml:space="preserve">9.12592220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17777442932129</t>
   </si>
   <si>
     <t xml:space="preserve">9.00277423858643</t>
@@ -797,34 +797,34 @@
     <t xml:space="preserve">9.18425559997559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0157356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02869892120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20369815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28147602081299</t>
+    <t xml:space="preserve">9.01573657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02869987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20369911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2814769744873</t>
   </si>
   <si>
     <t xml:space="preserve">9.30740356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34629344940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43703365325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32684707641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43055248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38518238067627</t>
+    <t xml:space="preserve">9.34629249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43703460693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32684803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43055152893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38518047332764</t>
   </si>
   <si>
     <t xml:space="preserve">9.41758823394775</t>
@@ -833,106 +833,106 @@
     <t xml:space="preserve">9.33332824707031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50184726715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50832843780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44351577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54721641540527</t>
+    <t xml:space="preserve">9.5018482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50832939147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44351387023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54721736907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.41110610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35925483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51501846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41343307495117</t>
+    <t xml:space="preserve">9.35925388336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51501655578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41343212127686</t>
   </si>
   <si>
     <t xml:space="preserve">9.59628391265869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50147151947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44729423522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4811544418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21026515960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09513664245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14931583404541</t>
+    <t xml:space="preserve">9.50147247314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44729328155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48115634918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21026611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09513854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14931488037109</t>
   </si>
   <si>
     <t xml:space="preserve">8.98678112030029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83101940155029</t>
+    <t xml:space="preserve">8.83101844787598</t>
   </si>
   <si>
     <t xml:space="preserve">8.84456348419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93937492370605</t>
+    <t xml:space="preserve">8.93937587738037</t>
   </si>
   <si>
     <t xml:space="preserve">8.81070327758789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93260192871094</t>
+    <t xml:space="preserve">8.93260288238525</t>
   </si>
   <si>
     <t xml:space="preserve">9.04096031188965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87165355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04773139953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08159160614014</t>
+    <t xml:space="preserve">8.8716516494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0477294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08159255981445</t>
   </si>
   <si>
     <t xml:space="preserve">9.10190868377686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349311828613</t>
+    <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
     <t xml:space="preserve">9.10868167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12222576141357</t>
+    <t xml:space="preserve">9.12222766876221</t>
   </si>
   <si>
     <t xml:space="preserve">9.0070972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07481861114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87842559814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92583179473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90551376342773</t>
+    <t xml:space="preserve">9.07481956481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8784236907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92582988739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90551471710205</t>
   </si>
   <si>
     <t xml:space="preserve">8.52626705169678</t>
@@ -941,16 +941,16 @@
     <t xml:space="preserve">8.58721828460693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5465841293335</t>
+    <t xml:space="preserve">8.54658508300781</t>
   </si>
   <si>
     <t xml:space="preserve">8.56012916564941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68880081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53981113433838</t>
+    <t xml:space="preserve">8.68880176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5398120880127</t>
   </si>
   <si>
     <t xml:space="preserve">8.44500160217285</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">8.33664512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47209072113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47886371612549</t>
+    <t xml:space="preserve">8.47208976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47886180877686</t>
   </si>
   <si>
     <t xml:space="preserve">8.4111385345459</t>
@@ -971,25 +971,25 @@
     <t xml:space="preserve">8.42468357086182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38404941558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39082336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32987308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28246688842773</t>
+    <t xml:space="preserve">8.38405132293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39082431793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32987213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2824649810791</t>
   </si>
   <si>
     <t xml:space="preserve">8.26892185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24860572814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19442749023438</t>
+    <t xml:space="preserve">8.24860668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19442653656006</t>
   </si>
   <si>
     <t xml:space="preserve">8.16733837127686</t>
@@ -998,34 +998,34 @@
     <t xml:space="preserve">8.21474361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37050437927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29601097106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39759540557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81747627258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97323608398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76329612731934</t>
+    <t xml:space="preserve">8.37050628662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29601001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81747436523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97323703765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76329708099365</t>
   </si>
   <si>
     <t xml:space="preserve">8.67525768280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68202972412109</t>
+    <t xml:space="preserve">8.68202877044678</t>
   </si>
   <si>
     <t xml:space="preserve">8.69557476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80393028259277</t>
+    <t xml:space="preserve">8.80392932891846</t>
   </si>
   <si>
     <t xml:space="preserve">8.8581075668335</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">8.74297904968262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74975204467773</t>
+    <t xml:space="preserve">8.74975299835205</t>
   </si>
   <si>
     <t xml:space="preserve">8.79038524627686</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">8.88519668579102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96646595001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91228580474854</t>
+    <t xml:space="preserve">8.96646404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91228675842285</t>
   </si>
   <si>
     <t xml:space="preserve">8.89196968078613</t>
@@ -1055,13 +1055,13 @@
     <t xml:space="preserve">9.18317699432373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19672203063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29153347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24412631988525</t>
+    <t xml:space="preserve">9.19672012329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29153156280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24412536621094</t>
   </si>
   <si>
     <t xml:space="preserve">9.36602783203125</t>
@@ -1070,25 +1070,25 @@
     <t xml:space="preserve">9.40666103363037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54210567474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46761035919189</t>
+    <t xml:space="preserve">9.54210662841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46761131286621</t>
   </si>
   <si>
     <t xml:space="preserve">9.38634395599365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52178955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49469947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84008502960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86717414855957</t>
+    <t xml:space="preserve">9.52178859710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49470043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84008407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86717319488525</t>
   </si>
   <si>
     <t xml:space="preserve">9.88749122619629</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">9.83331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76559066772461</t>
+    <t xml:space="preserve">9.76558876037598</t>
   </si>
   <si>
     <t xml:space="preserve">9.74527454376221</t>
@@ -1109,46 +1109,46 @@
     <t xml:space="preserve">9.58273887634277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71818542480469</t>
+    <t xml:space="preserve">9.71818447113037</t>
   </si>
   <si>
     <t xml:space="preserve">9.67077922821045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96875667572021</t>
+    <t xml:space="preserve">9.96875762939453</t>
   </si>
   <si>
     <t xml:space="preserve">9.94844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91457939147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0161628723145</t>
+    <t xml:space="preserve">9.91458034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0161647796631</t>
   </si>
   <si>
     <t xml:space="preserve">9.96198558807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92135143280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90103626251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2599649429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4451084136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.567008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.485743522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5128326416016</t>
+    <t xml:space="preserve">9.92135047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90103530883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2599658966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.445107460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5670099258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4857425689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5128316879272</t>
   </si>
   <si>
     <t xml:space="preserve">11.4518814086914</t>
@@ -1157,37 +1157,37 @@
     <t xml:space="preserve">11.4383363723755</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49928855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3502988815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0726346969604</t>
+    <t xml:space="preserve">11.4992876052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3502979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0726337432861</t>
   </si>
   <si>
     <t xml:space="preserve">10.9845952987671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8762397766113</t>
+    <t xml:space="preserve">10.876238822937</t>
   </si>
   <si>
     <t xml:space="preserve">11.1674470901489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8152894973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.585033416748</t>
+    <t xml:space="preserve">10.8152885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5850343704224</t>
   </si>
   <si>
     <t xml:space="preserve">10.4495887756348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56471824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5443983078003</t>
+    <t xml:space="preserve">10.5647172927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5443992614746</t>
   </si>
   <si>
     <t xml:space="preserve">10.4292707443237</t>
@@ -1196,19 +1196,19 @@
     <t xml:space="preserve">10.4699039459229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.632438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8220615386963</t>
+    <t xml:space="preserve">10.6324396133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8220624923706</t>
   </si>
   <si>
     <t xml:space="preserve">10.9168729782104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9913682937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8017454147339</t>
+    <t xml:space="preserve">10.9913673400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8017444610596</t>
   </si>
   <si>
     <t xml:space="preserve">10.7204780578613</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">10.8356065750122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9371900558472</t>
+    <t xml:space="preserve">10.9371891021729</t>
   </si>
   <si>
     <t xml:space="preserve">10.998140335083</t>
@@ -1232,22 +1232,22 @@
     <t xml:space="preserve">11.0455455780029</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1268148422241</t>
+    <t xml:space="preserve">11.1268129348755</t>
   </si>
   <si>
     <t xml:space="preserve">10.9304170608521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8423776626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7746553421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7340230941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5918054580688</t>
+    <t xml:space="preserve">10.842378616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7746562957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7340221405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5918064117432</t>
   </si>
   <si>
     <t xml:space="preserve">10.5376272201538</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">10.5173101425171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3615484237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0974311828613</t>
+    <t xml:space="preserve">10.3615493774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.097430229187</t>
   </si>
   <si>
     <t xml:space="preserve">9.87394714355469</t>
@@ -1274,37 +1274,37 @@
     <t xml:space="preserve">10.0364809036255</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0567970275879</t>
+    <t xml:space="preserve">10.0567979812622</t>
   </si>
   <si>
     <t xml:space="preserve">10.1245193481445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0838871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97552967071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69786834716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50824451446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44052219390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64368915557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66400527954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67755031585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083736419678</t>
+    <t xml:space="preserve">10.0838861465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97552871704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69786739349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50824356079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44052124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64369010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66400718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67755126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083831787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.55564975738525</t>
@@ -1322,256 +1322,256 @@
     <t xml:space="preserve">9.23058223724365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06804752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17640399932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33216667175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27798748016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23735523223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1628589630127</t>
+    <t xml:space="preserve">9.06804847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17640495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3321647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27798843383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23735332489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16286087036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29830551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42697715759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53533363342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62337303161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79945087432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80622291564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77236270904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95521354675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81976795196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75881862640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4743824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71141242980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01387023925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79715824127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03418636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39311599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26281547546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29120635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24152183532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1137580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14924907684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697345733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07117080688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03567981719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99309349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04277896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02148532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19183540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27701091766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39767456054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2131290435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10665988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12795352935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22732448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26991271972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1208553314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17764091491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38348007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44026279449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41187191009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60351657867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70288753509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56092929840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61771297454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65320205688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68159294128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57512474060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66029930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53253841400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45445919036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5041446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30540180206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34799098968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28410816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24861812591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0924654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82274150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71627235412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68078231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78725337982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97889804840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01438522338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14214897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23442363739014</t>
   </si>
   <si>
     <t xml:space="preserve">9.29830455780029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42697811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53533363342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62337398529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79945182800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80622386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77236270904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95521259307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81976699829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75881862640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4743824005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71141242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30507659912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01387023925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79715824127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03418636322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39311695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26281452178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2912073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24152278900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1137580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14924812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07116985321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03567981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99309253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04277896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19183540344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27700996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39767646789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2131290435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10665988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12795448303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22732543945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26991271972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1208553314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17763996124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3834810256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44026279449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41187191009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7028865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56092834472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61771202087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65320205688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6815938949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57512378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66029930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53253650665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45445823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50414371490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3054027557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34799003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28410816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24861907958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09246444702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8227424621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71627330780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68078327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78725242614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97889614105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01438522338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14214992523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23442459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29830646514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3905782699585</t>
+    <t xml:space="preserve">9.39057731628418</t>
   </si>
   <si>
     <t xml:space="preserve">9.42606735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37638092041016</t>
+    <t xml:space="preserve">9.37638187408447</t>
   </si>
   <si>
     <t xml:space="preserve">9.16344261169434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04987812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17054176330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74466514587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69497966766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51043224334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48204040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39686679840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59560680389404</t>
+    <t xml:space="preserve">9.04987716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17054271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74466419219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69497871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51043128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48203945159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39686584472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59560775756836</t>
   </si>
   <si>
     <t xml:space="preserve">8.49623775482178</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">8.22651481628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04196834564209</t>
+    <t xml:space="preserve">8.04196739196777</t>
   </si>
   <si>
     <t xml:space="preserve">8.06326198577881</t>
@@ -1607,22 +1607,22 @@
     <t xml:space="preserve">8.24071025848389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28329944610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38267040252686</t>
+    <t xml:space="preserve">8.28329849243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38266944885254</t>
   </si>
   <si>
     <t xml:space="preserve">8.36137580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50333499908447</t>
+    <t xml:space="preserve">8.50333404541016</t>
   </si>
   <si>
     <t xml:space="preserve">8.42525672912598</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15634441375732</t>
+    <t xml:space="preserve">9.15634536743164</t>
   </si>
   <si>
     <t xml:space="preserve">9.08536624908447</t>
@@ -1631,58 +1631,58 @@
     <t xml:space="preserve">9.06407356262207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8085470199585</t>
+    <t xml:space="preserve">8.80854606628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.81564426422119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65948963165283</t>
+    <t xml:space="preserve">8.65948867797852</t>
   </si>
   <si>
     <t xml:space="preserve">8.56011962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57431316375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4465503692627</t>
+    <t xml:space="preserve">8.57431411743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44655132293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.52462863922119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51753044128418</t>
+    <t xml:space="preserve">8.5175313949585</t>
   </si>
   <si>
     <t xml:space="preserve">8.40396404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36847400665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43945407867432</t>
+    <t xml:space="preserve">8.36847496032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43945217132568</t>
   </si>
   <si>
     <t xml:space="preserve">8.21231937408447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80144882202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60980319976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3400821685791</t>
+    <t xml:space="preserve">8.80144786834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60980415344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34008121490479</t>
   </si>
   <si>
     <t xml:space="preserve">8.19812393188477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37557315826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46074771881104</t>
+    <t xml:space="preserve">8.37557220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46074676513672</t>
   </si>
   <si>
     <t xml:space="preserve">8.62399959564209</t>
@@ -1694,22 +1694,22 @@
     <t xml:space="preserve">8.53172588348389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68788146972656</t>
+    <t xml:space="preserve">8.68788242340088</t>
   </si>
   <si>
     <t xml:space="preserve">8.83693885803223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85823249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90791797637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25571727752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5112419128418</t>
+    <t xml:space="preserve">8.85823154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90791702270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25571632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51124286651611</t>
   </si>
   <si>
     <t xml:space="preserve">9.58222198486328</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">9.47575378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35508823394775</t>
+    <t xml:space="preserve">9.35508728027344</t>
   </si>
   <si>
     <t xml:space="preserve">9.54673194885254</t>
@@ -1733,43 +1733,43 @@
     <t xml:space="preserve">9.63190746307373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51833915710449</t>
+    <t xml:space="preserve">9.51834011077881</t>
   </si>
   <si>
     <t xml:space="preserve">9.68869113922119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90872764587402</t>
+    <t xml:space="preserve">9.90872859954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.85904216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88033580780029</t>
+    <t xml:space="preserve">9.88033485412598</t>
   </si>
   <si>
     <t xml:space="preserve">9.75967121124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86614036560059</t>
+    <t xml:space="preserve">9.86613941192627</t>
   </si>
   <si>
     <t xml:space="preserve">9.85194396972656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0222940444946</t>
+    <t xml:space="preserve">10.0222930908203</t>
   </si>
   <si>
     <t xml:space="preserve">10.2423305511475</t>
   </si>
   <si>
-    <t xml:space="preserve">10.327507019043</t>
+    <t xml:space="preserve">10.3275060653687</t>
   </si>
   <si>
     <t xml:space="preserve">10.6114234924316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7604818344116</t>
+    <t xml:space="preserve">10.7604808807373</t>
   </si>
   <si>
     <t xml:space="preserve">10.6398143768311</t>
@@ -1778,31 +1778,31 @@
     <t xml:space="preserve">10.6824035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6043252944946</t>
+    <t xml:space="preserve">10.6043262481689</t>
   </si>
   <si>
     <t xml:space="preserve">10.7107963562012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6895008087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7746782302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7249917984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7888717651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7533826828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7391872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178936004639</t>
+    <t xml:space="preserve">10.6895027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7746772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7249898910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.788872718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7533836364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7391862869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178945541382</t>
   </si>
   <si>
     <t xml:space="preserve">10.6965990066528</t>
@@ -1814,19 +1814,19 @@
     <t xml:space="preserve">11.356707572937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3709030151367</t>
+    <t xml:space="preserve">11.370903968811</t>
   </si>
   <si>
     <t xml:space="preserve">11.49866771698</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3141212463379</t>
+    <t xml:space="preserve">11.3141193389893</t>
   </si>
   <si>
     <t xml:space="preserve">11.4418830871582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4276866912842</t>
+    <t xml:space="preserve">11.4276876449585</t>
   </si>
   <si>
     <t xml:space="preserve">11.2999248504639</t>
@@ -1835,10 +1835,10 @@
     <t xml:space="preserve">11.1579666137695</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9876136779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0018100738525</t>
+    <t xml:space="preserve">10.9876155853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0018110275269</t>
   </si>
   <si>
     <t xml:space="preserve">11.1863565444946</t>
@@ -1850,19 +1850,19 @@
     <t xml:space="preserve">11.4134912490845</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4844703674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4702749252319</t>
+    <t xml:space="preserve">11.484471321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4702758789062</t>
   </si>
   <si>
     <t xml:space="preserve">11.6122331619263</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5412540435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8535633087158</t>
+    <t xml:space="preserve">11.5412549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8535642623901</t>
   </si>
   <si>
     <t xml:space="preserve">11.938738822937</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">12.1090898513794</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9813251495361</t>
+    <t xml:space="preserve">11.9813261032104</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677597045898</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251724243164</t>
+    <t xml:space="preserve">11.8251714706421</t>
   </si>
   <si>
     <t xml:space="preserve">11.7399969100952</t>
@@ -1889,58 +1889,58 @@
     <t xml:space="preserve">11.7967805862427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8961524963379</t>
+    <t xml:space="preserve">11.8961515426636</t>
   </si>
   <si>
     <t xml:space="preserve">11.9103479385376</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8393678665161</t>
+    <t xml:space="preserve">11.8393688201904</t>
   </si>
   <si>
     <t xml:space="preserve">11.8819551467896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8109769821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.066502571106</t>
+    <t xml:space="preserve">11.8109760284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0665016174316</t>
   </si>
   <si>
     <t xml:space="preserve">12.1942653656006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2794399261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3078317642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3504180908203</t>
+    <t xml:space="preserve">12.2794389724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3078327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3504190444946</t>
   </si>
   <si>
     <t xml:space="preserve">12.4355955123901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5065755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5207681655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.534966468811</t>
+    <t xml:space="preserve">12.5065746307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.520770072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5349645614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.5917501449585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6627292633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6343374252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7053165435791</t>
+    <t xml:space="preserve">12.66273021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6343355178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7053146362305</t>
   </si>
   <si>
     <t xml:space="preserve">12.8161840438843</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">12.6683597564697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6387977600098</t>
+    <t xml:space="preserve">12.6387968063354</t>
   </si>
   <si>
     <t xml:space="preserve">12.3875007629395</t>
@@ -1961,22 +1961,22 @@
     <t xml:space="preserve">12.313588142395</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4466285705566</t>
+    <t xml:space="preserve">12.4466276168823</t>
   </si>
   <si>
     <t xml:space="preserve">12.8014011383057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7274904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5353212356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5796689987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7422723770142</t>
+    <t xml:space="preserve">12.7274894714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5353202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5796680450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7422733306885</t>
   </si>
   <si>
     <t xml:space="preserve">12.6831426620483</t>
@@ -1994,28 +1994,28 @@
     <t xml:space="preserve">12.8309659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9344415664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.697925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7127084732056</t>
+    <t xml:space="preserve">12.9344396591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6979265213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7127075195312</t>
   </si>
   <si>
     <t xml:space="preserve">12.5944509506226</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9048757553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8457469940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8900947570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0674810409546</t>
+    <t xml:space="preserve">12.9048767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8457479476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8900957107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0674819946289</t>
   </si>
   <si>
     <t xml:space="preserve">13.1118288040161</t>
@@ -2027,25 +2027,25 @@
     <t xml:space="preserve">12.9787874221802</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1413927078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0970449447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0822639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.023136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9492244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1561737060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9935693740845</t>
+    <t xml:space="preserve">13.141393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0970458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0822629928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0231351852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9492235183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1561727523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9935703277588</t>
   </si>
   <si>
     <t xml:space="preserve">12.6092319488525</t>
@@ -2054,37 +2054,37 @@
     <t xml:space="preserve">12.8605298995972</t>
   </si>
   <si>
-    <t xml:space="preserve">12.550103187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4518184661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3335628509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4961643218994</t>
+    <t xml:space="preserve">12.5501041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4518203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3335638046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.496166229248</t>
   </si>
   <si>
     <t xml:space="preserve">13.3483428955078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5405139923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9640073776245</t>
+    <t xml:space="preserve">13.5405111312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9640083312988</t>
   </si>
   <si>
     <t xml:space="preserve">13.1857395172119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1709575653076</t>
+    <t xml:space="preserve">13.1709566116333</t>
   </si>
   <si>
     <t xml:space="preserve">12.919659614563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2744302749634</t>
+    <t xml:space="preserve">13.2744312286377</t>
   </si>
   <si>
     <t xml:space="preserve">13.2596502304077</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">13.2892141342163</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2448682785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1266098022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7622480392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9396324157715</t>
+    <t xml:space="preserve">13.2448673248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1266107559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7622451782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9396343231201</t>
   </si>
   <si>
     <t xml:space="preserve">13.5552949905396</t>
@@ -2111,31 +2111,31 @@
     <t xml:space="preserve">13.7474641799927</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9691963195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.777027130127</t>
+    <t xml:space="preserve">13.9691972732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7770261764526</t>
   </si>
   <si>
     <t xml:space="preserve">13.6292057037354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8657197952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9544153213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4666013717651</t>
+    <t xml:space="preserve">13.8657207489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9544134140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4666004180908</t>
   </si>
   <si>
     <t xml:space="preserve">13.4813833236694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4370374679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918100357056</t>
+    <t xml:space="preserve">13.4370365142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918090820312</t>
   </si>
   <si>
     <t xml:space="preserve">13.998761177063</t>
@@ -2144,61 +2144,61 @@
     <t xml:space="preserve">14.0578889846802</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8213748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6883354187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6587705612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144237518311</t>
+    <t xml:space="preserve">13.8213758468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6883344650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6587696075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144218444824</t>
   </si>
   <si>
     <t xml:space="preserve">13.5257291793823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3631258010864</t>
+    <t xml:space="preserve">13.3631267547607</t>
   </si>
   <si>
     <t xml:space="preserve">13.2300853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.88050365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4570083618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4717922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6343946456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8191747665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0409088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300422668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0039529800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3735065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5582857131958</t>
+    <t xml:space="preserve">13.8805027008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4570093154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.471791267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6343965530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8191728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0409107208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300413131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0039520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3735046386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5582838058472</t>
   </si>
   <si>
     <t xml:space="preserve">15.9278421401978</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1126194000244</t>
+    <t xml:space="preserve">16.1126174926758</t>
   </si>
   <si>
     <t xml:space="preserve">16.0387077331543</t>
@@ -2222,37 +2222,37 @@
     <t xml:space="preserve">15.4474182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2256860733032</t>
+    <t xml:space="preserve">15.2256841659546</t>
   </si>
   <si>
     <t xml:space="preserve">15.262640953064</t>
   </si>
   <si>
-    <t xml:space="preserve">15.890887260437</t>
+    <t xml:space="preserve">15.8908853530884</t>
   </si>
   <si>
     <t xml:space="preserve">14.9669971466064</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7378740310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8561305999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4126625061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0874519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3091878890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5161380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5309200286865</t>
+    <t xml:space="preserve">14.7378730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8561296463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4126634597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0874547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3091888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5161361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5309228897095</t>
   </si>
   <si>
     <t xml:space="preserve">11.8257741928101</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">10.2145128250122</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57887649536133</t>
+    <t xml:space="preserve">9.57887744903564</t>
   </si>
   <si>
     <t xml:space="preserve">9.63800621032715</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">9.29801464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53453159332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65278911590576</t>
+    <t xml:space="preserve">9.53453063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65278816223145</t>
   </si>
   <si>
     <t xml:space="preserve">10.5545043945312</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">10.7023267745972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5988512039185</t>
+    <t xml:space="preserve">10.5988521575928</t>
   </si>
   <si>
     <t xml:space="preserve">10.9388418197632</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">10.8353662490845</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6801538467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7245006561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6505880355835</t>
+    <t xml:space="preserve">10.6801519393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7244997024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6505889892578</t>
   </si>
   <si>
     <t xml:space="preserve">10.5175485610962</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">11.3749170303345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2714405059814</t>
+    <t xml:space="preserve">11.2714414596558</t>
   </si>
   <si>
     <t xml:space="preserve">11.5301303863525</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">11.9735975265503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6040420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.219705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5153474807739</t>
+    <t xml:space="preserve">11.6040410995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2197046279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5153484344482</t>
   </si>
   <si>
     <t xml:space="preserve">11.73708152771</t>
@@ -2369,25 +2369,25 @@
     <t xml:space="preserve">12.4318466186523</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5648860931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3801078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4392356872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4096736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7644462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8974857330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8235750198364</t>
+    <t xml:space="preserve">12.5648851394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.380108833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4392366409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4096727371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7644453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8974866867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8235759735107</t>
   </si>
   <si>
     <t xml:space="preserve">12.971396446228</t>
@@ -2396,40 +2396,40 @@
     <t xml:space="preserve">13.6070308685303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8065929412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.89528465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0431070327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5331201553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.473991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0896530151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0600891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887723922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2966041564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2512512207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4521446228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1353530883789</t>
+    <t xml:space="preserve">13.8065938949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8952836990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0431089401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5331211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4739904403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.089653968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0600910186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2966060638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2512521743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4521465301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1353521347046</t>
   </si>
   <si>
     <t xml:space="preserve">12.9962720870972</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">13.204891204834</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4212398529053</t>
+    <t xml:space="preserve">13.421238899231</t>
   </si>
   <si>
     <t xml:space="preserve">13.544867515564</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">12.8108310699463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9576396942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2976121902466</t>
+    <t xml:space="preserve">12.9576387405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2976112365723</t>
   </si>
   <si>
     <t xml:space="preserve">13.150806427002</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">13.3362464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1894388198853</t>
+    <t xml:space="preserve">13.1894378662109</t>
   </si>
   <si>
     <t xml:space="preserve">12.7953777313232</t>
@@ -2495,58 +2495,58 @@
     <t xml:space="preserve">12.7644720077515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.328519821167</t>
+    <t xml:space="preserve">13.3285188674927</t>
   </si>
   <si>
     <t xml:space="preserve">13.2126188278198</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4366912841797</t>
+    <t xml:space="preserve">13.436692237854</t>
   </si>
   <si>
     <t xml:space="preserve">13.6453123092651</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9312019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.506233215332</t>
+    <t xml:space="preserve">13.9312009811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5062322616577</t>
   </si>
   <si>
     <t xml:space="preserve">13.5216875076294</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5371408462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8539342880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8230257034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8848390579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0702781677246</t>
+    <t xml:space="preserve">13.5371398925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8539333343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8230276107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8848400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0702791213989</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843923568726</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6916723251343</t>
+    <t xml:space="preserve">13.6916732788086</t>
   </si>
   <si>
     <t xml:space="preserve">13.4289655685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6221323013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5989542007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.274432182312</t>
+    <t xml:space="preserve">13.6221313476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5989532470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2744331359863</t>
   </si>
   <si>
     <t xml:space="preserve">13.4675989151001</t>
@@ -2558,19 +2558,19 @@
     <t xml:space="preserve">13.5757722854614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3053398132324</t>
+    <t xml:space="preserve">13.3053379058838</t>
   </si>
   <si>
     <t xml:space="preserve">13.6298589706421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4753265380859</t>
+    <t xml:space="preserve">13.4753274917603</t>
   </si>
   <si>
     <t xml:space="preserve">13.7921199798584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5680465698242</t>
+    <t xml:space="preserve">13.5680456161499</t>
   </si>
   <si>
     <t xml:space="preserve">13.4830532073975</t>
@@ -2579,34 +2579,34 @@
     <t xml:space="preserve">13.8462057113647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9234752655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9543790817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5912256240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3671531677246</t>
+    <t xml:space="preserve">13.9234733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9543781280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5912265777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.367151260376</t>
   </si>
   <si>
     <t xml:space="preserve">13.5525941848755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7380342483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0007419586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8925647735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9080200195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0780057907104</t>
+    <t xml:space="preserve">13.7380332946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0007400512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8925657272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9080190658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0780076980591</t>
   </si>
   <si>
     <t xml:space="preserve">13.9389276504517</t>
@@ -2615,25 +2615,25 @@
     <t xml:space="preserve">13.8616600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8384780883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0239191055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.047101020813</t>
+    <t xml:space="preserve">13.8384799957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0239200592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0470991134644</t>
   </si>
   <si>
     <t xml:space="preserve">14.332986831665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1861801147461</t>
+    <t xml:space="preserve">14.1861810684204</t>
   </si>
   <si>
     <t xml:space="preserve">14.1784543991089</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8152990341187</t>
+    <t xml:space="preserve">13.8152980804443</t>
   </si>
   <si>
     <t xml:space="preserve">13.6993980407715</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">13.3130655288696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2667045593262</t>
+    <t xml:space="preserve">13.2667064666748</t>
   </si>
   <si>
     <t xml:space="preserve">13.2898864746094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3748788833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.166259765625</t>
+    <t xml:space="preserve">13.3748769760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1662588119507</t>
   </si>
   <si>
     <t xml:space="preserve">13.7766666412354</t>
@@ -2660,31 +2660,31 @@
     <t xml:space="preserve">13.761212348938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7998456954956</t>
+    <t xml:space="preserve">13.7998476028442</t>
   </si>
   <si>
     <t xml:space="preserve">13.5834999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4907779693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5139598846436</t>
+    <t xml:space="preserve">13.4907789230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5139579772949</t>
   </si>
   <si>
     <t xml:space="preserve">14.0161924362183</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6375856399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.042631149292</t>
+    <t xml:space="preserve">13.6375865936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0426321029663</t>
   </si>
   <si>
     <t xml:space="preserve">12.8880987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8262844085693</t>
+    <t xml:space="preserve">12.8262853622437</t>
   </si>
   <si>
     <t xml:space="preserve">12.8494653701782</t>
@@ -2696,10 +2696,10 @@
     <t xml:space="preserve">12.5867586135864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.625391960144</t>
+    <t xml:space="preserve">12.6022119522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6253910064697</t>
   </si>
   <si>
     <t xml:space="preserve">12.6872043609619</t>
@@ -2711,46 +2711,46 @@
     <t xml:space="preserve">12.9267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1430788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3207931518555</t>
+    <t xml:space="preserve">13.1430778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3207921981812</t>
   </si>
   <si>
     <t xml:space="preserve">13.4135131835938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4057855606079</t>
+    <t xml:space="preserve">13.4057865142822</t>
   </si>
   <si>
     <t xml:space="preserve">13.1817121505737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.841739654541</t>
+    <t xml:space="preserve">12.8417387008667</t>
   </si>
   <si>
     <t xml:space="preserve">12.8726444244385</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9190044403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8571920394897</t>
+    <t xml:space="preserve">12.9190053939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8571910858154</t>
   </si>
   <si>
     <t xml:space="preserve">12.6331186294556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.772198677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7490186691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1971654891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0967197418213</t>
+    <t xml:space="preserve">12.7721996307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7490177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1971664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.096718788147</t>
   </si>
   <si>
     <t xml:space="preserve">13.3439722061157</t>
@@ -2759,22 +2759,22 @@
     <t xml:space="preserve">13.2821588516235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9808187484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7181100845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7258386611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6408443450928</t>
+    <t xml:space="preserve">12.9808177947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.718111038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7258377075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6408452987671</t>
   </si>
   <si>
     <t xml:space="preserve">12.6176643371582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7103853225708</t>
+    <t xml:space="preserve">12.7103862762451</t>
   </si>
   <si>
     <t xml:space="preserve">12.4554052352905</t>
@@ -2783,10 +2783,10 @@
     <t xml:space="preserve">12.8803720474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603199005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6839456558228</t>
+    <t xml:space="preserve">13.5603179931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6839466094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.9621076583862</t>
@@ -2795,43 +2795,43 @@
     <t xml:space="preserve">14.139820098877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.371621131897</t>
+    <t xml:space="preserve">14.3716201782227</t>
   </si>
   <si>
     <t xml:space="preserve">14.4102535247803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5570621490479</t>
+    <t xml:space="preserve">14.5570611953735</t>
   </si>
   <si>
     <t xml:space="preserve">14.5338802337646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4025278091431</t>
+    <t xml:space="preserve">14.4025268554688</t>
   </si>
   <si>
     <t xml:space="preserve">14.2402677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2557210922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3947992324829</t>
+    <t xml:space="preserve">14.2557201385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3948001861572</t>
   </si>
   <si>
     <t xml:space="preserve">14.5493354797363</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9588479995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1211061477661</t>
+    <t xml:space="preserve">14.9588470458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1211080551147</t>
   </si>
   <si>
     <t xml:space="preserve">14.8043155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6343288421631</t>
+    <t xml:space="preserve">14.6343278884888</t>
   </si>
   <si>
     <t xml:space="preserve">14.7656812667847</t>
@@ -2840,34 +2840,34 @@
     <t xml:space="preserve">14.7579555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6806869506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5261545181274</t>
+    <t xml:space="preserve">14.6806859970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5261535644531</t>
   </si>
   <si>
     <t xml:space="preserve">14.696141242981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6420545578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5725145339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6034212112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5956945419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.657506942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8352222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9974822998047</t>
+    <t xml:space="preserve">14.6420564651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5725154876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.603422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5956935882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6575078964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8352212905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9974813461304</t>
   </si>
   <si>
     <t xml:space="preserve">15.1983757019043</t>
@@ -2876,31 +2876,31 @@
     <t xml:space="preserve">15.0824747085571</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0283899307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0979290008545</t>
+    <t xml:space="preserve">15.0283861160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0979270935059</t>
   </si>
   <si>
     <t xml:space="preserve">15.175196647644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2061033248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747470855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8506736755371</t>
+    <t xml:space="preserve">15.2061014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747489929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8506746292114</t>
   </si>
   <si>
     <t xml:space="preserve">14.8661279678345</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9743003845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0592947006226</t>
+    <t xml:space="preserve">14.9743022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0592966079712</t>
   </si>
   <si>
     <t xml:space="preserve">15.0052080154419</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">15.1520166397095</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4147233963013</t>
+    <t xml:space="preserve">15.414722442627</t>
   </si>
   <si>
     <t xml:space="preserve">15.8551435470581</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">15.8087825775146</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6233406066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7624235153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9169569015503</t>
+    <t xml:space="preserve">15.6233425140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7624216079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9169549942017</t>
   </si>
   <si>
     <t xml:space="preserve">16.0714893341064</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">15.9942235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">16.179666519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.056037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3496494293213</t>
+    <t xml:space="preserve">16.1796646118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0560359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3496513366699</t>
   </si>
   <si>
     <t xml:space="preserve">16.4578247070312</t>
@@ -2957,22 +2957,22 @@
     <t xml:space="preserve">16.2651462554932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0564136505127</t>
+    <t xml:space="preserve">16.0564117431641</t>
   </si>
   <si>
     <t xml:space="preserve">15.8476800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7834548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8717632293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6871166229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6469745635986</t>
+    <t xml:space="preserve">15.7834529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8717651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6871147155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6469755172729</t>
   </si>
   <si>
     <t xml:space="preserve">15.5586652755737</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">15.6550025939941</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7192287445068</t>
+    <t xml:space="preserve">15.7192306518555</t>
   </si>
   <si>
     <t xml:space="preserve">15.7673988342285</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">15.5827484130859</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7111978530884</t>
+    <t xml:space="preserve">15.711199760437</t>
   </si>
   <si>
     <t xml:space="preserve">15.727255821228</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">15.5104942321777</t>
   </si>
   <si>
-    <t xml:space="preserve">15.213451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2616195678711</t>
+    <t xml:space="preserve">15.2134532928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2616214752197</t>
   </si>
   <si>
     <t xml:space="preserve">15.4703531265259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6630296707153</t>
+    <t xml:space="preserve">15.663031578064</t>
   </si>
   <si>
     <t xml:space="preserve">15.8557071685791</t>
@@ -3026,40 +3026,40 @@
     <t xml:space="preserve">15.7352848052979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.911904335022</t>
+    <t xml:space="preserve">15.9119062423706</t>
   </si>
   <si>
     <t xml:space="preserve">16.0162734985352</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7754259109497</t>
+    <t xml:space="preserve">15.7754278182983</t>
   </si>
   <si>
     <t xml:space="preserve">15.9921875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2490901947021</t>
+    <t xml:space="preserve">16.2490882873535</t>
   </si>
   <si>
     <t xml:space="preserve">16.3454284667969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5381050109863</t>
+    <t xml:space="preserve">16.5381031036377</t>
   </si>
   <si>
     <t xml:space="preserve">16.6665573120117</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9876842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0679683685303</t>
+    <t xml:space="preserve">16.9876861572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0679664611816</t>
   </si>
   <si>
     <t xml:space="preserve">16.9074020385742</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5702171325684</t>
+    <t xml:space="preserve">16.570219039917</t>
   </si>
   <si>
     <t xml:space="preserve">16.2330322265625</t>
@@ -3074,10 +3074,10 @@
     <t xml:space="preserve">16.2009201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3133144378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1366958618164</t>
+    <t xml:space="preserve">16.3133163452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.136697769165</t>
   </si>
   <si>
     <t xml:space="preserve">16.3293724060059</t>
@@ -3089,10 +3089,10 @@
     <t xml:space="preserve">16.0483837127686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9841585159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2812023162842</t>
+    <t xml:space="preserve">15.9841604232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2812042236328</t>
   </si>
   <si>
     <t xml:space="preserve">16.2972583770752</t>
@@ -3101,52 +3101,52 @@
     <t xml:space="preserve">16.1527519226074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8637361526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3981018066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1090850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9164085388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8040132522583</t>
+    <t xml:space="preserve">15.8637380599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.398099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1090831756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.916407585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8040142059326</t>
   </si>
   <si>
     <t xml:space="preserve">14.9806327819824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9886627197266</t>
+    <t xml:space="preserve">14.9886608123779</t>
   </si>
   <si>
     <t xml:space="preserve">14.9645767211914</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7478170394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8923234939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8120412826538</t>
+    <t xml:space="preserve">14.7478151321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8923225402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8120403289795</t>
   </si>
   <si>
     <t xml:space="preserve">14.900351524353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8521814346313</t>
+    <t xml:space="preserve">14.85218334198</t>
   </si>
   <si>
     <t xml:space="preserve">15.101056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6755638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7879571914673</t>
+    <t xml:space="preserve">14.6755628585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.787956237793</t>
   </si>
   <si>
     <t xml:space="preserve">15.1171140670776</t>
@@ -3155,37 +3155,37 @@
     <t xml:space="preserve">15.2375364303589</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0930290222168</t>
+    <t xml:space="preserve">15.0930271148682</t>
   </si>
   <si>
     <t xml:space="preserve">15.2937316894531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3900709152222</t>
+    <t xml:space="preserve">15.3900728225708</t>
   </si>
   <si>
     <t xml:space="preserve">15.0609149932861</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0368309020996</t>
+    <t xml:space="preserve">15.036828994751</t>
   </si>
   <si>
     <t xml:space="preserve">15.3419036865234</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2535924911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.197395324707</t>
+    <t xml:space="preserve">15.2535905838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1973943710327</t>
   </si>
   <si>
     <t xml:space="preserve">15.5345802307129</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1251430511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769729614258</t>
+    <t xml:space="preserve">15.1251411437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769710540771</t>
   </si>
   <si>
     <t xml:space="preserve">15.1492261886597</t>
@@ -3194,25 +3194,25 @@
     <t xml:space="preserve">14.8441534042358</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7076759338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6113357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6595039367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1858396530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.306263923645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3544330596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5792226791382</t>
+    <t xml:space="preserve">14.7076740264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6113367080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6595048904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1858406066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3062629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3544321060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5792245864868</t>
   </si>
   <si>
     <t xml:space="preserve">14.3464059829712</t>
@@ -3221,37 +3221,37 @@
     <t xml:space="preserve">14.3142919540405</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6996459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6193618774414</t>
+    <t xml:space="preserve">14.6996479034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6193628311157</t>
   </si>
   <si>
     <t xml:space="preserve">14.5551385879517</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5230264663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5471124649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273918151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8200674057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9244365692139</t>
+    <t xml:space="preserve">14.5230255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5471105575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273927688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8200693130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9244356155396</t>
   </si>
   <si>
     <t xml:space="preserve">14.5711946487427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3785171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.225980758667</t>
+    <t xml:space="preserve">14.3785181045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2259817123413</t>
   </si>
   <si>
     <t xml:space="preserve">14.1617546081543</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">14.0493621826172</t>
   </si>
   <si>
-    <t xml:space="preserve">14.193868637085</t>
+    <t xml:space="preserve">14.1938705444336</t>
   </si>
   <si>
     <t xml:space="preserve">13.8326005935669</t>
@@ -3269,16 +3269,16 @@
     <t xml:space="preserve">13.7442903518677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8486566543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8085155487061</t>
+    <t xml:space="preserve">13.8486557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8085165023804</t>
   </si>
   <si>
     <t xml:space="preserve">13.5355558395386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5917530059814</t>
+    <t xml:space="preserve">13.5917539596558</t>
   </si>
   <si>
     <t xml:space="preserve">13.8406276702881</t>
@@ -3287,19 +3287,19 @@
     <t xml:space="preserve">13.9690790176392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3704891204834</t>
+    <t xml:space="preserve">14.3704900741577</t>
   </si>
   <si>
     <t xml:space="preserve">14.3303489685059</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2179527282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8727416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6479520797729</t>
+    <t xml:space="preserve">14.2179536819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8727407455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6479511260986</t>
   </si>
   <si>
     <t xml:space="preserve">13.2947092056274</t>
@@ -3311,16 +3311,16 @@
     <t xml:space="preserve">13.5034437179565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2465410232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4151315689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3187952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4071054458618</t>
+    <t xml:space="preserve">13.2465400695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.415132522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3187942504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4071044921875</t>
   </si>
   <si>
     <t xml:space="preserve">13.1100606918335</t>
@@ -3329,25 +3329,25 @@
     <t xml:space="preserve">13.085976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2224569320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5756959915161</t>
+    <t xml:space="preserve">13.2224559783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5756969451904</t>
   </si>
   <si>
     <t xml:space="preserve">13.6640090942383</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1983728408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0217514038086</t>
+    <t xml:space="preserve">13.198371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0217504501343</t>
   </si>
   <si>
     <t xml:space="preserve">12.8611869812012</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7086505889893</t>
+    <t xml:space="preserve">12.7086515426636</t>
   </si>
   <si>
     <t xml:space="preserve">12.604284286499</t>
@@ -3356,16 +3356,16 @@
     <t xml:space="preserve">13.0137224197388</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3589363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1261186599731</t>
+    <t xml:space="preserve">13.3589353561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1261177062988</t>
   </si>
   <si>
     <t xml:space="preserve">12.8210458755493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6363964080811</t>
+    <t xml:space="preserve">12.6363973617554</t>
   </si>
   <si>
     <t xml:space="preserve">12.9735813140869</t>
@@ -3374,16 +3374,16 @@
     <t xml:space="preserve">12.9093561172485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8772439956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1421756744385</t>
+    <t xml:space="preserve">12.8772449493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1421747207642</t>
   </si>
   <si>
     <t xml:space="preserve">13.2706260681152</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5516109466553</t>
+    <t xml:space="preserve">13.5516119003296</t>
   </si>
   <si>
     <t xml:space="preserve">13.383020401001</t>
@@ -3401,19 +3401,19 @@
     <t xml:space="preserve">13.7202043533325</t>
   </si>
   <si>
-    <t xml:space="preserve">14.009220123291</t>
+    <t xml:space="preserve">14.0092210769653</t>
   </si>
   <si>
     <t xml:space="preserve">13.8807697296143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5596389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5997829437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4231605529785</t>
+    <t xml:space="preserve">13.5596399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5997819900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4231615066528</t>
   </si>
   <si>
     <t xml:space="preserve">13.3027381896973</t>
@@ -3425,19 +3425,19 @@
     <t xml:space="preserve">13.2304849624634</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0297794342041</t>
+    <t xml:space="preserve">13.0297784805298</t>
   </si>
   <si>
     <t xml:space="preserve">13.102032661438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0940036773682</t>
+    <t xml:space="preserve">13.0940046310425</t>
   </si>
   <si>
     <t xml:space="preserve">12.9494962692261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7487916946411</t>
+    <t xml:space="preserve">12.7487926483154</t>
   </si>
   <si>
     <t xml:space="preserve">12.8852710723877</t>
@@ -3446,16 +3446,16 @@
     <t xml:space="preserve">12.5240020751953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6444244384766</t>
+    <t xml:space="preserve">12.6444253921509</t>
   </si>
   <si>
     <t xml:space="preserve">12.7969608306885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9334402084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.804988861084</t>
+    <t xml:space="preserve">12.9334411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8049898147583</t>
   </si>
   <si>
     <t xml:space="preserve">12.9254131317139</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">13.1341466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9816102981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.463303565979</t>
+    <t xml:space="preserve">12.9816093444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4633026123047</t>
   </si>
   <si>
     <t xml:space="preserve">13.5837249755859</t>
@@ -3476,13 +3476,13 @@
     <t xml:space="preserve">13.3268232345581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2064008712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2786540985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6845655441284</t>
+    <t xml:space="preserve">13.2064018249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2786550521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6845664978027</t>
   </si>
   <si>
     <t xml:space="preserve">12.4838609695435</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">11.8018445968628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7424116134644</t>
+    <t xml:space="preserve">11.74241065979</t>
   </si>
   <si>
     <t xml:space="preserve">11.9546747207642</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">12.3112773895264</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1075038909912</t>
+    <t xml:space="preserve">12.1075048446655</t>
   </si>
   <si>
     <t xml:space="preserve">12.158447265625</t>
@@ -3521,13 +3521,13 @@
     <t xml:space="preserve">11.9801454544067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2433528900146</t>
+    <t xml:space="preserve">12.2433519363403</t>
   </si>
   <si>
     <t xml:space="preserve">11.9461841583252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.98863697052</t>
+    <t xml:space="preserve">11.9886360168457</t>
   </si>
   <si>
     <t xml:space="preserve">12.0141077041626</t>
@@ -3542,10 +3542,10 @@
     <t xml:space="preserve">11.6150531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4792041778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556182861328</t>
+    <t xml:space="preserve">11.4792051315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556192398071</t>
   </si>
   <si>
     <t xml:space="preserve">11.6659955978394</t>
@@ -3566,10 +3566,10 @@
     <t xml:space="preserve">11.7593927383423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8867492675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9631652832031</t>
+    <t xml:space="preserve">11.8867502212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9631643295288</t>
   </si>
   <si>
     <t xml:space="preserve">11.6744861602783</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">11.581090927124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4707136154175</t>
+    <t xml:space="preserve">11.4707145690918</t>
   </si>
   <si>
     <t xml:space="preserve">11.3688268661499</t>
@@ -3602,16 +3602,16 @@
     <t xml:space="preserve">11.3009042739868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2499589920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9358110427856</t>
+    <t xml:space="preserve">11.2499599456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9358100891113</t>
   </si>
   <si>
     <t xml:space="preserve">10.6386404037476</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6301517486572</t>
+    <t xml:space="preserve">10.6301507949829</t>
   </si>
   <si>
     <t xml:space="preserve">10.1461906433105</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">10.1886434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86600208282471</t>
+    <t xml:space="preserve">9.86600303649902</t>
   </si>
   <si>
     <t xml:space="preserve">9.71317291259766</t>
@@ -3665,19 +3665,19 @@
     <t xml:space="preserve">9.53487110137939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27166557312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45845794677734</t>
+    <t xml:space="preserve">9.2716646194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45845699310303</t>
   </si>
   <si>
     <t xml:space="preserve">9.74713516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90845584869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56034278869629</t>
+    <t xml:space="preserve">9.90845489501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56034374237061</t>
   </si>
   <si>
     <t xml:space="preserve">9.4160041809082</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">9.38204288482666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08487224578857</t>
+    <t xml:space="preserve">9.08487319946289</t>
   </si>
   <si>
     <t xml:space="preserve">9.46694755554199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7216625213623</t>
+    <t xml:space="preserve">9.72166347503662</t>
   </si>
   <si>
     <t xml:space="preserve">10.027322769165</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">10.1037368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1207180023193</t>
+    <t xml:space="preserve">10.1207189559937</t>
   </si>
   <si>
     <t xml:space="preserve">9.80656909942627</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">11.0716590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2839221954346</t>
+    <t xml:space="preserve">11.2839212417603</t>
   </si>
   <si>
     <t xml:space="preserve">11.2754316329956</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">11.4452409744263</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1395816802979</t>
+    <t xml:space="preserve">11.1395826339722</t>
   </si>
   <si>
     <t xml:space="preserve">11.2075071334839</t>
@@ -3767,13 +3767,13 @@
     <t xml:space="preserve">11.173544883728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0292053222656</t>
+    <t xml:space="preserve">11.0292062759399</t>
   </si>
   <si>
     <t xml:space="preserve">11.2584505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2924127578735</t>
+    <t xml:space="preserve">11.2924118041992</t>
   </si>
   <si>
     <t xml:space="preserve">11.1141109466553</t>
@@ -3797,10 +3797,10 @@
     <t xml:space="preserve">11.3603363037109</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0376968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0037336349487</t>
+    <t xml:space="preserve">11.0376958847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.003734588623</t>
   </si>
   <si>
     <t xml:space="preserve">11.1226024627686</t>
@@ -3812,13 +3812,13 @@
     <t xml:space="preserve">10.9697723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2244882583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.411280632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5216569900513</t>
+    <t xml:space="preserve">11.2244892120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4112796783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.521656036377</t>
   </si>
   <si>
     <t xml:space="preserve">11.5386381149292</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">12.1414661407471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0650520324707</t>
+    <t xml:space="preserve">12.0650510787964</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056180953979</t>
@@ -3875,13 +3875,13 @@
     <t xml:space="preserve">11.5641098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9018478393555</t>
+    <t xml:space="preserve">10.9018487930298</t>
   </si>
   <si>
     <t xml:space="preserve">10.5622253417969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4263772964478</t>
+    <t xml:space="preserve">10.4263782501221</t>
   </si>
   <si>
     <t xml:space="preserve">10.6556224822998</t>
@@ -3908,13 +3908,13 @@
     <t xml:space="preserve">10.8509044647217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6980743408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6641130447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320375442505</t>
+    <t xml:space="preserve">10.6980752944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6641139984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320365905762</t>
   </si>
   <si>
     <t xml:space="preserve">10.7999620437622</t>
@@ -3938,19 +3938,19 @@
     <t xml:space="preserve">11.6320343017578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5131673812866</t>
+    <t xml:space="preserve">11.5131664276123</t>
   </si>
   <si>
     <t xml:space="preserve">11.4622230529785</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6999578475952</t>
+    <t xml:space="preserve">11.6999588012695</t>
   </si>
   <si>
     <t xml:space="preserve">11.6829776763916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7678823471069</t>
+    <t xml:space="preserve">11.7678813934326</t>
   </si>
   <si>
     <t xml:space="preserve">11.8273162841797</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">10.877875328064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7331991195679</t>
+    <t xml:space="preserve">10.7331981658936</t>
   </si>
   <si>
     <t xml:space="preserve">10.8326635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8869171142578</t>
+    <t xml:space="preserve">10.8869180679321</t>
   </si>
   <si>
     <t xml:space="preserve">10.8507490158081</t>
@@ -3995,22 +3995,22 @@
     <t xml:space="preserve">10.6608600616455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3082113265991</t>
+    <t xml:space="preserve">10.3082103729248</t>
   </si>
   <si>
     <t xml:space="preserve">10.1544914245605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.145450592041</t>
+    <t xml:space="preserve">10.1454496383667</t>
   </si>
   <si>
     <t xml:space="preserve">10.3262958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.353422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4167184829712</t>
+    <t xml:space="preserve">10.3534231185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4167194366455</t>
   </si>
   <si>
     <t xml:space="preserve">10.2539577484131</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">10.3805494308472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4890575408936</t>
+    <t xml:space="preserve">10.4890565872192</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">10.0098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.073112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95556259155273</t>
+    <t xml:space="preserve">10.0731115341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95556163787842</t>
   </si>
   <si>
     <t xml:space="preserve">9.8560962677002</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">9.7114200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57578563690186</t>
+    <t xml:space="preserve">9.57578659057617</t>
   </si>
   <si>
     <t xml:space="preserve">9.34068584442139</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">9.43110942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28643321990967</t>
+    <t xml:space="preserve">9.28643226623535</t>
   </si>
   <si>
     <t xml:space="preserve">9.26834774017334</t>
@@ -4073,28 +4073,28 @@
     <t xml:space="preserve">9.30451679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33164310455322</t>
+    <t xml:space="preserve">9.33164405822754</t>
   </si>
   <si>
     <t xml:space="preserve">9.52153205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72046279907227</t>
+    <t xml:space="preserve">9.72046184539795</t>
   </si>
   <si>
     <t xml:space="preserve">9.76567363739014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91034984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91939258575439</t>
+    <t xml:space="preserve">9.91035079956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91939353942871</t>
   </si>
   <si>
     <t xml:space="preserve">9.90130805969238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87418174743652</t>
+    <t xml:space="preserve">9.87418079376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.82896995544434</t>
@@ -4130,10 +4130,10 @@
     <t xml:space="preserve">9.15984058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12367153167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32260131835938</t>
+    <t xml:space="preserve">9.12367057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32260227203369</t>
   </si>
   <si>
     <t xml:space="preserve">9.20505142211914</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">9.89226531982422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84705543518066</t>
+    <t xml:space="preserve">9.84705448150635</t>
   </si>
   <si>
     <t xml:space="preserve">10.0279006958008</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">10.0369424819946</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94651889801025</t>
+    <t xml:space="preserve">9.94651985168457</t>
   </si>
   <si>
     <t xml:space="preserve">10.1906623840332</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">10.4800148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5523538589478</t>
+    <t xml:space="preserve">10.5523529052734</t>
   </si>
   <si>
     <t xml:space="preserve">10.7151145935059</t>
@@ -4187,16 +4187,16 @@
     <t xml:space="preserve">10.4980993270874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.299168586731</t>
+    <t xml:space="preserve">10.2991695404053</t>
   </si>
   <si>
     <t xml:space="preserve">10.2901268005371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1816186904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5704374313354</t>
+    <t xml:space="preserve">10.181619644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5704364776611</t>
   </si>
   <si>
     <t xml:space="preserve">10.7603254318237</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">11.0768060684204</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2124395370483</t>
+    <t xml:space="preserve">11.2124404907227</t>
   </si>
   <si>
     <t xml:space="preserve">11.5560474395752</t>
@@ -4223,19 +4223,19 @@
     <t xml:space="preserve">11.2486085891724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6464710235596</t>
+    <t xml:space="preserve">11.6464700698853</t>
   </si>
   <si>
     <t xml:space="preserve">11.5289211273193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7188081741333</t>
+    <t xml:space="preserve">11.7188091278076</t>
   </si>
   <si>
     <t xml:space="preserve">11.9448661804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9629497528076</t>
+    <t xml:space="preserve">11.9629507064819</t>
   </si>
   <si>
     <t xml:space="preserve">11.9086971282959</t>
@@ -4250,10 +4250,10 @@
     <t xml:space="preserve">12.4783611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5054883956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1528387069702</t>
+    <t xml:space="preserve">12.5054874420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1528377532959</t>
   </si>
   <si>
     <t xml:space="preserve">12.3155994415283</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">12.1709232330322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1799659729004</t>
+    <t xml:space="preserve">12.1799650192261</t>
   </si>
   <si>
     <t xml:space="preserve">12.107626914978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2161340713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2703886032104</t>
+    <t xml:space="preserve">12.2161350250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2703876495361</t>
   </si>
   <si>
     <t xml:space="preserve">12.4874038696289</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">12.650164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4693183898926</t>
+    <t xml:space="preserve">12.4693193435669</t>
   </si>
   <si>
     <t xml:space="preserve">12.595911026001</t>
@@ -4316,16 +4316,16 @@
     <t xml:space="preserve">12.8852643966675</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0751514434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932369232178</t>
+    <t xml:space="preserve">13.0751523971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932359695435</t>
   </si>
   <si>
     <t xml:space="preserve">13.0028142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2198286056519</t>
+    <t xml:space="preserve">13.2198295593262</t>
   </si>
   <si>
     <t xml:space="preserve">12.9304752349854</t>
@@ -4346,16 +4346,16 @@
     <t xml:space="preserve">12.6772918701172</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2613468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5506992340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5778255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4602756500244</t>
+    <t xml:space="preserve">12.2613458633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5507001876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.577826499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4602766036987</t>
   </si>
   <si>
     <t xml:space="preserve">12.3517684936523</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">12.4060230255127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3608121871948</t>
+    <t xml:space="preserve">12.3608112335205</t>
   </si>
   <si>
     <t xml:space="preserve">12.4241065979004</t>
@@ -4391,19 +4391,19 @@
     <t xml:space="preserve">13.5091819763184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2144813537598</t>
+    <t xml:space="preserve">14.2144804000854</t>
   </si>
   <si>
     <t xml:space="preserve">14.1963958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0788459777832</t>
+    <t xml:space="preserve">14.0788469314575</t>
   </si>
   <si>
     <t xml:space="preserve">13.8980007171631</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9793815612793</t>
+    <t xml:space="preserve">13.979380607605</t>
   </si>
   <si>
     <t xml:space="preserve">14.0065078735352</t>
@@ -4424,16 +4424,16 @@
     <t xml:space="preserve">14.6485109329224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8474407196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5671310424805</t>
+    <t xml:space="preserve">14.8474416732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5671300888062</t>
   </si>
   <si>
     <t xml:space="preserve">14.6846799850464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8022308349609</t>
+    <t xml:space="preserve">14.8022298812866</t>
   </si>
   <si>
     <t xml:space="preserve">14.7389326095581</t>
@@ -4448,10 +4448,10 @@
     <t xml:space="preserve">14.1511840820312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1873540878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3049039840698</t>
+    <t xml:space="preserve">14.1873531341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3049030303955</t>
   </si>
   <si>
     <t xml:space="preserve">13.9341697692871</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">14.1421422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.295862197876</t>
+    <t xml:space="preserve">14.2958612442017</t>
   </si>
   <si>
     <t xml:space="preserve">14.4495801925659</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">14.5490455627441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8745679855347</t>
+    <t xml:space="preserve">14.874568939209</t>
   </si>
   <si>
     <t xml:space="preserve">14.7208499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">14.612340927124</t>
+    <t xml:space="preserve">14.6123418807983</t>
   </si>
   <si>
     <t xml:space="preserve">14.6304264068604</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">14.9649896621704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6575527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8926525115967</t>
+    <t xml:space="preserve">14.6575517654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8926515579224</t>
   </si>
   <si>
     <t xml:space="preserve">14.9740324020386</t>
@@ -4514,13 +4514,13 @@
     <t xml:space="preserve">15.082540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4713592529297</t>
+    <t xml:space="preserve">15.471360206604</t>
   </si>
   <si>
     <t xml:space="preserve">15.191047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2633848190308</t>
+    <t xml:space="preserve">15.2633857727051</t>
   </si>
   <si>
     <t xml:space="preserve">15.1458368301392</t>
@@ -4532,16 +4532,16 @@
     <t xml:space="preserve">15.2995548248291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2000894546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3718948364258</t>
+    <t xml:space="preserve">15.2000904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3718938827515</t>
   </si>
   <si>
     <t xml:space="preserve">15.7245426177979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5527391433716</t>
+    <t xml:space="preserve">15.5527410507202</t>
   </si>
   <si>
     <t xml:space="preserve">15.6974172592163</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">15.4171047210693</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2905120849609</t>
+    <t xml:space="preserve">15.2905130386353</t>
   </si>
   <si>
     <t xml:space="preserve">15.0011596679688</t>
@@ -4568,54 +4568,57 @@
     <t xml:space="preserve">14.5128755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6665945053101</t>
+    <t xml:space="preserve">14.6665954589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8112707138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5054912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4672689437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3812675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4577121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4386005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5246019363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2952661514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4099340438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6392698287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7826051712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5150461196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.687047958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1361646652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2890548706055</t>
   </si>
   <si>
     <t xml:space="preserve">14.8112716674805</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5054912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4672689437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3812675476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4577121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4386005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5246019363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2952661514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4099340438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6392698287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7826051712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5150461196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.687047958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1361646652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2890548706055</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.8017158508301</t>
   </si>
   <si>
@@ -5457,6 +5460,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.7199993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8199996948242</t>
   </si>
 </sst>
 </file>
@@ -62285,7 +62291,7 @@
         <v>15.5</v>
       </c>
       <c r="G2173" t="s">
-        <v>1519</v>
+        <v>1534</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62311,7 +62317,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G2174" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62337,7 +62343,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G2175" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62363,7 +62369,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62389,7 +62395,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G2177" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62415,7 +62421,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G2178" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62441,7 +62447,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G2179" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62467,7 +62473,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G2180" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62493,7 +62499,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G2181" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62519,7 +62525,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G2182" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62545,7 +62551,7 @@
         <v>16.5</v>
       </c>
       <c r="G2183" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62571,7 +62577,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2184" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62597,7 +62603,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G2185" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62623,7 +62629,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G2186" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62649,7 +62655,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G2187" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62675,7 +62681,7 @@
         <v>16.25</v>
       </c>
       <c r="G2188" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62701,7 +62707,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G2189" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62727,7 +62733,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2190" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62753,7 +62759,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2191" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62779,7 +62785,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62805,7 +62811,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G2193" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62831,7 +62837,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G2194" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62857,7 +62863,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G2195" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62883,7 +62889,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G2196" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62909,7 +62915,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2197" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62935,7 +62941,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2198" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62961,7 +62967,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G2199" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62987,7 +62993,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2200" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -63013,7 +63019,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G2201" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -63039,7 +63045,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G2202" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63065,7 +63071,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2203" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63091,7 +63097,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2204" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63117,7 +63123,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G2205" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63143,7 +63149,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2206" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63169,7 +63175,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G2207" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63195,7 +63201,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2208" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63221,7 +63227,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G2209" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63247,7 +63253,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2210" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63273,7 +63279,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2211" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63299,7 +63305,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G2212" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63325,7 +63331,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2213" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63351,7 +63357,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2214" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63377,7 +63383,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2215" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63403,7 +63409,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2216" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63429,7 +63435,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G2217" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63455,7 +63461,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G2218" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63481,7 +63487,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G2219" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63507,7 +63513,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2220" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63533,7 +63539,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2221" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63559,7 +63565,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G2222" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63585,7 +63591,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G2223" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63611,7 +63617,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2224" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63637,7 +63643,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G2225" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63663,7 +63669,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G2226" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63689,7 +63695,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G2227" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63715,7 +63721,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G2228" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63741,7 +63747,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2229" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63767,7 +63773,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G2230" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63793,7 +63799,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G2231" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63819,7 +63825,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2232" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63845,7 +63851,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G2233" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63871,7 +63877,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2234" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63897,7 +63903,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G2235" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63923,7 +63929,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G2236" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63949,7 +63955,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G2237" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63975,7 +63981,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2238" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -64001,7 +64007,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G2239" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -64027,7 +64033,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2240" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64053,7 +64059,7 @@
         <v>17.75</v>
       </c>
       <c r="G2241" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64079,7 +64085,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2242" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64105,7 +64111,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2243" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64131,7 +64137,7 @@
         <v>18.5</v>
       </c>
       <c r="G2244" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64157,7 +64163,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G2245" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64183,7 +64189,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2246" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64209,7 +64215,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2247" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64235,7 +64241,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2248" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64261,7 +64267,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64287,7 +64293,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2250" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64313,7 +64319,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2251" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64339,7 +64345,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G2252" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64365,7 +64371,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G2253" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64391,7 +64397,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2254" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64417,7 +64423,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G2255" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64443,7 +64449,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G2256" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64469,7 +64475,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2257" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64495,7 +64501,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G2258" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64521,7 +64527,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2259" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64547,7 +64553,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2260" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64573,7 +64579,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2261" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64599,7 +64605,7 @@
         <v>17</v>
       </c>
       <c r="G2262" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64625,7 +64631,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64651,7 +64657,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G2264" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64677,7 +64683,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G2265" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64703,7 +64709,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2266" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64729,7 +64735,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G2267" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64755,7 +64761,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2268" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64781,7 +64787,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2269" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64807,7 +64813,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G2270" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64833,7 +64839,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G2271" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64859,7 +64865,7 @@
         <v>18</v>
       </c>
       <c r="G2272" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64885,7 +64891,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G2273" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64911,7 +64917,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G2274" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64937,7 +64943,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G2275" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64963,7 +64969,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G2276" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64989,7 +64995,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G2277" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -65015,7 +65021,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2278" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -65041,7 +65047,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2279" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65067,7 +65073,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G2280" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65093,7 +65099,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G2281" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65119,7 +65125,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G2282" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65145,7 +65151,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2283" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65171,7 +65177,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2284" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65197,7 +65203,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G2285" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65223,7 +65229,7 @@
         <v>18.25</v>
       </c>
       <c r="G2286" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65249,7 +65255,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G2287" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65275,7 +65281,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2288" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65301,7 +65307,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G2289" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65327,7 +65333,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G2290" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65353,7 +65359,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G2291" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65379,7 +65385,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G2292" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65405,7 +65411,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G2293" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65431,7 +65437,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2294" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65457,7 +65463,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G2295" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65483,7 +65489,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G2296" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65509,7 +65515,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G2297" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65535,7 +65541,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2298" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65561,7 +65567,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G2299" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65587,7 +65593,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2300" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65613,7 +65619,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G2301" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65639,7 +65645,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2302" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65665,7 +65671,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G2303" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65691,7 +65697,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G2304" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65717,7 +65723,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G2305" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65743,7 +65749,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G2306" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65769,7 +65775,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65795,7 +65801,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G2308" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65821,7 +65827,7 @@
         <v>18.25</v>
       </c>
       <c r="G2309" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65847,7 +65853,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G2310" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65873,7 +65879,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G2311" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65899,7 +65905,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2312" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65925,7 +65931,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G2313" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65951,7 +65957,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2314" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65977,7 +65983,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G2315" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -66003,7 +66009,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2316" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -66029,7 +66035,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2317" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66055,7 +66061,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G2318" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66081,7 +66087,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G2319" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66107,7 +66113,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G2320" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66133,7 +66139,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G2321" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66159,7 +66165,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G2322" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66185,7 +66191,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2323" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66211,7 +66217,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2324" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66237,7 +66243,7 @@
         <v>17.25</v>
       </c>
       <c r="G2325" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66263,7 +66269,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G2326" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66289,7 +66295,7 @@
         <v>17.25</v>
       </c>
       <c r="G2327" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66315,7 +66321,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66341,7 +66347,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G2329" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66367,7 +66373,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G2330" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66393,7 +66399,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G2331" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66419,7 +66425,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G2332" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66445,7 +66451,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G2333" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66471,7 +66477,7 @@
         <v>17</v>
       </c>
       <c r="G2334" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66497,7 +66503,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66523,7 +66529,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G2336" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66549,7 +66555,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G2337" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66575,7 +66581,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2338" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66601,7 +66607,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2339" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66627,7 +66633,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G2340" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66653,7 +66659,7 @@
         <v>17.75</v>
       </c>
       <c r="G2341" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66679,7 +66685,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G2342" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66705,7 +66711,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G2343" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66731,7 +66737,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G2344" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66757,7 +66763,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2345" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66783,7 +66789,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G2346" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66809,7 +66815,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66835,7 +66841,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G2348" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66861,7 +66867,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G2349" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66887,7 +66893,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G2350" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66913,7 +66919,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66939,7 +66945,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2352" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66965,7 +66971,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G2353" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66991,7 +66997,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G2354" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67017,7 +67023,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G2355" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67043,7 +67049,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G2356" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67069,7 +67075,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G2357" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67095,7 +67101,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2358" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67121,7 +67127,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G2359" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67147,7 +67153,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G2360" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67173,7 +67179,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2361" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67199,7 +67205,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G2362" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67225,7 +67231,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G2363" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67251,7 +67257,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G2364" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67277,7 +67283,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2365" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67303,7 +67309,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2366" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67329,7 +67335,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G2367" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67355,7 +67361,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G2368" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67381,7 +67387,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G2369" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67407,7 +67413,7 @@
         <v>20</v>
       </c>
       <c r="G2370" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67433,7 +67439,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2371" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67459,7 +67465,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2372" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67485,7 +67491,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G2373" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67511,7 +67517,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2374" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67537,7 +67543,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G2375" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67563,7 +67569,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G2376" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67589,7 +67595,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67615,7 +67621,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G2378" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67641,7 +67647,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G2379" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67667,7 +67673,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2380" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67693,7 +67699,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2381" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67719,7 +67725,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G2382" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67745,7 +67751,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G2383" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67771,7 +67777,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2384" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67797,7 +67803,7 @@
         <v>21.5</v>
       </c>
       <c r="G2385" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67823,7 +67829,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G2386" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67849,7 +67855,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G2387" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67875,7 +67881,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G2388" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67901,7 +67907,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G2389" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67927,7 +67933,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67953,7 +67959,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G2391" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67979,7 +67985,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G2392" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68005,7 +68011,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G2393" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68031,7 +68037,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G2394" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68057,7 +68063,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68083,7 +68089,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2396" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68109,7 +68115,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2397" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68135,7 +68141,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G2398" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68161,7 +68167,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G2399" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68187,7 +68193,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G2400" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68213,7 +68219,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G2401" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68239,7 +68245,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G2402" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68265,7 +68271,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2403" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68291,7 +68297,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2404" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68317,7 +68323,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G2405" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68343,7 +68349,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2406" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68369,7 +68375,7 @@
         <v>21.5</v>
       </c>
       <c r="G2407" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68395,7 +68401,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G2408" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68421,7 +68427,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G2409" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68447,7 +68453,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G2410" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68473,7 +68479,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G2411" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68499,7 +68505,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2412" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68525,7 +68531,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2413" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68551,7 +68557,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2414" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68577,7 +68583,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2415" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68603,7 +68609,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2416" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68629,7 +68635,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68655,7 +68661,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2418" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68681,7 +68687,7 @@
         <v>19.75</v>
       </c>
       <c r="G2419" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68707,7 +68713,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G2420" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68733,7 +68739,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G2421" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68759,7 +68765,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G2422" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68785,7 +68791,7 @@
         <v>19.25</v>
       </c>
       <c r="G2423" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68811,7 +68817,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G2424" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68837,7 +68843,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G2425" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68863,7 +68869,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G2426" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68889,7 +68895,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G2427" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68915,7 +68921,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2428" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68941,7 +68947,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G2429" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68967,7 +68973,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G2430" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68993,7 +68999,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69019,7 +69025,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G2432" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69045,7 +69051,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2433" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69071,7 +69077,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2434" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69097,7 +69103,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G2435" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69123,7 +69129,7 @@
         <v>19.75</v>
       </c>
       <c r="G2436" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69149,7 +69155,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G2437" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69175,7 +69181,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G2438" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69201,7 +69207,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G2439" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69227,7 +69233,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G2440" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69253,7 +69259,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69279,7 +69285,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G2442" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69305,7 +69311,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2443" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69331,7 +69337,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G2444" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69357,7 +69363,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G2445" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69383,7 +69389,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2446" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69409,7 +69415,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G2447" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69435,7 +69441,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2448" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69461,7 +69467,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G2449" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69487,7 +69493,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G2450" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69513,7 +69519,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G2451" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69539,7 +69545,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G2452" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69565,7 +69571,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G2453" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69591,7 +69597,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G2454" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69617,7 +69623,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G2455" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -69643,7 +69649,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G2456" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69669,7 +69675,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G2457" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -69695,7 +69701,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G2458" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69721,7 +69727,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G2459" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69747,7 +69753,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G2460" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69773,7 +69779,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G2461" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69799,7 +69805,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G2462" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69825,7 +69831,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69851,7 +69857,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G2464" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69877,7 +69883,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G2465" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69903,7 +69909,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G2466" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69929,7 +69935,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2467" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69955,7 +69961,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G2468" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69981,7 +69987,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70007,7 +70013,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G2470" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70033,7 +70039,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G2471" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70059,7 +70065,7 @@
         <v>19.25</v>
       </c>
       <c r="G2472" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70085,7 +70091,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70111,7 +70117,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G2474" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70137,7 +70143,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G2475" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70163,7 +70169,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G2476" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70189,7 +70195,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G2477" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70215,7 +70221,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G2478" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70241,7 +70247,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2479" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70267,7 +70273,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G2480" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70293,7 +70299,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70319,7 +70325,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G2482" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70345,7 +70351,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2483" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70371,7 +70377,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2484" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70397,7 +70403,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2485" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70423,7 +70429,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2486" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70449,7 +70455,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2487" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70475,7 +70481,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2488" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70501,7 +70507,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G2489" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70527,7 +70533,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G2490" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70553,7 +70559,7 @@
         <v>20.5</v>
       </c>
       <c r="G2491" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70579,7 +70585,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G2492" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -70605,7 +70611,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G2493" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -70631,7 +70637,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G2494" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -70657,7 +70663,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G2495" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -70683,7 +70689,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2496" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -70709,7 +70715,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2497" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -70735,7 +70741,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2498" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -70761,7 +70767,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G2499" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -70787,7 +70793,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G2500" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -70813,7 +70819,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2501" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -70839,7 +70845,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G2502" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -70865,7 +70871,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G2503" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -70891,7 +70897,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2504" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -70917,7 +70923,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2505" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -70943,7 +70949,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G2506" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -70969,7 +70975,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G2507" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -70995,7 +71001,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2508" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -71021,7 +71027,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G2509" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -71047,7 +71053,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G2510" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -71073,7 +71079,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G2511" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -71099,7 +71105,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2512" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -71125,7 +71131,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2513" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -71151,7 +71157,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G2514" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -71177,7 +71183,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2515" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -71203,7 +71209,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G2516" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -71229,7 +71235,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2517" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -71255,7 +71261,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2518" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -71281,7 +71287,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G2519" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -71307,7 +71313,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G2520" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -71333,7 +71339,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2521" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -71359,7 +71365,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G2522" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -71385,7 +71391,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G2523" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -71411,7 +71417,7 @@
         <v>22.6200008392334</v>
       </c>
       <c r="G2524" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -71437,7 +71443,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G2525" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -71463,7 +71469,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2526" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -71489,7 +71495,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2527" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -71515,7 +71521,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G2528" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -71541,7 +71547,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G2529" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -71567,7 +71573,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2530" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -71575,7 +71581,7 @@
     </row>
     <row r="2531">
       <c r="A2531" s="1" t="n">
-        <v>46002.6912962963</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2531" t="n">
         <v>74254</v>
@@ -71593,9 +71599,35 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G2531" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.6910185185</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>53719</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>21.6800003051758</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>21.7600002288818</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>21.8199996948242</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>1816</v>
+      </c>
+      <c r="H2532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="1818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="1820">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59860897064209</t>
+    <t xml:space="preserve">8.59860992431641</t>
   </si>
   <si>
     <t xml:space="preserve">ACE.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">8.61100769042969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3010368347168</t>
+    <t xml:space="preserve">8.30103778839111</t>
   </si>
   <si>
     <t xml:space="preserve">8.437424659729</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">8.68540191650391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30723667144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35063362121582</t>
+    <t xml:space="preserve">8.30723571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3506326675415</t>
   </si>
   <si>
     <t xml:space="preserve">8.20804500579834</t>
@@ -80,25 +80,25 @@
     <t xml:space="preserve">7.97246789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13985061645508</t>
+    <t xml:space="preserve">8.13985157012939</t>
   </si>
   <si>
     <t xml:space="preserve">8.15225028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2762393951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3878288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49321842193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50561904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39402866363525</t>
+    <t xml:space="preserve">8.27623844146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38782787322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49321937561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50561714172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39402770996094</t>
   </si>
   <si>
     <t xml:space="preserve">8.36923122406006</t>
@@ -107,64 +107,64 @@
     <t xml:space="preserve">8.33203411102295</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99106645584106</t>
+    <t xml:space="preserve">7.99106550216675</t>
   </si>
   <si>
     <t xml:space="preserve">7.5943021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45791482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3153281211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46411323547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66869497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63149881362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65629625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65009832382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44551563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60050010681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6810941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55090618133545</t>
+    <t xml:space="preserve">7.45791292190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31532716751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46411371231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66869401931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63149785995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65629577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65009689331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44551467895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60050106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68109321594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55090665817261</t>
   </si>
   <si>
     <t xml:space="preserve">7.68729257583618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60670042037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73688936233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64389610290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57570362091064</t>
+    <t xml:space="preserve">7.60669946670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73688840866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64389705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57570314407349</t>
   </si>
   <si>
     <t xml:space="preserve">7.53230619430542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0158634185791</t>
+    <t xml:space="preserve">8.01586246490479</t>
   </si>
   <si>
     <t xml:space="preserve">8.38162994384766</t>
@@ -176,37 +176,37 @@
     <t xml:space="preserve">8.77219390869141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76599311828613</t>
+    <t xml:space="preserve">8.76599407196045</t>
   </si>
   <si>
     <t xml:space="preserve">8.83418750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78459167480469</t>
+    <t xml:space="preserve">8.78459358215332</t>
   </si>
   <si>
     <t xml:space="preserve">8.46842002868652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41882705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33823299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45602321624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49941825866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58621215820312</t>
+    <t xml:space="preserve">8.41882610321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33823394775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45602226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49941921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58621120452881</t>
   </si>
   <si>
     <t xml:space="preserve">8.43122482299805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40642642974854</t>
+    <t xml:space="preserve">8.40642738342285</t>
   </si>
   <si>
     <t xml:space="preserve">8.34443187713623</t>
@@ -221,40 +221,40 @@
     <t xml:space="preserve">7.90427350997925</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87327718734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73068809509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79268217086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85467767715454</t>
+    <t xml:space="preserve">7.8732762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73068904876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79268312454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85467863082886</t>
   </si>
   <si>
     <t xml:space="preserve">7.89807415008545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96006631851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0468578338623</t>
+    <t xml:space="preserve">7.9600682258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04686069488525</t>
   </si>
   <si>
     <t xml:space="preserve">7.99726486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96626758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8670768737793</t>
+    <t xml:space="preserve">7.96626663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86707592010498</t>
   </si>
   <si>
     <t xml:space="preserve">7.7802848815918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.090256690979</t>
+    <t xml:space="preserve">8.09025573730469</t>
   </si>
   <si>
     <t xml:space="preserve">8.1150541305542</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">7.88567447662354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82987976074219</t>
+    <t xml:space="preserve">7.8298807144165</t>
   </si>
   <si>
     <t xml:space="preserve">8.04065990447998</t>
@@ -281,10 +281,10 @@
     <t xml:space="preserve">8.09645652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19564819335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23284339904785</t>
+    <t xml:space="preserve">8.19564723968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23284244537354</t>
   </si>
   <si>
     <t xml:space="preserve">8.18324756622314</t>
@@ -293,49 +293,49 @@
     <t xml:space="preserve">8.05925846099854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76168632507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52610874176025</t>
+    <t xml:space="preserve">7.76168727874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52610778808594</t>
   </si>
   <si>
     <t xml:space="preserve">7.56330394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42071723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19133901596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85657024383545</t>
+    <t xml:space="preserve">7.4207181930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19133853912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85656929016113</t>
   </si>
   <si>
     <t xml:space="preserve">6.96815824508667</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9743595123291</t>
+    <t xml:space="preserve">6.97435855865479</t>
   </si>
   <si>
     <t xml:space="preserve">7.12314462661743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09073734283447</t>
+    <t xml:space="preserve">7.09073686599731</t>
   </si>
   <si>
     <t xml:space="preserve">7.05184841156006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14259099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05833148956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68240451812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37777519226074</t>
+    <t xml:space="preserve">7.14259052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05833101272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6824049949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37777471542358</t>
   </si>
   <si>
     <t xml:space="preserve">6.49444246292114</t>
@@ -344,52 +344,52 @@
     <t xml:space="preserve">6.61110782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08425569534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99999666213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03888511657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93518161773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78610849380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370073318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8249979019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86388540267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74073696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91573810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92869997024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89629316329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15555238723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907026290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58332967758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55740404129028</t>
+    <t xml:space="preserve">7.08425712585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99999713897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03888607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93518114089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78610801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370025634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82499742507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86388683319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7407374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91573762893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92869901657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89629411697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15555286407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58333015441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55740356445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.0694408416748</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">8.01110744476318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16666507720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17962646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07592296600342</t>
+    <t xml:space="preserve">8.16666412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17962551116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0759220123291</t>
   </si>
   <si>
     <t xml:space="preserve">8.05647754669189</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">7.9527735710144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82962703704834</t>
+    <t xml:space="preserve">7.82962608337402</t>
   </si>
   <si>
     <t xml:space="preserve">7.87499570846558</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.90740299224854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76481151580811</t>
+    <t xml:space="preserve">7.76481246948242</t>
   </si>
   <si>
     <t xml:space="preserve">7.75832986831665</t>
@@ -440,40 +440,40 @@
     <t xml:space="preserve">7.7712926864624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71944141387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57684803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65462636947632</t>
+    <t xml:space="preserve">7.71944046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57684898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65462732315063</t>
   </si>
   <si>
     <t xml:space="preserve">7.70647811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81666421890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79073810577393</t>
+    <t xml:space="preserve">7.81666326522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79073715209961</t>
   </si>
   <si>
     <t xml:space="preserve">7.69351434707642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72592258453369</t>
+    <t xml:space="preserve">7.72592163085938</t>
   </si>
   <si>
     <t xml:space="preserve">7.6999979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50555181503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37592315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39536619186401</t>
+    <t xml:space="preserve">7.50555276870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37592363357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39536666870117</t>
   </si>
   <si>
     <t xml:space="preserve">7.47314548492432</t>
@@ -482,91 +482,91 @@
     <t xml:space="preserve">7.32407093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25277328491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22684860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18147754669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2009220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22036647796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18796014785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16851472854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16203451156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19444227218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17499589920044</t>
+    <t xml:space="preserve">7.25277376174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22684764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18147945404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20092248916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22036838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18796062469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1685152053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16203308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19444179534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17499732971191</t>
   </si>
   <si>
     <t xml:space="preserve">7.07129287719727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96758842468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04536724090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98703384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23332977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34999752044678</t>
+    <t xml:space="preserve">6.96758937835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0453667640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9870343208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23333120346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34999704360962</t>
   </si>
   <si>
     <t xml:space="preserve">7.41481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55092239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52499580383301</t>
+    <t xml:space="preserve">7.55092191696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52499628067017</t>
   </si>
   <si>
     <t xml:space="preserve">7.64166259765625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59629249572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61573791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64814472198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49258947372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3888840675354</t>
+    <t xml:space="preserve">7.5962929725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61573696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64814424514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49258995056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38888549804688</t>
   </si>
   <si>
     <t xml:space="preserve">7.46018123626709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36944055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30462551116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84444141387939</t>
+    <t xml:space="preserve">7.36944007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30462598800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84444189071655</t>
   </si>
   <si>
     <t xml:space="preserve">6.57221984863281</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">6.59166383743286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54629373550415</t>
+    <t xml:space="preserve">6.54629325866699</t>
   </si>
   <si>
     <t xml:space="preserve">6.48147869110107</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43610954284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47823810577393</t>
+    <t xml:space="preserve">6.43610858917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47823762893677</t>
   </si>
   <si>
     <t xml:space="preserve">6.52684879302979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6499981880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53333139419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59814643859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5203685760498</t>
+    <t xml:space="preserve">6.64999723434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5333309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59814548492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52036762237549</t>
   </si>
   <si>
     <t xml:space="preserve">6.42962694168091</t>
@@ -608,28 +608,28 @@
     <t xml:space="preserve">6.87036752700806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10370111465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25925540924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48610830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4342565536499</t>
+    <t xml:space="preserve">7.1037015914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25925588607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48610734939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43425559997559</t>
   </si>
   <si>
     <t xml:space="preserve">7.42777442932129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38240385055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51851558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51203393936157</t>
+    <t xml:space="preserve">7.38240528106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851463317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51203346252441</t>
   </si>
   <si>
     <t xml:space="preserve">7.66758966445923</t>
@@ -638,13 +638,13 @@
     <t xml:space="preserve">7.68055200576782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71295928955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89444160461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79721975326538</t>
+    <t xml:space="preserve">7.7129602432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89444208145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79721784591675</t>
   </si>
   <si>
     <t xml:space="preserve">7.84258937835693</t>
@@ -653,31 +653,31 @@
     <t xml:space="preserve">7.34351539611816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40184879302979</t>
+    <t xml:space="preserve">7.40184783935547</t>
   </si>
   <si>
     <t xml:space="preserve">7.46666383743286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40833139419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73888444900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68703413009644</t>
+    <t xml:space="preserve">7.4083309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73888540267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68703317642212</t>
   </si>
   <si>
     <t xml:space="preserve">7.62221908569336</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63518190383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73240518569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7777738571167</t>
+    <t xml:space="preserve">7.63518142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73240423202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77777481079102</t>
   </si>
   <si>
     <t xml:space="preserve">7.83610820770264</t>
@@ -686,19 +686,19 @@
     <t xml:space="preserve">7.75184869766235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62870121002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97221946716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85555267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9268479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.037034034729</t>
+    <t xml:space="preserve">7.62869930267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97221851348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85555171966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92684888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03703308105469</t>
   </si>
   <si>
     <t xml:space="preserve">8.09536552429199</t>
@@ -713,10 +713,10 @@
     <t xml:space="preserve">8.28981113433838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24444198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147773742676</t>
+    <t xml:space="preserve">8.24444007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147869110107</t>
   </si>
   <si>
     <t xml:space="preserve">8.22499561309814</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">8.43240261077881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42592144012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35462665557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55555248260498</t>
+    <t xml:space="preserve">8.42592239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3546257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55555152893066</t>
   </si>
   <si>
     <t xml:space="preserve">8.52314472198486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39351463317871</t>
+    <t xml:space="preserve">8.39351558685303</t>
   </si>
   <si>
     <t xml:space="preserve">8.47129249572754</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">8.60740375518799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61388492584229</t>
+    <t xml:space="preserve">8.6138858795166</t>
   </si>
   <si>
     <t xml:space="preserve">8.62036609649658</t>
@@ -764,31 +764,31 @@
     <t xml:space="preserve">8.56203269958496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80832958221436</t>
+    <t xml:space="preserve">8.80832862854004</t>
   </si>
   <si>
     <t xml:space="preserve">8.67870044708252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81481266021729</t>
+    <t xml:space="preserve">8.81481075286865</t>
   </si>
   <si>
     <t xml:space="preserve">8.84073638916016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9249963760376</t>
+    <t xml:space="preserve">8.92499732971191</t>
   </si>
   <si>
     <t xml:space="preserve">9.12592220306396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17777442932129</t>
+    <t xml:space="preserve">9.17777252197266</t>
   </si>
   <si>
     <t xml:space="preserve">9.00277423858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9509220123291</t>
+    <t xml:space="preserve">8.95092296600342</t>
   </si>
   <si>
     <t xml:space="preserve">8.99629211425781</t>
@@ -797,25 +797,25 @@
     <t xml:space="preserve">9.18425559997559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01573753356934</t>
+    <t xml:space="preserve">9.0157356262207</t>
   </si>
   <si>
     <t xml:space="preserve">9.02869987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20369911193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2814769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30740356445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34629154205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43703460693359</t>
+    <t xml:space="preserve">9.20370006561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28147602081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30740451812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34629249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43703365325928</t>
   </si>
   <si>
     <t xml:space="preserve">9.32684898376465</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">9.43055152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38518142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41758918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33333015441895</t>
+    <t xml:space="preserve">9.38518047332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41758823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33332824707031</t>
   </si>
   <si>
     <t xml:space="preserve">9.5018482208252</t>
@@ -842,58 +842,58 @@
     <t xml:space="preserve">9.44351482391357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54721641540527</t>
+    <t xml:space="preserve">9.54721736907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.41110610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35925388336182</t>
+    <t xml:space="preserve">9.35925483703613</t>
   </si>
   <si>
     <t xml:space="preserve">9.51501750946045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41343307495117</t>
+    <t xml:space="preserve">9.41343212127686</t>
   </si>
   <si>
     <t xml:space="preserve">9.59628391265869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50147342681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44729328155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4811544418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21026706695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09513664245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14931488037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98678016662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83101844787598</t>
+    <t xml:space="preserve">9.50147151947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44729518890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48115539550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21026515960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09513759613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14931583404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98678207397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83101940155029</t>
   </si>
   <si>
     <t xml:space="preserve">8.84456348419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93937587738037</t>
+    <t xml:space="preserve">8.93937492370605</t>
   </si>
   <si>
     <t xml:space="preserve">8.81070137023926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93260288238525</t>
+    <t xml:space="preserve">8.93260192871094</t>
   </si>
   <si>
     <t xml:space="preserve">9.04095840454102</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">8.87165355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0477294921875</t>
+    <t xml:space="preserve">9.04773044586182</t>
   </si>
   <si>
     <t xml:space="preserve">9.08159255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10190868377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349311828613</t>
+    <t xml:space="preserve">9.10190773010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
     <t xml:space="preserve">9.10868167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12222576141357</t>
+    <t xml:space="preserve">9.12222671508789</t>
   </si>
   <si>
     <t xml:space="preserve">9.0070972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07481956481934</t>
+    <t xml:space="preserve">9.07482051849365</t>
   </si>
   <si>
     <t xml:space="preserve">8.87842464447021</t>
@@ -935,64 +935,64 @@
     <t xml:space="preserve">8.90551376342773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52626705169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58721828460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54658508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56013011932373</t>
+    <t xml:space="preserve">8.52626800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58721923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5465841293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5601282119751</t>
   </si>
   <si>
     <t xml:space="preserve">8.68880176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53981304168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44500160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33664608001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47209072113037</t>
+    <t xml:space="preserve">8.5398120880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44500064849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33664417266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47208976745605</t>
   </si>
   <si>
     <t xml:space="preserve">8.47886276245117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41114044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42468357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3840503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3908224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32987308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28246593475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26892375946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24860572814941</t>
+    <t xml:space="preserve">8.41113948822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4246826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38405132293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39082145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32987213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28246688842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26891994476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24860668182373</t>
   </si>
   <si>
     <t xml:space="preserve">8.19442749023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16733932495117</t>
+    <t xml:space="preserve">8.16733837127686</t>
   </si>
   <si>
     <t xml:space="preserve">8.21474361419678</t>
@@ -1001,43 +1001,43 @@
     <t xml:space="preserve">8.37050533294678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29601097106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39759540557861</t>
+    <t xml:space="preserve">8.29601192474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3975944519043</t>
   </si>
   <si>
     <t xml:space="preserve">8.81747531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97323703765869</t>
+    <t xml:space="preserve">8.97323608398438</t>
   </si>
   <si>
     <t xml:space="preserve">8.76329612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67525863647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68202972412109</t>
+    <t xml:space="preserve">8.67525768280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68202877044678</t>
   </si>
   <si>
     <t xml:space="preserve">8.69557476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80392932891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8581075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74297904968262</t>
+    <t xml:space="preserve">8.80393028259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85810852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74298000335693</t>
   </si>
   <si>
     <t xml:space="preserve">8.74975204467773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79038429260254</t>
+    <t xml:space="preserve">8.79038524627686</t>
   </si>
   <si>
     <t xml:space="preserve">8.88519763946533</t>
@@ -1049,19 +1049,19 @@
     <t xml:space="preserve">8.91228485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89196872711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18317604064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19672012329102</t>
+    <t xml:space="preserve">8.89196968078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18317699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19672107696533</t>
   </si>
   <si>
     <t xml:space="preserve">9.29153251647949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24412536621094</t>
+    <t xml:space="preserve">9.24412727355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.36602783203125</t>
@@ -1073,19 +1073,19 @@
     <t xml:space="preserve">9.54210567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46761131286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38634395599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52178955078125</t>
+    <t xml:space="preserve">9.46761035919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38634490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52178859710693</t>
   </si>
   <si>
     <t xml:space="preserve">9.49470043182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84008598327637</t>
+    <t xml:space="preserve">9.84008502960205</t>
   </si>
   <si>
     <t xml:space="preserve">9.86717414855957</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">9.83331203460693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76558971405029</t>
+    <t xml:space="preserve">9.76559066772461</t>
   </si>
   <si>
     <t xml:space="preserve">9.74527454376221</t>
@@ -1106,19 +1106,19 @@
     <t xml:space="preserve">9.70463943481445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58273887634277</t>
+    <t xml:space="preserve">9.58273983001709</t>
   </si>
   <si>
     <t xml:space="preserve">9.71818447113037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67077922821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96875762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94844150543213</t>
+    <t xml:space="preserve">9.67077827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96875953674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94844055175781</t>
   </si>
   <si>
     <t xml:space="preserve">9.91458034515381</t>
@@ -1127,25 +1127,25 @@
     <t xml:space="preserve">10.0161647796631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96198654174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92135143280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90103530883789</t>
+    <t xml:space="preserve">9.96198558807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92135334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90103435516357</t>
   </si>
   <si>
     <t xml:space="preserve">10.2599649429321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4451084136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5670108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4857416152954</t>
+    <t xml:space="preserve">11.4451093673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5670099258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4857425689697</t>
   </si>
   <si>
     <t xml:space="preserve">11.5128316879272</t>
@@ -1160,64 +1160,64 @@
     <t xml:space="preserve">11.4992876052856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3502988815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0726356506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9845952987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8762397766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1674461364746</t>
+    <t xml:space="preserve">11.3502979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0726366043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9845943450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8762407302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1674470901489</t>
   </si>
   <si>
     <t xml:space="preserve">10.8152904510498</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5850324630737</t>
+    <t xml:space="preserve">10.5850343704224</t>
   </si>
   <si>
     <t xml:space="preserve">10.4495878219604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5647163391113</t>
+    <t xml:space="preserve">10.564715385437</t>
   </si>
   <si>
     <t xml:space="preserve">10.5443992614746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4292697906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4699048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.632438659668</t>
+    <t xml:space="preserve">10.4292707443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4699039459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6324377059937</t>
   </si>
   <si>
     <t xml:space="preserve">10.8220615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9168739318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9913673400879</t>
+    <t xml:space="preserve">10.9168729782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9913692474365</t>
   </si>
   <si>
     <t xml:space="preserve">10.8017444610596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7204780578613</t>
+    <t xml:space="preserve">10.7204790115356</t>
   </si>
   <si>
     <t xml:space="preserve">10.6256656646729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6730728149414</t>
+    <t xml:space="preserve">10.6730718612671</t>
   </si>
   <si>
     <t xml:space="preserve">10.8356056213379</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">10.9981412887573</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0455455780029</t>
+    <t xml:space="preserve">11.0455465316772</t>
   </si>
   <si>
     <t xml:space="preserve">11.1268138885498</t>
@@ -1238,61 +1238,61 @@
     <t xml:space="preserve">10.9304170608521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.842378616333</t>
+    <t xml:space="preserve">10.8423795700073</t>
   </si>
   <si>
     <t xml:space="preserve">10.7746562957764</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7340230941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5918045043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5376262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5173091888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3615474700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.097430229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87394714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1922435760498</t>
+    <t xml:space="preserve">10.7340221405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5918054580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5376281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5173110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3615484237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0974311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87394618988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1922416687012</t>
   </si>
   <si>
     <t xml:space="preserve">9.92812442779541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0364809036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0567970275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1245203018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0838871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97552871704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69786739349365</t>
+    <t xml:space="preserve">10.0364799499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0567979812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1245193481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0838851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97552967071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69786643981934</t>
   </si>
   <si>
     <t xml:space="preserve">9.50824451446533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44052028656006</t>
+    <t xml:space="preserve">9.44052219390869</t>
   </si>
   <si>
     <t xml:space="preserve">9.64369010925293</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">9.66400718688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67755126953125</t>
+    <t xml:space="preserve">9.67755317687988</t>
   </si>
   <si>
     <t xml:space="preserve">9.46083927154541</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">9.21703720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13577079772949</t>
+    <t xml:space="preserve">9.13576984405518</t>
   </si>
   <si>
     <t xml:space="preserve">9.23058223724365</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">9.23735427856445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1628589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29830455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42697811126709</t>
+    <t xml:space="preserve">9.16285991668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29830265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42697715759277</t>
   </si>
   <si>
     <t xml:space="preserve">9.53533363342285</t>
@@ -1352,52 +1352,52 @@
     <t xml:space="preserve">9.62337303161621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79945182800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80622386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77236175537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95521354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81976890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75881862640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47438335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71141242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30507659912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01387119293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79715824127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03418636322021</t>
+    <t xml:space="preserve">9.79945278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80622291564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77236270904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95521259307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81976795196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75881767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47438430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71141147613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30507755279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0138692855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79715728759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03418731689453</t>
   </si>
   <si>
     <t xml:space="preserve">9.39311599731445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26281642913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29120540618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24152088165283</t>
+    <t xml:space="preserve">9.26281547546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29120635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24151992797852</t>
   </si>
   <si>
     <t xml:space="preserve">9.1137580871582</t>
@@ -1406,10 +1406,10 @@
     <t xml:space="preserve">9.14924812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05697536468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07116985321045</t>
+    <t xml:space="preserve">9.05697345733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07117080688477</t>
   </si>
   <si>
     <t xml:space="preserve">9.03568077087402</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">8.9930944442749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04277992248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.021484375</t>
+    <t xml:space="preserve">9.04277896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02148532867432</t>
   </si>
   <si>
     <t xml:space="preserve">9.19183540344238</t>
@@ -1433,40 +1433,40 @@
     <t xml:space="preserve">9.39767551422119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2131290435791</t>
+    <t xml:space="preserve">9.21312808990479</t>
   </si>
   <si>
     <t xml:space="preserve">9.10665988922119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12795352935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22732353210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26991271972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12085628509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17763805389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38347911834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44026279449463</t>
+    <t xml:space="preserve">9.12795448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22732543945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26991367340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12085723876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17763996124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38348007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44026470184326</t>
   </si>
   <si>
     <t xml:space="preserve">9.41187191009521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70288753509521</t>
+    <t xml:space="preserve">9.60351657867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7028865814209</t>
   </si>
   <si>
     <t xml:space="preserve">9.56092834472656</t>
@@ -1475,19 +1475,19 @@
     <t xml:space="preserve">9.61771202087402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65320301055908</t>
+    <t xml:space="preserve">9.65320205688477</t>
   </si>
   <si>
     <t xml:space="preserve">9.6815938949585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57512378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66029930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53253650665283</t>
+    <t xml:space="preserve">9.57512474060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66029834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53253555297852</t>
   </si>
   <si>
     <t xml:space="preserve">9.45445919036865</t>
@@ -1496,31 +1496,31 @@
     <t xml:space="preserve">9.50414562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30540180206299</t>
+    <t xml:space="preserve">9.3054027557373</t>
   </si>
   <si>
     <t xml:space="preserve">9.34799003601074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28410816192627</t>
+    <t xml:space="preserve">9.28410911560059</t>
   </si>
   <si>
     <t xml:space="preserve">9.24861812591553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0924654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8227424621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71627235412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68078231811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78725337982178</t>
+    <t xml:space="preserve">9.09246444702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82274150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71627330780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68078327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78725242614746</t>
   </si>
   <si>
     <t xml:space="preserve">8.97889614105225</t>
@@ -1529,49 +1529,49 @@
     <t xml:space="preserve">9.01438617706299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14214992523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2344217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29830551147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39057636260986</t>
+    <t xml:space="preserve">9.14214897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23442363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29830360412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39057731628418</t>
   </si>
   <si>
     <t xml:space="preserve">9.42606735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37638187408447</t>
+    <t xml:space="preserve">9.37638092041016</t>
   </si>
   <si>
     <t xml:space="preserve">9.16344261169434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04987621307373</t>
+    <t xml:space="preserve">9.04987716674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.17054176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74466514587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69497966766357</t>
+    <t xml:space="preserve">8.74466419219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69497871398926</t>
   </si>
   <si>
     <t xml:space="preserve">8.51043224334717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48204231262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39686584472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59560871124268</t>
+    <t xml:space="preserve">8.48204135894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3968677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59560775756836</t>
   </si>
   <si>
     <t xml:space="preserve">8.49623775482178</t>
@@ -1583,16 +1583,16 @@
     <t xml:space="preserve">8.26200580596924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2265157699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04196834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06326103210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07036018371582</t>
+    <t xml:space="preserve">8.22651481628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04196739196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06326198577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07036113739014</t>
   </si>
   <si>
     <t xml:space="preserve">7.93549966812134</t>
@@ -1601,22 +1601,22 @@
     <t xml:space="preserve">8.1484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16263389587402</t>
+    <t xml:space="preserve">8.16263580322266</t>
   </si>
   <si>
     <t xml:space="preserve">8.2407112121582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28329944610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38266944885254</t>
+    <t xml:space="preserve">8.28329753875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38267040252686</t>
   </si>
   <si>
     <t xml:space="preserve">8.36137580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50333499908447</t>
+    <t xml:space="preserve">8.50333404541016</t>
   </si>
   <si>
     <t xml:space="preserve">8.42525672912598</t>
@@ -1634,34 +1634,34 @@
     <t xml:space="preserve">8.8085470199585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81564521789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65948963165283</t>
+    <t xml:space="preserve">8.81564426422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65948867797852</t>
   </si>
   <si>
     <t xml:space="preserve">8.56011962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57431507110596</t>
+    <t xml:space="preserve">8.57431411743164</t>
   </si>
   <si>
     <t xml:space="preserve">8.44655132293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52462863922119</t>
+    <t xml:space="preserve">8.52462959289551</t>
   </si>
   <si>
     <t xml:space="preserve">8.51753044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40396308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36847400665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43945407867432</t>
+    <t xml:space="preserve">8.40396404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36847305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.439453125</t>
   </si>
   <si>
     <t xml:space="preserve">8.21231937408447</t>
@@ -1688,13 +1688,13 @@
     <t xml:space="preserve">8.62399959564209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38976860046387</t>
+    <t xml:space="preserve">8.38976669311523</t>
   </si>
   <si>
     <t xml:space="preserve">8.53172779083252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68788242340088</t>
+    <t xml:space="preserve">8.68788146972656</t>
   </si>
   <si>
     <t xml:space="preserve">8.83693885803223</t>
@@ -1703,22 +1703,22 @@
     <t xml:space="preserve">8.85823154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90791797637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25571632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5112419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5822229385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47575283050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35508823394775</t>
+    <t xml:space="preserve">8.90791702270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25571727752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51124286651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58222198486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47575378417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35508918762207</t>
   </si>
   <si>
     <t xml:space="preserve">9.54673194885254</t>
@@ -1736,13 +1736,13 @@
     <t xml:space="preserve">9.51834106445312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68869018554688</t>
+    <t xml:space="preserve">9.68869113922119</t>
   </si>
   <si>
     <t xml:space="preserve">9.90872859954834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85904216766357</t>
+    <t xml:space="preserve">9.85904121398926</t>
   </si>
   <si>
     <t xml:space="preserve">9.88033580780029</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">9.85194396972656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0222940444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2423305511475</t>
+    <t xml:space="preserve">10.0222930908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2423315048218</t>
   </si>
   <si>
     <t xml:space="preserve">10.3275060653687</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">10.6114234924316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7604808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6398153305054</t>
+    <t xml:space="preserve">10.760479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6398162841797</t>
   </si>
   <si>
     <t xml:space="preserve">10.6824045181274</t>
@@ -1781,34 +1781,34 @@
     <t xml:space="preserve">10.6043262481689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7107944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6895017623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7746772766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7249917984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.788872718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7533826828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7391872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178936004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6965990066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9166345596313</t>
+    <t xml:space="preserve">10.7107954025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6895008087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.774676322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7249898910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7888736724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7533836364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7391862869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178945541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6965999603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9166355133057</t>
   </si>
   <si>
     <t xml:space="preserve">11.356707572937</t>
@@ -1817,22 +1817,22 @@
     <t xml:space="preserve">11.370903968811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49866771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3141183853149</t>
+    <t xml:space="preserve">11.4986667633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3141193389893</t>
   </si>
   <si>
     <t xml:space="preserve">11.4418840408325</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4276866912842</t>
+    <t xml:space="preserve">11.4276876449585</t>
   </si>
   <si>
     <t xml:space="preserve">11.2999238967896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1579647064209</t>
+    <t xml:space="preserve">11.1579666137695</t>
   </si>
   <si>
     <t xml:space="preserve">10.9876146316528</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">11.484471321106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4702739715576</t>
+    <t xml:space="preserve">11.4702749252319</t>
   </si>
   <si>
     <t xml:space="preserve">11.6122341156006</t>
@@ -1862,37 +1862,37 @@
     <t xml:space="preserve">11.5412540435791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8535642623901</t>
+    <t xml:space="preserve">11.8535652160645</t>
   </si>
   <si>
     <t xml:space="preserve">11.938738822937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1090898513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9813261032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8677597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8251724243164</t>
+    <t xml:space="preserve">12.1090888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9813270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8677577972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8251714706421</t>
   </si>
   <si>
     <t xml:space="preserve">11.7399978637695</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6832113265991</t>
+    <t xml:space="preserve">11.6832122802734</t>
   </si>
   <si>
     <t xml:space="preserve">11.7967805862427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8961534500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9103488922119</t>
+    <t xml:space="preserve">11.8961524963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9103498458862</t>
   </si>
   <si>
     <t xml:space="preserve">11.8393678665161</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">11.8109760284424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0665016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1942663192749</t>
+    <t xml:space="preserve">12.066502571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1942653656006</t>
   </si>
   <si>
     <t xml:space="preserve">12.2794389724731</t>
@@ -1916,88 +1916,88 @@
     <t xml:space="preserve">12.3078336715698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3504199981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4355955123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5065755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5207691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5349655151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5917491912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6627311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6343364715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7053155899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8161849975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.668360710144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6387968063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3875007629395</t>
+    <t xml:space="preserve">12.3504190444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4355964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5065746307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.520770072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.534966468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5917501449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6627292633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6343374252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7053165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8161840438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6683616638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6387958526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3874998092651</t>
   </si>
   <si>
     <t xml:space="preserve">12.3727169036865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3135890960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4466285705566</t>
+    <t xml:space="preserve">12.3135871887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.446626663208</t>
   </si>
   <si>
     <t xml:space="preserve">12.8014011383057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7274894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5353212356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5796689987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7422723770142</t>
+    <t xml:space="preserve">12.7274904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5353202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5796680450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7422733306885</t>
   </si>
   <si>
     <t xml:space="preserve">12.6831436157227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8753128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7866172790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7718372344971</t>
+    <t xml:space="preserve">12.8753137588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7866182327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7718381881714</t>
   </si>
   <si>
     <t xml:space="preserve">12.8309659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9344415664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6979274749756</t>
+    <t xml:space="preserve">12.934440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6979265213013</t>
   </si>
   <si>
     <t xml:space="preserve">12.7127075195312</t>
@@ -2009,34 +2009,34 @@
     <t xml:space="preserve">12.9048757553101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8457479476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8900957107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0674810409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1118278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.052698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9787864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.141393661499</t>
+    <t xml:space="preserve">12.8457469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8900966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0674819946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1118288040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0526990890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9787874221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1413927078247</t>
   </si>
   <si>
     <t xml:space="preserve">13.0970449447632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0822629928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0231351852417</t>
+    <t xml:space="preserve">13.0822620391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0231342315674</t>
   </si>
   <si>
     <t xml:space="preserve">12.9492244720459</t>
@@ -2045,49 +2045,49 @@
     <t xml:space="preserve">13.1561737060547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9935703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6092329025269</t>
+    <t xml:space="preserve">12.9935712814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6092319488525</t>
   </si>
   <si>
     <t xml:space="preserve">12.8605298995972</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5501041412354</t>
+    <t xml:space="preserve">12.550103187561</t>
   </si>
   <si>
     <t xml:space="preserve">13.4518203735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3335638046265</t>
+    <t xml:space="preserve">13.3335628509521</t>
   </si>
   <si>
     <t xml:space="preserve">13.4961652755737</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3483428955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5405120849609</t>
+    <t xml:space="preserve">13.3483419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5405111312866</t>
   </si>
   <si>
     <t xml:space="preserve">12.9640064239502</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1857404708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.170955657959</t>
+    <t xml:space="preserve">13.1857395172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1709566116333</t>
   </si>
   <si>
     <t xml:space="preserve">12.9196586608887</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2744302749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.259651184082</t>
+    <t xml:space="preserve">13.2744312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2596521377563</t>
   </si>
   <si>
     <t xml:space="preserve">13.2892141342163</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">13.2448682785034</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1266088485718</t>
+    <t xml:space="preserve">13.1266098022461</t>
   </si>
   <si>
     <t xml:space="preserve">13.762246131897</t>
@@ -2105,28 +2105,28 @@
     <t xml:space="preserve">13.9396324157715</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5552940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7474632263184</t>
+    <t xml:space="preserve">13.5552949905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.747465133667</t>
   </si>
   <si>
     <t xml:space="preserve">13.9691963195801</t>
   </si>
   <si>
-    <t xml:space="preserve">13.777027130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6292057037354</t>
+    <t xml:space="preserve">13.7770280838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6292066574097</t>
   </si>
   <si>
     <t xml:space="preserve">13.8657207489014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9544134140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4665994644165</t>
+    <t xml:space="preserve">13.9544143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4666013717651</t>
   </si>
   <si>
     <t xml:space="preserve">13.4813833236694</t>
@@ -2135,31 +2135,31 @@
     <t xml:space="preserve">13.4370374679565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7918081283569</t>
+    <t xml:space="preserve">13.7918090820312</t>
   </si>
   <si>
     <t xml:space="preserve">13.998761177063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0578899383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8213748931885</t>
+    <t xml:space="preserve">14.0578880310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8213768005371</t>
   </si>
   <si>
     <t xml:space="preserve">13.6883344650269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6587705612183</t>
+    <t xml:space="preserve">13.6587696075439</t>
   </si>
   <si>
     <t xml:space="preserve">13.6144227981567</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5257301330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3631248474121</t>
+    <t xml:space="preserve">13.525731086731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3631258010864</t>
   </si>
   <si>
     <t xml:space="preserve">13.2300844192505</t>
@@ -2174,34 +2174,34 @@
     <t xml:space="preserve">14.4717922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6343946456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8191747665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0409078598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300413131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0039529800415</t>
+    <t xml:space="preserve">14.6343965530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8191738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0409069061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300403594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0039520263672</t>
   </si>
   <si>
     <t xml:space="preserve">15.3735065460205</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5582838058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9278402328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1126155853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.038703918457</t>
+    <t xml:space="preserve">15.5582857131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9278383255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1126174926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0387077331543</t>
   </si>
   <si>
     <t xml:space="preserve">15.7800207138062</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">15.7061071395874</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6321973800659</t>
+    <t xml:space="preserve">15.6321954727173</t>
   </si>
   <si>
     <t xml:space="preserve">15.5213289260864</t>
@@ -2219,40 +2219,40 @@
     <t xml:space="preserve">15.4104633331299</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4474191665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2256851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2626399993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8908815383911</t>
+    <t xml:space="preserve">15.4474182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2256841659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.262640953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8908834457397</t>
   </si>
   <si>
     <t xml:space="preserve">14.9669981002808</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7378721237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8561315536499</t>
+    <t xml:space="preserve">14.7378711700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8561296463013</t>
   </si>
   <si>
     <t xml:space="preserve">14.4126634597778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0874538421631</t>
+    <t xml:space="preserve">14.0874547958374</t>
   </si>
   <si>
     <t xml:space="preserve">14.3091888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5161380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5309219360352</t>
+    <t xml:space="preserve">14.5161399841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5309200286865</t>
   </si>
   <si>
     <t xml:space="preserve">11.8257741928101</t>
@@ -2270,13 +2270,13 @@
     <t xml:space="preserve">9.57887744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63800621032715</t>
+    <t xml:space="preserve">9.63800716400146</t>
   </si>
   <si>
     <t xml:space="preserve">9.1649751663208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29801559448242</t>
+    <t xml:space="preserve">9.29801464080811</t>
   </si>
   <si>
     <t xml:space="preserve">9.53453063964844</t>
@@ -2288,25 +2288,25 @@
     <t xml:space="preserve">10.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7023267745972</t>
+    <t xml:space="preserve">10.7023258209229</t>
   </si>
   <si>
     <t xml:space="preserve">10.5988512039185</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9388418197632</t>
+    <t xml:space="preserve">10.9388408660889</t>
   </si>
   <si>
     <t xml:space="preserve">10.7318906784058</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9018850326538</t>
+    <t xml:space="preserve">10.9018859863281</t>
   </si>
   <si>
     <t xml:space="preserve">11.2123126983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0275363922119</t>
+    <t xml:space="preserve">11.0275354385376</t>
   </si>
   <si>
     <t xml:space="preserve">10.9905796051025</t>
@@ -2315,16 +2315,16 @@
     <t xml:space="preserve">11.012752532959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0718803405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.315788269043</t>
+    <t xml:space="preserve">11.0718812942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3157892227173</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353662490845</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6801538467407</t>
+    <t xml:space="preserve">10.6801528930664</t>
   </si>
   <si>
     <t xml:space="preserve">10.7244997024536</t>
@@ -2333,40 +2333,40 @@
     <t xml:space="preserve">10.6505889892578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5175485610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9462337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3749170303345</t>
+    <t xml:space="preserve">10.5175476074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9462327957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3749179840088</t>
   </si>
   <si>
     <t xml:space="preserve">11.2714414596558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5301313400269</t>
+    <t xml:space="preserve">11.5301322937012</t>
   </si>
   <si>
     <t xml:space="preserve">11.9735975265503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6040420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2197046279907</t>
+    <t xml:space="preserve">11.6040410995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2197036743164</t>
   </si>
   <si>
     <t xml:space="preserve">11.5153484344482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.73708152771</t>
+    <t xml:space="preserve">11.7370824813843</t>
   </si>
   <si>
     <t xml:space="preserve">12.1288108825684</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4318466186523</t>
+    <t xml:space="preserve">12.431845664978</t>
   </si>
   <si>
     <t xml:space="preserve">12.5648860931396</t>
@@ -2375,16 +2375,16 @@
     <t xml:space="preserve">12.380108833313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4392375946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4096746444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7644453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8974857330322</t>
+    <t xml:space="preserve">12.4392356872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4096736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7644462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8974866867065</t>
   </si>
   <si>
     <t xml:space="preserve">12.8235750198364</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">12.971396446228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6070308685303</t>
+    <t xml:space="preserve">13.6070337295532</t>
   </si>
   <si>
     <t xml:space="preserve">13.8065919876099</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">13.89528465271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0431098937988</t>
+    <t xml:space="preserve">14.0431070327759</t>
   </si>
   <si>
     <t xml:space="preserve">13.5331211090088</t>
@@ -2414,22 +2414,22 @@
     <t xml:space="preserve">13.0896549224854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0600910186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887752532959</t>
+    <t xml:space="preserve">13.0600891113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887742996216</t>
   </si>
   <si>
     <t xml:space="preserve">13.2966051101685</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2512521743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4521455764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1353521347046</t>
+    <t xml:space="preserve">13.2512531280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4521465301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1353511810303</t>
   </si>
   <si>
     <t xml:space="preserve">12.9962711334229</t>
@@ -2438,40 +2438,40 @@
     <t xml:space="preserve">13.1585330963135</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3980598449707</t>
+    <t xml:space="preserve">13.3980588912964</t>
   </si>
   <si>
     <t xml:space="preserve">13.2048921585083</t>
   </si>
   <si>
-    <t xml:space="preserve">13.421238899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5448665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4444189071655</t>
+    <t xml:space="preserve">13.4212408065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.544867515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4444198608398</t>
   </si>
   <si>
     <t xml:space="preserve">13.5294132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3594264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1276254653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0812644958496</t>
+    <t xml:space="preserve">13.3594274520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1276235580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0812654495239</t>
   </si>
   <si>
     <t xml:space="preserve">12.9344577789307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8108310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9576396942139</t>
+    <t xml:space="preserve">12.8108320236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9576377868652</t>
   </si>
   <si>
     <t xml:space="preserve">13.2976121902466</t>
@@ -2483,103 +2483,103 @@
     <t xml:space="preserve">13.3362464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1894397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7953777313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5944843292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7644729614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.328519821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2126197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4366912841797</t>
+    <t xml:space="preserve">13.1894378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7953767776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944852828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7644720077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3285207748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2126188278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.436692237854</t>
   </si>
   <si>
     <t xml:space="preserve">13.6453132629395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9312019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.506233215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5216875076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5371389389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8539333343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8230257034302</t>
+    <t xml:space="preserve">13.9312000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5062322616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5216865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5371408462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8539323806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8230266571045</t>
   </si>
   <si>
     <t xml:space="preserve">13.8848400115967</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0702781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6916723251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4289646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6221323013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5989532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.274432182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4675998687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7148532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5757722854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3053398132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6298589706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4753246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7921199798584</t>
+    <t xml:space="preserve">14.0702800750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843942642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6916732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4289655685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6221332550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.598952293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2744331359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4675989151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7148542404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5757732391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3053379058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6298599243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4753265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7921209335327</t>
   </si>
   <si>
     <t xml:space="preserve">13.5680456161499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4830522537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8462066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9234752655029</t>
+    <t xml:space="preserve">13.4830532073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8462057113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.92347240448</t>
   </si>
   <si>
     <t xml:space="preserve">13.9543800354004</t>
@@ -2594,58 +2594,58 @@
     <t xml:space="preserve">13.5525932312012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7380352020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0007419586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8925657272339</t>
+    <t xml:space="preserve">13.7380342483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0007410049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8925666809082</t>
   </si>
   <si>
     <t xml:space="preserve">13.9080200195312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0780067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.938928604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8616600036621</t>
+    <t xml:space="preserve">14.0780076980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9389266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8616590499878</t>
   </si>
   <si>
     <t xml:space="preserve">13.8384790420532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0239191055298</t>
+    <t xml:space="preserve">14.0239200592041</t>
   </si>
   <si>
     <t xml:space="preserve">14.0471000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.332986831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1861810684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1784543991089</t>
+    <t xml:space="preserve">14.3329877853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1861801147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1784534454346</t>
   </si>
   <si>
     <t xml:space="preserve">13.815299987793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6993989944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3130664825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2667055130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2898855209351</t>
+    <t xml:space="preserve">13.6993999481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3130645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2667064666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2898874282837</t>
   </si>
   <si>
     <t xml:space="preserve">13.3748788833618</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">13.166259765625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7766666412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.761212348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7998466491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5834999084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.490777015686</t>
+    <t xml:space="preserve">13.776665687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7612113952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7998476028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5834980010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907779693604</t>
   </si>
   <si>
     <t xml:space="preserve">13.5139598846436</t>
@@ -2678,16 +2678,16 @@
     <t xml:space="preserve">13.6375865936279</t>
   </si>
   <si>
-    <t xml:space="preserve">13.042631149292</t>
+    <t xml:space="preserve">13.0426301956177</t>
   </si>
   <si>
     <t xml:space="preserve">12.8880987167358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8262853622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8494644165039</t>
+    <t xml:space="preserve">12.8262844085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8494634628296</t>
   </si>
   <si>
     <t xml:space="preserve">12.7567453384399</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">12.5867586135864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022109985352</t>
+    <t xml:space="preserve">12.6022119522095</t>
   </si>
   <si>
     <t xml:space="preserve">12.625391960144</t>
@@ -2705,37 +2705,37 @@
     <t xml:space="preserve">12.6872053146362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031044006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9267301559448</t>
+    <t xml:space="preserve">12.8031053543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">13.1430797576904</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3207931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4135122299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4057865142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1817121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.841739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8726444244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9190044403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8571920394897</t>
+    <t xml:space="preserve">13.3207921981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4135131835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4057855606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1817111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8417387008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8726453781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9190034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8571901321411</t>
   </si>
   <si>
     <t xml:space="preserve">12.6331186294556</t>
@@ -2744,28 +2744,28 @@
     <t xml:space="preserve">12.7721996307373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7490186691284</t>
+    <t xml:space="preserve">12.7490177154541</t>
   </si>
   <si>
     <t xml:space="preserve">13.1971654891968</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0967206954956</t>
+    <t xml:space="preserve">13.096718788147</t>
   </si>
   <si>
     <t xml:space="preserve">13.34397315979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821588516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9808187484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7181100845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7258386611938</t>
+    <t xml:space="preserve">13.2821598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9808177947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.718111038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7258377075195</t>
   </si>
   <si>
     <t xml:space="preserve">12.6408452987671</t>
@@ -2786,52 +2786,52 @@
     <t xml:space="preserve">13.5603189468384</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6839456558228</t>
+    <t xml:space="preserve">13.6839447021484</t>
   </si>
   <si>
     <t xml:space="preserve">13.9621067047119</t>
   </si>
   <si>
-    <t xml:space="preserve">14.139820098877</t>
+    <t xml:space="preserve">14.1398191452026</t>
   </si>
   <si>
     <t xml:space="preserve">14.371621131897</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4102535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5570621490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5338802337646</t>
+    <t xml:space="preserve">14.4102544784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5570611953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.533881187439</t>
   </si>
   <si>
     <t xml:space="preserve">14.4025268554688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2402677536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2557210922241</t>
+    <t xml:space="preserve">14.2402667999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2557220458984</t>
   </si>
   <si>
     <t xml:space="preserve">14.3948001861572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5493354797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9588489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1211071014404</t>
+    <t xml:space="preserve">14.549334526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9588470458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1211080551147</t>
   </si>
   <si>
     <t xml:space="preserve">14.8043146133423</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6343269348145</t>
+    <t xml:space="preserve">14.6343278884888</t>
   </si>
   <si>
     <t xml:space="preserve">14.7656812667847</t>
@@ -2840,19 +2840,19 @@
     <t xml:space="preserve">14.7579545974731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6806879043579</t>
+    <t xml:space="preserve">14.6806869506836</t>
   </si>
   <si>
     <t xml:space="preserve">14.5261535644531</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6961402893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.642053604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5725145339966</t>
+    <t xml:space="preserve">14.696141242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6420545578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5725135803223</t>
   </si>
   <si>
     <t xml:space="preserve">14.6034212112427</t>
@@ -2864,19 +2864,19 @@
     <t xml:space="preserve">14.657506942749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8352222442627</t>
+    <t xml:space="preserve">14.8352212905884</t>
   </si>
   <si>
     <t xml:space="preserve">14.9974813461304</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1983757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0824737548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0283880233765</t>
+    <t xml:space="preserve">15.19837474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0824756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0283889770508</t>
   </si>
   <si>
     <t xml:space="preserve">15.0979290008545</t>
@@ -2885,55 +2885,55 @@
     <t xml:space="preserve">15.1751947402954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2061033248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747470855713</t>
+    <t xml:space="preserve">15.2061023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747480392456</t>
   </si>
   <si>
     <t xml:space="preserve">14.8506736755371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8661289215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9743022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0592937469482</t>
+    <t xml:space="preserve">14.8661279678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9743003845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0592927932739</t>
   </si>
   <si>
     <t xml:space="preserve">15.0052080154419</t>
   </si>
   <si>
-    <t xml:space="preserve">14.927939414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1520166397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4147243499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8551435470581</t>
+    <t xml:space="preserve">14.9279413223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1520137786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4147214889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8551425933838</t>
   </si>
   <si>
     <t xml:space="preserve">15.808783531189</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6233406066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7624235153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9169569015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0714893341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9787702560425</t>
+    <t xml:space="preserve">15.6233425140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7624216079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.916955947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0714912414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9787693023682</t>
   </si>
   <si>
     <t xml:space="preserve">15.8860483169556</t>
@@ -2942,49 +2942,49 @@
     <t xml:space="preserve">15.9942235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">16.179666519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.056037902832</t>
+    <t xml:space="preserve">16.1796627044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0560359954834</t>
   </si>
   <si>
     <t xml:space="preserve">16.3496494293213</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4578227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2651462554932</t>
+    <t xml:space="preserve">16.4578247070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2651443481445</t>
   </si>
   <si>
     <t xml:space="preserve">16.0564117431641</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8476800918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7834539413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8717641830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6871166229248</t>
+    <t xml:space="preserve">15.8476791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7834529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8717651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6871156692505</t>
   </si>
   <si>
     <t xml:space="preserve">15.6469745635986</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5586652755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6550025939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7673969268799</t>
+    <t xml:space="preserve">15.5586643218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6550035476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192296981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7673988342285</t>
   </si>
   <si>
     <t xml:space="preserve">16.1045818328857</t>
@@ -2993,31 +2993,31 @@
     <t xml:space="preserve">15.5988073348999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5827493667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7111988067627</t>
+    <t xml:space="preserve">15.5827484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.711199760437</t>
   </si>
   <si>
     <t xml:space="preserve">15.7272567749023</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5907773971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5104932785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.213451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2616195678711</t>
+    <t xml:space="preserve">15.5907764434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5104951858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2134523391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2616214752197</t>
   </si>
   <si>
     <t xml:space="preserve">15.4703540802002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6630306243896</t>
+    <t xml:space="preserve">15.663031578064</t>
   </si>
   <si>
     <t xml:space="preserve">15.8557081222534</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">15.7352848052979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9119033813477</t>
+    <t xml:space="preserve">15.9119052886963</t>
   </si>
   <si>
     <t xml:space="preserve">16.0162734985352</t>
@@ -3056,25 +3056,25 @@
     <t xml:space="preserve">17.0679664611816</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9074039459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5702171325684</t>
+    <t xml:space="preserve">16.9074020385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.570219039917</t>
   </si>
   <si>
     <t xml:space="preserve">16.2330322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0724678039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4096565246582</t>
+    <t xml:space="preserve">16.0724697113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4096546173096</t>
   </si>
   <si>
     <t xml:space="preserve">16.2009201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3133144378662</t>
+    <t xml:space="preserve">16.3133163452148</t>
   </si>
   <si>
     <t xml:space="preserve">16.1366958618164</t>
@@ -3083,52 +3083,52 @@
     <t xml:space="preserve">16.3293724060059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0885257720947</t>
+    <t xml:space="preserve">16.0885276794434</t>
   </si>
   <si>
     <t xml:space="preserve">16.0483837127686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9841594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2812023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2972583770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1527519226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8637361526489</t>
+    <t xml:space="preserve">15.9841604232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2812042236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2972564697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1527500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8637380599976</t>
   </si>
   <si>
     <t xml:space="preserve">15.3981008529663</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1090860366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9164094924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8040132522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9806327819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9886627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9645767211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7478170394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8923225402832</t>
+    <t xml:space="preserve">15.1090841293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.916407585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8040142059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9806318283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9886608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9645757675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7478160858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8923215866089</t>
   </si>
   <si>
     <t xml:space="preserve">14.8120412826538</t>
@@ -3137,49 +3137,49 @@
     <t xml:space="preserve">14.900351524353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8521814346313</t>
+    <t xml:space="preserve">14.8521823883057</t>
   </si>
   <si>
     <t xml:space="preserve">15.101056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6755638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7879571914673</t>
+    <t xml:space="preserve">14.6755628585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.787956237793</t>
   </si>
   <si>
     <t xml:space="preserve">15.1171140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2375354766846</t>
+    <t xml:space="preserve">15.2375373840332</t>
   </si>
   <si>
     <t xml:space="preserve">15.0930280685425</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2937326431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3900709152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0609149932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0368309020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3419027328491</t>
+    <t xml:space="preserve">15.2937316894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3900718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0609159469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.036828994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3419046401978</t>
   </si>
   <si>
     <t xml:space="preserve">15.2535915374756</t>
   </si>
   <si>
-    <t xml:space="preserve">15.197395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5345811843872</t>
+    <t xml:space="preserve">15.1973943710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5345802307129</t>
   </si>
   <si>
     <t xml:space="preserve">15.1251420974731</t>
@@ -3194,109 +3194,109 @@
     <t xml:space="preserve">14.8441534042358</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7076759338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6113357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6595039367676</t>
+    <t xml:space="preserve">14.7076740264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6113367080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6595048904419</t>
   </si>
   <si>
     <t xml:space="preserve">14.1858406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3062648773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3544330596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5792217254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3464069366455</t>
+    <t xml:space="preserve">14.306263923645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3544321060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5792245864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3464059829712</t>
   </si>
   <si>
     <t xml:space="preserve">14.3142929077148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6996459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6193618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5551385879517</t>
+    <t xml:space="preserve">14.6996479034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.61936378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5551376342773</t>
   </si>
   <si>
     <t xml:space="preserve">14.5230255126953</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5471124649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273918151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8200674057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9244375228882</t>
+    <t xml:space="preserve">14.5471105575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273927688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.820068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9244356155396</t>
   </si>
   <si>
     <t xml:space="preserve">14.5711946487427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3785161972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.225980758667</t>
+    <t xml:space="preserve">14.3785181045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2259817123413</t>
   </si>
   <si>
     <t xml:space="preserve">14.1617555618286</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493631362915</t>
+    <t xml:space="preserve">14.0493612289429</t>
   </si>
   <si>
     <t xml:space="preserve">14.1938695907593</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8326005935669</t>
+    <t xml:space="preserve">13.8325996398926</t>
   </si>
   <si>
     <t xml:space="preserve">13.7442903518677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8486566543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8085155487061</t>
+    <t xml:space="preserve">13.8486557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8085165023804</t>
   </si>
   <si>
     <t xml:space="preserve">13.5355567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5917530059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406286239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9690790176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3704881668091</t>
+    <t xml:space="preserve">13.5917539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406276702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9690780639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3704900741577</t>
   </si>
   <si>
     <t xml:space="preserve">14.3303489685059</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2179527282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8727416992188</t>
+    <t xml:space="preserve">14.2179536819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8727407455444</t>
   </si>
   <si>
     <t xml:space="preserve">13.6479511260986</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">13.5114707946777</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034427642822</t>
+    <t xml:space="preserve">13.5034437179565</t>
   </si>
   <si>
     <t xml:space="preserve">13.2465410232544</t>
@@ -3317,28 +3317,28 @@
     <t xml:space="preserve">13.415132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3187952041626</t>
+    <t xml:space="preserve">13.3187942504883</t>
   </si>
   <si>
     <t xml:space="preserve">13.4071054458618</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1100606918335</t>
+    <t xml:space="preserve">13.1100616455078</t>
   </si>
   <si>
     <t xml:space="preserve">13.0859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2224559783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5756959915161</t>
+    <t xml:space="preserve">13.2224550247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5756969451904</t>
   </si>
   <si>
     <t xml:space="preserve">13.6640090942383</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1983728408813</t>
+    <t xml:space="preserve">13.198371887207</t>
   </si>
   <si>
     <t xml:space="preserve">13.0217504501343</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">12.604284286499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0137214660645</t>
+    <t xml:space="preserve">13.0137224197388</t>
   </si>
   <si>
     <t xml:space="preserve">13.3589353561401</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">12.8210468292236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6363964080811</t>
+    <t xml:space="preserve">12.6363973617554</t>
   </si>
   <si>
     <t xml:space="preserve">12.9735813140869</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">12.9093561172485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8772439956665</t>
+    <t xml:space="preserve">12.8772449493408</t>
   </si>
   <si>
     <t xml:space="preserve">13.1421747207642</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">13.5516119003296</t>
   </si>
   <si>
-    <t xml:space="preserve">13.383020401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3910484313965</t>
+    <t xml:space="preserve">13.3830194473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3910493850708</t>
   </si>
   <si>
     <t xml:space="preserve">13.4392175674438</t>
@@ -3398,64 +3398,64 @@
     <t xml:space="preserve">13.3509063720703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7202043533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.009220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8807697296143</t>
+    <t xml:space="preserve">13.7202053070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0092210769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8807706832886</t>
   </si>
   <si>
     <t xml:space="preserve">13.5596399307251</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5997829437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4231605529785</t>
+    <t xml:space="preserve">13.5997819900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4231615066528</t>
   </si>
   <si>
     <t xml:space="preserve">13.3027381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3749914169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2304840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0297794342041</t>
+    <t xml:space="preserve">13.3749923706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2304849624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0297784805298</t>
   </si>
   <si>
     <t xml:space="preserve">13.102032661438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0940036773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9494962692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7487916946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8852701187134</t>
+    <t xml:space="preserve">13.0940055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9494972229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7487926483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8852710723877</t>
   </si>
   <si>
     <t xml:space="preserve">12.5240020751953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6444244384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7969617843628</t>
+    <t xml:space="preserve">12.6444253921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7969608306885</t>
   </si>
   <si>
     <t xml:space="preserve">12.9334411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8049898147583</t>
+    <t xml:space="preserve">12.8049907684326</t>
   </si>
   <si>
     <t xml:space="preserve">12.9254131317139</t>
@@ -3467,19 +3467,19 @@
     <t xml:space="preserve">12.9816102981567</t>
   </si>
   <si>
-    <t xml:space="preserve">13.463303565979</t>
+    <t xml:space="preserve">13.4633026123047</t>
   </si>
   <si>
     <t xml:space="preserve">13.5837249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3268232345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2063999176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2786531448364</t>
+    <t xml:space="preserve">13.3268241882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2064008712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2786540985107</t>
   </si>
   <si>
     <t xml:space="preserve">12.6845664978027</t>
@@ -3503,10 +3503,10 @@
     <t xml:space="preserve">11.74241065979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9546747207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3112764358521</t>
+    <t xml:space="preserve">11.9546737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3112773895264</t>
   </si>
   <si>
     <t xml:space="preserve">12.1075038909912</t>
@@ -3524,40 +3524,40 @@
     <t xml:space="preserve">12.2433528900146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9461841583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.98863697052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0141077041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0905227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9376935958862</t>
+    <t xml:space="preserve">11.9461832046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9886360168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0141067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.090521812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9376926422119</t>
   </si>
   <si>
     <t xml:space="preserve">11.6150531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4792041778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556182861328</t>
+    <t xml:space="preserve">11.4792051315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556192398071</t>
   </si>
   <si>
     <t xml:space="preserve">11.6659955978394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6575050354004</t>
+    <t xml:space="preserve">11.6575059890747</t>
   </si>
   <si>
     <t xml:space="preserve">11.7509021759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7339210510254</t>
+    <t xml:space="preserve">11.7339200973511</t>
   </si>
   <si>
     <t xml:space="preserve">11.8358068466187</t>
@@ -3566,46 +3566,46 @@
     <t xml:space="preserve">11.7593927383423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8867492675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9631652832031</t>
+    <t xml:space="preserve">11.8867502212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9631643295288</t>
   </si>
   <si>
     <t xml:space="preserve">11.6744871139526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5725994110107</t>
+    <t xml:space="preserve">11.5726003646851</t>
   </si>
   <si>
     <t xml:space="preserve">11.5301475524902</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5980710983276</t>
+    <t xml:space="preserve">11.598072052002</t>
   </si>
   <si>
     <t xml:space="preserve">11.5471296310425</t>
   </si>
   <si>
-    <t xml:space="preserve">11.581090927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4707136154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3688268661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.343355178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3009033203125</t>
+    <t xml:space="preserve">11.5810918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4707145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3688278198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3433561325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3009042739868</t>
   </si>
   <si>
     <t xml:space="preserve">11.2499599456787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9358110427856</t>
+    <t xml:space="preserve">10.9358100891113</t>
   </si>
   <si>
     <t xml:space="preserve">10.6386413574219</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">10.0612850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075113296509</t>
+    <t xml:space="preserve">10.3075103759766</t>
   </si>
   <si>
     <t xml:space="preserve">10.1716613769531</t>
@@ -3662,22 +3662,22 @@
     <t xml:space="preserve">9.26317405700684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53487110137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27166557312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45845794677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7471342086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90845584869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56034278869629</t>
+    <t xml:space="preserve">9.53487205505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2716646194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45845699310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74713516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90845489501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56034374237061</t>
   </si>
   <si>
     <t xml:space="preserve">9.4160041809082</t>
@@ -3686,10 +3686,10 @@
     <t xml:space="preserve">9.36506080627441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49241924285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38204288482666</t>
+    <t xml:space="preserve">9.4924201965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38204193115234</t>
   </si>
   <si>
     <t xml:space="preserve">9.08487319946289</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">9.72166347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0273237228394</t>
+    <t xml:space="preserve">10.027322769165</t>
   </si>
   <si>
     <t xml:space="preserve">10.1037368774414</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">10.8678855895996</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8339242935181</t>
+    <t xml:space="preserve">10.8339233398438</t>
   </si>
   <si>
     <t xml:space="preserve">10.774489402771</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">11.173544883728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0292053222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2584495544434</t>
+    <t xml:space="preserve">11.0292062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2584505081177</t>
   </si>
   <si>
     <t xml:space="preserve">11.2924127578735</t>
@@ -3779,13 +3779,13 @@
     <t xml:space="preserve">11.1141109466553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1650543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2414684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.419771194458</t>
+    <t xml:space="preserve">11.1650533676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2414693832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4197702407837</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858079910278</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">11.3603372573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0376968383789</t>
+    <t xml:space="preserve">11.0376958847046</t>
   </si>
   <si>
     <t xml:space="preserve">11.003734588623</t>
@@ -3827,22 +3827,22 @@
     <t xml:space="preserve">11.9716558456421</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1159954071045</t>
+    <t xml:space="preserve">12.1159944534302</t>
   </si>
   <si>
     <t xml:space="preserve">12.149956703186</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1754293441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0480699539185</t>
+    <t xml:space="preserve">12.1754283905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0480690002441</t>
   </si>
   <si>
     <t xml:space="preserve">11.9971265792847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2093906402588</t>
+    <t xml:space="preserve">12.2093915939331</t>
   </si>
   <si>
     <t xml:space="preserve">12.1329755783081</t>
@@ -3851,13 +3851,13 @@
     <t xml:space="preserve">12.2009000778198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2263708114624</t>
+    <t xml:space="preserve">12.2263717651367</t>
   </si>
   <si>
     <t xml:space="preserve">12.1414661407471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0650520324707</t>
+    <t xml:space="preserve">12.0650510787964</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056180953979</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">11.8697681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7169399261475</t>
+    <t xml:space="preserve">11.7169389724731</t>
   </si>
   <si>
     <t xml:space="preserve">11.8188257217407</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">10.5622262954712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4263772964478</t>
+    <t xml:space="preserve">10.4263782501221</t>
   </si>
   <si>
     <t xml:space="preserve">10.6556224822998</t>
@@ -3893,13 +3893,13 @@
     <t xml:space="preserve">10.8763771057129</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6895837783813</t>
+    <t xml:space="preserve">10.6895847320557</t>
   </si>
   <si>
     <t xml:space="preserve">10.9867525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914714813232</t>
+    <t xml:space="preserve">10.7914705276489</t>
   </si>
   <si>
     <t xml:space="preserve">10.8084516525269</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">10.8509044647217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6980752944946</t>
+    <t xml:space="preserve">10.6980762481689</t>
   </si>
   <si>
     <t xml:space="preserve">10.6641130447388</t>
@@ -3917,16 +3917,16 @@
     <t xml:space="preserve">10.7320375442505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7999610900879</t>
+    <t xml:space="preserve">10.7999620437622</t>
   </si>
   <si>
     <t xml:space="preserve">11.012225151062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3093938827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0886402130127</t>
+    <t xml:space="preserve">11.3093929290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0886392593384</t>
   </si>
   <si>
     <t xml:space="preserve">11.3773183822632</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">11.6320343017578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5131673812866</t>
+    <t xml:space="preserve">11.5131664276123</t>
   </si>
   <si>
     <t xml:space="preserve">11.4622230529785</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">11.6999578475952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6829767227173</t>
+    <t xml:space="preserve">11.6829776763916</t>
   </si>
   <si>
     <t xml:space="preserve">11.7678823471069</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">10.877875328064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7331991195679</t>
+    <t xml:space="preserve">10.7331981658936</t>
   </si>
   <si>
     <t xml:space="preserve">10.8326635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8869171142578</t>
+    <t xml:space="preserve">10.8869180679321</t>
   </si>
   <si>
     <t xml:space="preserve">10.8507490158081</t>
@@ -3995,22 +3995,22 @@
     <t xml:space="preserve">10.6608600616455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3082113265991</t>
+    <t xml:space="preserve">10.3082103729248</t>
   </si>
   <si>
     <t xml:space="preserve">10.1544914245605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.145450592041</t>
+    <t xml:space="preserve">10.1454496383667</t>
   </si>
   <si>
     <t xml:space="preserve">10.3262958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.353422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4167184829712</t>
+    <t xml:space="preserve">10.3534231185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4167194366455</t>
   </si>
   <si>
     <t xml:space="preserve">10.2539577484131</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">10.3805494308472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4890575408936</t>
+    <t xml:space="preserve">10.4890565872192</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">10.0098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.073112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95556259155273</t>
+    <t xml:space="preserve">10.0731115341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95556163787842</t>
   </si>
   <si>
     <t xml:space="preserve">9.8560962677002</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">9.7114200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57578563690186</t>
+    <t xml:space="preserve">9.57578659057617</t>
   </si>
   <si>
     <t xml:space="preserve">9.34068584442139</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">9.43110942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28643321990967</t>
+    <t xml:space="preserve">9.28643226623535</t>
   </si>
   <si>
     <t xml:space="preserve">9.26834774017334</t>
@@ -4073,28 +4073,28 @@
     <t xml:space="preserve">9.30451679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33164310455322</t>
+    <t xml:space="preserve">9.33164405822754</t>
   </si>
   <si>
     <t xml:space="preserve">9.52153205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72046279907227</t>
+    <t xml:space="preserve">9.72046184539795</t>
   </si>
   <si>
     <t xml:space="preserve">9.76567363739014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91034984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91939258575439</t>
+    <t xml:space="preserve">9.91035079956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91939353942871</t>
   </si>
   <si>
     <t xml:space="preserve">9.90130805969238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87418174743652</t>
+    <t xml:space="preserve">9.87418079376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.82896995544434</t>
@@ -4130,10 +4130,10 @@
     <t xml:space="preserve">9.15984058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12367153167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32260131835938</t>
+    <t xml:space="preserve">9.12367057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32260227203369</t>
   </si>
   <si>
     <t xml:space="preserve">9.20505142211914</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">9.89226531982422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84705543518066</t>
+    <t xml:space="preserve">9.84705448150635</t>
   </si>
   <si>
     <t xml:space="preserve">10.0279006958008</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">10.0369424819946</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94651889801025</t>
+    <t xml:space="preserve">9.94651985168457</t>
   </si>
   <si>
     <t xml:space="preserve">10.1906623840332</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">10.4800148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5523538589478</t>
+    <t xml:space="preserve">10.5523529052734</t>
   </si>
   <si>
     <t xml:space="preserve">10.7151145935059</t>
@@ -4187,16 +4187,16 @@
     <t xml:space="preserve">10.4980993270874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.299168586731</t>
+    <t xml:space="preserve">10.2991695404053</t>
   </si>
   <si>
     <t xml:space="preserve">10.2901268005371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1816186904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5704374313354</t>
+    <t xml:space="preserve">10.181619644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5704364776611</t>
   </si>
   <si>
     <t xml:space="preserve">10.7603254318237</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">11.0768060684204</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2124395370483</t>
+    <t xml:space="preserve">11.2124404907227</t>
   </si>
   <si>
     <t xml:space="preserve">11.5560474395752</t>
@@ -4223,19 +4223,19 @@
     <t xml:space="preserve">11.2486085891724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6464710235596</t>
+    <t xml:space="preserve">11.6464700698853</t>
   </si>
   <si>
     <t xml:space="preserve">11.5289211273193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7188081741333</t>
+    <t xml:space="preserve">11.7188091278076</t>
   </si>
   <si>
     <t xml:space="preserve">11.9448661804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9629497528076</t>
+    <t xml:space="preserve">11.9629507064819</t>
   </si>
   <si>
     <t xml:space="preserve">11.9086971282959</t>
@@ -4250,10 +4250,10 @@
     <t xml:space="preserve">12.4783611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5054883956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1528387069702</t>
+    <t xml:space="preserve">12.5054874420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1528377532959</t>
   </si>
   <si>
     <t xml:space="preserve">12.3155994415283</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">12.1709232330322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1799659729004</t>
+    <t xml:space="preserve">12.1799650192261</t>
   </si>
   <si>
     <t xml:space="preserve">12.107626914978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2161340713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2703886032104</t>
+    <t xml:space="preserve">12.2161350250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2703876495361</t>
   </si>
   <si>
     <t xml:space="preserve">12.4874038696289</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">12.650164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4693183898926</t>
+    <t xml:space="preserve">12.4693193435669</t>
   </si>
   <si>
     <t xml:space="preserve">12.595911026001</t>
@@ -4316,16 +4316,16 @@
     <t xml:space="preserve">12.8852643966675</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0751514434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932369232178</t>
+    <t xml:space="preserve">13.0751523971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932359695435</t>
   </si>
   <si>
     <t xml:space="preserve">13.0028142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2198286056519</t>
+    <t xml:space="preserve">13.2198295593262</t>
   </si>
   <si>
     <t xml:space="preserve">12.9304752349854</t>
@@ -4346,16 +4346,16 @@
     <t xml:space="preserve">12.6772918701172</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2613468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5506992340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5778255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4602756500244</t>
+    <t xml:space="preserve">12.2613458633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5507001876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.577826499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4602766036987</t>
   </si>
   <si>
     <t xml:space="preserve">12.3517684936523</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">12.4060230255127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3608121871948</t>
+    <t xml:space="preserve">12.3608112335205</t>
   </si>
   <si>
     <t xml:space="preserve">12.4241065979004</t>
@@ -4391,19 +4391,19 @@
     <t xml:space="preserve">13.5091819763184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2144813537598</t>
+    <t xml:space="preserve">14.2144804000854</t>
   </si>
   <si>
     <t xml:space="preserve">14.1963958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0788459777832</t>
+    <t xml:space="preserve">14.0788469314575</t>
   </si>
   <si>
     <t xml:space="preserve">13.8980007171631</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9793815612793</t>
+    <t xml:space="preserve">13.979380607605</t>
   </si>
   <si>
     <t xml:space="preserve">14.0065078735352</t>
@@ -4424,16 +4424,16 @@
     <t xml:space="preserve">14.6485109329224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8474407196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5671310424805</t>
+    <t xml:space="preserve">14.8474416732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5671300888062</t>
   </si>
   <si>
     <t xml:space="preserve">14.6846799850464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8022308349609</t>
+    <t xml:space="preserve">14.8022298812866</t>
   </si>
   <si>
     <t xml:space="preserve">14.7389326095581</t>
@@ -4448,10 +4448,10 @@
     <t xml:space="preserve">14.1511840820312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1873540878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3049039840698</t>
+    <t xml:space="preserve">14.1873531341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3049030303955</t>
   </si>
   <si>
     <t xml:space="preserve">13.9341697692871</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">14.1421422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.295862197876</t>
+    <t xml:space="preserve">14.2958612442017</t>
   </si>
   <si>
     <t xml:space="preserve">14.4495801925659</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">14.5490455627441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8745679855347</t>
+    <t xml:space="preserve">14.874568939209</t>
   </si>
   <si>
     <t xml:space="preserve">14.7208499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">14.612340927124</t>
+    <t xml:space="preserve">14.6123418807983</t>
   </si>
   <si>
     <t xml:space="preserve">14.6304264068604</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">14.9649896621704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6575527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8926525115967</t>
+    <t xml:space="preserve">14.6575517654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8926515579224</t>
   </si>
   <si>
     <t xml:space="preserve">14.9740324020386</t>
@@ -4514,13 +4514,13 @@
     <t xml:space="preserve">15.082540512085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4713592529297</t>
+    <t xml:space="preserve">15.471360206604</t>
   </si>
   <si>
     <t xml:space="preserve">15.191047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2633848190308</t>
+    <t xml:space="preserve">15.2633857727051</t>
   </si>
   <si>
     <t xml:space="preserve">15.1458368301392</t>
@@ -4532,16 +4532,16 @@
     <t xml:space="preserve">15.2995548248291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2000894546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3718948364258</t>
+    <t xml:space="preserve">15.2000904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3718938827515</t>
   </si>
   <si>
     <t xml:space="preserve">15.7245426177979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5527391433716</t>
+    <t xml:space="preserve">15.5527410507202</t>
   </si>
   <si>
     <t xml:space="preserve">15.6974172592163</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">15.4171047210693</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2905120849609</t>
+    <t xml:space="preserve">15.2905130386353</t>
   </si>
   <si>
     <t xml:space="preserve">15.0011596679688</t>
@@ -4568,54 +4568,57 @@
     <t xml:space="preserve">14.5128755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6665945053101</t>
+    <t xml:space="preserve">14.6665954589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8112707138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5054912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4672689437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3812675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4577121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4386005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5246019363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2952661514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4099340438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6392698287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7826051712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5150461196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.687047958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1361646652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2890548706055</t>
   </si>
   <si>
     <t xml:space="preserve">14.8112716674805</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5054912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4672689437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3812675476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4577121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4386005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5246019363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2952661514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4099340438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6392698287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7826051712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5150461196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.687047958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1361646652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2890548706055</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.8017158508301</t>
   </si>
   <si>
@@ -5466,6 +5469,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.8400001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6599998474121</t>
   </si>
 </sst>
 </file>
@@ -62294,7 +62300,7 @@
         <v>15.5</v>
       </c>
       <c r="G2173" t="s">
-        <v>1519</v>
+        <v>1534</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62320,7 +62326,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G2174" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62346,7 +62352,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G2175" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62372,7 +62378,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62398,7 +62404,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G2177" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62424,7 +62430,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G2178" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62450,7 +62456,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G2179" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62476,7 +62482,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G2180" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62502,7 +62508,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G2181" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62528,7 +62534,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G2182" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62554,7 +62560,7 @@
         <v>16.5</v>
       </c>
       <c r="G2183" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62580,7 +62586,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2184" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62606,7 +62612,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G2185" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62632,7 +62638,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G2186" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62658,7 +62664,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G2187" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62684,7 +62690,7 @@
         <v>16.25</v>
       </c>
       <c r="G2188" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62710,7 +62716,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G2189" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62736,7 +62742,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2190" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62762,7 +62768,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2191" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62788,7 +62794,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2192" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62814,7 +62820,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G2193" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62840,7 +62846,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G2194" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62866,7 +62872,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G2195" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62892,7 +62898,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G2196" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62918,7 +62924,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2197" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62944,7 +62950,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2198" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62970,7 +62976,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G2199" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62996,7 +63002,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2200" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -63022,7 +63028,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G2201" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -63048,7 +63054,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G2202" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63074,7 +63080,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2203" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63100,7 +63106,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2204" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63126,7 +63132,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G2205" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63152,7 +63158,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2206" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63178,7 +63184,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G2207" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63204,7 +63210,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2208" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63230,7 +63236,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G2209" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63256,7 +63262,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2210" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63282,7 +63288,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2211" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63308,7 +63314,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G2212" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63334,7 +63340,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2213" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63360,7 +63366,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2214" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63386,7 +63392,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2215" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63412,7 +63418,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2216" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63438,7 +63444,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G2217" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63464,7 +63470,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G2218" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63490,7 +63496,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G2219" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63516,7 +63522,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2220" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63542,7 +63548,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2221" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63568,7 +63574,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G2222" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63594,7 +63600,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G2223" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63620,7 +63626,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2224" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63646,7 +63652,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G2225" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63672,7 +63678,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G2226" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63698,7 +63704,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G2227" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63724,7 +63730,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G2228" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63750,7 +63756,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2229" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63776,7 +63782,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G2230" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63802,7 +63808,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G2231" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63828,7 +63834,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2232" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63854,7 +63860,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G2233" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63880,7 +63886,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2234" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63906,7 +63912,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G2235" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63932,7 +63938,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G2236" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63958,7 +63964,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G2237" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63984,7 +63990,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2238" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -64010,7 +64016,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G2239" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -64036,7 +64042,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2240" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64062,7 +64068,7 @@
         <v>17.75</v>
       </c>
       <c r="G2241" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64088,7 +64094,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2242" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64114,7 +64120,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2243" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64140,7 +64146,7 @@
         <v>18.5</v>
       </c>
       <c r="G2244" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64166,7 +64172,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G2245" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64192,7 +64198,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2246" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64218,7 +64224,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2247" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64244,7 +64250,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2248" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64270,7 +64276,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64296,7 +64302,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2250" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64322,7 +64328,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2251" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64348,7 +64354,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G2252" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64374,7 +64380,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G2253" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64400,7 +64406,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G2254" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64426,7 +64432,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G2255" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64452,7 +64458,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G2256" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64478,7 +64484,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2257" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64504,7 +64510,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G2258" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64530,7 +64536,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2259" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64556,7 +64562,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G2260" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64582,7 +64588,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2261" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64608,7 +64614,7 @@
         <v>17</v>
       </c>
       <c r="G2262" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64634,7 +64640,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64660,7 +64666,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G2264" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64686,7 +64692,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G2265" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64712,7 +64718,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2266" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64738,7 +64744,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G2267" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64764,7 +64770,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2268" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64790,7 +64796,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2269" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64816,7 +64822,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G2270" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64842,7 +64848,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G2271" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64868,7 +64874,7 @@
         <v>18</v>
       </c>
       <c r="G2272" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64894,7 +64900,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G2273" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64920,7 +64926,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G2274" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64946,7 +64952,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G2275" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64972,7 +64978,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G2276" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64998,7 +65004,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G2277" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -65024,7 +65030,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2278" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -65050,7 +65056,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2279" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65076,7 +65082,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G2280" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65102,7 +65108,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G2281" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65128,7 +65134,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G2282" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65154,7 +65160,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2283" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65180,7 +65186,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2284" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65206,7 +65212,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G2285" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65232,7 +65238,7 @@
         <v>18.25</v>
       </c>
       <c r="G2286" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65258,7 +65264,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G2287" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65284,7 +65290,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2288" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65310,7 +65316,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G2289" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65336,7 +65342,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G2290" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65362,7 +65368,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G2291" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65388,7 +65394,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G2292" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65414,7 +65420,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G2293" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65440,7 +65446,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2294" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65466,7 +65472,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G2295" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65492,7 +65498,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G2296" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65518,7 +65524,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G2297" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65544,7 +65550,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2298" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65570,7 +65576,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G2299" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65596,7 +65602,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2300" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65622,7 +65628,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G2301" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65648,7 +65654,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2302" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65674,7 +65680,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G2303" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65700,7 +65706,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G2304" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65726,7 +65732,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G2305" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65752,7 +65758,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G2306" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65778,7 +65784,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65804,7 +65810,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G2308" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65830,7 +65836,7 @@
         <v>18.25</v>
       </c>
       <c r="G2309" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65856,7 +65862,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G2310" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65882,7 +65888,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G2311" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65908,7 +65914,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2312" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65934,7 +65940,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G2313" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65960,7 +65966,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2314" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65986,7 +65992,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G2315" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -66012,7 +66018,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2316" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -66038,7 +66044,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2317" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66064,7 +66070,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G2318" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66090,7 +66096,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G2319" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66116,7 +66122,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G2320" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66142,7 +66148,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G2321" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66168,7 +66174,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G2322" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66194,7 +66200,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2323" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66220,7 +66226,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2324" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66246,7 +66252,7 @@
         <v>17.25</v>
       </c>
       <c r="G2325" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66272,7 +66278,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G2326" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66298,7 +66304,7 @@
         <v>17.25</v>
       </c>
       <c r="G2327" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66324,7 +66330,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66350,7 +66356,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G2329" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66376,7 +66382,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G2330" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66402,7 +66408,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G2331" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66428,7 +66434,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G2332" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66454,7 +66460,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G2333" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66480,7 +66486,7 @@
         <v>17</v>
       </c>
       <c r="G2334" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66506,7 +66512,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66532,7 +66538,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G2336" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66558,7 +66564,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G2337" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66584,7 +66590,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2338" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66610,7 +66616,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2339" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66636,7 +66642,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G2340" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66662,7 +66668,7 @@
         <v>17.75</v>
       </c>
       <c r="G2341" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66688,7 +66694,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G2342" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66714,7 +66720,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G2343" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66740,7 +66746,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G2344" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66766,7 +66772,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2345" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66792,7 +66798,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G2346" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66818,7 +66824,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66844,7 +66850,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G2348" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66870,7 +66876,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G2349" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66896,7 +66902,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G2350" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66922,7 +66928,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66948,7 +66954,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2352" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66974,7 +66980,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G2353" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67000,7 +67006,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G2354" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67026,7 +67032,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G2355" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67052,7 +67058,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G2356" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67078,7 +67084,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G2357" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67104,7 +67110,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2358" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67130,7 +67136,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G2359" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67156,7 +67162,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G2360" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67182,7 +67188,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G2361" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67208,7 +67214,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G2362" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67234,7 +67240,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G2363" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67260,7 +67266,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G2364" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67286,7 +67292,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2365" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67312,7 +67318,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2366" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67338,7 +67344,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G2367" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67364,7 +67370,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G2368" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67390,7 +67396,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G2369" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67416,7 +67422,7 @@
         <v>20</v>
       </c>
       <c r="G2370" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67442,7 +67448,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2371" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67468,7 +67474,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2372" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67494,7 +67500,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G2373" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67520,7 +67526,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2374" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67546,7 +67552,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G2375" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67572,7 +67578,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G2376" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67598,7 +67604,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67624,7 +67630,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G2378" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67650,7 +67656,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G2379" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67676,7 +67682,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2380" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67702,7 +67708,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2381" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67728,7 +67734,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G2382" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67754,7 +67760,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G2383" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67780,7 +67786,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2384" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67806,7 +67812,7 @@
         <v>21.5</v>
       </c>
       <c r="G2385" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67832,7 +67838,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G2386" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67858,7 +67864,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G2387" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67884,7 +67890,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G2388" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67910,7 +67916,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G2389" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67936,7 +67942,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67962,7 +67968,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G2391" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67988,7 +67994,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G2392" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68014,7 +68020,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G2393" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68040,7 +68046,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G2394" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68066,7 +68072,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2395" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68092,7 +68098,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2396" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68118,7 +68124,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2397" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68144,7 +68150,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G2398" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68170,7 +68176,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G2399" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68196,7 +68202,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G2400" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68222,7 +68228,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G2401" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68248,7 +68254,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G2402" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68274,7 +68280,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2403" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68300,7 +68306,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2404" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68326,7 +68332,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G2405" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68352,7 +68358,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2406" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68378,7 +68384,7 @@
         <v>21.5</v>
       </c>
       <c r="G2407" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68404,7 +68410,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G2408" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68430,7 +68436,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G2409" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68456,7 +68462,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G2410" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68482,7 +68488,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G2411" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68508,7 +68514,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2412" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68534,7 +68540,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2413" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68560,7 +68566,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2414" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68586,7 +68592,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2415" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68612,7 +68618,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2416" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68638,7 +68644,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68664,7 +68670,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2418" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68690,7 +68696,7 @@
         <v>19.75</v>
       </c>
       <c r="G2419" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68716,7 +68722,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G2420" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68742,7 +68748,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G2421" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68768,7 +68774,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G2422" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68794,7 +68800,7 @@
         <v>19.25</v>
       </c>
       <c r="G2423" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68820,7 +68826,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G2424" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68846,7 +68852,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G2425" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68872,7 +68878,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G2426" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68898,7 +68904,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G2427" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68924,7 +68930,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2428" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68950,7 +68956,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G2429" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68976,7 +68982,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G2430" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69002,7 +69008,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69028,7 +69034,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G2432" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69054,7 +69060,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G2433" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69080,7 +69086,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2434" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69106,7 +69112,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G2435" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69132,7 +69138,7 @@
         <v>19.75</v>
       </c>
       <c r="G2436" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69158,7 +69164,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G2437" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69184,7 +69190,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G2438" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69210,7 +69216,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G2439" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69236,7 +69242,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G2440" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69262,7 +69268,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69288,7 +69294,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G2442" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69314,7 +69320,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2443" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69340,7 +69346,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G2444" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69366,7 +69372,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G2445" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69392,7 +69398,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G2446" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69418,7 +69424,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G2447" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69444,7 +69450,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G2448" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69470,7 +69476,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G2449" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69496,7 +69502,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G2450" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69522,7 +69528,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G2451" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69548,7 +69554,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G2452" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69574,7 +69580,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G2453" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69600,7 +69606,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G2454" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69626,7 +69632,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G2455" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -69652,7 +69658,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G2456" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69678,7 +69684,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G2457" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -69704,7 +69710,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G2458" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69730,7 +69736,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G2459" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69756,7 +69762,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G2460" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69782,7 +69788,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G2461" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69808,7 +69814,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G2462" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69834,7 +69840,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69860,7 +69866,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G2464" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69886,7 +69892,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G2465" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69912,7 +69918,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G2466" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69938,7 +69944,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2467" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69964,7 +69970,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G2468" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69990,7 +69996,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70016,7 +70022,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G2470" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70042,7 +70048,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G2471" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70068,7 +70074,7 @@
         <v>19.25</v>
       </c>
       <c r="G2472" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70094,7 +70100,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70120,7 +70126,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G2474" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70146,7 +70152,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G2475" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70172,7 +70178,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G2476" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70198,7 +70204,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G2477" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70224,7 +70230,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G2478" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70250,7 +70256,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G2479" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70276,7 +70282,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G2480" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70302,7 +70308,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70328,7 +70334,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G2482" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70354,7 +70360,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2483" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70380,7 +70386,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G2484" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70406,7 +70412,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2485" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70432,7 +70438,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2486" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70458,7 +70464,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2487" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70484,7 +70490,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G2488" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70510,7 +70516,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G2489" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70536,7 +70542,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G2490" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70562,7 +70568,7 @@
         <v>20.5</v>
       </c>
       <c r="G2491" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70588,7 +70594,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G2492" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -70614,7 +70620,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G2493" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -70640,7 +70646,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G2494" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -70666,7 +70672,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G2495" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -70692,7 +70698,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2496" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -70718,7 +70724,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2497" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -70744,7 +70750,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G2498" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -70770,7 +70776,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G2499" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -70796,7 +70802,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G2500" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -70822,7 +70828,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2501" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -70848,7 +70854,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G2502" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -70874,7 +70880,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G2503" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -70900,7 +70906,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2504" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -70926,7 +70932,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G2505" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -70952,7 +70958,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G2506" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -70978,7 +70984,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G2507" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -71004,7 +71010,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2508" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -71030,7 +71036,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G2509" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -71056,7 +71062,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G2510" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -71082,7 +71088,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G2511" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -71108,7 +71114,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2512" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -71134,7 +71140,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2513" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -71160,7 +71166,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G2514" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -71186,7 +71192,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2515" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -71212,7 +71218,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G2516" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -71238,7 +71244,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2517" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -71264,7 +71270,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2518" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -71290,7 +71296,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G2519" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -71316,7 +71322,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G2520" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -71342,7 +71348,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2521" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -71368,7 +71374,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G2522" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -71394,7 +71400,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G2523" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -71420,7 +71426,7 @@
         <v>22.6200008392334</v>
       </c>
       <c r="G2524" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -71446,7 +71452,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G2525" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -71472,7 +71478,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2526" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -71498,7 +71504,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2527" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -71524,7 +71530,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G2528" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -71550,7 +71556,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G2529" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -71576,7 +71582,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2530" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -71602,7 +71608,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G2531" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -71628,7 +71634,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G2532" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -71654,7 +71660,7 @@
         <v>22</v>
       </c>
       <c r="G2533" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -71662,7 +71668,7 @@
     </row>
     <row r="2534">
       <c r="A2534" s="1" t="n">
-        <v>46007.6910416667</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2534" t="n">
         <v>83216</v>
@@ -71680,9 +71686,35 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G2534" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.6912268518</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>58843</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>22.0799999237061</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>21.6599998474121</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>21.6599998474121</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>1819</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ACE.MI.xlsx
+++ b/data/ACE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="1821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1822" uniqueCount="1822">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,49 +44,49 @@
     <t xml:space="preserve">ACE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.611008644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3010368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43742370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48082160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61720943450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80319118499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68540096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30723571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35063171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20804405212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91667127609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97246646881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13985157012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15224933624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2762393951416</t>
+    <t xml:space="preserve">8.61100769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30103492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43742275238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48081970214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61720752716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80319023132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68540191650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30723667144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3506326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20804500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91667222976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97246551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13985252380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15225028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27623844146729</t>
   </si>
   <si>
     <t xml:space="preserve">8.3878288269043</t>
@@ -95,103 +95,103 @@
     <t xml:space="preserve">8.49321937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50561904907227</t>
+    <t xml:space="preserve">8.50561714172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.39402770996094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36922931671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33203220367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99106550216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5943021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45791292190552</t>
+    <t xml:space="preserve">8.36923027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33203506469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99106597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59430122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45791482925415</t>
   </si>
   <si>
     <t xml:space="preserve">7.31532764434814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46411371231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66869592666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63149833679199</t>
+    <t xml:space="preserve">7.46411466598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66869401931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63149785995483</t>
   </si>
   <si>
     <t xml:space="preserve">7.65629577636719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65009737014771</t>
+    <t xml:space="preserve">7.65009641647339</t>
   </si>
   <si>
     <t xml:space="preserve">7.44551563262939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60050058364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6810941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55090475082397</t>
+    <t xml:space="preserve">7.600501537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68109226226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55090713500977</t>
   </si>
   <si>
     <t xml:space="preserve">7.68729305267334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60670042037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73688793182373</t>
+    <t xml:space="preserve">7.60670232772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73688745498657</t>
   </si>
   <si>
     <t xml:space="preserve">7.64389753341675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57570314407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53230714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01586437225342</t>
+    <t xml:space="preserve">7.57570362091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53230667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01586246490479</t>
   </si>
   <si>
     <t xml:space="preserve">8.38162899017334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67920207977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77219295501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76599407196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83418655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78459167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46842193603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41882610321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33823204040527</t>
+    <t xml:space="preserve">8.67920303344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77219390869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76599311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83418560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.784592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46842098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41882514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33823299407959</t>
   </si>
   <si>
     <t xml:space="preserve">8.45602321624756</t>
@@ -200,46 +200,46 @@
     <t xml:space="preserve">8.49941825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58621215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43122577667236</t>
+    <t xml:space="preserve">8.58621025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43122482299805</t>
   </si>
   <si>
     <t xml:space="preserve">8.40642738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34443187713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47462177276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24524307250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90427350997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87327575683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73068952560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79268407821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85467767715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89807319641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96006774902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04685974121094</t>
+    <t xml:space="preserve">8.34443283081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4746208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24524211883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90427303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8732762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73068904876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79268360137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8546781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89807367324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9600682258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04686069488525</t>
   </si>
   <si>
     <t xml:space="preserve">7.99726486206055</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">7.96626710891724</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86707639694214</t>
+    <t xml:space="preserve">7.86707735061646</t>
   </si>
   <si>
     <t xml:space="preserve">7.78028440475464</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">8.09025764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11505508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1770486831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02206134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88567543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82987928390503</t>
+    <t xml:space="preserve">8.1150541305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17704772949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02206230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88567447662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82988119125366</t>
   </si>
   <si>
     <t xml:space="preserve">8.04066181182861</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">8.09645557403564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19564723968506</t>
+    <t xml:space="preserve">8.19564819335938</t>
   </si>
   <si>
     <t xml:space="preserve">8.23284244537354</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">8.05925941467285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76168632507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52610731124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56330490112305</t>
+    <t xml:space="preserve">7.7616868019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52610874176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56330442428589</t>
   </si>
   <si>
     <t xml:space="preserve">7.4207181930542</t>
@@ -308,49 +308,49 @@
     <t xml:space="preserve">7.19133901596069</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85656976699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96815824508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97435855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12314605712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09073781967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05184841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14258909225464</t>
+    <t xml:space="preserve">6.85656929016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96815967559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97435808181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12314462661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09073686599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05184936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1425895690918</t>
   </si>
   <si>
     <t xml:space="preserve">7.05833005905151</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6824049949646</t>
+    <t xml:space="preserve">6.68240451812744</t>
   </si>
   <si>
     <t xml:space="preserve">6.37777519226074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49444150924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61110877990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08425569534302</t>
+    <t xml:space="preserve">6.49444198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61110782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08425664901733</t>
   </si>
   <si>
     <t xml:space="preserve">6.99999666213989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03888559341431</t>
+    <t xml:space="preserve">7.03888607025146</t>
   </si>
   <si>
     <t xml:space="preserve">6.93518257141113</t>
@@ -359,88 +359,88 @@
     <t xml:space="preserve">6.78610849380493</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75370025634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82499647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86388635635376</t>
+    <t xml:space="preserve">6.75370073318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82499742507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86388683319092</t>
   </si>
   <si>
     <t xml:space="preserve">6.74073791503906</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91573762893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89629316329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15555238723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907169342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58333158493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55740356445312</t>
+    <t xml:space="preserve">6.91573715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92870092391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89629364013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15555334091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907121658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5833306312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55740404129028</t>
   </si>
   <si>
     <t xml:space="preserve">8.0694408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04351615905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01110744476318</t>
+    <t xml:space="preserve">8.0435152053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0111083984375</t>
   </si>
   <si>
     <t xml:space="preserve">8.16666412353516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17962455749512</t>
+    <t xml:space="preserve">8.17962551116943</t>
   </si>
   <si>
     <t xml:space="preserve">8.0759220123291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05647850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10184955596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95277404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82962656021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87499666213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90740394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481199264526</t>
+    <t xml:space="preserve">8.05647945404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10184764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9527759552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82962608337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87499570846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90740346908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481151580811</t>
   </si>
   <si>
     <t xml:space="preserve">7.75833034515381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74536657333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7712926864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71944093704224</t>
+    <t xml:space="preserve">7.7453670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77129173278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71943998336792</t>
   </si>
   <si>
     <t xml:space="preserve">7.57684803009033</t>
@@ -449,52 +449,52 @@
     <t xml:space="preserve">7.65462636947632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70647811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81666469573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79073667526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69351434707642</t>
+    <t xml:space="preserve">7.70647859573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81666374206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79073810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69351530075073</t>
   </si>
   <si>
     <t xml:space="preserve">7.72592258453369</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69999551773071</t>
+    <t xml:space="preserve">7.69999647140503</t>
   </si>
   <si>
     <t xml:space="preserve">7.50555229187012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37592267990112</t>
+    <t xml:space="preserve">7.37592124938965</t>
   </si>
   <si>
     <t xml:space="preserve">7.39536809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32407093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25277328491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22684812545776</t>
+    <t xml:space="preserve">7.47314357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32407140731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25277423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22684860229492</t>
   </si>
   <si>
     <t xml:space="preserve">7.18147897720337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20092344284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22036647796631</t>
+    <t xml:space="preserve">7.20092296600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22036695480347</t>
   </si>
   <si>
     <t xml:space="preserve">7.18796110153198</t>
@@ -503,46 +503,46 @@
     <t xml:space="preserve">7.1685152053833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16203498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19444227218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17499589920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07129335403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96758890151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0453667640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98703384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23332977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34999752044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41481113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55092287063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52499675750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64166450500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5962929725647</t>
+    <t xml:space="preserve">7.162034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19444179534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17499685287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07129192352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96758985519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04536771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9870343208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23333024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3499960899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41481161117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55092239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52499580383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64166355133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59629392623901</t>
   </si>
   <si>
     <t xml:space="preserve">7.6157374382019</t>
@@ -554,37 +554,37 @@
     <t xml:space="preserve">7.49258947372437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38888549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46018171310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36944055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30462741851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84444093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57221984863281</t>
+    <t xml:space="preserve">7.38888454437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46018075942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36944150924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30462646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84444141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57221937179565</t>
   </si>
   <si>
     <t xml:space="preserve">6.59166431427002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54629421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48147821426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43610811233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47823762893677</t>
+    <t xml:space="preserve">6.54629325866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48147916793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43610858917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47823858261108</t>
   </si>
   <si>
     <t xml:space="preserve">6.52684879302979</t>
@@ -593,82 +593,82 @@
     <t xml:space="preserve">6.64999723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53332996368408</t>
+    <t xml:space="preserve">6.5333309173584</t>
   </si>
   <si>
     <t xml:space="preserve">6.59814500808716</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52036714553833</t>
+    <t xml:space="preserve">6.52036809921265</t>
   </si>
   <si>
     <t xml:space="preserve">6.42962646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8703670501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10370063781738</t>
+    <t xml:space="preserve">6.87036752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10370111465454</t>
   </si>
   <si>
     <t xml:space="preserve">7.25925588607788</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48610782623291</t>
+    <t xml:space="preserve">7.48610877990723</t>
   </si>
   <si>
     <t xml:space="preserve">7.43425607681274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42777490615845</t>
+    <t xml:space="preserve">7.42777442932129</t>
   </si>
   <si>
     <t xml:space="preserve">7.38240528106689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51851463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51203346252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66758918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68055248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71295833587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8944411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79721832275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84259033203125</t>
+    <t xml:space="preserve">7.51851558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51203393936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6675877571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68055200576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71295976638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89444208145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79721927642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84259080886841</t>
   </si>
   <si>
     <t xml:space="preserve">7.34351491928101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40184879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46666288375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40832948684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73888540267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68703365325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62221956253052</t>
+    <t xml:space="preserve">7.40184831619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46666383743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40833044052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73888492584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68703317642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62221908569336</t>
   </si>
   <si>
     <t xml:space="preserve">7.63518190383911</t>
@@ -680,55 +680,55 @@
     <t xml:space="preserve">7.7777738571167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83610868453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75184726715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62870168685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97221994400024</t>
+    <t xml:space="preserve">7.83610773086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7518482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62870073318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9722204208374</t>
   </si>
   <si>
     <t xml:space="preserve">7.85555124282837</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92684841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.037034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09536552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13425636291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20555210113525</t>
+    <t xml:space="preserve">7.92684888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03703308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09536647796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13425540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20555114746094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28981113433838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24444007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147678375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22499656677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27036571502686</t>
+    <t xml:space="preserve">8.24444103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147773742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22499752044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27036762237549</t>
   </si>
   <si>
     <t xml:space="preserve">8.46481132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45833110809326</t>
+    <t xml:space="preserve">8.45833015441895</t>
   </si>
   <si>
     <t xml:space="preserve">8.43240356445312</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">8.55555152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52314472198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39351558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47129154205322</t>
+    <t xml:space="preserve">8.52314376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39351463317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47129249572754</t>
   </si>
   <si>
     <t xml:space="preserve">8.60740375518799</t>
@@ -764,94 +764,94 @@
     <t xml:space="preserve">8.56203269958496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80832958221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81481170654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84073829650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9249963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12592220306396</t>
+    <t xml:space="preserve">8.80832862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6786994934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81481075286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84073734283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92499732971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12592315673828</t>
   </si>
   <si>
     <t xml:space="preserve">9.17777347564697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00277423858643</t>
+    <t xml:space="preserve">9.00277328491211</t>
   </si>
   <si>
     <t xml:space="preserve">8.9509220123291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99629306793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18425464630127</t>
+    <t xml:space="preserve">8.99629211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18425559997559</t>
   </si>
   <si>
     <t xml:space="preserve">9.01573753356934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02870082855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20370006561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2814769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30740261077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34629154205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43703460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32684803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43055248260498</t>
+    <t xml:space="preserve">9.02869892120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20369911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28147792816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30740356445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34629249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43703365325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32684898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43055152893066</t>
   </si>
   <si>
     <t xml:space="preserve">9.38518047332764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41758918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33332824707031</t>
+    <t xml:space="preserve">9.41758728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33333015441895</t>
   </si>
   <si>
     <t xml:space="preserve">9.50184726715088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50833034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44351482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54721832275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41110706329346</t>
+    <t xml:space="preserve">9.50832939147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44351387023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54721736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41110515594482</t>
   </si>
   <si>
     <t xml:space="preserve">9.35925483703613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51501655578613</t>
+    <t xml:space="preserve">9.51501750946045</t>
   </si>
   <si>
     <t xml:space="preserve">9.41343307495117</t>
@@ -863,19 +863,19 @@
     <t xml:space="preserve">9.50147247314453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44729328155518</t>
+    <t xml:space="preserve">9.44729423522949</t>
   </si>
   <si>
     <t xml:space="preserve">9.48115634918213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21026611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09513664245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14931488037109</t>
+    <t xml:space="preserve">9.21026515960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09513759613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14931583404541</t>
   </si>
   <si>
     <t xml:space="preserve">8.98678207397461</t>
@@ -884,16 +884,16 @@
     <t xml:space="preserve">8.83101940155029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84456443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93937587738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81070232391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93260097503662</t>
+    <t xml:space="preserve">8.84456348419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93937492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81070327758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93260383605957</t>
   </si>
   <si>
     <t xml:space="preserve">9.04095840454102</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">9.08159160614014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10190963745117</t>
+    <t xml:space="preserve">9.10190773010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349216461182</t>
@@ -917,40 +917,40 @@
     <t xml:space="preserve">9.10868072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12222766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00709915161133</t>
+    <t xml:space="preserve">9.12222576141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0070972442627</t>
   </si>
   <si>
     <t xml:space="preserve">9.07482051849365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87842464447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92583084106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90551280975342</t>
+    <t xml:space="preserve">8.8784236907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92583179473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90551376342773</t>
   </si>
   <si>
     <t xml:space="preserve">8.52626705169678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58721828460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5465841293335</t>
+    <t xml:space="preserve">8.58721733093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54658508300781</t>
   </si>
   <si>
     <t xml:space="preserve">8.56012916564941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68880176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53981113433838</t>
+    <t xml:space="preserve">8.68880271911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5398120880127</t>
   </si>
   <si>
     <t xml:space="preserve">8.44500064849854</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">8.33664608001709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47208976745605</t>
+    <t xml:space="preserve">8.47209072113037</t>
   </si>
   <si>
     <t xml:space="preserve">8.47886276245117</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">8.41113948822021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42468357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38405132293701</t>
+    <t xml:space="preserve">8.4246826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3840503692627</t>
   </si>
   <si>
     <t xml:space="preserve">8.3908224105835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32987308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28246688842773</t>
+    <t xml:space="preserve">8.32987213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28246593475342</t>
   </si>
   <si>
     <t xml:space="preserve">8.26892185211182</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">8.37050628662109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29601192474365</t>
+    <t xml:space="preserve">8.29601097106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.39759540557861</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">8.81747531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97323513031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76329612731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67525768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68202972412109</t>
+    <t xml:space="preserve">8.97323703765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76329517364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67525863647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68202877044678</t>
   </si>
   <si>
     <t xml:space="preserve">8.69557476043701</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">8.80393028259277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85810852050781</t>
+    <t xml:space="preserve">8.8581075668335</t>
   </si>
   <si>
     <t xml:space="preserve">8.74297904968262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74975109100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79038524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88519668579102</t>
+    <t xml:space="preserve">8.74975204467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79038619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8851957321167</t>
   </si>
   <si>
     <t xml:space="preserve">8.96646499633789</t>
@@ -1049,25 +1049,25 @@
     <t xml:space="preserve">8.91228580474854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89196968078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18317699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19672012329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29153251647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24412536621094</t>
+    <t xml:space="preserve">8.89196872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1831750869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19672107696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29153347015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24412631988525</t>
   </si>
   <si>
     <t xml:space="preserve">9.36602687835693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40666103363037</t>
+    <t xml:space="preserve">9.40666198730469</t>
   </si>
   <si>
     <t xml:space="preserve">9.54210567474365</t>
@@ -1076,19 +1076,19 @@
     <t xml:space="preserve">9.46761035919189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38634395599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52178955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49470138549805</t>
+    <t xml:space="preserve">9.38634490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52178859710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49470043182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.84008598327637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86717319488525</t>
+    <t xml:space="preserve">9.86717414855957</t>
   </si>
   <si>
     <t xml:space="preserve">9.88749122619629</t>
@@ -1097,46 +1097,46 @@
     <t xml:space="preserve">9.83331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76558876037598</t>
+    <t xml:space="preserve">9.76558971405029</t>
   </si>
   <si>
     <t xml:space="preserve">9.74527359008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70464038848877</t>
+    <t xml:space="preserve">9.70463943481445</t>
   </si>
   <si>
     <t xml:space="preserve">9.58273887634277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71818542480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67077732086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96875762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94844055175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91458034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0161647796631</t>
-  </si>
-  <si>
-    <t xml:space